--- a/MASTER spreadsheet of community summaries.xlsx
+++ b/MASTER spreadsheet of community summaries.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\peri\Dropbox\Delta\Projects\Laboratory\Algal blooms, bacterial counts  for community\For Luke's HAB data display\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97BC50DD-4001-49FE-9C99-C2F7A68658FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A019CAC6-765D-4AC4-B759-8EED9510CBC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{9286397E-2757-492B-865A-39B2D6A15FF6}"/>
+    <workbookView xWindow="-28920" yWindow="1650" windowWidth="29040" windowHeight="15720" xr2:uid="{9286397E-2757-492B-865A-39B2D6A15FF6}"/>
   </bookViews>
   <sheets>
     <sheet name="Cells per mL" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1403" uniqueCount="392">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1443" uniqueCount="393">
   <si>
     <t>Date</t>
   </si>
@@ -862,9 +862,6 @@
     <t xml:space="preserve">StrawPT posedonia </t>
   </si>
   <si>
-    <t>MinOil</t>
-  </si>
-  <si>
     <t>DAHL5575</t>
   </si>
   <si>
@@ -925,9 +922,6 @@
     <t>LAMW5607</t>
   </si>
   <si>
-    <t>Second Valley beach</t>
-  </si>
-  <si>
     <t>Port Augusta Boat ramp</t>
   </si>
   <si>
@@ -1168,9 +1162,6 @@
     <t>Shoal Bay KI</t>
   </si>
   <si>
-    <t xml:space="preserve">MinOil </t>
-  </si>
-  <si>
     <t>Pt Vincent Wharf</t>
   </si>
   <si>
@@ -1207,9 +1198,6 @@
     <t>Flat Iron inshore/Waitpinga Cliffs</t>
   </si>
   <si>
-    <t>LEWK5222</t>
-  </si>
-  <si>
     <t>Pennington</t>
   </si>
   <si>
@@ -1232,17 +1220,33 @@
   </si>
   <si>
     <t>Wauraltee Beach (north of beach access)</t>
+  </si>
+  <si>
+    <t>Hardwicke Bay Reef North Shore Rd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">leSecond Valy Jetty </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Second Valley Jetty </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brown Beach </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Min Oil </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="0.0000"/>
     <numFmt numFmtId="165" formatCode="h:mm:ss;@"/>
     <numFmt numFmtId="166" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
+    <numFmt numFmtId="168" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
@@ -1313,10 +1317,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1355,8 +1360,11 @@
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1694,7 +1702,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F307807-E5C9-4450-88E0-159CBB3E9A67}">
-  <dimension ref="A1:T693"/>
+  <dimension ref="A1:T713"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="39.33203125" customWidth="1"/>
@@ -1730,7 +1738,7 @@
         <v>0</v>
       </c>
       <c r="E1" s="19" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>64</v>
@@ -14314,7 +14322,7 @@
     </row>
     <row r="357" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B357">
         <v>-35.509267000000001</v>
@@ -14343,7 +14351,7 @@
     </row>
     <row r="358" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B358">
         <v>-35.509166999999998</v>
@@ -15072,7 +15080,7 @@
     </row>
     <row r="379" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A379" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B379">
         <v>-35.6048446</v>
@@ -15107,7 +15115,7 @@
     </row>
     <row r="380" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A380" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B380">
         <v>-35.608333000000002</v>
@@ -15174,7 +15182,7 @@
     </row>
     <row r="382" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A382" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B382">
         <v>-35.63158</v>
@@ -15209,7 +15217,7 @@
     </row>
     <row r="383" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A383" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B383">
         <v>-35.61</v>
@@ -16379,7 +16387,7 @@
     </row>
     <row r="410" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A410" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B410">
         <v>-33.677014</v>
@@ -16406,7 +16414,7 @@
         <v>2556</v>
       </c>
       <c r="Q410" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="411" spans="1:17" x14ac:dyDescent="0.3">
@@ -16464,7 +16472,7 @@
     </row>
     <row r="412" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A412" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B412">
         <v>-34.765895999999998</v>
@@ -16499,7 +16507,7 @@
     </row>
     <row r="413" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A413" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B413">
         <v>-34.765996000000001</v>
@@ -17089,7 +17097,7 @@
     </row>
     <row r="429" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A429" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B429">
         <v>-35.093021</v>
@@ -17124,7 +17132,7 @@
     </row>
     <row r="430" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A430" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B430">
         <v>-35.115721999999998</v>
@@ -17421,7 +17429,7 @@
     </row>
     <row r="436" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A436" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B436">
         <v>-35.081834999999998</v>
@@ -18315,7 +18323,7 @@
     </row>
     <row r="457" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A457" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B457">
         <v>-35.242910000000002</v>
@@ -18497,7 +18505,7 @@
     </row>
     <row r="461" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A461" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B461">
         <v>-35.085709299999998</v>
@@ -18579,7 +18587,7 @@
     </row>
     <row r="463" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A463" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B463">
         <v>-32.486960000000003</v>
@@ -18603,12 +18611,12 @@
         <v>1666</v>
       </c>
       <c r="Q463" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="464" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A464" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B464">
         <v>-32.48724</v>
@@ -18632,12 +18640,12 @@
         <v>1049</v>
       </c>
       <c r="Q464" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="465" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A465" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B465">
         <v>-32.490589999999997</v>
@@ -18661,12 +18669,12 @@
         <v>1358</v>
       </c>
       <c r="Q465" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="466" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A466" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B466">
         <v>-35.579300000000003</v>
@@ -18704,7 +18712,7 @@
     </row>
     <row r="467" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A467" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B467">
         <v>-35.585419999999999</v>
@@ -18739,7 +18747,7 @@
     </row>
     <row r="468" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A468" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B468">
         <v>-35.570399999999999</v>
@@ -18871,7 +18879,7 @@
     </row>
     <row r="471" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A471" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B471">
         <v>-34.804662999999998</v>
@@ -18910,7 +18918,7 @@
     </row>
     <row r="472" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A472" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B472">
         <v>-34.824044999999998</v>
@@ -19057,7 +19065,7 @@
     </row>
     <row r="476" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A476" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B476">
         <v>-34.907184999999998</v>
@@ -19093,7 +19101,7 @@
     </row>
     <row r="477" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A477" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B477">
         <v>-35.092928999999998</v>
@@ -19129,7 +19137,7 @@
     </row>
     <row r="478" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A478" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B478">
         <v>-35.115721999999998</v>
@@ -19228,13 +19236,13 @@
         <v>0</v>
       </c>
       <c r="Q480" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="T480" s="2"/>
     </row>
     <row r="481" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A481" t="s">
-        <v>268</v>
+        <v>211</v>
       </c>
       <c r="B481">
         <v>-35.739091000000002</v>
@@ -19285,7 +19293,7 @@
     </row>
     <row r="482" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A482" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B482">
         <v>-34.827600699999998</v>
@@ -19324,7 +19332,7 @@
     </row>
     <row r="483" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A483" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B483">
         <v>-34.226579999999998</v>
@@ -19360,7 +19368,7 @@
     </row>
     <row r="484" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A484" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B484">
         <v>-34.917679100000001</v>
@@ -19405,13 +19413,13 @@
         <v>0</v>
       </c>
       <c r="Q485" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="T485" s="2"/>
     </row>
     <row r="486" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A486" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B486">
         <v>-34.970672</v>
@@ -19450,7 +19458,7 @@
     </row>
     <row r="487" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A487" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B487">
         <v>-35.011718100000003</v>
@@ -19488,7 +19496,7 @@
     </row>
     <row r="488" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A488" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B488">
         <v>-34.953057899999997</v>
@@ -19523,7 +19531,7 @@
     </row>
     <row r="489" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A489" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B489">
         <v>-34.906165799999997</v>
@@ -19561,7 +19569,7 @@
     </row>
     <row r="490" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A490" t="s">
-        <v>289</v>
+        <v>389</v>
       </c>
       <c r="B490">
         <v>-35.511031000000003</v>
@@ -19707,7 +19715,7 @@
         <v>306</v>
       </c>
       <c r="Q494" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="495" spans="1:20" x14ac:dyDescent="0.3">
@@ -19727,7 +19735,7 @@
         <v>0</v>
       </c>
       <c r="Q495" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="496" spans="1:20" x14ac:dyDescent="0.3">
@@ -19747,7 +19755,7 @@
         <v>0</v>
       </c>
       <c r="Q496" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="497" spans="1:17" x14ac:dyDescent="0.3">
@@ -19767,7 +19775,7 @@
         <v>0</v>
       </c>
       <c r="Q497" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="498" spans="1:17" x14ac:dyDescent="0.3">
@@ -19861,12 +19869,12 @@
         <v>1026</v>
       </c>
       <c r="Q499" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="500" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A500" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B500">
         <v>-35.110022000000001</v>
@@ -19919,7 +19927,7 @@
         <v>28</v>
       </c>
       <c r="Q501" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="502" spans="1:17" x14ac:dyDescent="0.3">
@@ -19939,12 +19947,12 @@
         <v>0</v>
       </c>
       <c r="Q502" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="503" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A503" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B503">
         <v>-34.630270000000003</v>
@@ -19971,12 +19979,12 @@
         <v>2889</v>
       </c>
       <c r="Q503" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="504" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A504" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B504">
         <v>-34.629179999999998</v>
@@ -20003,12 +20011,12 @@
         <v>945</v>
       </c>
       <c r="Q504" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="505" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A505" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B505">
         <v>-34.628860000000003</v>
@@ -20035,7 +20043,7 @@
         <v>723</v>
       </c>
       <c r="Q505" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="506" spans="1:17" x14ac:dyDescent="0.3">
@@ -20238,7 +20246,7 @@
     </row>
     <row r="513" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A513" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B513">
         <v>-34.630270000000003</v>
@@ -20265,12 +20273,12 @@
         <v>2889</v>
       </c>
       <c r="Q513" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="514" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A514" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B514">
         <v>-34.630270000000003</v>
@@ -20297,12 +20305,12 @@
         <v>2889</v>
       </c>
       <c r="Q514" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="515" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A515" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B515">
         <v>-35.119663000000003</v>
@@ -20408,7 +20416,7 @@
     </row>
     <row r="517" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A517" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B517">
         <v>-35.031672</v>
@@ -20461,7 +20469,7 @@
     </row>
     <row r="518" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A518" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B518">
         <v>-35.762554199999997</v>
@@ -20511,7 +20519,7 @@
     </row>
     <row r="519" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A519" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B519">
         <v>-35.511125999999997</v>
@@ -20546,7 +20554,7 @@
     </row>
     <row r="520" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A520" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B520">
         <v>-35.793973000000001</v>
@@ -20596,7 +20604,7 @@
     </row>
     <row r="521" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A521" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B521">
         <v>-35.132868999999999</v>
@@ -20631,7 +20639,7 @@
     </row>
     <row r="522" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A522" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B522">
         <v>-34.899749999999997</v>
@@ -20658,7 +20666,7 @@
         <v>194</v>
       </c>
       <c r="Q522" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="523" spans="1:17" x14ac:dyDescent="0.3">
@@ -20698,7 +20706,7 @@
     </row>
     <row r="524" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A524" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B524">
         <v>-33.040959000000001</v>
@@ -20725,12 +20733,12 @@
         <v>3335</v>
       </c>
       <c r="Q524" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="525" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A525" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B525">
         <v>-33.917679999999997</v>
@@ -20760,12 +20768,12 @@
         <v>4334</v>
       </c>
       <c r="Q525" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="526" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A526" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B526">
         <v>-33.922530000000002</v>
@@ -20795,12 +20803,12 @@
         <v>12722</v>
       </c>
       <c r="Q526" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="527" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A527" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B527">
         <v>-33.912199999999999</v>
@@ -20830,7 +20838,7 @@
         <v>2334</v>
       </c>
       <c r="Q527" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="528" spans="1:17" x14ac:dyDescent="0.3">
@@ -20853,7 +20861,7 @@
         <v>0</v>
       </c>
       <c r="Q528" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="529" spans="1:17" x14ac:dyDescent="0.3">
@@ -20876,12 +20884,12 @@
         <v>0</v>
       </c>
       <c r="Q529" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="530" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A530" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B530">
         <v>-35.594605999999999</v>
@@ -20919,7 +20927,7 @@
     </row>
     <row r="531" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A531" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B531">
         <v>-35.510753999999999</v>
@@ -21085,7 +21093,7 @@
     </row>
     <row r="536" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A536" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B536">
         <v>-35.6048446</v>
@@ -21120,7 +21128,7 @@
     </row>
     <row r="537" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A537" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B537">
         <v>-35.63158</v>
@@ -21155,7 +21163,7 @@
     </row>
     <row r="538" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A538" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B538">
         <v>-35.612963000000001</v>
@@ -21193,7 +21201,7 @@
     </row>
     <row r="539" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A539" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B539">
         <v>-34.911830000000002</v>
@@ -21217,12 +21225,12 @@
         <v>1723</v>
       </c>
       <c r="Q539" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="540" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A540" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B540">
         <v>-35.089612000000002</v>
@@ -21257,7 +21265,7 @@
     </row>
     <row r="541" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A541" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B541">
         <v>-34.994472000000002</v>
@@ -21289,7 +21297,7 @@
     </row>
     <row r="542" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A542" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B542">
         <v>-35.522570000000002</v>
@@ -21345,12 +21353,12 @@
         <v>0</v>
       </c>
       <c r="Q543" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="544" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A544" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B544">
         <v>-34.804662999999998</v>
@@ -21394,7 +21402,7 @@
     </row>
     <row r="545" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A545" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B545">
         <v>-34.824044999999998</v>
@@ -21491,7 +21499,7 @@
     </row>
     <row r="547" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A547" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B547">
         <v>-34.920539599999998</v>
@@ -21526,7 +21534,7 @@
     </row>
     <row r="548" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A548" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B548">
         <v>-35.085709299999998</v>
@@ -21558,7 +21566,7 @@
     </row>
     <row r="549" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A549" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B549">
         <v>-35.445188000000002</v>
@@ -21593,7 +21601,7 @@
     </row>
     <row r="550" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A550" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B550">
         <v>-35.516500000000001</v>
@@ -21619,7 +21627,7 @@
     </row>
     <row r="551" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A551" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B551">
         <v>-35.517899999999997</v>
@@ -21697,7 +21705,7 @@
     </row>
     <row r="554" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A554" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B554">
         <v>-35.5565</v>
@@ -21723,7 +21731,7 @@
     </row>
     <row r="555" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A555" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B555">
         <v>-35.563899999999997</v>
@@ -21775,7 +21783,7 @@
     </row>
     <row r="557" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A557" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B557">
         <v>-35.634900000000002</v>
@@ -21801,7 +21809,7 @@
     </row>
     <row r="558" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A558" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B558">
         <v>-34.929459999999999</v>
@@ -21819,12 +21827,12 @@
         <v>0</v>
       </c>
       <c r="Q558" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="559" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A559" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B559">
         <v>-34.928570000000001</v>
@@ -21842,12 +21850,12 @@
         <v>0</v>
       </c>
       <c r="Q559" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="560" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A560" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B560">
         <v>-34.901600000000002</v>
@@ -21865,12 +21873,12 @@
         <v>0</v>
       </c>
       <c r="Q560" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="561" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A561" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B561">
         <v>-34.630270000000003</v>
@@ -21903,12 +21911,12 @@
         <v>15888</v>
       </c>
       <c r="Q561" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="562" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A562" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B562">
         <v>-34.629179999999998</v>
@@ -21941,7 +21949,7 @@
         <v>23556</v>
       </c>
       <c r="Q562" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="563" spans="1:17" x14ac:dyDescent="0.3">
@@ -21990,7 +21998,7 @@
     </row>
     <row r="564" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A564" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B564">
         <v>-35.32508</v>
@@ -22020,12 +22028,12 @@
         <v>1167</v>
       </c>
       <c r="Q564" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="565" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A565" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B565">
         <v>-34.903820000000003</v>
@@ -22046,7 +22054,7 @@
         <v>722</v>
       </c>
       <c r="Q565" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="566" spans="1:17" x14ac:dyDescent="0.3">
@@ -22159,7 +22167,7 @@
     </row>
     <row r="569" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A569" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B569">
         <v>-34.911830000000002</v>
@@ -22180,12 +22188,12 @@
         <v>1611</v>
       </c>
       <c r="Q569" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="570" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A570" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B570">
         <v>-34.893770000000004</v>
@@ -22206,12 +22214,12 @@
         <v>389</v>
       </c>
       <c r="Q570" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="571" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A571" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B571" s="13">
         <f>-35.521088</f>
@@ -22251,7 +22259,7 @@
     </row>
     <row r="572" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A572" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="B572">
         <v>-34.495376</v>
@@ -22286,7 +22294,7 @@
     </row>
     <row r="573" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A573" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B573">
         <v>-34.750552999999996</v>
@@ -22318,7 +22326,7 @@
     </row>
     <row r="574" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A574" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B574">
         <v>-34.672504000000004</v>
@@ -22353,7 +22361,7 @@
     </row>
     <row r="575" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A575" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B575">
         <v>-34.588209999999997</v>
@@ -22385,7 +22393,7 @@
     </row>
     <row r="576" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A576" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B576">
         <v>-34.899749999999997</v>
@@ -22415,12 +22423,12 @@
         <v>5834</v>
       </c>
       <c r="Q576" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="577" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A577" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B577">
         <v>-34.812609999999999</v>
@@ -22438,7 +22446,7 @@
         <v>0</v>
       </c>
       <c r="Q577" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="578" spans="1:17" x14ac:dyDescent="0.3">
@@ -22461,7 +22469,7 @@
         <v>0</v>
       </c>
       <c r="Q578" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="579" spans="1:17" x14ac:dyDescent="0.3">
@@ -22484,7 +22492,7 @@
         <v>0</v>
       </c>
       <c r="Q579" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="580" spans="1:17" x14ac:dyDescent="0.3">
@@ -22533,7 +22541,7 @@
     </row>
     <row r="581" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A581" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B581">
         <v>-34.912934499999999</v>
@@ -22586,7 +22594,7 @@
         <v>0</v>
       </c>
       <c r="Q582" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="583" spans="1:17" x14ac:dyDescent="0.3">
@@ -22609,12 +22617,12 @@
         <v>0</v>
       </c>
       <c r="Q583" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="584" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A584" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B584">
         <v>-34.831850000000003</v>
@@ -22635,12 +22643,12 @@
         <v>56</v>
       </c>
       <c r="Q584" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="585" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A585" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B585">
         <v>-34.899749999999997</v>
@@ -22670,12 +22678,12 @@
         <v>6889</v>
       </c>
       <c r="Q585" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="586" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A586" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B586">
         <v>-34.920539599999998</v>
@@ -22725,7 +22733,7 @@
     </row>
     <row r="587" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A587" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B587">
         <v>-34.933680000000003</v>
@@ -22760,7 +22768,7 @@
     </row>
     <row r="588" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A588" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B588">
         <v>-34.804662999999998</v>
@@ -22813,7 +22821,7 @@
     </row>
     <row r="589" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A589" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B589">
         <v>-34.824044999999998</v>
@@ -23039,7 +23047,7 @@
     </row>
     <row r="594" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A594" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B594">
         <v>-34.628860000000003</v>
@@ -23072,12 +23080,12 @@
         <v>1279</v>
       </c>
       <c r="Q594" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="595" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A595" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B595">
         <v>-34.519669999999998</v>
@@ -23110,12 +23118,12 @@
         <v>446</v>
       </c>
       <c r="Q595" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="596" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A596" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B596">
         <v>-34.535609999999998</v>
@@ -23139,7 +23147,7 @@
         <v>222</v>
       </c>
       <c r="Q596" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="597" spans="1:17" x14ac:dyDescent="0.3">
@@ -23217,7 +23225,7 @@
     </row>
     <row r="599" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A599" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B599">
         <v>-34.890371899999998</v>
@@ -23255,7 +23263,7 @@
     </row>
     <row r="600" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A600" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B600">
         <v>-35.500242</v>
@@ -23309,7 +23317,7 @@
         <v>556</v>
       </c>
       <c r="Q601" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="602" spans="1:17" x14ac:dyDescent="0.3">
@@ -23329,12 +23337,12 @@
         <v>0</v>
       </c>
       <c r="Q602" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="603" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A603" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B603">
         <v>-34.670960000000001</v>
@@ -23349,12 +23357,12 @@
         <v>1167</v>
       </c>
       <c r="Q603" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="604" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A604" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B604">
         <v>-34.643329999999999</v>
@@ -23369,12 +23377,12 @@
         <v>1333</v>
       </c>
       <c r="Q604" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="605" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A605" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B605">
         <v>-34.586370000000002</v>
@@ -23389,12 +23397,12 @@
         <v>0</v>
       </c>
       <c r="Q605" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="606" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A606" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B606">
         <v>-34.9094768</v>
@@ -23488,7 +23496,7 @@
     </row>
     <row r="608" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A608" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B608">
         <v>-34.899749999999997</v>
@@ -23506,7 +23514,7 @@
         <v>1778</v>
       </c>
       <c r="Q608" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="609" spans="1:17" x14ac:dyDescent="0.3">
@@ -23529,12 +23537,12 @@
         <v>2833</v>
       </c>
       <c r="Q609" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="610" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A610" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B610">
         <v>-34.672490000000003</v>
@@ -23552,12 +23560,12 @@
         <v>500</v>
       </c>
       <c r="Q610" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="611" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A611" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B611">
         <v>-34.586370000000002</v>
@@ -23575,12 +23583,12 @@
         <v>0</v>
       </c>
       <c r="Q611" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="612" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A612" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B612">
         <v>-34.507260000000002</v>
@@ -23598,7 +23606,7 @@
         <v>0</v>
       </c>
       <c r="Q612" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="613" spans="1:17" x14ac:dyDescent="0.3">
@@ -23621,12 +23629,12 @@
         <v>2000</v>
       </c>
       <c r="Q613" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="614" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A614" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B614">
         <v>-34.899749999999997</v>
@@ -23644,12 +23652,12 @@
         <v>4278</v>
       </c>
       <c r="Q614" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="615" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A615" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B615">
         <v>-34.911830000000002</v>
@@ -23667,12 +23675,12 @@
         <v>0</v>
       </c>
       <c r="Q615" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="616" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A616" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B616">
         <v>-34.899749999999997</v>
@@ -23690,7 +23698,7 @@
         <v>5500</v>
       </c>
       <c r="Q616" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="617" spans="1:17" x14ac:dyDescent="0.3">
@@ -23713,12 +23721,12 @@
         <v>222</v>
       </c>
       <c r="Q617" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="618" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A618" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B618">
         <v>-34.672490000000003</v>
@@ -23736,12 +23744,12 @@
         <v>0</v>
       </c>
       <c r="Q618" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="619" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A619" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B619">
         <v>-35.642456000000003</v>
@@ -23779,7 +23787,7 @@
     </row>
     <row r="620" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A620" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B620">
         <v>-34.824044999999998</v>
@@ -23866,7 +23874,7 @@
     </row>
     <row r="622" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A622" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B622">
         <v>-34.860666999999999</v>
@@ -23938,7 +23946,7 @@
     </row>
     <row r="624" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A624" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B624">
         <v>-34.899749999999997</v>
@@ -23956,12 +23964,12 @@
         <v>3889</v>
       </c>
       <c r="Q624" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="625" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A625" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B625">
         <v>-34.899749999999997</v>
@@ -23979,12 +23987,12 @@
         <v>4278</v>
       </c>
       <c r="Q625" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="626" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A626" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B626">
         <v>-34.672490000000003</v>
@@ -24002,12 +24010,12 @@
         <v>333</v>
       </c>
       <c r="Q626" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="627" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A627" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B627">
         <v>-34.66301</v>
@@ -24025,12 +24033,12 @@
         <v>7222</v>
       </c>
       <c r="Q627" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="628" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A628" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B628">
         <v>-34.586370000000002</v>
@@ -24048,12 +24056,12 @@
         <v>222</v>
       </c>
       <c r="Q628" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="629" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A629" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B629">
         <v>-34.52664</v>
@@ -24071,12 +24079,12 @@
         <v>222</v>
       </c>
       <c r="Q629" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="630" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A630" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B630">
         <v>-34.494970000000002</v>
@@ -24094,12 +24102,12 @@
         <v>56</v>
       </c>
       <c r="Q630" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="631" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A631" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B631">
         <v>-35.445188000000002</v>
@@ -24127,12 +24135,12 @@
         <v>0</v>
       </c>
       <c r="Q631" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="632" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A632" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B632">
         <v>-34.637633999999998</v>
@@ -24156,12 +24164,12 @@
         <v>112</v>
       </c>
       <c r="Q632" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="633" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A633" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B633">
         <v>-34.864305100000003</v>
@@ -24185,7 +24193,7 @@
         <v>112</v>
       </c>
       <c r="Q633" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="634" spans="1:17" x14ac:dyDescent="0.3">
@@ -24226,7 +24234,7 @@
     </row>
     <row r="635" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A635" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B635">
         <v>-35.092981999999999</v>
@@ -24261,7 +24269,7 @@
     </row>
     <row r="636" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A636" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B636">
         <v>-34.672490000000003</v>
@@ -24279,12 +24287,12 @@
         <v>833</v>
       </c>
       <c r="Q636" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="637" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A637" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B637">
         <v>-34.899749999999997</v>
@@ -24302,7 +24310,7 @@
         <v>2611</v>
       </c>
       <c r="Q637" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="638" spans="1:17" x14ac:dyDescent="0.3">
@@ -24389,7 +24397,7 @@
     </row>
     <row r="640" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A640" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B640">
         <v>-34.672490000000003</v>
@@ -24417,12 +24425,12 @@
       <c r="O640" s="1"/>
       <c r="P640" s="1"/>
       <c r="Q640" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="641" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A641" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="B641">
         <v>-34.934266999999998</v>
@@ -24460,7 +24468,7 @@
     </row>
     <row r="642" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A642" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="B642">
         <v>-34.910024</v>
@@ -24618,7 +24626,7 @@
     </row>
     <row r="646" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A646" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="B646">
         <v>-35.612285999999997</v>
@@ -24659,7 +24667,7 @@
     </row>
     <row r="647" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A647" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="B647">
         <v>-34.933680000000003</v>
@@ -24694,7 +24702,7 @@
     </row>
     <row r="648" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A648" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B648">
         <v>-34.899749999999997</v>
@@ -24722,12 +24730,12 @@
       <c r="O648" s="1"/>
       <c r="P648" s="1"/>
       <c r="Q648" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="649" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A649" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B649">
         <v>-34.911830000000002</v>
@@ -24755,12 +24763,12 @@
       <c r="O649" s="1"/>
       <c r="P649" s="1"/>
       <c r="Q649" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="650" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A650" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B650">
         <v>-34.824044999999998</v>
@@ -24814,7 +24822,7 @@
     </row>
     <row r="651" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A651" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B651">
         <v>-34.860666999999999</v>
@@ -24922,7 +24930,7 @@
     </row>
     <row r="653" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A653" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B653">
         <v>-35.878667100000001</v>
@@ -24975,7 +24983,7 @@
     </row>
     <row r="654" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A654" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B654">
         <v>-34.586370000000002</v>
@@ -25003,7 +25011,7 @@
       <c r="O654" s="1"/>
       <c r="P654" s="1"/>
       <c r="Q654" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="655" spans="1:17" x14ac:dyDescent="0.3">
@@ -25036,12 +25044,12 @@
       <c r="O655" s="1"/>
       <c r="P655" s="1"/>
       <c r="Q655" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="656" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A656" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B656">
         <v>-35.853555700000001</v>
@@ -25094,7 +25102,7 @@
     </row>
     <row r="657" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A657" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B657">
         <v>-35.787276900000002</v>
@@ -25147,7 +25155,7 @@
     </row>
     <row r="658" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A658" s="17" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="B658">
         <v>-34.776083</v>
@@ -25186,7 +25194,7 @@
         <v>1111</v>
       </c>
       <c r="Q658" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
     </row>
     <row r="659" spans="1:17" x14ac:dyDescent="0.3">
@@ -25290,7 +25298,7 @@
     </row>
     <row r="662" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A662" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B662">
         <v>-35.5565</v>
@@ -25356,7 +25364,7 @@
     </row>
     <row r="664" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A664" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B664">
         <v>-35.634602000000001</v>
@@ -25389,7 +25397,7 @@
     </row>
     <row r="665" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A665" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="B665">
         <v>-34.918303199999997</v>
@@ -25416,12 +25424,12 @@
         <v>223</v>
       </c>
       <c r="Q665" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="666" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A666" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="B666">
         <v>-34.911405199999997</v>
@@ -25451,12 +25459,12 @@
         <v>390</v>
       </c>
       <c r="Q666" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="667" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A667" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B667">
         <v>-34.899749999999997</v>
@@ -25486,12 +25494,12 @@
       <c r="O667" s="1"/>
       <c r="P667" s="1"/>
       <c r="Q667" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="668" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A668" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="B668">
         <v>-34.82743</v>
@@ -25521,7 +25529,7 @@
       <c r="O668" s="1"/>
       <c r="P668" s="1"/>
       <c r="Q668" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="669" spans="1:17" x14ac:dyDescent="0.3">
@@ -25554,7 +25562,7 @@
       <c r="O669" s="1"/>
       <c r="P669" s="1"/>
       <c r="Q669" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="670" spans="1:17" x14ac:dyDescent="0.3">
@@ -25613,7 +25621,7 @@
     </row>
     <row r="671" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A671" t="s">
-        <v>370</v>
+        <v>392</v>
       </c>
       <c r="B671">
         <v>-35.739091000000002</v>
@@ -25663,7 +25671,7 @@
     </row>
     <row r="672" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A672" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B672">
         <v>-34.494970000000002</v>
@@ -25691,7 +25699,7 @@
       <c r="O672" s="1"/>
       <c r="P672" s="1"/>
       <c r="Q672" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="673" spans="1:17" x14ac:dyDescent="0.3">
@@ -25750,7 +25758,7 @@
     </row>
     <row r="674" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A674" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="B674">
         <v>-35.119663000000003</v>
@@ -25880,7 +25888,7 @@
     </row>
     <row r="677" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A677" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="B677">
         <v>-34.759169999999997</v>
@@ -25898,7 +25906,7 @@
         <v>1833</v>
       </c>
       <c r="Q677" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="678" spans="1:17" x14ac:dyDescent="0.3">
@@ -25918,12 +25926,12 @@
         <v>333</v>
       </c>
       <c r="Q678" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="679" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A679" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="B679">
         <v>-34.494970000000002</v>
@@ -25941,12 +25949,12 @@
         <v>167</v>
       </c>
       <c r="Q679" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="680" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A680" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="B680">
         <v>-34.584389999999999</v>
@@ -25964,12 +25972,12 @@
         <v>0</v>
       </c>
       <c r="Q680" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="681" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A681" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B681">
         <v>-34.899749999999997</v>
@@ -25987,12 +25995,12 @@
         <v>4833</v>
       </c>
       <c r="Q681" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="682" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A682" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="B682">
         <v>-34.902070808541197</v>
@@ -26013,7 +26021,7 @@
         <v>167</v>
       </c>
       <c r="K682" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="L682">
         <v>167</v>
@@ -26028,12 +26036,12 @@
         <v>1390</v>
       </c>
       <c r="Q682" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
     </row>
     <row r="683" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A683" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="B683">
         <v>-34.933680000000003</v>
@@ -26068,7 +26076,7 @@
     </row>
     <row r="684" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A684" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="B684">
         <v>-34.759169999999997</v>
@@ -26086,12 +26094,12 @@
         <v>1556</v>
       </c>
       <c r="Q684" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="685" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A685" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="B685">
         <v>-34.075153</v>
@@ -26129,7 +26137,7 @@
     </row>
     <row r="686" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A686" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B686">
         <v>-35.762554199999997</v>
@@ -26177,12 +26185,12 @@
         <v>8222</v>
       </c>
       <c r="Q686" t="s">
-        <v>383</v>
+        <v>151</v>
       </c>
     </row>
     <row r="687" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A687" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B687">
         <v>-35.853555700000001</v>
@@ -26230,12 +26238,12 @@
         <v>6110</v>
       </c>
       <c r="Q687" t="s">
-        <v>383</v>
+        <v>151</v>
       </c>
     </row>
     <row r="688" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A688" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="B688">
         <v>-35.852509699999999</v>
@@ -26280,12 +26288,12 @@
         <v>2888</v>
       </c>
       <c r="Q688" t="s">
-        <v>383</v>
+        <v>151</v>
       </c>
     </row>
     <row r="689" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A689" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="B689">
         <v>-35.787201000000003</v>
@@ -26333,12 +26341,12 @@
         <v>16111</v>
       </c>
       <c r="Q689" t="s">
-        <v>383</v>
+        <v>151</v>
       </c>
     </row>
     <row r="690" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A690" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="B690">
         <v>-34.759169999999997</v>
@@ -26356,12 +26364,12 @@
         <v>2667</v>
       </c>
       <c r="Q690" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="691" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A691" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="B691">
         <v>-34.494970000000002</v>
@@ -26379,12 +26387,12 @@
         <v>222</v>
       </c>
       <c r="Q691" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="692" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A692" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="B692">
         <v>-34.902070808541197</v>
@@ -26417,12 +26425,12 @@
         <v>1556</v>
       </c>
       <c r="Q692" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
     </row>
     <row r="693" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A693" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="B693">
         <v>-34.495376</v>
@@ -26458,9 +26466,733 @@
         <v>220</v>
       </c>
     </row>
+    <row r="694" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A694" t="s">
+        <v>385</v>
+      </c>
+      <c r="B694">
+        <v>-34.759169999999997</v>
+      </c>
+      <c r="C694">
+        <v>137.47612000000001</v>
+      </c>
+      <c r="D694" s="2">
+        <v>46085</v>
+      </c>
+      <c r="E694" s="20">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="J694">
+        <v>167</v>
+      </c>
+      <c r="Q694" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="695" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A695" t="s">
+        <v>305</v>
+      </c>
+      <c r="B695">
+        <v>-34.899749999999997</v>
+      </c>
+      <c r="C695">
+        <v>137.45174</v>
+      </c>
+      <c r="D695" s="2">
+        <v>46086</v>
+      </c>
+      <c r="E695" s="20">
+        <v>0.71875</v>
+      </c>
+      <c r="J695">
+        <v>3167</v>
+      </c>
+      <c r="Q695" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="696" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A696" t="s">
+        <v>385</v>
+      </c>
+      <c r="B696">
+        <v>-34.759169999999997</v>
+      </c>
+      <c r="C696">
+        <v>137.47612000000001</v>
+      </c>
+      <c r="D696" s="2">
+        <v>46087</v>
+      </c>
+      <c r="E696" s="20">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="J696">
+        <v>0</v>
+      </c>
+      <c r="Q696" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="697" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A697" t="s">
+        <v>380</v>
+      </c>
+      <c r="B697">
+        <v>-35.853555700000001</v>
+      </c>
+      <c r="C697">
+        <v>137.74248499999999</v>
+      </c>
+      <c r="D697" s="2">
+        <v>46087</v>
+      </c>
+      <c r="E697" s="20">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="F697">
+        <v>167</v>
+      </c>
+      <c r="G697">
+        <v>0</v>
+      </c>
+      <c r="H697">
+        <v>9222</v>
+      </c>
+      <c r="I697">
+        <v>444</v>
+      </c>
+      <c r="J697">
+        <v>444</v>
+      </c>
+      <c r="K697">
+        <v>0</v>
+      </c>
+      <c r="L697">
+        <v>1222</v>
+      </c>
+      <c r="M697">
+        <v>0</v>
+      </c>
+      <c r="N697">
+        <v>0</v>
+      </c>
+      <c r="O697">
+        <v>111</v>
+      </c>
+      <c r="P697">
+        <v>11166</v>
+      </c>
+      <c r="Q697" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="698" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A698" t="s">
+        <v>392</v>
+      </c>
+      <c r="B698">
+        <v>-35.739091000000002</v>
+      </c>
+      <c r="C698">
+        <v>137.67788400000001</v>
+      </c>
+      <c r="D698" s="2">
+        <v>46087</v>
+      </c>
+      <c r="E698" s="20">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="F698">
+        <v>0</v>
+      </c>
+      <c r="G698">
+        <v>0</v>
+      </c>
+      <c r="H698">
+        <v>0</v>
+      </c>
+      <c r="I698">
+        <v>0</v>
+      </c>
+      <c r="J698">
+        <v>0</v>
+      </c>
+      <c r="K698">
+        <v>0</v>
+      </c>
+      <c r="L698">
+        <v>0</v>
+      </c>
+      <c r="M698">
+        <v>0</v>
+      </c>
+      <c r="N698">
+        <v>150</v>
+      </c>
+      <c r="O698">
+        <v>0</v>
+      </c>
+      <c r="P698">
+        <v>150</v>
+      </c>
+      <c r="Q698" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="699" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A699" t="s">
+        <v>270</v>
+      </c>
+      <c r="B699">
+        <v>-34.824044999999998</v>
+      </c>
+      <c r="C699">
+        <v>138.48377600000001</v>
+      </c>
+      <c r="D699" s="2">
+        <v>46088</v>
+      </c>
+      <c r="E699" s="22"/>
+      <c r="G699">
+        <v>0.2</v>
+      </c>
+      <c r="I699">
+        <v>1.3</v>
+      </c>
+      <c r="J699">
+        <v>0</v>
+      </c>
+      <c r="K699" s="23"/>
+      <c r="L699">
+        <v>60.5</v>
+      </c>
+      <c r="M699" s="23"/>
+      <c r="N699">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="O699">
+        <v>0.6</v>
+      </c>
+      <c r="P699">
+        <f>SUM(F699:I699,K699:O699)</f>
+        <v>63.7</v>
+      </c>
+      <c r="Q699" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="700" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A700" t="s">
+        <v>85</v>
+      </c>
+      <c r="B700">
+        <v>-34.873964000000001</v>
+      </c>
+      <c r="C700">
+        <v>138.488134</v>
+      </c>
+      <c r="D700" s="2">
+        <v>46088</v>
+      </c>
+      <c r="E700" s="22"/>
+      <c r="I700">
+        <v>3.15</v>
+      </c>
+      <c r="J700">
+        <v>0</v>
+      </c>
+      <c r="K700" s="23"/>
+      <c r="L700">
+        <v>3.9</v>
+      </c>
+      <c r="M700" s="23"/>
+      <c r="N700">
+        <v>0.45</v>
+      </c>
+      <c r="O700">
+        <v>0.6</v>
+      </c>
+      <c r="P700">
+        <f>SUM(F700:I700,K700:O700)</f>
+        <v>8.1</v>
+      </c>
+      <c r="Q700" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="701" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A701" t="s">
+        <v>79</v>
+      </c>
+      <c r="B701">
+        <v>-34.804662999999998</v>
+      </c>
+      <c r="C701">
+        <v>138.540223</v>
+      </c>
+      <c r="D701" s="2">
+        <v>46088</v>
+      </c>
+      <c r="E701" s="22"/>
+      <c r="I701">
+        <v>0.4</v>
+      </c>
+      <c r="J701">
+        <v>0</v>
+      </c>
+      <c r="K701" s="23"/>
+      <c r="L701">
+        <v>35.6</v>
+      </c>
+      <c r="M701" s="23"/>
+      <c r="N701">
+        <v>0</v>
+      </c>
+      <c r="O701">
+        <v>0.4</v>
+      </c>
+      <c r="P701">
+        <f>SUM(F701:I701,K701:O701)</f>
+        <v>36.4</v>
+      </c>
+      <c r="Q701" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="702" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A702" t="s">
+        <v>317</v>
+      </c>
+      <c r="B702">
+        <v>-35.516800000000003</v>
+      </c>
+      <c r="C702">
+        <v>138.73820000000001</v>
+      </c>
+      <c r="D702" s="2">
+        <v>46089</v>
+      </c>
+      <c r="E702" s="20">
+        <v>0.64097222222222228</v>
+      </c>
+      <c r="I702">
+        <v>0</v>
+      </c>
+      <c r="J702">
+        <v>0</v>
+      </c>
+      <c r="L702">
+        <v>222</v>
+      </c>
+      <c r="P702">
+        <v>222</v>
+      </c>
+      <c r="Q702" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="703" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A703" t="s">
+        <v>188</v>
+      </c>
+      <c r="B703">
+        <v>-35.515900000000002</v>
+      </c>
+      <c r="C703">
+        <v>138.70529999999999</v>
+      </c>
+      <c r="D703" s="2">
+        <v>46089</v>
+      </c>
+      <c r="E703" s="20">
+        <v>0.6479166666666667</v>
+      </c>
+      <c r="I703">
+        <v>111</v>
+      </c>
+      <c r="J703">
+        <v>0</v>
+      </c>
+      <c r="L703">
+        <v>222</v>
+      </c>
+      <c r="P703">
+        <v>333</v>
+      </c>
+      <c r="Q703" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="704" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A704" t="s">
+        <v>91</v>
+      </c>
+      <c r="B704">
+        <v>-35.536299999999997</v>
+      </c>
+      <c r="C704">
+        <v>138.67859999999999</v>
+      </c>
+      <c r="D704" s="2">
+        <v>46089</v>
+      </c>
+      <c r="E704" s="20">
+        <v>0.65555555555555556</v>
+      </c>
+      <c r="I704">
+        <v>0</v>
+      </c>
+      <c r="J704">
+        <v>0</v>
+      </c>
+      <c r="L704">
+        <v>167</v>
+      </c>
+      <c r="P704">
+        <v>167</v>
+      </c>
+      <c r="Q704" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="705" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A705" t="s">
+        <v>186</v>
+      </c>
+      <c r="B705">
+        <v>-35.538600000000002</v>
+      </c>
+      <c r="C705">
+        <v>138.6497</v>
+      </c>
+      <c r="D705" s="2">
+        <v>46089</v>
+      </c>
+      <c r="E705" s="20">
+        <v>0.66249999999999998</v>
+      </c>
+      <c r="I705">
+        <v>0</v>
+      </c>
+      <c r="J705">
+        <v>0</v>
+      </c>
+      <c r="L705">
+        <v>0</v>
+      </c>
+      <c r="P705">
+        <v>0</v>
+      </c>
+      <c r="Q705" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="706" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A706" t="s">
+        <v>319</v>
+      </c>
+      <c r="B706">
+        <v>-35.5565</v>
+      </c>
+      <c r="C706">
+        <v>138.62610000000001</v>
+      </c>
+      <c r="D706" s="2">
+        <v>46089</v>
+      </c>
+      <c r="E706" s="20">
+        <v>0.67013888888888884</v>
+      </c>
+      <c r="I706">
+        <v>0</v>
+      </c>
+      <c r="J706">
+        <v>0</v>
+      </c>
+      <c r="L706">
+        <v>0</v>
+      </c>
+      <c r="P706">
+        <v>0</v>
+      </c>
+      <c r="Q706" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="707" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A707" t="s">
+        <v>190</v>
+      </c>
+      <c r="B707">
+        <v>-35.5565</v>
+      </c>
+      <c r="C707">
+        <v>138.62610000000001</v>
+      </c>
+      <c r="D707" s="2">
+        <v>46089</v>
+      </c>
+      <c r="E707" s="20">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="I707">
+        <v>0</v>
+      </c>
+      <c r="J707">
+        <v>0</v>
+      </c>
+      <c r="L707">
+        <v>167</v>
+      </c>
+      <c r="P707">
+        <v>167</v>
+      </c>
+      <c r="Q707" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="708" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A708" t="s">
+        <v>321</v>
+      </c>
+      <c r="B708">
+        <v>-35.634900000000002</v>
+      </c>
+      <c r="C708">
+        <v>138.49850000000001</v>
+      </c>
+      <c r="D708" s="2">
+        <v>46089</v>
+      </c>
+      <c r="E708" s="20">
+        <v>0.69374999999999998</v>
+      </c>
+      <c r="I708">
+        <v>0</v>
+      </c>
+      <c r="J708">
+        <v>0</v>
+      </c>
+      <c r="L708">
+        <v>111</v>
+      </c>
+      <c r="P708">
+        <v>111</v>
+      </c>
+      <c r="Q708" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="709" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A709" t="s">
+        <v>390</v>
+      </c>
+      <c r="B709">
+        <v>-35.510620000000003</v>
+      </c>
+      <c r="C709">
+        <v>138.21679599999999</v>
+      </c>
+      <c r="D709" s="2">
+        <v>46089</v>
+      </c>
+      <c r="E709" s="20">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="I709">
+        <v>278</v>
+      </c>
+      <c r="J709">
+        <v>0</v>
+      </c>
+      <c r="L709">
+        <v>444</v>
+      </c>
+      <c r="N709">
+        <v>3944</v>
+      </c>
+      <c r="O709">
+        <v>56</v>
+      </c>
+      <c r="P709">
+        <v>4722</v>
+      </c>
+      <c r="Q709" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="710" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A710" t="s">
+        <v>391</v>
+      </c>
+      <c r="B710">
+        <v>-35.793973000000001</v>
+      </c>
+      <c r="C710">
+        <v>137.852418</v>
+      </c>
+      <c r="D710" s="2">
+        <v>46089</v>
+      </c>
+      <c r="E710" s="20">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="F710">
+        <v>0</v>
+      </c>
+      <c r="G710">
+        <v>556</v>
+      </c>
+      <c r="H710">
+        <v>2000</v>
+      </c>
+      <c r="I710">
+        <v>444</v>
+      </c>
+      <c r="J710">
+        <v>0</v>
+      </c>
+      <c r="K710">
+        <v>444</v>
+      </c>
+      <c r="L710">
+        <v>3889</v>
+      </c>
+      <c r="M710">
+        <v>444</v>
+      </c>
+      <c r="N710">
+        <v>0</v>
+      </c>
+      <c r="O710">
+        <v>556</v>
+      </c>
+      <c r="P710">
+        <v>8333</v>
+      </c>
+      <c r="Q710" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="711" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A711" t="s">
+        <v>388</v>
+      </c>
+      <c r="B711">
+        <v>-34.88823</v>
+      </c>
+      <c r="C711">
+        <v>137.45353</v>
+      </c>
+      <c r="D711" s="2">
+        <v>46090</v>
+      </c>
+      <c r="E711" s="20">
+        <v>0.49305555555555558</v>
+      </c>
+      <c r="J711">
+        <v>1722</v>
+      </c>
+      <c r="Q711" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="712" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A712" t="s">
+        <v>364</v>
+      </c>
+      <c r="B712">
+        <v>-35.878667100000001</v>
+      </c>
+      <c r="C712">
+        <v>137.6963188</v>
+      </c>
+      <c r="D712" s="2">
+        <v>46091</v>
+      </c>
+      <c r="E712" s="20">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F712">
+        <v>0</v>
+      </c>
+      <c r="G712">
+        <v>0</v>
+      </c>
+      <c r="H712">
+        <v>222</v>
+      </c>
+      <c r="I712">
+        <v>333</v>
+      </c>
+      <c r="J712">
+        <v>222</v>
+      </c>
+      <c r="K712">
+        <v>111</v>
+      </c>
+      <c r="L712">
+        <v>1889</v>
+      </c>
+      <c r="M712">
+        <v>0</v>
+      </c>
+      <c r="N712">
+        <v>4111</v>
+      </c>
+      <c r="O712">
+        <v>0</v>
+      </c>
+      <c r="P712">
+        <v>6666</v>
+      </c>
+      <c r="Q712" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="713" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A713" t="s">
+        <v>59</v>
+      </c>
+      <c r="B713">
+        <v>-35.084850000000003</v>
+      </c>
+      <c r="C713">
+        <v>137.74889999999999</v>
+      </c>
+      <c r="D713" s="2">
+        <v>46092</v>
+      </c>
+      <c r="E713" s="20">
+        <v>0.5625</v>
+      </c>
+      <c r="G713">
+        <v>0</v>
+      </c>
+      <c r="I713">
+        <v>56</v>
+      </c>
+      <c r="J713">
+        <v>0</v>
+      </c>
+      <c r="L713">
+        <v>0</v>
+      </c>
+      <c r="N713">
+        <v>389</v>
+      </c>
+      <c r="P713">
+        <v>445</v>
+      </c>
+      <c r="Q713" t="s">
+        <v>149</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q693">
-    <sortCondition ref="D2:D693"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q713">
+    <sortCondition ref="D2:D713"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/MASTER spreadsheet of community summaries.xlsx
+++ b/MASTER spreadsheet of community summaries.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\peri\Dropbox\Delta\Projects\Laboratory\Algal blooms, bacterial counts  for community\For Luke's HAB data display\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AE5FCB8-4AC3-46B0-B02F-7941E7E4A92B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AABAF3B9-CB32-4631-B29B-6810A2244EBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="1650" windowWidth="29040" windowHeight="15720" xr2:uid="{9286397E-2757-492B-865A-39B2D6A15FF6}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{9286397E-2757-492B-865A-39B2D6A15FF6}"/>
   </bookViews>
   <sheets>
     <sheet name="Cells per mL" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1443" uniqueCount="393">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1489" uniqueCount="400">
   <si>
     <t>Date</t>
   </si>
@@ -1235,6 +1235,27 @@
   </si>
   <si>
     <t xml:space="preserve">Min Oil </t>
+  </si>
+  <si>
+    <t>Port Dock 1 (8m depth)</t>
+  </si>
+  <si>
+    <t>West Beach Boat Ramp</t>
+  </si>
+  <si>
+    <t>Port Elliot Beach</t>
+  </si>
+  <si>
+    <t>Antechamber</t>
+  </si>
+  <si>
+    <t>New Rapid Head Jetty</t>
+  </si>
+  <si>
+    <t>Balgowan beach access</t>
+  </si>
+  <si>
+    <t>Pinks Beach</t>
   </si>
 </sst>
 </file>
@@ -1702,7 +1723,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F307807-E5C9-4450-88E0-159CBB3E9A67}">
-  <dimension ref="A1:T713"/>
+  <dimension ref="A1:T736"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="39.33203125" customWidth="1"/>
@@ -26392,19 +26413,22 @@
     </row>
     <row r="692" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A692" t="s">
-        <v>378</v>
+        <v>399</v>
       </c>
       <c r="B692">
-        <v>-34.902070808541197</v>
+        <v>-36.866</v>
       </c>
       <c r="C692">
-        <v>137.79925776072</v>
+        <v>139.81913</v>
       </c>
       <c r="D692" s="2">
-        <v>46084</v>
-      </c>
-      <c r="E692" s="20">
-        <v>0.71527777777777779</v>
+        <v>46083</v>
+      </c>
+      <c r="G692">
+        <v>333</v>
+      </c>
+      <c r="H692">
+        <v>778</v>
       </c>
       <c r="I692">
         <v>667</v>
@@ -26413,100 +26437,115 @@
         <v>0</v>
       </c>
       <c r="L692">
-        <v>333</v>
+        <v>31333</v>
       </c>
       <c r="N692">
-        <v>389</v>
+        <v>1889</v>
       </c>
       <c r="O692">
-        <v>167</v>
+        <v>1389</v>
       </c>
       <c r="P692">
-        <v>1556</v>
+        <v>36389</v>
       </c>
       <c r="Q692" t="s">
-        <v>369</v>
+        <v>129</v>
       </c>
     </row>
     <row r="693" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A693" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="B693">
-        <v>-34.495376</v>
+        <v>-34.902070808541197</v>
       </c>
       <c r="C693">
-        <v>137.481537</v>
+        <v>137.79925776072</v>
       </c>
       <c r="D693" s="2">
         <v>46084</v>
       </c>
       <c r="E693" s="20">
-        <v>0.82291666666666663</v>
+        <v>0.71527777777777779</v>
       </c>
       <c r="I693">
-        <v>1444</v>
+        <v>667</v>
       </c>
       <c r="J693">
-        <v>833</v>
+        <v>0</v>
       </c>
       <c r="L693">
-        <v>1222</v>
+        <v>333</v>
       </c>
       <c r="N693">
-        <v>1000</v>
+        <v>389</v>
       </c>
       <c r="O693">
-        <v>223</v>
+        <v>167</v>
       </c>
       <c r="P693">
-        <v>3889</v>
+        <v>1556</v>
       </c>
       <c r="Q693" t="s">
-        <v>220</v>
+        <v>369</v>
       </c>
     </row>
     <row r="694" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A694" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B694">
-        <v>-34.759169999999997</v>
+        <v>-34.495376</v>
       </c>
       <c r="C694">
-        <v>137.47612000000001</v>
+        <v>137.481537</v>
       </c>
       <c r="D694" s="2">
-        <v>46085</v>
+        <v>46084</v>
       </c>
       <c r="E694" s="20">
-        <v>0.58333333333333337</v>
+        <v>0.82291666666666663</v>
+      </c>
+      <c r="I694">
+        <v>1444</v>
       </c>
       <c r="J694">
-        <v>167</v>
+        <v>833</v>
+      </c>
+      <c r="L694">
+        <v>1222</v>
+      </c>
+      <c r="N694">
+        <v>1000</v>
+      </c>
+      <c r="O694">
+        <v>223</v>
+      </c>
+      <c r="P694">
+        <v>3889</v>
       </c>
       <c r="Q694" t="s">
-        <v>268</v>
+        <v>220</v>
       </c>
     </row>
     <row r="695" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A695" t="s">
-        <v>305</v>
+        <v>385</v>
       </c>
       <c r="B695">
-        <v>-34.899749999999997</v>
+        <v>-34.759169999999997</v>
       </c>
       <c r="C695">
-        <v>137.45174</v>
+        <v>137.47612000000001</v>
       </c>
       <c r="D695" s="2">
-        <v>46086</v>
+        <v>46085</v>
       </c>
       <c r="E695" s="20">
-        <v>0.71875</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="J695">
-        <v>3167</v>
+        <v>167</v>
       </c>
       <c r="Q695" t="s">
         <v>268</v>
@@ -26514,22 +26553,22 @@
     </row>
     <row r="696" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A696" t="s">
-        <v>385</v>
+        <v>305</v>
       </c>
       <c r="B696">
-        <v>-34.759169999999997</v>
+        <v>-34.899749999999997</v>
       </c>
       <c r="C696">
-        <v>137.47612000000001</v>
+        <v>137.45174</v>
       </c>
       <c r="D696" s="2">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="E696" s="20">
-        <v>0.58333333333333337</v>
+        <v>0.71875</v>
       </c>
       <c r="J696">
-        <v>0</v>
+        <v>3167</v>
       </c>
       <c r="Q696" t="s">
         <v>268</v>
@@ -26537,105 +26576,75 @@
     </row>
     <row r="697" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A697" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="B697">
-        <v>-35.853555700000001</v>
+        <v>-34.759169999999997</v>
       </c>
       <c r="C697">
-        <v>137.74248499999999</v>
+        <v>137.47612000000001</v>
       </c>
       <c r="D697" s="2">
         <v>46087</v>
       </c>
       <c r="E697" s="20">
-        <v>0.47916666666666669</v>
-      </c>
-      <c r="F697">
-        <v>167</v>
-      </c>
-      <c r="G697">
-        <v>0</v>
-      </c>
-      <c r="H697">
-        <v>9222</v>
-      </c>
-      <c r="I697">
-        <v>444</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="J697">
-        <v>444</v>
-      </c>
-      <c r="K697">
-        <v>0</v>
-      </c>
-      <c r="L697">
-        <v>1222</v>
-      </c>
-      <c r="M697">
-        <v>0</v>
-      </c>
-      <c r="N697">
-        <v>0</v>
-      </c>
-      <c r="O697">
-        <v>111</v>
-      </c>
-      <c r="P697">
-        <v>11166</v>
+        <v>0</v>
       </c>
       <c r="Q697" t="s">
-        <v>151</v>
+        <v>268</v>
       </c>
     </row>
     <row r="698" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A698" t="s">
-        <v>392</v>
+        <v>380</v>
       </c>
       <c r="B698">
-        <v>-35.739091000000002</v>
+        <v>-35.853555700000001</v>
       </c>
       <c r="C698">
-        <v>137.67788400000001</v>
+        <v>137.74248499999999</v>
       </c>
       <c r="D698" s="2">
         <v>46087</v>
       </c>
       <c r="E698" s="20">
-        <v>0.58333333333333337</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="F698">
-        <v>0</v>
+        <v>167</v>
       </c>
       <c r="G698">
         <v>0</v>
       </c>
       <c r="H698">
-        <v>0</v>
+        <v>9222</v>
       </c>
       <c r="I698">
-        <v>0</v>
+        <v>444</v>
       </c>
       <c r="J698">
-        <v>0</v>
+        <v>444</v>
       </c>
       <c r="K698">
         <v>0</v>
       </c>
       <c r="L698">
-        <v>0</v>
+        <v>1222</v>
       </c>
       <c r="M698">
         <v>0</v>
       </c>
       <c r="N698">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="O698">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="P698">
-        <v>150</v>
+        <v>11166</v>
       </c>
       <c r="Q698" t="s">
         <v>151</v>
@@ -26643,80 +26652,94 @@
     </row>
     <row r="699" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A699" t="s">
-        <v>270</v>
+        <v>392</v>
       </c>
       <c r="B699">
-        <v>-34.824044999999998</v>
+        <v>-35.739091000000002</v>
       </c>
       <c r="C699">
-        <v>138.48377600000001</v>
+        <v>137.67788400000001</v>
       </c>
       <c r="D699" s="2">
-        <v>46088</v>
-      </c>
-      <c r="E699" s="22"/>
+        <v>46087</v>
+      </c>
+      <c r="E699" s="20">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="F699">
+        <v>0</v>
+      </c>
       <c r="G699">
-        <v>0.2</v>
+        <v>0</v>
+      </c>
+      <c r="H699">
+        <v>0</v>
       </c>
       <c r="I699">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="J699">
         <v>0</v>
       </c>
-      <c r="K699" s="23"/>
+      <c r="K699">
+        <v>0</v>
+      </c>
       <c r="L699">
-        <v>60.5</v>
-      </c>
-      <c r="M699" s="23"/>
+        <v>0</v>
+      </c>
+      <c r="M699">
+        <v>0</v>
+      </c>
       <c r="N699">
-        <v>1.1000000000000001</v>
+        <v>150</v>
       </c>
       <c r="O699">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="P699">
-        <f>SUM(F699:I699,K699:O699)</f>
-        <v>63.7</v>
+        <v>150</v>
       </c>
       <c r="Q699" t="s">
-        <v>78</v>
+        <v>151</v>
       </c>
     </row>
     <row r="700" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A700" t="s">
-        <v>85</v>
+        <v>270</v>
       </c>
       <c r="B700">
-        <v>-34.873964000000001</v>
+        <v>-34.824044999999998</v>
       </c>
       <c r="C700">
-        <v>138.488134</v>
+        <v>138.48377600000001</v>
       </c>
       <c r="D700" s="2">
         <v>46088</v>
       </c>
       <c r="E700" s="22"/>
+      <c r="G700">
+        <v>0.2</v>
+      </c>
       <c r="I700">
-        <v>3.15</v>
+        <v>1.3</v>
       </c>
       <c r="J700">
         <v>0</v>
       </c>
       <c r="K700" s="23"/>
       <c r="L700">
-        <v>3.9</v>
+        <v>60.5</v>
       </c>
       <c r="M700" s="23"/>
       <c r="N700">
-        <v>0.45</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="O700">
         <v>0.6</v>
       </c>
       <c r="P700">
         <f>SUM(F700:I700,K700:O700)</f>
-        <v>8.1</v>
+        <v>63.7</v>
       </c>
       <c r="Q700" t="s">
         <v>78</v>
@@ -26724,38 +26747,38 @@
     </row>
     <row r="701" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A701" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="B701">
-        <v>-34.804662999999998</v>
+        <v>-34.873964000000001</v>
       </c>
       <c r="C701">
-        <v>138.540223</v>
+        <v>138.488134</v>
       </c>
       <c r="D701" s="2">
         <v>46088</v>
       </c>
       <c r="E701" s="22"/>
       <c r="I701">
-        <v>0.4</v>
+        <v>3.15</v>
       </c>
       <c r="J701">
         <v>0</v>
       </c>
       <c r="K701" s="23"/>
       <c r="L701">
-        <v>35.6</v>
+        <v>3.9</v>
       </c>
       <c r="M701" s="23"/>
       <c r="N701">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="O701">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="P701">
         <f>SUM(F701:I701,K701:O701)</f>
-        <v>36.4</v>
+        <v>8.1</v>
       </c>
       <c r="Q701" t="s">
         <v>78</v>
@@ -26763,54 +26786,61 @@
     </row>
     <row r="702" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A702" t="s">
-        <v>317</v>
+        <v>79</v>
       </c>
       <c r="B702">
-        <v>-35.516800000000003</v>
+        <v>-34.804662999999998</v>
       </c>
       <c r="C702">
-        <v>138.73820000000001</v>
+        <v>138.540223</v>
       </c>
       <c r="D702" s="2">
-        <v>46089</v>
-      </c>
-      <c r="E702" s="20">
-        <v>0.64097222222222228</v>
-      </c>
+        <v>46088</v>
+      </c>
+      <c r="E702" s="22"/>
       <c r="I702">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="J702">
         <v>0</v>
       </c>
+      <c r="K702" s="23"/>
       <c r="L702">
-        <v>222</v>
+        <v>35.6</v>
+      </c>
+      <c r="M702" s="23"/>
+      <c r="N702">
+        <v>0</v>
+      </c>
+      <c r="O702">
+        <v>0.4</v>
       </c>
       <c r="P702">
-        <v>222</v>
+        <f>SUM(F702:I702,K702:O702)</f>
+        <v>36.4</v>
       </c>
       <c r="Q702" t="s">
-        <v>187</v>
+        <v>78</v>
       </c>
     </row>
     <row r="703" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A703" t="s">
-        <v>188</v>
+        <v>317</v>
       </c>
       <c r="B703">
-        <v>-35.515900000000002</v>
+        <v>-35.516800000000003</v>
       </c>
       <c r="C703">
-        <v>138.70529999999999</v>
+        <v>138.73820000000001</v>
       </c>
       <c r="D703" s="2">
         <v>46089</v>
       </c>
       <c r="E703" s="20">
-        <v>0.6479166666666667</v>
+        <v>0.64097222222222228</v>
       </c>
       <c r="I703">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="J703">
         <v>0</v>
@@ -26819,7 +26849,7 @@
         <v>222</v>
       </c>
       <c r="P703">
-        <v>333</v>
+        <v>222</v>
       </c>
       <c r="Q703" t="s">
         <v>187</v>
@@ -26827,31 +26857,31 @@
     </row>
     <row r="704" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A704" t="s">
-        <v>91</v>
+        <v>188</v>
       </c>
       <c r="B704">
-        <v>-35.536299999999997</v>
+        <v>-35.515900000000002</v>
       </c>
       <c r="C704">
-        <v>138.67859999999999</v>
+        <v>138.70529999999999</v>
       </c>
       <c r="D704" s="2">
         <v>46089</v>
       </c>
       <c r="E704" s="20">
-        <v>0.65555555555555556</v>
+        <v>0.6479166666666667</v>
       </c>
       <c r="I704">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="J704">
         <v>0</v>
       </c>
       <c r="L704">
-        <v>167</v>
+        <v>222</v>
       </c>
       <c r="P704">
-        <v>167</v>
+        <v>333</v>
       </c>
       <c r="Q704" t="s">
         <v>187</v>
@@ -26859,19 +26889,19 @@
     </row>
     <row r="705" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A705" t="s">
-        <v>186</v>
+        <v>91</v>
       </c>
       <c r="B705">
-        <v>-35.538600000000002</v>
+        <v>-35.536299999999997</v>
       </c>
       <c r="C705">
-        <v>138.6497</v>
+        <v>138.67859999999999</v>
       </c>
       <c r="D705" s="2">
         <v>46089</v>
       </c>
       <c r="E705" s="20">
-        <v>0.66249999999999998</v>
+        <v>0.65555555555555556</v>
       </c>
       <c r="I705">
         <v>0</v>
@@ -26880,10 +26910,10 @@
         <v>0</v>
       </c>
       <c r="L705">
-        <v>0</v>
+        <v>167</v>
       </c>
       <c r="P705">
-        <v>0</v>
+        <v>167</v>
       </c>
       <c r="Q705" t="s">
         <v>187</v>
@@ -26891,19 +26921,19 @@
     </row>
     <row r="706" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A706" t="s">
-        <v>319</v>
+        <v>186</v>
       </c>
       <c r="B706">
-        <v>-35.5565</v>
+        <v>-35.538600000000002</v>
       </c>
       <c r="C706">
-        <v>138.62610000000001</v>
+        <v>138.6497</v>
       </c>
       <c r="D706" s="2">
         <v>46089</v>
       </c>
       <c r="E706" s="20">
-        <v>0.67013888888888884</v>
+        <v>0.66249999999999998</v>
       </c>
       <c r="I706">
         <v>0</v>
@@ -26923,7 +26953,7 @@
     </row>
     <row r="707" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A707" t="s">
-        <v>190</v>
+        <v>319</v>
       </c>
       <c r="B707">
         <v>-35.5565</v>
@@ -26935,7 +26965,7 @@
         <v>46089</v>
       </c>
       <c r="E707" s="20">
-        <v>0.67708333333333337</v>
+        <v>0.67013888888888884</v>
       </c>
       <c r="I707">
         <v>0</v>
@@ -26944,10 +26974,10 @@
         <v>0</v>
       </c>
       <c r="L707">
-        <v>167</v>
+        <v>0</v>
       </c>
       <c r="P707">
-        <v>167</v>
+        <v>0</v>
       </c>
       <c r="Q707" t="s">
         <v>187</v>
@@ -26955,19 +26985,19 @@
     </row>
     <row r="708" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A708" t="s">
-        <v>321</v>
+        <v>190</v>
       </c>
       <c r="B708">
-        <v>-35.634900000000002</v>
+        <v>-35.5565</v>
       </c>
       <c r="C708">
-        <v>138.49850000000001</v>
+        <v>138.62610000000001</v>
       </c>
       <c r="D708" s="2">
         <v>46089</v>
       </c>
       <c r="E708" s="20">
-        <v>0.69374999999999998</v>
+        <v>0.67708333333333337</v>
       </c>
       <c r="I708">
         <v>0</v>
@@ -26976,10 +27006,10 @@
         <v>0</v>
       </c>
       <c r="L708">
-        <v>111</v>
+        <v>167</v>
       </c>
       <c r="P708">
-        <v>111</v>
+        <v>167</v>
       </c>
       <c r="Q708" t="s">
         <v>187</v>
@@ -26987,189 +27017,162 @@
     </row>
     <row r="709" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A709" t="s">
-        <v>390</v>
+        <v>321</v>
       </c>
       <c r="B709">
-        <v>-35.510620000000003</v>
+        <v>-35.634900000000002</v>
       </c>
       <c r="C709">
-        <v>138.21679599999999</v>
+        <v>138.49850000000001</v>
       </c>
       <c r="D709" s="2">
         <v>46089</v>
       </c>
       <c r="E709" s="20">
-        <v>0.66666666666666663</v>
+        <v>0.69374999999999998</v>
       </c>
       <c r="I709">
-        <v>278</v>
+        <v>0</v>
       </c>
       <c r="J709">
         <v>0</v>
       </c>
       <c r="L709">
-        <v>444</v>
-      </c>
-      <c r="N709">
-        <v>3944</v>
-      </c>
-      <c r="O709">
-        <v>56</v>
+        <v>111</v>
       </c>
       <c r="P709">
-        <v>4722</v>
+        <v>111</v>
       </c>
       <c r="Q709" t="s">
-        <v>254</v>
+        <v>187</v>
       </c>
     </row>
     <row r="710" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A710" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B710">
-        <v>-35.793973000000001</v>
+        <v>-35.510620000000003</v>
       </c>
       <c r="C710">
-        <v>137.852418</v>
+        <v>138.21679599999999</v>
       </c>
       <c r="D710" s="2">
         <v>46089</v>
       </c>
       <c r="E710" s="20">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="F710">
-        <v>0</v>
-      </c>
-      <c r="G710">
-        <v>556</v>
-      </c>
-      <c r="H710">
-        <v>2000</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="I710">
+        <v>278</v>
+      </c>
+      <c r="J710">
+        <v>0</v>
+      </c>
+      <c r="L710">
         <v>444</v>
       </c>
-      <c r="J710">
-        <v>0</v>
-      </c>
-      <c r="K710">
-        <v>444</v>
-      </c>
-      <c r="L710">
-        <v>3889</v>
-      </c>
-      <c r="M710">
-        <v>444</v>
-      </c>
       <c r="N710">
-        <v>0</v>
+        <v>3944</v>
       </c>
       <c r="O710">
-        <v>556</v>
+        <v>56</v>
       </c>
       <c r="P710">
-        <v>8333</v>
+        <v>4722</v>
       </c>
       <c r="Q710" t="s">
-        <v>151</v>
+        <v>254</v>
       </c>
     </row>
     <row r="711" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A711" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="B711">
-        <v>-34.88823</v>
+        <v>-35.793973000000001</v>
       </c>
       <c r="C711">
-        <v>137.45353</v>
+        <v>137.852418</v>
       </c>
       <c r="D711" s="2">
-        <v>46090</v>
+        <v>46089</v>
       </c>
       <c r="E711" s="20">
-        <v>0.49305555555555558</v>
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="F711">
+        <v>0</v>
+      </c>
+      <c r="G711">
+        <v>556</v>
+      </c>
+      <c r="H711">
+        <v>2000</v>
+      </c>
+      <c r="I711">
+        <v>444</v>
       </c>
       <c r="J711">
-        <v>1722</v>
+        <v>0</v>
+      </c>
+      <c r="K711">
+        <v>444</v>
+      </c>
+      <c r="L711">
+        <v>3889</v>
+      </c>
+      <c r="M711">
+        <v>444</v>
+      </c>
+      <c r="N711">
+        <v>0</v>
+      </c>
+      <c r="O711">
+        <v>556</v>
+      </c>
+      <c r="P711">
+        <v>8333</v>
       </c>
       <c r="Q711" t="s">
-        <v>268</v>
+        <v>151</v>
       </c>
     </row>
     <row r="712" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A712" t="s">
-        <v>364</v>
+        <v>388</v>
       </c>
       <c r="B712">
-        <v>-35.878667100000001</v>
+        <v>-34.88823</v>
       </c>
       <c r="C712">
-        <v>137.6963188</v>
+        <v>137.45353</v>
       </c>
       <c r="D712" s="2">
-        <v>46091</v>
+        <v>46090</v>
       </c>
       <c r="E712" s="20">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F712">
-        <v>0</v>
-      </c>
-      <c r="G712">
-        <v>0</v>
-      </c>
-      <c r="H712">
-        <v>222</v>
-      </c>
-      <c r="I712">
-        <v>333</v>
+        <v>0.49305555555555558</v>
       </c>
       <c r="J712">
-        <v>222</v>
-      </c>
-      <c r="K712">
-        <v>111</v>
-      </c>
-      <c r="L712">
-        <v>1889</v>
-      </c>
-      <c r="M712">
-        <v>0</v>
-      </c>
-      <c r="N712">
-        <v>4111</v>
-      </c>
-      <c r="O712">
-        <v>0</v>
-      </c>
-      <c r="P712">
-        <v>6666</v>
+        <v>1722</v>
       </c>
       <c r="Q712" t="s">
-        <v>151</v>
+        <v>268</v>
       </c>
     </row>
     <row r="713" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A713" t="s">
-        <v>59</v>
+        <v>94</v>
       </c>
       <c r="B713">
-        <v>-35.084850000000003</v>
+        <v>-35.58858</v>
       </c>
       <c r="C713">
-        <v>137.74889999999999</v>
+        <v>138.60474600000001</v>
       </c>
       <c r="D713" s="2">
-        <v>46092</v>
-      </c>
-      <c r="E713" s="20">
-        <v>0.5625</v>
-      </c>
-      <c r="G713">
-        <v>0</v>
+        <v>46090</v>
       </c>
       <c r="I713">
         <v>56</v>
@@ -27178,21 +27181,889 @@
         <v>0</v>
       </c>
       <c r="L713">
-        <v>0</v>
+        <v>222</v>
       </c>
       <c r="N713">
+        <v>278</v>
+      </c>
+      <c r="O713">
+        <v>833</v>
+      </c>
+      <c r="P713">
+        <v>1389</v>
+      </c>
+      <c r="Q713" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="714" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A714" t="s">
+        <v>89</v>
+      </c>
+      <c r="B714">
+        <v>-35.6048446</v>
+      </c>
+      <c r="C714">
+        <v>138.59278499999999</v>
+      </c>
+      <c r="D714" s="2">
+        <v>46090</v>
+      </c>
+      <c r="I714">
+        <v>56</v>
+      </c>
+      <c r="J714">
+        <v>0</v>
+      </c>
+      <c r="L714">
+        <v>222</v>
+      </c>
+      <c r="N714">
         <v>389</v>
       </c>
-      <c r="P713">
+      <c r="O714">
+        <v>333</v>
+      </c>
+      <c r="P714">
+        <v>1000</v>
+      </c>
+      <c r="Q714" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="715" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A715" t="s">
+        <v>364</v>
+      </c>
+      <c r="B715">
+        <v>-35.878667100000001</v>
+      </c>
+      <c r="C715">
+        <v>137.6963188</v>
+      </c>
+      <c r="D715" s="2">
+        <v>46091</v>
+      </c>
+      <c r="E715" s="20">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F715">
+        <v>0</v>
+      </c>
+      <c r="G715">
+        <v>0</v>
+      </c>
+      <c r="H715">
+        <v>222</v>
+      </c>
+      <c r="I715">
+        <v>333</v>
+      </c>
+      <c r="J715">
+        <v>222</v>
+      </c>
+      <c r="K715">
+        <v>111</v>
+      </c>
+      <c r="L715">
+        <v>1889</v>
+      </c>
+      <c r="M715">
+        <v>0</v>
+      </c>
+      <c r="N715">
+        <v>4111</v>
+      </c>
+      <c r="O715">
+        <v>0</v>
+      </c>
+      <c r="P715">
+        <v>6666</v>
+      </c>
+      <c r="Q715" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="716" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A716" t="s">
+        <v>59</v>
+      </c>
+      <c r="B716">
+        <v>-35.084850000000003</v>
+      </c>
+      <c r="C716">
+        <v>137.74889999999999</v>
+      </c>
+      <c r="D716" s="2">
+        <v>46092</v>
+      </c>
+      <c r="E716" s="20">
+        <v>0.5625</v>
+      </c>
+      <c r="G716">
+        <v>0</v>
+      </c>
+      <c r="I716">
+        <v>56</v>
+      </c>
+      <c r="J716">
+        <v>0</v>
+      </c>
+      <c r="L716">
+        <v>0</v>
+      </c>
+      <c r="N716">
+        <v>389</v>
+      </c>
+      <c r="P716">
         <v>445</v>
       </c>
-      <c r="Q713" t="s">
+      <c r="Q716" t="s">
         <v>149</v>
       </c>
     </row>
+    <row r="717" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A717" t="s">
+        <v>393</v>
+      </c>
+      <c r="B717">
+        <v>-34.842409000000004</v>
+      </c>
+      <c r="C717">
+        <v>138.50364999999999</v>
+      </c>
+      <c r="D717" s="2">
+        <v>46092</v>
+      </c>
+      <c r="E717" s="20">
+        <v>0.71875</v>
+      </c>
+      <c r="G717">
+        <v>0.36</v>
+      </c>
+      <c r="H717">
+        <v>0.24</v>
+      </c>
+      <c r="I717">
+        <v>0.36</v>
+      </c>
+      <c r="J717">
+        <v>0</v>
+      </c>
+      <c r="L717">
+        <v>476.64</v>
+      </c>
+      <c r="N717">
+        <v>3.24</v>
+      </c>
+      <c r="O717">
+        <v>0.48</v>
+      </c>
+      <c r="P717">
+        <v>481.32</v>
+      </c>
+      <c r="Q717" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="718" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A718" t="s">
+        <v>385</v>
+      </c>
+      <c r="B718">
+        <v>-34.759169999999997</v>
+      </c>
+      <c r="C718">
+        <v>137.47612000000001</v>
+      </c>
+      <c r="D718" s="2">
+        <v>46092</v>
+      </c>
+      <c r="E718" s="20">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="J718">
+        <v>167</v>
+      </c>
+      <c r="Q718" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="719" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A719" t="s">
+        <v>357</v>
+      </c>
+      <c r="B719">
+        <v>-34.672490000000003</v>
+      </c>
+      <c r="C719">
+        <v>137.49295000000001</v>
+      </c>
+      <c r="D719" s="2">
+        <v>46092</v>
+      </c>
+      <c r="E719" s="20">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="J719">
+        <v>0</v>
+      </c>
+      <c r="Q719" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="720" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A720" t="s">
+        <v>59</v>
+      </c>
+      <c r="B720">
+        <v>-35.084850000000003</v>
+      </c>
+      <c r="C720">
+        <v>137.74889999999999</v>
+      </c>
+      <c r="D720" s="2">
+        <v>46092</v>
+      </c>
+      <c r="E720" s="20">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="G720">
+        <v>0</v>
+      </c>
+      <c r="I720">
+        <v>56</v>
+      </c>
+      <c r="J720">
+        <v>0</v>
+      </c>
+      <c r="L720">
+        <v>0</v>
+      </c>
+      <c r="N720">
+        <v>333</v>
+      </c>
+      <c r="P720">
+        <v>389</v>
+      </c>
+      <c r="Q720" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="721" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A721" t="s">
+        <v>396</v>
+      </c>
+      <c r="B721">
+        <v>-35.786641000000003</v>
+      </c>
+      <c r="C721">
+        <v>138.07153940000001</v>
+      </c>
+      <c r="D721" s="2">
+        <v>46094</v>
+      </c>
+      <c r="E721" s="20">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="F721">
+        <v>0</v>
+      </c>
+      <c r="G721">
+        <v>0</v>
+      </c>
+      <c r="H721">
+        <v>0</v>
+      </c>
+      <c r="I721">
+        <v>0</v>
+      </c>
+      <c r="J721">
+        <v>0</v>
+      </c>
+      <c r="K721">
+        <v>0</v>
+      </c>
+      <c r="L721">
+        <v>1889</v>
+      </c>
+      <c r="M721">
+        <v>0</v>
+      </c>
+      <c r="N721">
+        <v>2000</v>
+      </c>
+      <c r="O721">
+        <v>111</v>
+      </c>
+      <c r="P721">
+        <v>4000</v>
+      </c>
+      <c r="Q721" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="722" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A722" t="s">
+        <v>223</v>
+      </c>
+      <c r="B722">
+        <v>-35.638145999999999</v>
+      </c>
+      <c r="C722">
+        <v>137.6249325</v>
+      </c>
+      <c r="D722" s="2">
+        <v>46095</v>
+      </c>
+      <c r="E722" s="20">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="F722">
+        <v>0</v>
+      </c>
+      <c r="G722">
+        <v>0</v>
+      </c>
+      <c r="H722">
+        <v>333</v>
+      </c>
+      <c r="I722">
+        <v>444</v>
+      </c>
+      <c r="J722">
+        <v>0</v>
+      </c>
+      <c r="K722">
+        <v>444</v>
+      </c>
+      <c r="L722">
+        <v>11222</v>
+      </c>
+      <c r="M722">
+        <v>333</v>
+      </c>
+      <c r="N722">
+        <v>4111</v>
+      </c>
+      <c r="O722">
+        <v>0</v>
+      </c>
+      <c r="P722">
+        <v>16887</v>
+      </c>
+      <c r="Q722" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="723" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A723" t="s">
+        <v>395</v>
+      </c>
+      <c r="B723">
+        <v>-35.532783000000002</v>
+      </c>
+      <c r="C723">
+        <v>138.68868499999999</v>
+      </c>
+      <c r="D723" s="2">
+        <v>46096</v>
+      </c>
+      <c r="E723" s="20">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="I723">
+        <v>0.3</v>
+      </c>
+      <c r="J723">
+        <v>0</v>
+      </c>
+      <c r="L723">
+        <v>13.574999999999999</v>
+      </c>
+      <c r="N723">
+        <v>0.75</v>
+      </c>
+      <c r="P723">
+        <v>14.625</v>
+      </c>
+      <c r="Q723" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="724" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A724" t="s">
+        <v>92</v>
+      </c>
+      <c r="B724">
+        <v>-35.632150000000003</v>
+      </c>
+      <c r="C724">
+        <v>138.48339999999999</v>
+      </c>
+      <c r="D724" s="2">
+        <v>46096</v>
+      </c>
+      <c r="E724" s="20">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="G724">
+        <v>0.15</v>
+      </c>
+      <c r="H724">
+        <v>0.1</v>
+      </c>
+      <c r="I724">
+        <v>1.6</v>
+      </c>
+      <c r="J724">
+        <v>0</v>
+      </c>
+      <c r="L724">
+        <v>18.600000000000001</v>
+      </c>
+      <c r="O724">
+        <v>0.1</v>
+      </c>
+      <c r="P724">
+        <v>20.550000000000004</v>
+      </c>
+      <c r="Q724" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="725" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A725" t="s">
+        <v>397</v>
+      </c>
+      <c r="B725">
+        <v>-35.521971999999998</v>
+      </c>
+      <c r="C725">
+        <v>138.18543600000001</v>
+      </c>
+      <c r="D725" s="2">
+        <v>46096</v>
+      </c>
+      <c r="E725" s="20">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="F725">
+        <v>0</v>
+      </c>
+      <c r="I725">
+        <v>167</v>
+      </c>
+      <c r="J725">
+        <v>0</v>
+      </c>
+      <c r="L725">
+        <v>222</v>
+      </c>
+      <c r="N725">
+        <v>278</v>
+      </c>
+      <c r="O725">
+        <v>722</v>
+      </c>
+      <c r="P725">
+        <v>1389</v>
+      </c>
+      <c r="Q725" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="726" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A726" t="s">
+        <v>86</v>
+      </c>
+      <c r="B726">
+        <v>-35.540277000000003</v>
+      </c>
+      <c r="C726">
+        <v>138.66416599999999</v>
+      </c>
+      <c r="D726" s="2">
+        <v>46096</v>
+      </c>
+      <c r="G726">
+        <v>167</v>
+      </c>
+      <c r="H726">
+        <v>167</v>
+      </c>
+      <c r="I726">
+        <v>222</v>
+      </c>
+      <c r="J726">
+        <v>0</v>
+      </c>
+      <c r="L726">
+        <v>1500</v>
+      </c>
+      <c r="N726">
+        <v>222</v>
+      </c>
+      <c r="O726">
+        <v>389</v>
+      </c>
+      <c r="P726">
+        <v>2667</v>
+      </c>
+      <c r="Q726" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="727" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A727" t="s">
+        <v>100</v>
+      </c>
+      <c r="B727">
+        <v>-35.536745000000003</v>
+      </c>
+      <c r="C727">
+        <v>138.6913744</v>
+      </c>
+      <c r="D727" s="2">
+        <v>46096</v>
+      </c>
+      <c r="G727">
+        <v>56</v>
+      </c>
+      <c r="H727">
+        <v>167</v>
+      </c>
+      <c r="I727">
+        <v>167</v>
+      </c>
+      <c r="J727">
+        <v>0</v>
+      </c>
+      <c r="L727">
+        <v>2721</v>
+      </c>
+      <c r="O727">
+        <v>3555</v>
+      </c>
+      <c r="P727">
+        <v>6666</v>
+      </c>
+      <c r="Q727" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="728" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A728" t="s">
+        <v>394</v>
+      </c>
+      <c r="B728">
+        <v>-34.958151000000001</v>
+      </c>
+      <c r="C728">
+        <v>138.503987</v>
+      </c>
+      <c r="D728" s="2">
+        <v>46097</v>
+      </c>
+      <c r="E728" s="20">
+        <v>0.36458333333333331</v>
+      </c>
+      <c r="I728">
+        <v>26.46</v>
+      </c>
+      <c r="J728">
+        <v>0</v>
+      </c>
+      <c r="L728">
+        <v>0.96</v>
+      </c>
+      <c r="N728">
+        <v>0.12</v>
+      </c>
+      <c r="P728">
+        <v>27.540000000000003</v>
+      </c>
+      <c r="Q728" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="729" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A729" t="s">
+        <v>353</v>
+      </c>
+      <c r="B729">
+        <v>-34.860666999999999</v>
+      </c>
+      <c r="C729">
+        <v>138.490938</v>
+      </c>
+      <c r="D729" s="2">
+        <v>46097</v>
+      </c>
+      <c r="E729" s="20">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="I729">
+        <v>0.45</v>
+      </c>
+      <c r="J729">
+        <v>0</v>
+      </c>
+      <c r="L729">
+        <v>186.3</v>
+      </c>
+      <c r="N729">
+        <v>0.15</v>
+      </c>
+      <c r="O729">
+        <v>0.3</v>
+      </c>
+      <c r="P729">
+        <v>187.20000000000002</v>
+      </c>
+      <c r="Q729" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="730" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A730" t="s">
+        <v>316</v>
+      </c>
+      <c r="B730">
+        <v>-35.445188000000002</v>
+      </c>
+      <c r="C730">
+        <v>138.307266</v>
+      </c>
+      <c r="D730" s="2">
+        <v>46097</v>
+      </c>
+      <c r="E730" s="20">
+        <v>0.375</v>
+      </c>
+      <c r="I730">
+        <v>111</v>
+      </c>
+      <c r="J730">
+        <v>0</v>
+      </c>
+      <c r="L730">
+        <v>167</v>
+      </c>
+      <c r="N730">
+        <v>167</v>
+      </c>
+      <c r="O730">
+        <v>1611</v>
+      </c>
+      <c r="P730">
+        <v>2056</v>
+      </c>
+      <c r="Q730" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="731" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A731" t="s">
+        <v>385</v>
+      </c>
+      <c r="B731">
+        <v>-34.759169999999997</v>
+      </c>
+      <c r="C731">
+        <v>137.47612000000001</v>
+      </c>
+      <c r="D731" s="2">
+        <v>46097</v>
+      </c>
+      <c r="E731" s="20">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="J731">
+        <v>0</v>
+      </c>
+      <c r="Q731" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="732" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A732" t="s">
+        <v>392</v>
+      </c>
+      <c r="B732">
+        <v>-35.739091000000002</v>
+      </c>
+      <c r="C732">
+        <v>137.67788400000001</v>
+      </c>
+      <c r="D732" s="2">
+        <v>46098</v>
+      </c>
+      <c r="E732" s="20">
+        <v>17.3</v>
+      </c>
+      <c r="F732">
+        <v>0</v>
+      </c>
+      <c r="G732">
+        <v>0</v>
+      </c>
+      <c r="H732">
+        <v>0</v>
+      </c>
+      <c r="I732">
+        <v>111</v>
+      </c>
+      <c r="J732">
+        <v>0</v>
+      </c>
+      <c r="K732">
+        <v>111</v>
+      </c>
+      <c r="L732">
+        <v>3778</v>
+      </c>
+      <c r="M732">
+        <v>111</v>
+      </c>
+      <c r="N732">
+        <v>2000</v>
+      </c>
+      <c r="O732">
+        <v>222</v>
+      </c>
+      <c r="P732">
+        <v>6333</v>
+      </c>
+      <c r="Q732" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="733" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A733" t="s">
+        <v>380</v>
+      </c>
+      <c r="B733">
+        <v>-35.853555700000001</v>
+      </c>
+      <c r="C733">
+        <v>137.74248499999999</v>
+      </c>
+      <c r="D733" s="2">
+        <v>46098</v>
+      </c>
+      <c r="E733" s="20">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F733">
+        <v>0</v>
+      </c>
+      <c r="G733">
+        <v>0</v>
+      </c>
+      <c r="H733">
+        <v>0</v>
+      </c>
+      <c r="I733">
+        <v>0</v>
+      </c>
+      <c r="J733">
+        <v>0</v>
+      </c>
+      <c r="K733">
+        <v>0</v>
+      </c>
+      <c r="L733">
+        <v>222</v>
+      </c>
+      <c r="M733">
+        <v>0</v>
+      </c>
+      <c r="N733">
+        <v>0</v>
+      </c>
+      <c r="O733">
+        <v>0</v>
+      </c>
+      <c r="P733">
+        <v>222</v>
+      </c>
+      <c r="Q733" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="734" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A734" t="s">
+        <v>398</v>
+      </c>
+      <c r="B734">
+        <v>-34.323770000000003</v>
+      </c>
+      <c r="C734">
+        <v>137.49154999999999</v>
+      </c>
+      <c r="D734" s="2">
+        <v>46098</v>
+      </c>
+      <c r="E734" s="20">
+        <v>0.69444444444444442</v>
+      </c>
+      <c r="J734">
+        <v>0</v>
+      </c>
+      <c r="Q734" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="735" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A735" t="s">
+        <v>361</v>
+      </c>
+      <c r="B735">
+        <v>-34.494970000000002</v>
+      </c>
+      <c r="C735">
+        <v>137.48038</v>
+      </c>
+      <c r="D735" s="2">
+        <v>46098</v>
+      </c>
+      <c r="E735" s="20">
+        <v>0.54861111111111116</v>
+      </c>
+      <c r="J735">
+        <v>0</v>
+      </c>
+      <c r="Q735" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="736" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A736" t="s">
+        <v>305</v>
+      </c>
+      <c r="B736">
+        <v>-34.899749999999997</v>
+      </c>
+      <c r="C736">
+        <v>137.45174</v>
+      </c>
+      <c r="D736" s="2">
+        <v>46098</v>
+      </c>
+      <c r="E736" s="20">
+        <v>0.6875</v>
+      </c>
+      <c r="J736">
+        <v>111</v>
+      </c>
+      <c r="Q736" t="s">
+        <v>268</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q713">
-    <sortCondition ref="D2:D713"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q736">
+    <sortCondition ref="D2:D736"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/MASTER spreadsheet of community summaries.xlsx
+++ b/MASTER spreadsheet of community summaries.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\peri\Dropbox\Delta\Projects\Laboratory\Algal blooms, bacterial counts  for community\For Luke's HAB data display\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AABAF3B9-CB32-4631-B29B-6810A2244EBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABE98617-43F7-42BB-9F70-737927583372}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{9286397E-2757-492B-865A-39B2D6A15FF6}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1489" uniqueCount="400">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1535" uniqueCount="408">
   <si>
     <t>Date</t>
   </si>
@@ -1225,9 +1225,6 @@
     <t>Hardwicke Bay Reef North Shore Rd</t>
   </si>
   <si>
-    <t xml:space="preserve">leSecond Valy Jetty </t>
-  </si>
-  <si>
     <t xml:space="preserve">Second Valley Jetty </t>
   </si>
   <si>
@@ -1256,6 +1253,33 @@
   </si>
   <si>
     <t>Pinks Beach</t>
+  </si>
+  <si>
+    <t>Ocean between Pullen and Seal island</t>
+  </si>
+  <si>
+    <t>LEWK5222</t>
+  </si>
+  <si>
+    <t>Brown Beach</t>
+  </si>
+  <si>
+    <t>Pt Hughes jetty</t>
+  </si>
+  <si>
+    <t>Hardwicke Bay horseshoe reef</t>
+  </si>
+  <si>
+    <t>Stansbury Boat Ramp</t>
+  </si>
+  <si>
+    <t>Port Vincent Marina</t>
+  </si>
+  <si>
+    <t>Second Valley Jetty</t>
+  </si>
+  <si>
+    <t>BOOL5204</t>
   </si>
 </sst>
 </file>
@@ -1302,12 +1326,14 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1723,11 +1749,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F307807-E5C9-4450-88E0-159CBB3E9A67}">
-  <dimension ref="A1:T736"/>
+  <dimension ref="A1:T759"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="39.33203125" customWidth="1"/>
-    <col min="2" max="2" width="12.33203125" customWidth="1"/>
+    <col min="2" max="2" width="17.77734375" customWidth="1"/>
     <col min="3" max="3" width="14.6640625" customWidth="1"/>
     <col min="4" max="4" width="10.44140625" customWidth="1"/>
     <col min="5" max="5" width="16.6640625" style="20" customWidth="1"/>
@@ -25595,7 +25621,7 @@
     </row>
     <row r="670" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A670" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B670">
         <v>-35.739091000000002</v>
@@ -26413,7 +26439,7 @@
     </row>
     <row r="692" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A692" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B692">
         <v>-36.866</v>
@@ -26652,7 +26678,7 @@
     </row>
     <row r="699" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A699" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B699">
         <v>-35.739091000000002</v>
@@ -27049,7 +27075,7 @@
     </row>
     <row r="710" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A710" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B710">
         <v>-35.510620000000003</v>
@@ -27087,7 +27113,7 @@
     </row>
     <row r="711" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A711" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B711">
         <v>-35.793973000000001</v>
@@ -27324,7 +27350,7 @@
     </row>
     <row r="717" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A717" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B717">
         <v>-34.842409000000004</v>
@@ -27452,7 +27478,7 @@
     </row>
     <row r="721" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A721" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B721">
         <v>-35.786641000000003</v>
@@ -27558,7 +27584,7 @@
     </row>
     <row r="723" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A723" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B723">
         <v>-35.532783000000002</v>
@@ -27634,7 +27660,7 @@
     </row>
     <row r="725" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A725" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B725">
         <v>-35.521971999999998</v>
@@ -27754,162 +27780,171 @@
     </row>
     <row r="728" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A728" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="B728">
-        <v>-34.958151000000001</v>
+        <v>-35.557299999999998</v>
       </c>
       <c r="C728">
-        <v>138.503987</v>
+        <v>138.66200000000001</v>
       </c>
       <c r="D728" s="2">
-        <v>46097</v>
-      </c>
-      <c r="E728" s="20">
-        <v>0.36458333333333331</v>
+        <v>46096</v>
+      </c>
+      <c r="G728">
+        <v>222</v>
+      </c>
+      <c r="H728">
+        <v>167</v>
       </c>
       <c r="I728">
-        <v>26.46</v>
+        <v>446</v>
       </c>
       <c r="J728">
         <v>0</v>
       </c>
       <c r="L728">
-        <v>0.96</v>
+        <v>833</v>
       </c>
       <c r="N728">
-        <v>0.12</v>
+        <v>556</v>
+      </c>
+      <c r="O728">
+        <v>1111</v>
       </c>
       <c r="P728">
-        <v>27.540000000000003</v>
+        <v>3335</v>
       </c>
       <c r="Q728" t="s">
-        <v>78</v>
+        <v>129</v>
       </c>
     </row>
     <row r="729" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A729" t="s">
-        <v>353</v>
+        <v>87</v>
       </c>
       <c r="B729">
-        <v>-34.860666999999999</v>
+        <v>-35.573300000000003</v>
       </c>
       <c r="C729">
-        <v>138.490938</v>
+        <v>138.64250000000001</v>
       </c>
       <c r="D729" s="2">
-        <v>46097</v>
-      </c>
-      <c r="E729" s="20">
-        <v>0.35416666666666669</v>
+        <v>46096</v>
+      </c>
+      <c r="G729">
+        <v>56</v>
+      </c>
+      <c r="H729">
+        <v>56</v>
       </c>
       <c r="I729">
-        <v>0.45</v>
+        <v>556</v>
       </c>
       <c r="J729">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="L729">
-        <v>186.3</v>
-      </c>
-      <c r="N729">
-        <v>0.15</v>
+        <v>2167</v>
       </c>
       <c r="O729">
-        <v>0.3</v>
+        <v>7056</v>
       </c>
       <c r="P729">
-        <v>187.20000000000002</v>
+        <v>9891</v>
       </c>
       <c r="Q729" t="s">
-        <v>78</v>
+        <v>129</v>
       </c>
     </row>
     <row r="730" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A730" t="s">
-        <v>316</v>
+        <v>393</v>
       </c>
       <c r="B730">
-        <v>-35.445188000000002</v>
+        <v>-34.958151000000001</v>
       </c>
       <c r="C730">
-        <v>138.307266</v>
+        <v>138.503987</v>
       </c>
       <c r="D730" s="2">
         <v>46097</v>
       </c>
       <c r="E730" s="20">
-        <v>0.375</v>
+        <v>0.36458333333333331</v>
       </c>
       <c r="I730">
-        <v>111</v>
+        <v>26.46</v>
       </c>
       <c r="J730">
         <v>0</v>
       </c>
       <c r="L730">
-        <v>167</v>
+        <v>0.96</v>
       </c>
       <c r="N730">
-        <v>167</v>
-      </c>
-      <c r="O730">
-        <v>1611</v>
+        <v>0.12</v>
       </c>
       <c r="P730">
-        <v>2056</v>
+        <v>27.540000000000003</v>
       </c>
       <c r="Q730" t="s">
-        <v>354</v>
+        <v>78</v>
       </c>
     </row>
     <row r="731" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A731" t="s">
-        <v>385</v>
+        <v>353</v>
       </c>
       <c r="B731">
-        <v>-34.759169999999997</v>
+        <v>-34.860666999999999</v>
       </c>
       <c r="C731">
-        <v>137.47612000000001</v>
+        <v>138.490938</v>
       </c>
       <c r="D731" s="2">
         <v>46097</v>
       </c>
       <c r="E731" s="20">
-        <v>0.58333333333333337</v>
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="I731">
+        <v>0.45</v>
       </c>
       <c r="J731">
         <v>0</v>
       </c>
+      <c r="L731">
+        <v>186.3</v>
+      </c>
+      <c r="N731">
+        <v>0.15</v>
+      </c>
+      <c r="O731">
+        <v>0.3</v>
+      </c>
+      <c r="P731">
+        <v>187.20000000000002</v>
+      </c>
       <c r="Q731" t="s">
-        <v>268</v>
+        <v>78</v>
       </c>
     </row>
     <row r="732" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A732" t="s">
-        <v>392</v>
+        <v>316</v>
       </c>
       <c r="B732">
-        <v>-35.739091000000002</v>
+        <v>-35.445188000000002</v>
       </c>
       <c r="C732">
-        <v>137.67788400000001</v>
+        <v>138.307266</v>
       </c>
       <c r="D732" s="2">
-        <v>46098</v>
+        <v>46097</v>
       </c>
       <c r="E732" s="20">
-        <v>17.3</v>
-      </c>
-      <c r="F732">
-        <v>0</v>
-      </c>
-      <c r="G732">
-        <v>0</v>
-      </c>
-      <c r="H732">
-        <v>0</v>
+        <v>0.375</v>
       </c>
       <c r="I732">
         <v>111</v>
@@ -27917,153 +27952,1000 @@
       <c r="J732">
         <v>0</v>
       </c>
-      <c r="K732">
-        <v>111</v>
-      </c>
       <c r="L732">
-        <v>3778</v>
-      </c>
-      <c r="M732">
-        <v>111</v>
+        <v>167</v>
       </c>
       <c r="N732">
-        <v>2000</v>
+        <v>167</v>
       </c>
       <c r="O732">
-        <v>222</v>
+        <v>1611</v>
       </c>
       <c r="P732">
-        <v>6333</v>
+        <v>2056</v>
       </c>
       <c r="Q732" t="s">
-        <v>151</v>
+        <v>354</v>
       </c>
     </row>
     <row r="733" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A733" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="B733">
-        <v>-35.853555700000001</v>
+        <v>-34.759169999999997</v>
       </c>
       <c r="C733">
-        <v>137.74248499999999</v>
+        <v>137.47612000000001</v>
       </c>
       <c r="D733" s="2">
-        <v>46098</v>
+        <v>46097</v>
       </c>
       <c r="E733" s="20">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F733">
-        <v>0</v>
-      </c>
-      <c r="G733">
-        <v>0</v>
-      </c>
-      <c r="H733">
-        <v>0</v>
-      </c>
-      <c r="I733">
-        <v>0</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="J733">
         <v>0</v>
       </c>
-      <c r="K733">
-        <v>0</v>
-      </c>
-      <c r="L733">
-        <v>222</v>
-      </c>
-      <c r="M733">
-        <v>0</v>
-      </c>
-      <c r="N733">
-        <v>0</v>
-      </c>
-      <c r="O733">
-        <v>0</v>
-      </c>
-      <c r="P733">
-        <v>222</v>
-      </c>
       <c r="Q733" t="s">
-        <v>151</v>
+        <v>268</v>
       </c>
     </row>
     <row r="734" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A734" t="s">
-        <v>398</v>
+        <v>391</v>
       </c>
       <c r="B734">
-        <v>-34.323770000000003</v>
+        <v>-35.739091000000002</v>
       </c>
       <c r="C734">
-        <v>137.49154999999999</v>
+        <v>137.67788400000001</v>
       </c>
       <c r="D734" s="2">
         <v>46098</v>
       </c>
       <c r="E734" s="20">
-        <v>0.69444444444444442</v>
+        <v>17.3</v>
+      </c>
+      <c r="F734">
+        <v>0</v>
+      </c>
+      <c r="G734">
+        <v>0</v>
+      </c>
+      <c r="H734">
+        <v>0</v>
+      </c>
+      <c r="I734">
+        <v>111</v>
       </c>
       <c r="J734">
         <v>0</v>
       </c>
+      <c r="K734">
+        <v>111</v>
+      </c>
+      <c r="L734">
+        <v>3778</v>
+      </c>
+      <c r="M734">
+        <v>111</v>
+      </c>
+      <c r="N734">
+        <v>2000</v>
+      </c>
+      <c r="O734">
+        <v>222</v>
+      </c>
+      <c r="P734">
+        <v>6333</v>
+      </c>
       <c r="Q734" t="s">
-        <v>268</v>
+        <v>151</v>
       </c>
     </row>
     <row r="735" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A735" t="s">
-        <v>361</v>
+        <v>380</v>
       </c>
       <c r="B735">
-        <v>-34.494970000000002</v>
+        <v>-35.853555700000001</v>
       </c>
       <c r="C735">
-        <v>137.48038</v>
+        <v>137.74248499999999</v>
       </c>
       <c r="D735" s="2">
         <v>46098</v>
       </c>
       <c r="E735" s="20">
-        <v>0.54861111111111116</v>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F735">
+        <v>0</v>
+      </c>
+      <c r="G735">
+        <v>0</v>
+      </c>
+      <c r="H735">
+        <v>0</v>
+      </c>
+      <c r="I735">
+        <v>0</v>
       </c>
       <c r="J735">
         <v>0</v>
       </c>
+      <c r="K735">
+        <v>0</v>
+      </c>
+      <c r="L735">
+        <v>222</v>
+      </c>
+      <c r="M735">
+        <v>0</v>
+      </c>
+      <c r="N735">
+        <v>0</v>
+      </c>
+      <c r="O735">
+        <v>0</v>
+      </c>
+      <c r="P735">
+        <v>222</v>
+      </c>
       <c r="Q735" t="s">
-        <v>268</v>
+        <v>151</v>
       </c>
     </row>
     <row r="736" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A736" t="s">
-        <v>305</v>
+        <v>397</v>
       </c>
       <c r="B736">
-        <v>-34.899749999999997</v>
+        <v>-34.323770000000003</v>
       </c>
       <c r="C736">
-        <v>137.45174</v>
+        <v>137.49154999999999</v>
       </c>
       <c r="D736" s="2">
         <v>46098</v>
       </c>
       <c r="E736" s="20">
-        <v>0.6875</v>
+        <v>0.69444444444444442</v>
       </c>
       <c r="J736">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="Q736" t="s">
         <v>268</v>
       </c>
     </row>
+    <row r="737" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A737" t="s">
+        <v>361</v>
+      </c>
+      <c r="B737">
+        <v>-34.494970000000002</v>
+      </c>
+      <c r="C737">
+        <v>137.48038</v>
+      </c>
+      <c r="D737" s="2">
+        <v>46098</v>
+      </c>
+      <c r="E737" s="20">
+        <v>0.54861111111111116</v>
+      </c>
+      <c r="J737">
+        <v>0</v>
+      </c>
+      <c r="Q737" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="738" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A738" t="s">
+        <v>305</v>
+      </c>
+      <c r="B738">
+        <v>-34.899749999999997</v>
+      </c>
+      <c r="C738">
+        <v>137.45174</v>
+      </c>
+      <c r="D738" s="2">
+        <v>46098</v>
+      </c>
+      <c r="E738" s="20">
+        <v>0.6875</v>
+      </c>
+      <c r="J738">
+        <v>111</v>
+      </c>
+      <c r="Q738" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="739" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A739" t="s">
+        <v>402</v>
+      </c>
+      <c r="B739">
+        <v>-34.075042000000003</v>
+      </c>
+      <c r="C739">
+        <v>137.54297600000001</v>
+      </c>
+      <c r="D739" s="2">
+        <v>46098</v>
+      </c>
+      <c r="J739">
+        <v>0</v>
+      </c>
+      <c r="L739">
+        <v>111</v>
+      </c>
+      <c r="O739">
+        <v>56</v>
+      </c>
+      <c r="P739">
+        <v>167</v>
+      </c>
+      <c r="Q739" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="740" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A740" t="s">
+        <v>231</v>
+      </c>
+      <c r="B740">
+        <v>-35.081918000000002</v>
+      </c>
+      <c r="C740">
+        <v>137.74822499999999</v>
+      </c>
+      <c r="D740" s="2">
+        <v>46099</v>
+      </c>
+      <c r="E740" s="20">
+        <v>0.82291666666666663</v>
+      </c>
+      <c r="I740">
+        <v>111</v>
+      </c>
+      <c r="J740">
+        <v>0</v>
+      </c>
+      <c r="L740">
+        <v>500</v>
+      </c>
+      <c r="N740">
+        <v>556</v>
+      </c>
+      <c r="O740">
+        <v>222</v>
+      </c>
+      <c r="P740">
+        <v>1389</v>
+      </c>
+      <c r="Q740" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="741" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A741" t="s">
+        <v>231</v>
+      </c>
+      <c r="B741">
+        <v>-35.081918000000002</v>
+      </c>
+      <c r="C741">
+        <v>137.74822499999999</v>
+      </c>
+      <c r="D741" s="2">
+        <v>46099</v>
+      </c>
+      <c r="E741" s="20">
+        <v>0.82291666666666663</v>
+      </c>
+      <c r="I741">
+        <v>111</v>
+      </c>
+      <c r="J741">
+        <v>0</v>
+      </c>
+      <c r="L741">
+        <v>500</v>
+      </c>
+      <c r="N741">
+        <v>556</v>
+      </c>
+      <c r="O741">
+        <v>222</v>
+      </c>
+      <c r="P741">
+        <v>1389</v>
+      </c>
+      <c r="Q741" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="742" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A742" t="s">
+        <v>378</v>
+      </c>
+      <c r="B742">
+        <v>-34.902070808541197</v>
+      </c>
+      <c r="C742">
+        <v>137.79925776072</v>
+      </c>
+      <c r="D742" s="2">
+        <v>46101</v>
+      </c>
+      <c r="E742" s="20">
+        <v>0.71527777777777779</v>
+      </c>
+      <c r="I742">
+        <v>333</v>
+      </c>
+      <c r="J742">
+        <v>0</v>
+      </c>
+      <c r="L742">
+        <v>56</v>
+      </c>
+      <c r="O742">
+        <v>111</v>
+      </c>
+      <c r="P742">
+        <v>500</v>
+      </c>
+      <c r="Q742" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="743" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A743" t="s">
+        <v>380</v>
+      </c>
+      <c r="B743">
+        <v>-35.853555700000001</v>
+      </c>
+      <c r="C743">
+        <v>137.74248499999999</v>
+      </c>
+      <c r="D743" s="2">
+        <v>46101</v>
+      </c>
+      <c r="E743" s="20">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="F743">
+        <v>0</v>
+      </c>
+      <c r="G743">
+        <v>0</v>
+      </c>
+      <c r="H743">
+        <v>0</v>
+      </c>
+      <c r="I743">
+        <v>0</v>
+      </c>
+      <c r="J743">
+        <v>0</v>
+      </c>
+      <c r="K743">
+        <v>222</v>
+      </c>
+      <c r="L743">
+        <v>333</v>
+      </c>
+      <c r="M743">
+        <v>0</v>
+      </c>
+      <c r="N743">
+        <v>0</v>
+      </c>
+      <c r="O743">
+        <v>0</v>
+      </c>
+      <c r="P743">
+        <v>555</v>
+      </c>
+      <c r="Q743" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="744" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A744" t="s">
+        <v>305</v>
+      </c>
+      <c r="B744">
+        <v>-34.899749999999997</v>
+      </c>
+      <c r="C744">
+        <v>137.45174</v>
+      </c>
+      <c r="D744" s="2">
+        <v>46101</v>
+      </c>
+      <c r="E744" s="20">
+        <v>0.65625</v>
+      </c>
+      <c r="J744">
+        <v>111</v>
+      </c>
+      <c r="Q744" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="745" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A745" t="s">
+        <v>357</v>
+      </c>
+      <c r="B745">
+        <v>-34.672499999999999</v>
+      </c>
+      <c r="C745">
+        <v>137.49298999999999</v>
+      </c>
+      <c r="D745" s="2">
+        <v>46102</v>
+      </c>
+      <c r="J745">
+        <v>0</v>
+      </c>
+      <c r="Q745" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="746" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A746" t="s">
+        <v>79</v>
+      </c>
+      <c r="B746">
+        <v>-34.804662999999998</v>
+      </c>
+      <c r="C746">
+        <v>138.540223</v>
+      </c>
+      <c r="D746" s="2">
+        <v>46102</v>
+      </c>
+      <c r="E746" s="20">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="I746">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="J746">
+        <v>0</v>
+      </c>
+      <c r="L746">
+        <v>43.35</v>
+      </c>
+      <c r="P746">
+        <v>52.650000000000006</v>
+      </c>
+      <c r="Q746" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="747" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A747" t="s">
+        <v>85</v>
+      </c>
+      <c r="B747">
+        <v>-34.873964000000001</v>
+      </c>
+      <c r="C747">
+        <v>138.488134</v>
+      </c>
+      <c r="D747" s="2">
+        <v>46102</v>
+      </c>
+      <c r="E747" s="20">
+        <v>0.45347222222222222</v>
+      </c>
+      <c r="I747">
+        <v>5.85</v>
+      </c>
+      <c r="J747">
+        <v>0</v>
+      </c>
+      <c r="L747">
+        <v>14.7</v>
+      </c>
+      <c r="O747">
+        <v>6.75</v>
+      </c>
+      <c r="P747">
+        <v>27.299999999999997</v>
+      </c>
+      <c r="Q747" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="748" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A748" t="s">
+        <v>270</v>
+      </c>
+      <c r="B748">
+        <v>-34.824044999999998</v>
+      </c>
+      <c r="C748">
+        <v>138.48377600000001</v>
+      </c>
+      <c r="D748" s="2">
+        <v>46102</v>
+      </c>
+      <c r="E748" s="20">
+        <v>0.46180555555555558</v>
+      </c>
+      <c r="G748">
+        <v>0.1</v>
+      </c>
+      <c r="I748">
+        <v>3.5</v>
+      </c>
+      <c r="J748">
+        <v>0</v>
+      </c>
+      <c r="L748">
+        <v>11.8</v>
+      </c>
+      <c r="P748">
+        <v>15.4</v>
+      </c>
+      <c r="Q748" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="749" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A749" t="s">
+        <v>393</v>
+      </c>
+      <c r="B749">
+        <v>-34.958151000000001</v>
+      </c>
+      <c r="C749">
+        <v>138.503987</v>
+      </c>
+      <c r="D749" s="2">
+        <v>46102</v>
+      </c>
+      <c r="E749" s="20">
+        <v>0.43402777777777779</v>
+      </c>
+      <c r="H749">
+        <v>0.3</v>
+      </c>
+      <c r="I749">
+        <v>1.65</v>
+      </c>
+      <c r="J749">
+        <v>0</v>
+      </c>
+      <c r="L749">
+        <v>35.424999999999997</v>
+      </c>
+      <c r="P749">
+        <v>37.375</v>
+      </c>
+      <c r="Q749" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="750" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A750" t="s">
+        <v>179</v>
+      </c>
+      <c r="B750">
+        <v>-35.078539999999997</v>
+      </c>
+      <c r="C750">
+        <v>138.49587</v>
+      </c>
+      <c r="D750" s="2">
+        <v>46102</v>
+      </c>
+      <c r="E750" s="20">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="I750">
+        <v>0.1</v>
+      </c>
+      <c r="J750">
+        <v>0</v>
+      </c>
+      <c r="L750">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="P750">
+        <v>2.4</v>
+      </c>
+      <c r="Q750" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="751" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A751" t="s">
+        <v>211</v>
+      </c>
+      <c r="B751">
+        <v>-35.739091000000002</v>
+      </c>
+      <c r="C751">
+        <v>137.67788400000001</v>
+      </c>
+      <c r="D751" s="2">
+        <v>46103</v>
+      </c>
+      <c r="E751" s="20">
+        <v>0.6875</v>
+      </c>
+      <c r="F751">
+        <v>0</v>
+      </c>
+      <c r="G751">
+        <v>0</v>
+      </c>
+      <c r="H751">
+        <v>0</v>
+      </c>
+      <c r="I751">
+        <v>0</v>
+      </c>
+      <c r="J751">
+        <v>0</v>
+      </c>
+      <c r="K751">
+        <v>111</v>
+      </c>
+      <c r="L751">
+        <v>0</v>
+      </c>
+      <c r="M751">
+        <v>555</v>
+      </c>
+      <c r="N751">
+        <v>0</v>
+      </c>
+      <c r="O751">
+        <v>0</v>
+      </c>
+      <c r="P751">
+        <v>666</v>
+      </c>
+      <c r="Q751" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="752" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A752" t="s">
+        <v>403</v>
+      </c>
+      <c r="B752">
+        <v>-34.903120000000001</v>
+      </c>
+      <c r="C752">
+        <v>137.44969</v>
+      </c>
+      <c r="D752" s="2">
+        <v>46103</v>
+      </c>
+      <c r="E752" s="20">
+        <v>0.62847222222222221</v>
+      </c>
+      <c r="I752">
+        <v>444</v>
+      </c>
+      <c r="J752">
+        <v>0</v>
+      </c>
+      <c r="L752">
+        <v>56</v>
+      </c>
+      <c r="P752">
+        <v>500</v>
+      </c>
+      <c r="Q752" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="753" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A753" t="s">
+        <v>232</v>
+      </c>
+      <c r="B753">
+        <v>-35.054707999999998</v>
+      </c>
+      <c r="C753">
+        <v>137.725145</v>
+      </c>
+      <c r="D753" s="2">
+        <v>46103</v>
+      </c>
+      <c r="E753" s="20">
+        <v>0.63541666666666663</v>
+      </c>
+      <c r="I753">
+        <v>66500</v>
+      </c>
+      <c r="J753">
+        <v>56</v>
+      </c>
+      <c r="L753">
+        <v>3000</v>
+      </c>
+      <c r="O753">
+        <v>667</v>
+      </c>
+      <c r="P753">
+        <v>70167</v>
+      </c>
+      <c r="Q753" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="754" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A754" t="s">
+        <v>404</v>
+      </c>
+      <c r="B754">
+        <v>-34.903466000000002</v>
+      </c>
+      <c r="C754">
+        <v>137.79804799999999</v>
+      </c>
+      <c r="D754" s="2">
+        <v>46103</v>
+      </c>
+      <c r="E754" s="20">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="I754">
+        <v>389</v>
+      </c>
+      <c r="J754">
+        <v>0</v>
+      </c>
+      <c r="L754">
+        <v>500</v>
+      </c>
+      <c r="N754">
+        <v>389</v>
+      </c>
+      <c r="O754">
+        <v>56</v>
+      </c>
+      <c r="P754">
+        <v>1333</v>
+      </c>
+      <c r="Q754" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="755" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A755" t="s">
+        <v>405</v>
+      </c>
+      <c r="B755">
+        <v>-34.765996000000001</v>
+      </c>
+      <c r="C755">
+        <v>137.86211299999999</v>
+      </c>
+      <c r="D755" s="2">
+        <v>46103</v>
+      </c>
+      <c r="E755" s="20">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="I755">
+        <v>0</v>
+      </c>
+      <c r="J755">
+        <v>0</v>
+      </c>
+      <c r="L755">
+        <v>222</v>
+      </c>
+      <c r="N755">
+        <v>389</v>
+      </c>
+      <c r="O755">
+        <v>56</v>
+      </c>
+      <c r="P755">
+        <v>667</v>
+      </c>
+      <c r="Q755" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="756" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A756" t="s">
+        <v>406</v>
+      </c>
+      <c r="B756">
+        <v>-35.510620000000003</v>
+      </c>
+      <c r="C756">
+        <v>138.21679599999999</v>
+      </c>
+      <c r="D756" s="2">
+        <v>46103</v>
+      </c>
+      <c r="I756">
+        <v>167</v>
+      </c>
+      <c r="J756">
+        <v>0</v>
+      </c>
+      <c r="L756">
+        <v>56</v>
+      </c>
+      <c r="N756">
+        <v>1389</v>
+      </c>
+      <c r="O756">
+        <v>722</v>
+      </c>
+      <c r="P756">
+        <v>2334</v>
+      </c>
+      <c r="Q756" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="757" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A757" t="s">
+        <v>401</v>
+      </c>
+      <c r="B757">
+        <v>-35.793973000000001</v>
+      </c>
+      <c r="C757">
+        <v>137.852418</v>
+      </c>
+      <c r="D757" s="2">
+        <v>46104</v>
+      </c>
+      <c r="E757" s="20">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="F757">
+        <v>0</v>
+      </c>
+      <c r="G757">
+        <v>0</v>
+      </c>
+      <c r="H757">
+        <v>1333</v>
+      </c>
+      <c r="I757">
+        <v>1000</v>
+      </c>
+      <c r="J757">
+        <v>0</v>
+      </c>
+      <c r="K757">
+        <v>0</v>
+      </c>
+      <c r="L757">
+        <v>3778</v>
+      </c>
+      <c r="M757">
+        <v>333</v>
+      </c>
+      <c r="N757">
+        <v>333</v>
+      </c>
+      <c r="O757">
+        <v>556</v>
+      </c>
+      <c r="P757">
+        <v>7333</v>
+      </c>
+      <c r="Q757" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="758" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A758" t="s">
+        <v>364</v>
+      </c>
+      <c r="B758">
+        <v>-35.878667100000001</v>
+      </c>
+      <c r="C758">
+        <v>137.6963188</v>
+      </c>
+      <c r="D758" s="2">
+        <v>46104</v>
+      </c>
+      <c r="E758" s="20">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F758">
+        <v>0</v>
+      </c>
+      <c r="G758">
+        <v>0</v>
+      </c>
+      <c r="H758">
+        <v>0</v>
+      </c>
+      <c r="I758">
+        <v>0</v>
+      </c>
+      <c r="J758">
+        <v>0</v>
+      </c>
+      <c r="K758">
+        <v>0</v>
+      </c>
+      <c r="L758">
+        <v>0</v>
+      </c>
+      <c r="M758">
+        <v>0</v>
+      </c>
+      <c r="N758">
+        <v>0</v>
+      </c>
+      <c r="O758">
+        <v>0</v>
+      </c>
+      <c r="P758">
+        <v>0</v>
+      </c>
+      <c r="Q758" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="759" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A759" t="s">
+        <v>316</v>
+      </c>
+      <c r="B759">
+        <v>-35.445188000000002</v>
+      </c>
+      <c r="C759">
+        <v>138.307266</v>
+      </c>
+      <c r="D759" s="2">
+        <v>46104</v>
+      </c>
+      <c r="I759">
+        <v>111</v>
+      </c>
+      <c r="J759">
+        <v>0</v>
+      </c>
+      <c r="L759">
+        <v>0</v>
+      </c>
+      <c r="N759">
+        <v>167</v>
+      </c>
+      <c r="O759">
+        <v>1444</v>
+      </c>
+      <c r="P759">
+        <v>1722</v>
+      </c>
+      <c r="Q759" t="s">
+        <v>407</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q736">
-    <sortCondition ref="D2:D736"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q759">
+    <sortCondition ref="D2:D759"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/MASTER spreadsheet of community summaries.xlsx
+++ b/MASTER spreadsheet of community summaries.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\peri\Dropbox\Delta\Projects\Laboratory\Algal blooms, bacterial counts  for community\For Luke's HAB data display\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABE98617-43F7-42BB-9F70-737927583372}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7AFD42A-7098-47E0-8EC7-8BE6F8D039EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{9286397E-2757-492B-865A-39B2D6A15FF6}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1535" uniqueCount="408">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1597" uniqueCount="411">
   <si>
     <t>Date</t>
   </si>
@@ -625,9 +625,6 @@
     <t>Middleton Bay</t>
   </si>
   <si>
-    <t>Middleton day Street</t>
-  </si>
-  <si>
     <t>Petrel Cove</t>
   </si>
   <si>
@@ -1280,6 +1277,18 @@
   </si>
   <si>
     <t>BOOL5204</t>
+  </si>
+  <si>
+    <t>Victor Yacht Club</t>
+  </si>
+  <si>
+    <t>Big Duck Landing</t>
+  </si>
+  <si>
+    <t>Bluff Boat Ramp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wirrina Cove Marina </t>
   </si>
 </sst>
 </file>
@@ -1749,7 +1758,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F307807-E5C9-4450-88E0-159CBB3E9A67}">
-  <dimension ref="A1:T759"/>
+  <dimension ref="A1:T790"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="39.33203125" customWidth="1"/>
@@ -1785,7 +1794,7 @@
         <v>0</v>
       </c>
       <c r="E1" s="19" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>64</v>
@@ -7033,7 +7042,7 @@
     </row>
     <row r="150" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B150">
         <v>-34.837600000000002</v>
@@ -7319,7 +7328,7 @@
     </row>
     <row r="158" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B158">
         <v>-34.837600000000002</v>
@@ -7558,7 +7567,7 @@
     </row>
     <row r="165" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B165">
         <v>-34.837600000000002</v>
@@ -8522,7 +8531,7 @@
     </row>
     <row r="191" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B191">
         <v>-34.837600000000002</v>
@@ -9618,7 +9627,7 @@
     </row>
     <row r="224" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B224">
         <v>-34.837600000000002</v>
@@ -9907,7 +9916,7 @@
     </row>
     <row r="232" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B232">
         <v>-34.837600000000002</v>
@@ -11433,7 +11442,7 @@
     </row>
     <row r="274" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B274">
         <v>-34.837600000000002</v>
@@ -11853,7 +11862,7 @@
     </row>
     <row r="286" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B286">
         <v>-34.837600000000002</v>
@@ -12158,7 +12167,7 @@
     </row>
     <row r="296" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A296" s="10" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B296" s="10">
         <v>-35.5691281</v>
@@ -12208,7 +12217,7 @@
     </row>
     <row r="297" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A297" s="10" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B297" s="10">
         <v>-35.5691281</v>
@@ -12305,7 +12314,7 @@
     </row>
     <row r="299" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
-        <v>189</v>
+        <v>212</v>
       </c>
       <c r="B299">
         <v>-35.515507999999997</v>
@@ -12385,7 +12394,7 @@
     </row>
     <row r="303" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B303">
         <v>-35.592393000000001</v>
@@ -12425,7 +12434,7 @@
     </row>
     <row r="305" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B305">
         <v>-35.638637000000003</v>
@@ -12489,7 +12498,7 @@
     </row>
     <row r="307" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B307">
         <v>-34.933939000000002</v>
@@ -12524,7 +12533,7 @@
     </row>
     <row r="308" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B308">
         <v>-34.191187999999997</v>
@@ -12559,7 +12568,7 @@
     </row>
     <row r="309" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B309">
         <v>-34.606234999999998</v>
@@ -12632,7 +12641,7 @@
     </row>
     <row r="311" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A311" s="10" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B311" s="10">
         <v>-35.793615000000003</v>
@@ -12680,7 +12689,7 @@
     </row>
     <row r="312" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A312" s="9" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B312" s="9">
         <v>-35.787857600000002</v>
@@ -12730,7 +12739,7 @@
     </row>
     <row r="313" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A313" s="10" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B313" s="10">
         <v>-35.593628899999999</v>
@@ -12780,7 +12789,7 @@
     </row>
     <row r="314" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A314" s="9" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B314" s="10">
         <v>-35.5909288</v>
@@ -12830,7 +12839,7 @@
     </row>
     <row r="315" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B315">
         <v>-35.610827999999998</v>
@@ -12859,7 +12868,7 @@
     </row>
     <row r="316" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B316">
         <v>-35.588391000000001</v>
@@ -12894,7 +12903,7 @@
     </row>
     <row r="317" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A317" s="10" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B317" s="10">
         <v>-35.802792599999997</v>
@@ -12944,7 +12953,7 @@
     </row>
     <row r="318" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A318" s="9" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B318" s="9">
         <v>-35.787857600000002</v>
@@ -12994,7 +13003,7 @@
     </row>
     <row r="319" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A319" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B319" s="10">
         <v>-35.781898699999999</v>
@@ -13088,7 +13097,7 @@
     </row>
     <row r="321" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B321">
         <v>-35.802792599999997</v>
@@ -13138,7 +13147,7 @@
     </row>
     <row r="322" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B322">
         <v>-35.8026926</v>
@@ -13188,7 +13197,7 @@
     </row>
     <row r="323" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B323">
         <v>-35.671777499999997</v>
@@ -13273,7 +13282,7 @@
     </row>
     <row r="325" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B325">
         <v>-34.940480000000001</v>
@@ -13343,7 +13352,7 @@
     </row>
     <row r="327" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B327">
         <v>-35.793615000000003</v>
@@ -13463,7 +13472,7 @@
     </row>
     <row r="330" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B330">
         <v>-35.581816000000003</v>
@@ -13533,7 +13542,7 @@
     </row>
     <row r="332" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B332">
         <v>-35.7391796</v>
@@ -13583,7 +13592,7 @@
     </row>
     <row r="333" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B333">
         <v>-35.789543199999997</v>
@@ -13633,7 +13642,7 @@
     </row>
     <row r="334" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B334">
         <v>-35.799307599999999</v>
@@ -13680,7 +13689,7 @@
     </row>
     <row r="335" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B335">
         <v>-35.515507999999997</v>
@@ -13760,7 +13769,7 @@
     </row>
     <row r="339" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B339">
         <v>-35.632100000000001</v>
@@ -13780,7 +13789,7 @@
     </row>
     <row r="340" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B340">
         <v>-35.549100000000003</v>
@@ -13800,7 +13809,7 @@
     </row>
     <row r="341" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B341">
         <v>-35.515507999999997</v>
@@ -13860,7 +13869,7 @@
     </row>
     <row r="344" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B344">
         <v>-35.549100000000003</v>
@@ -13880,7 +13889,7 @@
     </row>
     <row r="345" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B345">
         <v>-35.592393000000001</v>
@@ -14049,7 +14058,7 @@
     </row>
     <row r="350" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B350">
         <v>-35.054707999999998</v>
@@ -14079,12 +14088,12 @@
         <v>47889</v>
       </c>
       <c r="Q350" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="351" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B351">
         <v>-35.719856700000001</v>
@@ -14134,7 +14143,7 @@
     </row>
     <row r="352" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B352">
         <v>-35.120863999999997</v>
@@ -14272,7 +14281,7 @@
     </row>
     <row r="355" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B355">
         <v>-35.738910099999998</v>
@@ -14322,7 +14331,7 @@
     </row>
     <row r="356" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B356">
         <v>-35.509267000000001</v>
@@ -14351,7 +14360,7 @@
     </row>
     <row r="357" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B357">
         <v>-35.509166999999998</v>
@@ -14386,7 +14395,7 @@
     </row>
     <row r="358" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B358">
         <v>-35.638145999999999</v>
@@ -14436,7 +14445,7 @@
     </row>
     <row r="359" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A359" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B359">
         <v>-35.671809099999997</v>
@@ -14597,7 +14606,7 @@
     </row>
     <row r="363" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B363">
         <v>-34.180396000000002</v>
@@ -14638,7 +14647,7 @@
     </row>
     <row r="364" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A364" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B364">
         <v>-34.176642000000001</v>
@@ -14670,7 +14679,7 @@
     </row>
     <row r="365" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A365" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B365">
         <v>-34.322853000000002</v>
@@ -14708,7 +14717,7 @@
     </row>
     <row r="366" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A366" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B366">
         <v>-34.377982000000003</v>
@@ -14746,7 +14755,7 @@
     </row>
     <row r="367" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A367" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B367">
         <v>-35.515507999999997</v>
@@ -14838,7 +14847,7 @@
     </row>
     <row r="371" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A371" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B371">
         <v>-35.638637000000003</v>
@@ -14861,7 +14870,7 @@
     </row>
     <row r="372" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A372" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B372">
         <v>-35.558100000000003</v>
@@ -14928,7 +14937,7 @@
     </row>
     <row r="374" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A374" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B374">
         <v>-35.093015000000001</v>
@@ -14958,7 +14967,7 @@
         <v>2444</v>
       </c>
       <c r="Q374" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="375" spans="1:17" x14ac:dyDescent="0.3">
@@ -15080,7 +15089,7 @@
     </row>
     <row r="378" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A378" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B378">
         <v>-35.6048446</v>
@@ -15115,7 +15124,7 @@
     </row>
     <row r="379" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A379" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B379">
         <v>-35.608333000000002</v>
@@ -15182,7 +15191,7 @@
     </row>
     <row r="381" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A381" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B381">
         <v>-35.63158</v>
@@ -15217,7 +15226,7 @@
     </row>
     <row r="382" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A382" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B382">
         <v>-35.61</v>
@@ -15296,7 +15305,7 @@
     </row>
     <row r="384" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A384" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B384">
         <v>-34.940480000000001</v>
@@ -15378,7 +15387,7 @@
     </row>
     <row r="386" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A386" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B386">
         <v>-35.081918000000002</v>
@@ -15408,12 +15417,12 @@
         <v>2389</v>
       </c>
       <c r="Q386" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="387" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A387" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B387">
         <v>-35.054707999999998</v>
@@ -15440,12 +15449,12 @@
         <v>205403</v>
       </c>
       <c r="Q387" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="388" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A388" s="10" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B388" s="10">
         <v>-35.586970000000001</v>
@@ -15495,7 +15504,7 @@
     </row>
     <row r="389" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A389" s="10" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B389" s="10">
         <v>-35.586869999999998</v>
@@ -15545,7 +15554,7 @@
     </row>
     <row r="390" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A390" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B390">
         <v>-35.115375999999998</v>
@@ -15575,12 +15584,12 @@
         <v>4444</v>
       </c>
       <c r="Q390" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="391" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A391" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B391">
         <v>-35.465475320000003</v>
@@ -15630,7 +15639,7 @@
     </row>
     <row r="392" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A392" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B392">
         <v>-35.788755899999998</v>
@@ -15680,7 +15689,7 @@
     </row>
     <row r="393" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A393" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B393">
         <v>-35.784914800000003</v>
@@ -15730,7 +15739,7 @@
     </row>
     <row r="394" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A394" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B394">
         <v>-35.054707999999998</v>
@@ -15754,12 +15763,12 @@
         <v>396000</v>
       </c>
       <c r="Q394" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="395" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A395" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B395">
         <v>-35.082030000000003</v>
@@ -15859,7 +15868,7 @@
     </row>
     <row r="397" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A397" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B397">
         <v>-35.788755899999998</v>
@@ -15909,7 +15918,7 @@
     </row>
     <row r="398" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A398" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B398">
         <v>-35.054707999999998</v>
@@ -15936,12 +15945,12 @@
         <v>150500</v>
       </c>
       <c r="Q398" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="399" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A399" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B399">
         <v>-35.081918000000002</v>
@@ -15971,7 +15980,7 @@
         <v>3778</v>
       </c>
       <c r="Q399" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="400" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.3">
@@ -16026,7 +16035,7 @@
     </row>
     <row r="401" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A401" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B401">
         <v>-34.824044999999998</v>
@@ -16076,7 +16085,7 @@
     </row>
     <row r="402" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A402" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B402">
         <v>-35.788755899999998</v>
@@ -16126,7 +16135,7 @@
     </row>
     <row r="403" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A403" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B403">
         <v>-35.671777499999997</v>
@@ -16176,7 +16185,7 @@
     </row>
     <row r="404" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A404" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B404">
         <v>-35.054707999999998</v>
@@ -16206,12 +16215,12 @@
         <v>88000</v>
       </c>
       <c r="Q404" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="405" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A405" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B405">
         <v>-35.793615000000003</v>
@@ -16261,7 +16270,7 @@
     </row>
     <row r="406" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A406" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B406">
         <v>-35.654400000000003</v>
@@ -16281,7 +16290,7 @@
     </row>
     <row r="407" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A407" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B407">
         <v>-35.371586999999998</v>
@@ -16334,7 +16343,7 @@
     </row>
     <row r="408" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A408" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B408">
         <v>-35.017930999999997</v>
@@ -16387,7 +16396,7 @@
     </row>
     <row r="409" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A409" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B409">
         <v>-33.677014</v>
@@ -16414,12 +16423,12 @@
         <v>2556</v>
       </c>
       <c r="Q409" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="410" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A410" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B410">
         <v>-35.032207</v>
@@ -16472,7 +16481,7 @@
     </row>
     <row r="411" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A411" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B411">
         <v>-34.765895999999998</v>
@@ -16502,12 +16511,12 @@
         <v>3277</v>
       </c>
       <c r="Q411" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="412" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A412" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B412">
         <v>-34.765996000000001</v>
@@ -16537,7 +16546,7 @@
         <v>3222</v>
       </c>
       <c r="Q412" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="413" spans="1:17" x14ac:dyDescent="0.3">
@@ -16615,7 +16624,7 @@
     </row>
     <row r="415" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A415" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B415">
         <v>-35.515507999999997</v>
@@ -16675,7 +16684,7 @@
     </row>
     <row r="418" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A418" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B418">
         <v>-35.592393000000001</v>
@@ -16715,7 +16724,7 @@
     </row>
     <row r="420" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A420" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B420">
         <v>-35.558100000000003</v>
@@ -16735,7 +16744,7 @@
     </row>
     <row r="421" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A421" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B421">
         <v>-35.793615000000003</v>
@@ -16785,7 +16794,7 @@
     </row>
     <row r="422" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A422" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B422">
         <v>-34.824044999999998</v>
@@ -16891,7 +16900,7 @@
     </row>
     <row r="424" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A424" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B424">
         <v>-35.193919999999999</v>
@@ -16944,7 +16953,7 @@
     </row>
     <row r="425" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A425" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B425">
         <v>-35.308790000000002</v>
@@ -16997,7 +17006,7 @@
     </row>
     <row r="426" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A426" s="10" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B426" s="9">
         <v>-35.787201000000003</v>
@@ -17047,7 +17056,7 @@
     </row>
     <row r="427" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A427" s="10" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B427" s="12">
         <v>-35.787233399999998</v>
@@ -17097,7 +17106,7 @@
     </row>
     <row r="428" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A428" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B428">
         <v>-35.093021</v>
@@ -17127,12 +17136,12 @@
         <v>2889</v>
       </c>
       <c r="Q428" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="429" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A429" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B429">
         <v>-35.115721999999998</v>
@@ -17162,12 +17171,12 @@
         <v>4722</v>
       </c>
       <c r="Q429" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="430" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A430" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B430">
         <v>-35.427987000000002</v>
@@ -17273,7 +17282,7 @@
     </row>
     <row r="432" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A432" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B432">
         <v>-34.860666999999999</v>
@@ -17326,7 +17335,7 @@
     </row>
     <row r="433" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A433" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B433">
         <v>-34.873964000000001</v>
@@ -17379,7 +17388,7 @@
     </row>
     <row r="434" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A434" s="10" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B434" s="10">
         <v>-35.622483199999998</v>
@@ -17429,7 +17438,7 @@
     </row>
     <row r="435" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A435" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B435">
         <v>-35.081834999999998</v>
@@ -17459,12 +17468,12 @@
         <v>2389</v>
       </c>
       <c r="Q435" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="436" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A436" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B436">
         <v>-35.054707999999998</v>
@@ -17491,7 +17500,7 @@
         <v>110000</v>
       </c>
       <c r="Q436" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="437" spans="1:17" x14ac:dyDescent="0.3">
@@ -17572,7 +17581,7 @@
     </row>
     <row r="439" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A439" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B439">
         <v>-35.269129</v>
@@ -17602,7 +17611,7 @@
         <v>7778</v>
       </c>
       <c r="Q439" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="440" spans="1:17" x14ac:dyDescent="0.3">
@@ -17660,7 +17669,7 @@
     </row>
     <row r="441" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A441" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B441">
         <v>-34.838619999999999</v>
@@ -17713,7 +17722,7 @@
     </row>
     <row r="442" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A442" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B442">
         <v>-34.824044999999998</v>
@@ -17749,7 +17758,7 @@
         <v>5.4</v>
       </c>
       <c r="M442" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="N442">
         <v>0.1</v>
@@ -17766,7 +17775,7 @@
     </row>
     <row r="443" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A443" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B443">
         <v>-34.873964000000001</v>
@@ -17819,7 +17828,7 @@
     </row>
     <row r="444" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A444" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B444">
         <v>-34.860666999999999</v>
@@ -17872,7 +17881,7 @@
     </row>
     <row r="445" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A445" s="10" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B445" s="9">
         <v>-35.787201000000003</v>
@@ -17922,7 +17931,7 @@
     </row>
     <row r="446" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A446" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B446">
         <v>-33.926485999999997</v>
@@ -18001,7 +18010,7 @@
     </row>
     <row r="448" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A448" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B448">
         <v>-35.738910099999998</v>
@@ -18051,7 +18060,7 @@
     </row>
     <row r="449" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A449" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B449">
         <v>-35.193919999999999</v>
@@ -18092,7 +18101,7 @@
     </row>
     <row r="450" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A450" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B450">
         <v>-35.054707999999998</v>
@@ -18119,12 +18128,12 @@
         <v>122667</v>
       </c>
       <c r="Q450" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="451" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A451" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B451">
         <v>-35.523274000000001</v>
@@ -18151,12 +18160,12 @@
         <v>19500</v>
       </c>
       <c r="Q451" s="10" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="452" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A452" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B452">
         <v>-35.793615000000003</v>
@@ -18206,7 +18215,7 @@
     </row>
     <row r="453" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A453" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B453">
         <v>-34.873964000000001</v>
@@ -18244,7 +18253,7 @@
     </row>
     <row r="454" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A454" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B454">
         <v>-34.860666999999999</v>
@@ -18279,7 +18288,7 @@
     </row>
     <row r="455" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A455" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B455">
         <v>-34.908026999999997</v>
@@ -18323,7 +18332,7 @@
     </row>
     <row r="456" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A456" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B456">
         <v>-35.242910000000002</v>
@@ -18361,7 +18370,7 @@
     </row>
     <row r="457" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A457" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B457">
         <v>-35.668842900000001</v>
@@ -18411,7 +18420,7 @@
     </row>
     <row r="458" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A458" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B458">
         <v>-35.789543199999997</v>
@@ -18505,7 +18514,7 @@
     </row>
     <row r="460" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A460" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B460">
         <v>-35.085709299999998</v>
@@ -18550,12 +18559,12 @@
         <v>6333</v>
       </c>
       <c r="Q460" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="461" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A461" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B461">
         <v>-35.521411999999998</v>
@@ -18582,12 +18591,12 @@
         <v>1167</v>
       </c>
       <c r="Q461" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="462" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A462" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B462">
         <v>-32.486960000000003</v>
@@ -18611,12 +18620,12 @@
         <v>1666</v>
       </c>
       <c r="Q462" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="463" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A463" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B463">
         <v>-32.48724</v>
@@ -18640,12 +18649,12 @@
         <v>1049</v>
       </c>
       <c r="Q463" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="464" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A464" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B464">
         <v>-32.490589999999997</v>
@@ -18669,12 +18678,12 @@
         <v>1358</v>
       </c>
       <c r="Q464" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="465" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A465" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B465">
         <v>-35.579300000000003</v>
@@ -18712,7 +18721,7 @@
     </row>
     <row r="466" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A466" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B466">
         <v>-35.585419999999999</v>
@@ -18747,7 +18756,7 @@
     </row>
     <row r="467" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A467" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B467">
         <v>-35.570399999999999</v>
@@ -18782,7 +18791,7 @@
     </row>
     <row r="468" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A468" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B468">
         <v>-35.787201000000003</v>
@@ -18832,7 +18841,7 @@
     </row>
     <row r="469" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A469" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B469">
         <v>-35.787233000000001</v>
@@ -18879,7 +18888,7 @@
     </row>
     <row r="470" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A470" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B470">
         <v>-34.804662999999998</v>
@@ -18917,7 +18926,7 @@
     </row>
     <row r="471" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A471" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B471">
         <v>-34.824044999999998</v>
@@ -18989,7 +18998,7 @@
     </row>
     <row r="473" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A473" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B473">
         <v>-34.860666999999999</v>
@@ -19028,7 +19037,7 @@
     </row>
     <row r="474" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A474" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B474">
         <v>-34.838619999999999</v>
@@ -19064,7 +19073,7 @@
     </row>
     <row r="475" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A475" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B475">
         <v>-34.907184999999998</v>
@@ -19094,13 +19103,13 @@
         <v>5556</v>
       </c>
       <c r="Q475" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="T475" s="2"/>
     </row>
     <row r="476" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A476" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B476">
         <v>-35.092928999999998</v>
@@ -19130,13 +19139,13 @@
         <v>3944</v>
       </c>
       <c r="Q476" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="T476" s="2"/>
     </row>
     <row r="477" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A477" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B477">
         <v>-35.115721999999998</v>
@@ -19166,13 +19175,13 @@
         <v>2445</v>
       </c>
       <c r="Q477" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="T477" s="2"/>
     </row>
     <row r="478" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A478" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B478">
         <v>-34.860666999999999</v>
@@ -19220,7 +19229,7 @@
     </row>
     <row r="479" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A479" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B479">
         <v>-34.827359999999999</v>
@@ -19235,13 +19244,13 @@
         <v>0</v>
       </c>
       <c r="Q479" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="T479" s="2"/>
     </row>
     <row r="480" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A480" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B480">
         <v>-35.739091000000002</v>
@@ -19292,7 +19301,7 @@
     </row>
     <row r="481" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A481" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B481">
         <v>-34.827600699999998</v>
@@ -19331,7 +19340,7 @@
     </row>
     <row r="482" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A482" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B482">
         <v>-34.226579999999998</v>
@@ -19367,7 +19376,7 @@
     </row>
     <row r="483" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A483" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B483">
         <v>-34.917679100000001</v>
@@ -19391,13 +19400,13 @@
         <v>667</v>
       </c>
       <c r="Q483" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="T483" s="2"/>
     </row>
     <row r="484" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A484" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B484">
         <v>-34.929459999999999</v>
@@ -19412,13 +19421,13 @@
         <v>0</v>
       </c>
       <c r="Q484" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="T484" s="2"/>
     </row>
     <row r="485" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A485" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B485">
         <v>-34.970672</v>
@@ -19451,13 +19460,13 @@
         <v>19555</v>
       </c>
       <c r="Q485" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="T485" s="2"/>
     </row>
     <row r="486" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A486" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B486">
         <v>-35.011718100000003</v>
@@ -19490,13 +19499,13 @@
         <v>1779</v>
       </c>
       <c r="Q486" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="T486" s="2"/>
     </row>
     <row r="487" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A487" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B487">
         <v>-34.953057899999997</v>
@@ -19526,12 +19535,12 @@
         <v>29333</v>
       </c>
       <c r="Q487" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="488" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A488" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B488">
         <v>-34.906165799999997</v>
@@ -19564,12 +19573,12 @@
         <v>10222</v>
       </c>
       <c r="Q488" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="489" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A489" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B489">
         <v>-35.511031000000003</v>
@@ -19596,7 +19605,7 @@
         <v>4666</v>
       </c>
       <c r="Q489" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="490" spans="1:20" x14ac:dyDescent="0.3">
@@ -19631,7 +19640,7 @@
         <v>2723</v>
       </c>
       <c r="Q490" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="491" spans="1:20" x14ac:dyDescent="0.3">
@@ -19700,7 +19709,7 @@
     </row>
     <row r="493" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A493" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B493">
         <v>-34.895150000000001</v>
@@ -19715,12 +19724,12 @@
         <v>306</v>
       </c>
       <c r="Q493" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="494" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A494" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B494">
         <v>-34.918889999999998</v>
@@ -19735,12 +19744,12 @@
         <v>0</v>
       </c>
       <c r="Q494" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="495" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A495" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B495">
         <v>-34.933680000000003</v>
@@ -19755,12 +19764,12 @@
         <v>0</v>
       </c>
       <c r="Q495" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="496" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A496" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B496">
         <v>-34.672490000000003</v>
@@ -19775,12 +19784,12 @@
         <v>0</v>
       </c>
       <c r="Q496" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="497" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A497" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B497">
         <v>-35.7987082</v>
@@ -19869,12 +19878,12 @@
         <v>1026</v>
       </c>
       <c r="Q498" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="499" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A499" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B499">
         <v>-35.110022000000001</v>
@@ -19904,12 +19913,12 @@
         <v>1888</v>
       </c>
       <c r="Q499" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="500" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A500" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B500">
         <v>-34.92989</v>
@@ -19927,12 +19936,12 @@
         <v>28</v>
       </c>
       <c r="Q500" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="501" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A501" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B501">
         <v>-34.933680000000003</v>
@@ -19947,12 +19956,12 @@
         <v>0</v>
       </c>
       <c r="Q501" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="502" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A502" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B502">
         <v>-34.630270000000003</v>
@@ -19979,12 +19988,12 @@
         <v>2889</v>
       </c>
       <c r="Q502" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="503" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A503" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B503">
         <v>-34.629179999999998</v>
@@ -20011,12 +20020,12 @@
         <v>945</v>
       </c>
       <c r="Q503" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="504" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A504" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B504">
         <v>-34.628860000000003</v>
@@ -20043,12 +20052,12 @@
         <v>723</v>
       </c>
       <c r="Q504" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="505" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A505" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B505">
         <v>-35.515507999999997</v>
@@ -20168,7 +20177,7 @@
     </row>
     <row r="509" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A509" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B509">
         <v>-35.592393000000001</v>
@@ -20220,7 +20229,7 @@
     </row>
     <row r="511" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A511" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B511">
         <v>-35.557977000000001</v>
@@ -20246,7 +20255,7 @@
     </row>
     <row r="512" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A512" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B512">
         <v>-34.630270000000003</v>
@@ -20273,12 +20282,12 @@
         <v>2889</v>
       </c>
       <c r="Q512" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="513" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A513" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B513">
         <v>-34.630270000000003</v>
@@ -20305,12 +20314,12 @@
         <v>2889</v>
       </c>
       <c r="Q513" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="514" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A514" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B514">
         <v>-35.119663000000003</v>
@@ -20416,7 +20425,7 @@
     </row>
     <row r="516" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A516" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B516">
         <v>-35.031672</v>
@@ -20469,7 +20478,7 @@
     </row>
     <row r="517" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A517" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B517">
         <v>-35.762554199999997</v>
@@ -20519,7 +20528,7 @@
     </row>
     <row r="518" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A518" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B518">
         <v>-35.511125999999997</v>
@@ -20549,12 +20558,12 @@
         <v>4334</v>
       </c>
       <c r="Q518" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="519" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A519" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B519">
         <v>-35.793973000000001</v>
@@ -20604,7 +20613,7 @@
     </row>
     <row r="520" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A520" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B520">
         <v>-35.132868999999999</v>
@@ -20634,12 +20643,12 @@
         <v>1667</v>
       </c>
       <c r="Q520" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="521" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A521" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B521">
         <v>-34.899749999999997</v>
@@ -20666,12 +20675,12 @@
         <v>194</v>
       </c>
       <c r="Q521" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="522" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A522" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B522">
         <v>-35.054707999999998</v>
@@ -20701,12 +20710,12 @@
         <v>224333</v>
       </c>
       <c r="Q522" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="523" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A523" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B523">
         <v>-33.040959000000001</v>
@@ -20733,12 +20742,12 @@
         <v>3335</v>
       </c>
       <c r="Q523" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="524" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A524" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B524">
         <v>-33.917679999999997</v>
@@ -20768,12 +20777,12 @@
         <v>4334</v>
       </c>
       <c r="Q524" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="525" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A525" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B525">
         <v>-33.922530000000002</v>
@@ -20803,12 +20812,12 @@
         <v>12722</v>
       </c>
       <c r="Q525" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="526" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A526" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B526">
         <v>-33.912199999999999</v>
@@ -20838,12 +20847,12 @@
         <v>2334</v>
       </c>
       <c r="Q526" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="527" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A527" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B527">
         <v>-34.929459999999999</v>
@@ -20861,12 +20870,12 @@
         <v>0</v>
       </c>
       <c r="Q527" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="528" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A528" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B528">
         <v>-34.933680000000003</v>
@@ -20884,12 +20893,12 @@
         <v>0</v>
       </c>
       <c r="Q528" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="529" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A529" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B529">
         <v>-35.594605999999999</v>
@@ -20922,12 +20931,12 @@
         <v>10334</v>
       </c>
       <c r="Q529" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="530" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A530" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B530">
         <v>-35.510753999999999</v>
@@ -20960,7 +20969,7 @@
         <v>5333</v>
       </c>
       <c r="Q530" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="531" spans="1:17" x14ac:dyDescent="0.3">
@@ -21093,7 +21102,7 @@
     </row>
     <row r="535" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A535" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B535">
         <v>-35.6048446</v>
@@ -21128,7 +21137,7 @@
     </row>
     <row r="536" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A536" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B536">
         <v>-35.63158</v>
@@ -21163,7 +21172,7 @@
     </row>
     <row r="537" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A537" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B537">
         <v>-35.612963000000001</v>
@@ -21201,7 +21210,7 @@
     </row>
     <row r="538" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A538" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B538">
         <v>-34.911830000000002</v>
@@ -21225,12 +21234,12 @@
         <v>1723</v>
       </c>
       <c r="Q538" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="539" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A539" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B539">
         <v>-35.089612000000002</v>
@@ -21260,12 +21269,12 @@
         <v>2667</v>
       </c>
       <c r="Q539" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="540" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A540" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B540">
         <v>-34.994472000000002</v>
@@ -21292,12 +21301,12 @@
         <v>667</v>
       </c>
       <c r="Q540" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="541" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A541" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B541">
         <v>-35.522570000000002</v>
@@ -21330,12 +21339,12 @@
         <v>1612</v>
       </c>
       <c r="Q541" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="542" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A542" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B542">
         <v>-34.751460000000002</v>
@@ -21353,12 +21362,12 @@
         <v>0</v>
       </c>
       <c r="Q542" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="543" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A543" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B543">
         <v>-34.804662999999998</v>
@@ -21402,7 +21411,7 @@
     </row>
     <row r="544" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A544" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B544">
         <v>-34.824044999999998</v>
@@ -21499,7 +21508,7 @@
     </row>
     <row r="546" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A546" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B546">
         <v>-34.920539599999998</v>
@@ -21529,12 +21538,12 @@
         <v>8946</v>
       </c>
       <c r="Q546" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="547" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A547" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B547">
         <v>-35.085709299999998</v>
@@ -21561,12 +21570,12 @@
         <v>5888</v>
       </c>
       <c r="Q547" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="548" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A548" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B548">
         <v>-35.445188000000002</v>
@@ -21596,12 +21605,12 @@
         <v>890</v>
       </c>
       <c r="Q548" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="549" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A549" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B549">
         <v>-35.516500000000001</v>
@@ -21627,7 +21636,7 @@
     </row>
     <row r="550" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A550" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B550">
         <v>-35.517899999999997</v>
@@ -21705,7 +21714,7 @@
     </row>
     <row r="553" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A553" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B553">
         <v>-35.5565</v>
@@ -21731,7 +21740,7 @@
     </row>
     <row r="554" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A554" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B554">
         <v>-35.563899999999997</v>
@@ -21757,7 +21766,7 @@
     </row>
     <row r="555" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A555" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B555">
         <v>-35.592599999999997</v>
@@ -21783,7 +21792,7 @@
     </row>
     <row r="556" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A556" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B556">
         <v>-35.634900000000002</v>
@@ -21809,7 +21818,7 @@
     </row>
     <row r="557" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A557" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B557">
         <v>-34.929459999999999</v>
@@ -21827,12 +21836,12 @@
         <v>0</v>
       </c>
       <c r="Q557" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="558" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A558" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B558">
         <v>-34.928570000000001</v>
@@ -21850,12 +21859,12 @@
         <v>0</v>
       </c>
       <c r="Q558" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="559" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A559" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B559">
         <v>-34.901600000000002</v>
@@ -21873,12 +21882,12 @@
         <v>0</v>
       </c>
       <c r="Q559" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="560" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A560" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B560">
         <v>-34.630270000000003</v>
@@ -21911,12 +21920,12 @@
         <v>15888</v>
       </c>
       <c r="Q560" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="561" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A561" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B561">
         <v>-34.629179999999998</v>
@@ -21949,7 +21958,7 @@
         <v>23556</v>
       </c>
       <c r="Q561" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="562" spans="1:17" x14ac:dyDescent="0.3">
@@ -21998,7 +22007,7 @@
     </row>
     <row r="563" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A563" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B563">
         <v>-35.32508</v>
@@ -22028,12 +22037,12 @@
         <v>1167</v>
       </c>
       <c r="Q563" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="564" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A564" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B564">
         <v>-34.903820000000003</v>
@@ -22054,7 +22063,7 @@
         <v>722</v>
       </c>
       <c r="Q564" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="565" spans="1:17" x14ac:dyDescent="0.3">
@@ -22167,7 +22176,7 @@
     </row>
     <row r="568" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A568" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B568">
         <v>-34.911830000000002</v>
@@ -22188,12 +22197,12 @@
         <v>1611</v>
       </c>
       <c r="Q568" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="569" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A569" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B569">
         <v>-34.893770000000004</v>
@@ -22214,12 +22223,12 @@
         <v>389</v>
       </c>
       <c r="Q569" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="570" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A570" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B570" s="13">
         <f>-35.521088</f>
@@ -22254,12 +22263,12 @@
         <v>4556</v>
       </c>
       <c r="Q570" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="571" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A571" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B571">
         <v>-34.495376</v>
@@ -22289,12 +22298,12 @@
         <v>889</v>
       </c>
       <c r="Q571" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="572" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A572" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B572">
         <v>-34.750552999999996</v>
@@ -22321,12 +22330,12 @@
         <v>778</v>
       </c>
       <c r="Q572" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="573" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A573" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B573">
         <v>-34.672504000000004</v>
@@ -22356,12 +22365,12 @@
         <v>1056</v>
       </c>
       <c r="Q573" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="574" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A574" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B574">
         <v>-34.588209999999997</v>
@@ -22388,12 +22397,12 @@
         <v>500</v>
       </c>
       <c r="Q574" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="575" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A575" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B575">
         <v>-34.899749999999997</v>
@@ -22423,12 +22432,12 @@
         <v>5834</v>
       </c>
       <c r="Q575" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="576" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A576" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B576">
         <v>-34.812609999999999</v>
@@ -22446,12 +22455,12 @@
         <v>0</v>
       </c>
       <c r="Q576" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="577" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A577" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B577">
         <v>-34.827359999999999</v>
@@ -22469,12 +22478,12 @@
         <v>0</v>
       </c>
       <c r="Q577" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="578" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A578" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B578">
         <v>-34.672490000000003</v>
@@ -22492,12 +22501,12 @@
         <v>0</v>
       </c>
       <c r="Q578" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="579" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A579" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B579">
         <v>-34.827359999999999</v>
@@ -22541,7 +22550,7 @@
     </row>
     <row r="580" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A580" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B580">
         <v>-34.912934499999999</v>
@@ -22571,12 +22580,12 @@
         <v>6222</v>
       </c>
       <c r="Q580" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="581" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A581" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B581">
         <v>-34.672490000000003</v>
@@ -22594,12 +22603,12 @@
         <v>0</v>
       </c>
       <c r="Q581" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="582" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A582" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B582">
         <v>-34.751460000000002</v>
@@ -22617,12 +22626,12 @@
         <v>0</v>
       </c>
       <c r="Q582" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="583" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A583" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B583">
         <v>-34.831850000000003</v>
@@ -22643,12 +22652,12 @@
         <v>56</v>
       </c>
       <c r="Q583" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="584" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A584" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B584">
         <v>-34.899749999999997</v>
@@ -22678,12 +22687,12 @@
         <v>6889</v>
       </c>
       <c r="Q584" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="585" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A585" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B585">
         <v>-34.920539599999998</v>
@@ -22728,12 +22737,12 @@
         <v>1444</v>
       </c>
       <c r="Q585" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="586" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A586" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B586">
         <v>-34.933680000000003</v>
@@ -22763,12 +22772,12 @@
         <v>10334</v>
       </c>
       <c r="Q586" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="587" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A587" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B587">
         <v>-34.804662999999998</v>
@@ -22821,7 +22830,7 @@
     </row>
     <row r="588" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A588" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B588">
         <v>-34.824044999999998</v>
@@ -22927,7 +22936,7 @@
     </row>
     <row r="590" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A590" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B590">
         <v>-34.860666999999999</v>
@@ -23047,7 +23056,7 @@
     </row>
     <row r="593" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A593" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B593">
         <v>-34.628860000000003</v>
@@ -23080,12 +23089,12 @@
         <v>1279</v>
       </c>
       <c r="Q593" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="594" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A594" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B594">
         <v>-34.519669999999998</v>
@@ -23118,12 +23127,12 @@
         <v>446</v>
       </c>
       <c r="Q594" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="595" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A595" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B595">
         <v>-34.535609999999998</v>
@@ -23147,12 +23156,12 @@
         <v>222</v>
       </c>
       <c r="Q595" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="596" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A596" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B596">
         <v>-34.827359999999999</v>
@@ -23185,12 +23194,12 @@
         <v>13889</v>
       </c>
       <c r="Q596" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="597" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A597" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B597">
         <v>-34.672490000000003</v>
@@ -23220,12 +23229,12 @@
         <v>2111</v>
       </c>
       <c r="Q597" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="598" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A598" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B598">
         <v>-34.890371899999998</v>
@@ -23258,12 +23267,12 @@
         <v>14444</v>
       </c>
       <c r="Q598" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="599" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A599" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B599">
         <v>-35.500242</v>
@@ -23297,12 +23306,12 @@
         <v>611</v>
       </c>
       <c r="Q599" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="600" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A600" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B600">
         <v>-34.672490000000003</v>
@@ -23317,12 +23326,12 @@
         <v>556</v>
       </c>
       <c r="Q600" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="601" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A601" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B601">
         <v>-34.751460000000002</v>
@@ -23337,12 +23346,12 @@
         <v>0</v>
       </c>
       <c r="Q601" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="602" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A602" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B602">
         <v>-34.670960000000001</v>
@@ -23357,12 +23366,12 @@
         <v>1167</v>
       </c>
       <c r="Q602" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="603" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A603" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B603">
         <v>-34.643329999999999</v>
@@ -23377,12 +23386,12 @@
         <v>1333</v>
       </c>
       <c r="Q603" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="604" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A604" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B604">
         <v>-34.586370000000002</v>
@@ -23397,12 +23406,12 @@
         <v>0</v>
       </c>
       <c r="Q604" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="605" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A605" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B605">
         <v>-34.9094768</v>
@@ -23447,7 +23456,7 @@
         <v>8222</v>
       </c>
       <c r="Q605" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="606" spans="1:17" x14ac:dyDescent="0.3">
@@ -23496,7 +23505,7 @@
     </row>
     <row r="607" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A607" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B607">
         <v>-34.899749999999997</v>
@@ -23514,12 +23523,12 @@
         <v>1778</v>
       </c>
       <c r="Q607" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="608" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A608" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B608">
         <v>-34.751460000000002</v>
@@ -23537,12 +23546,12 @@
         <v>2833</v>
       </c>
       <c r="Q608" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="609" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A609" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B609">
         <v>-34.672490000000003</v>
@@ -23560,12 +23569,12 @@
         <v>500</v>
       </c>
       <c r="Q609" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="610" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A610" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B610">
         <v>-34.586370000000002</v>
@@ -23583,12 +23592,12 @@
         <v>0</v>
       </c>
       <c r="Q610" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="611" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A611" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B611">
         <v>-34.507260000000002</v>
@@ -23606,12 +23615,12 @@
         <v>0</v>
       </c>
       <c r="Q611" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="612" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A612" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B612">
         <v>-34.827359999999999</v>
@@ -23629,12 +23638,12 @@
         <v>2000</v>
       </c>
       <c r="Q612" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="613" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A613" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B613">
         <v>-34.899749999999997</v>
@@ -23652,12 +23661,12 @@
         <v>4278</v>
       </c>
       <c r="Q613" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="614" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A614" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B614">
         <v>-34.911830000000002</v>
@@ -23675,12 +23684,12 @@
         <v>0</v>
       </c>
       <c r="Q614" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="615" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A615" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B615">
         <v>-34.899749999999997</v>
@@ -23698,12 +23707,12 @@
         <v>5500</v>
       </c>
       <c r="Q615" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="616" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A616" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B616">
         <v>-34.751460000000002</v>
@@ -23721,12 +23730,12 @@
         <v>222</v>
       </c>
       <c r="Q616" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="617" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A617" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B617">
         <v>-34.672490000000003</v>
@@ -23744,12 +23753,12 @@
         <v>0</v>
       </c>
       <c r="Q617" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="618" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A618" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B618">
         <v>-35.642456000000003</v>
@@ -23787,7 +23796,7 @@
     </row>
     <row r="619" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A619" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B619">
         <v>-34.824044999999998</v>
@@ -23874,7 +23883,7 @@
     </row>
     <row r="621" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A621" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B621">
         <v>-34.860666999999999</v>
@@ -23946,7 +23955,7 @@
     </row>
     <row r="623" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A623" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B623">
         <v>-34.899749999999997</v>
@@ -23964,12 +23973,12 @@
         <v>3889</v>
       </c>
       <c r="Q623" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="624" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A624" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B624">
         <v>-34.899749999999997</v>
@@ -23987,12 +23996,12 @@
         <v>4278</v>
       </c>
       <c r="Q624" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="625" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A625" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B625">
         <v>-34.672490000000003</v>
@@ -24010,12 +24019,12 @@
         <v>333</v>
       </c>
       <c r="Q625" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="626" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A626" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B626">
         <v>-34.66301</v>
@@ -24033,12 +24042,12 @@
         <v>7222</v>
       </c>
       <c r="Q626" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="627" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A627" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B627">
         <v>-34.586370000000002</v>
@@ -24056,12 +24065,12 @@
         <v>222</v>
       </c>
       <c r="Q627" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="628" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A628" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B628">
         <v>-34.52664</v>
@@ -24079,12 +24088,12 @@
         <v>222</v>
       </c>
       <c r="Q628" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="629" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A629" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B629">
         <v>-34.494970000000002</v>
@@ -24102,12 +24111,12 @@
         <v>56</v>
       </c>
       <c r="Q629" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="630" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A630" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B630">
         <v>-35.445188000000002</v>
@@ -24135,12 +24144,12 @@
         <v>0</v>
       </c>
       <c r="Q630" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="631" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A631" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B631">
         <v>-34.637633999999998</v>
@@ -24164,12 +24173,12 @@
         <v>112</v>
       </c>
       <c r="Q631" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="632" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A632" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B632">
         <v>-34.864305100000003</v>
@@ -24193,7 +24202,7 @@
         <v>112</v>
       </c>
       <c r="Q632" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="633" spans="1:17" x14ac:dyDescent="0.3">
@@ -24234,7 +24243,7 @@
     </row>
     <row r="634" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A634" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B634">
         <v>-35.092981999999999</v>
@@ -24264,12 +24273,12 @@
         <v>5482</v>
       </c>
       <c r="Q634" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="635" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A635" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B635">
         <v>-34.672490000000003</v>
@@ -24287,12 +24296,12 @@
         <v>833</v>
       </c>
       <c r="Q635" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="636" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A636" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B636">
         <v>-34.899749999999997</v>
@@ -24310,7 +24319,7 @@
         <v>2611</v>
       </c>
       <c r="Q636" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="637" spans="1:17" x14ac:dyDescent="0.3">
@@ -24397,7 +24406,7 @@
     </row>
     <row r="639" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A639" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B639">
         <v>-34.672490000000003</v>
@@ -24425,12 +24434,12 @@
       <c r="O639" s="1"/>
       <c r="P639" s="1"/>
       <c r="Q639" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="640" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A640" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B640">
         <v>-34.934266999999998</v>
@@ -24463,12 +24472,12 @@
         <v>11723</v>
       </c>
       <c r="Q640" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="641" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A641" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B641">
         <v>-34.910024</v>
@@ -24498,7 +24507,7 @@
         <v>22944</v>
       </c>
       <c r="Q641" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="642" spans="1:17" x14ac:dyDescent="0.3">
@@ -24626,7 +24635,7 @@
     </row>
     <row r="645" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A645" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B645">
         <v>-35.612285999999997</v>
@@ -24667,7 +24676,7 @@
     </row>
     <row r="646" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A646" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B646">
         <v>-34.933680000000003</v>
@@ -24697,12 +24706,12 @@
         <v>8000</v>
       </c>
       <c r="Q646" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="647" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A647" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B647">
         <v>-34.899749999999997</v>
@@ -24730,12 +24739,12 @@
       <c r="O647" s="1"/>
       <c r="P647" s="1"/>
       <c r="Q647" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="648" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A648" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B648">
         <v>-34.911830000000002</v>
@@ -24763,12 +24772,12 @@
       <c r="O648" s="1"/>
       <c r="P648" s="1"/>
       <c r="Q648" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="649" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A649" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B649">
         <v>-34.824044999999998</v>
@@ -24822,7 +24831,7 @@
     </row>
     <row r="650" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A650" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B650">
         <v>-34.860666999999999</v>
@@ -24930,7 +24939,7 @@
     </row>
     <row r="652" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A652" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B652">
         <v>-35.878667100000001</v>
@@ -24983,7 +24992,7 @@
     </row>
     <row r="653" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A653" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B653">
         <v>-34.586370000000002</v>
@@ -25011,12 +25020,12 @@
       <c r="O653" s="1"/>
       <c r="P653" s="1"/>
       <c r="Q653" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="654" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A654" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B654">
         <v>-34.751460000000002</v>
@@ -25044,12 +25053,12 @@
       <c r="O654" s="1"/>
       <c r="P654" s="1"/>
       <c r="Q654" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="655" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A655" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B655">
         <v>-35.853555700000001</v>
@@ -25102,7 +25111,7 @@
     </row>
     <row r="656" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A656" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B656">
         <v>-35.787276900000002</v>
@@ -25155,7 +25164,7 @@
     </row>
     <row r="657" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A657" s="17" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B657">
         <v>-34.776083</v>
@@ -25190,16 +25199,16 @@
         <v>56</v>
       </c>
       <c r="P657" s="17">
-        <f>SUM(F657:I657,K657:O657)</f>
+        <f t="shared" ref="P657:P663" si="0">SUM(F657:I657,K657:O657)</f>
         <v>1111</v>
       </c>
       <c r="Q657" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="658" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A658" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B658">
         <v>-35.515507999999997</v>
@@ -25223,7 +25232,7 @@
         <v>111</v>
       </c>
       <c r="P658">
-        <f>SUM(F658:I658,K658:O658)</f>
+        <f t="shared" si="0"/>
         <v>444</v>
       </c>
       <c r="Q658" t="s">
@@ -25256,7 +25265,7 @@
         <v>0</v>
       </c>
       <c r="P659">
-        <f>SUM(F659:I659,K659:O659)</f>
+        <f t="shared" si="0"/>
         <v>56</v>
       </c>
       <c r="Q659" t="s">
@@ -25289,7 +25298,7 @@
         <v>167</v>
       </c>
       <c r="P660">
-        <f>SUM(F660:I660,K660:O660)</f>
+        <f t="shared" si="0"/>
         <v>167</v>
       </c>
       <c r="Q660" t="s">
@@ -25298,7 +25307,7 @@
     </row>
     <row r="661" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A661" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B661">
         <v>-35.5565</v>
@@ -25322,7 +25331,7 @@
         <v>56</v>
       </c>
       <c r="P661">
-        <f>SUM(F661:I661,K661:O661)</f>
+        <f t="shared" si="0"/>
         <v>112</v>
       </c>
       <c r="Q661" t="s">
@@ -25331,7 +25340,7 @@
     </row>
     <row r="662" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A662" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B662">
         <v>-35.592393000000001</v>
@@ -25355,7 +25364,7 @@
         <v>0</v>
       </c>
       <c r="P662">
-        <f>SUM(F662:I662,K662:O662)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Q662" t="s">
@@ -25364,7 +25373,7 @@
     </row>
     <row r="663" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A663" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B663">
         <v>-35.634602000000001</v>
@@ -25388,7 +25397,7 @@
         <v>222</v>
       </c>
       <c r="P663">
-        <f>SUM(F663:I663,K663:O663)</f>
+        <f t="shared" si="0"/>
         <v>278</v>
       </c>
       <c r="Q663" t="s">
@@ -25397,7 +25406,7 @@
     </row>
     <row r="664" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A664" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B664">
         <v>-34.918303199999997</v>
@@ -25424,12 +25433,12 @@
         <v>223</v>
       </c>
       <c r="Q664" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="665" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A665" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B665">
         <v>-34.911405199999997</v>
@@ -25459,12 +25468,12 @@
         <v>390</v>
       </c>
       <c r="Q665" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="666" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A666" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B666">
         <v>-34.899749999999997</v>
@@ -25494,12 +25503,12 @@
       <c r="O666" s="1"/>
       <c r="P666" s="1"/>
       <c r="Q666" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="667" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A667" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B667">
         <v>-34.82743</v>
@@ -25529,12 +25538,12 @@
       <c r="O667" s="1"/>
       <c r="P667" s="1"/>
       <c r="Q667" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="668" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A668" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B668">
         <v>-34.751460000000002</v>
@@ -25562,7 +25571,7 @@
       <c r="O668" s="1"/>
       <c r="P668" s="1"/>
       <c r="Q668" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="669" spans="1:17" x14ac:dyDescent="0.3">
@@ -25621,7 +25630,7 @@
     </row>
     <row r="670" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A670" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B670">
         <v>-35.739091000000002</v>
@@ -25671,7 +25680,7 @@
     </row>
     <row r="671" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A671" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B671">
         <v>-34.494970000000002</v>
@@ -25699,7 +25708,7 @@
       <c r="O671" s="1"/>
       <c r="P671" s="1"/>
       <c r="Q671" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="672" spans="1:17" x14ac:dyDescent="0.3">
@@ -25758,7 +25767,7 @@
     </row>
     <row r="673" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A673" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B673">
         <v>-35.119663000000003</v>
@@ -25888,7 +25897,7 @@
     </row>
     <row r="676" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A676" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B676">
         <v>-34.759169999999997</v>
@@ -25906,12 +25915,12 @@
         <v>1833</v>
       </c>
       <c r="Q676" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="677" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A677" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B677">
         <v>-34.672490000000003</v>
@@ -25926,12 +25935,12 @@
         <v>333</v>
       </c>
       <c r="Q677" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="678" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A678" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B678">
         <v>-34.494970000000002</v>
@@ -25949,12 +25958,12 @@
         <v>167</v>
       </c>
       <c r="Q678" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="679" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A679" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B679">
         <v>-34.584389999999999</v>
@@ -25972,12 +25981,12 @@
         <v>0</v>
       </c>
       <c r="Q679" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="680" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A680" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B680">
         <v>-34.899749999999997</v>
@@ -25995,7 +26004,7 @@
         <v>4833</v>
       </c>
       <c r="Q680" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="681" spans="1:17" x14ac:dyDescent="0.3">
@@ -26047,7 +26056,7 @@
     </row>
     <row r="682" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A682" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B682">
         <v>-34.902070808541197</v>
@@ -26068,7 +26077,7 @@
         <v>167</v>
       </c>
       <c r="K682" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="L682">
         <v>167</v>
@@ -26083,12 +26092,12 @@
         <v>1390</v>
       </c>
       <c r="Q682" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="683" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A683" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B683">
         <v>-34.933680000000003</v>
@@ -26118,12 +26127,12 @@
         <v>1057</v>
       </c>
       <c r="Q683" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="684" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A684" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B684">
         <v>-34.759169999999997</v>
@@ -26141,12 +26150,12 @@
         <v>1556</v>
       </c>
       <c r="Q684" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="685" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A685" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B685">
         <v>-34.075153</v>
@@ -26184,7 +26193,7 @@
     </row>
     <row r="686" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A686" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B686">
         <v>-35.762554199999997</v>
@@ -26237,7 +26246,7 @@
     </row>
     <row r="687" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A687" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B687">
         <v>-35.853555700000001</v>
@@ -26290,7 +26299,7 @@
     </row>
     <row r="688" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A688" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B688">
         <v>-35.852509699999999</v>
@@ -26340,7 +26349,7 @@
     </row>
     <row r="689" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A689" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B689">
         <v>-35.787201000000003</v>
@@ -26393,7 +26402,7 @@
     </row>
     <row r="690" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A690" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B690">
         <v>-34.759169999999997</v>
@@ -26411,12 +26420,12 @@
         <v>2667</v>
       </c>
       <c r="Q690" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="691" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A691" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B691">
         <v>-34.494970000000002</v>
@@ -26434,12 +26443,12 @@
         <v>222</v>
       </c>
       <c r="Q691" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="692" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A692" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B692">
         <v>-36.866</v>
@@ -26480,7 +26489,7 @@
     </row>
     <row r="693" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A693" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B693">
         <v>-34.902070808541197</v>
@@ -26513,12 +26522,12 @@
         <v>1556</v>
       </c>
       <c r="Q693" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="694" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A694" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B694">
         <v>-34.495376</v>
@@ -26551,12 +26560,12 @@
         <v>3889</v>
       </c>
       <c r="Q694" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="695" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A695" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B695">
         <v>-34.759169999999997</v>
@@ -26574,12 +26583,12 @@
         <v>167</v>
       </c>
       <c r="Q695" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="696" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A696" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B696">
         <v>-34.899749999999997</v>
@@ -26597,12 +26606,12 @@
         <v>3167</v>
       </c>
       <c r="Q696" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="697" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A697" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B697">
         <v>-34.759169999999997</v>
@@ -26620,12 +26629,12 @@
         <v>0</v>
       </c>
       <c r="Q697" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="698" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A698" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B698">
         <v>-35.853555700000001</v>
@@ -26678,7 +26687,7 @@
     </row>
     <row r="699" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A699" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B699">
         <v>-35.739091000000002</v>
@@ -26731,7 +26740,7 @@
     </row>
     <row r="700" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A700" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B700">
         <v>-34.824044999999998</v>
@@ -26851,7 +26860,7 @@
     </row>
     <row r="703" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A703" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B703">
         <v>-35.516800000000003</v>
@@ -26979,7 +26988,7 @@
     </row>
     <row r="707" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A707" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B707">
         <v>-35.5565</v>
@@ -27011,7 +27020,7 @@
     </row>
     <row r="708" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A708" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B708">
         <v>-35.5565</v>
@@ -27043,7 +27052,7 @@
     </row>
     <row r="709" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A709" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B709">
         <v>-35.634900000000002</v>
@@ -27075,7 +27084,7 @@
     </row>
     <row r="710" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A710" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B710">
         <v>-35.510620000000003</v>
@@ -27108,12 +27117,12 @@
         <v>4722</v>
       </c>
       <c r="Q710" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="711" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A711" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B711">
         <v>-35.793973000000001</v>
@@ -27166,7 +27175,7 @@
     </row>
     <row r="712" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A712" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B712">
         <v>-34.88823</v>
@@ -27184,7 +27193,7 @@
         <v>1722</v>
       </c>
       <c r="Q712" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="713" spans="1:17" x14ac:dyDescent="0.3">
@@ -27259,7 +27268,7 @@
     </row>
     <row r="715" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A715" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B715">
         <v>-35.878667100000001</v>
@@ -27350,7 +27359,7 @@
     </row>
     <row r="717" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A717" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B717">
         <v>-34.842409000000004</v>
@@ -27394,7 +27403,7 @@
     </row>
     <row r="718" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A718" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B718">
         <v>-34.759169999999997</v>
@@ -27412,12 +27421,12 @@
         <v>167</v>
       </c>
       <c r="Q718" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="719" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A719" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B719">
         <v>-34.672490000000003</v>
@@ -27435,7 +27444,7 @@
         <v>0</v>
       </c>
       <c r="Q719" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="720" spans="1:17" x14ac:dyDescent="0.3">
@@ -27478,7 +27487,7 @@
     </row>
     <row r="721" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A721" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B721">
         <v>-35.786641000000003</v>
@@ -27531,7 +27540,7 @@
     </row>
     <row r="722" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A722" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B722">
         <v>-35.638145999999999</v>
@@ -27584,7 +27593,7 @@
     </row>
     <row r="723" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A723" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B723">
         <v>-35.532783000000002</v>
@@ -27660,7 +27669,7 @@
     </row>
     <row r="725" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A725" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B725">
         <v>-35.521971999999998</v>
@@ -27696,7 +27705,7 @@
         <v>1389</v>
       </c>
       <c r="Q725" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="726" spans="1:17" x14ac:dyDescent="0.3">
@@ -27780,7 +27789,7 @@
     </row>
     <row r="728" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A728" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B728">
         <v>-35.557299999999998</v>
@@ -27859,7 +27868,7 @@
     </row>
     <row r="730" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A730" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B730">
         <v>-34.958151000000001</v>
@@ -27894,7 +27903,7 @@
     </row>
     <row r="731" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A731" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B731">
         <v>-34.860666999999999</v>
@@ -27932,7 +27941,7 @@
     </row>
     <row r="732" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A732" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B732">
         <v>-35.445188000000002</v>
@@ -27965,12 +27974,12 @@
         <v>2056</v>
       </c>
       <c r="Q732" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="733" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A733" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B733">
         <v>-34.759169999999997</v>
@@ -27988,12 +27997,12 @@
         <v>0</v>
       </c>
       <c r="Q733" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="734" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A734" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B734">
         <v>-35.739091000000002</v>
@@ -28046,7 +28055,7 @@
     </row>
     <row r="735" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A735" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B735">
         <v>-35.853555700000001</v>
@@ -28099,7 +28108,7 @@
     </row>
     <row r="736" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A736" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B736">
         <v>-34.323770000000003</v>
@@ -28117,12 +28126,12 @@
         <v>0</v>
       </c>
       <c r="Q736" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="737" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A737" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B737">
         <v>-34.494970000000002</v>
@@ -28140,12 +28149,12 @@
         <v>0</v>
       </c>
       <c r="Q737" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="738" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A738" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B738">
         <v>-34.899749999999997</v>
@@ -28163,12 +28172,12 @@
         <v>111</v>
       </c>
       <c r="Q738" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="739" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A739" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B739">
         <v>-34.075042000000003</v>
@@ -28192,12 +28201,12 @@
         <v>167</v>
       </c>
       <c r="Q739" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="740" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A740" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B740">
         <v>-35.081918000000002</v>
@@ -28230,12 +28239,12 @@
         <v>1389</v>
       </c>
       <c r="Q740" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="741" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A741" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B741">
         <v>-35.081918000000002</v>
@@ -28268,12 +28277,12 @@
         <v>1389</v>
       </c>
       <c r="Q741" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="742" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A742" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B742">
         <v>-34.902070808541197</v>
@@ -28303,12 +28312,12 @@
         <v>500</v>
       </c>
       <c r="Q742" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="743" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A743" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B743">
         <v>-35.853555700000001</v>
@@ -28356,12 +28365,12 @@
         <v>555</v>
       </c>
       <c r="Q743" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="744" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A744" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B744">
         <v>-34.899749999999997</v>
@@ -28379,12 +28388,12 @@
         <v>111</v>
       </c>
       <c r="Q744" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="745" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A745" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B745">
         <v>-34.672499999999999</v>
@@ -28399,7 +28408,7 @@
         <v>0</v>
       </c>
       <c r="Q745" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="746" spans="1:17" x14ac:dyDescent="0.3">
@@ -28471,7 +28480,7 @@
     </row>
     <row r="748" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A748" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B748">
         <v>-34.824044999999998</v>
@@ -28506,7 +28515,7 @@
     </row>
     <row r="749" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A749" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B749">
         <v>-34.958151000000001</v>
@@ -28573,7 +28582,7 @@
     </row>
     <row r="751" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A751" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B751">
         <v>-35.739091000000002</v>
@@ -28621,12 +28630,12 @@
         <v>666</v>
       </c>
       <c r="Q751" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="752" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A752" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B752">
         <v>-34.903120000000001</v>
@@ -28653,12 +28662,12 @@
         <v>500</v>
       </c>
       <c r="Q752" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="753" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A753" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B753">
         <v>-35.054707999999998</v>
@@ -28688,12 +28697,12 @@
         <v>70167</v>
       </c>
       <c r="Q753" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="754" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A754" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B754">
         <v>-34.903466000000002</v>
@@ -28726,12 +28735,12 @@
         <v>1333</v>
       </c>
       <c r="Q754" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="755" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A755" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B755">
         <v>-34.765996000000001</v>
@@ -28764,12 +28773,12 @@
         <v>667</v>
       </c>
       <c r="Q755" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="756" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A756" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B756">
         <v>-35.510620000000003</v>
@@ -28799,12 +28808,12 @@
         <v>2334</v>
       </c>
       <c r="Q756" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="757" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A757" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B757">
         <v>-35.793973000000001</v>
@@ -28852,12 +28861,12 @@
         <v>7333</v>
       </c>
       <c r="Q757" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="758" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A758" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B758">
         <v>-35.878667100000001</v>
@@ -28905,12 +28914,12 @@
         <v>0</v>
       </c>
       <c r="Q758" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="759" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A759" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B759">
         <v>-35.445188000000002</v>
@@ -28940,7 +28949,1180 @@
         <v>1722</v>
       </c>
       <c r="Q759" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="760" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A760" t="s">
+        <v>88</v>
+      </c>
+      <c r="B760">
+        <v>-35.581124000000003</v>
+      </c>
+      <c r="C760">
+        <v>138.60879700000001</v>
+      </c>
+      <c r="D760" s="2">
+        <v>46096</v>
+      </c>
+      <c r="G760">
+        <v>111</v>
+      </c>
+      <c r="H760">
+        <v>56</v>
+      </c>
+      <c r="I760">
+        <v>56</v>
+      </c>
+      <c r="J760">
+        <v>0</v>
+      </c>
+      <c r="L760">
+        <v>222</v>
+      </c>
+      <c r="N760">
+        <v>111</v>
+      </c>
+      <c r="O760">
+        <v>333</v>
+      </c>
+      <c r="P760">
+        <v>889</v>
+      </c>
+      <c r="Q760" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="761" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A761" t="s">
+        <v>89</v>
+      </c>
+      <c r="B761">
+        <v>-35.6048446</v>
+      </c>
+      <c r="C761">
+        <v>138.59278499999999</v>
+      </c>
+      <c r="D761" s="2">
+        <v>46096</v>
+      </c>
+      <c r="H761">
+        <v>389</v>
+      </c>
+      <c r="I761">
+        <v>222</v>
+      </c>
+      <c r="J761">
+        <v>0</v>
+      </c>
+      <c r="L761">
+        <v>111</v>
+      </c>
+      <c r="N761">
+        <v>500</v>
+      </c>
+      <c r="O761">
+        <v>1111</v>
+      </c>
+      <c r="P761">
+        <v>2333</v>
+      </c>
+      <c r="Q761" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="762" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A762" t="s">
+        <v>378</v>
+      </c>
+      <c r="B762">
+        <v>-35.612285999999997</v>
+      </c>
+      <c r="C762">
+        <v>138.564302</v>
+      </c>
+      <c r="D762" s="2">
+        <v>46096</v>
+      </c>
+      <c r="H762">
+        <v>56</v>
+      </c>
+      <c r="I762">
+        <v>56</v>
+      </c>
+      <c r="J762">
+        <v>0</v>
+      </c>
+      <c r="L762">
+        <v>333</v>
+      </c>
+      <c r="N762">
+        <v>222</v>
+      </c>
+      <c r="O762">
+        <v>389</v>
+      </c>
+      <c r="P762">
+        <v>1056</v>
+      </c>
+      <c r="Q762" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="763" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A763" t="s">
+        <v>301</v>
+      </c>
+      <c r="B763">
+        <v>-35.61</v>
+      </c>
+      <c r="C763">
+        <v>138.5925</v>
+      </c>
+      <c r="D763" s="2">
+        <v>46096</v>
+      </c>
+      <c r="I763">
+        <v>444</v>
+      </c>
+      <c r="J763">
+        <v>0</v>
+      </c>
+      <c r="L763">
+        <v>278</v>
+      </c>
+      <c r="N763">
+        <v>167</v>
+      </c>
+      <c r="O763">
+        <v>612</v>
+      </c>
+      <c r="P763">
+        <v>1501</v>
+      </c>
+      <c r="Q763" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="764" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A764" t="s">
+        <v>384</v>
+      </c>
+      <c r="B764">
+        <v>-34.759169999999997</v>
+      </c>
+      <c r="C764">
+        <v>137.47612000000001</v>
+      </c>
+      <c r="D764" s="2">
+        <v>46104</v>
+      </c>
+      <c r="E764" s="20">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="I764">
+        <v>111</v>
+      </c>
+      <c r="J764">
+        <v>0</v>
+      </c>
+      <c r="L764">
+        <v>56</v>
+      </c>
+      <c r="P764">
+        <v>167</v>
+      </c>
+      <c r="Q764" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="765" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A765" t="s">
+        <v>356</v>
+      </c>
+      <c r="B765">
+        <v>-34.672499999999999</v>
+      </c>
+      <c r="C765">
+        <v>137.49298999999999</v>
+      </c>
+      <c r="D765" s="2">
+        <v>46106</v>
+      </c>
+      <c r="E765" s="20">
+        <v>0.57291666666666663</v>
+      </c>
+      <c r="I765">
+        <v>56</v>
+      </c>
+      <c r="J765">
+        <v>0</v>
+      </c>
+      <c r="L765">
+        <v>111</v>
+      </c>
+      <c r="O765">
+        <v>56</v>
+      </c>
+      <c r="P765">
+        <v>223</v>
+      </c>
+      <c r="Q765" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="766" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A766" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="B766" s="1">
+        <v>-35.516800000000003</v>
+      </c>
+      <c r="C766" s="1">
+        <v>138.73820000000001</v>
+      </c>
+      <c r="D766" s="2">
+        <v>46109</v>
+      </c>
+      <c r="E766" s="20">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="F766" s="1"/>
+      <c r="G766" s="1"/>
+      <c r="H766" s="1"/>
+      <c r="I766" s="1">
+        <v>111</v>
+      </c>
+      <c r="J766" s="1">
+        <v>0</v>
+      </c>
+      <c r="K766" s="1"/>
+      <c r="L766" s="1">
+        <v>611</v>
+      </c>
+      <c r="M766" s="1"/>
+      <c r="N766" s="1"/>
+      <c r="O766" s="1"/>
+      <c r="P766">
+        <f>SUM(F766:I766,K766:O766)</f>
+        <v>722</v>
+      </c>
+      <c r="Q766" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="767" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A767" t="s">
+        <v>188</v>
+      </c>
+      <c r="B767">
+        <v>-35.515900000000002</v>
+      </c>
+      <c r="C767">
+        <v>138.70529999999999</v>
+      </c>
+      <c r="D767" s="2">
+        <v>46109</v>
+      </c>
+      <c r="E767" s="20">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="I767">
+        <v>56</v>
+      </c>
+      <c r="J767">
+        <v>0</v>
+      </c>
+      <c r="L767">
+        <v>111</v>
+      </c>
+      <c r="P767">
+        <f>SUM(F767:I767,K767:O767)</f>
+        <v>167</v>
+      </c>
+      <c r="Q767" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="768" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A768" t="s">
+        <v>91</v>
+      </c>
+      <c r="B768">
+        <v>-35.536299999999997</v>
+      </c>
+      <c r="C768">
+        <v>138.67859999999999</v>
+      </c>
+      <c r="D768" s="2">
+        <v>46109</v>
+      </c>
+      <c r="E768" s="20">
+        <v>0.4375</v>
+      </c>
+      <c r="I768">
+        <v>222</v>
+      </c>
+      <c r="J768">
+        <v>0</v>
+      </c>
+      <c r="L768">
+        <v>56</v>
+      </c>
+      <c r="P768">
+        <f t="shared" ref="P768:P777" si="1">SUM(F768:I768,K768:O768)</f>
+        <v>278</v>
+      </c>
+      <c r="Q768" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="769" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A769" t="s">
+        <v>186</v>
+      </c>
+      <c r="B769">
+        <v>-35.538600000000002</v>
+      </c>
+      <c r="C769">
+        <v>138.6497</v>
+      </c>
+      <c r="D769" s="2">
+        <v>46109</v>
+      </c>
+      <c r="E769" s="20">
+        <v>0.44791666666666669</v>
+      </c>
+      <c r="I769">
+        <v>56</v>
+      </c>
+      <c r="J769">
+        <v>0</v>
+      </c>
+      <c r="L769">
+        <v>56</v>
+      </c>
+      <c r="P769">
+        <f t="shared" si="1"/>
+        <v>112</v>
+      </c>
+      <c r="Q769" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="770" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A770" t="s">
+        <v>318</v>
+      </c>
+      <c r="B770">
+        <v>-35.5565</v>
+      </c>
+      <c r="C770">
+        <v>138.62610000000001</v>
+      </c>
+      <c r="D770" s="2">
+        <v>46109</v>
+      </c>
+      <c r="E770" s="20">
+        <v>0.4826388888888889</v>
+      </c>
+      <c r="I770">
+        <v>0</v>
+      </c>
+      <c r="J770">
+        <v>0</v>
+      </c>
+      <c r="L770">
+        <v>0</v>
+      </c>
+      <c r="P770">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q770" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="771" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A771" t="s">
+        <v>189</v>
+      </c>
+      <c r="B771">
+        <v>-35.5565</v>
+      </c>
+      <c r="C771">
+        <v>138.62610000000001</v>
+      </c>
+      <c r="D771" s="2">
+        <v>46109</v>
+      </c>
+      <c r="E771" s="20">
+        <v>0.46527777777777779</v>
+      </c>
+      <c r="I771">
+        <v>222</v>
+      </c>
+      <c r="J771">
+        <v>0</v>
+      </c>
+      <c r="L771">
+        <v>56</v>
+      </c>
+      <c r="P771">
+        <f t="shared" si="1"/>
+        <v>278</v>
+      </c>
+      <c r="Q771" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="772" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A772" t="s">
+        <v>320</v>
+      </c>
+      <c r="B772">
+        <v>-35.634900000000002</v>
+      </c>
+      <c r="C772">
+        <v>138.49850000000001</v>
+      </c>
+      <c r="D772" s="2">
+        <v>46109</v>
+      </c>
+      <c r="E772" s="20">
+        <v>0.4861111111111111</v>
+      </c>
+      <c r="I772">
+        <v>278</v>
+      </c>
+      <c r="J772">
+        <v>0</v>
+      </c>
+      <c r="L772">
+        <v>167</v>
+      </c>
+      <c r="P772">
+        <f t="shared" si="1"/>
+        <v>445</v>
+      </c>
+      <c r="Q772" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="773" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A773" t="s">
+        <v>319</v>
+      </c>
+      <c r="B773">
+        <v>-35.563899999999997</v>
+      </c>
+      <c r="C773">
+        <v>138.6131</v>
+      </c>
+      <c r="D773" s="2">
+        <v>46109</v>
+      </c>
+      <c r="E773" s="20">
+        <v>0.50347222222222221</v>
+      </c>
+      <c r="I773">
+        <v>56</v>
+      </c>
+      <c r="J773">
+        <v>0</v>
+      </c>
+      <c r="L773">
+        <v>0</v>
+      </c>
+      <c r="P773">
+        <f t="shared" si="1"/>
+        <v>56</v>
+      </c>
+      <c r="Q773" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="774" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A774" t="s">
         <v>407</v>
+      </c>
+      <c r="B774">
+        <v>-35.548499999999997</v>
+      </c>
+      <c r="C774">
+        <v>138.62710000000001</v>
+      </c>
+      <c r="D774" s="2">
+        <v>46109</v>
+      </c>
+      <c r="E774" s="20">
+        <v>0.47222222222222221</v>
+      </c>
+      <c r="I774">
+        <v>0</v>
+      </c>
+      <c r="J774">
+        <v>0</v>
+      </c>
+      <c r="L774">
+        <v>56</v>
+      </c>
+      <c r="P774">
+        <f t="shared" si="1"/>
+        <v>56</v>
+      </c>
+      <c r="Q774" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="775" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A775" t="s">
+        <v>408</v>
+      </c>
+      <c r="B775">
+        <v>-35.5595</v>
+      </c>
+      <c r="C775">
+        <v>138.6275</v>
+      </c>
+      <c r="D775" s="2">
+        <v>46109</v>
+      </c>
+      <c r="E775" s="20">
+        <v>0.48958333333333331</v>
+      </c>
+      <c r="I775">
+        <v>0</v>
+      </c>
+      <c r="J775">
+        <v>0</v>
+      </c>
+      <c r="L775">
+        <v>56</v>
+      </c>
+      <c r="P775">
+        <f t="shared" si="1"/>
+        <v>56</v>
+      </c>
+      <c r="Q775" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="776" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A776" t="s">
+        <v>409</v>
+      </c>
+      <c r="B776">
+        <v>-35.585299999999997</v>
+      </c>
+      <c r="C776">
+        <v>138.5985</v>
+      </c>
+      <c r="D776" s="2">
+        <v>46109</v>
+      </c>
+      <c r="E776" s="20">
+        <v>0.51388888888888884</v>
+      </c>
+      <c r="I776">
+        <v>56</v>
+      </c>
+      <c r="J776">
+        <v>0</v>
+      </c>
+      <c r="L776">
+        <v>0</v>
+      </c>
+      <c r="P776">
+        <f t="shared" si="1"/>
+        <v>56</v>
+      </c>
+      <c r="Q776" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="777" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A777" t="s">
+        <v>86</v>
+      </c>
+      <c r="B777">
+        <v>-35.5413</v>
+      </c>
+      <c r="C777">
+        <v>138.64080000000001</v>
+      </c>
+      <c r="D777" s="2">
+        <v>46109</v>
+      </c>
+      <c r="E777" s="20">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="I777">
+        <v>0</v>
+      </c>
+      <c r="J777">
+        <v>0</v>
+      </c>
+      <c r="L777">
+        <v>111</v>
+      </c>
+      <c r="P777">
+        <f t="shared" si="1"/>
+        <v>111</v>
+      </c>
+      <c r="Q777" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="778" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A778" t="s">
+        <v>59</v>
+      </c>
+      <c r="B778">
+        <v>-35.084850000000003</v>
+      </c>
+      <c r="C778">
+        <v>137.74889999999999</v>
+      </c>
+      <c r="D778" s="2">
+        <v>46113</v>
+      </c>
+      <c r="E778" s="20">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="G778">
+        <v>0</v>
+      </c>
+      <c r="I778">
+        <v>56</v>
+      </c>
+      <c r="J778">
+        <v>0</v>
+      </c>
+      <c r="L778">
+        <v>222</v>
+      </c>
+      <c r="M778">
+        <v>111</v>
+      </c>
+      <c r="N778">
+        <v>777</v>
+      </c>
+      <c r="P778">
+        <v>1166</v>
+      </c>
+      <c r="Q778" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="779" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A779" t="s">
+        <v>315</v>
+      </c>
+      <c r="B779">
+        <v>-35.445186</v>
+      </c>
+      <c r="C779">
+        <v>138.307424</v>
+      </c>
+      <c r="D779" s="2">
+        <v>46104</v>
+      </c>
+      <c r="E779" s="20">
+        <v>0.38541666666666669</v>
+      </c>
+      <c r="I779">
+        <v>0</v>
+      </c>
+      <c r="J779">
+        <v>0</v>
+      </c>
+      <c r="L779">
+        <v>56</v>
+      </c>
+      <c r="N779">
+        <v>56</v>
+      </c>
+      <c r="O779">
+        <v>778</v>
+      </c>
+      <c r="P779">
+        <v>890</v>
+      </c>
+      <c r="Q779" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="780" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A780" t="s">
+        <v>342</v>
+      </c>
+      <c r="B780">
+        <v>-35.500242</v>
+      </c>
+      <c r="C780">
+        <v>138.24491</v>
+      </c>
+      <c r="D780" s="2">
+        <v>46109</v>
+      </c>
+      <c r="E780" s="20">
+        <v>0.68055555555555547</v>
+      </c>
+      <c r="I780">
+        <v>444</v>
+      </c>
+      <c r="J780">
+        <v>0</v>
+      </c>
+      <c r="L780">
+        <v>2667</v>
+      </c>
+      <c r="N780">
+        <v>556</v>
+      </c>
+      <c r="O780">
+        <v>4889</v>
+      </c>
+      <c r="P780">
+        <v>8556</v>
+      </c>
+      <c r="Q780" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="781" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A781" t="s">
+        <v>410</v>
+      </c>
+      <c r="B781">
+        <v>-35.499946999999999</v>
+      </c>
+      <c r="C781">
+        <v>138.242954</v>
+      </c>
+      <c r="D781" s="2">
+        <v>46109</v>
+      </c>
+      <c r="E781" s="20">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="H781">
+        <v>2222</v>
+      </c>
+      <c r="I781">
+        <v>3333</v>
+      </c>
+      <c r="J781">
+        <v>0</v>
+      </c>
+      <c r="L781">
+        <v>222</v>
+      </c>
+      <c r="N781">
+        <v>2556</v>
+      </c>
+      <c r="O781">
+        <v>444</v>
+      </c>
+      <c r="P781">
+        <v>8777</v>
+      </c>
+      <c r="Q781" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="782" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A782" t="s">
+        <v>352</v>
+      </c>
+      <c r="B782">
+        <v>-34.860666999999999</v>
+      </c>
+      <c r="C782">
+        <v>138.490938</v>
+      </c>
+      <c r="D782" s="2">
+        <v>46108</v>
+      </c>
+      <c r="E782" s="20">
+        <v>0.46180555555555558</v>
+      </c>
+      <c r="I782">
+        <v>2.4</v>
+      </c>
+      <c r="J782">
+        <v>0</v>
+      </c>
+      <c r="L782">
+        <v>5.625</v>
+      </c>
+      <c r="M782">
+        <v>0.15</v>
+      </c>
+      <c r="N782">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="O782">
+        <v>0.15</v>
+      </c>
+      <c r="P782">
+        <v>8.4</v>
+      </c>
+      <c r="Q782" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="783" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A783" t="s">
+        <v>85</v>
+      </c>
+      <c r="B783">
+        <v>-34.873964000000001</v>
+      </c>
+      <c r="C783">
+        <v>138.488134</v>
+      </c>
+      <c r="D783" s="2">
+        <v>46108</v>
+      </c>
+      <c r="E783" s="20">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="I783">
+        <v>3.9</v>
+      </c>
+      <c r="J783">
+        <v>0</v>
+      </c>
+      <c r="L783">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="O783">
+        <v>0.22500000000000001</v>
+      </c>
+      <c r="P783">
+        <v>14.324999999999999</v>
+      </c>
+      <c r="Q783" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="784" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A784" t="s">
+        <v>79</v>
+      </c>
+      <c r="B784">
+        <v>-34.804662999999998</v>
+      </c>
+      <c r="C784">
+        <v>138.540223</v>
+      </c>
+      <c r="D784" s="2">
+        <v>46108</v>
+      </c>
+      <c r="E784" s="20">
+        <v>0.49305555555555558</v>
+      </c>
+      <c r="I784">
+        <v>2.25</v>
+      </c>
+      <c r="J784">
+        <v>0</v>
+      </c>
+      <c r="L784">
+        <v>37.950000000000003</v>
+      </c>
+      <c r="P784">
+        <v>40.200000000000003</v>
+      </c>
+      <c r="Q784" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="785" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A785" t="s">
+        <v>269</v>
+      </c>
+      <c r="B785">
+        <v>-34.824044999999998</v>
+      </c>
+      <c r="C785">
+        <v>138.48377600000001</v>
+      </c>
+      <c r="D785" s="2">
+        <v>46108</v>
+      </c>
+      <c r="E785" s="20">
+        <v>0.47569444444444442</v>
+      </c>
+      <c r="G785">
+        <v>0.3</v>
+      </c>
+      <c r="H785">
+        <v>0.05</v>
+      </c>
+      <c r="I785">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="J785">
+        <v>0</v>
+      </c>
+      <c r="L785">
+        <v>8.25</v>
+      </c>
+      <c r="P785">
+        <v>9.75</v>
+      </c>
+      <c r="Q785" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="786" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A786" t="s">
+        <v>93</v>
+      </c>
+      <c r="B786">
+        <v>-35.514747999999997</v>
+      </c>
+      <c r="C786">
+        <v>138.71989600000001</v>
+      </c>
+      <c r="D786" s="2">
+        <v>46111</v>
+      </c>
+      <c r="E786" s="20">
+        <v>0.375</v>
+      </c>
+      <c r="I786">
+        <v>0.9</v>
+      </c>
+      <c r="J786">
+        <v>0</v>
+      </c>
+      <c r="L786">
+        <v>111.6</v>
+      </c>
+      <c r="O786">
+        <v>0.1</v>
+      </c>
+      <c r="P786">
+        <v>112.6</v>
+      </c>
+      <c r="Q786" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="787" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A787" t="s">
+        <v>400</v>
+      </c>
+      <c r="B787">
+        <v>-35.793973000000001</v>
+      </c>
+      <c r="C787">
+        <v>137.852418</v>
+      </c>
+      <c r="D787" s="2">
+        <v>46110</v>
+      </c>
+      <c r="E787" s="20">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="F787">
+        <v>1222</v>
+      </c>
+      <c r="G787">
+        <v>667</v>
+      </c>
+      <c r="H787">
+        <v>1333</v>
+      </c>
+      <c r="I787">
+        <v>1000</v>
+      </c>
+      <c r="J787">
+        <v>0</v>
+      </c>
+      <c r="K787">
+        <v>0</v>
+      </c>
+      <c r="L787">
+        <v>3778</v>
+      </c>
+      <c r="M787">
+        <v>222</v>
+      </c>
+      <c r="N787">
+        <v>333</v>
+      </c>
+      <c r="O787">
+        <v>0</v>
+      </c>
+      <c r="P787">
+        <v>8555</v>
+      </c>
+      <c r="Q787" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="788" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A788" t="s">
+        <v>210</v>
+      </c>
+      <c r="B788">
+        <v>35.739091000000002</v>
+      </c>
+      <c r="C788">
+        <v>137.67788400000001</v>
+      </c>
+      <c r="D788" s="2">
+        <v>46110</v>
+      </c>
+      <c r="E788" s="20">
+        <v>0.4375</v>
+      </c>
+      <c r="F788">
+        <v>222</v>
+      </c>
+      <c r="G788">
+        <v>0</v>
+      </c>
+      <c r="H788">
+        <v>1333</v>
+      </c>
+      <c r="I788">
+        <v>0</v>
+      </c>
+      <c r="J788">
+        <v>0</v>
+      </c>
+      <c r="K788">
+        <v>0</v>
+      </c>
+      <c r="L788">
+        <v>5778</v>
+      </c>
+      <c r="M788">
+        <v>1444</v>
+      </c>
+      <c r="N788">
+        <v>0</v>
+      </c>
+      <c r="O788">
+        <v>0</v>
+      </c>
+      <c r="P788">
+        <v>8777</v>
+      </c>
+      <c r="Q788" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="789" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A789" t="s">
+        <v>379</v>
+      </c>
+      <c r="B789">
+        <v>-35.853555700000001</v>
+      </c>
+      <c r="C789">
+        <v>137.74248499999999</v>
+      </c>
+      <c r="D789" s="2">
+        <v>46110</v>
+      </c>
+      <c r="E789" s="20">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="F789">
+        <v>167</v>
+      </c>
+      <c r="G789">
+        <v>0</v>
+      </c>
+      <c r="H789">
+        <v>4000</v>
+      </c>
+      <c r="I789">
+        <v>444</v>
+      </c>
+      <c r="J789">
+        <v>0</v>
+      </c>
+      <c r="K789">
+        <v>0</v>
+      </c>
+      <c r="L789">
+        <v>1222</v>
+      </c>
+      <c r="M789">
+        <v>0</v>
+      </c>
+      <c r="N789">
+        <v>0</v>
+      </c>
+      <c r="O789">
+        <v>0</v>
+      </c>
+      <c r="P789">
+        <v>5833</v>
+      </c>
+      <c r="Q789" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="790" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A790" t="s">
+        <v>222</v>
+      </c>
+      <c r="B790">
+        <v>-35.638145999999999</v>
+      </c>
+      <c r="C790">
+        <v>137.6249325</v>
+      </c>
+      <c r="D790" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E790" s="20">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="F790">
+        <v>0</v>
+      </c>
+      <c r="G790">
+        <v>222</v>
+      </c>
+      <c r="H790">
+        <v>1556</v>
+      </c>
+      <c r="I790">
+        <v>556</v>
+      </c>
+      <c r="J790">
+        <v>0</v>
+      </c>
+      <c r="K790">
+        <v>0</v>
+      </c>
+      <c r="L790">
+        <v>4889</v>
+      </c>
+      <c r="M790">
+        <v>444</v>
+      </c>
+      <c r="N790">
+        <v>0</v>
+      </c>
+      <c r="O790">
+        <v>111</v>
+      </c>
+      <c r="P790">
+        <v>7778</v>
+      </c>
+      <c r="Q790" t="s">
+        <v>399</v>
       </c>
     </row>
   </sheetData>

--- a/MASTER spreadsheet of community summaries.xlsx
+++ b/MASTER spreadsheet of community summaries.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\peri\Dropbox\Delta\Projects\Laboratory\Algal blooms, bacterial counts  for community\For Luke's HAB data display\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7AFD42A-7098-47E0-8EC7-8BE6F8D039EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47C99D04-0DEF-4A2D-B267-CC9AACAB3BF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{9286397E-2757-492B-865A-39B2D6A15FF6}"/>
+    <workbookView xWindow="-24885" yWindow="1845" windowWidth="23250" windowHeight="13890" xr2:uid="{9286397E-2757-492B-865A-39B2D6A15FF6}"/>
   </bookViews>
   <sheets>
     <sheet name="Cells per mL" sheetId="1" r:id="rId1"/>
@@ -1764,7 +1764,7 @@
     <col min="1" max="1" width="39.33203125" customWidth="1"/>
     <col min="2" max="2" width="17.77734375" customWidth="1"/>
     <col min="3" max="3" width="14.6640625" customWidth="1"/>
-    <col min="4" max="4" width="10.44140625" customWidth="1"/>
+    <col min="4" max="4" width="13.109375" customWidth="1"/>
     <col min="5" max="5" width="16.6640625" style="20" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="15.44140625" customWidth="1"/>
@@ -25199,7 +25199,7 @@
         <v>56</v>
       </c>
       <c r="P657" s="17">
-        <f t="shared" ref="P657:P663" si="0">SUM(F657:I657,K657:O657)</f>
+        <f>SUM(F657:I657,K657:O657)</f>
         <v>1111</v>
       </c>
       <c r="Q657" t="s">
@@ -25232,7 +25232,7 @@
         <v>111</v>
       </c>
       <c r="P658">
-        <f t="shared" si="0"/>
+        <f>SUM(F658:I658,K658:O658)</f>
         <v>444</v>
       </c>
       <c r="Q658" t="s">
@@ -25265,7 +25265,7 @@
         <v>0</v>
       </c>
       <c r="P659">
-        <f t="shared" si="0"/>
+        <f>SUM(F659:I659,K659:O659)</f>
         <v>56</v>
       </c>
       <c r="Q659" t="s">
@@ -25298,7 +25298,7 @@
         <v>167</v>
       </c>
       <c r="P660">
-        <f t="shared" si="0"/>
+        <f>SUM(F660:I660,K660:O660)</f>
         <v>167</v>
       </c>
       <c r="Q660" t="s">
@@ -25331,7 +25331,7 @@
         <v>56</v>
       </c>
       <c r="P661">
-        <f t="shared" si="0"/>
+        <f>SUM(F661:I661,K661:O661)</f>
         <v>112</v>
       </c>
       <c r="Q661" t="s">
@@ -25364,7 +25364,7 @@
         <v>0</v>
       </c>
       <c r="P662">
-        <f t="shared" si="0"/>
+        <f>SUM(F662:I662,K662:O662)</f>
         <v>0</v>
       </c>
       <c r="Q662" t="s">
@@ -25397,7 +25397,7 @@
         <v>222</v>
       </c>
       <c r="P663">
-        <f t="shared" si="0"/>
+        <f>SUM(F663:I663,K663:O663)</f>
         <v>278</v>
       </c>
       <c r="Q663" t="s">
@@ -27868,282 +27868,282 @@
     </row>
     <row r="730" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A730" t="s">
-        <v>392</v>
+        <v>88</v>
       </c>
       <c r="B730">
-        <v>-34.958151000000001</v>
+        <v>-35.581124000000003</v>
       </c>
       <c r="C730">
-        <v>138.503987</v>
+        <v>138.60879700000001</v>
       </c>
       <c r="D730" s="2">
-        <v>46097</v>
-      </c>
-      <c r="E730" s="20">
-        <v>0.36458333333333331</v>
+        <v>46096</v>
+      </c>
+      <c r="G730">
+        <v>111</v>
+      </c>
+      <c r="H730">
+        <v>56</v>
       </c>
       <c r="I730">
-        <v>26.46</v>
+        <v>56</v>
       </c>
       <c r="J730">
         <v>0</v>
       </c>
       <c r="L730">
-        <v>0.96</v>
+        <v>222</v>
       </c>
       <c r="N730">
-        <v>0.12</v>
+        <v>111</v>
+      </c>
+      <c r="O730">
+        <v>333</v>
       </c>
       <c r="P730">
-        <v>27.540000000000003</v>
+        <v>889</v>
       </c>
       <c r="Q730" t="s">
-        <v>78</v>
+        <v>129</v>
       </c>
     </row>
     <row r="731" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A731" t="s">
-        <v>352</v>
+        <v>89</v>
       </c>
       <c r="B731">
-        <v>-34.860666999999999</v>
+        <v>-35.6048446</v>
       </c>
       <c r="C731">
-        <v>138.490938</v>
+        <v>138.59278499999999</v>
       </c>
       <c r="D731" s="2">
-        <v>46097</v>
-      </c>
-      <c r="E731" s="20">
-        <v>0.35416666666666669</v>
+        <v>46096</v>
+      </c>
+      <c r="H731">
+        <v>389</v>
       </c>
       <c r="I731">
-        <v>0.45</v>
+        <v>222</v>
       </c>
       <c r="J731">
         <v>0</v>
       </c>
       <c r="L731">
-        <v>186.3</v>
+        <v>111</v>
       </c>
       <c r="N731">
-        <v>0.15</v>
+        <v>500</v>
       </c>
       <c r="O731">
-        <v>0.3</v>
+        <v>1111</v>
       </c>
       <c r="P731">
-        <v>187.20000000000002</v>
+        <v>2333</v>
       </c>
       <c r="Q731" t="s">
-        <v>78</v>
+        <v>129</v>
       </c>
     </row>
     <row r="732" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A732" t="s">
-        <v>315</v>
+        <v>378</v>
       </c>
       <c r="B732">
-        <v>-35.445188000000002</v>
+        <v>-35.612285999999997</v>
       </c>
       <c r="C732">
-        <v>138.307266</v>
+        <v>138.564302</v>
       </c>
       <c r="D732" s="2">
-        <v>46097</v>
-      </c>
-      <c r="E732" s="20">
-        <v>0.375</v>
+        <v>46096</v>
+      </c>
+      <c r="H732">
+        <v>56</v>
       </c>
       <c r="I732">
-        <v>111</v>
+        <v>56</v>
       </c>
       <c r="J732">
         <v>0</v>
       </c>
       <c r="L732">
-        <v>167</v>
+        <v>333</v>
       </c>
       <c r="N732">
-        <v>167</v>
+        <v>222</v>
       </c>
       <c r="O732">
-        <v>1611</v>
+        <v>389</v>
       </c>
       <c r="P732">
-        <v>2056</v>
+        <v>1056</v>
       </c>
       <c r="Q732" t="s">
-        <v>353</v>
+        <v>129</v>
       </c>
     </row>
     <row r="733" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A733" t="s">
-        <v>384</v>
+        <v>301</v>
       </c>
       <c r="B733">
-        <v>-34.759169999999997</v>
+        <v>-35.61</v>
       </c>
       <c r="C733">
-        <v>137.47612000000001</v>
+        <v>138.5925</v>
       </c>
       <c r="D733" s="2">
-        <v>46097</v>
-      </c>
-      <c r="E733" s="20">
-        <v>0.58333333333333337</v>
+        <v>46096</v>
+      </c>
+      <c r="I733">
+        <v>444</v>
       </c>
       <c r="J733">
         <v>0</v>
       </c>
+      <c r="L733">
+        <v>278</v>
+      </c>
+      <c r="N733">
+        <v>167</v>
+      </c>
+      <c r="O733">
+        <v>612</v>
+      </c>
+      <c r="P733">
+        <v>1501</v>
+      </c>
       <c r="Q733" t="s">
-        <v>267</v>
+        <v>129</v>
       </c>
     </row>
     <row r="734" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A734" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B734">
-        <v>-35.739091000000002</v>
+        <v>-34.958151000000001</v>
       </c>
       <c r="C734">
-        <v>137.67788400000001</v>
+        <v>138.503987</v>
       </c>
       <c r="D734" s="2">
-        <v>46098</v>
+        <v>46097</v>
       </c>
       <c r="E734" s="20">
-        <v>17.3</v>
-      </c>
-      <c r="F734">
-        <v>0</v>
-      </c>
-      <c r="G734">
-        <v>0</v>
-      </c>
-      <c r="H734">
-        <v>0</v>
+        <v>0.36458333333333331</v>
       </c>
       <c r="I734">
-        <v>111</v>
+        <v>26.46</v>
       </c>
       <c r="J734">
         <v>0</v>
       </c>
-      <c r="K734">
-        <v>111</v>
-      </c>
       <c r="L734">
-        <v>3778</v>
-      </c>
-      <c r="M734">
-        <v>111</v>
+        <v>0.96</v>
       </c>
       <c r="N734">
-        <v>2000</v>
-      </c>
-      <c r="O734">
-        <v>222</v>
+        <v>0.12</v>
       </c>
       <c r="P734">
-        <v>6333</v>
+        <v>27.540000000000003</v>
       </c>
       <c r="Q734" t="s">
-        <v>151</v>
+        <v>78</v>
       </c>
     </row>
     <row r="735" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A735" t="s">
-        <v>379</v>
+        <v>352</v>
       </c>
       <c r="B735">
-        <v>-35.853555700000001</v>
+        <v>-34.860666999999999</v>
       </c>
       <c r="C735">
-        <v>137.74248499999999</v>
+        <v>138.490938</v>
       </c>
       <c r="D735" s="2">
-        <v>46098</v>
+        <v>46097</v>
       </c>
       <c r="E735" s="20">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F735">
-        <v>0</v>
-      </c>
-      <c r="G735">
-        <v>0</v>
-      </c>
-      <c r="H735">
-        <v>0</v>
+        <v>0.35416666666666669</v>
       </c>
       <c r="I735">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="J735">
         <v>0</v>
       </c>
-      <c r="K735">
-        <v>0</v>
-      </c>
       <c r="L735">
-        <v>222</v>
-      </c>
-      <c r="M735">
-        <v>0</v>
+        <v>186.3</v>
       </c>
       <c r="N735">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="O735">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="P735">
-        <v>222</v>
+        <v>187.20000000000002</v>
       </c>
       <c r="Q735" t="s">
-        <v>151</v>
+        <v>78</v>
       </c>
     </row>
     <row r="736" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A736" t="s">
-        <v>396</v>
+        <v>315</v>
       </c>
       <c r="B736">
-        <v>-34.323770000000003</v>
+        <v>-35.445188000000002</v>
       </c>
       <c r="C736">
-        <v>137.49154999999999</v>
+        <v>138.307266</v>
       </c>
       <c r="D736" s="2">
-        <v>46098</v>
+        <v>46097</v>
       </c>
       <c r="E736" s="20">
-        <v>0.69444444444444442</v>
+        <v>0.375</v>
+      </c>
+      <c r="I736">
+        <v>111</v>
       </c>
       <c r="J736">
         <v>0</v>
       </c>
+      <c r="L736">
+        <v>167</v>
+      </c>
+      <c r="N736">
+        <v>167</v>
+      </c>
+      <c r="O736">
+        <v>1611</v>
+      </c>
+      <c r="P736">
+        <v>2056</v>
+      </c>
       <c r="Q736" t="s">
-        <v>267</v>
+        <v>353</v>
       </c>
     </row>
     <row r="737" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A737" t="s">
-        <v>360</v>
+        <v>384</v>
       </c>
       <c r="B737">
-        <v>-34.494970000000002</v>
+        <v>-34.759169999999997</v>
       </c>
       <c r="C737">
-        <v>137.48038</v>
+        <v>137.47612000000001</v>
       </c>
       <c r="D737" s="2">
-        <v>46098</v>
+        <v>46097</v>
       </c>
       <c r="E737" s="20">
-        <v>0.54861111111111116</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="J737">
         <v>0</v>
@@ -28154,427 +28154,442 @@
     </row>
     <row r="738" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A738" t="s">
-        <v>304</v>
+        <v>390</v>
       </c>
       <c r="B738">
-        <v>-34.899749999999997</v>
+        <v>-35.739091000000002</v>
       </c>
       <c r="C738">
-        <v>137.45174</v>
+        <v>137.67788400000001</v>
       </c>
       <c r="D738" s="2">
         <v>46098</v>
       </c>
       <c r="E738" s="20">
-        <v>0.6875</v>
+        <v>17.3</v>
+      </c>
+      <c r="F738">
+        <v>0</v>
+      </c>
+      <c r="G738">
+        <v>0</v>
+      </c>
+      <c r="H738">
+        <v>0</v>
+      </c>
+      <c r="I738">
+        <v>111</v>
       </c>
       <c r="J738">
+        <v>0</v>
+      </c>
+      <c r="K738">
         <v>111</v>
       </c>
+      <c r="L738">
+        <v>3778</v>
+      </c>
+      <c r="M738">
+        <v>111</v>
+      </c>
+      <c r="N738">
+        <v>2000</v>
+      </c>
+      <c r="O738">
+        <v>222</v>
+      </c>
+      <c r="P738">
+        <v>6333</v>
+      </c>
       <c r="Q738" t="s">
-        <v>267</v>
+        <v>151</v>
       </c>
     </row>
     <row r="739" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A739" t="s">
-        <v>401</v>
+        <v>379</v>
       </c>
       <c r="B739">
-        <v>-34.075042000000003</v>
+        <v>-35.853555700000001</v>
       </c>
       <c r="C739">
-        <v>137.54297600000001</v>
+        <v>137.74248499999999</v>
       </c>
       <c r="D739" s="2">
         <v>46098</v>
       </c>
+      <c r="E739" s="20">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F739">
+        <v>0</v>
+      </c>
+      <c r="G739">
+        <v>0</v>
+      </c>
+      <c r="H739">
+        <v>0</v>
+      </c>
+      <c r="I739">
+        <v>0</v>
+      </c>
       <c r="J739">
         <v>0</v>
       </c>
+      <c r="K739">
+        <v>0</v>
+      </c>
       <c r="L739">
-        <v>111</v>
+        <v>222</v>
+      </c>
+      <c r="M739">
+        <v>0</v>
+      </c>
+      <c r="N739">
+        <v>0</v>
       </c>
       <c r="O739">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="P739">
-        <v>167</v>
+        <v>222</v>
       </c>
       <c r="Q739" t="s">
-        <v>267</v>
+        <v>151</v>
       </c>
     </row>
     <row r="740" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A740" t="s">
-        <v>230</v>
+        <v>396</v>
       </c>
       <c r="B740">
-        <v>-35.081918000000002</v>
+        <v>-34.323770000000003</v>
       </c>
       <c r="C740">
-        <v>137.74822499999999</v>
+        <v>137.49154999999999</v>
       </c>
       <c r="D740" s="2">
-        <v>46099</v>
+        <v>46098</v>
       </c>
       <c r="E740" s="20">
-        <v>0.82291666666666663</v>
-      </c>
-      <c r="I740">
-        <v>111</v>
+        <v>0.69444444444444442</v>
       </c>
       <c r="J740">
         <v>0</v>
       </c>
-      <c r="L740">
-        <v>500</v>
-      </c>
-      <c r="N740">
-        <v>556</v>
-      </c>
-      <c r="O740">
-        <v>222</v>
-      </c>
-      <c r="P740">
-        <v>1389</v>
-      </c>
       <c r="Q740" t="s">
-        <v>219</v>
+        <v>267</v>
       </c>
     </row>
     <row r="741" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A741" t="s">
-        <v>230</v>
+        <v>360</v>
       </c>
       <c r="B741">
-        <v>-35.081918000000002</v>
+        <v>-34.494970000000002</v>
       </c>
       <c r="C741">
-        <v>137.74822499999999</v>
+        <v>137.48038</v>
       </c>
       <c r="D741" s="2">
-        <v>46099</v>
+        <v>46098</v>
       </c>
       <c r="E741" s="20">
-        <v>0.82291666666666663</v>
-      </c>
-      <c r="I741">
-        <v>111</v>
+        <v>0.54861111111111116</v>
       </c>
       <c r="J741">
         <v>0</v>
       </c>
-      <c r="L741">
-        <v>500</v>
-      </c>
-      <c r="N741">
-        <v>556</v>
-      </c>
-      <c r="O741">
-        <v>222</v>
-      </c>
-      <c r="P741">
-        <v>1389</v>
-      </c>
       <c r="Q741" t="s">
-        <v>219</v>
+        <v>267</v>
       </c>
     </row>
     <row r="742" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A742" t="s">
-        <v>377</v>
+        <v>304</v>
       </c>
       <c r="B742">
-        <v>-34.902070808541197</v>
+        <v>-34.899749999999997</v>
       </c>
       <c r="C742">
-        <v>137.79925776072</v>
+        <v>137.45174</v>
       </c>
       <c r="D742" s="2">
-        <v>46101</v>
+        <v>46098</v>
       </c>
       <c r="E742" s="20">
-        <v>0.71527777777777779</v>
-      </c>
-      <c r="I742">
-        <v>333</v>
+        <v>0.6875</v>
       </c>
       <c r="J742">
-        <v>0</v>
-      </c>
-      <c r="L742">
-        <v>56</v>
-      </c>
-      <c r="O742">
         <v>111</v>
       </c>
-      <c r="P742">
-        <v>500</v>
-      </c>
       <c r="Q742" t="s">
-        <v>368</v>
+        <v>267</v>
       </c>
     </row>
     <row r="743" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A743" t="s">
-        <v>379</v>
+        <v>401</v>
       </c>
       <c r="B743">
-        <v>-35.853555700000001</v>
+        <v>-34.075042000000003</v>
       </c>
       <c r="C743">
-        <v>137.74248499999999</v>
+        <v>137.54297600000001</v>
       </c>
       <c r="D743" s="2">
-        <v>46101</v>
-      </c>
-      <c r="E743" s="20">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="F743">
-        <v>0</v>
-      </c>
-      <c r="G743">
-        <v>0</v>
-      </c>
-      <c r="H743">
-        <v>0</v>
-      </c>
-      <c r="I743">
-        <v>0</v>
+        <v>46098</v>
       </c>
       <c r="J743">
         <v>0</v>
       </c>
-      <c r="K743">
-        <v>222</v>
-      </c>
       <c r="L743">
-        <v>333</v>
-      </c>
-      <c r="M743">
-        <v>0</v>
-      </c>
-      <c r="N743">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="O743">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="P743">
-        <v>555</v>
+        <v>167</v>
       </c>
       <c r="Q743" t="s">
-        <v>399</v>
+        <v>267</v>
       </c>
     </row>
     <row r="744" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A744" t="s">
-        <v>304</v>
+        <v>230</v>
       </c>
       <c r="B744">
-        <v>-34.899749999999997</v>
+        <v>-35.081918000000002</v>
       </c>
       <c r="C744">
-        <v>137.45174</v>
+        <v>137.74822499999999</v>
       </c>
       <c r="D744" s="2">
-        <v>46101</v>
+        <v>46099</v>
       </c>
       <c r="E744" s="20">
-        <v>0.65625</v>
+        <v>0.82291666666666663</v>
+      </c>
+      <c r="I744">
+        <v>111</v>
       </c>
       <c r="J744">
-        <v>111</v>
+        <v>0</v>
+      </c>
+      <c r="L744">
+        <v>500</v>
+      </c>
+      <c r="N744">
+        <v>556</v>
+      </c>
+      <c r="O744">
+        <v>222</v>
+      </c>
+      <c r="P744">
+        <v>1389</v>
       </c>
       <c r="Q744" t="s">
-        <v>267</v>
+        <v>219</v>
       </c>
     </row>
     <row r="745" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A745" t="s">
-        <v>356</v>
+        <v>230</v>
       </c>
       <c r="B745">
-        <v>-34.672499999999999</v>
+        <v>-35.081918000000002</v>
       </c>
       <c r="C745">
-        <v>137.49298999999999</v>
+        <v>137.74822499999999</v>
       </c>
       <c r="D745" s="2">
-        <v>46102</v>
+        <v>46099</v>
+      </c>
+      <c r="E745" s="20">
+        <v>0.82291666666666663</v>
+      </c>
+      <c r="I745">
+        <v>111</v>
       </c>
       <c r="J745">
         <v>0</v>
       </c>
+      <c r="L745">
+        <v>500</v>
+      </c>
+      <c r="N745">
+        <v>556</v>
+      </c>
+      <c r="O745">
+        <v>222</v>
+      </c>
+      <c r="P745">
+        <v>1389</v>
+      </c>
       <c r="Q745" t="s">
-        <v>267</v>
+        <v>219</v>
       </c>
     </row>
     <row r="746" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A746" t="s">
-        <v>79</v>
+        <v>377</v>
       </c>
       <c r="B746">
-        <v>-34.804662999999998</v>
+        <v>-34.902070808541197</v>
       </c>
       <c r="C746">
-        <v>138.540223</v>
+        <v>137.79925776072</v>
       </c>
       <c r="D746" s="2">
-        <v>46102</v>
+        <v>46101</v>
       </c>
       <c r="E746" s="20">
-        <v>0.47916666666666669</v>
+        <v>0.71527777777777779</v>
       </c>
       <c r="I746">
-        <v>9.3000000000000007</v>
+        <v>333</v>
       </c>
       <c r="J746">
         <v>0</v>
       </c>
       <c r="L746">
-        <v>43.35</v>
+        <v>56</v>
+      </c>
+      <c r="O746">
+        <v>111</v>
       </c>
       <c r="P746">
-        <v>52.650000000000006</v>
+        <v>500</v>
       </c>
       <c r="Q746" t="s">
-        <v>78</v>
+        <v>368</v>
       </c>
     </row>
     <row r="747" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A747" t="s">
-        <v>85</v>
+        <v>379</v>
       </c>
       <c r="B747">
-        <v>-34.873964000000001</v>
+        <v>-35.853555700000001</v>
       </c>
       <c r="C747">
-        <v>138.488134</v>
+        <v>137.74248499999999</v>
       </c>
       <c r="D747" s="2">
-        <v>46102</v>
+        <v>46101</v>
       </c>
       <c r="E747" s="20">
-        <v>0.45347222222222222</v>
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="F747">
+        <v>0</v>
+      </c>
+      <c r="G747">
+        <v>0</v>
+      </c>
+      <c r="H747">
+        <v>0</v>
       </c>
       <c r="I747">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="J747">
         <v>0</v>
       </c>
+      <c r="K747">
+        <v>222</v>
+      </c>
       <c r="L747">
-        <v>14.7</v>
+        <v>333</v>
+      </c>
+      <c r="M747">
+        <v>0</v>
+      </c>
+      <c r="N747">
+        <v>0</v>
       </c>
       <c r="O747">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="P747">
-        <v>27.299999999999997</v>
+        <v>555</v>
       </c>
       <c r="Q747" t="s">
-        <v>78</v>
+        <v>399</v>
       </c>
     </row>
     <row r="748" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A748" t="s">
-        <v>269</v>
+        <v>304</v>
       </c>
       <c r="B748">
-        <v>-34.824044999999998</v>
+        <v>-34.899749999999997</v>
       </c>
       <c r="C748">
-        <v>138.48377600000001</v>
+        <v>137.45174</v>
       </c>
       <c r="D748" s="2">
-        <v>46102</v>
+        <v>46101</v>
       </c>
       <c r="E748" s="20">
-        <v>0.46180555555555558</v>
-      </c>
-      <c r="G748">
-        <v>0.1</v>
-      </c>
-      <c r="I748">
-        <v>3.5</v>
+        <v>0.65625</v>
       </c>
       <c r="J748">
-        <v>0</v>
-      </c>
-      <c r="L748">
-        <v>11.8</v>
-      </c>
-      <c r="P748">
-        <v>15.4</v>
+        <v>111</v>
       </c>
       <c r="Q748" t="s">
-        <v>78</v>
+        <v>267</v>
       </c>
     </row>
     <row r="749" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A749" t="s">
-        <v>392</v>
+        <v>356</v>
       </c>
       <c r="B749">
-        <v>-34.958151000000001</v>
+        <v>-34.672499999999999</v>
       </c>
       <c r="C749">
-        <v>138.503987</v>
+        <v>137.49298999999999</v>
       </c>
       <c r="D749" s="2">
         <v>46102</v>
       </c>
-      <c r="E749" s="20">
-        <v>0.43402777777777779</v>
-      </c>
-      <c r="H749">
-        <v>0.3</v>
-      </c>
-      <c r="I749">
-        <v>1.65</v>
-      </c>
       <c r="J749">
         <v>0</v>
       </c>
-      <c r="L749">
-        <v>35.424999999999997</v>
-      </c>
-      <c r="P749">
-        <v>37.375</v>
-      </c>
       <c r="Q749" t="s">
-        <v>78</v>
+        <v>267</v>
       </c>
     </row>
     <row r="750" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A750" t="s">
-        <v>179</v>
+        <v>79</v>
       </c>
       <c r="B750">
-        <v>-35.078539999999997</v>
+        <v>-34.804662999999998</v>
       </c>
       <c r="C750">
-        <v>138.49587</v>
+        <v>138.540223</v>
       </c>
       <c r="D750" s="2">
         <v>46102</v>
       </c>
       <c r="E750" s="20">
-        <v>0.41666666666666669</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="I750">
-        <v>0.1</v>
+        <v>9.3000000000000007</v>
       </c>
       <c r="J750">
         <v>0</v>
       </c>
       <c r="L750">
-        <v>2.2999999999999998</v>
+        <v>43.35</v>
       </c>
       <c r="P750">
-        <v>2.4</v>
+        <v>52.650000000000006</v>
       </c>
       <c r="Q750" t="s">
         <v>78</v>
@@ -28582,177 +28597,165 @@
     </row>
     <row r="751" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A751" t="s">
-        <v>210</v>
+        <v>85</v>
       </c>
       <c r="B751">
-        <v>-35.739091000000002</v>
+        <v>-34.873964000000001</v>
       </c>
       <c r="C751">
-        <v>137.67788400000001</v>
+        <v>138.488134</v>
       </c>
       <c r="D751" s="2">
-        <v>46103</v>
+        <v>46102</v>
       </c>
       <c r="E751" s="20">
-        <v>0.6875</v>
-      </c>
-      <c r="F751">
-        <v>0</v>
-      </c>
-      <c r="G751">
-        <v>0</v>
-      </c>
-      <c r="H751">
-        <v>0</v>
+        <v>0.45347222222222222</v>
       </c>
       <c r="I751">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="J751">
         <v>0</v>
       </c>
-      <c r="K751">
-        <v>111</v>
-      </c>
       <c r="L751">
-        <v>0</v>
-      </c>
-      <c r="M751">
-        <v>555</v>
-      </c>
-      <c r="N751">
-        <v>0</v>
+        <v>14.7</v>
       </c>
       <c r="O751">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="P751">
-        <v>666</v>
+        <v>27.299999999999997</v>
       </c>
       <c r="Q751" t="s">
-        <v>399</v>
+        <v>78</v>
       </c>
     </row>
     <row r="752" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A752" t="s">
-        <v>402</v>
+        <v>269</v>
       </c>
       <c r="B752">
-        <v>-34.903120000000001</v>
+        <v>-34.824044999999998</v>
       </c>
       <c r="C752">
-        <v>137.44969</v>
+        <v>138.48377600000001</v>
       </c>
       <c r="D752" s="2">
-        <v>46103</v>
+        <v>46102</v>
       </c>
       <c r="E752" s="20">
-        <v>0.62847222222222221</v>
+        <v>0.46180555555555558</v>
+      </c>
+      <c r="G752">
+        <v>0.1</v>
       </c>
       <c r="I752">
-        <v>444</v>
+        <v>3.5</v>
       </c>
       <c r="J752">
         <v>0</v>
       </c>
       <c r="L752">
-        <v>56</v>
+        <v>11.8</v>
       </c>
       <c r="P752">
-        <v>500</v>
+        <v>15.4</v>
       </c>
       <c r="Q752" t="s">
-        <v>267</v>
+        <v>78</v>
       </c>
     </row>
     <row r="753" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A753" t="s">
-        <v>231</v>
+        <v>392</v>
       </c>
       <c r="B753">
-        <v>-35.054707999999998</v>
+        <v>-34.958151000000001</v>
       </c>
       <c r="C753">
-        <v>137.725145</v>
+        <v>138.503987</v>
       </c>
       <c r="D753" s="2">
-        <v>46103</v>
+        <v>46102</v>
       </c>
       <c r="E753" s="20">
-        <v>0.63541666666666663</v>
+        <v>0.43402777777777779</v>
+      </c>
+      <c r="H753">
+        <v>0.3</v>
       </c>
       <c r="I753">
-        <v>66500</v>
+        <v>1.65</v>
       </c>
       <c r="J753">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="L753">
-        <v>3000</v>
-      </c>
-      <c r="O753">
-        <v>667</v>
+        <v>35.424999999999997</v>
       </c>
       <c r="P753">
-        <v>70167</v>
+        <v>37.375</v>
       </c>
       <c r="Q753" t="s">
-        <v>219</v>
+        <v>78</v>
       </c>
     </row>
     <row r="754" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A754" t="s">
-        <v>403</v>
+        <v>179</v>
       </c>
       <c r="B754">
-        <v>-34.903466000000002</v>
+        <v>-35.078539999999997</v>
       </c>
       <c r="C754">
-        <v>137.79804799999999</v>
+        <v>138.49587</v>
       </c>
       <c r="D754" s="2">
-        <v>46103</v>
+        <v>46102</v>
       </c>
       <c r="E754" s="20">
-        <v>0.70833333333333337</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="I754">
-        <v>389</v>
+        <v>0.1</v>
       </c>
       <c r="J754">
         <v>0</v>
       </c>
       <c r="L754">
-        <v>500</v>
-      </c>
-      <c r="N754">
-        <v>389</v>
-      </c>
-      <c r="O754">
-        <v>56</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="P754">
-        <v>1333</v>
+        <v>2.4</v>
       </c>
       <c r="Q754" t="s">
-        <v>219</v>
+        <v>78</v>
       </c>
     </row>
     <row r="755" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A755" t="s">
-        <v>404</v>
+        <v>210</v>
       </c>
       <c r="B755">
-        <v>-34.765996000000001</v>
+        <v>-35.739091000000002</v>
       </c>
       <c r="C755">
-        <v>137.86211299999999</v>
+        <v>137.67788400000001</v>
       </c>
       <c r="D755" s="2">
         <v>46103</v>
       </c>
       <c r="E755" s="20">
-        <v>0.67708333333333337</v>
+        <v>0.6875</v>
+      </c>
+      <c r="F755">
+        <v>0</v>
+      </c>
+      <c r="G755">
+        <v>0</v>
+      </c>
+      <c r="H755">
+        <v>0</v>
       </c>
       <c r="I755">
         <v>0</v>
@@ -28760,37 +28763,46 @@
       <c r="J755">
         <v>0</v>
       </c>
+      <c r="K755">
+        <v>111</v>
+      </c>
       <c r="L755">
-        <v>222</v>
+        <v>0</v>
+      </c>
+      <c r="M755">
+        <v>555</v>
       </c>
       <c r="N755">
-        <v>389</v>
+        <v>0</v>
       </c>
       <c r="O755">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="P755">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="Q755" t="s">
-        <v>219</v>
+        <v>399</v>
       </c>
     </row>
     <row r="756" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A756" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="B756">
-        <v>-35.510620000000003</v>
+        <v>-34.903120000000001</v>
       </c>
       <c r="C756">
-        <v>138.21679599999999</v>
+        <v>137.44969</v>
       </c>
       <c r="D756" s="2">
         <v>46103</v>
       </c>
+      <c r="E756" s="20">
+        <v>0.62847222222222221</v>
+      </c>
       <c r="I756">
-        <v>167</v>
+        <v>444</v>
       </c>
       <c r="J756">
         <v>0</v>
@@ -28798,310 +28810,298 @@
       <c r="L756">
         <v>56</v>
       </c>
-      <c r="N756">
-        <v>1389</v>
-      </c>
-      <c r="O756">
-        <v>722</v>
-      </c>
       <c r="P756">
-        <v>2334</v>
+        <v>500</v>
       </c>
       <c r="Q756" t="s">
-        <v>253</v>
+        <v>267</v>
       </c>
     </row>
     <row r="757" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A757" t="s">
-        <v>400</v>
+        <v>231</v>
       </c>
       <c r="B757">
-        <v>-35.793973000000001</v>
+        <v>-35.054707999999998</v>
       </c>
       <c r="C757">
-        <v>137.852418</v>
+        <v>137.725145</v>
       </c>
       <c r="D757" s="2">
-        <v>46104</v>
+        <v>46103</v>
       </c>
       <c r="E757" s="20">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="F757">
-        <v>0</v>
-      </c>
-      <c r="G757">
-        <v>0</v>
-      </c>
-      <c r="H757">
-        <v>1333</v>
+        <v>0.63541666666666663</v>
       </c>
       <c r="I757">
-        <v>1000</v>
+        <v>66500</v>
       </c>
       <c r="J757">
-        <v>0</v>
-      </c>
-      <c r="K757">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="L757">
-        <v>3778</v>
-      </c>
-      <c r="M757">
-        <v>333</v>
-      </c>
-      <c r="N757">
-        <v>333</v>
+        <v>3000</v>
       </c>
       <c r="O757">
-        <v>556</v>
+        <v>667</v>
       </c>
       <c r="P757">
-        <v>7333</v>
+        <v>70167</v>
       </c>
       <c r="Q757" t="s">
-        <v>399</v>
+        <v>219</v>
       </c>
     </row>
     <row r="758" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A758" t="s">
-        <v>363</v>
+        <v>403</v>
       </c>
       <c r="B758">
-        <v>-35.878667100000001</v>
+        <v>-34.903466000000002</v>
       </c>
       <c r="C758">
-        <v>137.6963188</v>
+        <v>137.79804799999999</v>
       </c>
       <c r="D758" s="2">
-        <v>46104</v>
+        <v>46103</v>
       </c>
       <c r="E758" s="20">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F758">
-        <v>0</v>
-      </c>
-      <c r="G758">
-        <v>0</v>
-      </c>
-      <c r="H758">
-        <v>0</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="I758">
-        <v>0</v>
+        <v>389</v>
       </c>
       <c r="J758">
         <v>0</v>
       </c>
-      <c r="K758">
-        <v>0</v>
-      </c>
       <c r="L758">
-        <v>0</v>
-      </c>
-      <c r="M758">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="N758">
-        <v>0</v>
+        <v>389</v>
       </c>
       <c r="O758">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="P758">
-        <v>0</v>
+        <v>1333</v>
       </c>
       <c r="Q758" t="s">
-        <v>399</v>
+        <v>219</v>
       </c>
     </row>
     <row r="759" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A759" t="s">
-        <v>315</v>
+        <v>404</v>
       </c>
       <c r="B759">
-        <v>-35.445188000000002</v>
+        <v>-34.765996000000001</v>
       </c>
       <c r="C759">
-        <v>138.307266</v>
+        <v>137.86211299999999</v>
       </c>
       <c r="D759" s="2">
-        <v>46104</v>
+        <v>46103</v>
+      </c>
+      <c r="E759" s="20">
+        <v>0.67708333333333337</v>
       </c>
       <c r="I759">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="J759">
         <v>0</v>
       </c>
       <c r="L759">
-        <v>0</v>
+        <v>222</v>
       </c>
       <c r="N759">
-        <v>167</v>
+        <v>389</v>
       </c>
       <c r="O759">
-        <v>1444</v>
+        <v>56</v>
       </c>
       <c r="P759">
-        <v>1722</v>
+        <v>667</v>
       </c>
       <c r="Q759" t="s">
-        <v>406</v>
+        <v>219</v>
       </c>
     </row>
     <row r="760" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A760" t="s">
-        <v>88</v>
+        <v>405</v>
       </c>
       <c r="B760">
-        <v>-35.581124000000003</v>
+        <v>-35.510620000000003</v>
       </c>
       <c r="C760">
-        <v>138.60879700000001</v>
+        <v>138.21679599999999</v>
       </c>
       <c r="D760" s="2">
-        <v>46096</v>
-      </c>
-      <c r="G760">
-        <v>111</v>
-      </c>
-      <c r="H760">
+        <v>46103</v>
+      </c>
+      <c r="I760">
+        <v>167</v>
+      </c>
+      <c r="J760">
+        <v>0</v>
+      </c>
+      <c r="L760">
         <v>56</v>
       </c>
-      <c r="I760">
-        <v>56</v>
-      </c>
-      <c r="J760">
-        <v>0</v>
-      </c>
-      <c r="L760">
-        <v>222</v>
-      </c>
       <c r="N760">
-        <v>111</v>
+        <v>1389</v>
       </c>
       <c r="O760">
-        <v>333</v>
+        <v>722</v>
       </c>
       <c r="P760">
-        <v>889</v>
+        <v>2334</v>
       </c>
       <c r="Q760" t="s">
-        <v>129</v>
+        <v>253</v>
       </c>
     </row>
     <row r="761" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A761" t="s">
-        <v>89</v>
+        <v>400</v>
       </c>
       <c r="B761">
-        <v>-35.6048446</v>
+        <v>-35.793973000000001</v>
       </c>
       <c r="C761">
-        <v>138.59278499999999</v>
+        <v>137.852418</v>
       </c>
       <c r="D761" s="2">
-        <v>46096</v>
+        <v>46104</v>
+      </c>
+      <c r="E761" s="20">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="F761">
+        <v>0</v>
+      </c>
+      <c r="G761">
+        <v>0</v>
       </c>
       <c r="H761">
-        <v>389</v>
+        <v>1333</v>
       </c>
       <c r="I761">
-        <v>222</v>
+        <v>1000</v>
       </c>
       <c r="J761">
         <v>0</v>
       </c>
+      <c r="K761">
+        <v>0</v>
+      </c>
       <c r="L761">
-        <v>111</v>
+        <v>3778</v>
+      </c>
+      <c r="M761">
+        <v>333</v>
       </c>
       <c r="N761">
-        <v>500</v>
+        <v>333</v>
       </c>
       <c r="O761">
-        <v>1111</v>
+        <v>556</v>
       </c>
       <c r="P761">
-        <v>2333</v>
+        <v>7333</v>
       </c>
       <c r="Q761" t="s">
-        <v>129</v>
+        <v>399</v>
       </c>
     </row>
     <row r="762" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A762" t="s">
-        <v>378</v>
+        <v>363</v>
       </c>
       <c r="B762">
-        <v>-35.612285999999997</v>
+        <v>-35.878667100000001</v>
       </c>
       <c r="C762">
-        <v>138.564302</v>
+        <v>137.6963188</v>
       </c>
       <c r="D762" s="2">
-        <v>46096</v>
+        <v>46104</v>
+      </c>
+      <c r="E762" s="20">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F762">
+        <v>0</v>
+      </c>
+      <c r="G762">
+        <v>0</v>
       </c>
       <c r="H762">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="I762">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="J762">
         <v>0</v>
       </c>
+      <c r="K762">
+        <v>0</v>
+      </c>
       <c r="L762">
-        <v>333</v>
+        <v>0</v>
+      </c>
+      <c r="M762">
+        <v>0</v>
       </c>
       <c r="N762">
-        <v>222</v>
+        <v>0</v>
       </c>
       <c r="O762">
-        <v>389</v>
+        <v>0</v>
       </c>
       <c r="P762">
-        <v>1056</v>
+        <v>0</v>
       </c>
       <c r="Q762" t="s">
-        <v>129</v>
+        <v>399</v>
       </c>
     </row>
     <row r="763" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A763" t="s">
-        <v>301</v>
+        <v>315</v>
       </c>
       <c r="B763">
-        <v>-35.61</v>
+        <v>-35.445188000000002</v>
       </c>
       <c r="C763">
-        <v>138.5925</v>
+        <v>138.307266</v>
       </c>
       <c r="D763" s="2">
-        <v>46096</v>
+        <v>46104</v>
       </c>
       <c r="I763">
-        <v>444</v>
+        <v>111</v>
       </c>
       <c r="J763">
         <v>0</v>
       </c>
       <c r="L763">
-        <v>278</v>
+        <v>0</v>
       </c>
       <c r="N763">
         <v>167</v>
       </c>
       <c r="O763">
-        <v>612</v>
+        <v>1444</v>
       </c>
       <c r="P763">
-        <v>1501</v>
+        <v>1722</v>
       </c>
       <c r="Q763" t="s">
-        <v>129</v>
+        <v>406</v>
       </c>
     </row>
     <row r="764" spans="1:17" x14ac:dyDescent="0.3">
@@ -29138,239 +29138,258 @@
     </row>
     <row r="765" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A765" t="s">
+        <v>315</v>
+      </c>
+      <c r="B765">
+        <v>-35.445186</v>
+      </c>
+      <c r="C765">
+        <v>138.307424</v>
+      </c>
+      <c r="D765" s="2">
+        <v>46104</v>
+      </c>
+      <c r="E765" s="20">
+        <v>0.38541666666666669</v>
+      </c>
+      <c r="I765">
+        <v>0</v>
+      </c>
+      <c r="J765">
+        <v>0</v>
+      </c>
+      <c r="L765">
+        <v>56</v>
+      </c>
+      <c r="N765">
+        <v>56</v>
+      </c>
+      <c r="O765">
+        <v>778</v>
+      </c>
+      <c r="P765">
+        <v>890</v>
+      </c>
+      <c r="Q765" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="766" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A766" t="s">
         <v>356</v>
       </c>
-      <c r="B765">
+      <c r="B766">
         <v>-34.672499999999999</v>
       </c>
-      <c r="C765">
+      <c r="C766">
         <v>137.49298999999999</v>
       </c>
-      <c r="D765" s="2">
+      <c r="D766" s="2">
         <v>46106</v>
       </c>
-      <c r="E765" s="20">
+      <c r="E766" s="20">
         <v>0.57291666666666663</v>
       </c>
-      <c r="I765">
+      <c r="I766">
         <v>56</v>
       </c>
-      <c r="J765">
-        <v>0</v>
-      </c>
-      <c r="L765">
+      <c r="J766">
+        <v>0</v>
+      </c>
+      <c r="L766">
         <v>111</v>
       </c>
-      <c r="O765">
+      <c r="O766">
         <v>56</v>
       </c>
-      <c r="P765">
+      <c r="P766">
         <v>223</v>
       </c>
-      <c r="Q765" t="s">
+      <c r="Q766" t="s">
         <v>267</v>
-      </c>
-    </row>
-    <row r="766" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A766" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="B766" s="1">
-        <v>-35.516800000000003</v>
-      </c>
-      <c r="C766" s="1">
-        <v>138.73820000000001</v>
-      </c>
-      <c r="D766" s="2">
-        <v>46109</v>
-      </c>
-      <c r="E766" s="20">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="F766" s="1"/>
-      <c r="G766" s="1"/>
-      <c r="H766" s="1"/>
-      <c r="I766" s="1">
-        <v>111</v>
-      </c>
-      <c r="J766" s="1">
-        <v>0</v>
-      </c>
-      <c r="K766" s="1"/>
-      <c r="L766" s="1">
-        <v>611</v>
-      </c>
-      <c r="M766" s="1"/>
-      <c r="N766" s="1"/>
-      <c r="O766" s="1"/>
-      <c r="P766">
-        <f>SUM(F766:I766,K766:O766)</f>
-        <v>722</v>
-      </c>
-      <c r="Q766" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="767" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A767" t="s">
-        <v>188</v>
+        <v>352</v>
       </c>
       <c r="B767">
-        <v>-35.515900000000002</v>
+        <v>-34.860666999999999</v>
       </c>
       <c r="C767">
-        <v>138.70529999999999</v>
+        <v>138.490938</v>
       </c>
       <c r="D767" s="2">
-        <v>46109</v>
+        <v>46108</v>
       </c>
       <c r="E767" s="20">
-        <v>0.42708333333333331</v>
+        <v>0.46180555555555558</v>
       </c>
       <c r="I767">
-        <v>56</v>
+        <v>2.4</v>
       </c>
       <c r="J767">
         <v>0</v>
       </c>
       <c r="L767">
-        <v>111</v>
+        <v>5.625</v>
+      </c>
+      <c r="M767">
+        <v>0.15</v>
+      </c>
+      <c r="N767">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="O767">
+        <v>0.15</v>
       </c>
       <c r="P767">
-        <f>SUM(F767:I767,K767:O767)</f>
-        <v>167</v>
+        <v>8.4</v>
       </c>
       <c r="Q767" t="s">
-        <v>187</v>
+        <v>78</v>
       </c>
     </row>
     <row r="768" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A768" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="B768">
-        <v>-35.536299999999997</v>
+        <v>-34.873964000000001</v>
       </c>
       <c r="C768">
-        <v>138.67859999999999</v>
+        <v>138.488134</v>
       </c>
       <c r="D768" s="2">
-        <v>46109</v>
+        <v>46108</v>
       </c>
       <c r="E768" s="20">
-        <v>0.4375</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="I768">
-        <v>222</v>
+        <v>3.9</v>
       </c>
       <c r="J768">
         <v>0</v>
       </c>
       <c r="L768">
-        <v>56</v>
+        <v>10.199999999999999</v>
+      </c>
+      <c r="O768">
+        <v>0.22500000000000001</v>
       </c>
       <c r="P768">
-        <f t="shared" ref="P768:P777" si="1">SUM(F768:I768,K768:O768)</f>
-        <v>278</v>
+        <v>14.324999999999999</v>
       </c>
       <c r="Q768" t="s">
-        <v>187</v>
+        <v>78</v>
       </c>
     </row>
     <row r="769" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A769" t="s">
-        <v>186</v>
+        <v>79</v>
       </c>
       <c r="B769">
-        <v>-35.538600000000002</v>
+        <v>-34.804662999999998</v>
       </c>
       <c r="C769">
-        <v>138.6497</v>
+        <v>138.540223</v>
       </c>
       <c r="D769" s="2">
-        <v>46109</v>
+        <v>46108</v>
       </c>
       <c r="E769" s="20">
-        <v>0.44791666666666669</v>
+        <v>0.49305555555555558</v>
       </c>
       <c r="I769">
-        <v>56</v>
+        <v>2.25</v>
       </c>
       <c r="J769">
         <v>0</v>
       </c>
       <c r="L769">
-        <v>56</v>
+        <v>37.950000000000003</v>
       </c>
       <c r="P769">
-        <f t="shared" si="1"/>
-        <v>112</v>
+        <v>40.200000000000003</v>
       </c>
       <c r="Q769" t="s">
-        <v>187</v>
+        <v>78</v>
       </c>
     </row>
     <row r="770" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A770" t="s">
-        <v>318</v>
+        <v>269</v>
       </c>
       <c r="B770">
-        <v>-35.5565</v>
+        <v>-34.824044999999998</v>
       </c>
       <c r="C770">
-        <v>138.62610000000001</v>
+        <v>138.48377600000001</v>
       </c>
       <c r="D770" s="2">
-        <v>46109</v>
+        <v>46108</v>
       </c>
       <c r="E770" s="20">
-        <v>0.4826388888888889</v>
+        <v>0.47569444444444442</v>
+      </c>
+      <c r="G770">
+        <v>0.3</v>
+      </c>
+      <c r="H770">
+        <v>0.05</v>
       </c>
       <c r="I770">
-        <v>0</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="J770">
         <v>0</v>
       </c>
       <c r="L770">
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="P770">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>9.75</v>
       </c>
       <c r="Q770" t="s">
-        <v>187</v>
+        <v>78</v>
       </c>
     </row>
     <row r="771" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A771" t="s">
-        <v>189</v>
-      </c>
-      <c r="B771">
-        <v>-35.5565</v>
-      </c>
-      <c r="C771">
-        <v>138.62610000000001</v>
+      <c r="A771" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="B771" s="1">
+        <v>-35.516800000000003</v>
+      </c>
+      <c r="C771" s="1">
+        <v>138.73820000000001</v>
       </c>
       <c r="D771" s="2">
         <v>46109</v>
       </c>
       <c r="E771" s="20">
-        <v>0.46527777777777779</v>
-      </c>
-      <c r="I771">
-        <v>222</v>
-      </c>
-      <c r="J771">
-        <v>0</v>
-      </c>
-      <c r="L771">
-        <v>56</v>
-      </c>
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="F771" s="1"/>
+      <c r="G771" s="1"/>
+      <c r="H771" s="1"/>
+      <c r="I771" s="1">
+        <v>111</v>
+      </c>
+      <c r="J771" s="1">
+        <v>0</v>
+      </c>
+      <c r="K771" s="1"/>
+      <c r="L771" s="1">
+        <v>611</v>
+      </c>
+      <c r="M771" s="1"/>
+      <c r="N771" s="1"/>
+      <c r="O771" s="1"/>
       <c r="P771">
-        <f t="shared" si="1"/>
-        <v>278</v>
+        <f>SUM(F771:I771,K771:O771)</f>
+        <v>722</v>
       </c>
       <c r="Q771" t="s">
         <v>187</v>
@@ -29378,32 +29397,32 @@
     </row>
     <row r="772" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A772" t="s">
-        <v>320</v>
+        <v>188</v>
       </c>
       <c r="B772">
-        <v>-35.634900000000002</v>
+        <v>-35.515900000000002</v>
       </c>
       <c r="C772">
-        <v>138.49850000000001</v>
+        <v>138.70529999999999</v>
       </c>
       <c r="D772" s="2">
         <v>46109</v>
       </c>
       <c r="E772" s="20">
-        <v>0.4861111111111111</v>
+        <v>0.42708333333333331</v>
       </c>
       <c r="I772">
-        <v>278</v>
+        <v>56</v>
       </c>
       <c r="J772">
         <v>0</v>
       </c>
       <c r="L772">
+        <v>111</v>
+      </c>
+      <c r="P772">
+        <f>SUM(F772:I772,K772:O772)</f>
         <v>167</v>
-      </c>
-      <c r="P772">
-        <f t="shared" si="1"/>
-        <v>445</v>
       </c>
       <c r="Q772" t="s">
         <v>187</v>
@@ -29411,32 +29430,32 @@
     </row>
     <row r="773" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A773" t="s">
-        <v>319</v>
+        <v>91</v>
       </c>
       <c r="B773">
-        <v>-35.563899999999997</v>
+        <v>-35.536299999999997</v>
       </c>
       <c r="C773">
-        <v>138.6131</v>
+        <v>138.67859999999999</v>
       </c>
       <c r="D773" s="2">
         <v>46109</v>
       </c>
       <c r="E773" s="20">
-        <v>0.50347222222222221</v>
+        <v>0.4375</v>
       </c>
       <c r="I773">
+        <v>222</v>
+      </c>
+      <c r="J773">
+        <v>0</v>
+      </c>
+      <c r="L773">
         <v>56</v>
       </c>
-      <c r="J773">
-        <v>0</v>
-      </c>
-      <c r="L773">
-        <v>0</v>
-      </c>
       <c r="P773">
-        <f t="shared" si="1"/>
-        <v>56</v>
+        <f>SUM(F773:I773,K773:O773)</f>
+        <v>278</v>
       </c>
       <c r="Q773" t="s">
         <v>187</v>
@@ -29444,22 +29463,22 @@
     </row>
     <row r="774" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A774" t="s">
-        <v>407</v>
+        <v>186</v>
       </c>
       <c r="B774">
-        <v>-35.548499999999997</v>
+        <v>-35.538600000000002</v>
       </c>
       <c r="C774">
-        <v>138.62710000000001</v>
+        <v>138.6497</v>
       </c>
       <c r="D774" s="2">
         <v>46109</v>
       </c>
       <c r="E774" s="20">
-        <v>0.47222222222222221</v>
+        <v>0.44791666666666669</v>
       </c>
       <c r="I774">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="J774">
         <v>0</v>
@@ -29468,8 +29487,8 @@
         <v>56</v>
       </c>
       <c r="P774">
-        <f t="shared" si="1"/>
-        <v>56</v>
+        <f>SUM(F774:I774,K774:O774)</f>
+        <v>112</v>
       </c>
       <c r="Q774" t="s">
         <v>187</v>
@@ -29477,19 +29496,19 @@
     </row>
     <row r="775" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A775" t="s">
-        <v>408</v>
+        <v>318</v>
       </c>
       <c r="B775">
-        <v>-35.5595</v>
+        <v>-35.5565</v>
       </c>
       <c r="C775">
-        <v>138.6275</v>
+        <v>138.62610000000001</v>
       </c>
       <c r="D775" s="2">
         <v>46109</v>
       </c>
       <c r="E775" s="20">
-        <v>0.48958333333333331</v>
+        <v>0.4826388888888889</v>
       </c>
       <c r="I775">
         <v>0</v>
@@ -29498,11 +29517,11 @@
         <v>0</v>
       </c>
       <c r="L775">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="P775">
-        <f t="shared" si="1"/>
-        <v>56</v>
+        <f>SUM(F775:I775,K775:O775)</f>
+        <v>0</v>
       </c>
       <c r="Q775" t="s">
         <v>187</v>
@@ -29510,32 +29529,32 @@
     </row>
     <row r="776" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A776" t="s">
-        <v>409</v>
+        <v>189</v>
       </c>
       <c r="B776">
-        <v>-35.585299999999997</v>
+        <v>-35.5565</v>
       </c>
       <c r="C776">
-        <v>138.5985</v>
+        <v>138.62610000000001</v>
       </c>
       <c r="D776" s="2">
         <v>46109</v>
       </c>
       <c r="E776" s="20">
-        <v>0.51388888888888884</v>
+        <v>0.46527777777777779</v>
       </c>
       <c r="I776">
+        <v>222</v>
+      </c>
+      <c r="J776">
+        <v>0</v>
+      </c>
+      <c r="L776">
         <v>56</v>
       </c>
-      <c r="J776">
-        <v>0</v>
-      </c>
-      <c r="L776">
-        <v>0</v>
-      </c>
       <c r="P776">
-        <f t="shared" si="1"/>
-        <v>56</v>
+        <f>SUM(F776:I776,K776:O776)</f>
+        <v>278</v>
       </c>
       <c r="Q776" t="s">
         <v>187</v>
@@ -29543,32 +29562,32 @@
     </row>
     <row r="777" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A777" t="s">
-        <v>86</v>
+        <v>320</v>
       </c>
       <c r="B777">
-        <v>-35.5413</v>
+        <v>-35.634900000000002</v>
       </c>
       <c r="C777">
-        <v>138.64080000000001</v>
+        <v>138.49850000000001</v>
       </c>
       <c r="D777" s="2">
         <v>46109</v>
       </c>
       <c r="E777" s="20">
-        <v>0.45833333333333331</v>
+        <v>0.4861111111111111</v>
       </c>
       <c r="I777">
-        <v>0</v>
+        <v>278</v>
       </c>
       <c r="J777">
         <v>0</v>
       </c>
       <c r="L777">
-        <v>111</v>
+        <v>167</v>
       </c>
       <c r="P777">
-        <f t="shared" si="1"/>
-        <v>111</v>
+        <f>SUM(F777:I777,K777:O777)</f>
+        <v>445</v>
       </c>
       <c r="Q777" t="s">
         <v>187</v>
@@ -29576,22 +29595,19 @@
     </row>
     <row r="778" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A778" t="s">
-        <v>59</v>
+        <v>319</v>
       </c>
       <c r="B778">
-        <v>-35.084850000000003</v>
+        <v>-35.563899999999997</v>
       </c>
       <c r="C778">
-        <v>137.74889999999999</v>
+        <v>138.6131</v>
       </c>
       <c r="D778" s="2">
-        <v>46113</v>
+        <v>46109</v>
       </c>
       <c r="E778" s="20">
-        <v>0.58333333333333337</v>
-      </c>
-      <c r="G778">
-        <v>0</v>
+        <v>0.50347222222222221</v>
       </c>
       <c r="I778">
         <v>56</v>
@@ -29600,36 +29616,31 @@
         <v>0</v>
       </c>
       <c r="L778">
-        <v>222</v>
-      </c>
-      <c r="M778">
-        <v>111</v>
-      </c>
-      <c r="N778">
-        <v>777</v>
+        <v>0</v>
       </c>
       <c r="P778">
-        <v>1166</v>
+        <f>SUM(F778:I778,K778:O778)</f>
+        <v>56</v>
       </c>
       <c r="Q778" t="s">
-        <v>149</v>
+        <v>187</v>
       </c>
     </row>
     <row r="779" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A779" t="s">
-        <v>315</v>
+        <v>407</v>
       </c>
       <c r="B779">
-        <v>-35.445186</v>
+        <v>-35.548499999999997</v>
       </c>
       <c r="C779">
-        <v>138.307424</v>
+        <v>138.62710000000001</v>
       </c>
       <c r="D779" s="2">
-        <v>46104</v>
+        <v>46109</v>
       </c>
       <c r="E779" s="20">
-        <v>0.38541666666666669</v>
+        <v>0.47222222222222221</v>
       </c>
       <c r="I779">
         <v>0</v>
@@ -29640,327 +29651,346 @@
       <c r="L779">
         <v>56</v>
       </c>
-      <c r="N779">
+      <c r="P779">
+        <f>SUM(F779:I779,K779:O779)</f>
         <v>56</v>
       </c>
-      <c r="O779">
-        <v>778</v>
-      </c>
-      <c r="P779">
-        <v>890</v>
-      </c>
       <c r="Q779" t="s">
-        <v>406</v>
+        <v>187</v>
       </c>
     </row>
     <row r="780" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A780" t="s">
-        <v>342</v>
+        <v>408</v>
       </c>
       <c r="B780">
-        <v>-35.500242</v>
+        <v>-35.5595</v>
       </c>
       <c r="C780">
-        <v>138.24491</v>
+        <v>138.6275</v>
       </c>
       <c r="D780" s="2">
         <v>46109</v>
       </c>
       <c r="E780" s="20">
-        <v>0.68055555555555547</v>
+        <v>0.48958333333333331</v>
       </c>
       <c r="I780">
-        <v>444</v>
+        <v>0</v>
       </c>
       <c r="J780">
         <v>0</v>
       </c>
       <c r="L780">
-        <v>2667</v>
-      </c>
-      <c r="N780">
-        <v>556</v>
-      </c>
-      <c r="O780">
-        <v>4889</v>
+        <v>56</v>
       </c>
       <c r="P780">
-        <v>8556</v>
+        <f>SUM(F780:I780,K780:O780)</f>
+        <v>56</v>
       </c>
       <c r="Q780" t="s">
-        <v>253</v>
+        <v>187</v>
       </c>
     </row>
     <row r="781" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A781" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B781">
-        <v>-35.499946999999999</v>
+        <v>-35.585299999999997</v>
       </c>
       <c r="C781">
-        <v>138.242954</v>
+        <v>138.5985</v>
       </c>
       <c r="D781" s="2">
         <v>46109</v>
       </c>
       <c r="E781" s="20">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="H781">
-        <v>2222</v>
+        <v>0.51388888888888884</v>
       </c>
       <c r="I781">
-        <v>3333</v>
+        <v>56</v>
       </c>
       <c r="J781">
         <v>0</v>
       </c>
       <c r="L781">
-        <v>222</v>
-      </c>
-      <c r="N781">
-        <v>2556</v>
-      </c>
-      <c r="O781">
-        <v>444</v>
+        <v>0</v>
       </c>
       <c r="P781">
-        <v>8777</v>
+        <f>SUM(F781:I781,K781:O781)</f>
+        <v>56</v>
       </c>
       <c r="Q781" t="s">
-        <v>253</v>
+        <v>187</v>
       </c>
     </row>
     <row r="782" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A782" t="s">
-        <v>352</v>
+        <v>86</v>
       </c>
       <c r="B782">
-        <v>-34.860666999999999</v>
+        <v>-35.5413</v>
       </c>
       <c r="C782">
-        <v>138.490938</v>
+        <v>138.64080000000001</v>
       </c>
       <c r="D782" s="2">
-        <v>46108</v>
+        <v>46109</v>
       </c>
       <c r="E782" s="20">
-        <v>0.46180555555555558</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="I782">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="J782">
         <v>0</v>
       </c>
       <c r="L782">
-        <v>5.625</v>
-      </c>
-      <c r="M782">
-        <v>0.15</v>
-      </c>
-      <c r="N782">
-        <v>7.4999999999999997E-2</v>
-      </c>
-      <c r="O782">
-        <v>0.15</v>
+        <v>111</v>
       </c>
       <c r="P782">
-        <v>8.4</v>
+        <f>SUM(F782:I782,K782:O782)</f>
+        <v>111</v>
       </c>
       <c r="Q782" t="s">
-        <v>78</v>
+        <v>187</v>
       </c>
     </row>
     <row r="783" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A783" t="s">
-        <v>85</v>
+        <v>342</v>
       </c>
       <c r="B783">
-        <v>-34.873964000000001</v>
+        <v>-35.500242</v>
       </c>
       <c r="C783">
-        <v>138.488134</v>
+        <v>138.24491</v>
       </c>
       <c r="D783" s="2">
-        <v>46108</v>
+        <v>46109</v>
       </c>
       <c r="E783" s="20">
-        <v>0.45833333333333331</v>
+        <v>0.68055555555555547</v>
       </c>
       <c r="I783">
-        <v>3.9</v>
+        <v>444</v>
       </c>
       <c r="J783">
         <v>0</v>
       </c>
       <c r="L783">
-        <v>10.199999999999999</v>
+        <v>2667</v>
+      </c>
+      <c r="N783">
+        <v>556</v>
       </c>
       <c r="O783">
-        <v>0.22500000000000001</v>
+        <v>4889</v>
       </c>
       <c r="P783">
-        <v>14.324999999999999</v>
+        <v>8556</v>
       </c>
       <c r="Q783" t="s">
-        <v>78</v>
+        <v>253</v>
       </c>
     </row>
     <row r="784" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A784" t="s">
-        <v>79</v>
+        <v>410</v>
       </c>
       <c r="B784">
-        <v>-34.804662999999998</v>
+        <v>-35.499946999999999</v>
       </c>
       <c r="C784">
-        <v>138.540223</v>
+        <v>138.242954</v>
       </c>
       <c r="D784" s="2">
-        <v>46108</v>
+        <v>46109</v>
       </c>
       <c r="E784" s="20">
-        <v>0.49305555555555558</v>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="H784">
+        <v>2222</v>
       </c>
       <c r="I784">
-        <v>2.25</v>
+        <v>3333</v>
       </c>
       <c r="J784">
         <v>0</v>
       </c>
       <c r="L784">
-        <v>37.950000000000003</v>
+        <v>222</v>
+      </c>
+      <c r="N784">
+        <v>2556</v>
+      </c>
+      <c r="O784">
+        <v>444</v>
       </c>
       <c r="P784">
-        <v>40.200000000000003</v>
+        <v>8777</v>
       </c>
       <c r="Q784" t="s">
-        <v>78</v>
+        <v>253</v>
       </c>
     </row>
     <row r="785" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A785" t="s">
-        <v>269</v>
+        <v>400</v>
       </c>
       <c r="B785">
-        <v>-34.824044999999998</v>
+        <v>-35.793973000000001</v>
       </c>
       <c r="C785">
-        <v>138.48377600000001</v>
+        <v>137.852418</v>
       </c>
       <c r="D785" s="2">
-        <v>46108</v>
+        <v>46110</v>
       </c>
       <c r="E785" s="20">
-        <v>0.47569444444444442</v>
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="F785">
+        <v>1222</v>
       </c>
       <c r="G785">
-        <v>0.3</v>
+        <v>667</v>
       </c>
       <c r="H785">
-        <v>0.05</v>
+        <v>1333</v>
       </c>
       <c r="I785">
-        <v>1.1499999999999999</v>
+        <v>1000</v>
       </c>
       <c r="J785">
         <v>0</v>
       </c>
+      <c r="K785">
+        <v>0</v>
+      </c>
       <c r="L785">
-        <v>8.25</v>
+        <v>3778</v>
+      </c>
+      <c r="M785">
+        <v>222</v>
+      </c>
+      <c r="N785">
+        <v>333</v>
+      </c>
+      <c r="O785">
+        <v>0</v>
       </c>
       <c r="P785">
-        <v>9.75</v>
+        <v>8555</v>
       </c>
       <c r="Q785" t="s">
-        <v>78</v>
+        <v>399</v>
       </c>
     </row>
     <row r="786" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A786" t="s">
-        <v>93</v>
+        <v>210</v>
       </c>
       <c r="B786">
-        <v>-35.514747999999997</v>
+        <v>-35.739091000000002</v>
       </c>
       <c r="C786">
-        <v>138.71989600000001</v>
+        <v>137.67788400000001</v>
       </c>
       <c r="D786" s="2">
-        <v>46111</v>
+        <v>46110</v>
       </c>
       <c r="E786" s="20">
-        <v>0.375</v>
+        <v>0.4375</v>
+      </c>
+      <c r="F786">
+        <v>222</v>
+      </c>
+      <c r="G786">
+        <v>0</v>
+      </c>
+      <c r="H786">
+        <v>1333</v>
       </c>
       <c r="I786">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="J786">
         <v>0</v>
       </c>
+      <c r="K786">
+        <v>0</v>
+      </c>
       <c r="L786">
-        <v>111.6</v>
+        <v>5778</v>
+      </c>
+      <c r="M786">
+        <v>1444</v>
+      </c>
+      <c r="N786">
+        <v>0</v>
       </c>
       <c r="O786">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="P786">
-        <v>112.6</v>
+        <v>8777</v>
       </c>
       <c r="Q786" t="s">
-        <v>78</v>
+        <v>399</v>
       </c>
     </row>
     <row r="787" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A787" t="s">
-        <v>400</v>
+        <v>379</v>
       </c>
       <c r="B787">
-        <v>-35.793973000000001</v>
+        <v>-35.853555700000001</v>
       </c>
       <c r="C787">
-        <v>137.852418</v>
+        <v>137.74248499999999</v>
       </c>
       <c r="D787" s="2">
         <v>46110</v>
       </c>
       <c r="E787" s="20">
-        <v>0.41666666666666669</v>
+        <v>0.39583333333333331</v>
       </c>
       <c r="F787">
+        <v>167</v>
+      </c>
+      <c r="G787">
+        <v>0</v>
+      </c>
+      <c r="H787">
+        <v>4000</v>
+      </c>
+      <c r="I787">
+        <v>444</v>
+      </c>
+      <c r="J787">
+        <v>0</v>
+      </c>
+      <c r="K787">
+        <v>0</v>
+      </c>
+      <c r="L787">
         <v>1222</v>
       </c>
-      <c r="G787">
-        <v>667</v>
-      </c>
-      <c r="H787">
-        <v>1333</v>
-      </c>
-      <c r="I787">
-        <v>1000</v>
-      </c>
-      <c r="J787">
-        <v>0</v>
-      </c>
-      <c r="K787">
-        <v>0</v>
-      </c>
-      <c r="L787">
-        <v>3778</v>
-      </c>
       <c r="M787">
-        <v>222</v>
+        <v>0</v>
       </c>
       <c r="N787">
-        <v>333</v>
+        <v>0</v>
       </c>
       <c r="O787">
         <v>0</v>
       </c>
       <c r="P787">
-        <v>8555</v>
+        <v>5833</v>
       </c>
       <c r="Q787" t="s">
         <v>399</v>
@@ -29968,105 +29998,87 @@
     </row>
     <row r="788" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A788" t="s">
-        <v>210</v>
+        <v>93</v>
       </c>
       <c r="B788">
-        <v>35.739091000000002</v>
+        <v>-35.514747999999997</v>
       </c>
       <c r="C788">
-        <v>137.67788400000001</v>
+        <v>138.71989600000001</v>
       </c>
       <c r="D788" s="2">
-        <v>46110</v>
+        <v>46111</v>
       </c>
       <c r="E788" s="20">
-        <v>0.4375</v>
-      </c>
-      <c r="F788">
-        <v>222</v>
-      </c>
-      <c r="G788">
-        <v>0</v>
-      </c>
-      <c r="H788">
-        <v>1333</v>
+        <v>0.375</v>
       </c>
       <c r="I788">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="J788">
         <v>0</v>
       </c>
-      <c r="K788">
-        <v>0</v>
-      </c>
       <c r="L788">
-        <v>5778</v>
-      </c>
-      <c r="M788">
-        <v>1444</v>
-      </c>
-      <c r="N788">
-        <v>0</v>
+        <v>111.6</v>
       </c>
       <c r="O788">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="P788">
-        <v>8777</v>
+        <v>112.6</v>
       </c>
       <c r="Q788" t="s">
-        <v>399</v>
+        <v>78</v>
       </c>
     </row>
     <row r="789" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A789" t="s">
-        <v>379</v>
+        <v>222</v>
       </c>
       <c r="B789">
-        <v>-35.853555700000001</v>
+        <v>-35.638145999999999</v>
       </c>
       <c r="C789">
-        <v>137.74248499999999</v>
+        <v>137.6249325</v>
       </c>
       <c r="D789" s="2">
-        <v>46110</v>
+        <v>46112</v>
       </c>
       <c r="E789" s="20">
-        <v>0.39583333333333331</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="F789">
-        <v>167</v>
+        <v>0</v>
       </c>
       <c r="G789">
-        <v>0</v>
+        <v>222</v>
       </c>
       <c r="H789">
-        <v>4000</v>
+        <v>1556</v>
       </c>
       <c r="I789">
+        <v>556</v>
+      </c>
+      <c r="J789">
+        <v>0</v>
+      </c>
+      <c r="K789">
+        <v>0</v>
+      </c>
+      <c r="L789">
+        <v>4889</v>
+      </c>
+      <c r="M789">
         <v>444</v>
       </c>
-      <c r="J789">
-        <v>0</v>
-      </c>
-      <c r="K789">
-        <v>0</v>
-      </c>
-      <c r="L789">
-        <v>1222</v>
-      </c>
-      <c r="M789">
-        <v>0</v>
-      </c>
       <c r="N789">
         <v>0</v>
       </c>
       <c r="O789">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="P789">
-        <v>5833</v>
+        <v>7778</v>
       </c>
       <c r="Q789" t="s">
         <v>399</v>
@@ -30074,60 +30086,48 @@
     </row>
     <row r="790" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A790" t="s">
+        <v>59</v>
+      </c>
+      <c r="B790">
+        <v>-35.084850000000003</v>
+      </c>
+      <c r="C790">
+        <v>137.74889999999999</v>
+      </c>
+      <c r="D790" s="2">
+        <v>46113</v>
+      </c>
+      <c r="E790" s="20">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="G790">
+        <v>0</v>
+      </c>
+      <c r="I790">
+        <v>56</v>
+      </c>
+      <c r="J790">
+        <v>0</v>
+      </c>
+      <c r="L790">
         <v>222</v>
       </c>
-      <c r="B790">
-        <v>-35.638145999999999</v>
-      </c>
-      <c r="C790">
-        <v>137.6249325</v>
-      </c>
-      <c r="D790" s="2">
-        <v>46112</v>
-      </c>
-      <c r="E790" s="20">
-        <v>0.47916666666666669</v>
-      </c>
-      <c r="F790">
-        <v>0</v>
-      </c>
-      <c r="G790">
-        <v>222</v>
-      </c>
-      <c r="H790">
-        <v>1556</v>
-      </c>
-      <c r="I790">
-        <v>556</v>
-      </c>
-      <c r="J790">
-        <v>0</v>
-      </c>
-      <c r="K790">
-        <v>0</v>
-      </c>
-      <c r="L790">
-        <v>4889</v>
-      </c>
       <c r="M790">
-        <v>444</v>
+        <v>111</v>
       </c>
       <c r="N790">
-        <v>0</v>
-      </c>
-      <c r="O790">
-        <v>111</v>
+        <v>777</v>
       </c>
       <c r="P790">
-        <v>7778</v>
+        <v>1166</v>
       </c>
       <c r="Q790" t="s">
-        <v>399</v>
+        <v>149</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q759">
-    <sortCondition ref="D2:D759"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q790">
+    <sortCondition ref="D2:D790"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/MASTER spreadsheet of community summaries.xlsx
+++ b/MASTER spreadsheet of community summaries.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\peri\Dropbox\Delta\Projects\Laboratory\Algal blooms, bacterial counts  for community\For Luke's HAB data display\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47C99D04-0DEF-4A2D-B267-CC9AACAB3BF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF738218-01D2-4C9C-BD9C-1F5687BB638E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-24885" yWindow="1845" windowWidth="23250" windowHeight="13890" xr2:uid="{9286397E-2757-492B-865A-39B2D6A15FF6}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{9286397E-2757-492B-865A-39B2D6A15FF6}"/>
   </bookViews>
   <sheets>
     <sheet name="Cells per mL" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1597" uniqueCount="411">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1637" uniqueCount="417">
   <si>
     <t>Date</t>
   </si>
@@ -1289,6 +1289,24 @@
   </si>
   <si>
     <t xml:space="preserve">Wirrina Cove Marina </t>
+  </si>
+  <si>
+    <t>Soldiers Reserve Victor Harbor</t>
+  </si>
+  <si>
+    <t>Port Noarlunga Jetty</t>
+  </si>
+  <si>
+    <t>Kingston SE</t>
+  </si>
+  <si>
+    <t>Port Hughes Jetty</t>
+  </si>
+  <si>
+    <t>Baudin Beach</t>
+  </si>
+  <si>
+    <t>Min oil</t>
   </si>
 </sst>
 </file>
@@ -1758,7 +1776,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F307807-E5C9-4450-88E0-159CBB3E9A67}">
-  <dimension ref="A1:T790"/>
+  <dimension ref="A1:T810"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="39.33203125" customWidth="1"/>
@@ -24116,500 +24134,491 @@
     </row>
     <row r="630" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A630" t="s">
-        <v>315</v>
+        <v>94</v>
       </c>
       <c r="B630">
-        <v>-35.445188000000002</v>
+        <v>-35.58858</v>
       </c>
       <c r="C630">
-        <v>138.307266</v>
+        <v>138.60474600000001</v>
       </c>
       <c r="D630" s="2">
-        <v>46069</v>
+        <v>46068</v>
+      </c>
+      <c r="G630">
+        <v>56</v>
+      </c>
+      <c r="H630">
+        <v>56</v>
+      </c>
+      <c r="I630">
+        <v>56</v>
       </c>
       <c r="J630">
         <v>0</v>
       </c>
       <c r="L630">
-        <v>0</v>
-      </c>
-      <c r="N630" s="16">
-        <v>0</v>
+        <v>56</v>
+      </c>
+      <c r="N630">
+        <v>333</v>
       </c>
       <c r="O630">
-        <v>0</v>
+        <v>556</v>
       </c>
       <c r="P630">
-        <f>SUM(F630:O630)</f>
-        <v>0</v>
+        <v>1113</v>
       </c>
       <c r="Q630" t="s">
-        <v>353</v>
+        <v>129</v>
       </c>
     </row>
     <row r="631" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A631" t="s">
-        <v>361</v>
+        <v>89</v>
       </c>
       <c r="B631">
-        <v>-34.637633999999998</v>
+        <v>-35.6048446</v>
       </c>
       <c r="C631">
-        <v>134.80187000000001</v>
+        <v>138.59278499999999</v>
       </c>
       <c r="D631" s="2">
-        <v>46069</v>
-      </c>
-      <c r="I631">
+        <v>46068</v>
+      </c>
+      <c r="H631">
         <v>56</v>
       </c>
       <c r="J631">
         <v>0</v>
       </c>
+      <c r="L631">
+        <v>444</v>
+      </c>
+      <c r="N631">
+        <v>111</v>
+      </c>
       <c r="O631">
-        <v>56</v>
+        <v>778</v>
       </c>
       <c r="P631">
-        <v>112</v>
+        <v>1389</v>
       </c>
       <c r="Q631" t="s">
-        <v>286</v>
+        <v>129</v>
       </c>
     </row>
     <row r="632" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A632" t="s">
-        <v>362</v>
+        <v>315</v>
       </c>
       <c r="B632">
-        <v>-34.864305100000003</v>
+        <v>-35.445188000000002</v>
       </c>
       <c r="C632">
-        <v>135.77572000000001</v>
+        <v>138.307266</v>
       </c>
       <c r="D632" s="2">
         <v>46069</v>
       </c>
-      <c r="I632">
-        <v>56</v>
-      </c>
       <c r="J632">
         <v>0</v>
       </c>
       <c r="L632">
-        <v>56</v>
+        <v>0</v>
+      </c>
+      <c r="N632" s="16">
+        <v>0</v>
+      </c>
+      <c r="O632">
+        <v>0</v>
       </c>
       <c r="P632">
-        <v>112</v>
+        <f>SUM(F632:O632)</f>
+        <v>0</v>
       </c>
       <c r="Q632" t="s">
-        <v>286</v>
+        <v>353</v>
       </c>
     </row>
     <row r="633" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A633" t="s">
-        <v>59</v>
+        <v>361</v>
       </c>
       <c r="B633">
-        <v>-35.084850000000003</v>
+        <v>-34.637633999999998</v>
       </c>
       <c r="C633">
-        <v>137.74889999999999</v>
+        <v>134.80187000000001</v>
       </c>
       <c r="D633" s="2">
-        <v>46070</v>
-      </c>
-      <c r="E633" s="20">
-        <v>0.54166666666666663</v>
-      </c>
-      <c r="F633" s="15"/>
+        <v>46069</v>
+      </c>
       <c r="I633">
-        <v>83</v>
+        <v>56</v>
       </c>
       <c r="J633">
         <v>0</v>
       </c>
-      <c r="L633">
-        <v>27</v>
-      </c>
-      <c r="N633">
-        <v>417</v>
+      <c r="O633">
+        <v>56</v>
       </c>
       <c r="P633">
-        <v>527</v>
+        <v>112</v>
       </c>
       <c r="Q633" t="s">
-        <v>149</v>
+        <v>286</v>
       </c>
     </row>
     <row r="634" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A634" t="s">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="B634">
-        <v>-35.092981999999999</v>
+        <v>-34.864305100000003</v>
       </c>
       <c r="C634">
-        <v>137.747029</v>
+        <v>135.77572000000001</v>
       </c>
       <c r="D634" s="2">
-        <v>46070</v>
+        <v>46069</v>
       </c>
       <c r="I634">
-        <v>1981</v>
+        <v>56</v>
       </c>
       <c r="J634">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="L634">
-        <v>2889</v>
-      </c>
-      <c r="N634">
-        <v>556</v>
-      </c>
-      <c r="O634">
         <v>56</v>
       </c>
       <c r="P634">
-        <v>5482</v>
+        <v>112</v>
       </c>
       <c r="Q634" t="s">
-        <v>219</v>
+        <v>286</v>
       </c>
     </row>
     <row r="635" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A635" t="s">
-        <v>356</v>
+        <v>59</v>
       </c>
       <c r="B635">
-        <v>-34.672490000000003</v>
+        <v>-35.084850000000003</v>
       </c>
       <c r="C635">
-        <v>137.49295000000001</v>
+        <v>137.74889999999999</v>
       </c>
       <c r="D635" s="2">
         <v>46070</v>
       </c>
       <c r="E635" s="20">
-        <v>0.60416666666666663</v>
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="F635" s="15"/>
+      <c r="I635">
+        <v>83</v>
       </c>
       <c r="J635">
-        <v>833</v>
+        <v>0</v>
+      </c>
+      <c r="L635">
+        <v>27</v>
+      </c>
+      <c r="N635">
+        <v>417</v>
+      </c>
+      <c r="P635">
+        <v>527</v>
       </c>
       <c r="Q635" t="s">
-        <v>267</v>
+        <v>149</v>
       </c>
     </row>
     <row r="636" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A636" t="s">
-        <v>304</v>
+        <v>354</v>
       </c>
       <c r="B636">
-        <v>-34.899749999999997</v>
+        <v>-35.092981999999999</v>
       </c>
       <c r="C636">
-        <v>137.45174</v>
+        <v>137.747029</v>
       </c>
       <c r="D636" s="2">
         <v>46070</v>
       </c>
-      <c r="E636" s="20">
-        <v>0.65277777777777779</v>
+      <c r="I636">
+        <v>1981</v>
       </c>
       <c r="J636">
-        <v>2611</v>
+        <v>37</v>
+      </c>
+      <c r="L636">
+        <v>2889</v>
+      </c>
+      <c r="N636">
+        <v>556</v>
+      </c>
+      <c r="O636">
+        <v>56</v>
+      </c>
+      <c r="P636">
+        <v>5482</v>
       </c>
       <c r="Q636" t="s">
-        <v>267</v>
+        <v>219</v>
       </c>
     </row>
     <row r="637" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A637" t="s">
-        <v>86</v>
+        <v>356</v>
       </c>
       <c r="B637">
-        <v>-35.540277000000003</v>
+        <v>-34.672490000000003</v>
       </c>
       <c r="C637">
-        <v>138.66416599999999</v>
+        <v>137.49295000000001</v>
       </c>
       <c r="D637" s="2">
-        <v>46071</v>
+        <v>46070</v>
       </c>
       <c r="E637" s="20">
-        <v>0.3611111111111111</v>
-      </c>
-      <c r="H637">
-        <v>56</v>
-      </c>
-      <c r="I637">
-        <v>111</v>
+        <v>0.60416666666666663</v>
       </c>
       <c r="J637">
-        <v>56</v>
-      </c>
-      <c r="L637">
-        <v>167</v>
-      </c>
-      <c r="N637">
-        <v>1222</v>
-      </c>
-      <c r="O637">
-        <v>1333</v>
-      </c>
-      <c r="P637">
-        <v>2889</v>
+        <v>833</v>
       </c>
       <c r="Q637" t="s">
-        <v>129</v>
+        <v>267</v>
       </c>
     </row>
     <row r="638" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A638" t="s">
-        <v>100</v>
+        <v>304</v>
       </c>
       <c r="B638">
-        <v>-35.536745000000003</v>
+        <v>-34.899749999999997</v>
       </c>
       <c r="C638">
-        <v>138.6913744</v>
+        <v>137.45174</v>
       </c>
       <c r="D638" s="2">
-        <v>46071</v>
+        <v>46070</v>
       </c>
       <c r="E638" s="20">
-        <v>0.36736111111111114</v>
-      </c>
-      <c r="H638">
-        <v>56</v>
-      </c>
-      <c r="I638">
-        <v>111</v>
+        <v>0.65277777777777779</v>
       </c>
       <c r="J638">
-        <v>0</v>
-      </c>
-      <c r="L638">
-        <v>1778</v>
-      </c>
-      <c r="N638">
-        <v>1667</v>
-      </c>
-      <c r="O638">
-        <v>4555</v>
-      </c>
-      <c r="P638">
-        <v>8167</v>
+        <v>2611</v>
       </c>
       <c r="Q638" t="s">
-        <v>129</v>
+        <v>267</v>
       </c>
     </row>
     <row r="639" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A639" t="s">
-        <v>356</v>
+        <v>86</v>
       </c>
       <c r="B639">
-        <v>-34.672490000000003</v>
+        <v>-35.540277000000003</v>
       </c>
       <c r="C639">
-        <v>137.49295000000001</v>
+        <v>138.66416599999999</v>
       </c>
       <c r="D639" s="2">
         <v>46071</v>
       </c>
       <c r="E639" s="20">
-        <v>0.54166666666666663</v>
-      </c>
-      <c r="F639" s="1"/>
-      <c r="G639" s="1"/>
-      <c r="H639" s="1"/>
-      <c r="I639" s="1"/>
-      <c r="J639" s="1">
-        <v>278</v>
-      </c>
-      <c r="K639" s="1"/>
-      <c r="L639" s="1"/>
-      <c r="M639" s="1"/>
-      <c r="N639" s="1"/>
-      <c r="O639" s="1"/>
-      <c r="P639" s="1"/>
+        <v>0.3611111111111111</v>
+      </c>
+      <c r="H639">
+        <v>56</v>
+      </c>
+      <c r="I639">
+        <v>111</v>
+      </c>
+      <c r="J639">
+        <v>56</v>
+      </c>
+      <c r="L639">
+        <v>167</v>
+      </c>
+      <c r="N639">
+        <v>1222</v>
+      </c>
+      <c r="O639">
+        <v>1333</v>
+      </c>
+      <c r="P639">
+        <v>2889</v>
+      </c>
       <c r="Q639" t="s">
-        <v>267</v>
+        <v>129</v>
       </c>
     </row>
     <row r="640" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A640" t="s">
-        <v>373</v>
+        <v>100</v>
       </c>
       <c r="B640">
-        <v>-34.934266999999998</v>
+        <v>-35.536745000000003</v>
       </c>
       <c r="C640">
-        <v>137.35267999999999</v>
+        <v>138.6913744</v>
       </c>
       <c r="D640" s="2">
         <v>46071</v>
       </c>
       <c r="E640" s="20">
-        <v>0.70833333333333337</v>
+        <v>0.36736111111111114</v>
+      </c>
+      <c r="H640">
+        <v>56</v>
       </c>
       <c r="I640">
-        <v>9000</v>
+        <v>111</v>
       </c>
       <c r="J640">
-        <v>3333</v>
+        <v>0</v>
       </c>
       <c r="L640">
-        <v>1278</v>
+        <v>1778</v>
       </c>
       <c r="N640">
-        <v>389</v>
+        <v>1667</v>
       </c>
       <c r="O640">
-        <v>1056</v>
+        <v>4555</v>
       </c>
       <c r="P640">
-        <v>11723</v>
+        <v>8167</v>
       </c>
       <c r="Q640" t="s">
-        <v>219</v>
+        <v>129</v>
       </c>
     </row>
     <row r="641" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A641" t="s">
-        <v>374</v>
+        <v>356</v>
       </c>
       <c r="B641">
-        <v>-34.910024</v>
+        <v>-34.672490000000003</v>
       </c>
       <c r="C641">
-        <v>137.446956</v>
+        <v>137.49295000000001</v>
       </c>
       <c r="D641" s="2">
         <v>46071</v>
       </c>
       <c r="E641" s="20">
-        <v>0.73958333333333337</v>
-      </c>
-      <c r="I641">
-        <v>17222</v>
-      </c>
-      <c r="J641">
-        <v>13611</v>
-      </c>
-      <c r="L641">
-        <v>4889</v>
-      </c>
-      <c r="O641">
-        <v>833</v>
-      </c>
-      <c r="P641">
-        <v>22944</v>
-      </c>
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="F641" s="1"/>
+      <c r="G641" s="1"/>
+      <c r="H641" s="1"/>
+      <c r="I641" s="1"/>
+      <c r="J641" s="1">
+        <v>278</v>
+      </c>
+      <c r="K641" s="1"/>
+      <c r="L641" s="1"/>
+      <c r="M641" s="1"/>
+      <c r="N641" s="1"/>
+      <c r="O641" s="1"/>
+      <c r="P641" s="1"/>
       <c r="Q641" t="s">
-        <v>219</v>
+        <v>267</v>
       </c>
     </row>
     <row r="642" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A642" t="s">
-        <v>87</v>
+        <v>373</v>
       </c>
       <c r="B642">
-        <v>-35.573300000000003</v>
+        <v>-34.934266999999998</v>
       </c>
       <c r="C642">
-        <v>138.64250000000001</v>
+        <v>137.35267999999999</v>
       </c>
       <c r="D642" s="2">
         <v>46071</v>
       </c>
       <c r="E642" s="20">
-        <v>0.38194444444444442</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="I642">
-        <v>56</v>
+        <v>9000</v>
       </c>
       <c r="J642">
-        <v>0</v>
+        <v>3333</v>
       </c>
       <c r="L642">
-        <v>778</v>
+        <v>1278</v>
       </c>
       <c r="N642">
-        <v>1222</v>
+        <v>389</v>
       </c>
       <c r="O642">
-        <v>1167</v>
+        <v>1056</v>
       </c>
       <c r="P642">
-        <v>3223</v>
+        <v>11723</v>
       </c>
       <c r="Q642" t="s">
-        <v>129</v>
+        <v>219</v>
       </c>
     </row>
     <row r="643" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A643" t="s">
-        <v>88</v>
+        <v>374</v>
       </c>
       <c r="B643">
-        <v>-35.581124000000003</v>
+        <v>-34.910024</v>
       </c>
       <c r="C643">
-        <v>138.60879700000001</v>
+        <v>137.446956</v>
       </c>
       <c r="D643" s="2">
         <v>46071</v>
       </c>
       <c r="E643" s="20">
-        <v>0.39027777777777778</v>
-      </c>
-      <c r="H643">
-        <v>111</v>
+        <v>0.73958333333333337</v>
       </c>
       <c r="I643">
-        <v>56</v>
+        <v>17222</v>
       </c>
       <c r="J643">
-        <v>0</v>
+        <v>13611</v>
       </c>
       <c r="L643">
-        <v>56</v>
-      </c>
-      <c r="N643">
-        <v>444</v>
+        <v>4889</v>
       </c>
       <c r="O643">
-        <v>556</v>
+        <v>833</v>
       </c>
       <c r="P643">
-        <v>1223</v>
+        <v>22944</v>
       </c>
       <c r="Q643" t="s">
-        <v>129</v>
+        <v>219</v>
       </c>
     </row>
     <row r="644" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A644" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B644">
-        <v>-35.6048446</v>
+        <v>-35.573300000000003</v>
       </c>
       <c r="C644">
-        <v>138.59278499999999</v>
+        <v>138.64250000000001</v>
       </c>
       <c r="D644" s="2">
         <v>46071</v>
       </c>
       <c r="E644" s="20">
-        <v>0.40625</v>
-      </c>
-      <c r="G644">
-        <v>56</v>
-      </c>
-      <c r="H644">
-        <v>56</v>
+        <v>0.38194444444444442</v>
       </c>
       <c r="I644">
         <v>56</v>
@@ -24618,16 +24627,16 @@
         <v>0</v>
       </c>
       <c r="L644">
-        <v>889</v>
+        <v>778</v>
       </c>
       <c r="N644">
-        <v>1000</v>
+        <v>1222</v>
       </c>
       <c r="O644">
-        <v>556</v>
+        <v>1167</v>
       </c>
       <c r="P644">
-        <v>2613</v>
+        <v>3223</v>
       </c>
       <c r="Q644" t="s">
         <v>129</v>
@@ -24635,40 +24644,40 @@
     </row>
     <row r="645" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A645" t="s">
-        <v>378</v>
+        <v>88</v>
       </c>
       <c r="B645">
-        <v>-35.612285999999997</v>
+        <v>-35.581124000000003</v>
       </c>
       <c r="C645">
-        <v>138.564302</v>
+        <v>138.60879700000001</v>
       </c>
       <c r="D645" s="2">
         <v>46071</v>
       </c>
       <c r="E645" s="20">
-        <v>0.4152777777777778</v>
-      </c>
-      <c r="G645">
+        <v>0.39027777777777778</v>
+      </c>
+      <c r="H645">
+        <v>111</v>
+      </c>
+      <c r="I645">
         <v>56</v>
       </c>
-      <c r="H645">
+      <c r="J645">
+        <v>0</v>
+      </c>
+      <c r="L645">
         <v>56</v>
-      </c>
-      <c r="J645">
-        <v>0</v>
-      </c>
-      <c r="L645">
-        <v>889</v>
       </c>
       <c r="N645">
         <v>444</v>
       </c>
       <c r="O645">
-        <v>1167</v>
+        <v>556</v>
       </c>
       <c r="P645">
-        <v>2612</v>
+        <v>1223</v>
       </c>
       <c r="Q645" t="s">
         <v>129</v>
@@ -24676,240 +24685,217 @@
     </row>
     <row r="646" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A646" t="s">
-        <v>382</v>
+        <v>89</v>
       </c>
       <c r="B646">
-        <v>-34.933680000000003</v>
+        <v>-35.6048446</v>
       </c>
       <c r="C646">
-        <v>137.35257300000001</v>
+        <v>138.59278499999999</v>
       </c>
       <c r="D646" s="2">
         <v>46071</v>
       </c>
       <c r="E646" s="20">
-        <v>0.71527777777777779</v>
+        <v>0.40625</v>
+      </c>
+      <c r="G646">
+        <v>56</v>
+      </c>
+      <c r="H646">
+        <v>56</v>
       </c>
       <c r="I646">
-        <v>2722</v>
+        <v>56</v>
       </c>
       <c r="J646">
-        <v>722</v>
+        <v>0</v>
       </c>
       <c r="L646">
-        <v>4500</v>
+        <v>889</v>
+      </c>
+      <c r="N646">
+        <v>1000</v>
       </c>
       <c r="O646">
-        <v>778</v>
+        <v>556</v>
       </c>
       <c r="P646">
-        <v>8000</v>
+        <v>2613</v>
       </c>
       <c r="Q646" t="s">
-        <v>219</v>
+        <v>129</v>
       </c>
     </row>
     <row r="647" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A647" t="s">
-        <v>304</v>
+        <v>378</v>
       </c>
       <c r="B647">
-        <v>-34.899749999999997</v>
+        <v>-35.612285999999997</v>
       </c>
       <c r="C647">
-        <v>137.45174</v>
+        <v>138.564302</v>
       </c>
       <c r="D647" s="2">
-        <v>46072</v>
+        <v>46071</v>
       </c>
       <c r="E647" s="20">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F647" s="1"/>
-      <c r="G647" s="1"/>
-      <c r="H647" s="1"/>
-      <c r="I647" s="1"/>
-      <c r="J647" s="1">
-        <v>833</v>
-      </c>
-      <c r="K647" s="1"/>
-      <c r="L647" s="1"/>
-      <c r="M647" s="1"/>
-      <c r="N647" s="1"/>
-      <c r="O647" s="1"/>
-      <c r="P647" s="1"/>
+        <v>0.4152777777777778</v>
+      </c>
+      <c r="G647">
+        <v>56</v>
+      </c>
+      <c r="H647">
+        <v>56</v>
+      </c>
+      <c r="J647">
+        <v>0</v>
+      </c>
+      <c r="L647">
+        <v>889</v>
+      </c>
+      <c r="N647">
+        <v>444</v>
+      </c>
+      <c r="O647">
+        <v>1167</v>
+      </c>
+      <c r="P647">
+        <v>2612</v>
+      </c>
       <c r="Q647" t="s">
-        <v>267</v>
+        <v>129</v>
       </c>
     </row>
     <row r="648" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A648" t="s">
-        <v>321</v>
+        <v>382</v>
       </c>
       <c r="B648">
-        <v>-34.911830000000002</v>
+        <v>-34.933680000000003</v>
       </c>
       <c r="C648">
-        <v>137.16248999999999</v>
+        <v>137.35257300000001</v>
       </c>
       <c r="D648" s="2">
-        <v>46072</v>
+        <v>46071</v>
       </c>
       <c r="E648" s="20">
-        <v>0.72916666666666663</v>
-      </c>
-      <c r="F648" s="1"/>
-      <c r="G648" s="1"/>
-      <c r="H648" s="1"/>
-      <c r="I648" s="1"/>
-      <c r="J648" s="1">
-        <v>0</v>
-      </c>
-      <c r="K648" s="1"/>
-      <c r="L648" s="1"/>
-      <c r="M648" s="1"/>
-      <c r="N648" s="1"/>
-      <c r="O648" s="1"/>
-      <c r="P648" s="1"/>
+        <v>0.71527777777777779</v>
+      </c>
+      <c r="I648">
+        <v>2722</v>
+      </c>
+      <c r="J648">
+        <v>722</v>
+      </c>
+      <c r="L648">
+        <v>4500</v>
+      </c>
+      <c r="O648">
+        <v>778</v>
+      </c>
+      <c r="P648">
+        <v>8000</v>
+      </c>
       <c r="Q648" t="s">
-        <v>267</v>
+        <v>219</v>
       </c>
     </row>
     <row r="649" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A649" t="s">
-        <v>269</v>
+        <v>304</v>
       </c>
       <c r="B649">
-        <v>-34.824044999999998</v>
+        <v>-34.899749999999997</v>
       </c>
       <c r="C649">
-        <v>138.48377600000001</v>
+        <v>137.45174</v>
       </c>
       <c r="D649" s="2">
         <v>46072</v>
       </c>
       <c r="E649" s="20">
-        <v>0.4375</v>
-      </c>
-      <c r="F649">
-        <v>0</v>
-      </c>
-      <c r="G649">
-        <v>0.375</v>
-      </c>
-      <c r="H649">
-        <v>0</v>
-      </c>
-      <c r="I649">
-        <v>0.15</v>
-      </c>
-      <c r="J649">
-        <v>0</v>
-      </c>
-      <c r="K649">
-        <v>0</v>
-      </c>
-      <c r="L649">
-        <v>1.5</v>
-      </c>
-      <c r="M649">
-        <v>0</v>
-      </c>
-      <c r="N649">
-        <v>0.15</v>
-      </c>
-      <c r="O649">
-        <v>2.5000000000000001E-2</v>
-      </c>
-      <c r="P649">
-        <f>SUM(F649:I649,K649:O649)</f>
-        <v>2.1999999999999997</v>
-      </c>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F649" s="1"/>
+      <c r="G649" s="1"/>
+      <c r="H649" s="1"/>
+      <c r="I649" s="1"/>
+      <c r="J649" s="1">
+        <v>833</v>
+      </c>
+      <c r="K649" s="1"/>
+      <c r="L649" s="1"/>
+      <c r="M649" s="1"/>
+      <c r="N649" s="1"/>
+      <c r="O649" s="1"/>
+      <c r="P649" s="1"/>
       <c r="Q649" t="s">
-        <v>78</v>
+        <v>267</v>
       </c>
     </row>
     <row r="650" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A650" t="s">
-        <v>352</v>
+        <v>321</v>
       </c>
       <c r="B650">
-        <v>-34.860666999999999</v>
+        <v>-34.911830000000002</v>
       </c>
       <c r="C650">
-        <v>138.490938</v>
+        <v>137.16248999999999</v>
       </c>
       <c r="D650" s="2">
         <v>46072</v>
       </c>
       <c r="E650" s="20">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="F650">
-        <v>0</v>
-      </c>
-      <c r="G650">
-        <v>0</v>
-      </c>
-      <c r="H650">
-        <v>0</v>
-      </c>
-      <c r="I650">
-        <v>0.05</v>
-      </c>
-      <c r="J650">
-        <v>0</v>
-      </c>
-      <c r="K650">
-        <v>0</v>
-      </c>
-      <c r="L650">
-        <v>24.2</v>
-      </c>
-      <c r="M650">
-        <v>0</v>
-      </c>
-      <c r="N650">
-        <v>0.2</v>
-      </c>
-      <c r="O650">
-        <v>0.15</v>
-      </c>
-      <c r="P650">
-        <f>SUM(F650:I650,K650:O650)</f>
-        <v>24.599999999999998</v>
-      </c>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="F650" s="1"/>
+      <c r="G650" s="1"/>
+      <c r="H650" s="1"/>
+      <c r="I650" s="1"/>
+      <c r="J650" s="1">
+        <v>0</v>
+      </c>
+      <c r="K650" s="1"/>
+      <c r="L650" s="1"/>
+      <c r="M650" s="1"/>
+      <c r="N650" s="1"/>
+      <c r="O650" s="1"/>
+      <c r="P650" s="1"/>
       <c r="Q650" t="s">
-        <v>78</v>
+        <v>267</v>
       </c>
     </row>
     <row r="651" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A651" t="s">
-        <v>79</v>
+        <v>269</v>
       </c>
       <c r="B651">
-        <v>-34.804662999999998</v>
+        <v>-34.824044999999998</v>
       </c>
       <c r="C651">
-        <v>138.540223</v>
+        <v>138.48377600000001</v>
       </c>
       <c r="D651" s="2">
         <v>46072</v>
       </c>
       <c r="E651" s="20">
-        <v>0.35416666666666669</v>
+        <v>0.4375</v>
       </c>
       <c r="F651">
         <v>0</v>
       </c>
       <c r="G651">
-        <v>0</v>
+        <v>0.375</v>
       </c>
       <c r="H651">
         <v>0</v>
       </c>
       <c r="I651">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="J651">
         <v>0</v>
@@ -24918,20 +24904,20 @@
         <v>0</v>
       </c>
       <c r="L651">
-        <v>17.100000000000001</v>
+        <v>1.5</v>
       </c>
       <c r="M651">
         <v>0</v>
       </c>
       <c r="N651">
-        <v>0.22500000000000001</v>
+        <v>0.15</v>
       </c>
       <c r="O651">
-        <v>0.52500000000000002</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="P651">
         <f>SUM(F651:I651,K651:O651)</f>
-        <v>17.850000000000001</v>
+        <v>2.1999999999999997</v>
       </c>
       <c r="Q651" t="s">
         <v>78</v>
@@ -24939,19 +24925,19 @@
     </row>
     <row r="652" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A652" t="s">
-        <v>363</v>
+        <v>352</v>
       </c>
       <c r="B652">
-        <v>-35.878667100000001</v>
+        <v>-34.860666999999999</v>
       </c>
       <c r="C652">
-        <v>137.6963188</v>
+        <v>138.490938</v>
       </c>
       <c r="D652" s="2">
-        <v>46073</v>
+        <v>46072</v>
       </c>
       <c r="E652" s="20">
-        <v>0.3</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="F652">
         <v>0</v>
@@ -24960,346 +24946,388 @@
         <v>0</v>
       </c>
       <c r="H652">
-        <v>866</v>
+        <v>0</v>
       </c>
       <c r="I652">
-        <v>2333</v>
+        <v>0.05</v>
       </c>
       <c r="J652">
-        <v>2222</v>
+        <v>0</v>
       </c>
       <c r="K652">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="L652">
-        <v>3111</v>
+        <v>24.2</v>
       </c>
       <c r="M652">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="N652">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="O652">
-        <v>222</v>
+        <v>0.15</v>
       </c>
       <c r="P652">
-        <v>6754</v>
+        <f>SUM(F652:I652,K652:O652)</f>
+        <v>24.599999999999998</v>
       </c>
       <c r="Q652" t="s">
-        <v>151</v>
+        <v>78</v>
       </c>
     </row>
     <row r="653" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A653" t="s">
-        <v>355</v>
+        <v>79</v>
       </c>
       <c r="B653">
-        <v>-34.586370000000002</v>
+        <v>-34.804662999999998</v>
       </c>
       <c r="C653">
-        <v>137.50527</v>
+        <v>138.540223</v>
       </c>
       <c r="D653" s="2">
-        <v>46073</v>
+        <v>46072</v>
       </c>
       <c r="E653" s="20">
-        <v>0.5</v>
-      </c>
-      <c r="F653" s="1"/>
-      <c r="G653" s="1"/>
-      <c r="H653" s="1"/>
-      <c r="I653" s="1"/>
-      <c r="J653" s="1">
-        <v>778</v>
-      </c>
-      <c r="K653" s="1"/>
-      <c r="L653" s="1"/>
-      <c r="M653" s="1"/>
-      <c r="N653" s="1"/>
-      <c r="O653" s="1"/>
-      <c r="P653" s="1"/>
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="F653">
+        <v>0</v>
+      </c>
+      <c r="G653">
+        <v>0</v>
+      </c>
+      <c r="H653">
+        <v>0</v>
+      </c>
+      <c r="I653">
+        <v>0</v>
+      </c>
+      <c r="J653">
+        <v>0</v>
+      </c>
+      <c r="K653">
+        <v>0</v>
+      </c>
+      <c r="L653">
+        <v>17.100000000000001</v>
+      </c>
+      <c r="M653">
+        <v>0</v>
+      </c>
+      <c r="N653">
+        <v>0.22500000000000001</v>
+      </c>
+      <c r="O653">
+        <v>0.52500000000000002</v>
+      </c>
+      <c r="P653">
+        <f>SUM(F653:I653,K653:O653)</f>
+        <v>17.850000000000001</v>
+      </c>
       <c r="Q653" t="s">
-        <v>267</v>
+        <v>78</v>
       </c>
     </row>
     <row r="654" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A654" t="s">
-        <v>213</v>
+        <v>363</v>
       </c>
       <c r="B654">
-        <v>-34.751460000000002</v>
+        <v>-35.878667100000001</v>
       </c>
       <c r="C654">
-        <v>137.47702000000001</v>
+        <v>137.6963188</v>
       </c>
       <c r="D654" s="2">
         <v>46073</v>
       </c>
       <c r="E654" s="20">
-        <v>0.57986111111111116</v>
-      </c>
-      <c r="F654" s="1"/>
-      <c r="G654" s="1"/>
-      <c r="H654" s="1"/>
-      <c r="I654" s="1"/>
-      <c r="J654" s="1">
-        <v>944</v>
-      </c>
-      <c r="K654" s="1"/>
-      <c r="L654" s="1"/>
-      <c r="M654" s="1"/>
-      <c r="N654" s="1"/>
-      <c r="O654" s="1"/>
-      <c r="P654" s="1"/>
+        <v>0.3</v>
+      </c>
+      <c r="F654">
+        <v>0</v>
+      </c>
+      <c r="G654">
+        <v>0</v>
+      </c>
+      <c r="H654">
+        <v>866</v>
+      </c>
+      <c r="I654">
+        <v>2333</v>
+      </c>
+      <c r="J654">
+        <v>2222</v>
+      </c>
+      <c r="K654">
+        <v>111</v>
+      </c>
+      <c r="L654">
+        <v>3111</v>
+      </c>
+      <c r="M654">
+        <v>111</v>
+      </c>
+      <c r="N654">
+        <v>0</v>
+      </c>
+      <c r="O654">
+        <v>222</v>
+      </c>
+      <c r="P654">
+        <v>6754</v>
+      </c>
       <c r="Q654" t="s">
-        <v>267</v>
+        <v>151</v>
       </c>
     </row>
     <row r="655" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A655" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="B655">
-        <v>-35.853555700000001</v>
+        <v>-34.586370000000002</v>
       </c>
       <c r="C655">
-        <v>137.74248499999999</v>
+        <v>137.50527</v>
       </c>
       <c r="D655" s="2">
-        <v>46074</v>
+        <v>46073</v>
       </c>
       <c r="E655" s="20">
-        <v>0.58333333333333337</v>
-      </c>
-      <c r="F655">
-        <v>0</v>
-      </c>
-      <c r="G655">
-        <v>0</v>
-      </c>
-      <c r="H655">
-        <v>0</v>
-      </c>
-      <c r="I655">
-        <v>5000</v>
-      </c>
-      <c r="J655">
-        <v>5000</v>
-      </c>
-      <c r="K655">
-        <v>0</v>
-      </c>
-      <c r="L655">
-        <v>1333</v>
-      </c>
-      <c r="M655">
-        <v>0</v>
-      </c>
-      <c r="N655">
-        <v>0</v>
-      </c>
-      <c r="O655">
-        <v>0</v>
-      </c>
-      <c r="P655">
-        <v>6333</v>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="F655" s="1"/>
+      <c r="G655" s="1"/>
+      <c r="H655" s="1"/>
+      <c r="I655" s="1"/>
+      <c r="J655" s="1">
+        <v>778</v>
+      </c>
+      <c r="K655" s="1"/>
+      <c r="L655" s="1"/>
+      <c r="M655" s="1"/>
+      <c r="N655" s="1"/>
+      <c r="O655" s="1"/>
+      <c r="P655" s="1"/>
       <c r="Q655" t="s">
-        <v>151</v>
+        <v>267</v>
       </c>
     </row>
     <row r="656" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A656" t="s">
-        <v>365</v>
+        <v>213</v>
       </c>
       <c r="B656">
-        <v>-35.787276900000002</v>
+        <v>-34.751460000000002</v>
       </c>
       <c r="C656">
-        <v>138.06910160000001</v>
+        <v>137.47702000000001</v>
       </c>
       <c r="D656" s="2">
+        <v>46073</v>
+      </c>
+      <c r="E656" s="20">
+        <v>0.57986111111111116</v>
+      </c>
+      <c r="F656" s="1"/>
+      <c r="G656" s="1"/>
+      <c r="H656" s="1"/>
+      <c r="I656" s="1"/>
+      <c r="J656" s="1">
+        <v>944</v>
+      </c>
+      <c r="K656" s="1"/>
+      <c r="L656" s="1"/>
+      <c r="M656" s="1"/>
+      <c r="N656" s="1"/>
+      <c r="O656" s="1"/>
+      <c r="P656" s="1"/>
+      <c r="Q656" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="657" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A657" t="s">
+        <v>364</v>
+      </c>
+      <c r="B657">
+        <v>-35.853555700000001</v>
+      </c>
+      <c r="C657">
+        <v>137.74248499999999</v>
+      </c>
+      <c r="D657" s="2">
         <v>46074</v>
       </c>
-      <c r="E656" s="20">
-        <v>0.15</v>
-      </c>
-      <c r="F656">
-        <v>1111</v>
-      </c>
-      <c r="G656">
-        <v>0</v>
-      </c>
-      <c r="H656">
-        <v>444</v>
-      </c>
-      <c r="I656">
-        <v>2333</v>
-      </c>
-      <c r="J656">
-        <v>0</v>
-      </c>
-      <c r="K656">
-        <v>444</v>
-      </c>
-      <c r="L656">
-        <v>15000</v>
-      </c>
-      <c r="M656">
-        <v>1111</v>
-      </c>
-      <c r="N656">
-        <v>0</v>
-      </c>
-      <c r="O656">
-        <v>222</v>
-      </c>
-      <c r="P656">
-        <v>20665</v>
-      </c>
-      <c r="Q656" t="s">
+      <c r="E657" s="20">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="F657">
+        <v>0</v>
+      </c>
+      <c r="G657">
+        <v>0</v>
+      </c>
+      <c r="H657">
+        <v>0</v>
+      </c>
+      <c r="I657">
+        <v>5000</v>
+      </c>
+      <c r="J657">
+        <v>5000</v>
+      </c>
+      <c r="K657">
+        <v>0</v>
+      </c>
+      <c r="L657">
+        <v>1333</v>
+      </c>
+      <c r="M657">
+        <v>0</v>
+      </c>
+      <c r="N657">
+        <v>0</v>
+      </c>
+      <c r="O657">
+        <v>0</v>
+      </c>
+      <c r="P657">
+        <v>6333</v>
+      </c>
+      <c r="Q657" t="s">
         <v>151</v>
-      </c>
-    </row>
-    <row r="657" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A657" s="17" t="s">
-        <v>367</v>
-      </c>
-      <c r="B657">
-        <v>-34.776083</v>
-      </c>
-      <c r="C657">
-        <v>137.86041700000001</v>
-      </c>
-      <c r="D657" s="18">
-        <v>46074</v>
-      </c>
-      <c r="E657" s="20">
-        <v>0.72916666666666663</v>
-      </c>
-      <c r="F657" s="17"/>
-      <c r="G657" s="17"/>
-      <c r="H657" s="17"/>
-      <c r="I657" s="17">
-        <v>444</v>
-      </c>
-      <c r="J657" s="17">
-        <v>56</v>
-      </c>
-      <c r="K657" s="17">
-        <v>444</v>
-      </c>
-      <c r="L657" s="17"/>
-      <c r="M657" s="17"/>
-      <c r="N657" s="17">
-        <v>167</v>
-      </c>
-      <c r="O657" s="17">
-        <v>56</v>
-      </c>
-      <c r="P657" s="17">
-        <f>SUM(F657:I657,K657:O657)</f>
-        <v>1111</v>
-      </c>
-      <c r="Q657" t="s">
-        <v>368</v>
       </c>
     </row>
     <row r="658" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A658" t="s">
-        <v>212</v>
+        <v>365</v>
       </c>
       <c r="B658">
-        <v>-35.515507999999997</v>
+        <v>-35.787276900000002</v>
       </c>
       <c r="C658">
-        <v>138.729004</v>
+        <v>138.06910160000001</v>
       </c>
       <c r="D658" s="2">
         <v>46074</v>
       </c>
       <c r="E658" s="20">
-        <v>0.47916666666666669</v>
+        <v>0.15</v>
+      </c>
+      <c r="F658">
+        <v>1111</v>
+      </c>
+      <c r="G658">
+        <v>0</v>
+      </c>
+      <c r="H658">
+        <v>444</v>
       </c>
       <c r="I658">
-        <v>333</v>
+        <v>2333</v>
       </c>
       <c r="J658">
         <v>0</v>
       </c>
+      <c r="K658">
+        <v>444</v>
+      </c>
       <c r="L658">
-        <v>111</v>
+        <v>15000</v>
+      </c>
+      <c r="M658">
+        <v>1111</v>
+      </c>
+      <c r="N658">
+        <v>0</v>
+      </c>
+      <c r="O658">
+        <v>222</v>
       </c>
       <c r="P658">
-        <f>SUM(F658:I658,K658:O658)</f>
+        <v>20665</v>
+      </c>
+      <c r="Q658" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="659" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A659" s="17" t="s">
+        <v>367</v>
+      </c>
+      <c r="B659">
+        <v>-34.776083</v>
+      </c>
+      <c r="C659">
+        <v>137.86041700000001</v>
+      </c>
+      <c r="D659" s="18">
+        <v>46074</v>
+      </c>
+      <c r="E659" s="20">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="F659" s="17"/>
+      <c r="G659" s="17"/>
+      <c r="H659" s="17"/>
+      <c r="I659" s="17">
         <v>444</v>
       </c>
-      <c r="Q658" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="659" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A659" t="s">
-        <v>91</v>
-      </c>
-      <c r="B659">
-        <v>-35.536168000000004</v>
-      </c>
-      <c r="C659">
-        <v>138.677615</v>
-      </c>
-      <c r="D659" s="2">
-        <v>46074</v>
-      </c>
-      <c r="E659" s="20">
-        <v>0.48958333333333331</v>
-      </c>
-      <c r="I659">
+      <c r="J659" s="17">
         <v>56</v>
       </c>
-      <c r="J659">
-        <v>0</v>
-      </c>
-      <c r="L659">
-        <v>0</v>
-      </c>
-      <c r="P659">
-        <f>SUM(F659:I659,K659:O659)</f>
+      <c r="K659" s="17">
+        <v>444</v>
+      </c>
+      <c r="L659" s="17"/>
+      <c r="M659" s="17"/>
+      <c r="N659" s="17">
+        <v>167</v>
+      </c>
+      <c r="O659" s="17">
         <v>56</v>
       </c>
+      <c r="P659" s="17">
+        <f t="shared" ref="P659:P665" si="0">SUM(F659:I659,K659:O659)</f>
+        <v>1111</v>
+      </c>
       <c r="Q659" t="s">
-        <v>187</v>
+        <v>368</v>
       </c>
     </row>
     <row r="660" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A660" t="s">
-        <v>186</v>
+        <v>212</v>
       </c>
       <c r="B660">
-        <v>-35.538469999999997</v>
+        <v>-35.515507999999997</v>
       </c>
       <c r="C660">
-        <v>138.649779</v>
+        <v>138.729004</v>
       </c>
       <c r="D660" s="2">
         <v>46074</v>
       </c>
       <c r="E660" s="20">
-        <v>0.49652777777777779</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="I660">
-        <v>0</v>
+        <v>333</v>
       </c>
       <c r="J660">
         <v>0</v>
       </c>
       <c r="L660">
-        <v>167</v>
+        <v>111</v>
       </c>
       <c r="P660">
-        <f>SUM(F660:I660,K660:O660)</f>
-        <v>167</v>
+        <f t="shared" si="0"/>
+        <v>444</v>
       </c>
       <c r="Q660" t="s">
         <v>187</v>
@@ -25307,19 +25335,19 @@
     </row>
     <row r="661" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A661" t="s">
-        <v>318</v>
+        <v>91</v>
       </c>
       <c r="B661">
-        <v>-35.5565</v>
+        <v>-35.536168000000004</v>
       </c>
       <c r="C661">
-        <v>138.62610000000001</v>
+        <v>138.677615</v>
       </c>
       <c r="D661" s="2">
         <v>46074</v>
       </c>
       <c r="E661" s="20">
-        <v>0.50694444444444442</v>
+        <v>0.48958333333333331</v>
       </c>
       <c r="I661">
         <v>56</v>
@@ -25328,11 +25356,11 @@
         <v>0</v>
       </c>
       <c r="L661">
+        <v>0</v>
+      </c>
+      <c r="P661">
+        <f t="shared" si="0"/>
         <v>56</v>
-      </c>
-      <c r="P661">
-        <f>SUM(F661:I661,K661:O661)</f>
-        <v>112</v>
       </c>
       <c r="Q661" t="s">
         <v>187</v>
@@ -25340,19 +25368,19 @@
     </row>
     <row r="662" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A662" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="B662">
-        <v>-35.592393000000001</v>
+        <v>-35.538469999999997</v>
       </c>
       <c r="C662">
-        <v>138.599706</v>
+        <v>138.649779</v>
       </c>
       <c r="D662" s="2">
         <v>46074</v>
       </c>
       <c r="E662" s="20">
-        <v>0.52083333333333337</v>
+        <v>0.49652777777777779</v>
       </c>
       <c r="I662">
         <v>0</v>
@@ -25361,11 +25389,11 @@
         <v>0</v>
       </c>
       <c r="L662">
-        <v>0</v>
+        <v>167</v>
       </c>
       <c r="P662">
-        <f>SUM(F662:I662,K662:O662)</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>167</v>
       </c>
       <c r="Q662" t="s">
         <v>187</v>
@@ -25373,19 +25401,19 @@
     </row>
     <row r="663" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A663" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B663">
-        <v>-35.634602000000001</v>
+        <v>-35.5565</v>
       </c>
       <c r="C663">
-        <v>138.49898300000001</v>
+        <v>138.62610000000001</v>
       </c>
       <c r="D663" s="2">
         <v>46074</v>
       </c>
       <c r="E663" s="20">
-        <v>0.55208333333333337</v>
+        <v>0.50694444444444442</v>
       </c>
       <c r="I663">
         <v>56</v>
@@ -25394,11 +25422,11 @@
         <v>0</v>
       </c>
       <c r="L663">
-        <v>222</v>
+        <v>56</v>
       </c>
       <c r="P663">
-        <f>SUM(F663:I663,K663:O663)</f>
-        <v>278</v>
+        <f t="shared" si="0"/>
+        <v>112</v>
       </c>
       <c r="Q663" t="s">
         <v>187</v>
@@ -25406,17 +25434,20 @@
     </row>
     <row r="664" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A664" t="s">
-        <v>371</v>
+        <v>189</v>
       </c>
       <c r="B664">
-        <v>-34.918303199999997</v>
+        <v>-35.592393000000001</v>
       </c>
       <c r="C664">
-        <v>135.68486999999999</v>
+        <v>138.599706</v>
       </c>
       <c r="D664" s="2">
         <v>46074</v>
       </c>
+      <c r="E664" s="20">
+        <v>0.52083333333333337</v>
+      </c>
       <c r="I664">
         <v>0</v>
       </c>
@@ -25424,145 +25455,140 @@
         <v>0</v>
       </c>
       <c r="L664">
-        <v>167</v>
-      </c>
-      <c r="O664">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="P664">
-        <v>223</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="Q664" t="s">
-        <v>286</v>
+        <v>187</v>
       </c>
     </row>
     <row r="665" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A665" t="s">
-        <v>372</v>
+        <v>320</v>
       </c>
       <c r="B665">
-        <v>-34.911405199999997</v>
+        <v>-35.634602000000001</v>
       </c>
       <c r="C665">
-        <v>135.68218999999999</v>
+        <v>138.49898300000001</v>
       </c>
       <c r="D665" s="2">
         <v>46074</v>
       </c>
+      <c r="E665" s="20">
+        <v>0.55208333333333337</v>
+      </c>
       <c r="I665">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="J665">
         <v>0</v>
       </c>
       <c r="L665">
-        <v>250</v>
-      </c>
-      <c r="N665">
-        <v>56</v>
-      </c>
-      <c r="O665">
-        <v>56</v>
+        <v>222</v>
       </c>
       <c r="P665">
-        <v>390</v>
+        <f t="shared" si="0"/>
+        <v>278</v>
       </c>
       <c r="Q665" t="s">
-        <v>286</v>
+        <v>187</v>
       </c>
     </row>
     <row r="666" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A666" t="s">
-        <v>304</v>
+        <v>371</v>
       </c>
       <c r="B666">
-        <v>-34.899749999999997</v>
+        <v>-34.918303199999997</v>
       </c>
       <c r="C666">
-        <v>137.45174</v>
+        <v>135.68486999999999</v>
       </c>
       <c r="D666" s="2">
-        <v>46075</v>
-      </c>
-      <c r="E666" s="20">
-        <v>0.60416666666666663</v>
-      </c>
-      <c r="F666" s="1"/>
-      <c r="G666" s="1"/>
-      <c r="H666" s="1"/>
-      <c r="I666" s="1">
-        <v>3333</v>
-      </c>
-      <c r="J666" s="1">
-        <v>1111</v>
-      </c>
-      <c r="K666" s="1"/>
-      <c r="L666" s="1"/>
-      <c r="M666" s="1"/>
-      <c r="N666" s="1"/>
-      <c r="O666" s="1"/>
-      <c r="P666" s="1"/>
+        <v>46074</v>
+      </c>
+      <c r="I666">
+        <v>0</v>
+      </c>
+      <c r="J666">
+        <v>0</v>
+      </c>
+      <c r="L666">
+        <v>167</v>
+      </c>
+      <c r="O666">
+        <v>56</v>
+      </c>
+      <c r="P666">
+        <v>223</v>
+      </c>
       <c r="Q666" t="s">
-        <v>267</v>
+        <v>286</v>
       </c>
     </row>
     <row r="667" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A667" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="B667">
-        <v>-34.82743</v>
+        <v>-34.911405199999997</v>
       </c>
       <c r="C667">
-        <v>137.45844</v>
+        <v>135.68218999999999</v>
       </c>
       <c r="D667" s="2">
-        <v>46075</v>
-      </c>
-      <c r="E667" s="20">
-        <v>0.59375</v>
-      </c>
-      <c r="F667" s="1"/>
-      <c r="G667" s="1"/>
-      <c r="H667" s="1"/>
-      <c r="I667" s="1">
-        <v>3111</v>
-      </c>
-      <c r="J667" s="1">
-        <v>389</v>
-      </c>
-      <c r="K667" s="1"/>
-      <c r="L667" s="1"/>
-      <c r="M667" s="1"/>
-      <c r="N667" s="1"/>
-      <c r="O667" s="1"/>
-      <c r="P667" s="1"/>
+        <v>46074</v>
+      </c>
+      <c r="I667">
+        <v>28</v>
+      </c>
+      <c r="J667">
+        <v>0</v>
+      </c>
+      <c r="L667">
+        <v>250</v>
+      </c>
+      <c r="N667">
+        <v>56</v>
+      </c>
+      <c r="O667">
+        <v>56</v>
+      </c>
+      <c r="P667">
+        <v>390</v>
+      </c>
       <c r="Q667" t="s">
-        <v>267</v>
+        <v>286</v>
       </c>
     </row>
     <row r="668" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A668" t="s">
-        <v>213</v>
+        <v>304</v>
       </c>
       <c r="B668">
-        <v>-34.751460000000002</v>
+        <v>-34.899749999999997</v>
       </c>
       <c r="C668">
-        <v>137.47702000000001</v>
+        <v>137.45174</v>
       </c>
       <c r="D668" s="2">
         <v>46075</v>
       </c>
       <c r="E668" s="20">
-        <v>0.58333333333333337</v>
+        <v>0.60416666666666663</v>
       </c>
       <c r="F668" s="1"/>
       <c r="G668" s="1"/>
       <c r="H668" s="1"/>
-      <c r="I668" s="1"/>
+      <c r="I668" s="1">
+        <v>3333</v>
+      </c>
       <c r="J668" s="1">
-        <v>111</v>
+        <v>1111</v>
       </c>
       <c r="K668" s="1"/>
       <c r="L668" s="1"/>
@@ -25576,156 +25602,141 @@
     </row>
     <row r="669" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A669" t="s">
-        <v>92</v>
+        <v>369</v>
       </c>
       <c r="B669">
-        <v>-35.632150000000003</v>
+        <v>-34.82743</v>
       </c>
       <c r="C669">
-        <v>138.48339999999999</v>
+        <v>137.45844</v>
       </c>
       <c r="D669" s="2">
         <v>46075</v>
       </c>
       <c r="E669" s="20">
-        <v>0.58333333333333337</v>
-      </c>
-      <c r="F669">
-        <v>0</v>
-      </c>
-      <c r="G669">
-        <v>0.3</v>
-      </c>
-      <c r="H669">
-        <v>0</v>
-      </c>
-      <c r="I669">
-        <v>0.63300000000000001</v>
-      </c>
-      <c r="J669">
-        <v>0</v>
-      </c>
-      <c r="K669">
-        <v>0</v>
-      </c>
-      <c r="L669">
-        <v>6.3</v>
-      </c>
-      <c r="M669">
-        <v>0</v>
-      </c>
-      <c r="N669">
-        <v>0.23300000000000001</v>
-      </c>
-      <c r="O669">
-        <v>0.1</v>
-      </c>
-      <c r="P669">
-        <f>SUM(F669:I669,K669:O669)</f>
-        <v>7.5659999999999989</v>
-      </c>
+        <v>0.59375</v>
+      </c>
+      <c r="F669" s="1"/>
+      <c r="G669" s="1"/>
+      <c r="H669" s="1"/>
+      <c r="I669" s="1">
+        <v>3111</v>
+      </c>
+      <c r="J669" s="1">
+        <v>389</v>
+      </c>
+      <c r="K669" s="1"/>
+      <c r="L669" s="1"/>
+      <c r="M669" s="1"/>
+      <c r="N669" s="1"/>
+      <c r="O669" s="1"/>
+      <c r="P669" s="1"/>
       <c r="Q669" t="s">
-        <v>78</v>
+        <v>267</v>
       </c>
     </row>
     <row r="670" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A670" t="s">
-        <v>390</v>
+        <v>213</v>
       </c>
       <c r="B670">
-        <v>-35.739091000000002</v>
+        <v>-34.751460000000002</v>
       </c>
       <c r="C670">
-        <v>137.67788400000001</v>
+        <v>137.47702000000001</v>
       </c>
       <c r="D670" s="2">
-        <v>46076</v>
+        <v>46075</v>
       </c>
       <c r="E670" s="20">
-        <v>0.3</v>
-      </c>
-      <c r="F670">
-        <v>0</v>
-      </c>
-      <c r="G670">
-        <v>0</v>
-      </c>
-      <c r="H670">
-        <v>0</v>
-      </c>
-      <c r="I670">
-        <v>222</v>
-      </c>
-      <c r="J670">
-        <v>0</v>
-      </c>
-      <c r="K670">
-        <v>0</v>
-      </c>
-      <c r="L670">
-        <v>4333</v>
-      </c>
-      <c r="M670">
-        <v>222</v>
-      </c>
-      <c r="N670">
-        <v>0</v>
-      </c>
-      <c r="P670">
-        <v>4777</v>
-      </c>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="F670" s="1"/>
+      <c r="G670" s="1"/>
+      <c r="H670" s="1"/>
+      <c r="I670" s="1"/>
+      <c r="J670" s="1">
+        <v>111</v>
+      </c>
+      <c r="K670" s="1"/>
+      <c r="L670" s="1"/>
+      <c r="M670" s="1"/>
+      <c r="N670" s="1"/>
+      <c r="O670" s="1"/>
+      <c r="P670" s="1"/>
       <c r="Q670" t="s">
-        <v>151</v>
+        <v>267</v>
       </c>
     </row>
     <row r="671" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A671" t="s">
-        <v>360</v>
+        <v>92</v>
       </c>
       <c r="B671">
-        <v>-34.494970000000002</v>
+        <v>-35.632150000000003</v>
       </c>
       <c r="C671">
-        <v>137.48038</v>
+        <v>138.48339999999999</v>
       </c>
       <c r="D671" s="2">
-        <v>46076</v>
+        <v>46075</v>
       </c>
       <c r="E671" s="20">
-        <v>0.57291666666666663</v>
-      </c>
-      <c r="F671" s="1"/>
-      <c r="G671" s="1"/>
-      <c r="H671" s="1"/>
-      <c r="I671" s="1"/>
-      <c r="J671" s="1">
-        <v>1389</v>
-      </c>
-      <c r="K671" s="1"/>
-      <c r="L671" s="1"/>
-      <c r="M671" s="1"/>
-      <c r="N671" s="1"/>
-      <c r="O671" s="1"/>
-      <c r="P671" s="1"/>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="F671">
+        <v>0</v>
+      </c>
+      <c r="G671">
+        <v>0.3</v>
+      </c>
+      <c r="H671">
+        <v>0</v>
+      </c>
+      <c r="I671">
+        <v>0.63300000000000001</v>
+      </c>
+      <c r="J671">
+        <v>0</v>
+      </c>
+      <c r="K671">
+        <v>0</v>
+      </c>
+      <c r="L671">
+        <v>6.3</v>
+      </c>
+      <c r="M671">
+        <v>0</v>
+      </c>
+      <c r="N671">
+        <v>0.23300000000000001</v>
+      </c>
+      <c r="O671">
+        <v>0.1</v>
+      </c>
+      <c r="P671">
+        <f>SUM(F671:I671,K671:O671)</f>
+        <v>7.5659999999999989</v>
+      </c>
       <c r="Q671" t="s">
-        <v>267</v>
+        <v>78</v>
       </c>
     </row>
     <row r="672" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A672" t="s">
-        <v>130</v>
+        <v>390</v>
       </c>
       <c r="B672">
-        <v>-35.078539999999997</v>
+        <v>-35.739091000000002</v>
       </c>
       <c r="C672">
-        <v>138.49587</v>
+        <v>137.67788400000001</v>
       </c>
       <c r="D672" s="2">
-        <v>46078</v>
+        <v>46076</v>
       </c>
       <c r="E672" s="20">
-        <v>0.625</v>
+        <v>0.3</v>
       </c>
       <c r="F672">
         <v>0</v>
@@ -25734,10 +25745,10 @@
         <v>0</v>
       </c>
       <c r="H672">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="I672">
-        <v>0.1</v>
+        <v>222</v>
       </c>
       <c r="J672">
         <v>0</v>
@@ -25746,216 +25757,256 @@
         <v>0</v>
       </c>
       <c r="L672">
-        <v>6.4</v>
+        <v>4333</v>
       </c>
       <c r="M672">
-        <v>0.3</v>
+        <v>222</v>
       </c>
       <c r="N672">
-        <v>0.1</v>
-      </c>
-      <c r="O672">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="P672">
-        <f>SUM(F672:I672,K672:O672)</f>
-        <v>7.2</v>
+        <v>4777</v>
       </c>
       <c r="Q672" t="s">
-        <v>78</v>
+        <v>151</v>
       </c>
     </row>
     <row r="673" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A673" t="s">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="B673">
-        <v>-35.119663000000003</v>
+        <v>-34.494970000000002</v>
       </c>
       <c r="C673">
-        <v>138.46739500000001</v>
+        <v>137.48038</v>
       </c>
       <c r="D673" s="2">
-        <v>46078</v>
+        <v>46076</v>
       </c>
       <c r="E673" s="20">
-        <v>0.61111111111111116</v>
-      </c>
-      <c r="F673">
-        <v>0</v>
-      </c>
-      <c r="G673">
-        <v>0</v>
-      </c>
-      <c r="H673">
-        <v>3.3000000000000002E-2</v>
-      </c>
-      <c r="I673">
-        <v>0.16700000000000001</v>
-      </c>
-      <c r="J673">
-        <v>0</v>
-      </c>
-      <c r="K673">
-        <v>0</v>
-      </c>
-      <c r="L673">
-        <v>0.33300000000000002</v>
-      </c>
-      <c r="M673">
-        <v>0</v>
-      </c>
-      <c r="N673">
-        <v>0.16700000000000001</v>
-      </c>
-      <c r="O673">
-        <v>5.7000000000000002E-2</v>
-      </c>
-      <c r="P673">
-        <f>SUM(F673:I673,K673:O673)</f>
-        <v>0.75700000000000012</v>
-      </c>
+        <v>0.57291666666666663</v>
+      </c>
+      <c r="F673" s="1"/>
+      <c r="G673" s="1"/>
+      <c r="H673" s="1"/>
+      <c r="I673" s="1"/>
+      <c r="J673" s="1">
+        <v>1389</v>
+      </c>
+      <c r="K673" s="1"/>
+      <c r="L673" s="1"/>
+      <c r="M673" s="1"/>
+      <c r="N673" s="1"/>
+      <c r="O673" s="1"/>
+      <c r="P673" s="1"/>
       <c r="Q673" t="s">
-        <v>78</v>
+        <v>267</v>
       </c>
     </row>
     <row r="674" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A674" t="s">
-        <v>59</v>
+        <v>130</v>
       </c>
       <c r="B674">
-        <v>-35.084850000000003</v>
+        <v>-35.078539999999997</v>
       </c>
       <c r="C674">
-        <v>137.74889999999999</v>
+        <v>138.49587</v>
       </c>
       <c r="D674" s="2">
         <v>46078</v>
       </c>
       <c r="E674" s="20">
-        <v>0.54166666666666663</v>
+        <v>0.625</v>
+      </c>
+      <c r="F674">
+        <v>0</v>
       </c>
       <c r="G674">
-        <v>56</v>
+        <v>0</v>
+      </c>
+      <c r="H674">
+        <v>0.1</v>
       </c>
       <c r="I674">
-        <v>222</v>
+        <v>0.1</v>
       </c>
       <c r="J674">
         <v>0</v>
       </c>
+      <c r="K674">
+        <v>0</v>
+      </c>
       <c r="L674">
-        <v>667</v>
+        <v>6.4</v>
+      </c>
+      <c r="M674">
+        <v>0.3</v>
       </c>
       <c r="N674">
-        <v>389</v>
+        <v>0.1</v>
+      </c>
+      <c r="O674">
+        <v>0.2</v>
       </c>
       <c r="P674">
-        <v>1334</v>
+        <f>SUM(F674:I674,K674:O674)</f>
+        <v>7.2</v>
       </c>
       <c r="Q674" t="s">
-        <v>149</v>
+        <v>78</v>
       </c>
     </row>
     <row r="675" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A675" t="s">
-        <v>59</v>
+        <v>370</v>
       </c>
       <c r="B675">
-        <v>-35.084850000000003</v>
+        <v>-35.119663000000003</v>
       </c>
       <c r="C675">
-        <v>137.74889999999999</v>
+        <v>138.46739500000001</v>
       </c>
       <c r="D675" s="2">
         <v>46078</v>
       </c>
       <c r="E675" s="20">
-        <v>0.54166666666666663</v>
+        <v>0.61111111111111116</v>
+      </c>
+      <c r="F675">
+        <v>0</v>
       </c>
       <c r="G675">
-        <v>56</v>
+        <v>0</v>
+      </c>
+      <c r="H675">
+        <v>3.3000000000000002E-2</v>
       </c>
       <c r="I675">
-        <v>56</v>
+        <v>0.16700000000000001</v>
       </c>
       <c r="J675">
         <v>0</v>
       </c>
+      <c r="K675">
+        <v>0</v>
+      </c>
       <c r="L675">
-        <v>444</v>
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="M675">
+        <v>0</v>
       </c>
       <c r="N675">
-        <v>1111</v>
+        <v>0.16700000000000001</v>
+      </c>
+      <c r="O675">
+        <v>5.7000000000000002E-2</v>
       </c>
       <c r="P675">
-        <v>1667</v>
+        <f>SUM(F675:I675,K675:O675)</f>
+        <v>0.75700000000000012</v>
       </c>
       <c r="Q675" t="s">
-        <v>149</v>
+        <v>78</v>
       </c>
     </row>
     <row r="676" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A676" t="s">
-        <v>384</v>
+        <v>59</v>
       </c>
       <c r="B676">
-        <v>-34.759169999999997</v>
+        <v>-35.084850000000003</v>
       </c>
       <c r="C676">
-        <v>137.47612000000001</v>
+        <v>137.74889999999999</v>
       </c>
       <c r="D676" s="2">
         <v>46078</v>
       </c>
       <c r="E676" s="20">
-        <v>0.58333333333333337</v>
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="G676">
+        <v>56</v>
+      </c>
+      <c r="I676">
+        <v>222</v>
       </c>
       <c r="J676">
-        <v>1833</v>
+        <v>0</v>
+      </c>
+      <c r="L676">
+        <v>667</v>
+      </c>
+      <c r="N676">
+        <v>389</v>
+      </c>
+      <c r="P676">
+        <v>1334</v>
       </c>
       <c r="Q676" t="s">
-        <v>267</v>
+        <v>149</v>
       </c>
     </row>
     <row r="677" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A677" t="s">
-        <v>264</v>
+        <v>59</v>
       </c>
       <c r="B677">
-        <v>-34.672490000000003</v>
+        <v>-35.084850000000003</v>
       </c>
       <c r="C677">
-        <v>137.49295000000001</v>
+        <v>137.74889999999999</v>
       </c>
       <c r="D677" s="2">
         <v>46078</v>
       </c>
+      <c r="E677" s="20">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="G677">
+        <v>56</v>
+      </c>
+      <c r="I677">
+        <v>56</v>
+      </c>
       <c r="J677">
-        <v>333</v>
+        <v>0</v>
+      </c>
+      <c r="L677">
+        <v>444</v>
+      </c>
+      <c r="N677">
+        <v>1111</v>
+      </c>
+      <c r="P677">
+        <v>1667</v>
       </c>
       <c r="Q677" t="s">
-        <v>267</v>
+        <v>149</v>
       </c>
     </row>
     <row r="678" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A678" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B678">
-        <v>-34.494970000000002</v>
+        <v>-34.759169999999997</v>
       </c>
       <c r="C678">
-        <v>137.48038</v>
+        <v>137.47612000000001</v>
       </c>
       <c r="D678" s="2">
         <v>46078</v>
       </c>
       <c r="E678" s="20">
-        <v>0.54861111111111116</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="J678">
-        <v>167</v>
+        <v>1833</v>
       </c>
       <c r="Q678" t="s">
         <v>267</v>
@@ -25963,22 +26014,19 @@
     </row>
     <row r="679" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A679" t="s">
-        <v>386</v>
+        <v>264</v>
       </c>
       <c r="B679">
-        <v>-34.584389999999999</v>
+        <v>-34.672490000000003</v>
       </c>
       <c r="C679">
-        <v>137.50560999999999</v>
+        <v>137.49295000000001</v>
       </c>
       <c r="D679" s="2">
         <v>46078</v>
       </c>
-      <c r="E679" s="20">
-        <v>0.5625</v>
-      </c>
       <c r="J679">
-        <v>0</v>
+        <v>333</v>
       </c>
       <c r="Q679" t="s">
         <v>267</v>
@@ -25986,22 +26034,22 @@
     </row>
     <row r="680" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A680" t="s">
-        <v>304</v>
+        <v>385</v>
       </c>
       <c r="B680">
-        <v>-34.899749999999997</v>
+        <v>-34.494970000000002</v>
       </c>
       <c r="C680">
-        <v>137.45174</v>
+        <v>137.48038</v>
       </c>
       <c r="D680" s="2">
-        <v>46079</v>
+        <v>46078</v>
       </c>
       <c r="E680" s="20">
-        <v>0.58333333333333337</v>
+        <v>0.54861111111111116</v>
       </c>
       <c r="J680">
-        <v>4833</v>
+        <v>167</v>
       </c>
       <c r="Q680" t="s">
         <v>267</v>
@@ -26009,309 +26057,249 @@
     </row>
     <row r="681" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A681" t="s">
-        <v>37</v>
+        <v>386</v>
       </c>
       <c r="B681">
-        <v>-34.289369999999998</v>
+        <v>-34.584389999999999</v>
       </c>
       <c r="C681">
-        <v>138.01242999999999</v>
+        <v>137.50560999999999</v>
       </c>
       <c r="D681" s="2">
-        <v>46080</v>
-      </c>
-      <c r="F681">
-        <v>56</v>
-      </c>
-      <c r="G681">
-        <v>389</v>
-      </c>
-      <c r="H681">
-        <v>1222</v>
-      </c>
-      <c r="I681">
-        <v>222</v>
+        <v>46078</v>
+      </c>
+      <c r="E681" s="20">
+        <v>0.5625</v>
       </c>
       <c r="J681">
         <v>0</v>
       </c>
-      <c r="L681">
-        <v>1556</v>
-      </c>
-      <c r="M681">
-        <v>56</v>
-      </c>
-      <c r="N681">
-        <v>3333</v>
-      </c>
-      <c r="O681">
-        <v>56</v>
-      </c>
-      <c r="P681">
-        <v>6889</v>
-      </c>
       <c r="Q681" t="s">
-        <v>76</v>
+        <v>267</v>
       </c>
     </row>
     <row r="682" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A682" t="s">
-        <v>377</v>
+        <v>304</v>
       </c>
       <c r="B682">
-        <v>-34.902070808541197</v>
+        <v>-34.899749999999997</v>
       </c>
       <c r="C682">
-        <v>137.79925776072</v>
+        <v>137.45174</v>
       </c>
       <c r="D682" s="2">
-        <v>46080</v>
+        <v>46079</v>
       </c>
       <c r="E682" s="20">
-        <v>0.71875</v>
-      </c>
-      <c r="I682">
-        <v>389</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="J682">
-        <v>167</v>
-      </c>
-      <c r="K682" t="s">
-        <v>375</v>
-      </c>
-      <c r="L682">
-        <v>167</v>
-      </c>
-      <c r="N682">
-        <v>556</v>
-      </c>
-      <c r="O682">
-        <v>278</v>
-      </c>
-      <c r="P682">
-        <v>1390</v>
+        <v>4833</v>
       </c>
       <c r="Q682" t="s">
-        <v>368</v>
+        <v>267</v>
       </c>
     </row>
     <row r="683" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A683" t="s">
-        <v>382</v>
+        <v>37</v>
       </c>
       <c r="B683">
-        <v>-34.933680000000003</v>
+        <v>-34.289369999999998</v>
       </c>
       <c r="C683">
-        <v>137.35257300000001</v>
+        <v>138.01242999999999</v>
       </c>
       <c r="D683" s="2">
         <v>46080</v>
       </c>
-      <c r="E683" s="20">
-        <v>0.53125</v>
+      <c r="F683">
+        <v>56</v>
+      </c>
+      <c r="G683">
+        <v>389</v>
+      </c>
+      <c r="H683">
+        <v>1222</v>
       </c>
       <c r="I683">
-        <v>834</v>
+        <v>222</v>
       </c>
       <c r="J683">
-        <v>556</v>
+        <v>0</v>
       </c>
       <c r="L683">
+        <v>1556</v>
+      </c>
+      <c r="M683">
         <v>56</v>
       </c>
+      <c r="N683">
+        <v>3333</v>
+      </c>
       <c r="O683">
-        <v>167</v>
+        <v>56</v>
       </c>
       <c r="P683">
-        <v>1057</v>
+        <v>6889</v>
       </c>
       <c r="Q683" t="s">
-        <v>219</v>
+        <v>76</v>
       </c>
     </row>
     <row r="684" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A684" t="s">
-        <v>384</v>
+        <v>377</v>
       </c>
       <c r="B684">
-        <v>-34.759169999999997</v>
+        <v>-34.902070808541197</v>
       </c>
       <c r="C684">
-        <v>137.47612000000001</v>
+        <v>137.79925776072</v>
       </c>
       <c r="D684" s="2">
         <v>46080</v>
       </c>
       <c r="E684" s="20">
-        <v>0.58333333333333337</v>
+        <v>0.71875</v>
+      </c>
+      <c r="I684">
+        <v>389</v>
       </c>
       <c r="J684">
-        <v>1556</v>
+        <v>167</v>
+      </c>
+      <c r="K684" t="s">
+        <v>375</v>
+      </c>
+      <c r="L684">
+        <v>167</v>
+      </c>
+      <c r="N684">
+        <v>556</v>
+      </c>
+      <c r="O684">
+        <v>278</v>
+      </c>
+      <c r="P684">
+        <v>1390</v>
       </c>
       <c r="Q684" t="s">
-        <v>267</v>
+        <v>368</v>
       </c>
     </row>
     <row r="685" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A685" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="B685">
-        <v>-34.075153</v>
+        <v>-34.933680000000003</v>
       </c>
       <c r="C685">
-        <v>137.543789</v>
+        <v>137.35257300000001</v>
       </c>
       <c r="D685" s="2">
-        <v>46081</v>
-      </c>
-      <c r="G685">
-        <v>778</v>
-      </c>
-      <c r="H685">
-        <v>111</v>
+        <v>46080</v>
+      </c>
+      <c r="E685" s="20">
+        <v>0.53125</v>
       </c>
       <c r="I685">
-        <v>222</v>
+        <v>834</v>
       </c>
       <c r="J685">
-        <v>0</v>
+        <v>556</v>
       </c>
       <c r="L685">
         <v>56</v>
       </c>
-      <c r="M685">
-        <v>111</v>
+      <c r="O685">
+        <v>167</v>
       </c>
       <c r="P685">
-        <v>1278</v>
+        <v>1057</v>
       </c>
       <c r="Q685" t="s">
-        <v>76</v>
+        <v>219</v>
       </c>
     </row>
     <row r="686" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A686" t="s">
-        <v>305</v>
+        <v>384</v>
       </c>
       <c r="B686">
-        <v>-35.762554199999997</v>
+        <v>-34.759169999999997</v>
       </c>
       <c r="C686">
-        <v>137.8867127</v>
+        <v>137.47612000000001</v>
       </c>
       <c r="D686" s="2">
-        <v>46081</v>
+        <v>46080</v>
       </c>
       <c r="E686" s="20">
-        <v>0.61458333333333337</v>
-      </c>
-      <c r="F686">
-        <v>0</v>
-      </c>
-      <c r="G686">
-        <v>0</v>
-      </c>
-      <c r="H686">
-        <v>0</v>
-      </c>
-      <c r="I686">
-        <v>0</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="J686">
-        <v>0</v>
-      </c>
-      <c r="K686">
-        <v>0</v>
-      </c>
-      <c r="L686">
-        <v>8000</v>
-      </c>
-      <c r="M686">
-        <v>222</v>
-      </c>
-      <c r="N686">
-        <v>0</v>
-      </c>
-      <c r="O686">
-        <v>0</v>
-      </c>
-      <c r="P686">
-        <v>8222</v>
+        <v>1556</v>
       </c>
       <c r="Q686" t="s">
-        <v>151</v>
+        <v>267</v>
       </c>
     </row>
     <row r="687" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A687" t="s">
-        <v>364</v>
+        <v>376</v>
       </c>
       <c r="B687">
-        <v>-35.853555700000001</v>
+        <v>-34.075153</v>
       </c>
       <c r="C687">
-        <v>137.74248499999999</v>
+        <v>137.543789</v>
       </c>
       <c r="D687" s="2">
         <v>46081</v>
       </c>
-      <c r="E687" s="20">
-        <v>0.72916666666666663</v>
-      </c>
-      <c r="F687">
-        <v>0</v>
-      </c>
       <c r="G687">
-        <v>0</v>
+        <v>778</v>
       </c>
       <c r="H687">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="I687">
         <v>222</v>
       </c>
       <c r="J687">
-        <v>222</v>
-      </c>
-      <c r="K687">
         <v>0</v>
       </c>
       <c r="L687">
-        <v>5333</v>
+        <v>56</v>
       </c>
       <c r="M687">
-        <v>333</v>
-      </c>
-      <c r="N687">
-        <v>0</v>
-      </c>
-      <c r="O687">
-        <v>222</v>
+        <v>111</v>
       </c>
       <c r="P687">
-        <v>6110</v>
+        <v>1278</v>
       </c>
       <c r="Q687" t="s">
-        <v>151</v>
+        <v>76</v>
       </c>
     </row>
     <row r="688" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A688" t="s">
-        <v>379</v>
+        <v>305</v>
       </c>
       <c r="B688">
-        <v>-35.852509699999999</v>
+        <v>-35.762554199999997</v>
       </c>
       <c r="C688">
-        <v>137.7474651</v>
+        <v>137.8867127</v>
       </c>
       <c r="D688" s="2">
-        <v>46083</v>
+        <v>46081</v>
       </c>
       <c r="E688" s="20">
-        <v>0.52083333333333337</v>
+        <v>0.61458333333333337</v>
       </c>
       <c r="F688">
         <v>0</v>
@@ -26323,25 +26311,28 @@
         <v>0</v>
       </c>
       <c r="I688">
-        <v>333</v>
+        <v>0</v>
       </c>
       <c r="J688">
-        <v>333</v>
+        <v>0</v>
+      </c>
+      <c r="K688">
+        <v>0</v>
       </c>
       <c r="L688">
-        <v>1444</v>
+        <v>8000</v>
       </c>
       <c r="M688">
-        <v>0</v>
+        <v>222</v>
       </c>
       <c r="N688">
         <v>0</v>
       </c>
       <c r="O688">
-        <v>1111</v>
+        <v>0</v>
       </c>
       <c r="P688">
-        <v>2888</v>
+        <v>8222</v>
       </c>
       <c r="Q688" t="s">
         <v>151</v>
@@ -26349,52 +26340,52 @@
     </row>
     <row r="689" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A689" t="s">
-        <v>380</v>
+        <v>364</v>
       </c>
       <c r="B689">
-        <v>-35.787201000000003</v>
+        <v>-35.853555700000001</v>
       </c>
       <c r="C689">
-        <v>137.778009</v>
+        <v>137.74248499999999</v>
       </c>
       <c r="D689" s="2">
-        <v>46083</v>
+        <v>46081</v>
       </c>
       <c r="E689" s="20">
-        <v>0.4826388888888889</v>
+        <v>0.72916666666666663</v>
       </c>
       <c r="F689">
         <v>0</v>
       </c>
       <c r="G689">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="H689">
         <v>0</v>
       </c>
       <c r="I689">
-        <v>1111</v>
+        <v>222</v>
       </c>
       <c r="J689">
-        <v>0</v>
+        <v>222</v>
       </c>
       <c r="K689">
-        <v>1111</v>
+        <v>0</v>
       </c>
       <c r="L689">
-        <v>11556</v>
+        <v>5333</v>
       </c>
       <c r="M689">
-        <v>1111</v>
+        <v>333</v>
       </c>
       <c r="N689">
         <v>0</v>
       </c>
       <c r="O689">
-        <v>1111</v>
+        <v>222</v>
       </c>
       <c r="P689">
-        <v>16111</v>
+        <v>6110</v>
       </c>
       <c r="Q689" t="s">
         <v>151</v>
@@ -26402,211 +26393,268 @@
     </row>
     <row r="690" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A690" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="B690">
-        <v>-34.759169999999997</v>
+        <v>-35.852509699999999</v>
       </c>
       <c r="C690">
-        <v>137.47612000000001</v>
+        <v>137.7474651</v>
       </c>
       <c r="D690" s="2">
         <v>46083</v>
       </c>
       <c r="E690" s="20">
-        <v>0.58333333333333337</v>
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="F690">
+        <v>0</v>
+      </c>
+      <c r="G690">
+        <v>0</v>
+      </c>
+      <c r="H690">
+        <v>0</v>
+      </c>
+      <c r="I690">
+        <v>333</v>
       </c>
       <c r="J690">
-        <v>2667</v>
+        <v>333</v>
+      </c>
+      <c r="L690">
+        <v>1444</v>
+      </c>
+      <c r="M690">
+        <v>0</v>
+      </c>
+      <c r="N690">
+        <v>0</v>
+      </c>
+      <c r="O690">
+        <v>1111</v>
+      </c>
+      <c r="P690">
+        <v>2888</v>
       </c>
       <c r="Q690" t="s">
-        <v>267</v>
+        <v>151</v>
       </c>
     </row>
     <row r="691" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A691" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="B691">
-        <v>-34.494970000000002</v>
+        <v>-35.787201000000003</v>
       </c>
       <c r="C691">
-        <v>137.48038</v>
+        <v>137.778009</v>
       </c>
       <c r="D691" s="2">
         <v>46083</v>
       </c>
       <c r="E691" s="20">
-        <v>0.5625</v>
+        <v>0.4826388888888889</v>
+      </c>
+      <c r="F691">
+        <v>0</v>
+      </c>
+      <c r="G691">
+        <v>111</v>
+      </c>
+      <c r="H691">
+        <v>0</v>
+      </c>
+      <c r="I691">
+        <v>1111</v>
       </c>
       <c r="J691">
-        <v>222</v>
+        <v>0</v>
+      </c>
+      <c r="K691">
+        <v>1111</v>
+      </c>
+      <c r="L691">
+        <v>11556</v>
+      </c>
+      <c r="M691">
+        <v>1111</v>
+      </c>
+      <c r="N691">
+        <v>0</v>
+      </c>
+      <c r="O691">
+        <v>1111</v>
+      </c>
+      <c r="P691">
+        <v>16111</v>
       </c>
       <c r="Q691" t="s">
-        <v>267</v>
+        <v>151</v>
       </c>
     </row>
     <row r="692" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A692" t="s">
-        <v>397</v>
+        <v>384</v>
       </c>
       <c r="B692">
-        <v>-36.866</v>
+        <v>-34.759169999999997</v>
       </c>
       <c r="C692">
-        <v>139.81913</v>
+        <v>137.47612000000001</v>
       </c>
       <c r="D692" s="2">
         <v>46083</v>
       </c>
-      <c r="G692">
-        <v>333</v>
-      </c>
-      <c r="H692">
-        <v>778</v>
-      </c>
-      <c r="I692">
-        <v>667</v>
+      <c r="E692" s="20">
+        <v>0.58333333333333337</v>
       </c>
       <c r="J692">
-        <v>0</v>
-      </c>
-      <c r="L692">
-        <v>31333</v>
-      </c>
-      <c r="N692">
-        <v>1889</v>
-      </c>
-      <c r="O692">
-        <v>1389</v>
-      </c>
-      <c r="P692">
-        <v>36389</v>
+        <v>2667</v>
       </c>
       <c r="Q692" t="s">
-        <v>129</v>
+        <v>267</v>
       </c>
     </row>
     <row r="693" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A693" t="s">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="B693">
-        <v>-34.902070808541197</v>
+        <v>-34.494970000000002</v>
       </c>
       <c r="C693">
-        <v>137.79925776072</v>
+        <v>137.48038</v>
       </c>
       <c r="D693" s="2">
-        <v>46084</v>
+        <v>46083</v>
       </c>
       <c r="E693" s="20">
-        <v>0.71527777777777779</v>
-      </c>
-      <c r="I693">
-        <v>667</v>
+        <v>0.5625</v>
       </c>
       <c r="J693">
-        <v>0</v>
-      </c>
-      <c r="L693">
-        <v>333</v>
-      </c>
-      <c r="N693">
-        <v>389</v>
-      </c>
-      <c r="O693">
-        <v>167</v>
-      </c>
-      <c r="P693">
-        <v>1556</v>
+        <v>222</v>
       </c>
       <c r="Q693" t="s">
-        <v>368</v>
+        <v>267</v>
       </c>
     </row>
     <row r="694" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A694" t="s">
-        <v>383</v>
+        <v>397</v>
       </c>
       <c r="B694">
-        <v>-34.495376</v>
+        <v>-36.866</v>
       </c>
       <c r="C694">
-        <v>137.481537</v>
+        <v>139.81913</v>
       </c>
       <c r="D694" s="2">
-        <v>46084</v>
-      </c>
-      <c r="E694" s="20">
-        <v>0.82291666666666663</v>
+        <v>46083</v>
+      </c>
+      <c r="G694">
+        <v>333</v>
+      </c>
+      <c r="H694">
+        <v>778</v>
       </c>
       <c r="I694">
-        <v>1444</v>
+        <v>667</v>
       </c>
       <c r="J694">
-        <v>833</v>
+        <v>0</v>
       </c>
       <c r="L694">
-        <v>1222</v>
+        <v>31333</v>
       </c>
       <c r="N694">
-        <v>1000</v>
+        <v>1889</v>
       </c>
       <c r="O694">
-        <v>223</v>
+        <v>1389</v>
       </c>
       <c r="P694">
-        <v>3889</v>
+        <v>36389</v>
       </c>
       <c r="Q694" t="s">
-        <v>219</v>
+        <v>129</v>
       </c>
     </row>
     <row r="695" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A695" t="s">
-        <v>384</v>
+        <v>377</v>
       </c>
       <c r="B695">
-        <v>-34.759169999999997</v>
+        <v>-34.902070808541197</v>
       </c>
       <c r="C695">
-        <v>137.47612000000001</v>
+        <v>137.79925776072</v>
       </c>
       <c r="D695" s="2">
-        <v>46085</v>
+        <v>46084</v>
       </c>
       <c r="E695" s="20">
-        <v>0.58333333333333337</v>
+        <v>0.71527777777777779</v>
+      </c>
+      <c r="I695">
+        <v>667</v>
       </c>
       <c r="J695">
+        <v>0</v>
+      </c>
+      <c r="L695">
+        <v>333</v>
+      </c>
+      <c r="N695">
+        <v>389</v>
+      </c>
+      <c r="O695">
         <v>167</v>
       </c>
+      <c r="P695">
+        <v>1556</v>
+      </c>
       <c r="Q695" t="s">
-        <v>267</v>
+        <v>368</v>
       </c>
     </row>
     <row r="696" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A696" t="s">
-        <v>304</v>
+        <v>383</v>
       </c>
       <c r="B696">
-        <v>-34.899749999999997</v>
+        <v>-34.495376</v>
       </c>
       <c r="C696">
-        <v>137.45174</v>
+        <v>137.481537</v>
       </c>
       <c r="D696" s="2">
-        <v>46086</v>
+        <v>46084</v>
       </c>
       <c r="E696" s="20">
-        <v>0.71875</v>
+        <v>0.82291666666666663</v>
+      </c>
+      <c r="I696">
+        <v>1444</v>
       </c>
       <c r="J696">
-        <v>3167</v>
+        <v>833</v>
+      </c>
+      <c r="L696">
+        <v>1222</v>
+      </c>
+      <c r="N696">
+        <v>1000</v>
+      </c>
+      <c r="O696">
+        <v>223</v>
+      </c>
+      <c r="P696">
+        <v>3889</v>
       </c>
       <c r="Q696" t="s">
-        <v>267</v>
+        <v>219</v>
       </c>
     </row>
     <row r="697" spans="1:17" x14ac:dyDescent="0.3">
@@ -26620,13 +26668,13 @@
         <v>137.47612000000001</v>
       </c>
       <c r="D697" s="2">
-        <v>46087</v>
+        <v>46085</v>
       </c>
       <c r="E697" s="20">
         <v>0.58333333333333337</v>
       </c>
       <c r="J697">
-        <v>0</v>
+        <v>167</v>
       </c>
       <c r="Q697" t="s">
         <v>267</v>
@@ -26634,66 +26682,36 @@
     </row>
     <row r="698" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A698" t="s">
-        <v>379</v>
+        <v>304</v>
       </c>
       <c r="B698">
-        <v>-35.853555700000001</v>
+        <v>-34.899749999999997</v>
       </c>
       <c r="C698">
-        <v>137.74248499999999</v>
+        <v>137.45174</v>
       </c>
       <c r="D698" s="2">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="E698" s="20">
-        <v>0.47916666666666669</v>
-      </c>
-      <c r="F698">
-        <v>167</v>
-      </c>
-      <c r="G698">
-        <v>0</v>
-      </c>
-      <c r="H698">
-        <v>9222</v>
-      </c>
-      <c r="I698">
-        <v>444</v>
+        <v>0.71875</v>
       </c>
       <c r="J698">
-        <v>444</v>
-      </c>
-      <c r="K698">
-        <v>0</v>
-      </c>
-      <c r="L698">
-        <v>1222</v>
-      </c>
-      <c r="M698">
-        <v>0</v>
-      </c>
-      <c r="N698">
-        <v>0</v>
-      </c>
-      <c r="O698">
-        <v>111</v>
-      </c>
-      <c r="P698">
-        <v>11166</v>
+        <v>3167</v>
       </c>
       <c r="Q698" t="s">
-        <v>151</v>
+        <v>267</v>
       </c>
     </row>
     <row r="699" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A699" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="B699">
-        <v>-35.739091000000002</v>
+        <v>-34.759169999999997</v>
       </c>
       <c r="C699">
-        <v>137.67788400000001</v>
+        <v>137.47612000000001</v>
       </c>
       <c r="D699" s="2">
         <v>46087</v>
@@ -26701,158 +26719,156 @@
       <c r="E699" s="20">
         <v>0.58333333333333337</v>
       </c>
-      <c r="F699">
-        <v>0</v>
-      </c>
-      <c r="G699">
-        <v>0</v>
-      </c>
-      <c r="H699">
-        <v>0</v>
-      </c>
-      <c r="I699">
-        <v>0</v>
-      </c>
       <c r="J699">
         <v>0</v>
       </c>
-      <c r="K699">
-        <v>0</v>
-      </c>
-      <c r="L699">
-        <v>0</v>
-      </c>
-      <c r="M699">
-        <v>0</v>
-      </c>
-      <c r="N699">
-        <v>150</v>
-      </c>
-      <c r="O699">
-        <v>0</v>
-      </c>
-      <c r="P699">
-        <v>150</v>
-      </c>
       <c r="Q699" t="s">
-        <v>151</v>
+        <v>267</v>
       </c>
     </row>
     <row r="700" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A700" t="s">
-        <v>269</v>
+        <v>379</v>
       </c>
       <c r="B700">
-        <v>-34.824044999999998</v>
+        <v>-35.853555700000001</v>
       </c>
       <c r="C700">
-        <v>138.48377600000001</v>
+        <v>137.74248499999999</v>
       </c>
       <c r="D700" s="2">
-        <v>46088</v>
-      </c>
-      <c r="E700" s="22"/>
+        <v>46087</v>
+      </c>
+      <c r="E700" s="20">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="F700">
+        <v>167</v>
+      </c>
       <c r="G700">
-        <v>0.2</v>
+        <v>0</v>
+      </c>
+      <c r="H700">
+        <v>9222</v>
       </c>
       <c r="I700">
-        <v>1.3</v>
+        <v>444</v>
       </c>
       <c r="J700">
-        <v>0</v>
-      </c>
-      <c r="K700" s="23"/>
+        <v>444</v>
+      </c>
+      <c r="K700">
+        <v>0</v>
+      </c>
       <c r="L700">
-        <v>60.5</v>
-      </c>
-      <c r="M700" s="23"/>
+        <v>1222</v>
+      </c>
+      <c r="M700">
+        <v>0</v>
+      </c>
       <c r="N700">
-        <v>1.1000000000000001</v>
+        <v>0</v>
       </c>
       <c r="O700">
-        <v>0.6</v>
+        <v>111</v>
       </c>
       <c r="P700">
-        <f>SUM(F700:I700,K700:O700)</f>
-        <v>63.7</v>
+        <v>11166</v>
       </c>
       <c r="Q700" t="s">
-        <v>78</v>
+        <v>151</v>
       </c>
     </row>
     <row r="701" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A701" t="s">
-        <v>85</v>
+        <v>390</v>
       </c>
       <c r="B701">
-        <v>-34.873964000000001</v>
+        <v>-35.739091000000002</v>
       </c>
       <c r="C701">
-        <v>138.488134</v>
+        <v>137.67788400000001</v>
       </c>
       <c r="D701" s="2">
-        <v>46088</v>
-      </c>
-      <c r="E701" s="22"/>
+        <v>46087</v>
+      </c>
+      <c r="E701" s="20">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="F701">
+        <v>0</v>
+      </c>
+      <c r="G701">
+        <v>0</v>
+      </c>
+      <c r="H701">
+        <v>0</v>
+      </c>
       <c r="I701">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="J701">
         <v>0</v>
       </c>
-      <c r="K701" s="23"/>
+      <c r="K701">
+        <v>0</v>
+      </c>
       <c r="L701">
-        <v>3.9</v>
-      </c>
-      <c r="M701" s="23"/>
+        <v>0</v>
+      </c>
+      <c r="M701">
+        <v>0</v>
+      </c>
       <c r="N701">
-        <v>0.45</v>
+        <v>150</v>
       </c>
       <c r="O701">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="P701">
-        <f>SUM(F701:I701,K701:O701)</f>
-        <v>8.1</v>
+        <v>150</v>
       </c>
       <c r="Q701" t="s">
-        <v>78</v>
+        <v>151</v>
       </c>
     </row>
     <row r="702" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A702" t="s">
-        <v>79</v>
+        <v>269</v>
       </c>
       <c r="B702">
-        <v>-34.804662999999998</v>
+        <v>-34.824044999999998</v>
       </c>
       <c r="C702">
-        <v>138.540223</v>
+        <v>138.48377600000001</v>
       </c>
       <c r="D702" s="2">
         <v>46088</v>
       </c>
       <c r="E702" s="22"/>
+      <c r="G702">
+        <v>0.2</v>
+      </c>
       <c r="I702">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="J702">
         <v>0</v>
       </c>
       <c r="K702" s="23"/>
       <c r="L702">
-        <v>35.6</v>
+        <v>60.5</v>
       </c>
       <c r="M702" s="23"/>
       <c r="N702">
-        <v>0</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="O702">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="P702">
         <f>SUM(F702:I702,K702:O702)</f>
-        <v>36.4</v>
+        <v>63.7</v>
       </c>
       <c r="Q702" t="s">
         <v>78</v>
@@ -26860,83 +26876,97 @@
     </row>
     <row r="703" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A703" t="s">
-        <v>316</v>
+        <v>85</v>
       </c>
       <c r="B703">
-        <v>-35.516800000000003</v>
+        <v>-34.873964000000001</v>
       </c>
       <c r="C703">
-        <v>138.73820000000001</v>
+        <v>138.488134</v>
       </c>
       <c r="D703" s="2">
-        <v>46089</v>
-      </c>
-      <c r="E703" s="20">
-        <v>0.64097222222222228</v>
-      </c>
+        <v>46088</v>
+      </c>
+      <c r="E703" s="22"/>
       <c r="I703">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="J703">
         <v>0</v>
       </c>
+      <c r="K703" s="23"/>
       <c r="L703">
-        <v>222</v>
+        <v>3.9</v>
+      </c>
+      <c r="M703" s="23"/>
+      <c r="N703">
+        <v>0.45</v>
+      </c>
+      <c r="O703">
+        <v>0.6</v>
       </c>
       <c r="P703">
-        <v>222</v>
+        <f>SUM(F703:I703,K703:O703)</f>
+        <v>8.1</v>
       </c>
       <c r="Q703" t="s">
-        <v>187</v>
+        <v>78</v>
       </c>
     </row>
     <row r="704" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A704" t="s">
-        <v>188</v>
+        <v>79</v>
       </c>
       <c r="B704">
-        <v>-35.515900000000002</v>
+        <v>-34.804662999999998</v>
       </c>
       <c r="C704">
-        <v>138.70529999999999</v>
+        <v>138.540223</v>
       </c>
       <c r="D704" s="2">
-        <v>46089</v>
-      </c>
-      <c r="E704" s="20">
-        <v>0.6479166666666667</v>
-      </c>
+        <v>46088</v>
+      </c>
+      <c r="E704" s="22"/>
       <c r="I704">
-        <v>111</v>
+        <v>0.4</v>
       </c>
       <c r="J704">
         <v>0</v>
       </c>
+      <c r="K704" s="23"/>
       <c r="L704">
-        <v>222</v>
+        <v>35.6</v>
+      </c>
+      <c r="M704" s="23"/>
+      <c r="N704">
+        <v>0</v>
+      </c>
+      <c r="O704">
+        <v>0.4</v>
       </c>
       <c r="P704">
-        <v>333</v>
+        <f>SUM(F704:I704,K704:O704)</f>
+        <v>36.4</v>
       </c>
       <c r="Q704" t="s">
-        <v>187</v>
+        <v>78</v>
       </c>
     </row>
     <row r="705" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A705" t="s">
-        <v>91</v>
+        <v>316</v>
       </c>
       <c r="B705">
-        <v>-35.536299999999997</v>
+        <v>-35.516800000000003</v>
       </c>
       <c r="C705">
-        <v>138.67859999999999</v>
+        <v>138.73820000000001</v>
       </c>
       <c r="D705" s="2">
         <v>46089</v>
       </c>
       <c r="E705" s="20">
-        <v>0.65555555555555556</v>
+        <v>0.64097222222222228</v>
       </c>
       <c r="I705">
         <v>0</v>
@@ -26945,10 +26975,10 @@
         <v>0</v>
       </c>
       <c r="L705">
-        <v>167</v>
+        <v>222</v>
       </c>
       <c r="P705">
-        <v>167</v>
+        <v>222</v>
       </c>
       <c r="Q705" t="s">
         <v>187</v>
@@ -26956,31 +26986,31 @@
     </row>
     <row r="706" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A706" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B706">
-        <v>-35.538600000000002</v>
+        <v>-35.515900000000002</v>
       </c>
       <c r="C706">
-        <v>138.6497</v>
+        <v>138.70529999999999</v>
       </c>
       <c r="D706" s="2">
         <v>46089</v>
       </c>
       <c r="E706" s="20">
-        <v>0.66249999999999998</v>
+        <v>0.6479166666666667</v>
       </c>
       <c r="I706">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="J706">
         <v>0</v>
       </c>
       <c r="L706">
-        <v>0</v>
+        <v>222</v>
       </c>
       <c r="P706">
-        <v>0</v>
+        <v>333</v>
       </c>
       <c r="Q706" t="s">
         <v>187</v>
@@ -26988,19 +27018,19 @@
     </row>
     <row r="707" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A707" t="s">
-        <v>318</v>
+        <v>91</v>
       </c>
       <c r="B707">
-        <v>-35.5565</v>
+        <v>-35.536299999999997</v>
       </c>
       <c r="C707">
-        <v>138.62610000000001</v>
+        <v>138.67859999999999</v>
       </c>
       <c r="D707" s="2">
         <v>46089</v>
       </c>
       <c r="E707" s="20">
-        <v>0.67013888888888884</v>
+        <v>0.65555555555555556</v>
       </c>
       <c r="I707">
         <v>0</v>
@@ -27009,10 +27039,10 @@
         <v>0</v>
       </c>
       <c r="L707">
-        <v>0</v>
+        <v>167</v>
       </c>
       <c r="P707">
-        <v>0</v>
+        <v>167</v>
       </c>
       <c r="Q707" t="s">
         <v>187</v>
@@ -27020,19 +27050,19 @@
     </row>
     <row r="708" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A708" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="B708">
-        <v>-35.5565</v>
+        <v>-35.538600000000002</v>
       </c>
       <c r="C708">
-        <v>138.62610000000001</v>
+        <v>138.6497</v>
       </c>
       <c r="D708" s="2">
         <v>46089</v>
       </c>
       <c r="E708" s="20">
-        <v>0.67708333333333337</v>
+        <v>0.66249999999999998</v>
       </c>
       <c r="I708">
         <v>0</v>
@@ -27041,10 +27071,10 @@
         <v>0</v>
       </c>
       <c r="L708">
-        <v>167</v>
+        <v>0</v>
       </c>
       <c r="P708">
-        <v>167</v>
+        <v>0</v>
       </c>
       <c r="Q708" t="s">
         <v>187</v>
@@ -27052,19 +27082,19 @@
     </row>
     <row r="709" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A709" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B709">
-        <v>-35.634900000000002</v>
+        <v>-35.5565</v>
       </c>
       <c r="C709">
-        <v>138.49850000000001</v>
+        <v>138.62610000000001</v>
       </c>
       <c r="D709" s="2">
         <v>46089</v>
       </c>
       <c r="E709" s="20">
-        <v>0.69374999999999998</v>
+        <v>0.67013888888888884</v>
       </c>
       <c r="I709">
         <v>0</v>
@@ -27073,10 +27103,10 @@
         <v>0</v>
       </c>
       <c r="L709">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="P709">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="Q709" t="s">
         <v>187</v>
@@ -27084,259 +27114,229 @@
     </row>
     <row r="710" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A710" t="s">
-        <v>388</v>
+        <v>189</v>
       </c>
       <c r="B710">
-        <v>-35.510620000000003</v>
+        <v>-35.5565</v>
       </c>
       <c r="C710">
-        <v>138.21679599999999</v>
+        <v>138.62610000000001</v>
       </c>
       <c r="D710" s="2">
         <v>46089</v>
       </c>
       <c r="E710" s="20">
-        <v>0.66666666666666663</v>
+        <v>0.67708333333333337</v>
       </c>
       <c r="I710">
-        <v>278</v>
+        <v>0</v>
       </c>
       <c r="J710">
         <v>0</v>
       </c>
       <c r="L710">
-        <v>444</v>
-      </c>
-      <c r="N710">
-        <v>3944</v>
-      </c>
-      <c r="O710">
-        <v>56</v>
+        <v>167</v>
       </c>
       <c r="P710">
-        <v>4722</v>
+        <v>167</v>
       </c>
       <c r="Q710" t="s">
-        <v>253</v>
+        <v>187</v>
       </c>
     </row>
     <row r="711" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A711" t="s">
-        <v>389</v>
+        <v>320</v>
       </c>
       <c r="B711">
-        <v>-35.793973000000001</v>
+        <v>-35.634900000000002</v>
       </c>
       <c r="C711">
-        <v>137.852418</v>
+        <v>138.49850000000001</v>
       </c>
       <c r="D711" s="2">
         <v>46089</v>
       </c>
       <c r="E711" s="20">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="F711">
-        <v>0</v>
-      </c>
-      <c r="G711">
-        <v>556</v>
-      </c>
-      <c r="H711">
-        <v>2000</v>
+        <v>0.69374999999999998</v>
       </c>
       <c r="I711">
-        <v>444</v>
+        <v>0</v>
       </c>
       <c r="J711">
         <v>0</v>
       </c>
-      <c r="K711">
-        <v>444</v>
-      </c>
       <c r="L711">
-        <v>3889</v>
-      </c>
-      <c r="M711">
-        <v>444</v>
-      </c>
-      <c r="N711">
-        <v>0</v>
-      </c>
-      <c r="O711">
-        <v>556</v>
+        <v>111</v>
       </c>
       <c r="P711">
-        <v>8333</v>
+        <v>111</v>
       </c>
       <c r="Q711" t="s">
-        <v>151</v>
+        <v>187</v>
       </c>
     </row>
     <row r="712" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A712" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B712">
-        <v>-34.88823</v>
+        <v>-35.510620000000003</v>
       </c>
       <c r="C712">
-        <v>137.45353</v>
+        <v>138.21679599999999</v>
       </c>
       <c r="D712" s="2">
-        <v>46090</v>
+        <v>46089</v>
       </c>
       <c r="E712" s="20">
-        <v>0.49305555555555558</v>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="I712">
+        <v>278</v>
       </c>
       <c r="J712">
-        <v>1722</v>
+        <v>0</v>
+      </c>
+      <c r="L712">
+        <v>444</v>
+      </c>
+      <c r="N712">
+        <v>3944</v>
+      </c>
+      <c r="O712">
+        <v>56</v>
+      </c>
+      <c r="P712">
+        <v>4722</v>
       </c>
       <c r="Q712" t="s">
-        <v>267</v>
+        <v>253</v>
       </c>
     </row>
     <row r="713" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A713" t="s">
-        <v>94</v>
+        <v>389</v>
       </c>
       <c r="B713">
-        <v>-35.58858</v>
+        <v>-35.793973000000001</v>
       </c>
       <c r="C713">
-        <v>138.60474600000001</v>
+        <v>137.852418</v>
       </c>
       <c r="D713" s="2">
-        <v>46090</v>
+        <v>46089</v>
+      </c>
+      <c r="E713" s="20">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="F713">
+        <v>0</v>
+      </c>
+      <c r="G713">
+        <v>556</v>
+      </c>
+      <c r="H713">
+        <v>2000</v>
       </c>
       <c r="I713">
-        <v>56</v>
+        <v>444</v>
       </c>
       <c r="J713">
         <v>0</v>
       </c>
+      <c r="K713">
+        <v>444</v>
+      </c>
       <c r="L713">
-        <v>222</v>
+        <v>3889</v>
+      </c>
+      <c r="M713">
+        <v>444</v>
       </c>
       <c r="N713">
-        <v>278</v>
+        <v>0</v>
       </c>
       <c r="O713">
-        <v>833</v>
+        <v>556</v>
       </c>
       <c r="P713">
-        <v>1389</v>
+        <v>8333</v>
       </c>
       <c r="Q713" t="s">
-        <v>129</v>
+        <v>151</v>
       </c>
     </row>
     <row r="714" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A714" t="s">
-        <v>89</v>
+        <v>387</v>
       </c>
       <c r="B714">
-        <v>-35.6048446</v>
+        <v>-34.88823</v>
       </c>
       <c r="C714">
-        <v>138.59278499999999</v>
+        <v>137.45353</v>
       </c>
       <c r="D714" s="2">
         <v>46090</v>
       </c>
-      <c r="I714">
-        <v>56</v>
+      <c r="E714" s="20">
+        <v>0.49305555555555558</v>
       </c>
       <c r="J714">
-        <v>0</v>
-      </c>
-      <c r="L714">
-        <v>222</v>
-      </c>
-      <c r="N714">
-        <v>389</v>
-      </c>
-      <c r="O714">
-        <v>333</v>
-      </c>
-      <c r="P714">
-        <v>1000</v>
+        <v>1722</v>
       </c>
       <c r="Q714" t="s">
-        <v>129</v>
+        <v>267</v>
       </c>
     </row>
     <row r="715" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A715" t="s">
-        <v>363</v>
+        <v>94</v>
       </c>
       <c r="B715">
-        <v>-35.878667100000001</v>
+        <v>-35.58858</v>
       </c>
       <c r="C715">
-        <v>137.6963188</v>
+        <v>138.60474600000001</v>
       </c>
       <c r="D715" s="2">
-        <v>46091</v>
-      </c>
-      <c r="E715" s="20">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F715">
-        <v>0</v>
-      </c>
-      <c r="G715">
-        <v>0</v>
-      </c>
-      <c r="H715">
+        <v>46090</v>
+      </c>
+      <c r="I715">
+        <v>56</v>
+      </c>
+      <c r="J715">
+        <v>0</v>
+      </c>
+      <c r="L715">
         <v>222</v>
       </c>
-      <c r="I715">
-        <v>333</v>
-      </c>
-      <c r="J715">
-        <v>222</v>
-      </c>
-      <c r="K715">
-        <v>111</v>
-      </c>
-      <c r="L715">
-        <v>1889</v>
-      </c>
-      <c r="M715">
-        <v>0</v>
-      </c>
       <c r="N715">
-        <v>4111</v>
+        <v>278</v>
       </c>
       <c r="O715">
-        <v>0</v>
+        <v>833</v>
       </c>
       <c r="P715">
-        <v>6666</v>
+        <v>1389</v>
       </c>
       <c r="Q715" t="s">
-        <v>151</v>
+        <v>129</v>
       </c>
     </row>
     <row r="716" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A716" t="s">
-        <v>59</v>
+        <v>89</v>
       </c>
       <c r="B716">
-        <v>-35.084850000000003</v>
+        <v>-35.6048446</v>
       </c>
       <c r="C716">
-        <v>137.74889999999999</v>
+        <v>138.59278499999999</v>
       </c>
       <c r="D716" s="2">
-        <v>46092</v>
-      </c>
-      <c r="E716" s="20">
-        <v>0.5625</v>
-      </c>
-      <c r="G716">
-        <v>0</v>
+        <v>46090</v>
       </c>
       <c r="I716">
         <v>56</v>
@@ -27345,117 +27345,165 @@
         <v>0</v>
       </c>
       <c r="L716">
-        <v>0</v>
+        <v>222</v>
       </c>
       <c r="N716">
         <v>389</v>
       </c>
+      <c r="O716">
+        <v>333</v>
+      </c>
       <c r="P716">
-        <v>445</v>
+        <v>1000</v>
       </c>
       <c r="Q716" t="s">
-        <v>149</v>
+        <v>129</v>
       </c>
     </row>
     <row r="717" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A717" t="s">
-        <v>391</v>
+        <v>363</v>
       </c>
       <c r="B717">
-        <v>-34.842409000000004</v>
+        <v>-35.878667100000001</v>
       </c>
       <c r="C717">
-        <v>138.50364999999999</v>
+        <v>137.6963188</v>
       </c>
       <c r="D717" s="2">
-        <v>46092</v>
+        <v>46091</v>
       </c>
       <c r="E717" s="20">
-        <v>0.71875</v>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F717">
+        <v>0</v>
       </c>
       <c r="G717">
-        <v>0.36</v>
+        <v>0</v>
       </c>
       <c r="H717">
-        <v>0.24</v>
+        <v>222</v>
       </c>
       <c r="I717">
-        <v>0.36</v>
+        <v>333</v>
       </c>
       <c r="J717">
-        <v>0</v>
+        <v>222</v>
+      </c>
+      <c r="K717">
+        <v>111</v>
       </c>
       <c r="L717">
-        <v>476.64</v>
+        <v>1889</v>
+      </c>
+      <c r="M717">
+        <v>0</v>
       </c>
       <c r="N717">
-        <v>3.24</v>
+        <v>4111</v>
       </c>
       <c r="O717">
-        <v>0.48</v>
+        <v>0</v>
       </c>
       <c r="P717">
-        <v>481.32</v>
+        <v>6666</v>
       </c>
       <c r="Q717" t="s">
-        <v>78</v>
+        <v>151</v>
       </c>
     </row>
     <row r="718" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A718" t="s">
-        <v>384</v>
+        <v>59</v>
       </c>
       <c r="B718">
-        <v>-34.759169999999997</v>
+        <v>-35.084850000000003</v>
       </c>
       <c r="C718">
-        <v>137.47612000000001</v>
+        <v>137.74889999999999</v>
       </c>
       <c r="D718" s="2">
         <v>46092</v>
       </c>
       <c r="E718" s="20">
-        <v>0.58333333333333337</v>
+        <v>0.5625</v>
+      </c>
+      <c r="G718">
+        <v>0</v>
+      </c>
+      <c r="I718">
+        <v>56</v>
       </c>
       <c r="J718">
-        <v>167</v>
+        <v>0</v>
+      </c>
+      <c r="L718">
+        <v>0</v>
+      </c>
+      <c r="N718">
+        <v>389</v>
+      </c>
+      <c r="P718">
+        <v>445</v>
       </c>
       <c r="Q718" t="s">
-        <v>267</v>
+        <v>149</v>
       </c>
     </row>
     <row r="719" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A719" t="s">
-        <v>356</v>
+        <v>391</v>
       </c>
       <c r="B719">
-        <v>-34.672490000000003</v>
+        <v>-34.842409000000004</v>
       </c>
       <c r="C719">
-        <v>137.49295000000001</v>
+        <v>138.50364999999999</v>
       </c>
       <c r="D719" s="2">
         <v>46092</v>
       </c>
       <c r="E719" s="20">
-        <v>0.54166666666666663</v>
+        <v>0.71875</v>
+      </c>
+      <c r="G719">
+        <v>0.36</v>
+      </c>
+      <c r="H719">
+        <v>0.24</v>
+      </c>
+      <c r="I719">
+        <v>0.36</v>
       </c>
       <c r="J719">
         <v>0</v>
       </c>
+      <c r="L719">
+        <v>476.64</v>
+      </c>
+      <c r="N719">
+        <v>3.24</v>
+      </c>
+      <c r="O719">
+        <v>0.48</v>
+      </c>
+      <c r="P719">
+        <v>481.32</v>
+      </c>
       <c r="Q719" t="s">
-        <v>267</v>
+        <v>78</v>
       </c>
     </row>
     <row r="720" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A720" t="s">
-        <v>59</v>
+        <v>384</v>
       </c>
       <c r="B720">
-        <v>-35.084850000000003</v>
+        <v>-34.759169999999997</v>
       </c>
       <c r="C720">
-        <v>137.74889999999999</v>
+        <v>137.47612000000001</v>
       </c>
       <c r="D720" s="2">
         <v>46092</v>
@@ -27463,310 +27511,274 @@
       <c r="E720" s="20">
         <v>0.58333333333333337</v>
       </c>
-      <c r="G720">
-        <v>0</v>
-      </c>
-      <c r="I720">
-        <v>56</v>
-      </c>
       <c r="J720">
-        <v>0</v>
-      </c>
-      <c r="L720">
-        <v>0</v>
-      </c>
-      <c r="N720">
-        <v>333</v>
-      </c>
-      <c r="P720">
-        <v>389</v>
+        <v>167</v>
       </c>
       <c r="Q720" t="s">
-        <v>149</v>
+        <v>267</v>
       </c>
     </row>
     <row r="721" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A721" t="s">
-        <v>394</v>
+        <v>356</v>
       </c>
       <c r="B721">
-        <v>-35.786641000000003</v>
+        <v>-34.672490000000003</v>
       </c>
       <c r="C721">
-        <v>138.07153940000001</v>
+        <v>137.49295000000001</v>
       </c>
       <c r="D721" s="2">
-        <v>46094</v>
+        <v>46092</v>
       </c>
       <c r="E721" s="20">
-        <v>0.58333333333333337</v>
-      </c>
-      <c r="F721">
-        <v>0</v>
-      </c>
-      <c r="G721">
-        <v>0</v>
-      </c>
-      <c r="H721">
-        <v>0</v>
-      </c>
-      <c r="I721">
-        <v>0</v>
+        <v>0.54166666666666663</v>
       </c>
       <c r="J721">
         <v>0</v>
       </c>
-      <c r="K721">
-        <v>0</v>
-      </c>
-      <c r="L721">
-        <v>1889</v>
-      </c>
-      <c r="M721">
-        <v>0</v>
-      </c>
-      <c r="N721">
-        <v>2000</v>
-      </c>
-      <c r="O721">
-        <v>111</v>
-      </c>
-      <c r="P721">
-        <v>4000</v>
-      </c>
       <c r="Q721" t="s">
-        <v>151</v>
+        <v>267</v>
       </c>
     </row>
     <row r="722" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A722" t="s">
-        <v>222</v>
+        <v>59</v>
       </c>
       <c r="B722">
-        <v>-35.638145999999999</v>
+        <v>-35.084850000000003</v>
       </c>
       <c r="C722">
-        <v>137.6249325</v>
+        <v>137.74889999999999</v>
       </c>
       <c r="D722" s="2">
-        <v>46095</v>
+        <v>46092</v>
       </c>
       <c r="E722" s="20">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="F722">
-        <v>0</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="G722">
         <v>0</v>
       </c>
-      <c r="H722">
+      <c r="I722">
+        <v>56</v>
+      </c>
+      <c r="J722">
+        <v>0</v>
+      </c>
+      <c r="L722">
+        <v>0</v>
+      </c>
+      <c r="N722">
         <v>333</v>
       </c>
-      <c r="I722">
-        <v>444</v>
-      </c>
-      <c r="J722">
-        <v>0</v>
-      </c>
-      <c r="K722">
-        <v>444</v>
-      </c>
-      <c r="L722">
-        <v>11222</v>
-      </c>
-      <c r="M722">
-        <v>333</v>
-      </c>
-      <c r="N722">
-        <v>4111</v>
-      </c>
-      <c r="O722">
-        <v>0</v>
-      </c>
       <c r="P722">
-        <v>16887</v>
+        <v>389</v>
       </c>
       <c r="Q722" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="723" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A723" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B723">
-        <v>-35.532783000000002</v>
+        <v>-35.786641000000003</v>
       </c>
       <c r="C723">
-        <v>138.68868499999999</v>
+        <v>138.07153940000001</v>
       </c>
       <c r="D723" s="2">
-        <v>46096</v>
+        <v>46094</v>
       </c>
       <c r="E723" s="20">
-        <v>0.45833333333333331</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="F723">
+        <v>0</v>
+      </c>
+      <c r="G723">
+        <v>0</v>
+      </c>
+      <c r="H723">
+        <v>0</v>
       </c>
       <c r="I723">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="J723">
         <v>0</v>
       </c>
+      <c r="K723">
+        <v>0</v>
+      </c>
       <c r="L723">
-        <v>13.574999999999999</v>
+        <v>1889</v>
+      </c>
+      <c r="M723">
+        <v>0</v>
       </c>
       <c r="N723">
-        <v>0.75</v>
+        <v>2000</v>
+      </c>
+      <c r="O723">
+        <v>111</v>
       </c>
       <c r="P723">
-        <v>14.625</v>
+        <v>4000</v>
       </c>
       <c r="Q723" t="s">
-        <v>78</v>
+        <v>151</v>
       </c>
     </row>
     <row r="724" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A724" t="s">
-        <v>92</v>
+        <v>222</v>
       </c>
       <c r="B724">
-        <v>-35.632150000000003</v>
+        <v>-35.638145999999999</v>
       </c>
       <c r="C724">
-        <v>138.48339999999999</v>
+        <v>137.6249325</v>
       </c>
       <c r="D724" s="2">
-        <v>46096</v>
+        <v>46095</v>
       </c>
       <c r="E724" s="20">
-        <v>0.52083333333333337</v>
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="F724">
+        <v>0</v>
       </c>
       <c r="G724">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="H724">
-        <v>0.1</v>
+        <v>333</v>
       </c>
       <c r="I724">
-        <v>1.6</v>
+        <v>444</v>
       </c>
       <c r="J724">
         <v>0</v>
       </c>
+      <c r="K724">
+        <v>444</v>
+      </c>
       <c r="L724">
-        <v>18.600000000000001</v>
+        <v>11222</v>
+      </c>
+      <c r="M724">
+        <v>333</v>
+      </c>
+      <c r="N724">
+        <v>4111</v>
       </c>
       <c r="O724">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="P724">
-        <v>20.550000000000004</v>
+        <v>16887</v>
       </c>
       <c r="Q724" t="s">
-        <v>78</v>
+        <v>151</v>
       </c>
     </row>
     <row r="725" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A725" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="B725">
-        <v>-35.521971999999998</v>
+        <v>-35.532783000000002</v>
       </c>
       <c r="C725">
-        <v>138.18543600000001</v>
+        <v>138.68868499999999</v>
       </c>
       <c r="D725" s="2">
         <v>46096</v>
       </c>
       <c r="E725" s="20">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="F725">
-        <v>0</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="I725">
-        <v>167</v>
+        <v>0.3</v>
       </c>
       <c r="J725">
         <v>0</v>
       </c>
       <c r="L725">
-        <v>222</v>
+        <v>13.574999999999999</v>
       </c>
       <c r="N725">
-        <v>278</v>
-      </c>
-      <c r="O725">
-        <v>722</v>
+        <v>0.75</v>
       </c>
       <c r="P725">
-        <v>1389</v>
+        <v>14.625</v>
       </c>
       <c r="Q725" t="s">
-        <v>253</v>
+        <v>78</v>
       </c>
     </row>
     <row r="726" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A726" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B726">
-        <v>-35.540277000000003</v>
+        <v>-35.632150000000003</v>
       </c>
       <c r="C726">
-        <v>138.66416599999999</v>
+        <v>138.48339999999999</v>
       </c>
       <c r="D726" s="2">
         <v>46096</v>
       </c>
+      <c r="E726" s="20">
+        <v>0.52083333333333337</v>
+      </c>
       <c r="G726">
-        <v>167</v>
+        <v>0.15</v>
       </c>
       <c r="H726">
-        <v>167</v>
+        <v>0.1</v>
       </c>
       <c r="I726">
-        <v>222</v>
+        <v>1.6</v>
       </c>
       <c r="J726">
         <v>0</v>
       </c>
       <c r="L726">
-        <v>1500</v>
-      </c>
-      <c r="N726">
-        <v>222</v>
+        <v>18.600000000000001</v>
       </c>
       <c r="O726">
-        <v>389</v>
+        <v>0.1</v>
       </c>
       <c r="P726">
-        <v>2667</v>
+        <v>20.550000000000004</v>
       </c>
       <c r="Q726" t="s">
-        <v>129</v>
+        <v>78</v>
       </c>
     </row>
     <row r="727" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A727" t="s">
-        <v>100</v>
+        <v>395</v>
       </c>
       <c r="B727">
-        <v>-35.536745000000003</v>
+        <v>-35.521971999999998</v>
       </c>
       <c r="C727">
-        <v>138.6913744</v>
+        <v>138.18543600000001</v>
       </c>
       <c r="D727" s="2">
         <v>46096</v>
       </c>
-      <c r="G727">
-        <v>56</v>
-      </c>
-      <c r="H727">
-        <v>167</v>
+      <c r="E727" s="20">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="F727">
+        <v>0</v>
       </c>
       <c r="I727">
         <v>167</v>
@@ -27775,54 +27787,57 @@
         <v>0</v>
       </c>
       <c r="L727">
-        <v>2721</v>
+        <v>222</v>
+      </c>
+      <c r="N727">
+        <v>278</v>
       </c>
       <c r="O727">
-        <v>3555</v>
+        <v>722</v>
       </c>
       <c r="P727">
-        <v>6666</v>
+        <v>1389</v>
       </c>
       <c r="Q727" t="s">
-        <v>129</v>
+        <v>253</v>
       </c>
     </row>
     <row r="728" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A728" t="s">
-        <v>398</v>
+        <v>86</v>
       </c>
       <c r="B728">
-        <v>-35.557299999999998</v>
+        <v>-35.540277000000003</v>
       </c>
       <c r="C728">
-        <v>138.66200000000001</v>
+        <v>138.66416599999999</v>
       </c>
       <c r="D728" s="2">
         <v>46096</v>
       </c>
       <c r="G728">
-        <v>222</v>
+        <v>167</v>
       </c>
       <c r="H728">
         <v>167</v>
       </c>
       <c r="I728">
-        <v>446</v>
+        <v>222</v>
       </c>
       <c r="J728">
         <v>0</v>
       </c>
       <c r="L728">
-        <v>833</v>
+        <v>1500</v>
       </c>
       <c r="N728">
-        <v>556</v>
+        <v>222</v>
       </c>
       <c r="O728">
-        <v>1111</v>
+        <v>389</v>
       </c>
       <c r="P728">
-        <v>3335</v>
+        <v>2667</v>
       </c>
       <c r="Q728" t="s">
         <v>129</v>
@@ -27830,13 +27845,13 @@
     </row>
     <row r="729" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A729" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="B729">
-        <v>-35.573300000000003</v>
+        <v>-35.536745000000003</v>
       </c>
       <c r="C729">
-        <v>138.64250000000001</v>
+        <v>138.6913744</v>
       </c>
       <c r="D729" s="2">
         <v>46096</v>
@@ -27845,22 +27860,22 @@
         <v>56</v>
       </c>
       <c r="H729">
-        <v>56</v>
+        <v>167</v>
       </c>
       <c r="I729">
-        <v>556</v>
+        <v>167</v>
       </c>
       <c r="J729">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="L729">
-        <v>2167</v>
+        <v>2721</v>
       </c>
       <c r="O729">
-        <v>7056</v>
+        <v>3555</v>
       </c>
       <c r="P729">
-        <v>9891</v>
+        <v>6666</v>
       </c>
       <c r="Q729" t="s">
         <v>129</v>
@@ -27868,40 +27883,40 @@
     </row>
     <row r="730" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A730" t="s">
-        <v>88</v>
+        <v>398</v>
       </c>
       <c r="B730">
-        <v>-35.581124000000003</v>
+        <v>-35.557299999999998</v>
       </c>
       <c r="C730">
-        <v>138.60879700000001</v>
+        <v>138.66200000000001</v>
       </c>
       <c r="D730" s="2">
         <v>46096</v>
       </c>
       <c r="G730">
-        <v>111</v>
+        <v>222</v>
       </c>
       <c r="H730">
-        <v>56</v>
+        <v>167</v>
       </c>
       <c r="I730">
-        <v>56</v>
+        <v>446</v>
       </c>
       <c r="J730">
         <v>0</v>
       </c>
       <c r="L730">
-        <v>222</v>
+        <v>833</v>
       </c>
       <c r="N730">
-        <v>111</v>
+        <v>556</v>
       </c>
       <c r="O730">
-        <v>333</v>
+        <v>1111</v>
       </c>
       <c r="P730">
-        <v>889</v>
+        <v>3335</v>
       </c>
       <c r="Q730" t="s">
         <v>129</v>
@@ -27909,37 +27924,37 @@
     </row>
     <row r="731" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A731" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B731">
-        <v>-35.6048446</v>
+        <v>-35.573300000000003</v>
       </c>
       <c r="C731">
-        <v>138.59278499999999</v>
+        <v>138.64250000000001</v>
       </c>
       <c r="D731" s="2">
         <v>46096</v>
       </c>
+      <c r="G731">
+        <v>56</v>
+      </c>
       <c r="H731">
-        <v>389</v>
+        <v>56</v>
       </c>
       <c r="I731">
-        <v>222</v>
+        <v>556</v>
       </c>
       <c r="J731">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="L731">
-        <v>111</v>
-      </c>
-      <c r="N731">
-        <v>500</v>
+        <v>2167</v>
       </c>
       <c r="O731">
-        <v>1111</v>
+        <v>7056</v>
       </c>
       <c r="P731">
-        <v>2333</v>
+        <v>9891</v>
       </c>
       <c r="Q731" t="s">
         <v>129</v>
@@ -27947,17 +27962,20 @@
     </row>
     <row r="732" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A732" t="s">
-        <v>378</v>
+        <v>88</v>
       </c>
       <c r="B732">
-        <v>-35.612285999999997</v>
+        <v>-35.581124000000003</v>
       </c>
       <c r="C732">
-        <v>138.564302</v>
+        <v>138.60879700000001</v>
       </c>
       <c r="D732" s="2">
         <v>46096</v>
       </c>
+      <c r="G732">
+        <v>111</v>
+      </c>
       <c r="H732">
         <v>56</v>
       </c>
@@ -27968,16 +27986,16 @@
         <v>0</v>
       </c>
       <c r="L732">
+        <v>222</v>
+      </c>
+      <c r="N732">
+        <v>111</v>
+      </c>
+      <c r="O732">
         <v>333</v>
       </c>
-      <c r="N732">
-        <v>222</v>
-      </c>
-      <c r="O732">
-        <v>389</v>
-      </c>
       <c r="P732">
-        <v>1056</v>
+        <v>889</v>
       </c>
       <c r="Q732" t="s">
         <v>129</v>
@@ -27985,34 +28003,37 @@
     </row>
     <row r="733" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A733" t="s">
-        <v>301</v>
+        <v>89</v>
       </c>
       <c r="B733">
-        <v>-35.61</v>
+        <v>-35.6048446</v>
       </c>
       <c r="C733">
-        <v>138.5925</v>
+        <v>138.59278499999999</v>
       </c>
       <c r="D733" s="2">
         <v>46096</v>
       </c>
+      <c r="H733">
+        <v>389</v>
+      </c>
       <c r="I733">
-        <v>444</v>
+        <v>222</v>
       </c>
       <c r="J733">
         <v>0</v>
       </c>
       <c r="L733">
-        <v>278</v>
+        <v>111</v>
       </c>
       <c r="N733">
-        <v>167</v>
+        <v>500</v>
       </c>
       <c r="O733">
-        <v>612</v>
+        <v>1111</v>
       </c>
       <c r="P733">
-        <v>1501</v>
+        <v>2333</v>
       </c>
       <c r="Q733" t="s">
         <v>129</v>
@@ -28020,162 +28041,165 @@
     </row>
     <row r="734" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A734" t="s">
-        <v>392</v>
+        <v>378</v>
       </c>
       <c r="B734">
-        <v>-34.958151000000001</v>
+        <v>-35.612285999999997</v>
       </c>
       <c r="C734">
-        <v>138.503987</v>
+        <v>138.564302</v>
       </c>
       <c r="D734" s="2">
-        <v>46097</v>
-      </c>
-      <c r="E734" s="20">
-        <v>0.36458333333333331</v>
+        <v>46096</v>
+      </c>
+      <c r="H734">
+        <v>56</v>
       </c>
       <c r="I734">
-        <v>26.46</v>
+        <v>56</v>
       </c>
       <c r="J734">
         <v>0</v>
       </c>
       <c r="L734">
-        <v>0.96</v>
+        <v>333</v>
       </c>
       <c r="N734">
-        <v>0.12</v>
+        <v>222</v>
+      </c>
+      <c r="O734">
+        <v>389</v>
       </c>
       <c r="P734">
-        <v>27.540000000000003</v>
+        <v>1056</v>
       </c>
       <c r="Q734" t="s">
-        <v>78</v>
+        <v>129</v>
       </c>
     </row>
     <row r="735" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A735" t="s">
-        <v>352</v>
+        <v>301</v>
       </c>
       <c r="B735">
-        <v>-34.860666999999999</v>
+        <v>-35.61</v>
       </c>
       <c r="C735">
-        <v>138.490938</v>
+        <v>138.5925</v>
       </c>
       <c r="D735" s="2">
-        <v>46097</v>
-      </c>
-      <c r="E735" s="20">
-        <v>0.35416666666666669</v>
+        <v>46096</v>
       </c>
       <c r="I735">
-        <v>0.45</v>
+        <v>444</v>
       </c>
       <c r="J735">
         <v>0</v>
       </c>
       <c r="L735">
-        <v>186.3</v>
+        <v>278</v>
       </c>
       <c r="N735">
-        <v>0.15</v>
+        <v>167</v>
       </c>
       <c r="O735">
-        <v>0.3</v>
+        <v>612</v>
       </c>
       <c r="P735">
-        <v>187.20000000000002</v>
+        <v>1501</v>
       </c>
       <c r="Q735" t="s">
-        <v>78</v>
+        <v>129</v>
       </c>
     </row>
     <row r="736" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A736" t="s">
-        <v>315</v>
+        <v>392</v>
       </c>
       <c r="B736">
-        <v>-35.445188000000002</v>
+        <v>-34.958151000000001</v>
       </c>
       <c r="C736">
-        <v>138.307266</v>
+        <v>138.503987</v>
       </c>
       <c r="D736" s="2">
         <v>46097</v>
       </c>
       <c r="E736" s="20">
-        <v>0.375</v>
+        <v>0.36458333333333331</v>
       </c>
       <c r="I736">
-        <v>111</v>
+        <v>26.46</v>
       </c>
       <c r="J736">
         <v>0</v>
       </c>
       <c r="L736">
-        <v>167</v>
+        <v>0.96</v>
       </c>
       <c r="N736">
-        <v>167</v>
-      </c>
-      <c r="O736">
-        <v>1611</v>
+        <v>0.12</v>
       </c>
       <c r="P736">
-        <v>2056</v>
+        <v>27.540000000000003</v>
       </c>
       <c r="Q736" t="s">
-        <v>353</v>
+        <v>78</v>
       </c>
     </row>
     <row r="737" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A737" t="s">
-        <v>384</v>
+        <v>352</v>
       </c>
       <c r="B737">
-        <v>-34.759169999999997</v>
+        <v>-34.860666999999999</v>
       </c>
       <c r="C737">
-        <v>137.47612000000001</v>
+        <v>138.490938</v>
       </c>
       <c r="D737" s="2">
         <v>46097</v>
       </c>
       <c r="E737" s="20">
-        <v>0.58333333333333337</v>
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="I737">
+        <v>0.45</v>
       </c>
       <c r="J737">
         <v>0</v>
       </c>
+      <c r="L737">
+        <v>186.3</v>
+      </c>
+      <c r="N737">
+        <v>0.15</v>
+      </c>
+      <c r="O737">
+        <v>0.3</v>
+      </c>
+      <c r="P737">
+        <v>187.20000000000002</v>
+      </c>
       <c r="Q737" t="s">
-        <v>267</v>
+        <v>78</v>
       </c>
     </row>
     <row r="738" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A738" t="s">
-        <v>390</v>
+        <v>315</v>
       </c>
       <c r="B738">
-        <v>-35.739091000000002</v>
+        <v>-35.445188000000002</v>
       </c>
       <c r="C738">
-        <v>137.67788400000001</v>
+        <v>138.307266</v>
       </c>
       <c r="D738" s="2">
-        <v>46098</v>
+        <v>46097</v>
       </c>
       <c r="E738" s="20">
-        <v>17.3</v>
-      </c>
-      <c r="F738">
-        <v>0</v>
-      </c>
-      <c r="G738">
-        <v>0</v>
-      </c>
-      <c r="H738">
-        <v>0</v>
+        <v>0.375</v>
       </c>
       <c r="I738">
         <v>111</v>
@@ -28183,145 +28207,169 @@
       <c r="J738">
         <v>0</v>
       </c>
-      <c r="K738">
-        <v>111</v>
-      </c>
       <c r="L738">
-        <v>3778</v>
-      </c>
-      <c r="M738">
-        <v>111</v>
+        <v>167</v>
       </c>
       <c r="N738">
-        <v>2000</v>
+        <v>167</v>
       </c>
       <c r="O738">
-        <v>222</v>
+        <v>1611</v>
       </c>
       <c r="P738">
-        <v>6333</v>
+        <v>2056</v>
       </c>
       <c r="Q738" t="s">
-        <v>151</v>
+        <v>353</v>
       </c>
     </row>
     <row r="739" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A739" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="B739">
-        <v>-35.853555700000001</v>
+        <v>-34.759169999999997</v>
       </c>
       <c r="C739">
-        <v>137.74248499999999</v>
+        <v>137.47612000000001</v>
       </c>
       <c r="D739" s="2">
-        <v>46098</v>
+        <v>46097</v>
       </c>
       <c r="E739" s="20">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F739">
-        <v>0</v>
-      </c>
-      <c r="G739">
-        <v>0</v>
-      </c>
-      <c r="H739">
-        <v>0</v>
-      </c>
-      <c r="I739">
-        <v>0</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="J739">
         <v>0</v>
       </c>
-      <c r="K739">
-        <v>0</v>
-      </c>
-      <c r="L739">
-        <v>222</v>
-      </c>
-      <c r="M739">
-        <v>0</v>
-      </c>
-      <c r="N739">
-        <v>0</v>
-      </c>
-      <c r="O739">
-        <v>0</v>
-      </c>
-      <c r="P739">
-        <v>222</v>
-      </c>
       <c r="Q739" t="s">
-        <v>151</v>
+        <v>267</v>
       </c>
     </row>
     <row r="740" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A740" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="B740">
-        <v>-34.323770000000003</v>
+        <v>-35.739091000000002</v>
       </c>
       <c r="C740">
-        <v>137.49154999999999</v>
+        <v>137.67788400000001</v>
       </c>
       <c r="D740" s="2">
         <v>46098</v>
       </c>
       <c r="E740" s="20">
-        <v>0.69444444444444442</v>
+        <v>17.3</v>
+      </c>
+      <c r="F740">
+        <v>0</v>
+      </c>
+      <c r="G740">
+        <v>0</v>
+      </c>
+      <c r="H740">
+        <v>0</v>
+      </c>
+      <c r="I740">
+        <v>111</v>
       </c>
       <c r="J740">
         <v>0</v>
       </c>
+      <c r="K740">
+        <v>111</v>
+      </c>
+      <c r="L740">
+        <v>3778</v>
+      </c>
+      <c r="M740">
+        <v>111</v>
+      </c>
+      <c r="N740">
+        <v>2000</v>
+      </c>
+      <c r="O740">
+        <v>222</v>
+      </c>
+      <c r="P740">
+        <v>6333</v>
+      </c>
       <c r="Q740" t="s">
-        <v>267</v>
+        <v>151</v>
       </c>
     </row>
     <row r="741" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A741" t="s">
-        <v>360</v>
+        <v>379</v>
       </c>
       <c r="B741">
-        <v>-34.494970000000002</v>
+        <v>-35.853555700000001</v>
       </c>
       <c r="C741">
-        <v>137.48038</v>
+        <v>137.74248499999999</v>
       </c>
       <c r="D741" s="2">
         <v>46098</v>
       </c>
       <c r="E741" s="20">
-        <v>0.54861111111111116</v>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F741">
+        <v>0</v>
+      </c>
+      <c r="G741">
+        <v>0</v>
+      </c>
+      <c r="H741">
+        <v>0</v>
+      </c>
+      <c r="I741">
+        <v>0</v>
       </c>
       <c r="J741">
         <v>0</v>
       </c>
+      <c r="K741">
+        <v>0</v>
+      </c>
+      <c r="L741">
+        <v>222</v>
+      </c>
+      <c r="M741">
+        <v>0</v>
+      </c>
+      <c r="N741">
+        <v>0</v>
+      </c>
+      <c r="O741">
+        <v>0</v>
+      </c>
+      <c r="P741">
+        <v>222</v>
+      </c>
       <c r="Q741" t="s">
-        <v>267</v>
+        <v>151</v>
       </c>
     </row>
     <row r="742" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A742" t="s">
-        <v>304</v>
+        <v>396</v>
       </c>
       <c r="B742">
-        <v>-34.899749999999997</v>
+        <v>-34.323770000000003</v>
       </c>
       <c r="C742">
-        <v>137.45174</v>
+        <v>137.49154999999999</v>
       </c>
       <c r="D742" s="2">
         <v>46098</v>
       </c>
       <c r="E742" s="20">
-        <v>0.6875</v>
+        <v>0.69444444444444442</v>
       </c>
       <c r="J742">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="Q742" t="s">
         <v>267</v>
@@ -28329,28 +28377,22 @@
     </row>
     <row r="743" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A743" t="s">
-        <v>401</v>
+        <v>360</v>
       </c>
       <c r="B743">
-        <v>-34.075042000000003</v>
+        <v>-34.494970000000002</v>
       </c>
       <c r="C743">
-        <v>137.54297600000001</v>
+        <v>137.48038</v>
       </c>
       <c r="D743" s="2">
         <v>46098</v>
       </c>
+      <c r="E743" s="20">
+        <v>0.54861111111111116</v>
+      </c>
       <c r="J743">
         <v>0</v>
-      </c>
-      <c r="L743">
-        <v>111</v>
-      </c>
-      <c r="O743">
-        <v>56</v>
-      </c>
-      <c r="P743">
-        <v>167</v>
       </c>
       <c r="Q743" t="s">
         <v>267</v>
@@ -28358,308 +28400,290 @@
     </row>
     <row r="744" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A744" t="s">
-        <v>230</v>
+        <v>304</v>
       </c>
       <c r="B744">
-        <v>-35.081918000000002</v>
+        <v>-34.899749999999997</v>
       </c>
       <c r="C744">
-        <v>137.74822499999999</v>
+        <v>137.45174</v>
       </c>
       <c r="D744" s="2">
-        <v>46099</v>
+        <v>46098</v>
       </c>
       <c r="E744" s="20">
-        <v>0.82291666666666663</v>
-      </c>
-      <c r="I744">
+        <v>0.6875</v>
+      </c>
+      <c r="J744">
         <v>111</v>
       </c>
-      <c r="J744">
-        <v>0</v>
-      </c>
-      <c r="L744">
-        <v>500</v>
-      </c>
-      <c r="N744">
-        <v>556</v>
-      </c>
-      <c r="O744">
-        <v>222</v>
-      </c>
-      <c r="P744">
-        <v>1389</v>
-      </c>
       <c r="Q744" t="s">
-        <v>219</v>
+        <v>267</v>
       </c>
     </row>
     <row r="745" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A745" t="s">
-        <v>230</v>
+        <v>401</v>
       </c>
       <c r="B745">
-        <v>-35.081918000000002</v>
+        <v>-34.075042000000003</v>
       </c>
       <c r="C745">
-        <v>137.74822499999999</v>
+        <v>137.54297600000001</v>
       </c>
       <c r="D745" s="2">
-        <v>46099</v>
-      </c>
-      <c r="E745" s="20">
-        <v>0.82291666666666663</v>
-      </c>
-      <c r="I745">
+        <v>46098</v>
+      </c>
+      <c r="J745">
+        <v>0</v>
+      </c>
+      <c r="L745">
         <v>111</v>
       </c>
-      <c r="J745">
-        <v>0</v>
-      </c>
-      <c r="L745">
-        <v>500</v>
-      </c>
-      <c r="N745">
-        <v>556</v>
-      </c>
       <c r="O745">
-        <v>222</v>
+        <v>56</v>
       </c>
       <c r="P745">
-        <v>1389</v>
+        <v>167</v>
       </c>
       <c r="Q745" t="s">
-        <v>219</v>
+        <v>267</v>
       </c>
     </row>
     <row r="746" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A746" t="s">
-        <v>377</v>
+        <v>230</v>
       </c>
       <c r="B746">
-        <v>-34.902070808541197</v>
+        <v>-35.081918000000002</v>
       </c>
       <c r="C746">
-        <v>137.79925776072</v>
+        <v>137.74822499999999</v>
       </c>
       <c r="D746" s="2">
-        <v>46101</v>
+        <v>46099</v>
       </c>
       <c r="E746" s="20">
-        <v>0.71527777777777779</v>
+        <v>0.82291666666666663</v>
       </c>
       <c r="I746">
-        <v>333</v>
+        <v>111</v>
       </c>
       <c r="J746">
         <v>0</v>
       </c>
       <c r="L746">
-        <v>56</v>
+        <v>500</v>
+      </c>
+      <c r="N746">
+        <v>556</v>
       </c>
       <c r="O746">
-        <v>111</v>
+        <v>222</v>
       </c>
       <c r="P746">
-        <v>500</v>
+        <v>1389</v>
       </c>
       <c r="Q746" t="s">
-        <v>368</v>
+        <v>219</v>
       </c>
     </row>
     <row r="747" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A747" t="s">
-        <v>379</v>
+        <v>230</v>
       </c>
       <c r="B747">
-        <v>-35.853555700000001</v>
+        <v>-35.081918000000002</v>
       </c>
       <c r="C747">
-        <v>137.74248499999999</v>
+        <v>137.74822499999999</v>
       </c>
       <c r="D747" s="2">
-        <v>46101</v>
+        <v>46099</v>
       </c>
       <c r="E747" s="20">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="F747">
-        <v>0</v>
-      </c>
-      <c r="G747">
-        <v>0</v>
-      </c>
-      <c r="H747">
-        <v>0</v>
+        <v>0.82291666666666663</v>
       </c>
       <c r="I747">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="J747">
         <v>0</v>
       </c>
-      <c r="K747">
+      <c r="L747">
+        <v>500</v>
+      </c>
+      <c r="N747">
+        <v>556</v>
+      </c>
+      <c r="O747">
         <v>222</v>
       </c>
-      <c r="L747">
-        <v>333</v>
-      </c>
-      <c r="M747">
-        <v>0</v>
-      </c>
-      <c r="N747">
-        <v>0</v>
-      </c>
-      <c r="O747">
-        <v>0</v>
-      </c>
       <c r="P747">
-        <v>555</v>
+        <v>1389</v>
       </c>
       <c r="Q747" t="s">
-        <v>399</v>
+        <v>219</v>
       </c>
     </row>
     <row r="748" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A748" t="s">
-        <v>304</v>
+        <v>377</v>
       </c>
       <c r="B748">
-        <v>-34.899749999999997</v>
+        <v>-34.902070808541197</v>
       </c>
       <c r="C748">
-        <v>137.45174</v>
+        <v>137.79925776072</v>
       </c>
       <c r="D748" s="2">
         <v>46101</v>
       </c>
       <c r="E748" s="20">
-        <v>0.65625</v>
+        <v>0.71527777777777779</v>
+      </c>
+      <c r="I748">
+        <v>333</v>
       </c>
       <c r="J748">
+        <v>0</v>
+      </c>
+      <c r="L748">
+        <v>56</v>
+      </c>
+      <c r="O748">
         <v>111</v>
       </c>
+      <c r="P748">
+        <v>500</v>
+      </c>
       <c r="Q748" t="s">
-        <v>267</v>
+        <v>368</v>
       </c>
     </row>
     <row r="749" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A749" t="s">
-        <v>356</v>
+        <v>379</v>
       </c>
       <c r="B749">
-        <v>-34.672499999999999</v>
+        <v>-35.853555700000001</v>
       </c>
       <c r="C749">
-        <v>137.49298999999999</v>
+        <v>137.74248499999999</v>
       </c>
       <c r="D749" s="2">
-        <v>46102</v>
+        <v>46101</v>
+      </c>
+      <c r="E749" s="20">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="F749">
+        <v>0</v>
+      </c>
+      <c r="G749">
+        <v>0</v>
+      </c>
+      <c r="H749">
+        <v>0</v>
+      </c>
+      <c r="I749">
+        <v>0</v>
       </c>
       <c r="J749">
         <v>0</v>
       </c>
+      <c r="K749">
+        <v>222</v>
+      </c>
+      <c r="L749">
+        <v>333</v>
+      </c>
+      <c r="M749">
+        <v>0</v>
+      </c>
+      <c r="N749">
+        <v>0</v>
+      </c>
+      <c r="O749">
+        <v>0</v>
+      </c>
+      <c r="P749">
+        <v>555</v>
+      </c>
       <c r="Q749" t="s">
-        <v>267</v>
+        <v>399</v>
       </c>
     </row>
     <row r="750" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A750" t="s">
-        <v>79</v>
+        <v>304</v>
       </c>
       <c r="B750">
-        <v>-34.804662999999998</v>
+        <v>-34.899749999999997</v>
       </c>
       <c r="C750">
-        <v>138.540223</v>
+        <v>137.45174</v>
       </c>
       <c r="D750" s="2">
-        <v>46102</v>
+        <v>46101</v>
       </c>
       <c r="E750" s="20">
-        <v>0.47916666666666669</v>
-      </c>
-      <c r="I750">
-        <v>9.3000000000000007</v>
+        <v>0.65625</v>
       </c>
       <c r="J750">
-        <v>0</v>
-      </c>
-      <c r="L750">
-        <v>43.35</v>
-      </c>
-      <c r="P750">
-        <v>52.650000000000006</v>
+        <v>111</v>
       </c>
       <c r="Q750" t="s">
-        <v>78</v>
+        <v>267</v>
       </c>
     </row>
     <row r="751" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A751" t="s">
-        <v>85</v>
+        <v>356</v>
       </c>
       <c r="B751">
-        <v>-34.873964000000001</v>
+        <v>-34.672499999999999</v>
       </c>
       <c r="C751">
-        <v>138.488134</v>
+        <v>137.49298999999999</v>
       </c>
       <c r="D751" s="2">
         <v>46102</v>
       </c>
-      <c r="E751" s="20">
-        <v>0.45347222222222222</v>
-      </c>
-      <c r="I751">
-        <v>5.85</v>
-      </c>
       <c r="J751">
         <v>0</v>
       </c>
-      <c r="L751">
-        <v>14.7</v>
-      </c>
-      <c r="O751">
-        <v>6.75</v>
-      </c>
-      <c r="P751">
-        <v>27.299999999999997</v>
-      </c>
       <c r="Q751" t="s">
-        <v>78</v>
+        <v>267</v>
       </c>
     </row>
     <row r="752" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A752" t="s">
-        <v>269</v>
+        <v>79</v>
       </c>
       <c r="B752">
-        <v>-34.824044999999998</v>
+        <v>-34.804662999999998</v>
       </c>
       <c r="C752">
-        <v>138.48377600000001</v>
+        <v>138.540223</v>
       </c>
       <c r="D752" s="2">
         <v>46102</v>
       </c>
       <c r="E752" s="20">
-        <v>0.46180555555555558</v>
-      </c>
-      <c r="G752">
-        <v>0.1</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="I752">
-        <v>3.5</v>
+        <v>9.3000000000000007</v>
       </c>
       <c r="J752">
         <v>0</v>
       </c>
       <c r="L752">
-        <v>11.8</v>
+        <v>43.35</v>
       </c>
       <c r="P752">
-        <v>15.4</v>
+        <v>52.650000000000006</v>
       </c>
       <c r="Q752" t="s">
         <v>78</v>
@@ -28667,34 +28691,34 @@
     </row>
     <row r="753" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A753" t="s">
-        <v>392</v>
+        <v>85</v>
       </c>
       <c r="B753">
-        <v>-34.958151000000001</v>
+        <v>-34.873964000000001</v>
       </c>
       <c r="C753">
-        <v>138.503987</v>
+        <v>138.488134</v>
       </c>
       <c r="D753" s="2">
         <v>46102</v>
       </c>
       <c r="E753" s="20">
-        <v>0.43402777777777779</v>
-      </c>
-      <c r="H753">
-        <v>0.3</v>
+        <v>0.45347222222222222</v>
       </c>
       <c r="I753">
-        <v>1.65</v>
+        <v>5.85</v>
       </c>
       <c r="J753">
         <v>0</v>
       </c>
       <c r="L753">
-        <v>35.424999999999997</v>
+        <v>14.7</v>
+      </c>
+      <c r="O753">
+        <v>6.75</v>
       </c>
       <c r="P753">
-        <v>37.375</v>
+        <v>27.299999999999997</v>
       </c>
       <c r="Q753" t="s">
         <v>78</v>
@@ -28702,31 +28726,34 @@
     </row>
     <row r="754" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A754" t="s">
-        <v>179</v>
+        <v>269</v>
       </c>
       <c r="B754">
-        <v>-35.078539999999997</v>
+        <v>-34.824044999999998</v>
       </c>
       <c r="C754">
-        <v>138.49587</v>
+        <v>138.48377600000001</v>
       </c>
       <c r="D754" s="2">
         <v>46102</v>
       </c>
       <c r="E754" s="20">
-        <v>0.41666666666666669</v>
+        <v>0.46180555555555558</v>
+      </c>
+      <c r="G754">
+        <v>0.1</v>
       </c>
       <c r="I754">
-        <v>0.1</v>
+        <v>3.5</v>
       </c>
       <c r="J754">
         <v>0</v>
       </c>
       <c r="L754">
-        <v>2.2999999999999998</v>
+        <v>11.8</v>
       </c>
       <c r="P754">
-        <v>2.4</v>
+        <v>15.4</v>
       </c>
       <c r="Q754" t="s">
         <v>78</v>
@@ -28734,195 +28761,186 @@
     </row>
     <row r="755" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A755" t="s">
-        <v>210</v>
+        <v>392</v>
       </c>
       <c r="B755">
-        <v>-35.739091000000002</v>
+        <v>-34.958151000000001</v>
       </c>
       <c r="C755">
-        <v>137.67788400000001</v>
+        <v>138.503987</v>
       </c>
       <c r="D755" s="2">
-        <v>46103</v>
+        <v>46102</v>
       </c>
       <c r="E755" s="20">
-        <v>0.6875</v>
-      </c>
-      <c r="F755">
-        <v>0</v>
-      </c>
-      <c r="G755">
-        <v>0</v>
+        <v>0.43402777777777779</v>
       </c>
       <c r="H755">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="I755">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="J755">
         <v>0</v>
       </c>
-      <c r="K755">
-        <v>111</v>
-      </c>
       <c r="L755">
-        <v>0</v>
-      </c>
-      <c r="M755">
-        <v>555</v>
-      </c>
-      <c r="N755">
-        <v>0</v>
-      </c>
-      <c r="O755">
-        <v>0</v>
+        <v>35.424999999999997</v>
       </c>
       <c r="P755">
-        <v>666</v>
+        <v>37.375</v>
       </c>
       <c r="Q755" t="s">
-        <v>399</v>
+        <v>78</v>
       </c>
     </row>
     <row r="756" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A756" t="s">
-        <v>402</v>
+        <v>179</v>
       </c>
       <c r="B756">
-        <v>-34.903120000000001</v>
+        <v>-35.078539999999997</v>
       </c>
       <c r="C756">
-        <v>137.44969</v>
+        <v>138.49587</v>
       </c>
       <c r="D756" s="2">
-        <v>46103</v>
+        <v>46102</v>
       </c>
       <c r="E756" s="20">
-        <v>0.62847222222222221</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="I756">
-        <v>444</v>
+        <v>0.1</v>
       </c>
       <c r="J756">
         <v>0</v>
       </c>
       <c r="L756">
-        <v>56</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="P756">
-        <v>500</v>
+        <v>2.4</v>
       </c>
       <c r="Q756" t="s">
-        <v>267</v>
+        <v>78</v>
       </c>
     </row>
     <row r="757" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A757" t="s">
-        <v>231</v>
+        <v>210</v>
       </c>
       <c r="B757">
-        <v>-35.054707999999998</v>
+        <v>-35.739091000000002</v>
       </c>
       <c r="C757">
-        <v>137.725145</v>
+        <v>137.67788400000001</v>
       </c>
       <c r="D757" s="2">
         <v>46103</v>
       </c>
       <c r="E757" s="20">
-        <v>0.63541666666666663</v>
+        <v>0.6875</v>
+      </c>
+      <c r="F757">
+        <v>0</v>
+      </c>
+      <c r="G757">
+        <v>0</v>
+      </c>
+      <c r="H757">
+        <v>0</v>
       </c>
       <c r="I757">
-        <v>66500</v>
+        <v>0</v>
       </c>
       <c r="J757">
-        <v>56</v>
+        <v>0</v>
+      </c>
+      <c r="K757">
+        <v>111</v>
       </c>
       <c r="L757">
-        <v>3000</v>
+        <v>0</v>
+      </c>
+      <c r="M757">
+        <v>555</v>
+      </c>
+      <c r="N757">
+        <v>0</v>
       </c>
       <c r="O757">
-        <v>667</v>
+        <v>0</v>
       </c>
       <c r="P757">
-        <v>70167</v>
+        <v>666</v>
       </c>
       <c r="Q757" t="s">
-        <v>219</v>
+        <v>399</v>
       </c>
     </row>
     <row r="758" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A758" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B758">
-        <v>-34.903466000000002</v>
+        <v>-34.903120000000001</v>
       </c>
       <c r="C758">
-        <v>137.79804799999999</v>
+        <v>137.44969</v>
       </c>
       <c r="D758" s="2">
         <v>46103</v>
       </c>
       <c r="E758" s="20">
-        <v>0.70833333333333337</v>
+        <v>0.62847222222222221</v>
       </c>
       <c r="I758">
-        <v>389</v>
+        <v>444</v>
       </c>
       <c r="J758">
         <v>0</v>
       </c>
       <c r="L758">
+        <v>56</v>
+      </c>
+      <c r="P758">
         <v>500</v>
       </c>
-      <c r="N758">
-        <v>389</v>
-      </c>
-      <c r="O758">
-        <v>56</v>
-      </c>
-      <c r="P758">
-        <v>1333</v>
-      </c>
       <c r="Q758" t="s">
-        <v>219</v>
+        <v>267</v>
       </c>
     </row>
     <row r="759" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A759" t="s">
-        <v>404</v>
+        <v>231</v>
       </c>
       <c r="B759">
-        <v>-34.765996000000001</v>
+        <v>-35.054707999999998</v>
       </c>
       <c r="C759">
-        <v>137.86211299999999</v>
+        <v>137.725145</v>
       </c>
       <c r="D759" s="2">
         <v>46103</v>
       </c>
       <c r="E759" s="20">
-        <v>0.67708333333333337</v>
+        <v>0.63541666666666663</v>
       </c>
       <c r="I759">
-        <v>0</v>
+        <v>66500</v>
       </c>
       <c r="J759">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="L759">
-        <v>222</v>
-      </c>
-      <c r="N759">
-        <v>389</v>
+        <v>3000</v>
       </c>
       <c r="O759">
-        <v>56</v>
+        <v>667</v>
       </c>
       <c r="P759">
-        <v>667</v>
+        <v>70167</v>
       </c>
       <c r="Q759" t="s">
         <v>219</v>
@@ -28930,210 +28948,219 @@
     </row>
     <row r="760" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A760" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B760">
-        <v>-35.510620000000003</v>
+        <v>-34.903466000000002</v>
       </c>
       <c r="C760">
-        <v>138.21679599999999</v>
+        <v>137.79804799999999</v>
       </c>
       <c r="D760" s="2">
         <v>46103</v>
       </c>
+      <c r="E760" s="20">
+        <v>0.70833333333333337</v>
+      </c>
       <c r="I760">
-        <v>167</v>
+        <v>389</v>
       </c>
       <c r="J760">
         <v>0</v>
       </c>
       <c r="L760">
+        <v>500</v>
+      </c>
+      <c r="N760">
+        <v>389</v>
+      </c>
+      <c r="O760">
         <v>56</v>
       </c>
-      <c r="N760">
-        <v>1389</v>
-      </c>
-      <c r="O760">
-        <v>722</v>
-      </c>
       <c r="P760">
-        <v>2334</v>
+        <v>1333</v>
       </c>
       <c r="Q760" t="s">
-        <v>253</v>
+        <v>219</v>
       </c>
     </row>
     <row r="761" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A761" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="B761">
-        <v>-35.793973000000001</v>
+        <v>-34.765996000000001</v>
       </c>
       <c r="C761">
-        <v>137.852418</v>
+        <v>137.86211299999999</v>
       </c>
       <c r="D761" s="2">
-        <v>46104</v>
+        <v>46103</v>
       </c>
       <c r="E761" s="20">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="F761">
-        <v>0</v>
-      </c>
-      <c r="G761">
-        <v>0</v>
-      </c>
-      <c r="H761">
-        <v>1333</v>
+        <v>0.67708333333333337</v>
       </c>
       <c r="I761">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="J761">
         <v>0</v>
       </c>
-      <c r="K761">
-        <v>0</v>
-      </c>
       <c r="L761">
-        <v>3778</v>
-      </c>
-      <c r="M761">
-        <v>333</v>
+        <v>222</v>
       </c>
       <c r="N761">
-        <v>333</v>
+        <v>389</v>
       </c>
       <c r="O761">
-        <v>556</v>
+        <v>56</v>
       </c>
       <c r="P761">
-        <v>7333</v>
+        <v>667</v>
       </c>
       <c r="Q761" t="s">
-        <v>399</v>
+        <v>219</v>
       </c>
     </row>
     <row r="762" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A762" t="s">
-        <v>363</v>
+        <v>405</v>
       </c>
       <c r="B762">
-        <v>-35.878667100000001</v>
+        <v>-35.510620000000003</v>
       </c>
       <c r="C762">
-        <v>137.6963188</v>
+        <v>138.21679599999999</v>
       </c>
       <c r="D762" s="2">
-        <v>46104</v>
-      </c>
-      <c r="E762" s="20">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F762">
-        <v>0</v>
-      </c>
-      <c r="G762">
-        <v>0</v>
-      </c>
-      <c r="H762">
-        <v>0</v>
+        <v>46103</v>
       </c>
       <c r="I762">
-        <v>0</v>
+        <v>167</v>
       </c>
       <c r="J762">
         <v>0</v>
       </c>
-      <c r="K762">
-        <v>0</v>
-      </c>
       <c r="L762">
-        <v>0</v>
-      </c>
-      <c r="M762">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="N762">
-        <v>0</v>
+        <v>1389</v>
       </c>
       <c r="O762">
-        <v>0</v>
+        <v>722</v>
       </c>
       <c r="P762">
-        <v>0</v>
+        <v>2334</v>
       </c>
       <c r="Q762" t="s">
-        <v>399</v>
+        <v>253</v>
       </c>
     </row>
     <row r="763" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A763" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
       <c r="B763">
-        <v>-35.445188000000002</v>
+        <v>-35.793973000000001</v>
       </c>
       <c r="C763">
-        <v>138.307266</v>
+        <v>137.852418</v>
       </c>
       <c r="D763" s="2">
         <v>46104</v>
       </c>
+      <c r="E763" s="20">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="F763">
+        <v>0</v>
+      </c>
+      <c r="G763">
+        <v>0</v>
+      </c>
+      <c r="H763">
+        <v>1333</v>
+      </c>
       <c r="I763">
-        <v>111</v>
+        <v>1000</v>
       </c>
       <c r="J763">
         <v>0</v>
       </c>
+      <c r="K763">
+        <v>0</v>
+      </c>
       <c r="L763">
-        <v>0</v>
+        <v>3778</v>
+      </c>
+      <c r="M763">
+        <v>333</v>
       </c>
       <c r="N763">
-        <v>167</v>
+        <v>333</v>
       </c>
       <c r="O763">
-        <v>1444</v>
+        <v>556</v>
       </c>
       <c r="P763">
-        <v>1722</v>
+        <v>7333</v>
       </c>
       <c r="Q763" t="s">
-        <v>406</v>
+        <v>399</v>
       </c>
     </row>
     <row r="764" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A764" t="s">
-        <v>384</v>
+        <v>363</v>
       </c>
       <c r="B764">
-        <v>-34.759169999999997</v>
+        <v>-35.878667100000001</v>
       </c>
       <c r="C764">
-        <v>137.47612000000001</v>
+        <v>137.6963188</v>
       </c>
       <c r="D764" s="2">
         <v>46104</v>
       </c>
       <c r="E764" s="20">
-        <v>0.58333333333333337</v>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F764">
+        <v>0</v>
+      </c>
+      <c r="G764">
+        <v>0</v>
+      </c>
+      <c r="H764">
+        <v>0</v>
       </c>
       <c r="I764">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="J764">
         <v>0</v>
       </c>
+      <c r="K764">
+        <v>0</v>
+      </c>
       <c r="L764">
-        <v>56</v>
+        <v>0</v>
+      </c>
+      <c r="M764">
+        <v>0</v>
+      </c>
+      <c r="N764">
+        <v>0</v>
+      </c>
+      <c r="O764">
+        <v>0</v>
       </c>
       <c r="P764">
-        <v>167</v>
+        <v>0</v>
       </c>
       <c r="Q764" t="s">
-        <v>267</v>
+        <v>399</v>
       </c>
     </row>
     <row r="765" spans="1:17" x14ac:dyDescent="0.3">
@@ -29141,34 +29168,31 @@
         <v>315</v>
       </c>
       <c r="B765">
-        <v>-35.445186</v>
+        <v>-35.445188000000002</v>
       </c>
       <c r="C765">
-        <v>138.307424</v>
+        <v>138.307266</v>
       </c>
       <c r="D765" s="2">
         <v>46104</v>
       </c>
-      <c r="E765" s="20">
-        <v>0.38541666666666669</v>
-      </c>
       <c r="I765">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="J765">
         <v>0</v>
       </c>
       <c r="L765">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="N765">
-        <v>56</v>
+        <v>167</v>
       </c>
       <c r="O765">
-        <v>778</v>
+        <v>1444</v>
       </c>
       <c r="P765">
-        <v>890</v>
+        <v>1722</v>
       </c>
       <c r="Q765" t="s">
         <v>406</v>
@@ -29176,34 +29200,31 @@
     </row>
     <row r="766" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A766" t="s">
-        <v>356</v>
+        <v>384</v>
       </c>
       <c r="B766">
-        <v>-34.672499999999999</v>
+        <v>-34.759169999999997</v>
       </c>
       <c r="C766">
-        <v>137.49298999999999</v>
+        <v>137.47612000000001</v>
       </c>
       <c r="D766" s="2">
-        <v>46106</v>
+        <v>46104</v>
       </c>
       <c r="E766" s="20">
-        <v>0.57291666666666663</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="I766">
+        <v>111</v>
+      </c>
+      <c r="J766">
+        <v>0</v>
+      </c>
+      <c r="L766">
         <v>56</v>
       </c>
-      <c r="J766">
-        <v>0</v>
-      </c>
-      <c r="L766">
-        <v>111</v>
-      </c>
-      <c r="O766">
-        <v>56</v>
-      </c>
       <c r="P766">
-        <v>223</v>
+        <v>167</v>
       </c>
       <c r="Q766" t="s">
         <v>267</v>
@@ -29211,284 +29232,299 @@
     </row>
     <row r="767" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A767" t="s">
-        <v>352</v>
+        <v>315</v>
       </c>
       <c r="B767">
-        <v>-34.860666999999999</v>
+        <v>-35.445186</v>
       </c>
       <c r="C767">
-        <v>138.490938</v>
+        <v>138.307424</v>
       </c>
       <c r="D767" s="2">
-        <v>46108</v>
+        <v>46104</v>
       </c>
       <c r="E767" s="20">
-        <v>0.46180555555555558</v>
+        <v>0.38541666666666669</v>
       </c>
       <c r="I767">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="J767">
         <v>0</v>
       </c>
       <c r="L767">
-        <v>5.625</v>
-      </c>
-      <c r="M767">
-        <v>0.15</v>
+        <v>56</v>
       </c>
       <c r="N767">
-        <v>7.4999999999999997E-2</v>
+        <v>56</v>
       </c>
       <c r="O767">
-        <v>0.15</v>
+        <v>778</v>
       </c>
       <c r="P767">
-        <v>8.4</v>
+        <v>890</v>
       </c>
       <c r="Q767" t="s">
-        <v>78</v>
+        <v>406</v>
       </c>
     </row>
     <row r="768" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A768" t="s">
-        <v>85</v>
+        <v>356</v>
       </c>
       <c r="B768">
-        <v>-34.873964000000001</v>
+        <v>-34.672499999999999</v>
       </c>
       <c r="C768">
-        <v>138.488134</v>
+        <v>137.49298999999999</v>
       </c>
       <c r="D768" s="2">
-        <v>46108</v>
+        <v>46106</v>
       </c>
       <c r="E768" s="20">
-        <v>0.45833333333333331</v>
+        <v>0.57291666666666663</v>
       </c>
       <c r="I768">
-        <v>3.9</v>
+        <v>56</v>
       </c>
       <c r="J768">
         <v>0</v>
       </c>
       <c r="L768">
-        <v>10.199999999999999</v>
+        <v>111</v>
       </c>
       <c r="O768">
-        <v>0.22500000000000001</v>
+        <v>56</v>
       </c>
       <c r="P768">
-        <v>14.324999999999999</v>
+        <v>223</v>
       </c>
       <c r="Q768" t="s">
-        <v>78</v>
+        <v>267</v>
       </c>
     </row>
     <row r="769" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A769" t="s">
-        <v>79</v>
+        <v>411</v>
       </c>
       <c r="B769">
-        <v>-34.804662999999998</v>
+        <v>-35.557499999999997</v>
       </c>
       <c r="C769">
-        <v>138.540223</v>
+        <v>138.62200000000001</v>
       </c>
       <c r="D769" s="2">
-        <v>46108</v>
-      </c>
-      <c r="E769" s="20">
-        <v>0.49305555555555558</v>
+        <v>46106</v>
+      </c>
+      <c r="G769">
+        <v>56</v>
+      </c>
+      <c r="H769">
+        <v>56</v>
       </c>
       <c r="I769">
-        <v>2.25</v>
+        <v>556</v>
       </c>
       <c r="J769">
         <v>0</v>
       </c>
       <c r="L769">
-        <v>37.950000000000003</v>
+        <v>2111</v>
+      </c>
+      <c r="N769">
+        <v>444</v>
+      </c>
+      <c r="O769">
+        <v>2667</v>
       </c>
       <c r="P769">
-        <v>40.200000000000003</v>
+        <v>5890</v>
       </c>
       <c r="Q769" t="s">
-        <v>78</v>
+        <v>129</v>
       </c>
     </row>
     <row r="770" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A770" t="s">
-        <v>269</v>
+        <v>352</v>
       </c>
       <c r="B770">
-        <v>-34.824044999999998</v>
+        <v>-34.860666999999999</v>
       </c>
       <c r="C770">
-        <v>138.48377600000001</v>
+        <v>138.490938</v>
       </c>
       <c r="D770" s="2">
         <v>46108</v>
       </c>
       <c r="E770" s="20">
-        <v>0.47569444444444442</v>
-      </c>
-      <c r="G770">
-        <v>0.3</v>
-      </c>
-      <c r="H770">
-        <v>0.05</v>
+        <v>0.46180555555555558</v>
       </c>
       <c r="I770">
-        <v>1.1499999999999999</v>
+        <v>2.4</v>
       </c>
       <c r="J770">
         <v>0</v>
       </c>
       <c r="L770">
-        <v>8.25</v>
+        <v>5.625</v>
+      </c>
+      <c r="M770">
+        <v>0.15</v>
+      </c>
+      <c r="N770">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="O770">
+        <v>0.15</v>
       </c>
       <c r="P770">
-        <v>9.75</v>
+        <v>8.4</v>
       </c>
       <c r="Q770" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="771" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A771" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="B771" s="1">
-        <v>-35.516800000000003</v>
-      </c>
-      <c r="C771" s="1">
-        <v>138.73820000000001</v>
+      <c r="A771" t="s">
+        <v>85</v>
+      </c>
+      <c r="B771">
+        <v>-34.873964000000001</v>
+      </c>
+      <c r="C771">
+        <v>138.488134</v>
       </c>
       <c r="D771" s="2">
-        <v>46109</v>
+        <v>46108</v>
       </c>
       <c r="E771" s="20">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="F771" s="1"/>
-      <c r="G771" s="1"/>
-      <c r="H771" s="1"/>
-      <c r="I771" s="1">
-        <v>111</v>
-      </c>
-      <c r="J771" s="1">
-        <v>0</v>
-      </c>
-      <c r="K771" s="1"/>
-      <c r="L771" s="1">
-        <v>611</v>
-      </c>
-      <c r="M771" s="1"/>
-      <c r="N771" s="1"/>
-      <c r="O771" s="1"/>
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="I771">
+        <v>3.9</v>
+      </c>
+      <c r="J771">
+        <v>0</v>
+      </c>
+      <c r="L771">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="O771">
+        <v>0.22500000000000001</v>
+      </c>
       <c r="P771">
-        <f>SUM(F771:I771,K771:O771)</f>
-        <v>722</v>
+        <v>14.324999999999999</v>
       </c>
       <c r="Q771" t="s">
-        <v>187</v>
+        <v>78</v>
       </c>
     </row>
     <row r="772" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A772" t="s">
-        <v>188</v>
+        <v>79</v>
       </c>
       <c r="B772">
-        <v>-35.515900000000002</v>
+        <v>-34.804662999999998</v>
       </c>
       <c r="C772">
-        <v>138.70529999999999</v>
+        <v>138.540223</v>
       </c>
       <c r="D772" s="2">
-        <v>46109</v>
+        <v>46108</v>
       </c>
       <c r="E772" s="20">
-        <v>0.42708333333333331</v>
+        <v>0.49305555555555558</v>
       </c>
       <c r="I772">
-        <v>56</v>
+        <v>2.25</v>
       </c>
       <c r="J772">
         <v>0</v>
       </c>
       <c r="L772">
-        <v>111</v>
+        <v>37.950000000000003</v>
       </c>
       <c r="P772">
-        <f>SUM(F772:I772,K772:O772)</f>
-        <v>167</v>
+        <v>40.200000000000003</v>
       </c>
       <c r="Q772" t="s">
-        <v>187</v>
+        <v>78</v>
       </c>
     </row>
     <row r="773" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A773" t="s">
-        <v>91</v>
+        <v>269</v>
       </c>
       <c r="B773">
-        <v>-35.536299999999997</v>
+        <v>-34.824044999999998</v>
       </c>
       <c r="C773">
-        <v>138.67859999999999</v>
+        <v>138.48377600000001</v>
       </c>
       <c r="D773" s="2">
-        <v>46109</v>
+        <v>46108</v>
       </c>
       <c r="E773" s="20">
-        <v>0.4375</v>
+        <v>0.47569444444444442</v>
+      </c>
+      <c r="G773">
+        <v>0.3</v>
+      </c>
+      <c r="H773">
+        <v>0.05</v>
       </c>
       <c r="I773">
-        <v>222</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="J773">
         <v>0</v>
       </c>
       <c r="L773">
-        <v>56</v>
+        <v>8.25</v>
       </c>
       <c r="P773">
-        <f>SUM(F773:I773,K773:O773)</f>
-        <v>278</v>
+        <v>9.75</v>
       </c>
       <c r="Q773" t="s">
-        <v>187</v>
+        <v>78</v>
       </c>
     </row>
     <row r="774" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A774" t="s">
-        <v>186</v>
-      </c>
-      <c r="B774">
-        <v>-35.538600000000002</v>
-      </c>
-      <c r="C774">
-        <v>138.6497</v>
+      <c r="A774" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="B774" s="1">
+        <v>-35.516800000000003</v>
+      </c>
+      <c r="C774" s="1">
+        <v>138.73820000000001</v>
       </c>
       <c r="D774" s="2">
         <v>46109</v>
       </c>
       <c r="E774" s="20">
-        <v>0.44791666666666669</v>
-      </c>
-      <c r="I774">
-        <v>56</v>
-      </c>
-      <c r="J774">
-        <v>0</v>
-      </c>
-      <c r="L774">
-        <v>56</v>
-      </c>
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="F774" s="1"/>
+      <c r="G774" s="1"/>
+      <c r="H774" s="1"/>
+      <c r="I774" s="1">
+        <v>111</v>
+      </c>
+      <c r="J774" s="1">
+        <v>0</v>
+      </c>
+      <c r="K774" s="1"/>
+      <c r="L774" s="1">
+        <v>611</v>
+      </c>
+      <c r="M774" s="1"/>
+      <c r="N774" s="1"/>
+      <c r="O774" s="1"/>
       <c r="P774">
-        <f>SUM(F774:I774,K774:O774)</f>
-        <v>112</v>
+        <f t="shared" ref="P774:P785" si="1">SUM(F774:I774,K774:O774)</f>
+        <v>722</v>
       </c>
       <c r="Q774" t="s">
         <v>187</v>
@@ -29496,32 +29532,32 @@
     </row>
     <row r="775" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A775" t="s">
-        <v>318</v>
+        <v>188</v>
       </c>
       <c r="B775">
-        <v>-35.5565</v>
+        <v>-35.515900000000002</v>
       </c>
       <c r="C775">
-        <v>138.62610000000001</v>
+        <v>138.70529999999999</v>
       </c>
       <c r="D775" s="2">
         <v>46109</v>
       </c>
       <c r="E775" s="20">
-        <v>0.4826388888888889</v>
+        <v>0.42708333333333331</v>
       </c>
       <c r="I775">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="J775">
         <v>0</v>
       </c>
       <c r="L775">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="P775">
-        <f>SUM(F775:I775,K775:O775)</f>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>167</v>
       </c>
       <c r="Q775" t="s">
         <v>187</v>
@@ -29529,19 +29565,19 @@
     </row>
     <row r="776" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A776" t="s">
-        <v>189</v>
+        <v>91</v>
       </c>
       <c r="B776">
-        <v>-35.5565</v>
+        <v>-35.536299999999997</v>
       </c>
       <c r="C776">
-        <v>138.62610000000001</v>
+        <v>138.67859999999999</v>
       </c>
       <c r="D776" s="2">
         <v>46109</v>
       </c>
       <c r="E776" s="20">
-        <v>0.46527777777777779</v>
+        <v>0.4375</v>
       </c>
       <c r="I776">
         <v>222</v>
@@ -29553,7 +29589,7 @@
         <v>56</v>
       </c>
       <c r="P776">
-        <f>SUM(F776:I776,K776:O776)</f>
+        <f t="shared" si="1"/>
         <v>278</v>
       </c>
       <c r="Q776" t="s">
@@ -29562,32 +29598,32 @@
     </row>
     <row r="777" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A777" t="s">
-        <v>320</v>
+        <v>186</v>
       </c>
       <c r="B777">
-        <v>-35.634900000000002</v>
+        <v>-35.538600000000002</v>
       </c>
       <c r="C777">
-        <v>138.49850000000001</v>
+        <v>138.6497</v>
       </c>
       <c r="D777" s="2">
         <v>46109</v>
       </c>
       <c r="E777" s="20">
-        <v>0.4861111111111111</v>
+        <v>0.44791666666666669</v>
       </c>
       <c r="I777">
-        <v>278</v>
+        <v>56</v>
       </c>
       <c r="J777">
         <v>0</v>
       </c>
       <c r="L777">
-        <v>167</v>
+        <v>56</v>
       </c>
       <c r="P777">
-        <f>SUM(F777:I777,K777:O777)</f>
-        <v>445</v>
+        <f t="shared" si="1"/>
+        <v>112</v>
       </c>
       <c r="Q777" t="s">
         <v>187</v>
@@ -29595,22 +29631,22 @@
     </row>
     <row r="778" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A778" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B778">
-        <v>-35.563899999999997</v>
+        <v>-35.5565</v>
       </c>
       <c r="C778">
-        <v>138.6131</v>
+        <v>138.62610000000001</v>
       </c>
       <c r="D778" s="2">
         <v>46109</v>
       </c>
       <c r="E778" s="20">
-        <v>0.50347222222222221</v>
+        <v>0.4826388888888889</v>
       </c>
       <c r="I778">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="J778">
         <v>0</v>
@@ -29619,8 +29655,8 @@
         <v>0</v>
       </c>
       <c r="P778">
-        <f>SUM(F778:I778,K778:O778)</f>
-        <v>56</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="Q778" t="s">
         <v>187</v>
@@ -29628,22 +29664,22 @@
     </row>
     <row r="779" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A779" t="s">
-        <v>407</v>
+        <v>189</v>
       </c>
       <c r="B779">
-        <v>-35.548499999999997</v>
+        <v>-35.5565</v>
       </c>
       <c r="C779">
-        <v>138.62710000000001</v>
+        <v>138.62610000000001</v>
       </c>
       <c r="D779" s="2">
         <v>46109</v>
       </c>
       <c r="E779" s="20">
-        <v>0.47222222222222221</v>
+        <v>0.46527777777777779</v>
       </c>
       <c r="I779">
-        <v>0</v>
+        <v>222</v>
       </c>
       <c r="J779">
         <v>0</v>
@@ -29652,8 +29688,8 @@
         <v>56</v>
       </c>
       <c r="P779">
-        <f>SUM(F779:I779,K779:O779)</f>
-        <v>56</v>
+        <f t="shared" si="1"/>
+        <v>278</v>
       </c>
       <c r="Q779" t="s">
         <v>187</v>
@@ -29661,32 +29697,32 @@
     </row>
     <row r="780" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A780" t="s">
-        <v>408</v>
+        <v>320</v>
       </c>
       <c r="B780">
-        <v>-35.5595</v>
+        <v>-35.634900000000002</v>
       </c>
       <c r="C780">
-        <v>138.6275</v>
+        <v>138.49850000000001</v>
       </c>
       <c r="D780" s="2">
         <v>46109</v>
       </c>
       <c r="E780" s="20">
-        <v>0.48958333333333331</v>
+        <v>0.4861111111111111</v>
       </c>
       <c r="I780">
-        <v>0</v>
+        <v>278</v>
       </c>
       <c r="J780">
         <v>0</v>
       </c>
       <c r="L780">
-        <v>56</v>
+        <v>167</v>
       </c>
       <c r="P780">
-        <f>SUM(F780:I780,K780:O780)</f>
-        <v>56</v>
+        <f t="shared" si="1"/>
+        <v>445</v>
       </c>
       <c r="Q780" t="s">
         <v>187</v>
@@ -29694,19 +29730,19 @@
     </row>
     <row r="781" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A781" t="s">
-        <v>409</v>
+        <v>319</v>
       </c>
       <c r="B781">
-        <v>-35.585299999999997</v>
+        <v>-35.563899999999997</v>
       </c>
       <c r="C781">
-        <v>138.5985</v>
+        <v>138.6131</v>
       </c>
       <c r="D781" s="2">
         <v>46109</v>
       </c>
       <c r="E781" s="20">
-        <v>0.51388888888888884</v>
+        <v>0.50347222222222221</v>
       </c>
       <c r="I781">
         <v>56</v>
@@ -29718,7 +29754,7 @@
         <v>0</v>
       </c>
       <c r="P781">
-        <f>SUM(F781:I781,K781:O781)</f>
+        <f t="shared" si="1"/>
         <v>56</v>
       </c>
       <c r="Q781" t="s">
@@ -29727,19 +29763,19 @@
     </row>
     <row r="782" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A782" t="s">
-        <v>86</v>
+        <v>407</v>
       </c>
       <c r="B782">
-        <v>-35.5413</v>
+        <v>-35.548499999999997</v>
       </c>
       <c r="C782">
-        <v>138.64080000000001</v>
+        <v>138.62710000000001</v>
       </c>
       <c r="D782" s="2">
         <v>46109</v>
       </c>
       <c r="E782" s="20">
-        <v>0.45833333333333331</v>
+        <v>0.47222222222222221</v>
       </c>
       <c r="I782">
         <v>0</v>
@@ -29748,11 +29784,11 @@
         <v>0</v>
       </c>
       <c r="L782">
-        <v>111</v>
+        <v>56</v>
       </c>
       <c r="P782">
-        <f>SUM(F782:I782,K782:O782)</f>
-        <v>111</v>
+        <f t="shared" si="1"/>
+        <v>56</v>
       </c>
       <c r="Q782" t="s">
         <v>187</v>
@@ -29760,304 +29796,262 @@
     </row>
     <row r="783" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A783" t="s">
-        <v>342</v>
+        <v>408</v>
       </c>
       <c r="B783">
-        <v>-35.500242</v>
+        <v>-35.5595</v>
       </c>
       <c r="C783">
-        <v>138.24491</v>
+        <v>138.6275</v>
       </c>
       <c r="D783" s="2">
         <v>46109</v>
       </c>
       <c r="E783" s="20">
-        <v>0.68055555555555547</v>
+        <v>0.48958333333333331</v>
       </c>
       <c r="I783">
-        <v>444</v>
+        <v>0</v>
       </c>
       <c r="J783">
         <v>0</v>
       </c>
       <c r="L783">
-        <v>2667</v>
-      </c>
-      <c r="N783">
-        <v>556</v>
-      </c>
-      <c r="O783">
-        <v>4889</v>
+        <v>56</v>
       </c>
       <c r="P783">
-        <v>8556</v>
+        <f t="shared" si="1"/>
+        <v>56</v>
       </c>
       <c r="Q783" t="s">
-        <v>253</v>
+        <v>187</v>
       </c>
     </row>
     <row r="784" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A784" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B784">
-        <v>-35.499946999999999</v>
+        <v>-35.585299999999997</v>
       </c>
       <c r="C784">
-        <v>138.242954</v>
+        <v>138.5985</v>
       </c>
       <c r="D784" s="2">
         <v>46109</v>
       </c>
       <c r="E784" s="20">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="H784">
-        <v>2222</v>
+        <v>0.51388888888888884</v>
       </c>
       <c r="I784">
-        <v>3333</v>
+        <v>56</v>
       </c>
       <c r="J784">
         <v>0</v>
       </c>
       <c r="L784">
-        <v>222</v>
-      </c>
-      <c r="N784">
-        <v>2556</v>
-      </c>
-      <c r="O784">
-        <v>444</v>
+        <v>0</v>
       </c>
       <c r="P784">
-        <v>8777</v>
+        <f t="shared" si="1"/>
+        <v>56</v>
       </c>
       <c r="Q784" t="s">
-        <v>253</v>
+        <v>187</v>
       </c>
     </row>
     <row r="785" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A785" t="s">
-        <v>400</v>
+        <v>86</v>
       </c>
       <c r="B785">
-        <v>-35.793973000000001</v>
+        <v>-35.5413</v>
       </c>
       <c r="C785">
-        <v>137.852418</v>
+        <v>138.64080000000001</v>
       </c>
       <c r="D785" s="2">
-        <v>46110</v>
+        <v>46109</v>
       </c>
       <c r="E785" s="20">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="F785">
-        <v>1222</v>
-      </c>
-      <c r="G785">
-        <v>667</v>
-      </c>
-      <c r="H785">
-        <v>1333</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="I785">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="J785">
         <v>0</v>
       </c>
-      <c r="K785">
-        <v>0</v>
-      </c>
       <c r="L785">
-        <v>3778</v>
-      </c>
-      <c r="M785">
-        <v>222</v>
-      </c>
-      <c r="N785">
-        <v>333</v>
-      </c>
-      <c r="O785">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="P785">
-        <v>8555</v>
+        <f t="shared" si="1"/>
+        <v>111</v>
       </c>
       <c r="Q785" t="s">
-        <v>399</v>
+        <v>187</v>
       </c>
     </row>
     <row r="786" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A786" t="s">
-        <v>210</v>
+        <v>342</v>
       </c>
       <c r="B786">
-        <v>-35.739091000000002</v>
+        <v>-35.500242</v>
       </c>
       <c r="C786">
-        <v>137.67788400000001</v>
+        <v>138.24491</v>
       </c>
       <c r="D786" s="2">
-        <v>46110</v>
+        <v>46109</v>
       </c>
       <c r="E786" s="20">
-        <v>0.4375</v>
-      </c>
-      <c r="F786">
-        <v>222</v>
-      </c>
-      <c r="G786">
-        <v>0</v>
-      </c>
-      <c r="H786">
-        <v>1333</v>
+        <v>0.68055555555555547</v>
       </c>
       <c r="I786">
-        <v>0</v>
+        <v>444</v>
       </c>
       <c r="J786">
         <v>0</v>
       </c>
-      <c r="K786">
-        <v>0</v>
-      </c>
       <c r="L786">
-        <v>5778</v>
-      </c>
-      <c r="M786">
-        <v>1444</v>
+        <v>2667</v>
       </c>
       <c r="N786">
-        <v>0</v>
+        <v>556</v>
       </c>
       <c r="O786">
-        <v>0</v>
+        <v>4889</v>
       </c>
       <c r="P786">
-        <v>8777</v>
+        <v>8556</v>
       </c>
       <c r="Q786" t="s">
-        <v>399</v>
+        <v>253</v>
       </c>
     </row>
     <row r="787" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A787" t="s">
-        <v>379</v>
+        <v>410</v>
       </c>
       <c r="B787">
-        <v>-35.853555700000001</v>
+        <v>-35.499946999999999</v>
       </c>
       <c r="C787">
-        <v>137.74248499999999</v>
+        <v>138.242954</v>
       </c>
       <c r="D787" s="2">
-        <v>46110</v>
+        <v>46109</v>
       </c>
       <c r="E787" s="20">
-        <v>0.39583333333333331</v>
-      </c>
-      <c r="F787">
-        <v>167</v>
-      </c>
-      <c r="G787">
-        <v>0</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="H787">
-        <v>4000</v>
+        <v>2222</v>
       </c>
       <c r="I787">
+        <v>3333</v>
+      </c>
+      <c r="J787">
+        <v>0</v>
+      </c>
+      <c r="L787">
+        <v>222</v>
+      </c>
+      <c r="N787">
+        <v>2556</v>
+      </c>
+      <c r="O787">
         <v>444</v>
       </c>
-      <c r="J787">
-        <v>0</v>
-      </c>
-      <c r="K787">
-        <v>0</v>
-      </c>
-      <c r="L787">
-        <v>1222</v>
-      </c>
-      <c r="M787">
-        <v>0</v>
-      </c>
-      <c r="N787">
-        <v>0</v>
-      </c>
-      <c r="O787">
-        <v>0</v>
-      </c>
       <c r="P787">
-        <v>5833</v>
+        <v>8777</v>
       </c>
       <c r="Q787" t="s">
-        <v>399</v>
+        <v>253</v>
       </c>
     </row>
     <row r="788" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A788" t="s">
-        <v>93</v>
+        <v>400</v>
       </c>
       <c r="B788">
-        <v>-35.514747999999997</v>
+        <v>-35.793973000000001</v>
       </c>
       <c r="C788">
-        <v>138.71989600000001</v>
+        <v>137.852418</v>
       </c>
       <c r="D788" s="2">
-        <v>46111</v>
+        <v>46110</v>
       </c>
       <c r="E788" s="20">
-        <v>0.375</v>
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="F788">
+        <v>1222</v>
+      </c>
+      <c r="G788">
+        <v>667</v>
+      </c>
+      <c r="H788">
+        <v>1333</v>
       </c>
       <c r="I788">
-        <v>0.9</v>
+        <v>1000</v>
       </c>
       <c r="J788">
         <v>0</v>
       </c>
+      <c r="K788">
+        <v>0</v>
+      </c>
       <c r="L788">
-        <v>111.6</v>
+        <v>3778</v>
+      </c>
+      <c r="M788">
+        <v>222</v>
+      </c>
+      <c r="N788">
+        <v>333</v>
       </c>
       <c r="O788">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="P788">
-        <v>112.6</v>
+        <v>8555</v>
       </c>
       <c r="Q788" t="s">
-        <v>78</v>
+        <v>399</v>
       </c>
     </row>
     <row r="789" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A789" t="s">
+        <v>210</v>
+      </c>
+      <c r="B789">
+        <v>-35.739091000000002</v>
+      </c>
+      <c r="C789">
+        <v>137.67788400000001</v>
+      </c>
+      <c r="D789" s="2">
+        <v>46110</v>
+      </c>
+      <c r="E789" s="20">
+        <v>0.4375</v>
+      </c>
+      <c r="F789">
         <v>222</v>
       </c>
-      <c r="B789">
-        <v>-35.638145999999999</v>
-      </c>
-      <c r="C789">
-        <v>137.6249325</v>
-      </c>
-      <c r="D789" s="2">
-        <v>46112</v>
-      </c>
-      <c r="E789" s="20">
-        <v>0.47916666666666669</v>
-      </c>
-      <c r="F789">
-        <v>0</v>
-      </c>
       <c r="G789">
-        <v>222</v>
+        <v>0</v>
       </c>
       <c r="H789">
-        <v>1556</v>
+        <v>1333</v>
       </c>
       <c r="I789">
-        <v>556</v>
+        <v>0</v>
       </c>
       <c r="J789">
         <v>0</v>
@@ -30066,19 +30060,19 @@
         <v>0</v>
       </c>
       <c r="L789">
-        <v>4889</v>
+        <v>5778</v>
       </c>
       <c r="M789">
-        <v>444</v>
+        <v>1444</v>
       </c>
       <c r="N789">
         <v>0</v>
       </c>
       <c r="O789">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="P789">
-        <v>7778</v>
+        <v>8777</v>
       </c>
       <c r="Q789" t="s">
         <v>399</v>
@@ -30086,48 +30080,919 @@
     </row>
     <row r="790" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A790" t="s">
+        <v>379</v>
+      </c>
+      <c r="B790">
+        <v>-35.853555700000001</v>
+      </c>
+      <c r="C790">
+        <v>137.74248499999999</v>
+      </c>
+      <c r="D790" s="2">
+        <v>46110</v>
+      </c>
+      <c r="E790" s="20">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="F790">
+        <v>167</v>
+      </c>
+      <c r="G790">
+        <v>0</v>
+      </c>
+      <c r="H790">
+        <v>4000</v>
+      </c>
+      <c r="I790">
+        <v>444</v>
+      </c>
+      <c r="J790">
+        <v>0</v>
+      </c>
+      <c r="K790">
+        <v>0</v>
+      </c>
+      <c r="L790">
+        <v>1222</v>
+      </c>
+      <c r="M790">
+        <v>0</v>
+      </c>
+      <c r="N790">
+        <v>0</v>
+      </c>
+      <c r="O790">
+        <v>0</v>
+      </c>
+      <c r="P790">
+        <v>5833</v>
+      </c>
+      <c r="Q790" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="791" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A791" t="s">
+        <v>414</v>
+      </c>
+      <c r="B791">
+        <v>-34.075042000000003</v>
+      </c>
+      <c r="C791">
+        <v>137.54297600000001</v>
+      </c>
+      <c r="D791" s="2">
+        <v>46110</v>
+      </c>
+      <c r="I791">
+        <v>306</v>
+      </c>
+      <c r="J791">
+        <v>28</v>
+      </c>
+      <c r="L791">
+        <v>1111</v>
+      </c>
+      <c r="N791">
+        <v>1556</v>
+      </c>
+      <c r="O791">
+        <v>167</v>
+      </c>
+      <c r="P791">
+        <v>3140</v>
+      </c>
+      <c r="Q791" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="792" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A792" t="s">
+        <v>93</v>
+      </c>
+      <c r="B792">
+        <v>-35.514747999999997</v>
+      </c>
+      <c r="C792">
+        <v>138.71989600000001</v>
+      </c>
+      <c r="D792" s="2">
+        <v>46111</v>
+      </c>
+      <c r="E792" s="20">
+        <v>0.375</v>
+      </c>
+      <c r="I792">
+        <v>0.9</v>
+      </c>
+      <c r="J792">
+        <v>0</v>
+      </c>
+      <c r="L792">
+        <v>111.6</v>
+      </c>
+      <c r="O792">
+        <v>0.1</v>
+      </c>
+      <c r="P792">
+        <v>112.6</v>
+      </c>
+      <c r="Q792" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="793" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A793" t="s">
+        <v>93</v>
+      </c>
+      <c r="B793">
+        <v>-35.514581999999997</v>
+      </c>
+      <c r="C793">
+        <v>138.71894700000001</v>
+      </c>
+      <c r="D793" s="2">
+        <v>46111</v>
+      </c>
+      <c r="E793" s="20">
+        <v>0.375</v>
+      </c>
+      <c r="I793">
+        <v>0.9</v>
+      </c>
+      <c r="J793">
+        <v>0</v>
+      </c>
+      <c r="L793">
+        <v>111.6</v>
+      </c>
+      <c r="O793">
+        <v>0.1</v>
+      </c>
+      <c r="P793">
+        <v>112.6</v>
+      </c>
+      <c r="Q793" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="794" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A794" t="s">
+        <v>222</v>
+      </c>
+      <c r="B794">
+        <v>-35.638145999999999</v>
+      </c>
+      <c r="C794">
+        <v>137.6249325</v>
+      </c>
+      <c r="D794" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E794" s="20">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="F794">
+        <v>0</v>
+      </c>
+      <c r="G794">
+        <v>222</v>
+      </c>
+      <c r="H794">
+        <v>1556</v>
+      </c>
+      <c r="I794">
+        <v>556</v>
+      </c>
+      <c r="J794">
+        <v>0</v>
+      </c>
+      <c r="K794">
+        <v>0</v>
+      </c>
+      <c r="L794">
+        <v>4889</v>
+      </c>
+      <c r="M794">
+        <v>444</v>
+      </c>
+      <c r="N794">
+        <v>0</v>
+      </c>
+      <c r="O794">
+        <v>111</v>
+      </c>
+      <c r="P794">
+        <v>7778</v>
+      </c>
+      <c r="Q794" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="795" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A795" t="s">
         <v>59</v>
       </c>
-      <c r="B790">
+      <c r="B795">
         <v>-35.084850000000003</v>
       </c>
-      <c r="C790">
+      <c r="C795">
         <v>137.74889999999999</v>
       </c>
-      <c r="D790" s="2">
+      <c r="D795" s="2">
         <v>46113</v>
       </c>
-      <c r="E790" s="20">
+      <c r="E795" s="20">
         <v>0.58333333333333337</v>
       </c>
-      <c r="G790">
-        <v>0</v>
-      </c>
-      <c r="I790">
+      <c r="G795">
+        <v>0</v>
+      </c>
+      <c r="I795">
         <v>56</v>
       </c>
-      <c r="J790">
-        <v>0</v>
-      </c>
-      <c r="L790">
+      <c r="J795">
+        <v>0</v>
+      </c>
+      <c r="L795">
         <v>222</v>
       </c>
-      <c r="M790">
+      <c r="M795">
         <v>111</v>
       </c>
-      <c r="N790">
+      <c r="N795">
         <v>777</v>
       </c>
-      <c r="P790">
+      <c r="P795">
         <v>1166</v>
       </c>
-      <c r="Q790" t="s">
+      <c r="Q795" t="s">
         <v>149</v>
       </c>
     </row>
+    <row r="796" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A796" t="s">
+        <v>412</v>
+      </c>
+      <c r="B796">
+        <v>-35.149287000000001</v>
+      </c>
+      <c r="C796">
+        <v>138.46426199999999</v>
+      </c>
+      <c r="D796" s="2">
+        <v>46114</v>
+      </c>
+      <c r="I796">
+        <v>0.187</v>
+      </c>
+      <c r="J796">
+        <v>0</v>
+      </c>
+      <c r="L796">
+        <v>1.8</v>
+      </c>
+      <c r="M796">
+        <v>3.7999999999999999E-2</v>
+      </c>
+      <c r="O796">
+        <v>0.113</v>
+      </c>
+      <c r="P796">
+        <v>2.1379999999999999</v>
+      </c>
+      <c r="Q796" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="797" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A797" t="s">
+        <v>413</v>
+      </c>
+      <c r="B797">
+        <v>-36.825802000000003</v>
+      </c>
+      <c r="C797">
+        <v>139.84628799999999</v>
+      </c>
+      <c r="D797" s="2">
+        <v>46115</v>
+      </c>
+      <c r="G797">
+        <v>0.2</v>
+      </c>
+      <c r="I797">
+        <v>1.6</v>
+      </c>
+      <c r="J797">
+        <v>0</v>
+      </c>
+      <c r="L797">
+        <v>480.83300000000003</v>
+      </c>
+      <c r="M797">
+        <v>0.1</v>
+      </c>
+      <c r="N797">
+        <v>0.6</v>
+      </c>
+      <c r="P797">
+        <v>483.33300000000008</v>
+      </c>
+      <c r="Q797" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="798" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A798" t="s">
+        <v>363</v>
+      </c>
+      <c r="B798">
+        <v>-35.878667100000001</v>
+      </c>
+      <c r="C798">
+        <v>137.6963188</v>
+      </c>
+      <c r="D798" s="2">
+        <v>46115</v>
+      </c>
+      <c r="E798" s="20">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F798">
+        <v>0</v>
+      </c>
+      <c r="G798">
+        <v>0</v>
+      </c>
+      <c r="H798">
+        <v>778</v>
+      </c>
+      <c r="I798">
+        <v>0</v>
+      </c>
+      <c r="J798">
+        <v>0</v>
+      </c>
+      <c r="K798">
+        <v>0</v>
+      </c>
+      <c r="L798">
+        <v>2333</v>
+      </c>
+      <c r="M798">
+        <v>0</v>
+      </c>
+      <c r="N798">
+        <v>0</v>
+      </c>
+      <c r="O798">
+        <v>111</v>
+      </c>
+      <c r="P798">
+        <v>3222</v>
+      </c>
+      <c r="Q798" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="799" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A799" t="s">
+        <v>415</v>
+      </c>
+      <c r="B799">
+        <v>-35.781129999999997</v>
+      </c>
+      <c r="C799">
+        <v>137.86444</v>
+      </c>
+      <c r="D799" s="2">
+        <v>46115</v>
+      </c>
+      <c r="E799" s="20">
+        <v>0.625</v>
+      </c>
+      <c r="F799">
+        <v>0</v>
+      </c>
+      <c r="G799">
+        <v>0</v>
+      </c>
+      <c r="H799">
+        <v>0</v>
+      </c>
+      <c r="I799">
+        <v>0</v>
+      </c>
+      <c r="J799">
+        <v>0</v>
+      </c>
+      <c r="K799">
+        <v>0</v>
+      </c>
+      <c r="L799">
+        <v>778</v>
+      </c>
+      <c r="M799">
+        <v>0</v>
+      </c>
+      <c r="N799">
+        <v>0</v>
+      </c>
+      <c r="O799">
+        <v>0</v>
+      </c>
+      <c r="P799">
+        <v>778</v>
+      </c>
+      <c r="Q799" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="800" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A800" t="s">
+        <v>231</v>
+      </c>
+      <c r="B800">
+        <v>-35.054707999999998</v>
+      </c>
+      <c r="C800">
+        <v>137.725145</v>
+      </c>
+      <c r="D800" s="2">
+        <v>46116</v>
+      </c>
+      <c r="E800" s="20">
+        <v>0.61458333333333337</v>
+      </c>
+      <c r="I800">
+        <v>39333</v>
+      </c>
+      <c r="J800">
+        <v>0</v>
+      </c>
+      <c r="L800">
+        <v>4000</v>
+      </c>
+      <c r="N800">
+        <v>110500</v>
+      </c>
+      <c r="O800">
+        <v>667</v>
+      </c>
+      <c r="P800">
+        <v>154500</v>
+      </c>
+      <c r="Q800" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="801" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A801" t="s">
+        <v>394</v>
+      </c>
+      <c r="B801">
+        <v>-35.786641000000003</v>
+      </c>
+      <c r="C801">
+        <v>138.07153940000001</v>
+      </c>
+      <c r="D801" s="2">
+        <v>46116</v>
+      </c>
+      <c r="E801" s="20">
+        <v>0.625</v>
+      </c>
+      <c r="F801">
+        <v>0</v>
+      </c>
+      <c r="G801">
+        <v>0</v>
+      </c>
+      <c r="H801">
+        <v>0</v>
+      </c>
+      <c r="I801">
+        <v>111</v>
+      </c>
+      <c r="J801">
+        <v>0</v>
+      </c>
+      <c r="K801">
+        <v>0</v>
+      </c>
+      <c r="L801">
+        <v>0</v>
+      </c>
+      <c r="M801">
+        <v>0</v>
+      </c>
+      <c r="N801">
+        <v>0</v>
+      </c>
+      <c r="O801">
+        <v>0</v>
+      </c>
+      <c r="P801">
+        <v>111</v>
+      </c>
+      <c r="Q801" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="802" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A802" t="s">
+        <v>94</v>
+      </c>
+      <c r="B802">
+        <v>-35.58858</v>
+      </c>
+      <c r="C802">
+        <v>138.60474600000001</v>
+      </c>
+      <c r="D802" s="2">
+        <v>46117</v>
+      </c>
+      <c r="J802">
+        <v>0</v>
+      </c>
+      <c r="L802">
+        <v>333</v>
+      </c>
+      <c r="N802">
+        <v>111</v>
+      </c>
+      <c r="O802">
+        <v>444</v>
+      </c>
+      <c r="P802">
+        <v>888</v>
+      </c>
+      <c r="Q802" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="803" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A803" t="s">
+        <v>92</v>
+      </c>
+      <c r="B803">
+        <v>-35.632150000000003</v>
+      </c>
+      <c r="C803">
+        <v>138.48339999999999</v>
+      </c>
+      <c r="D803" s="2">
+        <v>46117</v>
+      </c>
+      <c r="E803" s="20">
+        <v>0.50694444444444442</v>
+      </c>
+      <c r="H803">
+        <v>0.1</v>
+      </c>
+      <c r="I803">
+        <v>0.45</v>
+      </c>
+      <c r="J803">
+        <v>0</v>
+      </c>
+      <c r="L803">
+        <v>29.65</v>
+      </c>
+      <c r="N803">
+        <v>0.3</v>
+      </c>
+      <c r="O803">
+        <v>0.5</v>
+      </c>
+      <c r="P803">
+        <v>31</v>
+      </c>
+      <c r="Q803" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="804" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A804" t="s">
+        <v>393</v>
+      </c>
+      <c r="B804">
+        <v>-35.533231000000001</v>
+      </c>
+      <c r="C804">
+        <v>138.685574</v>
+      </c>
+      <c r="D804" s="2">
+        <v>46117</v>
+      </c>
+      <c r="E804" s="20">
+        <v>0.63888888888888884</v>
+      </c>
+      <c r="H804">
+        <v>0.35</v>
+      </c>
+      <c r="I804">
+        <v>0.6</v>
+      </c>
+      <c r="J804">
+        <v>0</v>
+      </c>
+      <c r="L804">
+        <v>16.45</v>
+      </c>
+      <c r="N804">
+        <v>0.45</v>
+      </c>
+      <c r="O804">
+        <v>0.15</v>
+      </c>
+      <c r="P804">
+        <v>17.999999999999996</v>
+      </c>
+      <c r="Q804" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="805" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A805" t="s">
+        <v>315</v>
+      </c>
+      <c r="B805">
+        <v>-35.445188000000002</v>
+      </c>
+      <c r="C805">
+        <v>138.307266</v>
+      </c>
+      <c r="D805" s="2">
+        <v>46118</v>
+      </c>
+      <c r="E805" s="20">
+        <v>0.34375</v>
+      </c>
+      <c r="I805">
+        <v>0</v>
+      </c>
+      <c r="J805">
+        <v>0</v>
+      </c>
+      <c r="L805">
+        <v>56</v>
+      </c>
+      <c r="N805">
+        <v>0</v>
+      </c>
+      <c r="O805">
+        <v>0</v>
+      </c>
+      <c r="P805">
+        <v>56</v>
+      </c>
+      <c r="Q805" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="806" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A806" t="s">
+        <v>405</v>
+      </c>
+      <c r="B806">
+        <v>-35.510620000000003</v>
+      </c>
+      <c r="C806">
+        <v>138.21679599999999</v>
+      </c>
+      <c r="D806" s="2">
+        <v>46118</v>
+      </c>
+      <c r="E806" s="20">
+        <v>0.59375</v>
+      </c>
+      <c r="F806">
+        <v>0</v>
+      </c>
+      <c r="G806">
+        <v>0</v>
+      </c>
+      <c r="H806">
+        <v>0</v>
+      </c>
+      <c r="I806">
+        <v>0</v>
+      </c>
+      <c r="J806">
+        <v>0</v>
+      </c>
+      <c r="K806">
+        <v>0</v>
+      </c>
+      <c r="L806">
+        <v>56</v>
+      </c>
+      <c r="N806">
+        <v>278</v>
+      </c>
+      <c r="O806">
+        <v>0</v>
+      </c>
+      <c r="P806">
+        <v>334</v>
+      </c>
+      <c r="Q806" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="807" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A807" t="s">
+        <v>410</v>
+      </c>
+      <c r="B807">
+        <v>-35.499946999999999</v>
+      </c>
+      <c r="C807">
+        <v>138.242954</v>
+      </c>
+      <c r="D807" s="2">
+        <v>46119</v>
+      </c>
+      <c r="E807" s="20">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="H807">
+        <v>0</v>
+      </c>
+      <c r="I807">
+        <v>111</v>
+      </c>
+      <c r="J807">
+        <v>0</v>
+      </c>
+      <c r="L807">
+        <v>0</v>
+      </c>
+      <c r="N807">
+        <v>444</v>
+      </c>
+      <c r="O807">
+        <v>0</v>
+      </c>
+      <c r="P807">
+        <v>555</v>
+      </c>
+      <c r="Q807" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="808" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A808" t="s">
+        <v>416</v>
+      </c>
+      <c r="B808">
+        <v>-35.739091000000002</v>
+      </c>
+      <c r="C808">
+        <v>137.67788400000001</v>
+      </c>
+      <c r="D808" s="2">
+        <v>46119</v>
+      </c>
+      <c r="E808" s="20">
+        <v>0.6875</v>
+      </c>
+      <c r="F808">
+        <v>0</v>
+      </c>
+      <c r="G808">
+        <v>0</v>
+      </c>
+      <c r="H808">
+        <v>0</v>
+      </c>
+      <c r="I808">
+        <v>0</v>
+      </c>
+      <c r="J808">
+        <v>0</v>
+      </c>
+      <c r="K808">
+        <v>0</v>
+      </c>
+      <c r="L808">
+        <v>222</v>
+      </c>
+      <c r="M808">
+        <v>0</v>
+      </c>
+      <c r="N808">
+        <v>0</v>
+      </c>
+      <c r="O808">
+        <v>0</v>
+      </c>
+      <c r="P808">
+        <v>222</v>
+      </c>
+      <c r="Q808" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="809" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A809" t="s">
+        <v>379</v>
+      </c>
+      <c r="B809">
+        <v>-35.853557000000002</v>
+      </c>
+      <c r="C809">
+        <v>137.74248499999999</v>
+      </c>
+      <c r="D809" s="2">
+        <v>46119</v>
+      </c>
+      <c r="E809" s="20">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="F809">
+        <v>0</v>
+      </c>
+      <c r="G809">
+        <v>0</v>
+      </c>
+      <c r="H809">
+        <v>333</v>
+      </c>
+      <c r="I809">
+        <v>0</v>
+      </c>
+      <c r="J809">
+        <v>0</v>
+      </c>
+      <c r="K809">
+        <v>0</v>
+      </c>
+      <c r="L809">
+        <v>111</v>
+      </c>
+      <c r="M809">
+        <v>0</v>
+      </c>
+      <c r="N809">
+        <v>0</v>
+      </c>
+      <c r="O809">
+        <v>0</v>
+      </c>
+      <c r="P809">
+        <v>444</v>
+      </c>
+      <c r="Q809" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="810" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A810" t="s">
+        <v>59</v>
+      </c>
+      <c r="B810">
+        <v>-35.084850000000003</v>
+      </c>
+      <c r="C810">
+        <v>137.74889999999999</v>
+      </c>
+      <c r="D810" s="2">
+        <v>46120</v>
+      </c>
+      <c r="E810" s="20">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="G810">
+        <v>0</v>
+      </c>
+      <c r="I810">
+        <v>56</v>
+      </c>
+      <c r="J810">
+        <v>0</v>
+      </c>
+      <c r="L810">
+        <v>444</v>
+      </c>
+      <c r="M810">
+        <v>0</v>
+      </c>
+      <c r="N810">
+        <v>889</v>
+      </c>
+      <c r="P810">
+        <v>1389</v>
+      </c>
+      <c r="Q810" t="s">
+        <v>149</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q790">
-    <sortCondition ref="D2:D790"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q809">
+    <sortCondition ref="D2:D809"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/MASTER spreadsheet of community summaries.xlsx
+++ b/MASTER spreadsheet of community summaries.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\peri\Dropbox\Delta\Projects\Laboratory\Algal blooms, bacterial counts  for community\For Luke's HAB data display\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A3AE609-E744-456B-B8F7-44A08E7640A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C067153-1D51-4D1E-A88B-1C3725B49881}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{9286397E-2757-492B-865A-39B2D6A15FF6}"/>
+    <workbookView xWindow="-28920" yWindow="1650" windowWidth="29040" windowHeight="15720" xr2:uid="{9286397E-2757-492B-865A-39B2D6A15FF6}"/>
   </bookViews>
   <sheets>
     <sheet name="Cells per mL" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1657" uniqueCount="421">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1681" uniqueCount="427">
   <si>
     <t>Date</t>
   </si>
@@ -1319,6 +1319,24 @@
   </si>
   <si>
     <t>Cape Jervis Boat Ramp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Baudin Beach </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emu Bay </t>
+  </si>
+  <si>
+    <t>Cattle Point, Coorong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flour Cask </t>
+  </si>
+  <si>
+    <t>Wirrina Cove Marina</t>
+  </si>
+  <si>
+    <t>Glenelg Jetty</t>
   </si>
 </sst>
 </file>
@@ -1788,7 +1806,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F307807-E5C9-4450-88E0-159CBB3E9A67}">
-  <dimension ref="A1:T820"/>
+  <dimension ref="A1:T832"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="39.33203125" customWidth="1"/>
@@ -1808,6 +1826,7 @@
     <col min="15" max="15" width="7.6640625" customWidth="1"/>
     <col min="16" max="16" width="12.44140625" customWidth="1"/>
     <col min="17" max="17" width="10.33203125" customWidth="1"/>
+    <col min="18" max="18" width="10" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
@@ -19611,10 +19630,10 @@
         <v>387</v>
       </c>
       <c r="B489">
-        <v>-35.511031000000003</v>
+        <v>-35.510497000000001</v>
       </c>
       <c r="C489">
-        <v>138.21822299999999</v>
+        <v>138.21676299999999</v>
       </c>
       <c r="D489" s="2">
         <v>46041</v>
@@ -25337,7 +25356,7 @@
         <v>56</v>
       </c>
       <c r="P660" s="17">
-        <f>SUM(F660:I660,K660:O660)</f>
+        <f t="shared" ref="P660:P666" si="0">SUM(F660:I660,K660:O660)</f>
         <v>1111</v>
       </c>
       <c r="Q660" t="s">
@@ -25370,7 +25389,7 @@
         <v>111</v>
       </c>
       <c r="P661">
-        <f>SUM(F661:I661,K661:O661)</f>
+        <f t="shared" si="0"/>
         <v>444</v>
       </c>
       <c r="Q661" t="s">
@@ -25403,7 +25422,7 @@
         <v>0</v>
       </c>
       <c r="P662">
-        <f>SUM(F662:I662,K662:O662)</f>
+        <f t="shared" si="0"/>
         <v>56</v>
       </c>
       <c r="Q662" t="s">
@@ -25436,7 +25455,7 @@
         <v>167</v>
       </c>
       <c r="P663">
-        <f>SUM(F663:I663,K663:O663)</f>
+        <f t="shared" si="0"/>
         <v>167</v>
       </c>
       <c r="Q663" t="s">
@@ -25469,7 +25488,7 @@
         <v>56</v>
       </c>
       <c r="P664">
-        <f>SUM(F664:I664,K664:O664)</f>
+        <f t="shared" si="0"/>
         <v>112</v>
       </c>
       <c r="Q664" t="s">
@@ -25502,7 +25521,7 @@
         <v>0</v>
       </c>
       <c r="P665">
-        <f>SUM(F665:I665,K665:O665)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Q665" t="s">
@@ -25535,7 +25554,7 @@
         <v>222</v>
       </c>
       <c r="P666">
-        <f>SUM(F666:I666,K666:O666)</f>
+        <f t="shared" si="0"/>
         <v>278</v>
       </c>
       <c r="Q666" t="s">
@@ -27254,10 +27273,10 @@
         <v>387</v>
       </c>
       <c r="B714">
-        <v>-35.510620000000003</v>
+        <v>-35.510497000000001</v>
       </c>
       <c r="C714">
-        <v>138.21679599999999</v>
+        <v>138.21676299999999</v>
       </c>
       <c r="D714" s="2">
         <v>46089</v>
@@ -29132,10 +29151,10 @@
         <v>404</v>
       </c>
       <c r="B765">
-        <v>-35.510620000000003</v>
+        <v>-35.510497000000001</v>
       </c>
       <c r="C765">
-        <v>138.21679599999999</v>
+        <v>138.21676299999999</v>
       </c>
       <c r="D765" s="2">
         <v>46103</v>
@@ -29628,7 +29647,7 @@
       <c r="N777" s="1"/>
       <c r="O777" s="1"/>
       <c r="P777">
-        <f>SUM(F777:I777,K777:O777)</f>
+        <f t="shared" ref="P777:P788" si="1">SUM(F777:I777,K777:O777)</f>
         <v>722</v>
       </c>
       <c r="Q777" t="s">
@@ -29661,7 +29680,7 @@
         <v>111</v>
       </c>
       <c r="P778">
-        <f>SUM(F778:I778,K778:O778)</f>
+        <f t="shared" si="1"/>
         <v>167</v>
       </c>
       <c r="Q778" t="s">
@@ -29694,7 +29713,7 @@
         <v>56</v>
       </c>
       <c r="P779">
-        <f>SUM(F779:I779,K779:O779)</f>
+        <f t="shared" si="1"/>
         <v>278</v>
       </c>
       <c r="Q779" t="s">
@@ -29727,7 +29746,7 @@
         <v>56</v>
       </c>
       <c r="P780">
-        <f>SUM(F780:I780,K780:O780)</f>
+        <f t="shared" si="1"/>
         <v>112</v>
       </c>
       <c r="Q780" t="s">
@@ -29760,7 +29779,7 @@
         <v>0</v>
       </c>
       <c r="P781">
-        <f>SUM(F781:I781,K781:O781)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Q781" t="s">
@@ -29793,7 +29812,7 @@
         <v>56</v>
       </c>
       <c r="P782">
-        <f>SUM(F782:I782,K782:O782)</f>
+        <f t="shared" si="1"/>
         <v>278</v>
       </c>
       <c r="Q782" t="s">
@@ -29826,7 +29845,7 @@
         <v>167</v>
       </c>
       <c r="P783">
-        <f>SUM(F783:I783,K783:O783)</f>
+        <f t="shared" si="1"/>
         <v>445</v>
       </c>
       <c r="Q783" t="s">
@@ -29859,7 +29878,7 @@
         <v>0</v>
       </c>
       <c r="P784">
-        <f>SUM(F784:I784,K784:O784)</f>
+        <f t="shared" si="1"/>
         <v>56</v>
       </c>
       <c r="Q784" t="s">
@@ -29892,7 +29911,7 @@
         <v>56</v>
       </c>
       <c r="P785">
-        <f>SUM(F785:I785,K785:O785)</f>
+        <f t="shared" si="1"/>
         <v>56</v>
       </c>
       <c r="Q785" t="s">
@@ -29925,7 +29944,7 @@
         <v>56</v>
       </c>
       <c r="P786">
-        <f>SUM(F786:I786,K786:O786)</f>
+        <f t="shared" si="1"/>
         <v>56</v>
       </c>
       <c r="Q786" t="s">
@@ -29958,7 +29977,7 @@
         <v>0</v>
       </c>
       <c r="P787">
-        <f>SUM(F787:I787,K787:O787)</f>
+        <f t="shared" si="1"/>
         <v>56</v>
       </c>
       <c r="Q787" t="s">
@@ -29991,7 +30010,7 @@
         <v>111</v>
       </c>
       <c r="P788">
-        <f>SUM(F788:I788,K788:O788)</f>
+        <f t="shared" si="1"/>
         <v>111</v>
       </c>
       <c r="Q788" t="s">
@@ -30926,10 +30945,10 @@
         <v>404</v>
       </c>
       <c r="B811">
-        <v>-35.510620000000003</v>
+        <v>-35.510497000000001</v>
       </c>
       <c r="C811">
-        <v>138.21679599999999</v>
+        <v>138.21676299999999</v>
       </c>
       <c r="D811" s="2">
         <v>46118</v>
@@ -30976,10 +30995,10 @@
         <v>409</v>
       </c>
       <c r="B812">
-        <v>-35.499946999999999</v>
+        <v>-35.500024000000003</v>
       </c>
       <c r="C812">
-        <v>138.242954</v>
+        <v>138.24287699999999</v>
       </c>
       <c r="D812" s="2">
         <v>46119</v>
@@ -31161,119 +31180,140 @@
     </row>
     <row r="816" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A816" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B816">
-        <v>-35.605305999999999</v>
+        <v>-35.463515299999997</v>
       </c>
       <c r="C816">
-        <v>138.09375</v>
+        <v>137.51524000000001</v>
       </c>
       <c r="D816" s="2">
-        <v>46124</v>
+        <v>46121</v>
       </c>
       <c r="E816" s="20">
-        <v>0.51041666666666663</v>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F816">
+        <v>0</v>
+      </c>
+      <c r="G816">
+        <v>0</v>
       </c>
       <c r="H816">
-        <v>56</v>
+        <v>1222</v>
       </c>
       <c r="I816">
-        <v>389</v>
+        <v>444</v>
       </c>
       <c r="J816">
         <v>0</v>
       </c>
+      <c r="K816">
+        <v>0</v>
+      </c>
       <c r="L816">
-        <v>667</v>
+        <v>1667</v>
+      </c>
+      <c r="M816">
+        <v>0</v>
       </c>
       <c r="N816">
-        <v>2278</v>
+        <v>0</v>
       </c>
       <c r="O816">
         <v>111</v>
       </c>
       <c r="P816">
-        <v>3501</v>
+        <v>3444</v>
       </c>
       <c r="Q816" t="s">
-        <v>252</v>
+        <v>398</v>
       </c>
     </row>
     <row r="817" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A817" t="s">
-        <v>268</v>
+        <v>420</v>
       </c>
       <c r="B817">
-        <v>-34.824044999999998</v>
+        <v>-35.605305999999999</v>
       </c>
       <c r="C817">
-        <v>138.48377600000001</v>
+        <v>138.09375</v>
       </c>
       <c r="D817" s="2">
-        <v>46125</v>
+        <v>46124</v>
       </c>
       <c r="E817" s="20">
-        <v>0.55555555555555558</v>
-      </c>
-      <c r="G817">
-        <v>0.1</v>
+        <v>0.51041666666666663</v>
       </c>
       <c r="H817">
-        <v>1.05</v>
+        <v>56</v>
       </c>
       <c r="I817">
-        <v>3.75</v>
+        <v>389</v>
       </c>
       <c r="J817">
         <v>0</v>
       </c>
       <c r="L817">
-        <v>12.75</v>
-      </c>
-      <c r="M817">
-        <v>0.15</v>
+        <v>667</v>
       </c>
       <c r="N817">
-        <v>0.5</v>
+        <v>2278</v>
       </c>
       <c r="O817">
-        <v>0.1</v>
+        <v>111</v>
       </c>
       <c r="P817">
-        <v>18.399999999999999</v>
+        <v>3501</v>
       </c>
       <c r="Q817" t="s">
-        <v>78</v>
+        <v>252</v>
       </c>
     </row>
     <row r="818" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A818" t="s">
-        <v>79</v>
+        <v>268</v>
       </c>
       <c r="B818">
-        <v>-34.804662999999998</v>
+        <v>-34.824044999999998</v>
       </c>
       <c r="C818">
-        <v>138.540223</v>
+        <v>138.48377600000001</v>
       </c>
       <c r="D818" s="2">
         <v>46125</v>
       </c>
       <c r="E818" s="20">
-        <v>0.53472222222222221</v>
+        <v>0.55555555555555558</v>
+      </c>
+      <c r="G818">
+        <v>0.1</v>
+      </c>
+      <c r="H818">
+        <v>1.05</v>
       </c>
       <c r="I818">
-        <v>0.6</v>
+        <v>3.75</v>
       </c>
       <c r="J818">
         <v>0</v>
       </c>
       <c r="L818">
-        <v>31.8</v>
+        <v>12.75</v>
+      </c>
+      <c r="M818">
+        <v>0.15</v>
+      </c>
+      <c r="N818">
+        <v>0.5</v>
+      </c>
+      <c r="O818">
+        <v>0.1</v>
       </c>
       <c r="P818">
-        <v>32.4</v>
+        <v>18.399999999999999</v>
       </c>
       <c r="Q818" t="s">
         <v>78</v>
@@ -31281,40 +31321,31 @@
     </row>
     <row r="819" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A819" t="s">
-        <v>419</v>
+        <v>79</v>
       </c>
       <c r="B819">
-        <v>-34.875185999999999</v>
+        <v>-34.804662999999998</v>
       </c>
       <c r="C819">
-        <v>138.485422</v>
+        <v>138.540223</v>
       </c>
       <c r="D819" s="2">
         <v>46125</v>
       </c>
       <c r="E819" s="20">
-        <v>0.6875</v>
-      </c>
-      <c r="H819">
+        <v>0.53472222222222221</v>
+      </c>
+      <c r="I819">
         <v>0.6</v>
       </c>
-      <c r="I819">
-        <v>7.2</v>
-      </c>
       <c r="J819">
         <v>0</v>
       </c>
       <c r="L819">
-        <v>1141.3679999999999</v>
-      </c>
-      <c r="N819">
-        <v>0.3</v>
-      </c>
-      <c r="O819">
-        <v>0.6</v>
+        <v>31.8</v>
       </c>
       <c r="P819">
-        <v>1150.0679999999998</v>
+        <v>32.4</v>
       </c>
       <c r="Q819" t="s">
         <v>78</v>
@@ -31322,45 +31353,570 @@
     </row>
     <row r="820" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A820" t="s">
-        <v>314</v>
+        <v>419</v>
       </c>
       <c r="B820">
-        <v>-35.445188000000002</v>
+        <v>-34.875185999999999</v>
       </c>
       <c r="C820">
-        <v>138.307266</v>
+        <v>138.485422</v>
       </c>
       <c r="D820" s="2">
         <v>46125</v>
       </c>
       <c r="E820" s="20">
+        <v>0.6875</v>
+      </c>
+      <c r="H820">
+        <v>0.6</v>
+      </c>
+      <c r="I820">
+        <v>7.2</v>
+      </c>
+      <c r="J820">
+        <v>0</v>
+      </c>
+      <c r="L820">
+        <v>1141.3679999999999</v>
+      </c>
+      <c r="N820">
+        <v>0.3</v>
+      </c>
+      <c r="O820">
+        <v>0.6</v>
+      </c>
+      <c r="P820">
+        <v>1150.0679999999998</v>
+      </c>
+      <c r="Q820" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="821" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A821" t="s">
+        <v>314</v>
+      </c>
+      <c r="B821">
+        <v>-35.445188000000002</v>
+      </c>
+      <c r="C821">
+        <v>138.307266</v>
+      </c>
+      <c r="D821" s="2">
+        <v>46125</v>
+      </c>
+      <c r="E821" s="20">
         <v>0.39583333333333331</v>
       </c>
-      <c r="I820">
+      <c r="I821">
         <v>111</v>
       </c>
-      <c r="J820">
-        <v>0</v>
-      </c>
-      <c r="L820">
-        <v>0</v>
-      </c>
-      <c r="N820">
-        <v>0</v>
-      </c>
-      <c r="O820">
+      <c r="J821">
+        <v>0</v>
+      </c>
+      <c r="L821">
+        <v>0</v>
+      </c>
+      <c r="N821">
+        <v>0</v>
+      </c>
+      <c r="O821">
         <v>667</v>
       </c>
-      <c r="P820">
+      <c r="P821">
         <v>778</v>
       </c>
-      <c r="Q820" t="s">
+      <c r="Q821" t="s">
         <v>352</v>
       </c>
     </row>
+    <row r="822" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A822" t="s">
+        <v>422</v>
+      </c>
+      <c r="B822">
+        <v>-35.591330800000001</v>
+      </c>
+      <c r="C822">
+        <v>137.5061887</v>
+      </c>
+      <c r="D822" s="2">
+        <v>46126</v>
+      </c>
+      <c r="E822" s="20">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="F822">
+        <v>0</v>
+      </c>
+      <c r="G822">
+        <v>0</v>
+      </c>
+      <c r="H822">
+        <v>1667</v>
+      </c>
+      <c r="I822">
+        <v>333</v>
+      </c>
+      <c r="J822">
+        <v>0</v>
+      </c>
+      <c r="K822">
+        <v>0</v>
+      </c>
+      <c r="L822">
+        <v>2556</v>
+      </c>
+      <c r="M822">
+        <v>222</v>
+      </c>
+      <c r="N822">
+        <v>0</v>
+      </c>
+      <c r="O822">
+        <v>0</v>
+      </c>
+      <c r="P822">
+        <v>4778</v>
+      </c>
+      <c r="Q822" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="823" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A823" t="s">
+        <v>399</v>
+      </c>
+      <c r="B823">
+        <v>-35.793973000000001</v>
+      </c>
+      <c r="C823">
+        <v>137.852418</v>
+      </c>
+      <c r="D823" s="2">
+        <v>46126</v>
+      </c>
+      <c r="E823" s="20">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="F823">
+        <v>0</v>
+      </c>
+      <c r="G823">
+        <v>0</v>
+      </c>
+      <c r="H823">
+        <v>111</v>
+      </c>
+      <c r="I823">
+        <v>0</v>
+      </c>
+      <c r="J823">
+        <v>0</v>
+      </c>
+      <c r="K823">
+        <v>0</v>
+      </c>
+      <c r="L823">
+        <v>333</v>
+      </c>
+      <c r="M823">
+        <v>333</v>
+      </c>
+      <c r="N823">
+        <v>0</v>
+      </c>
+      <c r="O823">
+        <v>0</v>
+      </c>
+      <c r="P823">
+        <v>777</v>
+      </c>
+      <c r="Q823" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="824" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A824" t="s">
+        <v>423</v>
+      </c>
+      <c r="B824">
+        <v>-35.638117999999999</v>
+      </c>
+      <c r="C824">
+        <v>139.070425</v>
+      </c>
+      <c r="D824" s="2">
+        <v>46127</v>
+      </c>
+      <c r="G824">
+        <v>1000</v>
+      </c>
+      <c r="H824">
+        <v>444</v>
+      </c>
+      <c r="I824">
+        <v>333</v>
+      </c>
+      <c r="J824">
+        <v>0</v>
+      </c>
+      <c r="L824">
+        <v>9000</v>
+      </c>
+      <c r="N824">
+        <v>189</v>
+      </c>
+      <c r="O824">
+        <v>11555</v>
+      </c>
+      <c r="P824">
+        <v>22521</v>
+      </c>
+      <c r="Q824" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="825" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A825" t="s">
+        <v>425</v>
+      </c>
+      <c r="B825">
+        <v>-35.500024000000003</v>
+      </c>
+      <c r="C825">
+        <v>138.24287699999999</v>
+      </c>
+      <c r="D825" s="2">
+        <v>46130</v>
+      </c>
+      <c r="E825" s="20">
+        <v>0.61458333333333337</v>
+      </c>
+      <c r="H825">
+        <v>222</v>
+      </c>
+      <c r="I825">
+        <v>56</v>
+      </c>
+      <c r="J825">
+        <v>0</v>
+      </c>
+      <c r="K825">
+        <v>0</v>
+      </c>
+      <c r="L825">
+        <v>56</v>
+      </c>
+      <c r="N825">
+        <v>944</v>
+      </c>
+      <c r="O825">
+        <v>56</v>
+      </c>
+      <c r="P825">
+        <v>1334</v>
+      </c>
+      <c r="Q825" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="826" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A826" t="s">
+        <v>89</v>
+      </c>
+      <c r="B826">
+        <v>-35.6048446</v>
+      </c>
+      <c r="C826">
+        <v>138.59278499999999</v>
+      </c>
+      <c r="D826" s="2">
+        <v>46131</v>
+      </c>
+      <c r="G826">
+        <v>111</v>
+      </c>
+      <c r="I826">
+        <v>222</v>
+      </c>
+      <c r="J826">
+        <v>0</v>
+      </c>
+      <c r="L826">
+        <v>222</v>
+      </c>
+      <c r="N826">
+        <v>389</v>
+      </c>
+      <c r="O826">
+        <v>444</v>
+      </c>
+      <c r="P826">
+        <v>1388</v>
+      </c>
+      <c r="Q826" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="827" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A827" t="s">
+        <v>404</v>
+      </c>
+      <c r="B827">
+        <v>-35.510497000000001</v>
+      </c>
+      <c r="C827">
+        <v>138.21676299999999</v>
+      </c>
+      <c r="D827" s="2">
+        <v>46131</v>
+      </c>
+      <c r="E827" s="20">
+        <v>0.625</v>
+      </c>
+      <c r="I827">
+        <v>0</v>
+      </c>
+      <c r="J827">
+        <v>0</v>
+      </c>
+      <c r="K827">
+        <v>0</v>
+      </c>
+      <c r="L827">
+        <v>0</v>
+      </c>
+      <c r="M827">
+        <v>0</v>
+      </c>
+      <c r="N827">
+        <v>278</v>
+      </c>
+      <c r="O827">
+        <v>111</v>
+      </c>
+      <c r="P827">
+        <v>389</v>
+      </c>
+      <c r="Q827" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="828" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A828" t="s">
+        <v>426</v>
+      </c>
+      <c r="B828">
+        <v>-34.980508999999998</v>
+      </c>
+      <c r="C828">
+        <v>138.508081</v>
+      </c>
+      <c r="D828" s="2">
+        <v>46131</v>
+      </c>
+      <c r="E828" s="20">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="G828">
+        <v>0.12</v>
+      </c>
+      <c r="I828">
+        <v>4.68</v>
+      </c>
+      <c r="J828">
+        <v>0</v>
+      </c>
+      <c r="L828">
+        <v>380.28</v>
+      </c>
+      <c r="N828">
+        <v>0.6</v>
+      </c>
+      <c r="O828">
+        <v>0.48</v>
+      </c>
+      <c r="P828">
+        <v>386.16</v>
+      </c>
+      <c r="Q828" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="829" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A829" t="s">
+        <v>179</v>
+      </c>
+      <c r="B829">
+        <v>-35.078539999999997</v>
+      </c>
+      <c r="C829">
+        <v>138.49587</v>
+      </c>
+      <c r="D829" s="2">
+        <v>46131</v>
+      </c>
+      <c r="E829" s="20">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="H829">
+        <v>0.1</v>
+      </c>
+      <c r="I829">
+        <v>0.36699999999999999</v>
+      </c>
+      <c r="J829">
+        <v>0</v>
+      </c>
+      <c r="L829">
+        <v>4.5</v>
+      </c>
+      <c r="M829">
+        <v>6.7000000000000004E-2</v>
+      </c>
+      <c r="P829">
+        <v>5.0339999999999998</v>
+      </c>
+      <c r="Q829" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="830" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A830" t="s">
+        <v>314</v>
+      </c>
+      <c r="B830">
+        <v>-35.445188000000002</v>
+      </c>
+      <c r="C830">
+        <v>138.307266</v>
+      </c>
+      <c r="D830" s="2">
+        <v>46132</v>
+      </c>
+      <c r="E830" s="20">
+        <v>0.375</v>
+      </c>
+      <c r="I830">
+        <v>111</v>
+      </c>
+      <c r="J830">
+        <v>0</v>
+      </c>
+      <c r="L830">
+        <v>222</v>
+      </c>
+      <c r="N830">
+        <v>0</v>
+      </c>
+      <c r="O830">
+        <v>2167</v>
+      </c>
+      <c r="P830">
+        <v>2500</v>
+      </c>
+      <c r="Q830" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="831" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A831" t="s">
+        <v>424</v>
+      </c>
+      <c r="B831">
+        <v>-35.878133800000001</v>
+      </c>
+      <c r="C831">
+        <v>137.69381060000001</v>
+      </c>
+      <c r="D831" s="2">
+        <v>46133</v>
+      </c>
+      <c r="E831" s="20">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="F831">
+        <v>0</v>
+      </c>
+      <c r="G831">
+        <v>0</v>
+      </c>
+      <c r="H831">
+        <v>2778</v>
+      </c>
+      <c r="I831">
+        <v>0</v>
+      </c>
+      <c r="J831">
+        <v>0</v>
+      </c>
+      <c r="K831">
+        <v>0</v>
+      </c>
+      <c r="L831">
+        <v>18333</v>
+      </c>
+      <c r="M831">
+        <v>556</v>
+      </c>
+      <c r="N831">
+        <v>0</v>
+      </c>
+      <c r="O831">
+        <v>0</v>
+      </c>
+      <c r="P831">
+        <v>21667</v>
+      </c>
+      <c r="Q831" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="832" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A832" t="s">
+        <v>59</v>
+      </c>
+      <c r="B832">
+        <v>-35.084850000000003</v>
+      </c>
+      <c r="C832">
+        <v>137.74889999999999</v>
+      </c>
+      <c r="D832" s="2">
+        <v>46134</v>
+      </c>
+      <c r="E832" s="20">
+        <v>0.5625</v>
+      </c>
+      <c r="G832">
+        <v>444</v>
+      </c>
+      <c r="I832">
+        <v>56</v>
+      </c>
+      <c r="J832">
+        <v>0</v>
+      </c>
+      <c r="L832">
+        <v>0</v>
+      </c>
+      <c r="M832">
+        <v>0</v>
+      </c>
+      <c r="N832">
+        <v>389</v>
+      </c>
+      <c r="P832">
+        <v>889</v>
+      </c>
+      <c r="Q832" t="s">
+        <v>149</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q820">
-    <sortCondition ref="D2:D820"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q831">
+    <sortCondition ref="D2:D831"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/MASTER spreadsheet of community summaries.xlsx
+++ b/MASTER spreadsheet of community summaries.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\peri\Dropbox\Delta\Projects\Laboratory\Algal blooms, bacterial counts  for community\For Luke's HAB data display\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C067153-1D51-4D1E-A88B-1C3725B49881}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E01EE52-D29F-4CA3-80A3-5D409C13E3F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="1650" windowWidth="29040" windowHeight="15720" xr2:uid="{9286397E-2757-492B-865A-39B2D6A15FF6}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{9286397E-2757-492B-865A-39B2D6A15FF6}"/>
   </bookViews>
   <sheets>
     <sheet name="Cells per mL" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1681" uniqueCount="427">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1701" uniqueCount="430">
   <si>
     <t>Date</t>
   </si>
@@ -1252,9 +1252,6 @@
     <t>Ocean between Pullen and Seal island</t>
   </si>
   <si>
-    <t>LEWK5222</t>
-  </si>
-  <si>
     <t>Brown Beach</t>
   </si>
   <si>
@@ -1337,6 +1334,18 @@
   </si>
   <si>
     <t>Glenelg Jetty</t>
+  </si>
+  <si>
+    <t>Waitpinga Cliffs, 1km offshore</t>
+  </si>
+  <si>
+    <t>Between Wright Island and Granite Island</t>
+  </si>
+  <si>
+    <t>Emu Bay</t>
+  </si>
+  <si>
+    <t>North Carrickalinga Beach</t>
   </si>
 </sst>
 </file>
@@ -1806,7 +1815,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F307807-E5C9-4450-88E0-159CBB3E9A67}">
-  <dimension ref="A1:T832"/>
+  <dimension ref="A1:T842"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="39.33203125" customWidth="1"/>
@@ -24241,7 +24250,7 @@
     </row>
     <row r="632" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A632" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B632">
         <v>-33.043101999999998</v>
@@ -25356,7 +25365,7 @@
         <v>56</v>
       </c>
       <c r="P660" s="17">
-        <f t="shared" ref="P660:P666" si="0">SUM(F660:I660,K660:O660)</f>
+        <f>SUM(F660:I660,K660:O660)</f>
         <v>1111</v>
       </c>
       <c r="Q660" t="s">
@@ -25389,7 +25398,7 @@
         <v>111</v>
       </c>
       <c r="P661">
-        <f t="shared" si="0"/>
+        <f>SUM(F661:I661,K661:O661)</f>
         <v>444</v>
       </c>
       <c r="Q661" t="s">
@@ -25422,7 +25431,7 @@
         <v>0</v>
       </c>
       <c r="P662">
-        <f t="shared" si="0"/>
+        <f>SUM(F662:I662,K662:O662)</f>
         <v>56</v>
       </c>
       <c r="Q662" t="s">
@@ -25455,7 +25464,7 @@
         <v>167</v>
       </c>
       <c r="P663">
-        <f t="shared" si="0"/>
+        <f>SUM(F663:I663,K663:O663)</f>
         <v>167</v>
       </c>
       <c r="Q663" t="s">
@@ -25488,7 +25497,7 @@
         <v>56</v>
       </c>
       <c r="P664">
-        <f t="shared" si="0"/>
+        <f>SUM(F664:I664,K664:O664)</f>
         <v>112</v>
       </c>
       <c r="Q664" t="s">
@@ -25521,7 +25530,7 @@
         <v>0</v>
       </c>
       <c r="P665">
-        <f t="shared" si="0"/>
+        <f>SUM(F665:I665,K665:O665)</f>
         <v>0</v>
       </c>
       <c r="Q665" t="s">
@@ -25554,7 +25563,7 @@
         <v>222</v>
       </c>
       <c r="P666">
-        <f t="shared" si="0"/>
+        <f>SUM(F666:I666,K666:O666)</f>
         <v>278</v>
       </c>
       <c r="Q666" t="s">
@@ -27454,7 +27463,7 @@
     </row>
     <row r="719" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A719" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B719">
         <v>-33.043101999999998</v>
@@ -28547,7 +28556,7 @@
     </row>
     <row r="748" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A748" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B748">
         <v>-34.075042000000003</v>
@@ -28735,7 +28744,7 @@
         <v>555</v>
       </c>
       <c r="Q752" t="s">
-        <v>398</v>
+        <v>151</v>
       </c>
     </row>
     <row r="753" spans="1:17" x14ac:dyDescent="0.3">
@@ -29000,12 +29009,12 @@
         <v>666</v>
       </c>
       <c r="Q760" t="s">
-        <v>398</v>
+        <v>151</v>
       </c>
     </row>
     <row r="761" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A761" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B761">
         <v>-34.903120000000001</v>
@@ -29072,7 +29081,7 @@
     </row>
     <row r="763" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A763" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B763">
         <v>-34.903466000000002</v>
@@ -29110,7 +29119,7 @@
     </row>
     <row r="764" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A764" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B764">
         <v>-34.765996000000001</v>
@@ -29148,7 +29157,7 @@
     </row>
     <row r="765" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A765" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B765">
         <v>-35.510497000000001</v>
@@ -29183,7 +29192,7 @@
     </row>
     <row r="766" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A766" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B766">
         <v>-35.793973000000001</v>
@@ -29231,7 +29240,7 @@
         <v>7333</v>
       </c>
       <c r="Q766" t="s">
-        <v>398</v>
+        <v>151</v>
       </c>
     </row>
     <row r="767" spans="1:17" x14ac:dyDescent="0.3">
@@ -29284,7 +29293,7 @@
         <v>0</v>
       </c>
       <c r="Q767" t="s">
-        <v>398</v>
+        <v>151</v>
       </c>
     </row>
     <row r="768" spans="1:17" x14ac:dyDescent="0.3">
@@ -29319,7 +29328,7 @@
         <v>1722</v>
       </c>
       <c r="Q768" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="769" spans="1:17" x14ac:dyDescent="0.3">
@@ -29389,7 +29398,7 @@
         <v>890</v>
       </c>
       <c r="Q770" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="771" spans="1:17" x14ac:dyDescent="0.3">
@@ -29429,7 +29438,7 @@
     </row>
     <row r="772" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A772" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B772">
         <v>-35.557499999999997</v>
@@ -29647,7 +29656,7 @@
       <c r="N777" s="1"/>
       <c r="O777" s="1"/>
       <c r="P777">
-        <f t="shared" ref="P777:P788" si="1">SUM(F777:I777,K777:O777)</f>
+        <f>SUM(F777:I777,K777:O777)</f>
         <v>722</v>
       </c>
       <c r="Q777" t="s">
@@ -29680,7 +29689,7 @@
         <v>111</v>
       </c>
       <c r="P778">
-        <f t="shared" si="1"/>
+        <f>SUM(F778:I778,K778:O778)</f>
         <v>167</v>
       </c>
       <c r="Q778" t="s">
@@ -29713,7 +29722,7 @@
         <v>56</v>
       </c>
       <c r="P779">
-        <f t="shared" si="1"/>
+        <f>SUM(F779:I779,K779:O779)</f>
         <v>278</v>
       </c>
       <c r="Q779" t="s">
@@ -29746,7 +29755,7 @@
         <v>56</v>
       </c>
       <c r="P780">
-        <f t="shared" si="1"/>
+        <f>SUM(F780:I780,K780:O780)</f>
         <v>112</v>
       </c>
       <c r="Q780" t="s">
@@ -29779,7 +29788,7 @@
         <v>0</v>
       </c>
       <c r="P781">
-        <f t="shared" si="1"/>
+        <f>SUM(F781:I781,K781:O781)</f>
         <v>0</v>
       </c>
       <c r="Q781" t="s">
@@ -29812,7 +29821,7 @@
         <v>56</v>
       </c>
       <c r="P782">
-        <f t="shared" si="1"/>
+        <f>SUM(F782:I782,K782:O782)</f>
         <v>278</v>
       </c>
       <c r="Q782" t="s">
@@ -29845,7 +29854,7 @@
         <v>167</v>
       </c>
       <c r="P783">
-        <f t="shared" si="1"/>
+        <f>SUM(F783:I783,K783:O783)</f>
         <v>445</v>
       </c>
       <c r="Q783" t="s">
@@ -29878,7 +29887,7 @@
         <v>0</v>
       </c>
       <c r="P784">
-        <f t="shared" si="1"/>
+        <f>SUM(F784:I784,K784:O784)</f>
         <v>56</v>
       </c>
       <c r="Q784" t="s">
@@ -29887,7 +29896,7 @@
     </row>
     <row r="785" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A785" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B785">
         <v>-35.548499999999997</v>
@@ -29911,7 +29920,7 @@
         <v>56</v>
       </c>
       <c r="P785">
-        <f t="shared" si="1"/>
+        <f>SUM(F785:I785,K785:O785)</f>
         <v>56</v>
       </c>
       <c r="Q785" t="s">
@@ -29920,7 +29929,7 @@
     </row>
     <row r="786" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A786" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B786">
         <v>-35.5595</v>
@@ -29944,7 +29953,7 @@
         <v>56</v>
       </c>
       <c r="P786">
-        <f t="shared" si="1"/>
+        <f>SUM(F786:I786,K786:O786)</f>
         <v>56</v>
       </c>
       <c r="Q786" t="s">
@@ -29953,7 +29962,7 @@
     </row>
     <row r="787" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A787" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B787">
         <v>-35.585299999999997</v>
@@ -29977,7 +29986,7 @@
         <v>0</v>
       </c>
       <c r="P787">
-        <f t="shared" si="1"/>
+        <f>SUM(F787:I787,K787:O787)</f>
         <v>56</v>
       </c>
       <c r="Q787" t="s">
@@ -30010,7 +30019,7 @@
         <v>111</v>
       </c>
       <c r="P788">
-        <f t="shared" si="1"/>
+        <f>SUM(F788:I788,K788:O788)</f>
         <v>111</v>
       </c>
       <c r="Q788" t="s">
@@ -30057,7 +30066,7 @@
     </row>
     <row r="790" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A790" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B790">
         <v>-35.499946999999999</v>
@@ -30098,7 +30107,7 @@
     </row>
     <row r="791" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A791" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B791">
         <v>-35.793973000000001</v>
@@ -30146,7 +30155,7 @@
         <v>8555</v>
       </c>
       <c r="Q791" t="s">
-        <v>398</v>
+        <v>151</v>
       </c>
     </row>
     <row r="792" spans="1:17" x14ac:dyDescent="0.3">
@@ -30199,7 +30208,7 @@
         <v>8777</v>
       </c>
       <c r="Q792" t="s">
-        <v>398</v>
+        <v>151</v>
       </c>
     </row>
     <row r="793" spans="1:17" x14ac:dyDescent="0.3">
@@ -30252,12 +30261,12 @@
         <v>5833</v>
       </c>
       <c r="Q793" t="s">
-        <v>398</v>
+        <v>151</v>
       </c>
     </row>
     <row r="794" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A794" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B794">
         <v>-34.075042000000003</v>
@@ -30410,7 +30419,7 @@
         <v>7778</v>
       </c>
       <c r="Q797" t="s">
-        <v>398</v>
+        <v>151</v>
       </c>
     </row>
     <row r="798" spans="1:17" x14ac:dyDescent="0.3">
@@ -30456,7 +30465,7 @@
     </row>
     <row r="799" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A799" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B799">
         <v>-35.149287000000001</v>
@@ -30491,7 +30500,7 @@
     </row>
     <row r="800" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A800" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B800">
         <v>-36.825802000000003</v>
@@ -30577,12 +30586,12 @@
         <v>3222</v>
       </c>
       <c r="Q801" t="s">
-        <v>398</v>
+        <v>151</v>
       </c>
     </row>
     <row r="802" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A802" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B802">
         <v>-35.781129999999997</v>
@@ -30630,7 +30639,7 @@
         <v>778</v>
       </c>
       <c r="Q802" t="s">
-        <v>398</v>
+        <v>151</v>
       </c>
     </row>
     <row r="803" spans="1:17" x14ac:dyDescent="0.3">
@@ -30721,12 +30730,12 @@
         <v>111</v>
       </c>
       <c r="Q804" t="s">
-        <v>398</v>
+        <v>151</v>
       </c>
     </row>
     <row r="805" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A805" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B805">
         <v>-32.915069000000003</v>
@@ -30758,7 +30767,7 @@
     </row>
     <row r="806" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A806" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B806">
         <v>-32.913386000000003</v>
@@ -30937,12 +30946,12 @@
         <v>56</v>
       </c>
       <c r="Q810" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="811" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A811" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B811">
         <v>-35.510497000000001</v>
@@ -30992,7 +31001,7 @@
     </row>
     <row r="812" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A812" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B812">
         <v>-35.500024000000003</v>
@@ -31033,7 +31042,7 @@
     </row>
     <row r="813" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A813" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B813">
         <v>-35.739091000000002</v>
@@ -31081,7 +31090,7 @@
         <v>222</v>
       </c>
       <c r="Q813" t="s">
-        <v>398</v>
+        <v>151</v>
       </c>
     </row>
     <row r="814" spans="1:17" x14ac:dyDescent="0.3">
@@ -31134,7 +31143,7 @@
         <v>444</v>
       </c>
       <c r="Q814" t="s">
-        <v>398</v>
+        <v>151</v>
       </c>
     </row>
     <row r="815" spans="1:17" x14ac:dyDescent="0.3">
@@ -31180,7 +31189,7 @@
     </row>
     <row r="816" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A816" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B816">
         <v>-35.463515299999997</v>
@@ -31228,12 +31237,12 @@
         <v>3444</v>
       </c>
       <c r="Q816" t="s">
-        <v>398</v>
+        <v>151</v>
       </c>
     </row>
     <row r="817" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A817" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B817">
         <v>-35.605305999999999</v>
@@ -31353,7 +31362,7 @@
     </row>
     <row r="820" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A820" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B820">
         <v>-34.875185999999999</v>
@@ -31432,7 +31441,7 @@
     </row>
     <row r="822" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A822" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B822">
         <v>-35.591330800000001</v>
@@ -31480,12 +31489,12 @@
         <v>4778</v>
       </c>
       <c r="Q822" t="s">
-        <v>398</v>
+        <v>151</v>
       </c>
     </row>
     <row r="823" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A823" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B823">
         <v>-35.793973000000001</v>
@@ -31533,12 +31542,12 @@
         <v>777</v>
       </c>
       <c r="Q823" t="s">
-        <v>398</v>
+        <v>151</v>
       </c>
     </row>
     <row r="824" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A824" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B824">
         <v>-35.638117999999999</v>
@@ -31579,7 +31588,7 @@
     </row>
     <row r="825" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A825" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B825">
         <v>-35.500024000000003</v>
@@ -31661,7 +31670,7 @@
     </row>
     <row r="827" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A827" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B827">
         <v>-35.510497000000001</v>
@@ -31705,7 +31714,7 @@
     </row>
     <row r="828" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A828" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B828">
         <v>-34.980508999999998</v>
@@ -31822,7 +31831,7 @@
     </row>
     <row r="831" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A831" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B831">
         <v>-35.878133800000001</v>
@@ -31870,7 +31879,7 @@
         <v>21667</v>
       </c>
       <c r="Q831" t="s">
-        <v>398</v>
+        <v>151</v>
       </c>
     </row>
     <row r="832" spans="1:17" x14ac:dyDescent="0.3">
@@ -31914,9 +31923,431 @@
         <v>149</v>
       </c>
     </row>
+    <row r="833" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A833" t="s">
+        <v>86</v>
+      </c>
+      <c r="B833">
+        <v>-35.540277000000003</v>
+      </c>
+      <c r="C833">
+        <v>138.66416599999999</v>
+      </c>
+      <c r="D833" s="2">
+        <v>46135</v>
+      </c>
+      <c r="E833" s="20">
+        <v>0.5180555555555556</v>
+      </c>
+      <c r="G833">
+        <v>56</v>
+      </c>
+      <c r="H833">
+        <v>278</v>
+      </c>
+      <c r="I833">
+        <v>167</v>
+      </c>
+      <c r="J833">
+        <v>0</v>
+      </c>
+      <c r="K833">
+        <v>56</v>
+      </c>
+      <c r="L833">
+        <v>4389</v>
+      </c>
+      <c r="N833">
+        <v>389</v>
+      </c>
+      <c r="O833">
+        <v>944</v>
+      </c>
+      <c r="P833">
+        <v>6279</v>
+      </c>
+      <c r="Q833" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="834" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A834" t="s">
+        <v>87</v>
+      </c>
+      <c r="B834">
+        <v>-35.573300000000003</v>
+      </c>
+      <c r="C834">
+        <v>138.64250000000001</v>
+      </c>
+      <c r="D834" s="2">
+        <v>46135</v>
+      </c>
+      <c r="E834" s="20">
+        <v>0.50555555555555554</v>
+      </c>
+      <c r="G834">
+        <v>56</v>
+      </c>
+      <c r="H834">
+        <v>111</v>
+      </c>
+      <c r="I834">
+        <v>278</v>
+      </c>
+      <c r="J834">
+        <v>0</v>
+      </c>
+      <c r="L834">
+        <v>167</v>
+      </c>
+      <c r="N834">
+        <v>667</v>
+      </c>
+      <c r="O834">
+        <v>778</v>
+      </c>
+      <c r="P834">
+        <v>2057</v>
+      </c>
+      <c r="Q834" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="835" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A835" t="s">
+        <v>427</v>
+      </c>
+      <c r="B835">
+        <v>-35.574167000000003</v>
+      </c>
+      <c r="C835">
+        <v>138.61528000000001</v>
+      </c>
+      <c r="D835" s="2">
+        <v>46135</v>
+      </c>
+      <c r="E835" s="20">
+        <v>0.49652777777777779</v>
+      </c>
+      <c r="G835">
+        <v>222</v>
+      </c>
+      <c r="I835">
+        <v>56</v>
+      </c>
+      <c r="J835">
+        <v>0</v>
+      </c>
+      <c r="L835">
+        <v>111</v>
+      </c>
+      <c r="N835">
+        <v>222</v>
+      </c>
+      <c r="O835">
+        <v>722</v>
+      </c>
+      <c r="P835">
+        <v>1333</v>
+      </c>
+      <c r="Q835" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="836" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A836" t="s">
+        <v>89</v>
+      </c>
+      <c r="B836">
+        <v>-35.6048446</v>
+      </c>
+      <c r="C836">
+        <v>138.59278499999999</v>
+      </c>
+      <c r="D836" s="2">
+        <v>46135</v>
+      </c>
+      <c r="E836" s="20">
+        <v>0.48749999999999999</v>
+      </c>
+      <c r="H836">
+        <v>111</v>
+      </c>
+      <c r="I836">
+        <v>1667</v>
+      </c>
+      <c r="J836">
+        <v>0</v>
+      </c>
+      <c r="L836">
+        <v>56</v>
+      </c>
+      <c r="N836">
+        <v>167</v>
+      </c>
+      <c r="O836">
+        <v>278</v>
+      </c>
+      <c r="P836">
+        <v>2279</v>
+      </c>
+      <c r="Q836" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="837" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A837" t="s">
+        <v>426</v>
+      </c>
+      <c r="B837">
+        <v>-35.620086000000001</v>
+      </c>
+      <c r="C837">
+        <v>138.56635800000001</v>
+      </c>
+      <c r="D837" s="2">
+        <v>46135</v>
+      </c>
+      <c r="E837" s="20">
+        <v>0.47708333333333336</v>
+      </c>
+      <c r="G837">
+        <v>56</v>
+      </c>
+      <c r="J837">
+        <v>0</v>
+      </c>
+      <c r="L837">
+        <v>56</v>
+      </c>
+      <c r="N837">
+        <v>167</v>
+      </c>
+      <c r="O837">
+        <v>222</v>
+      </c>
+      <c r="P837">
+        <v>501</v>
+      </c>
+      <c r="Q837" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="838" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A838" t="s">
+        <v>428</v>
+      </c>
+      <c r="B838">
+        <v>35.591330800000001</v>
+      </c>
+      <c r="C838">
+        <v>137.5061887</v>
+      </c>
+      <c r="D838" s="2">
+        <v>46136</v>
+      </c>
+      <c r="E838" s="20">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="F838">
+        <v>0</v>
+      </c>
+      <c r="G838">
+        <v>0</v>
+      </c>
+      <c r="H838">
+        <v>778</v>
+      </c>
+      <c r="I838">
+        <v>667</v>
+      </c>
+      <c r="J838">
+        <v>0</v>
+      </c>
+      <c r="K838">
+        <v>0</v>
+      </c>
+      <c r="L838">
+        <v>778</v>
+      </c>
+      <c r="M838">
+        <v>0</v>
+      </c>
+      <c r="N838">
+        <v>0</v>
+      </c>
+      <c r="O838">
+        <v>0</v>
+      </c>
+      <c r="P838">
+        <v>2223</v>
+      </c>
+      <c r="Q838" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="839" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A839" t="s">
+        <v>290</v>
+      </c>
+      <c r="B839">
+        <v>-34.629179999999998</v>
+      </c>
+      <c r="C839">
+        <v>135.86635000000001</v>
+      </c>
+      <c r="D839" s="2">
+        <v>46136</v>
+      </c>
+      <c r="I839">
+        <v>160</v>
+      </c>
+      <c r="J839">
+        <v>11</v>
+      </c>
+      <c r="L839">
+        <v>311</v>
+      </c>
+      <c r="O839">
+        <v>93</v>
+      </c>
+      <c r="P839">
+        <v>564</v>
+      </c>
+      <c r="Q839" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="840" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A840" t="s">
+        <v>341</v>
+      </c>
+      <c r="B840">
+        <v>-35.500242</v>
+      </c>
+      <c r="C840">
+        <v>138.24491</v>
+      </c>
+      <c r="D840" s="2">
+        <v>46137</v>
+      </c>
+      <c r="E840" s="20">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="F840">
+        <v>0</v>
+      </c>
+      <c r="H840">
+        <v>278</v>
+      </c>
+      <c r="I840">
+        <v>222</v>
+      </c>
+      <c r="J840">
+        <v>0</v>
+      </c>
+      <c r="L840">
+        <v>1000</v>
+      </c>
+      <c r="N840">
+        <v>1056</v>
+      </c>
+      <c r="O840">
+        <v>222</v>
+      </c>
+      <c r="P840">
+        <v>2778</v>
+      </c>
+      <c r="Q840" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="841" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A841" t="s">
+        <v>314</v>
+      </c>
+      <c r="B841">
+        <v>-35.445188000000002</v>
+      </c>
+      <c r="C841">
+        <v>138.307266</v>
+      </c>
+      <c r="D841" s="2">
+        <v>46139</v>
+      </c>
+      <c r="E841" s="20">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="I841">
+        <v>0</v>
+      </c>
+      <c r="J841">
+        <v>0</v>
+      </c>
+      <c r="L841">
+        <v>611</v>
+      </c>
+      <c r="N841">
+        <v>0</v>
+      </c>
+      <c r="O841">
+        <v>56</v>
+      </c>
+      <c r="P841">
+        <v>667</v>
+      </c>
+      <c r="Q841" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="842" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A842" t="s">
+        <v>429</v>
+      </c>
+      <c r="B842">
+        <v>-35.410254000000002</v>
+      </c>
+      <c r="C842">
+        <v>138.32751999999999</v>
+      </c>
+      <c r="D842" s="2">
+        <v>46139</v>
+      </c>
+      <c r="E842" s="20">
+        <v>0.30208333333333331</v>
+      </c>
+      <c r="H842">
+        <v>0</v>
+      </c>
+      <c r="I842">
+        <v>0</v>
+      </c>
+      <c r="J842">
+        <v>0</v>
+      </c>
+      <c r="K842">
+        <v>0</v>
+      </c>
+      <c r="L842">
+        <v>56</v>
+      </c>
+      <c r="M842">
+        <v>0</v>
+      </c>
+      <c r="N842">
+        <v>0</v>
+      </c>
+      <c r="P842">
+        <v>56</v>
+      </c>
+      <c r="Q842" t="s">
+        <v>352</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q831">
-    <sortCondition ref="D2:D831"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q842">
+    <sortCondition ref="D2:D842"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/MASTER spreadsheet of community summaries.xlsx
+++ b/MASTER spreadsheet of community summaries.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\peri\Dropbox\Delta\Projects\Laboratory\Algal blooms, bacterial counts  for community\For Luke's HAB data display\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\a1675510\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E01EE52-D29F-4CA3-80A3-5D409C13E3F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51E8E6DC-6B75-4E25-8A63-133AF91D28A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{9286397E-2757-492B-865A-39B2D6A15FF6}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{9286397E-2757-492B-865A-39B2D6A15FF6}"/>
   </bookViews>
   <sheets>
     <sheet name="Cells per mL" sheetId="1" r:id="rId1"/>
@@ -1816,29 +1816,29 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F307807-E5C9-4450-88E0-159CBB3E9A67}">
   <dimension ref="A1:T842"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="39.33203125" customWidth="1"/>
-    <col min="2" max="2" width="17.77734375" customWidth="1"/>
-    <col min="3" max="3" width="14.6640625" customWidth="1"/>
-    <col min="4" max="4" width="13.109375" customWidth="1"/>
-    <col min="5" max="5" width="16.6640625" style="20" customWidth="1"/>
+    <col min="1" max="1" width="39.36328125" customWidth="1"/>
+    <col min="2" max="2" width="17.81640625" customWidth="1"/>
+    <col min="3" max="3" width="14.6328125" customWidth="1"/>
+    <col min="4" max="4" width="13.08984375" customWidth="1"/>
+    <col min="5" max="5" width="16.6328125" style="20" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="15.44140625" customWidth="1"/>
-    <col min="8" max="8" width="11.88671875" customWidth="1"/>
-    <col min="9" max="9" width="14.109375" customWidth="1"/>
-    <col min="10" max="10" width="11.88671875" customWidth="1"/>
-    <col min="11" max="11" width="14.109375" customWidth="1"/>
-    <col min="12" max="12" width="10.44140625" customWidth="1"/>
-    <col min="13" max="13" width="15.5546875" customWidth="1"/>
+    <col min="7" max="7" width="15.453125" customWidth="1"/>
+    <col min="8" max="8" width="11.90625" customWidth="1"/>
+    <col min="9" max="9" width="14.08984375" customWidth="1"/>
+    <col min="10" max="10" width="11.90625" customWidth="1"/>
+    <col min="11" max="11" width="14.08984375" customWidth="1"/>
+    <col min="12" max="12" width="10.453125" customWidth="1"/>
+    <col min="13" max="13" width="15.54296875" customWidth="1"/>
     <col min="14" max="14" width="13" customWidth="1"/>
-    <col min="15" max="15" width="7.6640625" customWidth="1"/>
-    <col min="16" max="16" width="12.44140625" customWidth="1"/>
-    <col min="17" max="17" width="10.33203125" customWidth="1"/>
+    <col min="15" max="15" width="7.6328125" customWidth="1"/>
+    <col min="16" max="16" width="12.453125" customWidth="1"/>
+    <col min="17" max="17" width="10.36328125" customWidth="1"/>
     <col min="18" max="18" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" ht="35" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1891,7 +1891,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1920,7 +1920,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -1958,7 +1958,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -1999,7 +1999,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -2034,7 +2034,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -2078,7 +2078,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -2122,7 +2122,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -2160,7 +2160,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -2201,7 +2201,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>92</v>
       </c>
@@ -2227,7 +2227,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>91</v>
       </c>
@@ -2253,7 +2253,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>86</v>
       </c>
@@ -2279,7 +2279,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>87</v>
       </c>
@@ -2305,7 +2305,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>88</v>
       </c>
@@ -2331,7 +2331,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>89</v>
       </c>
@@ -2357,7 +2357,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>90</v>
       </c>
@@ -2383,7 +2383,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>91</v>
       </c>
@@ -2409,7 +2409,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>93</v>
       </c>
@@ -2435,7 +2435,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>8</v>
       </c>
@@ -2479,7 +2479,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>9</v>
       </c>
@@ -2511,7 +2511,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>10</v>
       </c>
@@ -2543,7 +2543,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>93</v>
       </c>
@@ -2569,7 +2569,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>8</v>
       </c>
@@ -2613,7 +2613,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>11</v>
       </c>
@@ -2660,7 +2660,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>12</v>
       </c>
@@ -2692,7 +2692,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>13</v>
       </c>
@@ -2733,7 +2733,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>14</v>
       </c>
@@ -2777,7 +2777,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>15</v>
       </c>
@@ -2818,7 +2818,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>5</v>
       </c>
@@ -2856,7 +2856,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>16</v>
       </c>
@@ -2888,7 +2888,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>94</v>
       </c>
@@ -2914,7 +2914,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>17</v>
       </c>
@@ -2958,7 +2958,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>95</v>
       </c>
@@ -2990,7 +2990,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>96</v>
       </c>
@@ -3019,7 +3019,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>18</v>
       </c>
@@ -3060,7 +3060,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>19</v>
       </c>
@@ -3104,7 +3104,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>20</v>
       </c>
@@ -3148,7 +3148,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>21</v>
       </c>
@@ -3189,7 +3189,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>22</v>
       </c>
@@ -3239,7 +3239,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>23</v>
       </c>
@@ -3286,7 +3286,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>97</v>
       </c>
@@ -3318,7 +3318,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>98</v>
       </c>
@@ -3353,7 +3353,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>99</v>
       </c>
@@ -3382,7 +3382,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>87</v>
       </c>
@@ -3408,7 +3408,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>100</v>
       </c>
@@ -3437,7 +3437,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>88</v>
       </c>
@@ -3466,7 +3466,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>86</v>
       </c>
@@ -3495,7 +3495,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>101</v>
       </c>
@@ -3524,7 +3524,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>90</v>
       </c>
@@ -3553,7 +3553,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>102</v>
       </c>
@@ -3594,7 +3594,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>103</v>
       </c>
@@ -3632,7 +3632,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>104</v>
       </c>
@@ -3661,7 +3661,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>24</v>
       </c>
@@ -3699,7 +3699,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>105</v>
       </c>
@@ -3731,7 +3731,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>106</v>
       </c>
@@ -3763,7 +3763,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>107</v>
       </c>
@@ -3795,7 +3795,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>108</v>
       </c>
@@ -3827,7 +3827,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>25</v>
       </c>
@@ -3865,7 +3865,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>19</v>
       </c>
@@ -3903,7 +3903,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>26</v>
       </c>
@@ -3944,7 +3944,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>27</v>
       </c>
@@ -3982,7 +3982,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>20</v>
       </c>
@@ -4020,7 +4020,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>105</v>
       </c>
@@ -4052,7 +4052,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>109</v>
       </c>
@@ -4084,7 +4084,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>110</v>
       </c>
@@ -4116,7 +4116,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>111</v>
       </c>
@@ -4148,7 +4148,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>112</v>
       </c>
@@ -4180,7 +4180,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>113</v>
       </c>
@@ -4212,7 +4212,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>105</v>
       </c>
@@ -4244,7 +4244,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>114</v>
       </c>
@@ -4276,7 +4276,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>28</v>
       </c>
@@ -4320,7 +4320,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>28</v>
       </c>
@@ -4362,7 +4362,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>28</v>
       </c>
@@ -4404,7 +4404,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>28</v>
       </c>
@@ -4446,7 +4446,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>28</v>
       </c>
@@ -4490,7 +4490,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>28</v>
       </c>
@@ -4534,7 +4534,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>115</v>
       </c>
@@ -4563,7 +4563,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>116</v>
       </c>
@@ -4592,7 +4592,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>157</v>
       </c>
@@ -4621,7 +4621,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>158</v>
       </c>
@@ -4647,7 +4647,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>29</v>
       </c>
@@ -4691,7 +4691,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>30</v>
       </c>
@@ -4735,7 +4735,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>31</v>
       </c>
@@ -4782,7 +4782,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>32</v>
       </c>
@@ -4826,7 +4826,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>33</v>
       </c>
@@ -4872,7 +4872,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>153</v>
       </c>
@@ -4904,7 +4904,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>155</v>
       </c>
@@ -4930,7 +4930,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>156</v>
       </c>
@@ -4956,7 +4956,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>159</v>
       </c>
@@ -4985,7 +4985,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>34</v>
       </c>
@@ -5032,7 +5032,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A91" s="2" t="s">
         <v>35</v>
       </c>
@@ -5073,7 +5073,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>36</v>
       </c>
@@ -5105,7 +5105,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>37</v>
       </c>
@@ -5147,7 +5147,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>153</v>
       </c>
@@ -5173,7 +5173,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>154</v>
       </c>
@@ -5199,7 +5199,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>94</v>
       </c>
@@ -5228,7 +5228,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>140</v>
       </c>
@@ -5254,7 +5254,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>141</v>
       </c>
@@ -5286,7 +5286,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>152</v>
       </c>
@@ -5312,7 +5312,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>160</v>
       </c>
@@ -5341,7 +5341,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>34</v>
       </c>
@@ -5385,7 +5385,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>38</v>
       </c>
@@ -5420,7 +5420,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>39</v>
       </c>
@@ -5461,7 +5461,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>40</v>
       </c>
@@ -5499,7 +5499,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>41</v>
       </c>
@@ -5537,7 +5537,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>41</v>
       </c>
@@ -5578,7 +5578,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>92</v>
       </c>
@@ -5607,7 +5607,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>42</v>
       </c>
@@ -5639,7 +5639,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>43</v>
       </c>
@@ -5683,7 +5683,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>86</v>
       </c>
@@ -5715,7 +5715,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>101</v>
       </c>
@@ -5744,7 +5744,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>87</v>
       </c>
@@ -5776,7 +5776,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>88</v>
       </c>
@@ -5802,7 +5802,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>89</v>
       </c>
@@ -5831,7 +5831,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>90</v>
       </c>
@@ -5857,7 +5857,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>44</v>
       </c>
@@ -5901,7 +5901,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>45</v>
       </c>
@@ -5945,7 +5945,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>46</v>
       </c>
@@ -5986,7 +5986,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>47</v>
       </c>
@@ -6024,7 +6024,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>48</v>
       </c>
@@ -6065,7 +6065,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>49</v>
       </c>
@@ -6103,7 +6103,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>5</v>
       </c>
@@ -6150,7 +6150,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>37</v>
       </c>
@@ -6191,7 +6191,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>77</v>
       </c>
@@ -6223,7 +6223,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>80</v>
       </c>
@@ -6255,7 +6255,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>130</v>
       </c>
@@ -6290,7 +6290,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>117</v>
       </c>
@@ -6319,7 +6319,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>118</v>
       </c>
@@ -6345,7 +6345,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>81</v>
       </c>
@@ -6377,7 +6377,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>161</v>
       </c>
@@ -6406,7 +6406,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="131" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>79</v>
       </c>
@@ -6438,7 +6438,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="132" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>157</v>
       </c>
@@ -6467,7 +6467,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="133" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>158</v>
       </c>
@@ -6499,7 +6499,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="134" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>125</v>
       </c>
@@ -6531,7 +6531,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="135" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>126</v>
       </c>
@@ -6572,7 +6572,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="136" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>127</v>
       </c>
@@ -6610,7 +6610,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="137" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>128</v>
       </c>
@@ -6648,7 +6648,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="138" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>132</v>
       </c>
@@ -6689,7 +6689,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>133</v>
       </c>
@@ -6730,7 +6730,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="140" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>134</v>
       </c>
@@ -6768,7 +6768,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="141" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>135</v>
       </c>
@@ -6806,7 +6806,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="142" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>136</v>
       </c>
@@ -6841,7 +6841,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="143" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>137</v>
       </c>
@@ -6876,7 +6876,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="144" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>138</v>
       </c>
@@ -6914,7 +6914,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="145" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>139</v>
       </c>
@@ -6949,7 +6949,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="146" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>37</v>
       </c>
@@ -6990,7 +6990,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="147" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>119</v>
       </c>
@@ -7028,7 +7028,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="148" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>120</v>
       </c>
@@ -7063,7 +7063,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="149" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>79</v>
       </c>
@@ -7098,7 +7098,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="150" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>236</v>
       </c>
@@ -7133,7 +7133,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="151" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>85</v>
       </c>
@@ -7165,7 +7165,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="152" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
         <v>18</v>
       </c>
@@ -7206,7 +7206,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="153" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
         <v>50</v>
       </c>
@@ -7244,7 +7244,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="154" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>27</v>
       </c>
@@ -7279,7 +7279,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="155" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
         <v>37</v>
       </c>
@@ -7320,7 +7320,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="156" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>79</v>
       </c>
@@ -7352,7 +7352,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="157" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
         <v>131</v>
       </c>
@@ -7384,7 +7384,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="158" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
         <v>236</v>
       </c>
@@ -7419,7 +7419,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="159" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>85</v>
       </c>
@@ -7451,7 +7451,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="160" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
         <v>51</v>
       </c>
@@ -7489,7 +7489,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="161" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>121</v>
       </c>
@@ -7521,7 +7521,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="162" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
         <v>18</v>
       </c>
@@ -7562,7 +7562,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="163" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
         <v>122</v>
       </c>
@@ -7591,7 +7591,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="164" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>79</v>
       </c>
@@ -7623,7 +7623,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="165" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
         <v>236</v>
       </c>
@@ -7655,7 +7655,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="166" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
         <v>85</v>
       </c>
@@ -7687,7 +7687,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="167" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
         <v>52</v>
       </c>
@@ -7731,7 +7731,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="168" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
         <v>53</v>
       </c>
@@ -7775,7 +7775,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="169" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
         <v>37</v>
       </c>
@@ -7816,7 +7816,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="170" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
         <v>82</v>
       </c>
@@ -7848,7 +7848,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="171" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
         <v>82</v>
       </c>
@@ -7880,7 +7880,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="172" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
         <v>84</v>
       </c>
@@ -7912,7 +7912,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="173" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
         <v>84</v>
       </c>
@@ -7944,7 +7944,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="174" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
         <v>54</v>
       </c>
@@ -7982,7 +7982,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="175" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
         <v>55</v>
       </c>
@@ -8020,7 +8020,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="176" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
         <v>56</v>
       </c>
@@ -8058,7 +8058,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="177" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
         <v>57</v>
       </c>
@@ -8093,7 +8093,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="178" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
         <v>58</v>
       </c>
@@ -8134,7 +8134,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="179" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
         <v>59</v>
       </c>
@@ -8169,7 +8169,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="180" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
         <v>15</v>
       </c>
@@ -8210,7 +8210,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="181" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
         <v>15</v>
       </c>
@@ -8251,7 +8251,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="182" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
         <v>60</v>
       </c>
@@ -8292,7 +8292,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="183" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
         <v>37</v>
       </c>
@@ -8333,7 +8333,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="184" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
         <v>131</v>
       </c>
@@ -8365,7 +8365,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="185" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
         <v>61</v>
       </c>
@@ -8406,7 +8406,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="186" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
         <v>62</v>
       </c>
@@ -8444,7 +8444,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="187" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
         <v>63</v>
       </c>
@@ -8482,7 +8482,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="188" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
         <v>94</v>
       </c>
@@ -8511,7 +8511,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="189" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
         <v>176</v>
       </c>
@@ -8552,7 +8552,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="190" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
         <v>79</v>
       </c>
@@ -8587,7 +8587,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="191" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
         <v>236</v>
       </c>
@@ -8619,7 +8619,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="192" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
         <v>85</v>
       </c>
@@ -8651,7 +8651,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="193" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
         <v>37</v>
       </c>
@@ -8692,7 +8692,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="194" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
         <v>130</v>
       </c>
@@ -8727,7 +8727,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="195" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
         <v>83</v>
       </c>
@@ -8759,7 +8759,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="196" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
         <v>18</v>
       </c>
@@ -8803,7 +8803,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="197" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
         <v>86</v>
       </c>
@@ -8832,7 +8832,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="198" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
         <v>100</v>
       </c>
@@ -8870,7 +8870,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="199" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
         <v>87</v>
       </c>
@@ -8914,7 +8914,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="200" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
         <v>123</v>
       </c>
@@ -8952,7 +8952,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="201" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
         <v>124</v>
       </c>
@@ -8981,7 +8981,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="202" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
         <v>89</v>
       </c>
@@ -9013,7 +9013,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="203" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
         <v>90</v>
       </c>
@@ -9048,7 +9048,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="204" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
         <v>25</v>
       </c>
@@ -9095,7 +9095,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="205" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
         <v>79</v>
       </c>
@@ -9127,7 +9127,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="206" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
         <v>130</v>
       </c>
@@ -9159,7 +9159,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="207" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
         <v>85</v>
       </c>
@@ -9191,7 +9191,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="208" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
         <v>37</v>
       </c>
@@ -9229,7 +9229,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="209" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
         <v>162</v>
       </c>
@@ -9264,7 +9264,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="210" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
         <v>162</v>
       </c>
@@ -9296,7 +9296,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="211" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
         <v>162</v>
       </c>
@@ -9328,7 +9328,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="212" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
         <v>142</v>
       </c>
@@ -9354,7 +9354,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="213" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
         <v>144</v>
       </c>
@@ -9380,7 +9380,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="214" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
         <v>145</v>
       </c>
@@ -9406,7 +9406,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="215" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
         <v>146</v>
       </c>
@@ -9432,7 +9432,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="216" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
         <v>37</v>
       </c>
@@ -9470,7 +9470,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="217" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
         <v>142</v>
       </c>
@@ -9496,7 +9496,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="218" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
         <v>144</v>
       </c>
@@ -9522,7 +9522,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="219" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
         <v>145</v>
       </c>
@@ -9548,7 +9548,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="220" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
         <v>146</v>
       </c>
@@ -9574,7 +9574,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="221" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
         <v>18</v>
       </c>
@@ -9618,7 +9618,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="222" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
         <v>79</v>
       </c>
@@ -9650,7 +9650,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="223" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
         <v>130</v>
       </c>
@@ -9683,7 +9683,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="224" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
         <v>236</v>
       </c>
@@ -9716,7 +9716,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="225" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
         <v>85</v>
       </c>
@@ -9749,7 +9749,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="226" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
         <v>142</v>
       </c>
@@ -9775,7 +9775,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="227" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
         <v>59</v>
       </c>
@@ -9819,7 +9819,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="228" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
         <v>37</v>
       </c>
@@ -9863,7 +9863,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="229" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
         <v>147</v>
       </c>
@@ -9889,7 +9889,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="230" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A230" s="7" t="s">
         <v>168</v>
       </c>
@@ -9940,7 +9940,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="231" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
         <v>79</v>
       </c>
@@ -9972,7 +9972,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="232" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
         <v>236</v>
       </c>
@@ -10004,7 +10004,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="233" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
         <v>85</v>
       </c>
@@ -10036,7 +10036,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="234" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
         <v>59</v>
       </c>
@@ -10062,7 +10062,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="235" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
         <v>156</v>
       </c>
@@ -10100,7 +10100,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="236" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
         <v>154</v>
       </c>
@@ -10135,7 +10135,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="237" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
         <v>37</v>
       </c>
@@ -10179,7 +10179,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="238" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
         <v>141</v>
       </c>
@@ -10211,7 +10211,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="239" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
         <v>93</v>
       </c>
@@ -10246,7 +10246,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="240" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
         <v>152</v>
       </c>
@@ -10281,7 +10281,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="241" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
         <v>142</v>
       </c>
@@ -10307,7 +10307,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="242" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
         <v>145</v>
       </c>
@@ -10333,7 +10333,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="243" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
         <v>146</v>
       </c>
@@ -10359,7 +10359,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="244" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
         <v>142</v>
       </c>
@@ -10385,7 +10385,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="245" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
         <v>148</v>
       </c>
@@ -10411,7 +10411,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="246" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
         <v>163</v>
       </c>
@@ -10449,7 +10449,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="247" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
         <v>164</v>
       </c>
@@ -10481,7 +10481,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="248" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
         <v>59</v>
       </c>
@@ -10513,7 +10513,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="249" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A249" s="7" t="s">
         <v>167</v>
       </c>
@@ -10548,7 +10548,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="250" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
         <v>142</v>
       </c>
@@ -10574,7 +10574,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="251" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
         <v>177</v>
       </c>
@@ -10609,7 +10609,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="252" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
         <v>37</v>
       </c>
@@ -10656,7 +10656,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="253" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
         <v>142</v>
       </c>
@@ -10682,7 +10682,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="254" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
         <v>150</v>
       </c>
@@ -10708,7 +10708,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="255" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
         <v>38</v>
       </c>
@@ -10755,7 +10755,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="256" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
         <v>165</v>
       </c>
@@ -10790,7 +10790,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="257" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
         <v>88</v>
       </c>
@@ -10825,7 +10825,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="258" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A258" s="7" t="s">
         <v>166</v>
       </c>
@@ -10874,7 +10874,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="259" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
         <v>89</v>
       </c>
@@ -10903,7 +10903,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="260" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
         <v>174</v>
       </c>
@@ -10941,7 +10941,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="261" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
         <v>175</v>
       </c>
@@ -10970,7 +10970,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="262" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
         <v>59</v>
       </c>
@@ -11005,7 +11005,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="263" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
         <v>37</v>
       </c>
@@ -11052,7 +11052,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="264" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A264" s="7" t="s">
         <v>169</v>
       </c>
@@ -11098,7 +11098,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="265" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A265" s="7" t="s">
         <v>171</v>
       </c>
@@ -11145,7 +11145,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="266" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A266" s="7" t="s">
         <v>172</v>
       </c>
@@ -11192,7 +11192,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="267" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A267" s="7" t="s">
         <v>170</v>
       </c>
@@ -11240,7 +11240,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="268" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A268" s="7" t="s">
         <v>173</v>
       </c>
@@ -11287,7 +11287,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="269" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
         <v>178</v>
       </c>
@@ -11331,7 +11331,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="270" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
         <v>37</v>
       </c>
@@ -11378,7 +11378,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="271" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
         <v>181</v>
       </c>
@@ -11419,7 +11419,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="272" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
         <v>182</v>
       </c>
@@ -11463,7 +11463,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="273" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
         <v>79</v>
       </c>
@@ -11498,7 +11498,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="274" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
         <v>236</v>
       </c>
@@ -11533,7 +11533,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="275" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
         <v>85</v>
       </c>
@@ -11568,7 +11568,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="276" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
         <v>179</v>
       </c>
@@ -11603,7 +11603,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="277" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
         <v>121</v>
       </c>
@@ -11638,7 +11638,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="278" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
         <v>92</v>
       </c>
@@ -11658,7 +11658,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="279" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
         <v>94</v>
       </c>
@@ -11693,7 +11693,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="280" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
         <v>186</v>
       </c>
@@ -11713,7 +11713,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="281" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
         <v>92</v>
       </c>
@@ -11733,7 +11733,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="282" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
         <v>183</v>
       </c>
@@ -11783,7 +11783,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="283" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
         <v>184</v>
       </c>
@@ -11833,7 +11833,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="284" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
         <v>185</v>
       </c>
@@ -11883,7 +11883,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="285" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
         <v>79</v>
       </c>
@@ -11918,7 +11918,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="286" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
         <v>236</v>
       </c>
@@ -11953,7 +11953,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="287" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
         <v>85</v>
       </c>
@@ -11988,7 +11988,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="288" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
         <v>86</v>
       </c>
@@ -12023,7 +12023,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="289" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
         <v>100</v>
       </c>
@@ -12061,7 +12061,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="290" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
         <v>87</v>
       </c>
@@ -12093,7 +12093,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="291" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
         <v>88</v>
       </c>
@@ -12122,7 +12122,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="292" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
         <v>89</v>
       </c>
@@ -12145,7 +12145,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="293" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
         <v>174</v>
       </c>
@@ -12183,7 +12183,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="294" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
         <v>91</v>
       </c>
@@ -12203,7 +12203,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="295" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
         <v>188</v>
       </c>
@@ -12223,7 +12223,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="296" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A296" s="10" t="s">
         <v>199</v>
       </c>
@@ -12273,7 +12273,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="297" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A297" s="10" t="s">
         <v>200</v>
       </c>
@@ -12323,7 +12323,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="298" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
         <v>59</v>
       </c>
@@ -12370,7 +12370,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="299" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
         <v>212</v>
       </c>
@@ -12390,7 +12390,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="300" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
         <v>188</v>
       </c>
@@ -12410,7 +12410,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="301" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
         <v>91</v>
       </c>
@@ -12430,7 +12430,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="302" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
         <v>186</v>
       </c>
@@ -12450,7 +12450,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="303" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
         <v>189</v>
       </c>
@@ -12470,7 +12470,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="304" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
         <v>92</v>
       </c>
@@ -12490,7 +12490,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="305" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
         <v>190</v>
       </c>
@@ -12510,7 +12510,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="306" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
         <v>37</v>
       </c>
@@ -12554,7 +12554,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="307" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
         <v>192</v>
       </c>
@@ -12589,7 +12589,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="308" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A308" t="s">
         <v>191</v>
       </c>
@@ -12624,7 +12624,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="309" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A309" t="s">
         <v>193</v>
       </c>
@@ -12659,7 +12659,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="310" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
         <v>94</v>
       </c>
@@ -12697,7 +12697,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="311" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A311" s="10" t="s">
         <v>198</v>
       </c>
@@ -12745,7 +12745,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="312" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A312" s="9" t="s">
         <v>196</v>
       </c>
@@ -12795,7 +12795,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="313" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A313" s="10" t="s">
         <v>201</v>
       </c>
@@ -12845,7 +12845,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="314" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A314" s="9" t="s">
         <v>202</v>
       </c>
@@ -12895,7 +12895,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="315" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
         <v>194</v>
       </c>
@@ -12924,7 +12924,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="316" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
         <v>195</v>
       </c>
@@ -12959,7 +12959,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="317" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A317" s="10" t="s">
         <v>203</v>
       </c>
@@ -13009,7 +13009,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="318" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A318" s="9" t="s">
         <v>196</v>
       </c>
@@ -13059,7 +13059,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="319" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A319" s="10" t="s">
         <v>197</v>
       </c>
@@ -13109,7 +13109,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="320" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
         <v>178</v>
       </c>
@@ -13153,7 +13153,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="321" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
         <v>205</v>
       </c>
@@ -13203,7 +13203,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="322" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
         <v>206</v>
       </c>
@@ -13253,7 +13253,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="323" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
         <v>209</v>
       </c>
@@ -13303,7 +13303,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="324" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
         <v>79</v>
       </c>
@@ -13338,7 +13338,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="325" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
         <v>204</v>
       </c>
@@ -13373,7 +13373,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="326" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
         <v>85</v>
       </c>
@@ -13408,7 +13408,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="327" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
         <v>198</v>
       </c>
@@ -13458,7 +13458,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="328" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
         <v>94</v>
       </c>
@@ -13490,7 +13490,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="329" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A329" t="s">
         <v>86</v>
       </c>
@@ -13528,7 +13528,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="330" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A330" t="s">
         <v>211</v>
       </c>
@@ -13563,7 +13563,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="331" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A331" t="s">
         <v>87</v>
       </c>
@@ -13598,7 +13598,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="332" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A332" t="s">
         <v>210</v>
       </c>
@@ -13648,7 +13648,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="333" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A333" t="s">
         <v>207</v>
       </c>
@@ -13698,7 +13698,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="334" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A334" t="s">
         <v>208</v>
       </c>
@@ -13745,7 +13745,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="335" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A335" t="s">
         <v>212</v>
       </c>
@@ -13765,7 +13765,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="336" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A336" t="s">
         <v>186</v>
       </c>
@@ -13785,7 +13785,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="337" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A337" t="s">
         <v>91</v>
       </c>
@@ -13805,7 +13805,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="338" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A338" t="s">
         <v>92</v>
       </c>
@@ -13825,7 +13825,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="339" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A339" t="s">
         <v>213</v>
       </c>
@@ -13845,7 +13845,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="340" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A340" t="s">
         <v>214</v>
       </c>
@@ -13865,7 +13865,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="341" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A341" t="s">
         <v>212</v>
       </c>
@@ -13885,7 +13885,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="342" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A342" t="s">
         <v>91</v>
       </c>
@@ -13905,7 +13905,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="343" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A343" t="s">
         <v>186</v>
       </c>
@@ -13925,7 +13925,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="344" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A344" t="s">
         <v>214</v>
       </c>
@@ -13945,7 +13945,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="345" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A345" t="s">
         <v>189</v>
       </c>
@@ -13965,7 +13965,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="346" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A346" t="s">
         <v>92</v>
       </c>
@@ -13985,7 +13985,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="347" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A347" t="s">
         <v>178</v>
       </c>
@@ -14032,7 +14032,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="348" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A348" t="s">
         <v>156</v>
       </c>
@@ -14070,7 +14070,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="349" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A349" t="s">
         <v>37</v>
       </c>
@@ -14114,7 +14114,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="350" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A350" t="s">
         <v>231</v>
       </c>
@@ -14149,7 +14149,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="351" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A351" t="s">
         <v>220</v>
       </c>
@@ -14199,7 +14199,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="352" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A352" t="s">
         <v>225</v>
       </c>
@@ -14249,7 +14249,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="353" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A353" t="s">
         <v>179</v>
       </c>
@@ -14299,7 +14299,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="354" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A354" t="s">
         <v>154</v>
       </c>
@@ -14337,7 +14337,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="355" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A355" t="s">
         <v>221</v>
       </c>
@@ -14387,7 +14387,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="356" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A356" t="s">
         <v>295</v>
       </c>
@@ -14416,7 +14416,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="357" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A357" t="s">
         <v>296</v>
       </c>
@@ -14451,7 +14451,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="358" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A358" t="s">
         <v>222</v>
       </c>
@@ -14501,7 +14501,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="359" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A359" t="s">
         <v>223</v>
       </c>
@@ -14551,7 +14551,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="360" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A360" t="s">
         <v>94</v>
       </c>
@@ -14589,7 +14589,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="361" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A361" t="s">
         <v>89</v>
       </c>
@@ -14627,7 +14627,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="362" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A362" t="s">
         <v>18</v>
       </c>
@@ -14662,7 +14662,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="363" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A363" t="s">
         <v>215</v>
       </c>
@@ -14703,7 +14703,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="364" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A364" t="s">
         <v>216</v>
       </c>
@@ -14735,7 +14735,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="365" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A365" t="s">
         <v>217</v>
       </c>
@@ -14773,7 +14773,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="366" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A366" t="s">
         <v>218</v>
       </c>
@@ -14811,7 +14811,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="367" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A367" t="s">
         <v>212</v>
       </c>
@@ -14834,7 +14834,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="368" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A368" t="s">
         <v>186</v>
       </c>
@@ -14857,7 +14857,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="369" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A369" t="s">
         <v>91</v>
       </c>
@@ -14880,7 +14880,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="370" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A370" t="s">
         <v>92</v>
       </c>
@@ -14903,7 +14903,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="371" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A371" t="s">
         <v>190</v>
       </c>
@@ -14926,7 +14926,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="372" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A372" t="s">
         <v>224</v>
       </c>
@@ -14949,7 +14949,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="373" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A373" t="s">
         <v>59</v>
       </c>
@@ -14993,7 +14993,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="374" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A374" t="s">
         <v>229</v>
       </c>
@@ -15028,7 +15028,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="375" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A375" t="s">
         <v>100</v>
       </c>
@@ -15069,7 +15069,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="376" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A376" t="s">
         <v>87</v>
       </c>
@@ -15104,7 +15104,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="377" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A377" t="s">
         <v>88</v>
       </c>
@@ -15145,7 +15145,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="378" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A378" t="s">
         <v>297</v>
       </c>
@@ -15180,7 +15180,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="379" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A379" t="s">
         <v>298</v>
       </c>
@@ -15215,7 +15215,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="380" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A380" t="s">
         <v>174</v>
       </c>
@@ -15247,7 +15247,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="381" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A381" t="s">
         <v>299</v>
       </c>
@@ -15282,7 +15282,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="382" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A382" t="s">
         <v>300</v>
       </c>
@@ -15317,7 +15317,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="383" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A383" t="s">
         <v>79</v>
       </c>
@@ -15361,7 +15361,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="384" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A384" t="s">
         <v>236</v>
       </c>
@@ -15408,7 +15408,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="385" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A385" t="s">
         <v>85</v>
       </c>
@@ -15443,7 +15443,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="386" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A386" t="s">
         <v>230</v>
       </c>
@@ -15478,7 +15478,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="387" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A387" t="s">
         <v>231</v>
       </c>
@@ -15510,7 +15510,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="388" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A388" s="10" t="s">
         <v>226</v>
       </c>
@@ -15560,7 +15560,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="389" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A389" s="10" t="s">
         <v>227</v>
       </c>
@@ -15610,7 +15610,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="390" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A390" t="s">
         <v>232</v>
       </c>
@@ -15645,7 +15645,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="391" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A391" t="s">
         <v>234</v>
       </c>
@@ -15695,7 +15695,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="392" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A392" t="s">
         <v>208</v>
       </c>
@@ -15745,7 +15745,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="393" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A393" t="s">
         <v>228</v>
       </c>
@@ -15795,7 +15795,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="394" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A394" t="s">
         <v>231</v>
       </c>
@@ -15824,7 +15824,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="395" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A395" t="s">
         <v>233</v>
       </c>
@@ -15874,7 +15874,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="396" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A396" t="s">
         <v>37</v>
       </c>
@@ -15924,7 +15924,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="397" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A397" t="s">
         <v>208</v>
       </c>
@@ -15974,7 +15974,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="398" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A398" t="s">
         <v>231</v>
       </c>
@@ -16006,7 +16006,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="399" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A399" t="s">
         <v>230</v>
       </c>
@@ -16041,7 +16041,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="400" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A400" t="s">
         <v>79</v>
       </c>
@@ -16091,7 +16091,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="401" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A401" t="s">
         <v>236</v>
       </c>
@@ -16141,7 +16141,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="402" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A402" t="s">
         <v>208</v>
       </c>
@@ -16191,7 +16191,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="403" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A403" t="s">
         <v>209</v>
       </c>
@@ -16241,7 +16241,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="404" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A404" t="s">
         <v>231</v>
       </c>
@@ -16276,7 +16276,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="405" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A405" t="s">
         <v>198</v>
       </c>
@@ -16326,7 +16326,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="406" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A406" t="s">
         <v>235</v>
       </c>
@@ -16346,7 +16346,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="407" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A407" t="s">
         <v>237</v>
       </c>
@@ -16399,7 +16399,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="408" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A408" t="s">
         <v>238</v>
       </c>
@@ -16452,7 +16452,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="409" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A409" t="s">
         <v>284</v>
       </c>
@@ -16484,7 +16484,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="410" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A410" t="s">
         <v>239</v>
       </c>
@@ -16537,7 +16537,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="411" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A411" t="s">
         <v>272</v>
       </c>
@@ -16572,7 +16572,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="412" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A412" t="s">
         <v>273</v>
       </c>
@@ -16607,7 +16607,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="413" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A413" t="s">
         <v>94</v>
       </c>
@@ -16648,7 +16648,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="414" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A414" t="s">
         <v>89</v>
       </c>
@@ -16680,7 +16680,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="415" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A415" t="s">
         <v>212</v>
       </c>
@@ -16700,7 +16700,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="416" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A416" t="s">
         <v>186</v>
       </c>
@@ -16720,7 +16720,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="417" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A417" t="s">
         <v>91</v>
       </c>
@@ -16740,7 +16740,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="418" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A418" t="s">
         <v>189</v>
       </c>
@@ -16760,7 +16760,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="419" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A419" t="s">
         <v>92</v>
       </c>
@@ -16780,7 +16780,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="420" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A420" t="s">
         <v>224</v>
       </c>
@@ -16800,7 +16800,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="421" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A421" t="s">
         <v>198</v>
       </c>
@@ -16850,7 +16850,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="422" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A422" t="s">
         <v>236</v>
       </c>
@@ -16903,7 +16903,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="423" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A423" t="s">
         <v>79</v>
       </c>
@@ -16956,7 +16956,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="424" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A424" t="s">
         <v>241</v>
       </c>
@@ -17009,7 +17009,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="425" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A425" t="s">
         <v>240</v>
       </c>
@@ -17062,7 +17062,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="426" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A426" s="10" t="s">
         <v>246</v>
       </c>
@@ -17112,7 +17112,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="427" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A427" s="10" t="s">
         <v>248</v>
       </c>
@@ -17162,7 +17162,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="428" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A428" t="s">
         <v>274</v>
       </c>
@@ -17197,7 +17197,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="429" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A429" t="s">
         <v>278</v>
       </c>
@@ -17232,7 +17232,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="430" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A430" t="s">
         <v>242</v>
       </c>
@@ -17285,7 +17285,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="431" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A431" t="s">
         <v>92</v>
       </c>
@@ -17338,7 +17338,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="432" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A432" t="s">
         <v>243</v>
       </c>
@@ -17391,7 +17391,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="433" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A433" t="s">
         <v>85</v>
       </c>
@@ -17444,7 +17444,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="434" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A434" s="10" t="s">
         <v>249</v>
       </c>
@@ -17494,7 +17494,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="435" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A435" t="s">
         <v>275</v>
       </c>
@@ -17529,7 +17529,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="436" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A436" t="s">
         <v>231</v>
       </c>
@@ -17561,7 +17561,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="437" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A437" t="s">
         <v>94</v>
       </c>
@@ -17593,7 +17593,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="438" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A438" t="s">
         <v>89</v>
       </c>
@@ -17637,7 +17637,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="439" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A439" t="s">
         <v>247</v>
       </c>
@@ -17672,7 +17672,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="440" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A440" t="s">
         <v>79</v>
       </c>
@@ -17725,7 +17725,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="441" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A441" t="s">
         <v>244</v>
       </c>
@@ -17778,7 +17778,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="442" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A442" t="s">
         <v>236</v>
       </c>
@@ -17831,7 +17831,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="443" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A443" t="s">
         <v>85</v>
       </c>
@@ -17884,7 +17884,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="444" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A444" t="s">
         <v>243</v>
       </c>
@@ -17937,7 +17937,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="445" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A445" s="10" t="s">
         <v>246</v>
       </c>
@@ -17987,7 +17987,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="446" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A446" t="s">
         <v>250</v>
       </c>
@@ -18028,7 +18028,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="447" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A447" t="s">
         <v>37</v>
       </c>
@@ -18066,7 +18066,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="448" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A448" t="s">
         <v>221</v>
       </c>
@@ -18116,7 +18116,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="449" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A449" t="s">
         <v>241</v>
       </c>
@@ -18157,7 +18157,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="450" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A450" t="s">
         <v>231</v>
       </c>
@@ -18189,7 +18189,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="451" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A451" t="s">
         <v>251</v>
       </c>
@@ -18221,7 +18221,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="452" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A452" t="s">
         <v>198</v>
       </c>
@@ -18271,7 +18271,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="453" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A453" t="s">
         <v>85</v>
       </c>
@@ -18309,7 +18309,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="454" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A454" t="s">
         <v>243</v>
       </c>
@@ -18344,7 +18344,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="455" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A455" t="s">
         <v>256</v>
       </c>
@@ -18388,7 +18388,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="456" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A456" t="s">
         <v>344</v>
       </c>
@@ -18426,7 +18426,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="457" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A457" t="s">
         <v>254</v>
       </c>
@@ -18476,7 +18476,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="458" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A458" t="s">
         <v>257</v>
       </c>
@@ -18526,7 +18526,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="459" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A459" t="s">
         <v>59</v>
       </c>
@@ -18570,7 +18570,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="460" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A460" t="s">
         <v>325</v>
       </c>
@@ -18620,7 +18620,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="461" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A461" t="s">
         <v>253</v>
       </c>
@@ -18652,7 +18652,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="462" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A462" t="s">
         <v>286</v>
       </c>
@@ -18681,7 +18681,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="463" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A463" t="s">
         <v>287</v>
       </c>
@@ -18710,7 +18710,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="464" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A464" t="s">
         <v>288</v>
       </c>
@@ -18739,7 +18739,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="465" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A465" t="s">
         <v>345</v>
       </c>
@@ -18777,7 +18777,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="466" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A466" t="s">
         <v>346</v>
       </c>
@@ -18812,7 +18812,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="467" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A467" t="s">
         <v>347</v>
       </c>
@@ -18847,7 +18847,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="468" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A468" t="s">
         <v>246</v>
       </c>
@@ -18897,7 +18897,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="469" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A469" t="s">
         <v>265</v>
       </c>
@@ -18944,7 +18944,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="470" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A470" t="s">
         <v>267</v>
       </c>
@@ -18982,7 +18982,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="471" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A471" t="s">
         <v>268</v>
       </c>
@@ -19018,7 +19018,7 @@
       </c>
       <c r="T471" s="2"/>
     </row>
-    <row r="472" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A472" t="s">
         <v>85</v>
       </c>
@@ -19054,7 +19054,7 @@
       </c>
       <c r="T472" s="2"/>
     </row>
-    <row r="473" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A473" t="s">
         <v>243</v>
       </c>
@@ -19093,7 +19093,7 @@
       </c>
       <c r="T473" s="2"/>
     </row>
-    <row r="474" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A474" t="s">
         <v>244</v>
       </c>
@@ -19129,7 +19129,7 @@
       </c>
       <c r="T474" s="2"/>
     </row>
-    <row r="475" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A475" t="s">
         <v>276</v>
       </c>
@@ -19165,7 +19165,7 @@
       </c>
       <c r="T475" s="2"/>
     </row>
-    <row r="476" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A476" t="s">
         <v>277</v>
       </c>
@@ -19201,7 +19201,7 @@
       </c>
       <c r="T476" s="2"/>
     </row>
-    <row r="477" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A477" t="s">
         <v>278</v>
       </c>
@@ -19237,7 +19237,7 @@
       </c>
       <c r="T477" s="2"/>
     </row>
-    <row r="478" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A478" t="s">
         <v>243</v>
       </c>
@@ -19285,7 +19285,7 @@
       </c>
       <c r="T478" s="2"/>
     </row>
-    <row r="479" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A479" t="s">
         <v>258</v>
       </c>
@@ -19306,7 +19306,7 @@
       </c>
       <c r="T479" s="2"/>
     </row>
-    <row r="480" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A480" t="s">
         <v>210</v>
       </c>
@@ -19357,7 +19357,7 @@
       </c>
       <c r="T480" s="2"/>
     </row>
-    <row r="481" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A481" t="s">
         <v>270</v>
       </c>
@@ -19396,7 +19396,7 @@
       </c>
       <c r="T481" s="2"/>
     </row>
-    <row r="482" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A482" t="s">
         <v>269</v>
       </c>
@@ -19432,7 +19432,7 @@
       </c>
       <c r="T482" s="2"/>
     </row>
-    <row r="483" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A483" t="s">
         <v>282</v>
       </c>
@@ -19462,7 +19462,7 @@
       </c>
       <c r="T483" s="2"/>
     </row>
-    <row r="484" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A484" t="s">
         <v>259</v>
       </c>
@@ -19483,7 +19483,7 @@
       </c>
       <c r="T484" s="2"/>
     </row>
-    <row r="485" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A485" t="s">
         <v>279</v>
       </c>
@@ -19522,7 +19522,7 @@
       </c>
       <c r="T485" s="2"/>
     </row>
-    <row r="486" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A486" t="s">
         <v>280</v>
       </c>
@@ -19561,7 +19561,7 @@
       </c>
       <c r="T486" s="2"/>
     </row>
-    <row r="487" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A487" t="s">
         <v>281</v>
       </c>
@@ -19596,7 +19596,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="488" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A488" t="s">
         <v>283</v>
       </c>
@@ -19634,7 +19634,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="489" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A489" t="s">
         <v>387</v>
       </c>
@@ -19666,7 +19666,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="490" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A490" t="s">
         <v>120</v>
       </c>
@@ -19701,7 +19701,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="491" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A491" t="s">
         <v>94</v>
       </c>
@@ -19730,7 +19730,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="492" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A492" t="s">
         <v>89</v>
       </c>
@@ -19765,7 +19765,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="493" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A493" t="s">
         <v>260</v>
       </c>
@@ -19785,7 +19785,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="494" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A494" t="s">
         <v>261</v>
       </c>
@@ -19805,7 +19805,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="495" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A495" t="s">
         <v>262</v>
       </c>
@@ -19825,7 +19825,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="496" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A496" t="s">
         <v>263</v>
       </c>
@@ -19845,7 +19845,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="497" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A497" t="s">
         <v>208</v>
       </c>
@@ -19895,7 +19895,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="498" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A498" t="s">
         <v>59</v>
       </c>
@@ -19939,7 +19939,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="499" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A499" t="s">
         <v>308</v>
       </c>
@@ -19974,7 +19974,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="500" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A500" t="s">
         <v>264</v>
       </c>
@@ -19997,7 +19997,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="501" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A501" t="s">
         <v>262</v>
       </c>
@@ -20017,7 +20017,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="502" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A502" t="s">
         <v>289</v>
       </c>
@@ -20049,7 +20049,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="503" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A503" t="s">
         <v>290</v>
       </c>
@@ -20081,7 +20081,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="504" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A504" t="s">
         <v>291</v>
       </c>
@@ -20113,7 +20113,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="505" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A505" t="s">
         <v>212</v>
       </c>
@@ -20147,7 +20147,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="506" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A506" t="s">
         <v>188</v>
       </c>
@@ -20181,7 +20181,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="507" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A507" t="s">
         <v>186</v>
       </c>
@@ -20207,7 +20207,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="508" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A508" t="s">
         <v>91</v>
       </c>
@@ -20233,7 +20233,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="509" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A509" t="s">
         <v>189</v>
       </c>
@@ -20259,7 +20259,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="510" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A510" t="s">
         <v>92</v>
       </c>
@@ -20285,7 +20285,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="511" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A511" t="s">
         <v>224</v>
       </c>
@@ -20311,7 +20311,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="512" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A512" t="s">
         <v>289</v>
       </c>
@@ -20343,7 +20343,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="513" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A513" t="s">
         <v>289</v>
       </c>
@@ -20375,7 +20375,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="514" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A514" t="s">
         <v>301</v>
       </c>
@@ -20428,7 +20428,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="515" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A515" t="s">
         <v>179</v>
       </c>
@@ -20481,7 +20481,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="516" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A516" t="s">
         <v>302</v>
       </c>
@@ -20534,7 +20534,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="517" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A517" t="s">
         <v>304</v>
       </c>
@@ -20584,7 +20584,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="518" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A518" t="s">
         <v>306</v>
       </c>
@@ -20619,7 +20619,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="519" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A519" t="s">
         <v>305</v>
       </c>
@@ -20669,7 +20669,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="520" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A520" t="s">
         <v>309</v>
       </c>
@@ -20704,7 +20704,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="521" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A521" t="s">
         <v>303</v>
       </c>
@@ -20736,7 +20736,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="522" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A522" t="s">
         <v>231</v>
       </c>
@@ -20771,7 +20771,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="523" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A523" t="s">
         <v>348</v>
       </c>
@@ -20803,7 +20803,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="524" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A524" t="s">
         <v>292</v>
       </c>
@@ -20838,7 +20838,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="525" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A525" t="s">
         <v>293</v>
       </c>
@@ -20873,7 +20873,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="526" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A526" t="s">
         <v>294</v>
       </c>
@@ -20908,7 +20908,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="527" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A527" t="s">
         <v>259</v>
       </c>
@@ -20931,7 +20931,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="528" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A528" t="s">
         <v>262</v>
       </c>
@@ -20954,7 +20954,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="529" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A529" t="s">
         <v>307</v>
       </c>
@@ -20992,7 +20992,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="530" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A530" t="s">
         <v>313</v>
       </c>
@@ -21030,7 +21030,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="531" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A531" t="s">
         <v>100</v>
       </c>
@@ -21056,7 +21056,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="532" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A532" t="s">
         <v>86</v>
       </c>
@@ -21085,7 +21085,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="533" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A533" t="s">
         <v>87</v>
       </c>
@@ -21120,7 +21120,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="534" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A534" t="s">
         <v>88</v>
       </c>
@@ -21158,7 +21158,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="535" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A535" t="s">
         <v>297</v>
       </c>
@@ -21193,7 +21193,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="536" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A536" t="s">
         <v>299</v>
       </c>
@@ -21228,7 +21228,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="537" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A537" t="s">
         <v>300</v>
       </c>
@@ -21266,7 +21266,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="538" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A538" t="s">
         <v>320</v>
       </c>
@@ -21295,7 +21295,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="539" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A539" t="s">
         <v>311</v>
       </c>
@@ -21330,7 +21330,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="540" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A540" t="s">
         <v>310</v>
       </c>
@@ -21362,7 +21362,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="541" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A541" t="s">
         <v>312</v>
       </c>
@@ -21400,7 +21400,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="542" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A542" t="s">
         <v>213</v>
       </c>
@@ -21423,7 +21423,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="543" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A543" t="s">
         <v>267</v>
       </c>
@@ -21467,7 +21467,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="544" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A544" t="s">
         <v>268</v>
       </c>
@@ -21517,7 +21517,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="545" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A545" t="s">
         <v>85</v>
       </c>
@@ -21564,7 +21564,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="546" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A546" t="s">
         <v>326</v>
       </c>
@@ -21599,7 +21599,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="547" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A547" t="s">
         <v>325</v>
       </c>
@@ -21631,7 +21631,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="548" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A548" t="s">
         <v>314</v>
       </c>
@@ -21666,7 +21666,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="549" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A549" t="s">
         <v>315</v>
       </c>
@@ -21692,7 +21692,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="550" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A550" t="s">
         <v>316</v>
       </c>
@@ -21718,7 +21718,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="551" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A551" t="s">
         <v>91</v>
       </c>
@@ -21744,7 +21744,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="552" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A552" t="s">
         <v>186</v>
       </c>
@@ -21770,7 +21770,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="553" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A553" t="s">
         <v>317</v>
       </c>
@@ -21796,7 +21796,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="554" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A554" t="s">
         <v>318</v>
       </c>
@@ -21822,7 +21822,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="555" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A555" t="s">
         <v>189</v>
       </c>
@@ -21848,7 +21848,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="556" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A556" t="s">
         <v>319</v>
       </c>
@@ -21874,7 +21874,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="557" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A557" t="s">
         <v>321</v>
       </c>
@@ -21897,7 +21897,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="558" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A558" t="s">
         <v>322</v>
       </c>
@@ -21920,7 +21920,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="559" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A559" t="s">
         <v>323</v>
       </c>
@@ -21943,7 +21943,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="560" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A560" t="s">
         <v>289</v>
       </c>
@@ -21981,7 +21981,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="561" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A561" t="s">
         <v>290</v>
       </c>
@@ -22019,7 +22019,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="562" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A562" t="s">
         <v>59</v>
       </c>
@@ -22063,7 +22063,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="563" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A563" t="s">
         <v>324</v>
       </c>
@@ -22098,7 +22098,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="564" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A564" t="s">
         <v>330</v>
       </c>
@@ -22124,7 +22124,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="565" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="565" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A565" t="s">
         <v>94</v>
       </c>
@@ -22153,7 +22153,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="566" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="566" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A566" t="s">
         <v>89</v>
       </c>
@@ -22185,7 +22185,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="567" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A567" t="s">
         <v>37</v>
       </c>
@@ -22232,7 +22232,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="568" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A568" t="s">
         <v>320</v>
       </c>
@@ -22258,7 +22258,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="569" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A569" t="s">
         <v>331</v>
       </c>
@@ -22284,7 +22284,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="570" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A570" t="s">
         <v>340</v>
       </c>
@@ -22324,7 +22324,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="571" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A571" t="s">
         <v>380</v>
       </c>
@@ -22359,7 +22359,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="572" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A572" t="s">
         <v>327</v>
       </c>
@@ -22391,7 +22391,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="573" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A573" t="s">
         <v>328</v>
       </c>
@@ -22426,7 +22426,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="574" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A574" t="s">
         <v>329</v>
       </c>
@@ -22458,7 +22458,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="575" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A575" t="s">
         <v>303</v>
       </c>
@@ -22493,7 +22493,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="576" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A576" t="s">
         <v>332</v>
       </c>
@@ -22516,7 +22516,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="577" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A577" t="s">
         <v>258</v>
       </c>
@@ -22539,7 +22539,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="578" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="578" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A578" t="s">
         <v>263</v>
       </c>
@@ -22562,7 +22562,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="579" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="579" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A579" t="s">
         <v>258</v>
       </c>
@@ -22606,7 +22606,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="580" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="580" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A580" t="s">
         <v>335</v>
       </c>
@@ -22641,7 +22641,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="581" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="581" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A581" t="s">
         <v>263</v>
       </c>
@@ -22664,7 +22664,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="582" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A582" t="s">
         <v>213</v>
       </c>
@@ -22687,7 +22687,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="583" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="583" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A583" t="s">
         <v>333</v>
       </c>
@@ -22713,7 +22713,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="584" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="584" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A584" t="s">
         <v>303</v>
       </c>
@@ -22748,7 +22748,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="585" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="585" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A585" t="s">
         <v>326</v>
       </c>
@@ -22798,7 +22798,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="586" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="586" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A586" t="s">
         <v>334</v>
       </c>
@@ -22833,7 +22833,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="587" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="587" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A587" t="s">
         <v>267</v>
       </c>
@@ -22886,7 +22886,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="588" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="588" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A588" t="s">
         <v>268</v>
       </c>
@@ -22939,7 +22939,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="589" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="589" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A589" t="s">
         <v>85</v>
       </c>
@@ -22992,7 +22992,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="590" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="590" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A590" t="s">
         <v>243</v>
       </c>
@@ -23045,7 +23045,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="591" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="591" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A591" t="s">
         <v>94</v>
       </c>
@@ -23080,7 +23080,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="592" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="592" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A592" t="s">
         <v>89</v>
       </c>
@@ -23112,7 +23112,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="593" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="593" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A593" t="s">
         <v>291</v>
       </c>
@@ -23150,7 +23150,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="594" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="594" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A594" t="s">
         <v>336</v>
       </c>
@@ -23188,7 +23188,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="595" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="595" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A595" t="s">
         <v>337</v>
       </c>
@@ -23217,7 +23217,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="596" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="596" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A596" t="s">
         <v>258</v>
       </c>
@@ -23255,7 +23255,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="597" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="597" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A597" t="s">
         <v>263</v>
       </c>
@@ -23290,7 +23290,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="598" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="598" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A598" t="s">
         <v>339</v>
       </c>
@@ -23328,7 +23328,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="599" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="599" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A599" t="s">
         <v>341</v>
       </c>
@@ -23367,7 +23367,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="600" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="600" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A600" t="s">
         <v>263</v>
       </c>
@@ -23387,7 +23387,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="601" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="601" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A601" t="s">
         <v>213</v>
       </c>
@@ -23407,7 +23407,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="602" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="602" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A602" t="s">
         <v>342</v>
       </c>
@@ -23427,7 +23427,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="603" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="603" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A603" t="s">
         <v>343</v>
       </c>
@@ -23447,7 +23447,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="604" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="604" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A604" t="s">
         <v>354</v>
       </c>
@@ -23467,7 +23467,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="605" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="605" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A605" t="s">
         <v>338</v>
       </c>
@@ -23517,7 +23517,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="606" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="606" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A606" t="s">
         <v>59</v>
       </c>
@@ -23561,7 +23561,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="607" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="607" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A607" t="s">
         <v>303</v>
       </c>
@@ -23584,7 +23584,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="608" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="608" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A608" t="s">
         <v>213</v>
       </c>
@@ -23607,7 +23607,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="609" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="609" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A609" t="s">
         <v>355</v>
       </c>
@@ -23630,7 +23630,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="610" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="610" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A610" t="s">
         <v>354</v>
       </c>
@@ -23653,7 +23653,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="611" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="611" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A611" t="s">
         <v>356</v>
       </c>
@@ -23676,7 +23676,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="612" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="612" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A612" t="s">
         <v>258</v>
       </c>
@@ -23699,7 +23699,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="613" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="613" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A613" t="s">
         <v>303</v>
       </c>
@@ -23722,7 +23722,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="614" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="614" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A614" t="s">
         <v>320</v>
       </c>
@@ -23745,7 +23745,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="615" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="615" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A615" t="s">
         <v>303</v>
       </c>
@@ -23768,7 +23768,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="616" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="616" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A616" t="s">
         <v>213</v>
       </c>
@@ -23791,7 +23791,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="617" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="617" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A617" t="s">
         <v>355</v>
       </c>
@@ -23814,7 +23814,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="618" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="618" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A618" t="s">
         <v>365</v>
       </c>
@@ -23852,7 +23852,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="619" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="619" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A619" t="s">
         <v>268</v>
       </c>
@@ -23897,7 +23897,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="620" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="620" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A620" t="s">
         <v>85</v>
       </c>
@@ -23939,7 +23939,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="621" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="621" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A621" t="s">
         <v>351</v>
       </c>
@@ -23972,7 +23972,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="622" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="622" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A622" t="s">
         <v>79</v>
       </c>
@@ -24011,7 +24011,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="623" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="623" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A623" t="s">
         <v>303</v>
       </c>
@@ -24034,7 +24034,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="624" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="624" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A624" t="s">
         <v>303</v>
       </c>
@@ -24057,7 +24057,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="625" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="625" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A625" t="s">
         <v>355</v>
       </c>
@@ -24080,7 +24080,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="626" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="626" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A626" t="s">
         <v>357</v>
       </c>
@@ -24103,7 +24103,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="627" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="627" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A627" t="s">
         <v>354</v>
       </c>
@@ -24126,7 +24126,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="628" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="628" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A628" t="s">
         <v>358</v>
       </c>
@@ -24149,7 +24149,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="629" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="629" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A629" t="s">
         <v>359</v>
       </c>
@@ -24172,7 +24172,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="630" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="630" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A630" t="s">
         <v>94</v>
       </c>
@@ -24213,7 +24213,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="631" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="631" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A631" t="s">
         <v>89</v>
       </c>
@@ -24248,7 +24248,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="632" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="632" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A632" t="s">
         <v>415</v>
       </c>
@@ -24280,7 +24280,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="633" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="633" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A633" t="s">
         <v>314</v>
       </c>
@@ -24313,7 +24313,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="634" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="634" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A634" t="s">
         <v>360</v>
       </c>
@@ -24342,7 +24342,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="635" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="635" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A635" t="s">
         <v>361</v>
       </c>
@@ -24371,7 +24371,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="636" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="636" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A636" t="s">
         <v>59</v>
       </c>
@@ -24407,7 +24407,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="637" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="637" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A637" t="s">
         <v>353</v>
       </c>
@@ -24442,7 +24442,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="638" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="638" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A638" t="s">
         <v>355</v>
       </c>
@@ -24465,7 +24465,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="639" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="639" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A639" t="s">
         <v>303</v>
       </c>
@@ -24488,7 +24488,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="640" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="640" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A640" t="s">
         <v>86</v>
       </c>
@@ -24529,7 +24529,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="641" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="641" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A641" t="s">
         <v>100</v>
       </c>
@@ -24570,7 +24570,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="642" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="642" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A642" t="s">
         <v>355</v>
       </c>
@@ -24603,7 +24603,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="643" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="643" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A643" t="s">
         <v>372</v>
       </c>
@@ -24641,7 +24641,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="644" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="644" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A644" t="s">
         <v>373</v>
       </c>
@@ -24676,7 +24676,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="645" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="645" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A645" t="s">
         <v>87</v>
       </c>
@@ -24714,7 +24714,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="646" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="646" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A646" t="s">
         <v>88</v>
       </c>
@@ -24755,7 +24755,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="647" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="647" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A647" t="s">
         <v>89</v>
       </c>
@@ -24799,7 +24799,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="648" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="648" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A648" t="s">
         <v>377</v>
       </c>
@@ -24840,7 +24840,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="649" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="649" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A649" t="s">
         <v>381</v>
       </c>
@@ -24875,7 +24875,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="650" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="650" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A650" t="s">
         <v>303</v>
       </c>
@@ -24908,7 +24908,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="651" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="651" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A651" t="s">
         <v>320</v>
       </c>
@@ -24941,7 +24941,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="652" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="652" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A652" t="s">
         <v>268</v>
       </c>
@@ -24995,7 +24995,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="653" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="653" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A653" t="s">
         <v>351</v>
       </c>
@@ -25049,7 +25049,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="654" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="654" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A654" t="s">
         <v>79</v>
       </c>
@@ -25103,7 +25103,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="655" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="655" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A655" t="s">
         <v>362</v>
       </c>
@@ -25156,7 +25156,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="656" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="656" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A656" t="s">
         <v>354</v>
       </c>
@@ -25189,7 +25189,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="657" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="657" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A657" t="s">
         <v>213</v>
       </c>
@@ -25222,7 +25222,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="658" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="658" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A658" t="s">
         <v>363</v>
       </c>
@@ -25275,7 +25275,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="659" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="659" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A659" t="s">
         <v>364</v>
       </c>
@@ -25328,7 +25328,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="660" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="660" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A660" s="17" t="s">
         <v>366</v>
       </c>
@@ -25365,14 +25365,14 @@
         <v>56</v>
       </c>
       <c r="P660" s="17">
-        <f>SUM(F660:I660,K660:O660)</f>
+        <f t="shared" ref="P660:P666" si="0">SUM(F660:I660,K660:O660)</f>
         <v>1111</v>
       </c>
       <c r="Q660" t="s">
         <v>367</v>
       </c>
     </row>
-    <row r="661" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="661" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A661" t="s">
         <v>212</v>
       </c>
@@ -25398,14 +25398,14 @@
         <v>111</v>
       </c>
       <c r="P661">
-        <f>SUM(F661:I661,K661:O661)</f>
+        <f t="shared" si="0"/>
         <v>444</v>
       </c>
       <c r="Q661" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="662" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="662" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A662" t="s">
         <v>91</v>
       </c>
@@ -25431,14 +25431,14 @@
         <v>0</v>
       </c>
       <c r="P662">
-        <f>SUM(F662:I662,K662:O662)</f>
+        <f t="shared" si="0"/>
         <v>56</v>
       </c>
       <c r="Q662" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="663" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="663" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A663" t="s">
         <v>186</v>
       </c>
@@ -25464,14 +25464,14 @@
         <v>167</v>
       </c>
       <c r="P663">
-        <f>SUM(F663:I663,K663:O663)</f>
+        <f t="shared" si="0"/>
         <v>167</v>
       </c>
       <c r="Q663" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="664" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="664" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A664" t="s">
         <v>317</v>
       </c>
@@ -25497,14 +25497,14 @@
         <v>56</v>
       </c>
       <c r="P664">
-        <f>SUM(F664:I664,K664:O664)</f>
+        <f t="shared" si="0"/>
         <v>112</v>
       </c>
       <c r="Q664" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="665" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="665" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A665" t="s">
         <v>189</v>
       </c>
@@ -25530,14 +25530,14 @@
         <v>0</v>
       </c>
       <c r="P665">
-        <f>SUM(F665:I665,K665:O665)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Q665" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="666" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="666" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A666" t="s">
         <v>319</v>
       </c>
@@ -25563,14 +25563,14 @@
         <v>222</v>
       </c>
       <c r="P666">
-        <f>SUM(F666:I666,K666:O666)</f>
+        <f t="shared" si="0"/>
         <v>278</v>
       </c>
       <c r="Q666" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="667" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="667" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A667" t="s">
         <v>370</v>
       </c>
@@ -25602,7 +25602,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="668" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="668" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A668" t="s">
         <v>371</v>
       </c>
@@ -25637,7 +25637,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="669" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="669" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A669" t="s">
         <v>303</v>
       </c>
@@ -25672,7 +25672,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="670" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="670" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A670" t="s">
         <v>368</v>
       </c>
@@ -25707,7 +25707,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="671" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="671" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A671" t="s">
         <v>213</v>
       </c>
@@ -25740,7 +25740,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="672" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="672" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A672" t="s">
         <v>92</v>
       </c>
@@ -25794,7 +25794,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="673" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="673" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A673" t="s">
         <v>89</v>
       </c>
@@ -25823,7 +25823,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="674" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="674" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A674" t="s">
         <v>389</v>
       </c>
@@ -25873,7 +25873,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="675" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="675" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A675" t="s">
         <v>359</v>
       </c>
@@ -25906,7 +25906,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="676" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="676" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A676" t="s">
         <v>130</v>
       </c>
@@ -25960,7 +25960,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="677" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="677" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A677" t="s">
         <v>369</v>
       </c>
@@ -26014,7 +26014,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="678" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="678" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A678" t="s">
         <v>59</v>
       </c>
@@ -26052,7 +26052,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="679" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="679" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A679" t="s">
         <v>59</v>
       </c>
@@ -26090,7 +26090,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="680" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="680" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A680" t="s">
         <v>383</v>
       </c>
@@ -26113,7 +26113,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="681" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="681" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A681" t="s">
         <v>263</v>
       </c>
@@ -26133,7 +26133,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="682" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="682" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A682" t="s">
         <v>384</v>
       </c>
@@ -26156,7 +26156,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="683" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="683" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A683" t="s">
         <v>385</v>
       </c>
@@ -26179,7 +26179,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="684" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="684" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A684" t="s">
         <v>303</v>
       </c>
@@ -26202,7 +26202,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="685" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="685" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A685" t="s">
         <v>37</v>
       </c>
@@ -26249,7 +26249,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="686" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="686" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A686" t="s">
         <v>376</v>
       </c>
@@ -26290,7 +26290,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="687" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="687" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A687" t="s">
         <v>381</v>
       </c>
@@ -26325,7 +26325,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="688" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="688" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A688" t="s">
         <v>383</v>
       </c>
@@ -26348,7 +26348,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="689" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="689" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A689" t="s">
         <v>375</v>
       </c>
@@ -26386,7 +26386,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="690" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="690" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A690" t="s">
         <v>304</v>
       </c>
@@ -26439,7 +26439,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="691" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="691" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A691" t="s">
         <v>363</v>
       </c>
@@ -26492,7 +26492,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="692" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="692" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A692" t="s">
         <v>378</v>
       </c>
@@ -26542,7 +26542,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="693" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="693" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A693" t="s">
         <v>379</v>
       </c>
@@ -26595,7 +26595,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="694" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="694" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A694" t="s">
         <v>383</v>
       </c>
@@ -26618,7 +26618,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="695" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="695" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A695" t="s">
         <v>384</v>
       </c>
@@ -26641,7 +26641,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="696" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="696" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A696" t="s">
         <v>396</v>
       </c>
@@ -26682,7 +26682,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="697" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="697" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A697" t="s">
         <v>376</v>
       </c>
@@ -26720,7 +26720,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="698" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="698" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A698" t="s">
         <v>382</v>
       </c>
@@ -26758,7 +26758,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="699" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="699" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A699" t="s">
         <v>383</v>
       </c>
@@ -26781,7 +26781,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="700" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="700" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A700" t="s">
         <v>303</v>
       </c>
@@ -26804,7 +26804,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="701" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="701" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A701" t="s">
         <v>383</v>
       </c>
@@ -26827,7 +26827,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="702" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="702" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A702" t="s">
         <v>378</v>
       </c>
@@ -26880,7 +26880,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="703" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="703" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A703" t="s">
         <v>389</v>
       </c>
@@ -26933,7 +26933,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="704" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="704" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A704" t="s">
         <v>268</v>
       </c>
@@ -26975,7 +26975,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="705" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="705" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A705" t="s">
         <v>85</v>
       </c>
@@ -27014,7 +27014,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="706" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="706" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A706" t="s">
         <v>79</v>
       </c>
@@ -27053,7 +27053,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="707" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="707" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A707" t="s">
         <v>315</v>
       </c>
@@ -27085,7 +27085,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="708" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="708" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A708" t="s">
         <v>188</v>
       </c>
@@ -27117,7 +27117,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="709" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="709" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A709" t="s">
         <v>91</v>
       </c>
@@ -27149,7 +27149,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="710" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="710" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A710" t="s">
         <v>186</v>
       </c>
@@ -27181,7 +27181,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="711" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="711" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A711" t="s">
         <v>317</v>
       </c>
@@ -27213,7 +27213,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="712" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="712" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A712" t="s">
         <v>189</v>
       </c>
@@ -27245,7 +27245,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="713" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="713" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A713" t="s">
         <v>319</v>
       </c>
@@ -27277,7 +27277,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="714" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="714" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A714" t="s">
         <v>387</v>
       </c>
@@ -27315,7 +27315,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="715" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="715" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A715" t="s">
         <v>388</v>
       </c>
@@ -27368,7 +27368,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="716" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="716" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A716" t="s">
         <v>386</v>
       </c>
@@ -27391,7 +27391,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="717" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="717" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A717" t="s">
         <v>94</v>
       </c>
@@ -27426,7 +27426,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="718" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="718" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A718" t="s">
         <v>89</v>
       </c>
@@ -27461,7 +27461,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="719" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="719" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A719" t="s">
         <v>415</v>
       </c>
@@ -27493,7 +27493,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="720" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="720" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A720" t="s">
         <v>362</v>
       </c>
@@ -27546,7 +27546,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="721" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="721" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A721" t="s">
         <v>59</v>
       </c>
@@ -27584,7 +27584,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="722" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="722" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A722" t="s">
         <v>390</v>
       </c>
@@ -27628,7 +27628,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="723" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="723" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A723" t="s">
         <v>383</v>
       </c>
@@ -27651,7 +27651,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="724" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="724" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A724" t="s">
         <v>355</v>
       </c>
@@ -27674,7 +27674,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="725" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="725" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A725" t="s">
         <v>59</v>
       </c>
@@ -27712,7 +27712,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="726" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="726" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A726" t="s">
         <v>393</v>
       </c>
@@ -27765,7 +27765,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="727" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="727" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A727" t="s">
         <v>222</v>
       </c>
@@ -27818,7 +27818,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="728" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="728" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A728" t="s">
         <v>392</v>
       </c>
@@ -27853,7 +27853,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="729" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="729" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A729" t="s">
         <v>92</v>
       </c>
@@ -27894,7 +27894,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="730" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="730" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A730" t="s">
         <v>394</v>
       </c>
@@ -27935,7 +27935,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="731" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="731" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A731" t="s">
         <v>86</v>
       </c>
@@ -27976,7 +27976,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="732" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="732" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A732" t="s">
         <v>100</v>
       </c>
@@ -28014,7 +28014,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="733" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="733" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A733" t="s">
         <v>397</v>
       </c>
@@ -28055,7 +28055,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="734" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="734" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A734" t="s">
         <v>87</v>
       </c>
@@ -28093,7 +28093,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="735" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="735" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A735" t="s">
         <v>88</v>
       </c>
@@ -28134,7 +28134,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="736" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="736" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A736" t="s">
         <v>89</v>
       </c>
@@ -28172,7 +28172,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="737" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="737" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A737" t="s">
         <v>377</v>
       </c>
@@ -28210,7 +28210,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="738" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="738" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A738" t="s">
         <v>300</v>
       </c>
@@ -28245,7 +28245,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="739" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="739" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A739" t="s">
         <v>391</v>
       </c>
@@ -28280,7 +28280,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="740" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="740" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A740" t="s">
         <v>351</v>
       </c>
@@ -28318,7 +28318,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="741" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="741" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A741" t="s">
         <v>314</v>
       </c>
@@ -28356,7 +28356,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="742" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="742" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A742" t="s">
         <v>383</v>
       </c>
@@ -28379,7 +28379,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="743" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="743" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A743" t="s">
         <v>389</v>
       </c>
@@ -28432,7 +28432,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="744" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="744" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A744" t="s">
         <v>378</v>
       </c>
@@ -28485,7 +28485,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="745" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="745" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A745" t="s">
         <v>395</v>
       </c>
@@ -28508,7 +28508,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="746" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="746" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A746" t="s">
         <v>359</v>
       </c>
@@ -28531,7 +28531,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="747" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="747" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A747" t="s">
         <v>303</v>
       </c>
@@ -28554,7 +28554,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="748" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="748" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A748" t="s">
         <v>399</v>
       </c>
@@ -28583,7 +28583,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="749" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="749" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A749" t="s">
         <v>230</v>
       </c>
@@ -28621,7 +28621,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="750" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="750" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A750" t="s">
         <v>230</v>
       </c>
@@ -28659,7 +28659,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="751" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="751" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A751" t="s">
         <v>376</v>
       </c>
@@ -28694,7 +28694,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="752" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="752" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A752" t="s">
         <v>378</v>
       </c>
@@ -28747,7 +28747,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="753" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="753" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A753" t="s">
         <v>303</v>
       </c>
@@ -28770,7 +28770,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="754" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="754" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A754" t="s">
         <v>355</v>
       </c>
@@ -28790,7 +28790,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="755" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="755" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A755" t="s">
         <v>79</v>
       </c>
@@ -28822,7 +28822,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="756" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="756" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A756" t="s">
         <v>85</v>
       </c>
@@ -28857,7 +28857,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="757" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="757" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A757" t="s">
         <v>268</v>
       </c>
@@ -28892,7 +28892,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="758" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="758" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A758" t="s">
         <v>391</v>
       </c>
@@ -28927,7 +28927,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="759" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="759" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A759" t="s">
         <v>179</v>
       </c>
@@ -28959,7 +28959,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="760" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="760" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A760" t="s">
         <v>210</v>
       </c>
@@ -29012,7 +29012,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="761" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="761" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A761" t="s">
         <v>400</v>
       </c>
@@ -29044,7 +29044,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="762" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="762" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A762" t="s">
         <v>231</v>
       </c>
@@ -29079,7 +29079,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="763" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="763" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A763" t="s">
         <v>401</v>
       </c>
@@ -29117,7 +29117,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="764" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="764" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A764" t="s">
         <v>402</v>
       </c>
@@ -29155,7 +29155,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="765" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="765" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A765" t="s">
         <v>403</v>
       </c>
@@ -29190,7 +29190,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="766" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="766" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A766" t="s">
         <v>398</v>
       </c>
@@ -29243,7 +29243,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="767" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="767" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A767" t="s">
         <v>362</v>
       </c>
@@ -29296,7 +29296,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="768" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="768" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A768" t="s">
         <v>314</v>
       </c>
@@ -29331,7 +29331,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="769" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="769" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A769" t="s">
         <v>383</v>
       </c>
@@ -29363,7 +29363,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="770" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="770" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A770" t="s">
         <v>314</v>
       </c>
@@ -29401,7 +29401,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="771" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="771" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A771" t="s">
         <v>355</v>
       </c>
@@ -29436,7 +29436,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="772" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="772" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A772" t="s">
         <v>409</v>
       </c>
@@ -29477,7 +29477,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="773" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="773" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A773" t="s">
         <v>351</v>
       </c>
@@ -29518,7 +29518,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="774" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="774" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A774" t="s">
         <v>85</v>
       </c>
@@ -29553,7 +29553,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="775" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="775" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A775" t="s">
         <v>79</v>
       </c>
@@ -29585,7 +29585,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="776" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="776" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A776" t="s">
         <v>268</v>
       </c>
@@ -29623,7 +29623,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="777" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="777" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A777" s="1" t="s">
         <v>315</v>
       </c>
@@ -29656,14 +29656,14 @@
       <c r="N777" s="1"/>
       <c r="O777" s="1"/>
       <c r="P777">
-        <f>SUM(F777:I777,K777:O777)</f>
+        <f t="shared" ref="P777:P788" si="1">SUM(F777:I777,K777:O777)</f>
         <v>722</v>
       </c>
       <c r="Q777" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="778" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="778" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A778" t="s">
         <v>188</v>
       </c>
@@ -29689,14 +29689,14 @@
         <v>111</v>
       </c>
       <c r="P778">
-        <f>SUM(F778:I778,K778:O778)</f>
+        <f t="shared" si="1"/>
         <v>167</v>
       </c>
       <c r="Q778" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="779" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="779" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A779" t="s">
         <v>91</v>
       </c>
@@ -29722,14 +29722,14 @@
         <v>56</v>
       </c>
       <c r="P779">
-        <f>SUM(F779:I779,K779:O779)</f>
+        <f t="shared" si="1"/>
         <v>278</v>
       </c>
       <c r="Q779" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="780" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="780" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A780" t="s">
         <v>186</v>
       </c>
@@ -29755,14 +29755,14 @@
         <v>56</v>
       </c>
       <c r="P780">
-        <f>SUM(F780:I780,K780:O780)</f>
+        <f t="shared" si="1"/>
         <v>112</v>
       </c>
       <c r="Q780" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="781" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="781" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A781" t="s">
         <v>317</v>
       </c>
@@ -29788,14 +29788,14 @@
         <v>0</v>
       </c>
       <c r="P781">
-        <f>SUM(F781:I781,K781:O781)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Q781" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="782" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="782" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A782" t="s">
         <v>189</v>
       </c>
@@ -29821,14 +29821,14 @@
         <v>56</v>
       </c>
       <c r="P782">
-        <f>SUM(F782:I782,K782:O782)</f>
+        <f t="shared" si="1"/>
         <v>278</v>
       </c>
       <c r="Q782" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="783" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="783" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A783" t="s">
         <v>319</v>
       </c>
@@ -29854,14 +29854,14 @@
         <v>167</v>
       </c>
       <c r="P783">
-        <f>SUM(F783:I783,K783:O783)</f>
+        <f t="shared" si="1"/>
         <v>445</v>
       </c>
       <c r="Q783" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="784" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="784" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A784" t="s">
         <v>318</v>
       </c>
@@ -29887,14 +29887,14 @@
         <v>0</v>
       </c>
       <c r="P784">
-        <f>SUM(F784:I784,K784:O784)</f>
+        <f t="shared" si="1"/>
         <v>56</v>
       </c>
       <c r="Q784" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="785" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="785" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A785" t="s">
         <v>405</v>
       </c>
@@ -29920,14 +29920,14 @@
         <v>56</v>
       </c>
       <c r="P785">
-        <f>SUM(F785:I785,K785:O785)</f>
+        <f t="shared" si="1"/>
         <v>56</v>
       </c>
       <c r="Q785" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="786" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="786" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A786" t="s">
         <v>406</v>
       </c>
@@ -29953,14 +29953,14 @@
         <v>56</v>
       </c>
       <c r="P786">
-        <f>SUM(F786:I786,K786:O786)</f>
+        <f t="shared" si="1"/>
         <v>56</v>
       </c>
       <c r="Q786" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="787" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="787" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A787" t="s">
         <v>407</v>
       </c>
@@ -29986,14 +29986,14 @@
         <v>0</v>
       </c>
       <c r="P787">
-        <f>SUM(F787:I787,K787:O787)</f>
+        <f t="shared" si="1"/>
         <v>56</v>
       </c>
       <c r="Q787" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="788" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="788" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A788" t="s">
         <v>86</v>
       </c>
@@ -30019,14 +30019,14 @@
         <v>111</v>
       </c>
       <c r="P788">
-        <f>SUM(F788:I788,K788:O788)</f>
+        <f t="shared" si="1"/>
         <v>111</v>
       </c>
       <c r="Q788" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="789" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="789" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A789" t="s">
         <v>341</v>
       </c>
@@ -30064,7 +30064,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="790" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="790" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A790" t="s">
         <v>408</v>
       </c>
@@ -30105,7 +30105,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="791" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="791" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A791" t="s">
         <v>398</v>
       </c>
@@ -30158,7 +30158,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="792" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="792" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A792" t="s">
         <v>210</v>
       </c>
@@ -30211,7 +30211,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="793" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="793" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A793" t="s">
         <v>378</v>
       </c>
@@ -30264,7 +30264,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="794" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="794" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A794" t="s">
         <v>412</v>
       </c>
@@ -30299,7 +30299,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="795" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="795" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A795" t="s">
         <v>93</v>
       </c>
@@ -30334,7 +30334,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="796" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="796" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A796" t="s">
         <v>93</v>
       </c>
@@ -30369,7 +30369,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="797" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="797" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A797" t="s">
         <v>222</v>
       </c>
@@ -30422,7 +30422,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="798" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="798" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A798" t="s">
         <v>59</v>
       </c>
@@ -30463,7 +30463,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="799" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="799" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A799" t="s">
         <v>410</v>
       </c>
@@ -30498,7 +30498,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="800" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="800" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A800" t="s">
         <v>411</v>
       </c>
@@ -30536,7 +30536,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="801" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="801" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A801" t="s">
         <v>362</v>
       </c>
@@ -30589,7 +30589,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="802" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="802" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A802" t="s">
         <v>413</v>
       </c>
@@ -30642,7 +30642,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="803" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="803" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A803" t="s">
         <v>231</v>
       </c>
@@ -30680,7 +30680,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="804" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="804" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A804" t="s">
         <v>393</v>
       </c>
@@ -30733,7 +30733,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="805" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="805" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A805" t="s">
         <v>416</v>
       </c>
@@ -30765,7 +30765,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="806" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="806" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A806" t="s">
         <v>417</v>
       </c>
@@ -30797,7 +30797,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="807" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="807" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A807" t="s">
         <v>94</v>
       </c>
@@ -30829,7 +30829,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="808" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="808" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A808" t="s">
         <v>92</v>
       </c>
@@ -30870,7 +30870,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="809" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="809" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A809" t="s">
         <v>392</v>
       </c>
@@ -30911,7 +30911,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="810" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="810" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A810" t="s">
         <v>314</v>
       </c>
@@ -30949,7 +30949,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="811" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="811" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A811" t="s">
         <v>403</v>
       </c>
@@ -30999,7 +30999,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="812" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="812" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A812" t="s">
         <v>408</v>
       </c>
@@ -31040,7 +31040,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="813" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="813" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A813" t="s">
         <v>414</v>
       </c>
@@ -31093,7 +31093,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="814" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="814" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A814" t="s">
         <v>378</v>
       </c>
@@ -31146,7 +31146,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="815" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="815" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A815" t="s">
         <v>59</v>
       </c>
@@ -31187,7 +31187,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="816" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="816" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A816" t="s">
         <v>420</v>
       </c>
@@ -31240,7 +31240,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="817" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="817" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A817" t="s">
         <v>419</v>
       </c>
@@ -31281,7 +31281,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="818" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="818" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A818" t="s">
         <v>268</v>
       </c>
@@ -31328,7 +31328,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="819" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="819" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A819" t="s">
         <v>79</v>
       </c>
@@ -31360,7 +31360,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="820" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="820" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A820" t="s">
         <v>418</v>
       </c>
@@ -31401,7 +31401,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="821" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="821" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A821" t="s">
         <v>314</v>
       </c>
@@ -31439,7 +31439,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="822" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="822" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A822" t="s">
         <v>421</v>
       </c>
@@ -31492,7 +31492,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="823" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="823" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A823" t="s">
         <v>398</v>
       </c>
@@ -31545,7 +31545,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="824" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="824" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A824" t="s">
         <v>422</v>
       </c>
@@ -31586,7 +31586,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="825" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="825" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A825" t="s">
         <v>424</v>
       </c>
@@ -31630,7 +31630,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="826" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="826" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A826" t="s">
         <v>89</v>
       </c>
@@ -31668,7 +31668,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="827" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="827" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A827" t="s">
         <v>403</v>
       </c>
@@ -31712,7 +31712,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="828" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="828" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A828" t="s">
         <v>425</v>
       </c>
@@ -31753,7 +31753,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="829" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="829" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A829" t="s">
         <v>179</v>
       </c>
@@ -31791,7 +31791,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="830" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="830" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A830" t="s">
         <v>314</v>
       </c>
@@ -31829,7 +31829,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="831" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="831" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A831" t="s">
         <v>423</v>
       </c>
@@ -31882,7 +31882,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="832" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="832" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A832" t="s">
         <v>59</v>
       </c>
@@ -31923,7 +31923,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="833" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="833" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A833" t="s">
         <v>86</v>
       </c>
@@ -31970,7 +31970,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="834" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="834" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A834" t="s">
         <v>87</v>
       </c>
@@ -32014,7 +32014,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="835" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="835" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A835" t="s">
         <v>427</v>
       </c>
@@ -32055,7 +32055,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="836" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="836" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A836" t="s">
         <v>89</v>
       </c>
@@ -32096,7 +32096,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="837" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="837" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A837" t="s">
         <v>426</v>
       </c>
@@ -32134,12 +32134,12 @@
         <v>129</v>
       </c>
     </row>
-    <row r="838" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="838" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A838" t="s">
         <v>428</v>
       </c>
       <c r="B838">
-        <v>35.591330800000001</v>
+        <v>-35.591330800000001</v>
       </c>
       <c r="C838">
         <v>137.5061887</v>
@@ -32187,7 +32187,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="839" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="839" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A839" t="s">
         <v>290</v>
       </c>
@@ -32219,7 +32219,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="840" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="840" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A840" t="s">
         <v>341</v>
       </c>
@@ -32263,7 +32263,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="841" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="841" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A841" t="s">
         <v>314</v>
       </c>
@@ -32301,7 +32301,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="842" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="842" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A842" t="s">
         <v>429</v>
       </c>

--- a/MASTER spreadsheet of community summaries.xlsx
+++ b/MASTER spreadsheet of community summaries.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\a1675510\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\peri\Dropbox\Delta\Projects\Laboratory\Algal blooms, bacterial counts  for community\For Luke's HAB data display\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51E8E6DC-6B75-4E25-8A63-133AF91D28A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A504616A-7E3F-4247-8D1B-3FF7D345E414}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{9286397E-2757-492B-865A-39B2D6A15FF6}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{9286397E-2757-492B-865A-39B2D6A15FF6}"/>
   </bookViews>
   <sheets>
     <sheet name="Cells per mL" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1701" uniqueCount="430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1713" uniqueCount="431">
   <si>
     <t>Date</t>
   </si>
@@ -1346,6 +1346,9 @@
   </si>
   <si>
     <t>North Carrickalinga Beach</t>
+  </si>
+  <si>
+    <t>Stansbury- ST-05A</t>
   </si>
 </sst>
 </file>
@@ -1815,30 +1818,30 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F307807-E5C9-4450-88E0-159CBB3E9A67}">
-  <dimension ref="A1:T842"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:T848"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="39.36328125" customWidth="1"/>
-    <col min="2" max="2" width="17.81640625" customWidth="1"/>
-    <col min="3" max="3" width="14.6328125" customWidth="1"/>
-    <col min="4" max="4" width="13.08984375" customWidth="1"/>
-    <col min="5" max="5" width="16.6328125" style="20" customWidth="1"/>
+    <col min="1" max="1" width="39.33203125" customWidth="1"/>
+    <col min="2" max="2" width="17.77734375" customWidth="1"/>
+    <col min="3" max="3" width="14.6640625" customWidth="1"/>
+    <col min="4" max="4" width="13.109375" customWidth="1"/>
+    <col min="5" max="5" width="16.6640625" style="20" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="15.453125" customWidth="1"/>
-    <col min="8" max="8" width="11.90625" customWidth="1"/>
-    <col min="9" max="9" width="14.08984375" customWidth="1"/>
-    <col min="10" max="10" width="11.90625" customWidth="1"/>
-    <col min="11" max="11" width="14.08984375" customWidth="1"/>
-    <col min="12" max="12" width="10.453125" customWidth="1"/>
-    <col min="13" max="13" width="15.54296875" customWidth="1"/>
+    <col min="7" max="7" width="15.44140625" customWidth="1"/>
+    <col min="8" max="8" width="11.88671875" customWidth="1"/>
+    <col min="9" max="9" width="14.109375" customWidth="1"/>
+    <col min="10" max="10" width="11.88671875" customWidth="1"/>
+    <col min="11" max="11" width="14.109375" customWidth="1"/>
+    <col min="12" max="12" width="10.44140625" customWidth="1"/>
+    <col min="13" max="13" width="15.5546875" customWidth="1"/>
     <col min="14" max="14" width="13" customWidth="1"/>
-    <col min="15" max="15" width="7.6328125" customWidth="1"/>
-    <col min="16" max="16" width="12.453125" customWidth="1"/>
-    <col min="17" max="17" width="10.36328125" customWidth="1"/>
+    <col min="15" max="15" width="7.6640625" customWidth="1"/>
+    <col min="16" max="16" width="12.44140625" customWidth="1"/>
+    <col min="17" max="17" width="10.33203125" customWidth="1"/>
     <col min="18" max="18" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="35" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:17" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1891,7 +1894,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1920,7 +1923,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -1958,7 +1961,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -1999,7 +2002,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -2034,7 +2037,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -2078,7 +2081,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -2122,7 +2125,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -2160,7 +2163,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -2201,7 +2204,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>92</v>
       </c>
@@ -2227,7 +2230,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>91</v>
       </c>
@@ -2253,7 +2256,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>86</v>
       </c>
@@ -2279,7 +2282,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>87</v>
       </c>
@@ -2305,7 +2308,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>88</v>
       </c>
@@ -2331,7 +2334,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>89</v>
       </c>
@@ -2357,7 +2360,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>90</v>
       </c>
@@ -2383,7 +2386,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>91</v>
       </c>
@@ -2409,7 +2412,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>93</v>
       </c>
@@ -2435,7 +2438,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>8</v>
       </c>
@@ -2479,7 +2482,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>9</v>
       </c>
@@ -2511,7 +2514,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>10</v>
       </c>
@@ -2543,7 +2546,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>93</v>
       </c>
@@ -2569,7 +2572,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>8</v>
       </c>
@@ -2613,7 +2616,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>11</v>
       </c>
@@ -2660,7 +2663,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>12</v>
       </c>
@@ -2692,7 +2695,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>13</v>
       </c>
@@ -2733,7 +2736,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>14</v>
       </c>
@@ -2777,7 +2780,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>15</v>
       </c>
@@ -2818,7 +2821,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>5</v>
       </c>
@@ -2856,7 +2859,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>16</v>
       </c>
@@ -2888,7 +2891,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>94</v>
       </c>
@@ -2914,7 +2917,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>17</v>
       </c>
@@ -2958,7 +2961,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>95</v>
       </c>
@@ -2990,7 +2993,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>96</v>
       </c>
@@ -3019,7 +3022,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>18</v>
       </c>
@@ -3060,7 +3063,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>19</v>
       </c>
@@ -3104,7 +3107,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>20</v>
       </c>
@@ -3148,7 +3151,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>21</v>
       </c>
@@ -3189,7 +3192,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>22</v>
       </c>
@@ -3239,7 +3242,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>23</v>
       </c>
@@ -3286,7 +3289,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>97</v>
       </c>
@@ -3318,7 +3321,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>98</v>
       </c>
@@ -3353,7 +3356,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>99</v>
       </c>
@@ -3382,7 +3385,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>87</v>
       </c>
@@ -3408,7 +3411,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>100</v>
       </c>
@@ -3437,7 +3440,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>88</v>
       </c>
@@ -3466,7 +3469,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>86</v>
       </c>
@@ -3495,7 +3498,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>101</v>
       </c>
@@ -3524,7 +3527,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>90</v>
       </c>
@@ -3553,7 +3556,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>102</v>
       </c>
@@ -3594,7 +3597,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>103</v>
       </c>
@@ -3632,7 +3635,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>104</v>
       </c>
@@ -3661,7 +3664,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>24</v>
       </c>
@@ -3699,7 +3702,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>105</v>
       </c>
@@ -3731,7 +3734,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>106</v>
       </c>
@@ -3763,7 +3766,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>107</v>
       </c>
@@ -3795,7 +3798,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>108</v>
       </c>
@@ -3827,7 +3830,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>25</v>
       </c>
@@ -3865,7 +3868,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>19</v>
       </c>
@@ -3903,7 +3906,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>26</v>
       </c>
@@ -3944,7 +3947,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>27</v>
       </c>
@@ -3982,7 +3985,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>20</v>
       </c>
@@ -4020,7 +4023,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>105</v>
       </c>
@@ -4052,7 +4055,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>109</v>
       </c>
@@ -4084,7 +4087,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>110</v>
       </c>
@@ -4116,7 +4119,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>111</v>
       </c>
@@ -4148,7 +4151,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>112</v>
       </c>
@@ -4180,7 +4183,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>113</v>
       </c>
@@ -4212,7 +4215,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>105</v>
       </c>
@@ -4244,7 +4247,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>114</v>
       </c>
@@ -4276,7 +4279,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>28</v>
       </c>
@@ -4320,7 +4323,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>28</v>
       </c>
@@ -4362,7 +4365,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>28</v>
       </c>
@@ -4404,7 +4407,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>28</v>
       </c>
@@ -4446,7 +4449,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>28</v>
       </c>
@@ -4490,7 +4493,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>28</v>
       </c>
@@ -4534,7 +4537,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>115</v>
       </c>
@@ -4563,7 +4566,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>116</v>
       </c>
@@ -4592,7 +4595,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>157</v>
       </c>
@@ -4621,7 +4624,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>158</v>
       </c>
@@ -4647,7 +4650,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>29</v>
       </c>
@@ -4691,7 +4694,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>30</v>
       </c>
@@ -4735,7 +4738,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>31</v>
       </c>
@@ -4782,7 +4785,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>32</v>
       </c>
@@ -4826,7 +4829,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>33</v>
       </c>
@@ -4872,7 +4875,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>153</v>
       </c>
@@ -4904,7 +4907,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>155</v>
       </c>
@@ -4930,7 +4933,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>156</v>
       </c>
@@ -4956,7 +4959,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>159</v>
       </c>
@@ -4985,7 +4988,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>34</v>
       </c>
@@ -5032,7 +5035,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A91" s="2" t="s">
         <v>35</v>
       </c>
@@ -5073,7 +5076,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>36</v>
       </c>
@@ -5105,7 +5108,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>37</v>
       </c>
@@ -5147,7 +5150,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>153</v>
       </c>
@@ -5173,7 +5176,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>154</v>
       </c>
@@ -5199,7 +5202,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>94</v>
       </c>
@@ -5228,7 +5231,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>140</v>
       </c>
@@ -5254,7 +5257,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>141</v>
       </c>
@@ -5286,7 +5289,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>152</v>
       </c>
@@ -5312,7 +5315,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>160</v>
       </c>
@@ -5341,7 +5344,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>34</v>
       </c>
@@ -5385,7 +5388,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>38</v>
       </c>
@@ -5420,7 +5423,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>39</v>
       </c>
@@ -5461,7 +5464,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>40</v>
       </c>
@@ -5499,7 +5502,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>41</v>
       </c>
@@ -5537,7 +5540,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>41</v>
       </c>
@@ -5578,7 +5581,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>92</v>
       </c>
@@ -5607,7 +5610,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>42</v>
       </c>
@@ -5639,7 +5642,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>43</v>
       </c>
@@ -5683,7 +5686,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>86</v>
       </c>
@@ -5715,7 +5718,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>101</v>
       </c>
@@ -5744,7 +5747,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>87</v>
       </c>
@@ -5776,7 +5779,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>88</v>
       </c>
@@ -5802,7 +5805,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>89</v>
       </c>
@@ -5831,7 +5834,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>90</v>
       </c>
@@ -5857,7 +5860,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>44</v>
       </c>
@@ -5901,7 +5904,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>45</v>
       </c>
@@ -5945,7 +5948,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>46</v>
       </c>
@@ -5986,7 +5989,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>47</v>
       </c>
@@ -6024,7 +6027,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>48</v>
       </c>
@@ -6065,7 +6068,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>49</v>
       </c>
@@ -6103,7 +6106,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>5</v>
       </c>
@@ -6150,7 +6153,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>37</v>
       </c>
@@ -6191,7 +6194,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>77</v>
       </c>
@@ -6223,7 +6226,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>80</v>
       </c>
@@ -6255,7 +6258,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>130</v>
       </c>
@@ -6290,7 +6293,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>117</v>
       </c>
@@ -6319,7 +6322,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>118</v>
       </c>
@@ -6345,7 +6348,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>81</v>
       </c>
@@ -6377,7 +6380,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>161</v>
       </c>
@@ -6406,7 +6409,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="131" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>79</v>
       </c>
@@ -6438,7 +6441,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="132" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>157</v>
       </c>
@@ -6467,7 +6470,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="133" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>158</v>
       </c>
@@ -6499,7 +6502,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="134" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>125</v>
       </c>
@@ -6531,7 +6534,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="135" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>126</v>
       </c>
@@ -6572,7 +6575,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="136" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>127</v>
       </c>
@@ -6610,7 +6613,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="137" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>128</v>
       </c>
@@ -6648,7 +6651,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="138" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>132</v>
       </c>
@@ -6689,7 +6692,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>133</v>
       </c>
@@ -6730,7 +6733,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="140" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>134</v>
       </c>
@@ -6768,7 +6771,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="141" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>135</v>
       </c>
@@ -6806,7 +6809,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="142" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>136</v>
       </c>
@@ -6841,7 +6844,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="143" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>137</v>
       </c>
@@ -6876,7 +6879,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="144" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>138</v>
       </c>
@@ -6914,7 +6917,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="145" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>139</v>
       </c>
@@ -6949,7 +6952,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="146" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>37</v>
       </c>
@@ -6990,7 +6993,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="147" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>119</v>
       </c>
@@ -7028,7 +7031,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="148" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>120</v>
       </c>
@@ -7063,7 +7066,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="149" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>79</v>
       </c>
@@ -7098,7 +7101,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="150" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>236</v>
       </c>
@@ -7133,7 +7136,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="151" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>85</v>
       </c>
@@ -7165,7 +7168,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="152" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>18</v>
       </c>
@@ -7206,7 +7209,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="153" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>50</v>
       </c>
@@ -7244,7 +7247,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="154" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>27</v>
       </c>
@@ -7279,7 +7282,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="155" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>37</v>
       </c>
@@ -7320,7 +7323,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="156" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>79</v>
       </c>
@@ -7352,7 +7355,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="157" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>131</v>
       </c>
@@ -7384,7 +7387,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="158" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>236</v>
       </c>
@@ -7419,7 +7422,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="159" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>85</v>
       </c>
@@ -7451,7 +7454,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="160" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>51</v>
       </c>
@@ -7489,7 +7492,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="161" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>121</v>
       </c>
@@ -7521,7 +7524,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="162" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>18</v>
       </c>
@@ -7562,7 +7565,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="163" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>122</v>
       </c>
@@ -7591,7 +7594,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="164" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>79</v>
       </c>
@@ -7623,7 +7626,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="165" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>236</v>
       </c>
@@ -7655,7 +7658,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="166" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>85</v>
       </c>
@@ -7687,7 +7690,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="167" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>52</v>
       </c>
@@ -7731,7 +7734,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="168" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>53</v>
       </c>
@@ -7775,7 +7778,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="169" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>37</v>
       </c>
@@ -7816,7 +7819,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="170" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>82</v>
       </c>
@@ -7848,7 +7851,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="171" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>82</v>
       </c>
@@ -7880,7 +7883,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="172" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>84</v>
       </c>
@@ -7912,7 +7915,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="173" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>84</v>
       </c>
@@ -7944,7 +7947,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="174" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>54</v>
       </c>
@@ -7982,7 +7985,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="175" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>55</v>
       </c>
@@ -8020,7 +8023,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="176" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>56</v>
       </c>
@@ -8058,7 +8061,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="177" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>57</v>
       </c>
@@ -8093,7 +8096,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="178" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>58</v>
       </c>
@@ -8134,7 +8137,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="179" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>59</v>
       </c>
@@ -8169,7 +8172,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="180" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>15</v>
       </c>
@@ -8210,7 +8213,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="181" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>15</v>
       </c>
@@ -8251,7 +8254,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="182" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>60</v>
       </c>
@@ -8292,7 +8295,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="183" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>37</v>
       </c>
@@ -8333,7 +8336,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="184" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>131</v>
       </c>
@@ -8365,7 +8368,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="185" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>61</v>
       </c>
@@ -8406,7 +8409,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="186" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>62</v>
       </c>
@@ -8444,7 +8447,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="187" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>63</v>
       </c>
@@ -8482,7 +8485,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="188" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>94</v>
       </c>
@@ -8511,7 +8514,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="189" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>176</v>
       </c>
@@ -8552,7 +8555,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="190" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>79</v>
       </c>
@@ -8587,7 +8590,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="191" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>236</v>
       </c>
@@ -8619,7 +8622,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="192" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>85</v>
       </c>
@@ -8651,7 +8654,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="193" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>37</v>
       </c>
@@ -8692,7 +8695,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="194" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>130</v>
       </c>
@@ -8727,7 +8730,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="195" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>83</v>
       </c>
@@ -8759,7 +8762,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="196" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>18</v>
       </c>
@@ -8803,7 +8806,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="197" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>86</v>
       </c>
@@ -8832,7 +8835,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="198" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>100</v>
       </c>
@@ -8870,7 +8873,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="199" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>87</v>
       </c>
@@ -8914,7 +8917,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="200" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>123</v>
       </c>
@@ -8952,7 +8955,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="201" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>124</v>
       </c>
@@ -8981,7 +8984,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="202" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>89</v>
       </c>
@@ -9013,7 +9016,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="203" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>90</v>
       </c>
@@ -9048,7 +9051,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="204" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>25</v>
       </c>
@@ -9095,7 +9098,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="205" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>79</v>
       </c>
@@ -9127,7 +9130,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="206" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>130</v>
       </c>
@@ -9159,7 +9162,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="207" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>85</v>
       </c>
@@ -9191,7 +9194,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="208" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>37</v>
       </c>
@@ -9229,7 +9232,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="209" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>162</v>
       </c>
@@ -9264,7 +9267,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="210" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>162</v>
       </c>
@@ -9296,7 +9299,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="211" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>162</v>
       </c>
@@ -9328,7 +9331,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="212" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>142</v>
       </c>
@@ -9354,7 +9357,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="213" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>144</v>
       </c>
@@ -9380,7 +9383,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="214" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>145</v>
       </c>
@@ -9406,7 +9409,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="215" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>146</v>
       </c>
@@ -9432,7 +9435,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="216" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>37</v>
       </c>
@@ -9470,7 +9473,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="217" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>142</v>
       </c>
@@ -9496,7 +9499,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="218" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>144</v>
       </c>
@@ -9522,7 +9525,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="219" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>145</v>
       </c>
@@ -9548,7 +9551,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="220" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>146</v>
       </c>
@@ -9574,7 +9577,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="221" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>18</v>
       </c>
@@ -9618,7 +9621,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="222" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>79</v>
       </c>
@@ -9650,7 +9653,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="223" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>130</v>
       </c>
@@ -9683,7 +9686,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="224" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>236</v>
       </c>
@@ -9716,7 +9719,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="225" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>85</v>
       </c>
@@ -9749,7 +9752,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="226" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>142</v>
       </c>
@@ -9775,7 +9778,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="227" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>59</v>
       </c>
@@ -9819,7 +9822,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="228" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>37</v>
       </c>
@@ -9863,7 +9866,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="229" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>147</v>
       </c>
@@ -9889,7 +9892,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="230" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A230" s="7" t="s">
         <v>168</v>
       </c>
@@ -9940,7 +9943,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="231" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>79</v>
       </c>
@@ -9972,7 +9975,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="232" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>236</v>
       </c>
@@ -10004,7 +10007,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="233" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>85</v>
       </c>
@@ -10036,7 +10039,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="234" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>59</v>
       </c>
@@ -10062,7 +10065,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="235" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>156</v>
       </c>
@@ -10100,7 +10103,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="236" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>154</v>
       </c>
@@ -10135,7 +10138,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="237" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>37</v>
       </c>
@@ -10179,7 +10182,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="238" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>141</v>
       </c>
@@ -10211,7 +10214,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="239" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>93</v>
       </c>
@@ -10246,7 +10249,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="240" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>152</v>
       </c>
@@ -10281,7 +10284,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="241" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>142</v>
       </c>
@@ -10307,7 +10310,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="242" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>145</v>
       </c>
@@ -10333,7 +10336,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="243" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>146</v>
       </c>
@@ -10359,7 +10362,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="244" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>142</v>
       </c>
@@ -10385,7 +10388,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="245" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>148</v>
       </c>
@@ -10411,7 +10414,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="246" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>163</v>
       </c>
@@ -10449,7 +10452,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="247" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>164</v>
       </c>
@@ -10481,7 +10484,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="248" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>59</v>
       </c>
@@ -10513,7 +10516,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="249" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A249" s="7" t="s">
         <v>167</v>
       </c>
@@ -10548,7 +10551,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="250" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>142</v>
       </c>
@@ -10574,7 +10577,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="251" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>177</v>
       </c>
@@ -10609,7 +10612,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="252" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
         <v>37</v>
       </c>
@@ -10656,7 +10659,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="253" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
         <v>142</v>
       </c>
@@ -10682,7 +10685,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="254" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
         <v>150</v>
       </c>
@@ -10708,7 +10711,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="255" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
         <v>38</v>
       </c>
@@ -10755,7 +10758,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="256" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
         <v>165</v>
       </c>
@@ -10790,7 +10793,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="257" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
         <v>88</v>
       </c>
@@ -10825,7 +10828,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="258" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A258" s="7" t="s">
         <v>166</v>
       </c>
@@ -10874,7 +10877,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="259" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
         <v>89</v>
       </c>
@@ -10903,7 +10906,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="260" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
         <v>174</v>
       </c>
@@ -10941,7 +10944,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="261" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
         <v>175</v>
       </c>
@@ -10970,7 +10973,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="262" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
         <v>59</v>
       </c>
@@ -11005,7 +11008,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="263" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
         <v>37</v>
       </c>
@@ -11052,7 +11055,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="264" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A264" s="7" t="s">
         <v>169</v>
       </c>
@@ -11098,7 +11101,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="265" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A265" s="7" t="s">
         <v>171</v>
       </c>
@@ -11145,7 +11148,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="266" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A266" s="7" t="s">
         <v>172</v>
       </c>
@@ -11192,7 +11195,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="267" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A267" s="7" t="s">
         <v>170</v>
       </c>
@@ -11240,7 +11243,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="268" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A268" s="7" t="s">
         <v>173</v>
       </c>
@@ -11287,7 +11290,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="269" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
         <v>178</v>
       </c>
@@ -11331,7 +11334,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="270" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
         <v>37</v>
       </c>
@@ -11378,7 +11381,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="271" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>181</v>
       </c>
@@ -11419,7 +11422,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="272" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
         <v>182</v>
       </c>
@@ -11463,7 +11466,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="273" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
         <v>79</v>
       </c>
@@ -11498,7 +11501,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="274" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
         <v>236</v>
       </c>
@@ -11533,7 +11536,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="275" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
         <v>85</v>
       </c>
@@ -11568,7 +11571,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="276" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
         <v>179</v>
       </c>
@@ -11603,7 +11606,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="277" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
         <v>121</v>
       </c>
@@ -11638,7 +11641,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="278" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
         <v>92</v>
       </c>
@@ -11658,7 +11661,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="279" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
         <v>94</v>
       </c>
@@ -11693,7 +11696,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="280" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
         <v>186</v>
       </c>
@@ -11713,7 +11716,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="281" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
         <v>92</v>
       </c>
@@ -11733,7 +11736,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="282" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
         <v>183</v>
       </c>
@@ -11783,7 +11786,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="283" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
         <v>184</v>
       </c>
@@ -11833,7 +11836,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="284" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
         <v>185</v>
       </c>
@@ -11883,7 +11886,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="285" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
         <v>79</v>
       </c>
@@ -11918,7 +11921,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="286" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
         <v>236</v>
       </c>
@@ -11953,7 +11956,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="287" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
         <v>85</v>
       </c>
@@ -11988,7 +11991,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="288" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
         <v>86</v>
       </c>
@@ -12023,7 +12026,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="289" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
         <v>100</v>
       </c>
@@ -12061,7 +12064,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="290" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
         <v>87</v>
       </c>
@@ -12093,7 +12096,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="291" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
         <v>88</v>
       </c>
@@ -12122,7 +12125,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="292" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
         <v>89</v>
       </c>
@@ -12145,7 +12148,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="293" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
         <v>174</v>
       </c>
@@ -12183,7 +12186,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="294" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
         <v>91</v>
       </c>
@@ -12203,7 +12206,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="295" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
         <v>188</v>
       </c>
@@ -12223,7 +12226,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="296" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A296" s="10" t="s">
         <v>199</v>
       </c>
@@ -12273,7 +12276,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="297" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A297" s="10" t="s">
         <v>200</v>
       </c>
@@ -12323,7 +12326,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="298" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
         <v>59</v>
       </c>
@@ -12370,7 +12373,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="299" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
         <v>212</v>
       </c>
@@ -12390,7 +12393,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="300" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
         <v>188</v>
       </c>
@@ -12410,7 +12413,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="301" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
         <v>91</v>
       </c>
@@ -12430,7 +12433,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="302" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
         <v>186</v>
       </c>
@@ -12450,7 +12453,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="303" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
         <v>189</v>
       </c>
@@ -12470,7 +12473,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="304" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
         <v>92</v>
       </c>
@@ -12490,7 +12493,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="305" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
         <v>190</v>
       </c>
@@ -12510,7 +12513,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="306" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
         <v>37</v>
       </c>
@@ -12554,7 +12557,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="307" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
         <v>192</v>
       </c>
@@ -12589,7 +12592,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="308" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
         <v>191</v>
       </c>
@@ -12624,7 +12627,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="309" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
         <v>193</v>
       </c>
@@ -12659,7 +12662,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="310" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
         <v>94</v>
       </c>
@@ -12697,7 +12700,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="311" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A311" s="10" t="s">
         <v>198</v>
       </c>
@@ -12745,7 +12748,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="312" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A312" s="9" t="s">
         <v>196</v>
       </c>
@@ -12795,7 +12798,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="313" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A313" s="10" t="s">
         <v>201</v>
       </c>
@@ -12845,7 +12848,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="314" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A314" s="9" t="s">
         <v>202</v>
       </c>
@@ -12895,7 +12898,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="315" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
         <v>194</v>
       </c>
@@ -12924,7 +12927,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="316" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
         <v>195</v>
       </c>
@@ -12959,7 +12962,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="317" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A317" s="10" t="s">
         <v>203</v>
       </c>
@@ -13009,7 +13012,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="318" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A318" s="9" t="s">
         <v>196</v>
       </c>
@@ -13059,7 +13062,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="319" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A319" s="10" t="s">
         <v>197</v>
       </c>
@@ -13109,7 +13112,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="320" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
         <v>178</v>
       </c>
@@ -13153,7 +13156,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="321" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
         <v>205</v>
       </c>
@@ -13203,7 +13206,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="322" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
         <v>206</v>
       </c>
@@ -13253,7 +13256,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="323" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
         <v>209</v>
       </c>
@@ -13303,7 +13306,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="324" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
         <v>79</v>
       </c>
@@ -13338,7 +13341,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="325" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
         <v>204</v>
       </c>
@@ -13373,7 +13376,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="326" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
         <v>85</v>
       </c>
@@ -13408,7 +13411,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="327" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
         <v>198</v>
       </c>
@@ -13458,7 +13461,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="328" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
         <v>94</v>
       </c>
@@ -13490,7 +13493,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="329" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
         <v>86</v>
       </c>
@@ -13528,7 +13531,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="330" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
         <v>211</v>
       </c>
@@ -13563,7 +13566,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="331" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
         <v>87</v>
       </c>
@@ -13598,7 +13601,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="332" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
         <v>210</v>
       </c>
@@ -13648,7 +13651,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="333" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
         <v>207</v>
       </c>
@@ -13698,7 +13701,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="334" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
         <v>208</v>
       </c>
@@ -13745,7 +13748,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="335" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
         <v>212</v>
       </c>
@@ -13765,7 +13768,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="336" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
         <v>186</v>
       </c>
@@ -13785,7 +13788,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="337" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
         <v>91</v>
       </c>
@@ -13805,7 +13808,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="338" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
         <v>92</v>
       </c>
@@ -13825,7 +13828,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="339" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
         <v>213</v>
       </c>
@@ -13845,7 +13848,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="340" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
         <v>214</v>
       </c>
@@ -13865,7 +13868,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="341" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
         <v>212</v>
       </c>
@@ -13885,7 +13888,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="342" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
         <v>91</v>
       </c>
@@ -13905,7 +13908,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="343" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
         <v>186</v>
       </c>
@@ -13925,7 +13928,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="344" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
         <v>214</v>
       </c>
@@ -13945,7 +13948,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="345" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
         <v>189</v>
       </c>
@@ -13965,7 +13968,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="346" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
         <v>92</v>
       </c>
@@ -13985,7 +13988,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="347" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
         <v>178</v>
       </c>
@@ -14032,7 +14035,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="348" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
         <v>156</v>
       </c>
@@ -14070,7 +14073,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="349" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
         <v>37</v>
       </c>
@@ -14114,7 +14117,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="350" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
         <v>231</v>
       </c>
@@ -14149,7 +14152,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="351" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
         <v>220</v>
       </c>
@@ -14199,7 +14202,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="352" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
         <v>225</v>
       </c>
@@ -14249,7 +14252,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="353" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
         <v>179</v>
       </c>
@@ -14299,7 +14302,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="354" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
         <v>154</v>
       </c>
@@ -14337,7 +14340,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="355" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
         <v>221</v>
       </c>
@@ -14387,7 +14390,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="356" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
         <v>295</v>
       </c>
@@ -14416,7 +14419,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="357" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
         <v>296</v>
       </c>
@@ -14451,7 +14454,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="358" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
         <v>222</v>
       </c>
@@ -14501,7 +14504,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="359" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A359" t="s">
         <v>223</v>
       </c>
@@ -14551,7 +14554,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="360" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A360" t="s">
         <v>94</v>
       </c>
@@ -14589,7 +14592,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="361" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A361" t="s">
         <v>89</v>
       </c>
@@ -14627,7 +14630,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="362" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A362" t="s">
         <v>18</v>
       </c>
@@ -14662,7 +14665,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="363" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
         <v>215</v>
       </c>
@@ -14703,7 +14706,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="364" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A364" t="s">
         <v>216</v>
       </c>
@@ -14735,7 +14738,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="365" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A365" t="s">
         <v>217</v>
       </c>
@@ -14773,7 +14776,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="366" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A366" t="s">
         <v>218</v>
       </c>
@@ -14811,7 +14814,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="367" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A367" t="s">
         <v>212</v>
       </c>
@@ -14834,7 +14837,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="368" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A368" t="s">
         <v>186</v>
       </c>
@@ -14857,7 +14860,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="369" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A369" t="s">
         <v>91</v>
       </c>
@@ -14880,7 +14883,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="370" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A370" t="s">
         <v>92</v>
       </c>
@@ -14903,7 +14906,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="371" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A371" t="s">
         <v>190</v>
       </c>
@@ -14926,7 +14929,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="372" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A372" t="s">
         <v>224</v>
       </c>
@@ -14949,7 +14952,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="373" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A373" t="s">
         <v>59</v>
       </c>
@@ -14993,7 +14996,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="374" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A374" t="s">
         <v>229</v>
       </c>
@@ -15028,7 +15031,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="375" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A375" t="s">
         <v>100</v>
       </c>
@@ -15069,7 +15072,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="376" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A376" t="s">
         <v>87</v>
       </c>
@@ -15104,7 +15107,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="377" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A377" t="s">
         <v>88</v>
       </c>
@@ -15145,7 +15148,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="378" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A378" t="s">
         <v>297</v>
       </c>
@@ -15180,7 +15183,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="379" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A379" t="s">
         <v>298</v>
       </c>
@@ -15215,7 +15218,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="380" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A380" t="s">
         <v>174</v>
       </c>
@@ -15247,7 +15250,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="381" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A381" t="s">
         <v>299</v>
       </c>
@@ -15282,7 +15285,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="382" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A382" t="s">
         <v>300</v>
       </c>
@@ -15317,7 +15320,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="383" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A383" t="s">
         <v>79</v>
       </c>
@@ -15361,7 +15364,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="384" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A384" t="s">
         <v>236</v>
       </c>
@@ -15408,7 +15411,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="385" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A385" t="s">
         <v>85</v>
       </c>
@@ -15443,7 +15446,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="386" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A386" t="s">
         <v>230</v>
       </c>
@@ -15478,7 +15481,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="387" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A387" t="s">
         <v>231</v>
       </c>
@@ -15510,7 +15513,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="388" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A388" s="10" t="s">
         <v>226</v>
       </c>
@@ -15560,7 +15563,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="389" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A389" s="10" t="s">
         <v>227</v>
       </c>
@@ -15610,7 +15613,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="390" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A390" t="s">
         <v>232</v>
       </c>
@@ -15645,7 +15648,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="391" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A391" t="s">
         <v>234</v>
       </c>
@@ -15695,7 +15698,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="392" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A392" t="s">
         <v>208</v>
       </c>
@@ -15745,7 +15748,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="393" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A393" t="s">
         <v>228</v>
       </c>
@@ -15795,7 +15798,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="394" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A394" t="s">
         <v>231</v>
       </c>
@@ -15824,7 +15827,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="395" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A395" t="s">
         <v>233</v>
       </c>
@@ -15874,7 +15877,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="396" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A396" t="s">
         <v>37</v>
       </c>
@@ -15924,7 +15927,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="397" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A397" t="s">
         <v>208</v>
       </c>
@@ -15974,7 +15977,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="398" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A398" t="s">
         <v>231</v>
       </c>
@@ -16006,7 +16009,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="399" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A399" t="s">
         <v>230</v>
       </c>
@@ -16041,7 +16044,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="400" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A400" t="s">
         <v>79</v>
       </c>
@@ -16091,7 +16094,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="401" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A401" t="s">
         <v>236</v>
       </c>
@@ -16141,7 +16144,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="402" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A402" t="s">
         <v>208</v>
       </c>
@@ -16191,7 +16194,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="403" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="403" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A403" t="s">
         <v>209</v>
       </c>
@@ -16241,7 +16244,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="404" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A404" t="s">
         <v>231</v>
       </c>
@@ -16276,7 +16279,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="405" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A405" t="s">
         <v>198</v>
       </c>
@@ -16326,7 +16329,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="406" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A406" t="s">
         <v>235</v>
       </c>
@@ -16346,7 +16349,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="407" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A407" t="s">
         <v>237</v>
       </c>
@@ -16399,7 +16402,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="408" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="408" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A408" t="s">
         <v>238</v>
       </c>
@@ -16452,7 +16455,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="409" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A409" t="s">
         <v>284</v>
       </c>
@@ -16484,7 +16487,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="410" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A410" t="s">
         <v>239</v>
       </c>
@@ -16537,7 +16540,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="411" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A411" t="s">
         <v>272</v>
       </c>
@@ -16572,7 +16575,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="412" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A412" t="s">
         <v>273</v>
       </c>
@@ -16607,7 +16610,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="413" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="413" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A413" t="s">
         <v>94</v>
       </c>
@@ -16648,7 +16651,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="414" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A414" t="s">
         <v>89</v>
       </c>
@@ -16680,7 +16683,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="415" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A415" t="s">
         <v>212</v>
       </c>
@@ -16700,7 +16703,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="416" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A416" t="s">
         <v>186</v>
       </c>
@@ -16720,7 +16723,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="417" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A417" t="s">
         <v>91</v>
       </c>
@@ -16740,7 +16743,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="418" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="418" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A418" t="s">
         <v>189</v>
       </c>
@@ -16760,7 +16763,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="419" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="419" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A419" t="s">
         <v>92</v>
       </c>
@@ -16780,7 +16783,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="420" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="420" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A420" t="s">
         <v>224</v>
       </c>
@@ -16800,7 +16803,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="421" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A421" t="s">
         <v>198</v>
       </c>
@@ -16850,7 +16853,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="422" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="422" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A422" t="s">
         <v>236</v>
       </c>
@@ -16903,7 +16906,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="423" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="423" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A423" t="s">
         <v>79</v>
       </c>
@@ -16956,7 +16959,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="424" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="424" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A424" t="s">
         <v>241</v>
       </c>
@@ -17009,7 +17012,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="425" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="425" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A425" t="s">
         <v>240</v>
       </c>
@@ -17062,7 +17065,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="426" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="426" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A426" s="10" t="s">
         <v>246</v>
       </c>
@@ -17112,7 +17115,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="427" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="427" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A427" s="10" t="s">
         <v>248</v>
       </c>
@@ -17162,7 +17165,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="428" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="428" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A428" t="s">
         <v>274</v>
       </c>
@@ -17197,7 +17200,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="429" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="429" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A429" t="s">
         <v>278</v>
       </c>
@@ -17232,7 +17235,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="430" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="430" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A430" t="s">
         <v>242</v>
       </c>
@@ -17285,7 +17288,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="431" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="431" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A431" t="s">
         <v>92</v>
       </c>
@@ -17338,7 +17341,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="432" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="432" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A432" t="s">
         <v>243</v>
       </c>
@@ -17391,7 +17394,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="433" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="433" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A433" t="s">
         <v>85</v>
       </c>
@@ -17444,7 +17447,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="434" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="434" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A434" s="10" t="s">
         <v>249</v>
       </c>
@@ -17494,7 +17497,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="435" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="435" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A435" t="s">
         <v>275</v>
       </c>
@@ -17529,7 +17532,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="436" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="436" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A436" t="s">
         <v>231</v>
       </c>
@@ -17561,7 +17564,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="437" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="437" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A437" t="s">
         <v>94</v>
       </c>
@@ -17593,7 +17596,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="438" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="438" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A438" t="s">
         <v>89</v>
       </c>
@@ -17637,7 +17640,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="439" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="439" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A439" t="s">
         <v>247</v>
       </c>
@@ -17672,7 +17675,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="440" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="440" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A440" t="s">
         <v>79</v>
       </c>
@@ -17725,7 +17728,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="441" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="441" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A441" t="s">
         <v>244</v>
       </c>
@@ -17778,7 +17781,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="442" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="442" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A442" t="s">
         <v>236</v>
       </c>
@@ -17831,7 +17834,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="443" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="443" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A443" t="s">
         <v>85</v>
       </c>
@@ -17884,7 +17887,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="444" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="444" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A444" t="s">
         <v>243</v>
       </c>
@@ -17937,7 +17940,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="445" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="445" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A445" s="10" t="s">
         <v>246</v>
       </c>
@@ -17987,7 +17990,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="446" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="446" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A446" t="s">
         <v>250</v>
       </c>
@@ -18028,7 +18031,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="447" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="447" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A447" t="s">
         <v>37</v>
       </c>
@@ -18066,7 +18069,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="448" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="448" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A448" t="s">
         <v>221</v>
       </c>
@@ -18116,7 +18119,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="449" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="449" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A449" t="s">
         <v>241</v>
       </c>
@@ -18157,7 +18160,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="450" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="450" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A450" t="s">
         <v>231</v>
       </c>
@@ -18189,7 +18192,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="451" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="451" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A451" t="s">
         <v>251</v>
       </c>
@@ -18221,7 +18224,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="452" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="452" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A452" t="s">
         <v>198</v>
       </c>
@@ -18271,7 +18274,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="453" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="453" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A453" t="s">
         <v>85</v>
       </c>
@@ -18309,7 +18312,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="454" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="454" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A454" t="s">
         <v>243</v>
       </c>
@@ -18344,7 +18347,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="455" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="455" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A455" t="s">
         <v>256</v>
       </c>
@@ -18388,7 +18391,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="456" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="456" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A456" t="s">
         <v>344</v>
       </c>
@@ -18426,7 +18429,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="457" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="457" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A457" t="s">
         <v>254</v>
       </c>
@@ -18476,7 +18479,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="458" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="458" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A458" t="s">
         <v>257</v>
       </c>
@@ -18526,7 +18529,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="459" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="459" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A459" t="s">
         <v>59</v>
       </c>
@@ -18570,7 +18573,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="460" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="460" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A460" t="s">
         <v>325</v>
       </c>
@@ -18620,7 +18623,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="461" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="461" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A461" t="s">
         <v>253</v>
       </c>
@@ -18652,7 +18655,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="462" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="462" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A462" t="s">
         <v>286</v>
       </c>
@@ -18681,7 +18684,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="463" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="463" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A463" t="s">
         <v>287</v>
       </c>
@@ -18710,7 +18713,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="464" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="464" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A464" t="s">
         <v>288</v>
       </c>
@@ -18739,7 +18742,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="465" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="465" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A465" t="s">
         <v>345</v>
       </c>
@@ -18777,7 +18780,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="466" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="466" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A466" t="s">
         <v>346</v>
       </c>
@@ -18812,7 +18815,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="467" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="467" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A467" t="s">
         <v>347</v>
       </c>
@@ -18847,7 +18850,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="468" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="468" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A468" t="s">
         <v>246</v>
       </c>
@@ -18897,7 +18900,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="469" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="469" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A469" t="s">
         <v>265</v>
       </c>
@@ -18944,7 +18947,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="470" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="470" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A470" t="s">
         <v>267</v>
       </c>
@@ -18982,7 +18985,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="471" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="471" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A471" t="s">
         <v>268</v>
       </c>
@@ -19018,7 +19021,7 @@
       </c>
       <c r="T471" s="2"/>
     </row>
-    <row r="472" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="472" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A472" t="s">
         <v>85</v>
       </c>
@@ -19054,7 +19057,7 @@
       </c>
       <c r="T472" s="2"/>
     </row>
-    <row r="473" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="473" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A473" t="s">
         <v>243</v>
       </c>
@@ -19093,7 +19096,7 @@
       </c>
       <c r="T473" s="2"/>
     </row>
-    <row r="474" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="474" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A474" t="s">
         <v>244</v>
       </c>
@@ -19129,7 +19132,7 @@
       </c>
       <c r="T474" s="2"/>
     </row>
-    <row r="475" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="475" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A475" t="s">
         <v>276</v>
       </c>
@@ -19165,7 +19168,7 @@
       </c>
       <c r="T475" s="2"/>
     </row>
-    <row r="476" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="476" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A476" t="s">
         <v>277</v>
       </c>
@@ -19201,7 +19204,7 @@
       </c>
       <c r="T476" s="2"/>
     </row>
-    <row r="477" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="477" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A477" t="s">
         <v>278</v>
       </c>
@@ -19237,7 +19240,7 @@
       </c>
       <c r="T477" s="2"/>
     </row>
-    <row r="478" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="478" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A478" t="s">
         <v>243</v>
       </c>
@@ -19285,7 +19288,7 @@
       </c>
       <c r="T478" s="2"/>
     </row>
-    <row r="479" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="479" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A479" t="s">
         <v>258</v>
       </c>
@@ -19306,7 +19309,7 @@
       </c>
       <c r="T479" s="2"/>
     </row>
-    <row r="480" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="480" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A480" t="s">
         <v>210</v>
       </c>
@@ -19357,7 +19360,7 @@
       </c>
       <c r="T480" s="2"/>
     </row>
-    <row r="481" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="481" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A481" t="s">
         <v>270</v>
       </c>
@@ -19396,7 +19399,7 @@
       </c>
       <c r="T481" s="2"/>
     </row>
-    <row r="482" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="482" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A482" t="s">
         <v>269</v>
       </c>
@@ -19432,7 +19435,7 @@
       </c>
       <c r="T482" s="2"/>
     </row>
-    <row r="483" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="483" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A483" t="s">
         <v>282</v>
       </c>
@@ -19462,7 +19465,7 @@
       </c>
       <c r="T483" s="2"/>
     </row>
-    <row r="484" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="484" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A484" t="s">
         <v>259</v>
       </c>
@@ -19483,7 +19486,7 @@
       </c>
       <c r="T484" s="2"/>
     </row>
-    <row r="485" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="485" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A485" t="s">
         <v>279</v>
       </c>
@@ -19522,7 +19525,7 @@
       </c>
       <c r="T485" s="2"/>
     </row>
-    <row r="486" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="486" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A486" t="s">
         <v>280</v>
       </c>
@@ -19561,7 +19564,7 @@
       </c>
       <c r="T486" s="2"/>
     </row>
-    <row r="487" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="487" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A487" t="s">
         <v>281</v>
       </c>
@@ -19596,7 +19599,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="488" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="488" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A488" t="s">
         <v>283</v>
       </c>
@@ -19634,7 +19637,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="489" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="489" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A489" t="s">
         <v>387</v>
       </c>
@@ -19666,7 +19669,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="490" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="490" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A490" t="s">
         <v>120</v>
       </c>
@@ -19701,7 +19704,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="491" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="491" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A491" t="s">
         <v>94</v>
       </c>
@@ -19730,7 +19733,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="492" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="492" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A492" t="s">
         <v>89</v>
       </c>
@@ -19765,7 +19768,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="493" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="493" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A493" t="s">
         <v>260</v>
       </c>
@@ -19785,7 +19788,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="494" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="494" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A494" t="s">
         <v>261</v>
       </c>
@@ -19805,7 +19808,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="495" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="495" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A495" t="s">
         <v>262</v>
       </c>
@@ -19825,7 +19828,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="496" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="496" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A496" t="s">
         <v>263</v>
       </c>
@@ -19845,7 +19848,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="497" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="497" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A497" t="s">
         <v>208</v>
       </c>
@@ -19895,7 +19898,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="498" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="498" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A498" t="s">
         <v>59</v>
       </c>
@@ -19939,7 +19942,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="499" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="499" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A499" t="s">
         <v>308</v>
       </c>
@@ -19974,7 +19977,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="500" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="500" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A500" t="s">
         <v>264</v>
       </c>
@@ -19997,7 +20000,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="501" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="501" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A501" t="s">
         <v>262</v>
       </c>
@@ -20017,7 +20020,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="502" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="502" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A502" t="s">
         <v>289</v>
       </c>
@@ -20049,7 +20052,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="503" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="503" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A503" t="s">
         <v>290</v>
       </c>
@@ -20081,7 +20084,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="504" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="504" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A504" t="s">
         <v>291</v>
       </c>
@@ -20113,7 +20116,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="505" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="505" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A505" t="s">
         <v>212</v>
       </c>
@@ -20147,7 +20150,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="506" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="506" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A506" t="s">
         <v>188</v>
       </c>
@@ -20181,7 +20184,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="507" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="507" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A507" t="s">
         <v>186</v>
       </c>
@@ -20207,7 +20210,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="508" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="508" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A508" t="s">
         <v>91</v>
       </c>
@@ -20233,7 +20236,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="509" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="509" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A509" t="s">
         <v>189</v>
       </c>
@@ -20259,7 +20262,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="510" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="510" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A510" t="s">
         <v>92</v>
       </c>
@@ -20285,7 +20288,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="511" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="511" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A511" t="s">
         <v>224</v>
       </c>
@@ -20311,7 +20314,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="512" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="512" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A512" t="s">
         <v>289</v>
       </c>
@@ -20343,7 +20346,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="513" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="513" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A513" t="s">
         <v>289</v>
       </c>
@@ -20375,7 +20378,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="514" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="514" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A514" t="s">
         <v>301</v>
       </c>
@@ -20428,7 +20431,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="515" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="515" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A515" t="s">
         <v>179</v>
       </c>
@@ -20481,7 +20484,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="516" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="516" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A516" t="s">
         <v>302</v>
       </c>
@@ -20534,7 +20537,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="517" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="517" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A517" t="s">
         <v>304</v>
       </c>
@@ -20584,7 +20587,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="518" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="518" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A518" t="s">
         <v>306</v>
       </c>
@@ -20619,7 +20622,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="519" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="519" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A519" t="s">
         <v>305</v>
       </c>
@@ -20669,7 +20672,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="520" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="520" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A520" t="s">
         <v>309</v>
       </c>
@@ -20704,7 +20707,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="521" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="521" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A521" t="s">
         <v>303</v>
       </c>
@@ -20736,7 +20739,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="522" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="522" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A522" t="s">
         <v>231</v>
       </c>
@@ -20771,7 +20774,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="523" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="523" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A523" t="s">
         <v>348</v>
       </c>
@@ -20803,7 +20806,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="524" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="524" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A524" t="s">
         <v>292</v>
       </c>
@@ -20838,7 +20841,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="525" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="525" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A525" t="s">
         <v>293</v>
       </c>
@@ -20873,7 +20876,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="526" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="526" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A526" t="s">
         <v>294</v>
       </c>
@@ -20908,7 +20911,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="527" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="527" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A527" t="s">
         <v>259</v>
       </c>
@@ -20931,7 +20934,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="528" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="528" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A528" t="s">
         <v>262</v>
       </c>
@@ -20954,7 +20957,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="529" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="529" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A529" t="s">
         <v>307</v>
       </c>
@@ -20992,7 +20995,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="530" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="530" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A530" t="s">
         <v>313</v>
       </c>
@@ -21030,7 +21033,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="531" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="531" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A531" t="s">
         <v>100</v>
       </c>
@@ -21056,7 +21059,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="532" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="532" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A532" t="s">
         <v>86</v>
       </c>
@@ -21085,7 +21088,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="533" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="533" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A533" t="s">
         <v>87</v>
       </c>
@@ -21120,7 +21123,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="534" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="534" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A534" t="s">
         <v>88</v>
       </c>
@@ -21158,7 +21161,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="535" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="535" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A535" t="s">
         <v>297</v>
       </c>
@@ -21193,7 +21196,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="536" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="536" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A536" t="s">
         <v>299</v>
       </c>
@@ -21228,7 +21231,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="537" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="537" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A537" t="s">
         <v>300</v>
       </c>
@@ -21266,7 +21269,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="538" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="538" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A538" t="s">
         <v>320</v>
       </c>
@@ -21295,7 +21298,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="539" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="539" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A539" t="s">
         <v>311</v>
       </c>
@@ -21330,7 +21333,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="540" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="540" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A540" t="s">
         <v>310</v>
       </c>
@@ -21362,7 +21365,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="541" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="541" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A541" t="s">
         <v>312</v>
       </c>
@@ -21400,7 +21403,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="542" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="542" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A542" t="s">
         <v>213</v>
       </c>
@@ -21423,7 +21426,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="543" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="543" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A543" t="s">
         <v>267</v>
       </c>
@@ -21467,7 +21470,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="544" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="544" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A544" t="s">
         <v>268</v>
       </c>
@@ -21517,7 +21520,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="545" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="545" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A545" t="s">
         <v>85</v>
       </c>
@@ -21564,7 +21567,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="546" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="546" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A546" t="s">
         <v>326</v>
       </c>
@@ -21599,7 +21602,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="547" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="547" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A547" t="s">
         <v>325</v>
       </c>
@@ -21631,7 +21634,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="548" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="548" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A548" t="s">
         <v>314</v>
       </c>
@@ -21666,7 +21669,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="549" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="549" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A549" t="s">
         <v>315</v>
       </c>
@@ -21692,7 +21695,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="550" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="550" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A550" t="s">
         <v>316</v>
       </c>
@@ -21718,7 +21721,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="551" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="551" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A551" t="s">
         <v>91</v>
       </c>
@@ -21744,7 +21747,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="552" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="552" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A552" t="s">
         <v>186</v>
       </c>
@@ -21770,7 +21773,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="553" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="553" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A553" t="s">
         <v>317</v>
       </c>
@@ -21796,7 +21799,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="554" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="554" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A554" t="s">
         <v>318</v>
       </c>
@@ -21822,7 +21825,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="555" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="555" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A555" t="s">
         <v>189</v>
       </c>
@@ -21848,7 +21851,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="556" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="556" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A556" t="s">
         <v>319</v>
       </c>
@@ -21874,7 +21877,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="557" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="557" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A557" t="s">
         <v>321</v>
       </c>
@@ -21897,7 +21900,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="558" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="558" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A558" t="s">
         <v>322</v>
       </c>
@@ -21920,7 +21923,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="559" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="559" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A559" t="s">
         <v>323</v>
       </c>
@@ -21943,7 +21946,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="560" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="560" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A560" t="s">
         <v>289</v>
       </c>
@@ -21981,7 +21984,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="561" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="561" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A561" t="s">
         <v>290</v>
       </c>
@@ -22019,7 +22022,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="562" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="562" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A562" t="s">
         <v>59</v>
       </c>
@@ -22063,7 +22066,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="563" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="563" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A563" t="s">
         <v>324</v>
       </c>
@@ -22098,7 +22101,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="564" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="564" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A564" t="s">
         <v>330</v>
       </c>
@@ -22124,7 +22127,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="565" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="565" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A565" t="s">
         <v>94</v>
       </c>
@@ -22153,7 +22156,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="566" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="566" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A566" t="s">
         <v>89</v>
       </c>
@@ -22185,7 +22188,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="567" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="567" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A567" t="s">
         <v>37</v>
       </c>
@@ -22232,7 +22235,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="568" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="568" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A568" t="s">
         <v>320</v>
       </c>
@@ -22258,7 +22261,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="569" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="569" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A569" t="s">
         <v>331</v>
       </c>
@@ -22284,7 +22287,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="570" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="570" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A570" t="s">
         <v>340</v>
       </c>
@@ -22324,7 +22327,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="571" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="571" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A571" t="s">
         <v>380</v>
       </c>
@@ -22359,7 +22362,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="572" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="572" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A572" t="s">
         <v>327</v>
       </c>
@@ -22391,7 +22394,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="573" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="573" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A573" t="s">
         <v>328</v>
       </c>
@@ -22426,7 +22429,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="574" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="574" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A574" t="s">
         <v>329</v>
       </c>
@@ -22458,7 +22461,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="575" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="575" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A575" t="s">
         <v>303</v>
       </c>
@@ -22493,7 +22496,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="576" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="576" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A576" t="s">
         <v>332</v>
       </c>
@@ -22516,7 +22519,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="577" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="577" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A577" t="s">
         <v>258</v>
       </c>
@@ -22539,7 +22542,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="578" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="578" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A578" t="s">
         <v>263</v>
       </c>
@@ -22562,7 +22565,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="579" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="579" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A579" t="s">
         <v>258</v>
       </c>
@@ -22606,7 +22609,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="580" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="580" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A580" t="s">
         <v>335</v>
       </c>
@@ -22641,7 +22644,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="581" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="581" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A581" t="s">
         <v>263</v>
       </c>
@@ -22664,7 +22667,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="582" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="582" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A582" t="s">
         <v>213</v>
       </c>
@@ -22687,7 +22690,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="583" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="583" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A583" t="s">
         <v>333</v>
       </c>
@@ -22713,7 +22716,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="584" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="584" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A584" t="s">
         <v>303</v>
       </c>
@@ -22748,7 +22751,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="585" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="585" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A585" t="s">
         <v>326</v>
       </c>
@@ -22798,7 +22801,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="586" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="586" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A586" t="s">
         <v>334</v>
       </c>
@@ -22833,7 +22836,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="587" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="587" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A587" t="s">
         <v>267</v>
       </c>
@@ -22886,7 +22889,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="588" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="588" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A588" t="s">
         <v>268</v>
       </c>
@@ -22939,7 +22942,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="589" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="589" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A589" t="s">
         <v>85</v>
       </c>
@@ -22992,7 +22995,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="590" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="590" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A590" t="s">
         <v>243</v>
       </c>
@@ -23045,7 +23048,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="591" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="591" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A591" t="s">
         <v>94</v>
       </c>
@@ -23080,7 +23083,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="592" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="592" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A592" t="s">
         <v>89</v>
       </c>
@@ -23112,7 +23115,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="593" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="593" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A593" t="s">
         <v>291</v>
       </c>
@@ -23150,7 +23153,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="594" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="594" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A594" t="s">
         <v>336</v>
       </c>
@@ -23188,7 +23191,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="595" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="595" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A595" t="s">
         <v>337</v>
       </c>
@@ -23217,7 +23220,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="596" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="596" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A596" t="s">
         <v>258</v>
       </c>
@@ -23255,7 +23258,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="597" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="597" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A597" t="s">
         <v>263</v>
       </c>
@@ -23290,7 +23293,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="598" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="598" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A598" t="s">
         <v>339</v>
       </c>
@@ -23328,7 +23331,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="599" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="599" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A599" t="s">
         <v>341</v>
       </c>
@@ -23367,7 +23370,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="600" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="600" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A600" t="s">
         <v>263</v>
       </c>
@@ -23387,7 +23390,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="601" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="601" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A601" t="s">
         <v>213</v>
       </c>
@@ -23407,7 +23410,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="602" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="602" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A602" t="s">
         <v>342</v>
       </c>
@@ -23427,7 +23430,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="603" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="603" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A603" t="s">
         <v>343</v>
       </c>
@@ -23447,7 +23450,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="604" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="604" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A604" t="s">
         <v>354</v>
       </c>
@@ -23467,7 +23470,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="605" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="605" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A605" t="s">
         <v>338</v>
       </c>
@@ -23517,7 +23520,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="606" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="606" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A606" t="s">
         <v>59</v>
       </c>
@@ -23561,7 +23564,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="607" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="607" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A607" t="s">
         <v>303</v>
       </c>
@@ -23584,7 +23587,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="608" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="608" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A608" t="s">
         <v>213</v>
       </c>
@@ -23607,7 +23610,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="609" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="609" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A609" t="s">
         <v>355</v>
       </c>
@@ -23630,7 +23633,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="610" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="610" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A610" t="s">
         <v>354</v>
       </c>
@@ -23653,7 +23656,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="611" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="611" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A611" t="s">
         <v>356</v>
       </c>
@@ -23676,7 +23679,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="612" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="612" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A612" t="s">
         <v>258</v>
       </c>
@@ -23699,7 +23702,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="613" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="613" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A613" t="s">
         <v>303</v>
       </c>
@@ -23722,7 +23725,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="614" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="614" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A614" t="s">
         <v>320</v>
       </c>
@@ -23745,7 +23748,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="615" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="615" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A615" t="s">
         <v>303</v>
       </c>
@@ -23768,7 +23771,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="616" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="616" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A616" t="s">
         <v>213</v>
       </c>
@@ -23791,7 +23794,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="617" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="617" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A617" t="s">
         <v>355</v>
       </c>
@@ -23814,7 +23817,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="618" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="618" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A618" t="s">
         <v>365</v>
       </c>
@@ -23852,7 +23855,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="619" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="619" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A619" t="s">
         <v>268</v>
       </c>
@@ -23897,7 +23900,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="620" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="620" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A620" t="s">
         <v>85</v>
       </c>
@@ -23939,7 +23942,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="621" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="621" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A621" t="s">
         <v>351</v>
       </c>
@@ -23972,7 +23975,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="622" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="622" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A622" t="s">
         <v>79</v>
       </c>
@@ -24011,7 +24014,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="623" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="623" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A623" t="s">
         <v>303</v>
       </c>
@@ -24034,7 +24037,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="624" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="624" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A624" t="s">
         <v>303</v>
       </c>
@@ -24057,7 +24060,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="625" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="625" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A625" t="s">
         <v>355</v>
       </c>
@@ -24080,7 +24083,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="626" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="626" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A626" t="s">
         <v>357</v>
       </c>
@@ -24103,7 +24106,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="627" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="627" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A627" t="s">
         <v>354</v>
       </c>
@@ -24126,7 +24129,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="628" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="628" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A628" t="s">
         <v>358</v>
       </c>
@@ -24149,7 +24152,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="629" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="629" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A629" t="s">
         <v>359</v>
       </c>
@@ -24172,7 +24175,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="630" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="630" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A630" t="s">
         <v>94</v>
       </c>
@@ -24213,7 +24216,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="631" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="631" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A631" t="s">
         <v>89</v>
       </c>
@@ -24248,7 +24251,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="632" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="632" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A632" t="s">
         <v>415</v>
       </c>
@@ -24280,7 +24283,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="633" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="633" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A633" t="s">
         <v>314</v>
       </c>
@@ -24313,7 +24316,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="634" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="634" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A634" t="s">
         <v>360</v>
       </c>
@@ -24342,7 +24345,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="635" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="635" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A635" t="s">
         <v>361</v>
       </c>
@@ -24371,7 +24374,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="636" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="636" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A636" t="s">
         <v>59</v>
       </c>
@@ -24407,7 +24410,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="637" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="637" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A637" t="s">
         <v>353</v>
       </c>
@@ -24442,7 +24445,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="638" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="638" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A638" t="s">
         <v>355</v>
       </c>
@@ -24465,7 +24468,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="639" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="639" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A639" t="s">
         <v>303</v>
       </c>
@@ -24488,7 +24491,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="640" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="640" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A640" t="s">
         <v>86</v>
       </c>
@@ -24529,7 +24532,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="641" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="641" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A641" t="s">
         <v>100</v>
       </c>
@@ -24570,7 +24573,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="642" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="642" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A642" t="s">
         <v>355</v>
       </c>
@@ -24603,7 +24606,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="643" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="643" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A643" t="s">
         <v>372</v>
       </c>
@@ -24641,7 +24644,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="644" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="644" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A644" t="s">
         <v>373</v>
       </c>
@@ -24676,7 +24679,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="645" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="645" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A645" t="s">
         <v>87</v>
       </c>
@@ -24714,7 +24717,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="646" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="646" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A646" t="s">
         <v>88</v>
       </c>
@@ -24755,7 +24758,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="647" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="647" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A647" t="s">
         <v>89</v>
       </c>
@@ -24799,7 +24802,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="648" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="648" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A648" t="s">
         <v>377</v>
       </c>
@@ -24840,7 +24843,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="649" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="649" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A649" t="s">
         <v>381</v>
       </c>
@@ -24875,7 +24878,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="650" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="650" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A650" t="s">
         <v>303</v>
       </c>
@@ -24908,7 +24911,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="651" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="651" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A651" t="s">
         <v>320</v>
       </c>
@@ -24941,7 +24944,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="652" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="652" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A652" t="s">
         <v>268</v>
       </c>
@@ -24995,7 +24998,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="653" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="653" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A653" t="s">
         <v>351</v>
       </c>
@@ -25049,7 +25052,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="654" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="654" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A654" t="s">
         <v>79</v>
       </c>
@@ -25103,7 +25106,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="655" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="655" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A655" t="s">
         <v>362</v>
       </c>
@@ -25156,7 +25159,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="656" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="656" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A656" t="s">
         <v>354</v>
       </c>
@@ -25189,7 +25192,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="657" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="657" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A657" t="s">
         <v>213</v>
       </c>
@@ -25222,7 +25225,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="658" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="658" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A658" t="s">
         <v>363</v>
       </c>
@@ -25275,7 +25278,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="659" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="659" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A659" t="s">
         <v>364</v>
       </c>
@@ -25328,7 +25331,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="660" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="660" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A660" s="17" t="s">
         <v>366</v>
       </c>
@@ -25365,14 +25368,14 @@
         <v>56</v>
       </c>
       <c r="P660" s="17">
-        <f t="shared" ref="P660:P666" si="0">SUM(F660:I660,K660:O660)</f>
+        <f>SUM(F660:I660,K660:O660)</f>
         <v>1111</v>
       </c>
       <c r="Q660" t="s">
         <v>367</v>
       </c>
     </row>
-    <row r="661" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="661" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A661" t="s">
         <v>212</v>
       </c>
@@ -25398,14 +25401,14 @@
         <v>111</v>
       </c>
       <c r="P661">
-        <f t="shared" si="0"/>
+        <f>SUM(F661:I661,K661:O661)</f>
         <v>444</v>
       </c>
       <c r="Q661" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="662" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="662" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A662" t="s">
         <v>91</v>
       </c>
@@ -25431,14 +25434,14 @@
         <v>0</v>
       </c>
       <c r="P662">
-        <f t="shared" si="0"/>
+        <f>SUM(F662:I662,K662:O662)</f>
         <v>56</v>
       </c>
       <c r="Q662" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="663" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="663" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A663" t="s">
         <v>186</v>
       </c>
@@ -25464,14 +25467,14 @@
         <v>167</v>
       </c>
       <c r="P663">
-        <f t="shared" si="0"/>
+        <f>SUM(F663:I663,K663:O663)</f>
         <v>167</v>
       </c>
       <c r="Q663" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="664" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="664" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A664" t="s">
         <v>317</v>
       </c>
@@ -25497,14 +25500,14 @@
         <v>56</v>
       </c>
       <c r="P664">
-        <f t="shared" si="0"/>
+        <f>SUM(F664:I664,K664:O664)</f>
         <v>112</v>
       </c>
       <c r="Q664" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="665" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="665" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A665" t="s">
         <v>189</v>
       </c>
@@ -25530,14 +25533,14 @@
         <v>0</v>
       </c>
       <c r="P665">
-        <f t="shared" si="0"/>
+        <f>SUM(F665:I665,K665:O665)</f>
         <v>0</v>
       </c>
       <c r="Q665" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="666" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="666" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A666" t="s">
         <v>319</v>
       </c>
@@ -25563,14 +25566,14 @@
         <v>222</v>
       </c>
       <c r="P666">
-        <f t="shared" si="0"/>
+        <f>SUM(F666:I666,K666:O666)</f>
         <v>278</v>
       </c>
       <c r="Q666" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="667" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="667" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A667" t="s">
         <v>370</v>
       </c>
@@ -25602,7 +25605,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="668" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="668" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A668" t="s">
         <v>371</v>
       </c>
@@ -25637,7 +25640,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="669" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="669" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A669" t="s">
         <v>303</v>
       </c>
@@ -25672,7 +25675,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="670" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="670" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A670" t="s">
         <v>368</v>
       </c>
@@ -25707,7 +25710,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="671" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="671" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A671" t="s">
         <v>213</v>
       </c>
@@ -25740,7 +25743,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="672" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="672" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A672" t="s">
         <v>92</v>
       </c>
@@ -25794,7 +25797,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="673" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="673" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A673" t="s">
         <v>89</v>
       </c>
@@ -25823,7 +25826,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="674" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="674" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A674" t="s">
         <v>389</v>
       </c>
@@ -25873,7 +25876,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="675" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="675" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A675" t="s">
         <v>359</v>
       </c>
@@ -25906,7 +25909,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="676" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="676" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A676" t="s">
         <v>130</v>
       </c>
@@ -25960,7 +25963,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="677" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="677" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A677" t="s">
         <v>369</v>
       </c>
@@ -26014,7 +26017,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="678" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="678" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A678" t="s">
         <v>59</v>
       </c>
@@ -26052,7 +26055,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="679" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="679" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A679" t="s">
         <v>59</v>
       </c>
@@ -26090,7 +26093,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="680" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="680" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A680" t="s">
         <v>383</v>
       </c>
@@ -26113,7 +26116,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="681" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="681" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A681" t="s">
         <v>263</v>
       </c>
@@ -26133,7 +26136,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="682" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="682" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A682" t="s">
         <v>384</v>
       </c>
@@ -26156,7 +26159,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="683" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="683" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A683" t="s">
         <v>385</v>
       </c>
@@ -26179,7 +26182,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="684" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="684" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A684" t="s">
         <v>303</v>
       </c>
@@ -26202,7 +26205,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="685" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="685" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A685" t="s">
         <v>37</v>
       </c>
@@ -26249,7 +26252,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="686" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="686" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A686" t="s">
         <v>376</v>
       </c>
@@ -26290,7 +26293,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="687" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="687" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A687" t="s">
         <v>381</v>
       </c>
@@ -26325,7 +26328,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="688" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="688" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A688" t="s">
         <v>383</v>
       </c>
@@ -26348,7 +26351,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="689" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="689" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A689" t="s">
         <v>375</v>
       </c>
@@ -26386,7 +26389,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="690" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="690" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A690" t="s">
         <v>304</v>
       </c>
@@ -26439,7 +26442,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="691" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="691" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A691" t="s">
         <v>363</v>
       </c>
@@ -26492,7 +26495,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="692" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="692" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A692" t="s">
         <v>378</v>
       </c>
@@ -26542,7 +26545,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="693" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="693" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A693" t="s">
         <v>379</v>
       </c>
@@ -26595,7 +26598,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="694" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="694" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A694" t="s">
         <v>383</v>
       </c>
@@ -26618,7 +26621,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="695" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="695" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A695" t="s">
         <v>384</v>
       </c>
@@ -26641,7 +26644,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="696" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="696" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A696" t="s">
         <v>396</v>
       </c>
@@ -26682,7 +26685,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="697" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="697" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A697" t="s">
         <v>376</v>
       </c>
@@ -26720,7 +26723,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="698" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="698" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A698" t="s">
         <v>382</v>
       </c>
@@ -26758,7 +26761,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="699" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="699" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A699" t="s">
         <v>383</v>
       </c>
@@ -26781,7 +26784,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="700" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="700" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A700" t="s">
         <v>303</v>
       </c>
@@ -26804,7 +26807,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="701" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="701" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A701" t="s">
         <v>383</v>
       </c>
@@ -26827,7 +26830,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="702" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="702" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A702" t="s">
         <v>378</v>
       </c>
@@ -26880,7 +26883,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="703" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="703" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A703" t="s">
         <v>389</v>
       </c>
@@ -26933,7 +26936,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="704" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="704" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A704" t="s">
         <v>268</v>
       </c>
@@ -26975,7 +26978,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="705" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="705" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A705" t="s">
         <v>85</v>
       </c>
@@ -27014,7 +27017,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="706" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="706" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A706" t="s">
         <v>79</v>
       </c>
@@ -27053,7 +27056,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="707" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="707" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A707" t="s">
         <v>315</v>
       </c>
@@ -27085,7 +27088,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="708" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="708" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A708" t="s">
         <v>188</v>
       </c>
@@ -27117,7 +27120,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="709" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="709" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A709" t="s">
         <v>91</v>
       </c>
@@ -27149,7 +27152,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="710" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="710" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A710" t="s">
         <v>186</v>
       </c>
@@ -27181,7 +27184,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="711" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="711" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A711" t="s">
         <v>317</v>
       </c>
@@ -27213,7 +27216,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="712" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="712" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A712" t="s">
         <v>189</v>
       </c>
@@ -27245,7 +27248,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="713" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="713" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A713" t="s">
         <v>319</v>
       </c>
@@ -27277,7 +27280,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="714" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="714" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A714" t="s">
         <v>387</v>
       </c>
@@ -27315,7 +27318,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="715" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="715" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A715" t="s">
         <v>388</v>
       </c>
@@ -27368,7 +27371,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="716" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="716" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A716" t="s">
         <v>386</v>
       </c>
@@ -27391,7 +27394,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="717" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="717" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A717" t="s">
         <v>94</v>
       </c>
@@ -27426,7 +27429,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="718" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="718" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A718" t="s">
         <v>89</v>
       </c>
@@ -27461,7 +27464,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="719" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="719" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A719" t="s">
         <v>415</v>
       </c>
@@ -27493,7 +27496,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="720" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="720" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A720" t="s">
         <v>362</v>
       </c>
@@ -27546,7 +27549,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="721" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="721" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A721" t="s">
         <v>59</v>
       </c>
@@ -27584,7 +27587,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="722" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="722" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A722" t="s">
         <v>390</v>
       </c>
@@ -27628,7 +27631,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="723" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="723" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A723" t="s">
         <v>383</v>
       </c>
@@ -27651,7 +27654,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="724" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="724" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A724" t="s">
         <v>355</v>
       </c>
@@ -27674,7 +27677,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="725" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="725" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A725" t="s">
         <v>59</v>
       </c>
@@ -27712,7 +27715,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="726" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="726" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A726" t="s">
         <v>393</v>
       </c>
@@ -27765,7 +27768,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="727" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="727" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A727" t="s">
         <v>222</v>
       </c>
@@ -27818,7 +27821,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="728" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="728" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A728" t="s">
         <v>392</v>
       </c>
@@ -27853,7 +27856,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="729" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="729" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A729" t="s">
         <v>92</v>
       </c>
@@ -27894,7 +27897,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="730" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="730" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A730" t="s">
         <v>394</v>
       </c>
@@ -27935,7 +27938,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="731" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="731" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A731" t="s">
         <v>86</v>
       </c>
@@ -27976,7 +27979,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="732" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="732" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A732" t="s">
         <v>100</v>
       </c>
@@ -28014,7 +28017,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="733" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="733" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A733" t="s">
         <v>397</v>
       </c>
@@ -28055,7 +28058,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="734" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="734" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A734" t="s">
         <v>87</v>
       </c>
@@ -28093,7 +28096,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="735" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="735" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A735" t="s">
         <v>88</v>
       </c>
@@ -28134,7 +28137,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="736" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="736" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A736" t="s">
         <v>89</v>
       </c>
@@ -28172,7 +28175,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="737" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="737" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A737" t="s">
         <v>377</v>
       </c>
@@ -28210,7 +28213,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="738" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="738" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A738" t="s">
         <v>300</v>
       </c>
@@ -28245,7 +28248,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="739" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="739" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A739" t="s">
         <v>391</v>
       </c>
@@ -28280,7 +28283,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="740" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="740" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A740" t="s">
         <v>351</v>
       </c>
@@ -28318,7 +28321,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="741" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="741" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A741" t="s">
         <v>314</v>
       </c>
@@ -28356,7 +28359,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="742" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="742" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A742" t="s">
         <v>383</v>
       </c>
@@ -28379,7 +28382,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="743" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="743" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A743" t="s">
         <v>389</v>
       </c>
@@ -28432,7 +28435,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="744" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="744" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A744" t="s">
         <v>378</v>
       </c>
@@ -28485,7 +28488,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="745" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="745" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A745" t="s">
         <v>395</v>
       </c>
@@ -28508,7 +28511,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="746" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="746" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A746" t="s">
         <v>359</v>
       </c>
@@ -28531,7 +28534,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="747" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="747" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A747" t="s">
         <v>303</v>
       </c>
@@ -28554,7 +28557,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="748" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="748" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A748" t="s">
         <v>399</v>
       </c>
@@ -28583,7 +28586,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="749" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="749" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A749" t="s">
         <v>230</v>
       </c>
@@ -28621,7 +28624,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="750" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="750" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A750" t="s">
         <v>230</v>
       </c>
@@ -28659,7 +28662,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="751" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="751" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A751" t="s">
         <v>376</v>
       </c>
@@ -28694,7 +28697,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="752" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="752" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A752" t="s">
         <v>378</v>
       </c>
@@ -28747,7 +28750,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="753" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="753" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A753" t="s">
         <v>303</v>
       </c>
@@ -28770,7 +28773,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="754" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="754" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A754" t="s">
         <v>355</v>
       </c>
@@ -28790,7 +28793,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="755" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="755" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A755" t="s">
         <v>79</v>
       </c>
@@ -28822,7 +28825,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="756" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="756" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A756" t="s">
         <v>85</v>
       </c>
@@ -28857,7 +28860,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="757" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="757" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A757" t="s">
         <v>268</v>
       </c>
@@ -28892,7 +28895,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="758" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="758" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A758" t="s">
         <v>391</v>
       </c>
@@ -28927,7 +28930,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="759" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="759" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A759" t="s">
         <v>179</v>
       </c>
@@ -28959,7 +28962,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="760" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="760" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A760" t="s">
         <v>210</v>
       </c>
@@ -29012,7 +29015,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="761" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="761" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A761" t="s">
         <v>400</v>
       </c>
@@ -29044,7 +29047,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="762" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="762" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A762" t="s">
         <v>231</v>
       </c>
@@ -29079,7 +29082,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="763" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="763" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A763" t="s">
         <v>401</v>
       </c>
@@ -29117,7 +29120,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="764" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="764" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A764" t="s">
         <v>402</v>
       </c>
@@ -29155,7 +29158,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="765" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="765" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A765" t="s">
         <v>403</v>
       </c>
@@ -29190,7 +29193,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="766" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="766" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A766" t="s">
         <v>398</v>
       </c>
@@ -29243,7 +29246,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="767" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="767" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A767" t="s">
         <v>362</v>
       </c>
@@ -29296,7 +29299,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="768" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="768" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A768" t="s">
         <v>314</v>
       </c>
@@ -29331,7 +29334,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="769" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="769" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A769" t="s">
         <v>383</v>
       </c>
@@ -29363,7 +29366,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="770" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="770" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A770" t="s">
         <v>314</v>
       </c>
@@ -29401,7 +29404,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="771" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="771" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A771" t="s">
         <v>355</v>
       </c>
@@ -29436,7 +29439,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="772" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="772" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A772" t="s">
         <v>409</v>
       </c>
@@ -29477,7 +29480,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="773" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="773" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A773" t="s">
         <v>351</v>
       </c>
@@ -29518,7 +29521,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="774" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="774" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A774" t="s">
         <v>85</v>
       </c>
@@ -29553,7 +29556,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="775" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="775" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A775" t="s">
         <v>79</v>
       </c>
@@ -29585,7 +29588,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="776" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="776" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A776" t="s">
         <v>268</v>
       </c>
@@ -29623,7 +29626,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="777" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="777" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A777" s="1" t="s">
         <v>315</v>
       </c>
@@ -29656,14 +29659,14 @@
       <c r="N777" s="1"/>
       <c r="O777" s="1"/>
       <c r="P777">
-        <f t="shared" ref="P777:P788" si="1">SUM(F777:I777,K777:O777)</f>
+        <f>SUM(F777:I777,K777:O777)</f>
         <v>722</v>
       </c>
       <c r="Q777" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="778" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="778" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A778" t="s">
         <v>188</v>
       </c>
@@ -29689,14 +29692,14 @@
         <v>111</v>
       </c>
       <c r="P778">
-        <f t="shared" si="1"/>
+        <f>SUM(F778:I778,K778:O778)</f>
         <v>167</v>
       </c>
       <c r="Q778" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="779" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="779" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A779" t="s">
         <v>91</v>
       </c>
@@ -29722,14 +29725,14 @@
         <v>56</v>
       </c>
       <c r="P779">
-        <f t="shared" si="1"/>
+        <f>SUM(F779:I779,K779:O779)</f>
         <v>278</v>
       </c>
       <c r="Q779" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="780" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="780" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A780" t="s">
         <v>186</v>
       </c>
@@ -29755,14 +29758,14 @@
         <v>56</v>
       </c>
       <c r="P780">
-        <f t="shared" si="1"/>
+        <f>SUM(F780:I780,K780:O780)</f>
         <v>112</v>
       </c>
       <c r="Q780" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="781" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="781" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A781" t="s">
         <v>317</v>
       </c>
@@ -29788,14 +29791,14 @@
         <v>0</v>
       </c>
       <c r="P781">
-        <f t="shared" si="1"/>
+        <f>SUM(F781:I781,K781:O781)</f>
         <v>0</v>
       </c>
       <c r="Q781" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="782" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="782" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A782" t="s">
         <v>189</v>
       </c>
@@ -29821,14 +29824,14 @@
         <v>56</v>
       </c>
       <c r="P782">
-        <f t="shared" si="1"/>
+        <f>SUM(F782:I782,K782:O782)</f>
         <v>278</v>
       </c>
       <c r="Q782" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="783" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="783" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A783" t="s">
         <v>319</v>
       </c>
@@ -29854,14 +29857,14 @@
         <v>167</v>
       </c>
       <c r="P783">
-        <f t="shared" si="1"/>
+        <f>SUM(F783:I783,K783:O783)</f>
         <v>445</v>
       </c>
       <c r="Q783" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="784" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="784" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A784" t="s">
         <v>318</v>
       </c>
@@ -29887,14 +29890,14 @@
         <v>0</v>
       </c>
       <c r="P784">
-        <f t="shared" si="1"/>
+        <f>SUM(F784:I784,K784:O784)</f>
         <v>56</v>
       </c>
       <c r="Q784" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="785" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="785" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A785" t="s">
         <v>405</v>
       </c>
@@ -29920,14 +29923,14 @@
         <v>56</v>
       </c>
       <c r="P785">
-        <f t="shared" si="1"/>
+        <f>SUM(F785:I785,K785:O785)</f>
         <v>56</v>
       </c>
       <c r="Q785" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="786" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="786" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A786" t="s">
         <v>406</v>
       </c>
@@ -29953,14 +29956,14 @@
         <v>56</v>
       </c>
       <c r="P786">
-        <f t="shared" si="1"/>
+        <f>SUM(F786:I786,K786:O786)</f>
         <v>56</v>
       </c>
       <c r="Q786" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="787" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="787" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A787" t="s">
         <v>407</v>
       </c>
@@ -29986,14 +29989,14 @@
         <v>0</v>
       </c>
       <c r="P787">
-        <f t="shared" si="1"/>
+        <f>SUM(F787:I787,K787:O787)</f>
         <v>56</v>
       </c>
       <c r="Q787" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="788" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="788" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A788" t="s">
         <v>86</v>
       </c>
@@ -30019,14 +30022,14 @@
         <v>111</v>
       </c>
       <c r="P788">
-        <f t="shared" si="1"/>
+        <f>SUM(F788:I788,K788:O788)</f>
         <v>111</v>
       </c>
       <c r="Q788" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="789" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="789" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A789" t="s">
         <v>341</v>
       </c>
@@ -30064,7 +30067,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="790" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="790" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A790" t="s">
         <v>408</v>
       </c>
@@ -30105,7 +30108,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="791" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="791" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A791" t="s">
         <v>398</v>
       </c>
@@ -30158,7 +30161,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="792" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="792" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A792" t="s">
         <v>210</v>
       </c>
@@ -30211,7 +30214,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="793" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="793" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A793" t="s">
         <v>378</v>
       </c>
@@ -30264,7 +30267,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="794" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="794" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A794" t="s">
         <v>412</v>
       </c>
@@ -30299,7 +30302,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="795" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="795" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A795" t="s">
         <v>93</v>
       </c>
@@ -30334,7 +30337,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="796" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="796" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A796" t="s">
         <v>93</v>
       </c>
@@ -30369,7 +30372,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="797" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="797" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A797" t="s">
         <v>222</v>
       </c>
@@ -30422,7 +30425,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="798" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="798" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A798" t="s">
         <v>59</v>
       </c>
@@ -30463,7 +30466,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="799" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="799" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A799" t="s">
         <v>410</v>
       </c>
@@ -30498,7 +30501,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="800" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="800" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A800" t="s">
         <v>411</v>
       </c>
@@ -30536,7 +30539,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="801" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="801" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A801" t="s">
         <v>362</v>
       </c>
@@ -30589,7 +30592,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="802" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="802" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A802" t="s">
         <v>413</v>
       </c>
@@ -30642,7 +30645,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="803" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="803" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A803" t="s">
         <v>231</v>
       </c>
@@ -30680,7 +30683,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="804" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="804" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A804" t="s">
         <v>393</v>
       </c>
@@ -30733,7 +30736,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="805" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="805" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A805" t="s">
         <v>416</v>
       </c>
@@ -30765,7 +30768,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="806" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="806" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A806" t="s">
         <v>417</v>
       </c>
@@ -30797,7 +30800,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="807" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="807" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A807" t="s">
         <v>94</v>
       </c>
@@ -30829,7 +30832,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="808" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="808" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A808" t="s">
         <v>92</v>
       </c>
@@ -30870,7 +30873,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="809" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="809" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A809" t="s">
         <v>392</v>
       </c>
@@ -30911,7 +30914,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="810" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="810" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A810" t="s">
         <v>314</v>
       </c>
@@ -30949,7 +30952,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="811" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="811" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A811" t="s">
         <v>403</v>
       </c>
@@ -30999,7 +31002,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="812" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="812" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A812" t="s">
         <v>408</v>
       </c>
@@ -31040,7 +31043,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="813" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="813" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A813" t="s">
         <v>414</v>
       </c>
@@ -31093,7 +31096,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="814" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="814" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A814" t="s">
         <v>378</v>
       </c>
@@ -31146,7 +31149,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="815" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="815" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A815" t="s">
         <v>59</v>
       </c>
@@ -31187,7 +31190,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="816" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="816" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A816" t="s">
         <v>420</v>
       </c>
@@ -31240,7 +31243,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="817" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="817" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A817" t="s">
         <v>419</v>
       </c>
@@ -31281,7 +31284,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="818" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="818" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A818" t="s">
         <v>268</v>
       </c>
@@ -31328,7 +31331,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="819" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="819" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A819" t="s">
         <v>79</v>
       </c>
@@ -31360,7 +31363,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="820" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="820" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A820" t="s">
         <v>418</v>
       </c>
@@ -31401,7 +31404,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="821" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="821" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A821" t="s">
         <v>314</v>
       </c>
@@ -31439,7 +31442,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="822" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="822" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A822" t="s">
         <v>421</v>
       </c>
@@ -31492,7 +31495,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="823" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="823" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A823" t="s">
         <v>398</v>
       </c>
@@ -31545,7 +31548,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="824" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="824" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A824" t="s">
         <v>422</v>
       </c>
@@ -31586,7 +31589,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="825" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="825" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A825" t="s">
         <v>424</v>
       </c>
@@ -31630,7 +31633,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="826" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="826" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A826" t="s">
         <v>89</v>
       </c>
@@ -31668,7 +31671,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="827" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="827" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A827" t="s">
         <v>403</v>
       </c>
@@ -31712,7 +31715,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="828" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="828" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A828" t="s">
         <v>425</v>
       </c>
@@ -31753,7 +31756,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="829" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="829" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A829" t="s">
         <v>179</v>
       </c>
@@ -31791,7 +31794,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="830" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="830" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A830" t="s">
         <v>314</v>
       </c>
@@ -31829,7 +31832,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="831" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="831" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A831" t="s">
         <v>423</v>
       </c>
@@ -31882,7 +31885,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="832" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="832" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A832" t="s">
         <v>59</v>
       </c>
@@ -31923,7 +31926,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="833" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="833" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A833" t="s">
         <v>86</v>
       </c>
@@ -31970,7 +31973,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="834" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="834" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A834" t="s">
         <v>87</v>
       </c>
@@ -32014,7 +32017,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="835" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="835" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A835" t="s">
         <v>427</v>
       </c>
@@ -32055,7 +32058,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="836" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="836" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A836" t="s">
         <v>89</v>
       </c>
@@ -32096,7 +32099,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="837" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="837" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A837" t="s">
         <v>426</v>
       </c>
@@ -32134,7 +32137,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="838" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="838" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A838" t="s">
         <v>428</v>
       </c>
@@ -32187,7 +32190,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="839" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="839" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A839" t="s">
         <v>290</v>
       </c>
@@ -32219,7 +32222,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="840" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="840" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A840" t="s">
         <v>341</v>
       </c>
@@ -32263,7 +32266,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="841" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="841" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A841" t="s">
         <v>314</v>
       </c>
@@ -32301,7 +32304,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="842" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="842" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A842" t="s">
         <v>429</v>
       </c>
@@ -32345,9 +32348,228 @@
         <v>352</v>
       </c>
     </row>
+    <row r="843" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A843" t="s">
+        <v>290</v>
+      </c>
+      <c r="B843">
+        <v>-34.629179999999998</v>
+      </c>
+      <c r="C843">
+        <v>135.86635000000001</v>
+      </c>
+      <c r="D843" s="2">
+        <v>46141</v>
+      </c>
+      <c r="I843">
+        <v>56</v>
+      </c>
+      <c r="J843">
+        <v>9</v>
+      </c>
+      <c r="L843">
+        <v>65</v>
+      </c>
+      <c r="N843">
+        <v>46</v>
+      </c>
+      <c r="O843">
+        <v>259</v>
+      </c>
+      <c r="P843">
+        <v>426</v>
+      </c>
+      <c r="Q843" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="844" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A844" t="s">
+        <v>430</v>
+      </c>
+      <c r="B844">
+        <v>-34.891616999999997</v>
+      </c>
+      <c r="C844">
+        <v>137.83265</v>
+      </c>
+      <c r="D844" s="2">
+        <v>46142</v>
+      </c>
+      <c r="E844" s="20">
+        <v>0.40625</v>
+      </c>
+      <c r="I844">
+        <v>56</v>
+      </c>
+      <c r="J844">
+        <v>0</v>
+      </c>
+      <c r="L844">
+        <v>56</v>
+      </c>
+      <c r="N844">
+        <v>56</v>
+      </c>
+      <c r="P844">
+        <v>168</v>
+      </c>
+      <c r="Q844" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="845" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A845" t="s">
+        <v>291</v>
+      </c>
+      <c r="B845">
+        <v>-34.628860000000003</v>
+      </c>
+      <c r="C845">
+        <v>135.86708999999999</v>
+      </c>
+      <c r="D845" s="2">
+        <v>46143</v>
+      </c>
+      <c r="I845">
+        <v>28</v>
+      </c>
+      <c r="J845">
+        <v>19</v>
+      </c>
+      <c r="L845">
+        <v>74</v>
+      </c>
+      <c r="M845">
+        <v>0</v>
+      </c>
+      <c r="N845">
+        <v>0</v>
+      </c>
+      <c r="O845">
+        <v>185</v>
+      </c>
+      <c r="P845">
+        <v>287</v>
+      </c>
+      <c r="Q845" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="846" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A846" t="s">
+        <v>403</v>
+      </c>
+      <c r="B846">
+        <v>-35.510497000000001</v>
+      </c>
+      <c r="C846">
+        <v>138.21676299999999</v>
+      </c>
+      <c r="D846" s="2">
+        <v>46146</v>
+      </c>
+      <c r="E846" s="20">
+        <v>0.3923611111111111</v>
+      </c>
+      <c r="I846">
+        <v>0</v>
+      </c>
+      <c r="J846">
+        <v>0</v>
+      </c>
+      <c r="L846">
+        <v>111</v>
+      </c>
+      <c r="P846">
+        <v>111</v>
+      </c>
+      <c r="Q846" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="847" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A847" t="s">
+        <v>291</v>
+      </c>
+      <c r="B847">
+        <v>-34.628860000000003</v>
+      </c>
+      <c r="C847">
+        <v>135.86708999999999</v>
+      </c>
+      <c r="D847" s="2">
+        <v>46146</v>
+      </c>
+      <c r="E847" s="20">
+        <v>0.375</v>
+      </c>
+      <c r="I847">
+        <v>148</v>
+      </c>
+      <c r="J847">
+        <v>83</v>
+      </c>
+      <c r="L847">
+        <v>250</v>
+      </c>
+      <c r="M847">
+        <v>0</v>
+      </c>
+      <c r="N847">
+        <v>0</v>
+      </c>
+      <c r="O847">
+        <v>65</v>
+      </c>
+      <c r="P847">
+        <v>463</v>
+      </c>
+      <c r="Q847" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="848" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A848" t="s">
+        <v>314</v>
+      </c>
+      <c r="B848">
+        <v>-35.445188000000002</v>
+      </c>
+      <c r="C848">
+        <v>138.307266</v>
+      </c>
+      <c r="D848" s="2">
+        <v>46147</v>
+      </c>
+      <c r="E848" s="20">
+        <v>0.375</v>
+      </c>
+      <c r="I848">
+        <v>333</v>
+      </c>
+      <c r="J848">
+        <v>0</v>
+      </c>
+      <c r="L848">
+        <v>444</v>
+      </c>
+      <c r="N848">
+        <v>167</v>
+      </c>
+      <c r="O848">
+        <v>56</v>
+      </c>
+      <c r="P848">
+        <v>1000</v>
+      </c>
+      <c r="Q848" t="s">
+        <v>352</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q842">
-    <sortCondition ref="D2:D842"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q848">
+    <sortCondition ref="D2:D848"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/MASTER spreadsheet of community summaries.xlsx
+++ b/MASTER spreadsheet of community summaries.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\peri\Dropbox\Delta\Projects\Laboratory\Algal blooms, bacterial counts  for community\For Luke's HAB data display\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A504616A-7E3F-4247-8D1B-3FF7D345E414}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C637A2F-755B-4B12-B6F9-BBF48375C3B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{9286397E-2757-492B-865A-39B2D6A15FF6}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1713" uniqueCount="431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1751" uniqueCount="433">
   <si>
     <t>Date</t>
   </si>
@@ -1349,6 +1349,12 @@
   </si>
   <si>
     <t>Stansbury- ST-05A</t>
+  </si>
+  <si>
+    <t>Louth Bay jetty</t>
+  </si>
+  <si>
+    <t>Lady Bay</t>
   </si>
 </sst>
 </file>
@@ -1818,7 +1824,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F307807-E5C9-4450-88E0-159CBB3E9A67}">
-  <dimension ref="A1:T848"/>
+  <dimension ref="A1:T867"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="39.33203125" customWidth="1"/>
@@ -32268,189 +32274,177 @@
     </row>
     <row r="841" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A841" t="s">
-        <v>314</v>
+        <v>94</v>
       </c>
       <c r="B841">
-        <v>-35.445188000000002</v>
+        <v>-35.58858</v>
       </c>
       <c r="C841">
-        <v>138.307266</v>
+        <v>138.60474600000001</v>
       </c>
       <c r="D841" s="2">
-        <v>46139</v>
-      </c>
-      <c r="E841" s="20">
-        <v>0.47916666666666669</v>
-      </c>
-      <c r="I841">
-        <v>0</v>
-      </c>
-      <c r="J841">
-        <v>0</v>
+        <v>46138</v>
       </c>
       <c r="L841">
-        <v>611</v>
+        <v>167</v>
       </c>
       <c r="N841">
-        <v>0</v>
+        <v>278</v>
       </c>
       <c r="O841">
-        <v>56</v>
+        <v>833</v>
       </c>
       <c r="P841">
-        <v>667</v>
+        <v>1278</v>
       </c>
       <c r="Q841" t="s">
-        <v>352</v>
+        <v>129</v>
       </c>
     </row>
     <row r="842" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A842" t="s">
-        <v>429</v>
+        <v>89</v>
       </c>
       <c r="B842">
-        <v>-35.410254000000002</v>
+        <v>-35.6048446</v>
       </c>
       <c r="C842">
-        <v>138.32751999999999</v>
+        <v>138.59278499999999</v>
       </c>
       <c r="D842" s="2">
-        <v>46139</v>
-      </c>
-      <c r="E842" s="20">
-        <v>0.30208333333333331</v>
-      </c>
-      <c r="H842">
-        <v>0</v>
-      </c>
-      <c r="I842">
-        <v>0</v>
-      </c>
-      <c r="J842">
-        <v>0</v>
-      </c>
-      <c r="K842">
-        <v>0</v>
+        <v>46138</v>
+      </c>
+      <c r="G842">
+        <v>111</v>
       </c>
       <c r="L842">
         <v>56</v>
       </c>
-      <c r="M842">
-        <v>0</v>
-      </c>
       <c r="N842">
-        <v>0</v>
+        <v>722</v>
+      </c>
+      <c r="O842">
+        <v>944</v>
       </c>
       <c r="P842">
-        <v>56</v>
+        <v>1833</v>
       </c>
       <c r="Q842" t="s">
-        <v>352</v>
+        <v>129</v>
       </c>
     </row>
     <row r="843" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A843" t="s">
-        <v>290</v>
+        <v>314</v>
       </c>
       <c r="B843">
-        <v>-34.629179999999998</v>
+        <v>-35.445188000000002</v>
       </c>
       <c r="C843">
-        <v>135.86635000000001</v>
+        <v>138.307266</v>
       </c>
       <c r="D843" s="2">
-        <v>46141</v>
+        <v>46139</v>
+      </c>
+      <c r="E843" s="20">
+        <v>0.47916666666666669</v>
       </c>
       <c r="I843">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="J843">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L843">
-        <v>65</v>
+        <v>611</v>
       </c>
       <c r="N843">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="O843">
-        <v>259</v>
+        <v>56</v>
       </c>
       <c r="P843">
-        <v>426</v>
+        <v>667</v>
       </c>
       <c r="Q843" t="s">
-        <v>285</v>
+        <v>352</v>
       </c>
     </row>
     <row r="844" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A844" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B844">
-        <v>-34.891616999999997</v>
+        <v>-35.410254000000002</v>
       </c>
       <c r="C844">
-        <v>137.83265</v>
+        <v>138.32751999999999</v>
       </c>
       <c r="D844" s="2">
-        <v>46142</v>
+        <v>46139</v>
       </c>
       <c r="E844" s="20">
-        <v>0.40625</v>
+        <v>0.30208333333333331</v>
+      </c>
+      <c r="H844">
+        <v>0</v>
       </c>
       <c r="I844">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="J844">
         <v>0</v>
       </c>
+      <c r="K844">
+        <v>0</v>
+      </c>
       <c r="L844">
         <v>56</v>
       </c>
+      <c r="M844">
+        <v>0</v>
+      </c>
       <c r="N844">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="P844">
-        <v>168</v>
+        <v>56</v>
       </c>
       <c r="Q844" t="s">
-        <v>367</v>
+        <v>352</v>
       </c>
     </row>
     <row r="845" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A845" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B845">
-        <v>-34.628860000000003</v>
+        <v>-34.629179999999998</v>
       </c>
       <c r="C845">
-        <v>135.86708999999999</v>
+        <v>135.86635000000001</v>
       </c>
       <c r="D845" s="2">
-        <v>46143</v>
+        <v>46141</v>
       </c>
       <c r="I845">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="J845">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="L845">
-        <v>74</v>
-      </c>
-      <c r="M845">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="N845">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="O845">
-        <v>185</v>
+        <v>259</v>
       </c>
       <c r="P845">
-        <v>287</v>
+        <v>426</v>
       </c>
       <c r="Q845" t="s">
         <v>285</v>
@@ -32458,34 +32452,37 @@
     </row>
     <row r="846" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A846" t="s">
-        <v>403</v>
+        <v>430</v>
       </c>
       <c r="B846">
-        <v>-35.510497000000001</v>
+        <v>-34.891616999999997</v>
       </c>
       <c r="C846">
-        <v>138.21676299999999</v>
+        <v>137.83265</v>
       </c>
       <c r="D846" s="2">
-        <v>46146</v>
+        <v>46142</v>
       </c>
       <c r="E846" s="20">
-        <v>0.3923611111111111</v>
+        <v>0.40625</v>
       </c>
       <c r="I846">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="J846">
         <v>0</v>
       </c>
       <c r="L846">
-        <v>111</v>
+        <v>56</v>
+      </c>
+      <c r="N846">
+        <v>56</v>
       </c>
       <c r="P846">
-        <v>111</v>
+        <v>168</v>
       </c>
       <c r="Q846" t="s">
-        <v>252</v>
+        <v>367</v>
       </c>
     </row>
     <row r="847" spans="1:17" x14ac:dyDescent="0.3">
@@ -32499,19 +32496,16 @@
         <v>135.86708999999999</v>
       </c>
       <c r="D847" s="2">
-        <v>46146</v>
-      </c>
-      <c r="E847" s="20">
-        <v>0.375</v>
+        <v>46143</v>
       </c>
       <c r="I847">
-        <v>148</v>
+        <v>28</v>
       </c>
       <c r="J847">
-        <v>83</v>
+        <v>19</v>
       </c>
       <c r="L847">
-        <v>250</v>
+        <v>74</v>
       </c>
       <c r="M847">
         <v>0</v>
@@ -32520,10 +32514,10 @@
         <v>0</v>
       </c>
       <c r="O847">
-        <v>65</v>
+        <v>185</v>
       </c>
       <c r="P847">
-        <v>463</v>
+        <v>287</v>
       </c>
       <c r="Q847" t="s">
         <v>285</v>
@@ -32531,45 +32525,806 @@
     </row>
     <row r="848" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A848" t="s">
+        <v>152</v>
+      </c>
+      <c r="B848">
+        <v>-35.824725999999998</v>
+      </c>
+      <c r="C848">
+        <v>137.75102200000001</v>
+      </c>
+      <c r="D848" s="2">
+        <v>46145</v>
+      </c>
+      <c r="G848">
+        <v>56</v>
+      </c>
+      <c r="I848">
+        <v>56</v>
+      </c>
+      <c r="L848">
+        <v>278</v>
+      </c>
+      <c r="N848">
+        <v>333</v>
+      </c>
+      <c r="O848">
+        <v>2722</v>
+      </c>
+      <c r="P848">
+        <v>3445</v>
+      </c>
+      <c r="Q848" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="849" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A849" t="s">
+        <v>403</v>
+      </c>
+      <c r="B849">
+        <v>-35.510497000000001</v>
+      </c>
+      <c r="C849">
+        <v>138.21676299999999</v>
+      </c>
+      <c r="D849" s="2">
+        <v>46146</v>
+      </c>
+      <c r="E849" s="20">
+        <v>0.3923611111111111</v>
+      </c>
+      <c r="I849">
+        <v>0</v>
+      </c>
+      <c r="J849">
+        <v>0</v>
+      </c>
+      <c r="L849">
+        <v>111</v>
+      </c>
+      <c r="P849">
+        <v>111</v>
+      </c>
+      <c r="Q849" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="850" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A850" t="s">
+        <v>291</v>
+      </c>
+      <c r="B850">
+        <v>-34.628860000000003</v>
+      </c>
+      <c r="C850">
+        <v>135.86708999999999</v>
+      </c>
+      <c r="D850" s="2">
+        <v>46146</v>
+      </c>
+      <c r="E850" s="20">
+        <v>0.375</v>
+      </c>
+      <c r="I850">
+        <v>15</v>
+      </c>
+      <c r="J850">
+        <v>8</v>
+      </c>
+      <c r="L850">
+        <v>25</v>
+      </c>
+      <c r="M850">
+        <v>0</v>
+      </c>
+      <c r="N850">
+        <v>0</v>
+      </c>
+      <c r="O850">
+        <v>6</v>
+      </c>
+      <c r="P850">
+        <v>46</v>
+      </c>
+      <c r="Q850" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="851" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A851" t="s">
         <v>314</v>
       </c>
-      <c r="B848">
+      <c r="B851">
         <v>-35.445188000000002</v>
       </c>
-      <c r="C848">
+      <c r="C851">
         <v>138.307266</v>
       </c>
-      <c r="D848" s="2">
+      <c r="D851" s="2">
         <v>46147</v>
       </c>
-      <c r="E848" s="20">
+      <c r="E851" s="20">
         <v>0.375</v>
       </c>
-      <c r="I848">
+      <c r="I851">
         <v>333</v>
       </c>
-      <c r="J848">
-        <v>0</v>
-      </c>
-      <c r="L848">
+      <c r="J851">
+        <v>0</v>
+      </c>
+      <c r="L851">
         <v>444</v>
       </c>
-      <c r="N848">
+      <c r="N851">
         <v>167</v>
       </c>
-      <c r="O848">
-        <v>56</v>
-      </c>
-      <c r="P848">
+      <c r="O851">
+        <v>56</v>
+      </c>
+      <c r="P851">
         <v>1000</v>
       </c>
-      <c r="Q848" t="s">
+      <c r="Q851" t="s">
         <v>352</v>
       </c>
     </row>
+    <row r="852" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A852" t="s">
+        <v>94</v>
+      </c>
+      <c r="B852">
+        <v>-35.58858</v>
+      </c>
+      <c r="C852">
+        <v>138.60474600000001</v>
+      </c>
+      <c r="D852" s="2">
+        <v>46147</v>
+      </c>
+      <c r="I852">
+        <v>56</v>
+      </c>
+      <c r="J852">
+        <v>56</v>
+      </c>
+      <c r="L852">
+        <v>333</v>
+      </c>
+      <c r="N852">
+        <v>222</v>
+      </c>
+      <c r="O852">
+        <v>556</v>
+      </c>
+      <c r="P852">
+        <v>1167</v>
+      </c>
+      <c r="Q852" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="853" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A853" t="s">
+        <v>89</v>
+      </c>
+      <c r="B853">
+        <v>-35.6048446</v>
+      </c>
+      <c r="C853">
+        <v>138.59278499999999</v>
+      </c>
+      <c r="D853" s="2">
+        <v>46147</v>
+      </c>
+      <c r="I853">
+        <v>56</v>
+      </c>
+      <c r="L853">
+        <v>389</v>
+      </c>
+      <c r="N853">
+        <v>389</v>
+      </c>
+      <c r="O853">
+        <v>944</v>
+      </c>
+      <c r="P853">
+        <v>1778</v>
+      </c>
+      <c r="Q853" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="854" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A854" t="s">
+        <v>424</v>
+      </c>
+      <c r="B854">
+        <v>-35.500024000000003</v>
+      </c>
+      <c r="C854">
+        <v>138.24287699999999</v>
+      </c>
+      <c r="D854" s="2">
+        <v>46147</v>
+      </c>
+      <c r="E854" s="20">
+        <v>0.48958333333333331</v>
+      </c>
+      <c r="F854">
+        <v>0</v>
+      </c>
+      <c r="H854">
+        <v>500</v>
+      </c>
+      <c r="I854">
+        <v>111</v>
+      </c>
+      <c r="J854">
+        <v>0</v>
+      </c>
+      <c r="K854">
+        <v>0</v>
+      </c>
+      <c r="L854">
+        <v>278</v>
+      </c>
+      <c r="M854">
+        <v>0</v>
+      </c>
+      <c r="N854">
+        <v>2167</v>
+      </c>
+      <c r="O854">
+        <v>167</v>
+      </c>
+      <c r="P854">
+        <v>3223</v>
+      </c>
+      <c r="Q854" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="855" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A855" t="s">
+        <v>59</v>
+      </c>
+      <c r="B855">
+        <v>-35.084850000000003</v>
+      </c>
+      <c r="C855">
+        <v>137.74889999999999</v>
+      </c>
+      <c r="D855" s="2">
+        <v>46148</v>
+      </c>
+      <c r="E855" s="20">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="G855">
+        <v>277</v>
+      </c>
+      <c r="H855">
+        <v>56</v>
+      </c>
+      <c r="I855">
+        <v>56</v>
+      </c>
+      <c r="L855">
+        <v>0</v>
+      </c>
+      <c r="M855">
+        <v>0</v>
+      </c>
+      <c r="N855">
+        <v>444</v>
+      </c>
+      <c r="P855">
+        <v>833</v>
+      </c>
+      <c r="Q855" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="856" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A856" t="s">
+        <v>429</v>
+      </c>
+      <c r="B856">
+        <v>-35.410254000000002</v>
+      </c>
+      <c r="C856">
+        <v>138.32751999999999</v>
+      </c>
+      <c r="D856" s="2">
+        <v>46148</v>
+      </c>
+      <c r="E856" s="20">
+        <v>0.36458333333333331</v>
+      </c>
+      <c r="F856">
+        <v>0</v>
+      </c>
+      <c r="G856">
+        <v>0</v>
+      </c>
+      <c r="H856">
+        <v>722</v>
+      </c>
+      <c r="I856">
+        <v>333</v>
+      </c>
+      <c r="J856">
+        <v>0</v>
+      </c>
+      <c r="K856">
+        <v>0</v>
+      </c>
+      <c r="L856">
+        <v>667</v>
+      </c>
+      <c r="M856">
+        <v>0</v>
+      </c>
+      <c r="N856">
+        <v>3389</v>
+      </c>
+      <c r="O856">
+        <v>167</v>
+      </c>
+      <c r="P856">
+        <v>5278</v>
+      </c>
+      <c r="Q856" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="857" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A857" t="s">
+        <v>431</v>
+      </c>
+      <c r="B857">
+        <v>-34.54036</v>
+      </c>
+      <c r="C857">
+        <v>135.93406999999999</v>
+      </c>
+      <c r="D857" s="2">
+        <v>46149</v>
+      </c>
+      <c r="E857" s="20">
+        <v>0.53125</v>
+      </c>
+      <c r="I857">
+        <v>17</v>
+      </c>
+      <c r="J857">
+        <v>6</v>
+      </c>
+      <c r="L857">
+        <v>9</v>
+      </c>
+      <c r="M857">
+        <v>0</v>
+      </c>
+      <c r="N857">
+        <v>0</v>
+      </c>
+      <c r="O857">
+        <v>3</v>
+      </c>
+      <c r="P857">
+        <v>29</v>
+      </c>
+      <c r="Q857" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="858" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A858" t="s">
+        <v>94</v>
+      </c>
+      <c r="B858">
+        <v>-35.58858</v>
+      </c>
+      <c r="C858">
+        <v>138.60474600000001</v>
+      </c>
+      <c r="D858" s="2">
+        <v>46152</v>
+      </c>
+      <c r="G858">
+        <v>278</v>
+      </c>
+      <c r="H858">
+        <v>167</v>
+      </c>
+      <c r="I858">
+        <v>333</v>
+      </c>
+      <c r="L858">
+        <v>56</v>
+      </c>
+      <c r="N858">
+        <v>389</v>
+      </c>
+      <c r="O858">
+        <v>944</v>
+      </c>
+      <c r="P858">
+        <v>2167</v>
+      </c>
+      <c r="Q858" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="859" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A859" t="s">
+        <v>89</v>
+      </c>
+      <c r="B859">
+        <v>-35.6048446</v>
+      </c>
+      <c r="C859">
+        <v>138.59278499999999</v>
+      </c>
+      <c r="D859" s="2">
+        <v>46152</v>
+      </c>
+      <c r="G859">
+        <v>111</v>
+      </c>
+      <c r="I859">
+        <v>56</v>
+      </c>
+      <c r="L859">
+        <v>167</v>
+      </c>
+      <c r="N859">
+        <v>667</v>
+      </c>
+      <c r="O859">
+        <v>944</v>
+      </c>
+      <c r="P859">
+        <v>1945</v>
+      </c>
+      <c r="Q859" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="860" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A860" t="s">
+        <v>291</v>
+      </c>
+      <c r="B860">
+        <v>-34.628860000000003</v>
+      </c>
+      <c r="C860">
+        <v>135.86708999999999</v>
+      </c>
+      <c r="D860" s="2">
+        <v>46152</v>
+      </c>
+      <c r="E860" s="20">
+        <v>0.4375</v>
+      </c>
+      <c r="I860">
+        <v>19</v>
+      </c>
+      <c r="J860">
+        <v>12</v>
+      </c>
+      <c r="L860">
+        <v>63</v>
+      </c>
+      <c r="M860">
+        <v>0</v>
+      </c>
+      <c r="N860">
+        <v>0</v>
+      </c>
+      <c r="O860">
+        <v>1</v>
+      </c>
+      <c r="P860">
+        <v>83</v>
+      </c>
+      <c r="Q860" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="861" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A861" t="s">
+        <v>432</v>
+      </c>
+      <c r="B861">
+        <v>-35.472737000000002</v>
+      </c>
+      <c r="C861">
+        <v>138.28932900000001</v>
+      </c>
+      <c r="D861" s="2">
+        <v>46152</v>
+      </c>
+      <c r="E861" s="20">
+        <v>0.36458333333333331</v>
+      </c>
+      <c r="F861">
+        <v>0</v>
+      </c>
+      <c r="G861">
+        <v>0</v>
+      </c>
+      <c r="H861">
+        <v>167</v>
+      </c>
+      <c r="I861">
+        <v>0</v>
+      </c>
+      <c r="J861">
+        <v>0</v>
+      </c>
+      <c r="K861">
+        <v>0</v>
+      </c>
+      <c r="L861">
+        <v>333</v>
+      </c>
+      <c r="M861">
+        <v>0</v>
+      </c>
+      <c r="N861">
+        <v>611</v>
+      </c>
+      <c r="O861">
+        <v>167</v>
+      </c>
+      <c r="P861">
+        <v>1278</v>
+      </c>
+      <c r="Q861" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="862" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A862" t="s">
+        <v>291</v>
+      </c>
+      <c r="B862">
+        <v>-34.628860000000003</v>
+      </c>
+      <c r="C862">
+        <v>135.86708999999999</v>
+      </c>
+      <c r="D862" s="2">
+        <v>46153</v>
+      </c>
+      <c r="E862" s="20">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="I862">
+        <v>17</v>
+      </c>
+      <c r="J862">
+        <v>13</v>
+      </c>
+      <c r="L862">
+        <v>56</v>
+      </c>
+      <c r="M862">
+        <v>0</v>
+      </c>
+      <c r="N862">
+        <v>0</v>
+      </c>
+      <c r="O862">
+        <v>6</v>
+      </c>
+      <c r="P862">
+        <v>79</v>
+      </c>
+      <c r="Q862" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="863" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A863" t="s">
+        <v>314</v>
+      </c>
+      <c r="B863">
+        <v>-35.445188000000002</v>
+      </c>
+      <c r="C863">
+        <v>138.307266</v>
+      </c>
+      <c r="D863" s="2">
+        <v>46153</v>
+      </c>
+      <c r="E863" s="20">
+        <v>0.375</v>
+      </c>
+      <c r="F863">
+        <v>0</v>
+      </c>
+      <c r="G863">
+        <v>0</v>
+      </c>
+      <c r="H863">
+        <v>56</v>
+      </c>
+      <c r="I863">
+        <v>0</v>
+      </c>
+      <c r="J863">
+        <v>0</v>
+      </c>
+      <c r="K863">
+        <v>0</v>
+      </c>
+      <c r="L863">
+        <v>111</v>
+      </c>
+      <c r="M863">
+        <v>0</v>
+      </c>
+      <c r="N863">
+        <v>111</v>
+      </c>
+      <c r="O863">
+        <v>0</v>
+      </c>
+      <c r="P863">
+        <v>278</v>
+      </c>
+      <c r="Q863" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="864" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A864" t="s">
+        <v>86</v>
+      </c>
+      <c r="B864">
+        <v>-35.540277000000003</v>
+      </c>
+      <c r="C864">
+        <v>138.66416599999999</v>
+      </c>
+      <c r="D864" s="2">
+        <v>46154</v>
+      </c>
+      <c r="E864" s="20">
+        <v>0.35972222222222222</v>
+      </c>
+      <c r="G864">
+        <v>56</v>
+      </c>
+      <c r="N864">
+        <v>444</v>
+      </c>
+      <c r="O864">
+        <v>278</v>
+      </c>
+      <c r="P864">
+        <v>778</v>
+      </c>
+      <c r="Q864" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="865" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A865" t="s">
+        <v>100</v>
+      </c>
+      <c r="B865">
+        <v>-35.536745000000003</v>
+      </c>
+      <c r="C865">
+        <v>138.6913744</v>
+      </c>
+      <c r="D865" s="2">
+        <v>46154</v>
+      </c>
+      <c r="E865" s="20">
+        <v>0.36666666666666664</v>
+      </c>
+      <c r="I865">
+        <v>167</v>
+      </c>
+      <c r="L865">
+        <v>7000</v>
+      </c>
+      <c r="M865">
+        <v>167</v>
+      </c>
+      <c r="N865">
+        <v>222</v>
+      </c>
+      <c r="O865">
+        <v>1667</v>
+      </c>
+      <c r="P865">
+        <v>9223</v>
+      </c>
+      <c r="Q865" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="866" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A866" t="s">
+        <v>59</v>
+      </c>
+      <c r="B866">
+        <v>-35.084850000000003</v>
+      </c>
+      <c r="C866">
+        <v>137.74889999999999</v>
+      </c>
+      <c r="D866" s="2">
+        <v>46155</v>
+      </c>
+      <c r="E866" s="20">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="G866">
+        <v>277</v>
+      </c>
+      <c r="L866">
+        <v>0</v>
+      </c>
+      <c r="M866">
+        <v>0</v>
+      </c>
+      <c r="N866">
+        <v>333</v>
+      </c>
+      <c r="P866">
+        <v>610</v>
+      </c>
+      <c r="Q866" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="867" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A867" t="s">
+        <v>291</v>
+      </c>
+      <c r="B867">
+        <v>-34.628860000000003</v>
+      </c>
+      <c r="C867">
+        <v>135.86708999999999</v>
+      </c>
+      <c r="D867" s="2">
+        <v>46155</v>
+      </c>
+      <c r="E867" s="20">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="I867">
+        <v>17</v>
+      </c>
+      <c r="J867">
+        <v>0</v>
+      </c>
+      <c r="L867">
+        <v>33</v>
+      </c>
+      <c r="O867">
+        <v>0</v>
+      </c>
+      <c r="P867">
+        <v>50</v>
+      </c>
+      <c r="Q867" t="s">
+        <v>285</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q848">
-    <sortCondition ref="D2:D848"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q867">
+    <sortCondition ref="D2:D867"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/MASTER spreadsheet of community summaries.xlsx
+++ b/MASTER spreadsheet of community summaries.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\peri\Dropbox\Delta\Projects\Laboratory\Algal blooms, bacterial counts  for community\For Luke's HAB data display\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C637A2F-755B-4B12-B6F9-BBF48375C3B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24D5B567-794A-4681-93F4-DA73FFBA6FFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{9286397E-2757-492B-865A-39B2D6A15FF6}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1751" uniqueCount="433">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1751" uniqueCount="431">
   <si>
     <t>Date</t>
   </si>
@@ -598,9 +598,6 @@
     <t>Hallet Cove</t>
   </si>
   <si>
-    <t>HANC5233</t>
-  </si>
-  <si>
     <t>Kent Reserve Beach Victor Harbor</t>
   </si>
   <si>
@@ -869,9 +866,6 @@
   </si>
   <si>
     <t>Port Minlacowie Boatramp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JOHT5583 </t>
   </si>
   <si>
     <t>Pt Vincent Marina, 500mm deep</t>
@@ -1489,7 +1483,18 @@
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
@@ -1861,7 +1866,7 @@
         <v>0</v>
       </c>
       <c r="E1" s="19" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>64</v>
@@ -7109,7 +7114,7 @@
     </row>
     <row r="150" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B150">
         <v>-34.837600000000002</v>
@@ -7395,7 +7400,7 @@
     </row>
     <row r="158" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B158">
         <v>-34.837600000000002</v>
@@ -7634,7 +7639,7 @@
     </row>
     <row r="165" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B165">
         <v>-34.837600000000002</v>
@@ -8598,7 +8603,7 @@
     </row>
     <row r="191" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B191">
         <v>-34.837600000000002</v>
@@ -9694,7 +9699,7 @@
     </row>
     <row r="224" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B224">
         <v>-34.837600000000002</v>
@@ -9983,7 +9988,7 @@
     </row>
     <row r="232" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B232">
         <v>-34.837600000000002</v>
@@ -11389,7 +11394,7 @@
     </row>
     <row r="271" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B271">
         <v>-35.563558</v>
@@ -11430,7 +11435,7 @@
     </row>
     <row r="272" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B272">
         <v>-35.135489999999997</v>
@@ -11509,7 +11514,7 @@
     </row>
     <row r="274" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B274">
         <v>-34.837600000000002</v>
@@ -11609,7 +11614,7 @@
         <v>172</v>
       </c>
       <c r="Q276" t="s">
-        <v>180</v>
+        <v>78</v>
       </c>
     </row>
     <row r="277" spans="1:17" x14ac:dyDescent="0.3">
@@ -11664,7 +11669,7 @@
         <v>278</v>
       </c>
       <c r="Q278" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="279" spans="1:17" x14ac:dyDescent="0.3">
@@ -11704,7 +11709,7 @@
     </row>
     <row r="280" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B280">
         <v>-35.538469999999997</v>
@@ -11719,7 +11724,7 @@
         <v>0</v>
       </c>
       <c r="Q280" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="281" spans="1:17" x14ac:dyDescent="0.3">
@@ -11739,12 +11744,12 @@
         <v>56</v>
       </c>
       <c r="Q281" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="282" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B282">
         <v>-35.592570000000002</v>
@@ -11794,7 +11799,7 @@
     </row>
     <row r="283" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B283">
         <v>-35.592669999999998</v>
@@ -11844,7 +11849,7 @@
     </row>
     <row r="284" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B284">
         <v>-35.592770000000002</v>
@@ -11929,7 +11934,7 @@
     </row>
     <row r="286" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B286">
         <v>-34.837600000000002</v>
@@ -12209,12 +12214,12 @@
         <v>722</v>
       </c>
       <c r="Q294" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="295" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B295">
         <v>-35.515810999999999</v>
@@ -12229,12 +12234,12 @@
         <v>0</v>
       </c>
       <c r="Q295" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="296" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A296" s="10" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B296" s="10">
         <v>-35.5691281</v>
@@ -12284,7 +12289,7 @@
     </row>
     <row r="297" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A297" s="10" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B297" s="10">
         <v>-35.5691281</v>
@@ -12381,7 +12386,7 @@
     </row>
     <row r="299" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B299">
         <v>-35.515507999999997</v>
@@ -12396,12 +12401,12 @@
         <v>667</v>
       </c>
       <c r="Q299" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="300" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B300">
         <v>-35.515810999999999</v>
@@ -12416,7 +12421,7 @@
         <v>56</v>
       </c>
       <c r="Q300" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="301" spans="1:17" x14ac:dyDescent="0.3">
@@ -12436,12 +12441,12 @@
         <v>444</v>
       </c>
       <c r="Q301" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="302" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B302">
         <v>-35.538469999999997</v>
@@ -12456,12 +12461,12 @@
         <v>167</v>
       </c>
       <c r="Q302" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="303" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B303">
         <v>-35.592393000000001</v>
@@ -12476,7 +12481,7 @@
         <v>111</v>
       </c>
       <c r="Q303" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="304" spans="1:17" x14ac:dyDescent="0.3">
@@ -12496,12 +12501,12 @@
         <v>667</v>
       </c>
       <c r="Q304" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="305" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B305">
         <v>-35.638637000000003</v>
@@ -12516,7 +12521,7 @@
         <v>1333</v>
       </c>
       <c r="Q305" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="306" spans="1:17" x14ac:dyDescent="0.3">
@@ -12565,7 +12570,7 @@
     </row>
     <row r="307" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B307">
         <v>-34.933939000000002</v>
@@ -12600,7 +12605,7 @@
     </row>
     <row r="308" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B308">
         <v>-34.191187999999997</v>
@@ -12635,7 +12640,7 @@
     </row>
     <row r="309" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B309">
         <v>-34.606234999999998</v>
@@ -12708,7 +12713,7 @@
     </row>
     <row r="311" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A311" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B311" s="10">
         <v>-35.793615000000003</v>
@@ -12756,7 +12761,7 @@
     </row>
     <row r="312" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A312" s="9" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B312" s="9">
         <v>-35.787857600000002</v>
@@ -12806,7 +12811,7 @@
     </row>
     <row r="313" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A313" s="10" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B313" s="10">
         <v>-35.593628899999999</v>
@@ -12856,7 +12861,7 @@
     </row>
     <row r="314" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A314" s="9" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B314" s="10">
         <v>-35.5909288</v>
@@ -12906,7 +12911,7 @@
     </row>
     <row r="315" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B315">
         <v>-35.610827999999998</v>
@@ -12935,7 +12940,7 @@
     </row>
     <row r="316" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B316">
         <v>-35.588391000000001</v>
@@ -12970,7 +12975,7 @@
     </row>
     <row r="317" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A317" s="10" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B317" s="10">
         <v>-35.802792599999997</v>
@@ -13020,7 +13025,7 @@
     </row>
     <row r="318" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A318" s="9" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B318" s="9">
         <v>-35.787857600000002</v>
@@ -13070,7 +13075,7 @@
     </row>
     <row r="319" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A319" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B319" s="10">
         <v>-35.781898699999999</v>
@@ -13164,7 +13169,7 @@
     </row>
     <row r="321" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B321">
         <v>-35.802792599999997</v>
@@ -13214,7 +13219,7 @@
     </row>
     <row r="322" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B322">
         <v>-35.8026926</v>
@@ -13264,7 +13269,7 @@
     </row>
     <row r="323" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B323">
         <v>-35.671777499999997</v>
@@ -13349,7 +13354,7 @@
     </row>
     <row r="325" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B325">
         <v>-34.940480000000001</v>
@@ -13419,7 +13424,7 @@
     </row>
     <row r="327" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B327">
         <v>-35.793615000000003</v>
@@ -13539,7 +13544,7 @@
     </row>
     <row r="330" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B330">
         <v>-35.581816000000003</v>
@@ -13609,7 +13614,7 @@
     </row>
     <row r="332" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B332">
         <v>-35.7391796</v>
@@ -13659,7 +13664,7 @@
     </row>
     <row r="333" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B333">
         <v>-35.789543199999997</v>
@@ -13709,7 +13714,7 @@
     </row>
     <row r="334" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B334">
         <v>-35.799307599999999</v>
@@ -13756,7 +13761,7 @@
     </row>
     <row r="335" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B335">
         <v>-35.515507999999997</v>
@@ -13771,12 +13776,12 @@
         <v>0</v>
       </c>
       <c r="Q335" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="336" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B336">
         <v>-35.538469999999997</v>
@@ -13791,7 +13796,7 @@
         <v>0</v>
       </c>
       <c r="Q336" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="337" spans="1:17" x14ac:dyDescent="0.3">
@@ -13811,7 +13816,7 @@
         <v>0</v>
       </c>
       <c r="Q337" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="338" spans="1:17" x14ac:dyDescent="0.3">
@@ -13831,12 +13836,12 @@
         <v>0</v>
       </c>
       <c r="Q338" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="339" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B339">
         <v>-35.632100000000001</v>
@@ -13851,12 +13856,12 @@
         <v>0</v>
       </c>
       <c r="Q339" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="340" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B340">
         <v>-35.549100000000003</v>
@@ -13871,12 +13876,12 @@
         <v>0</v>
       </c>
       <c r="Q340" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="341" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B341">
         <v>-35.515507999999997</v>
@@ -13891,7 +13896,7 @@
         <v>0</v>
       </c>
       <c r="Q341" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="342" spans="1:17" x14ac:dyDescent="0.3">
@@ -13911,12 +13916,12 @@
         <v>0</v>
       </c>
       <c r="Q342" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="343" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B343">
         <v>-35.538469999999997</v>
@@ -13931,12 +13936,12 @@
         <v>0</v>
       </c>
       <c r="Q343" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="344" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B344">
         <v>-35.549100000000003</v>
@@ -13951,12 +13956,12 @@
         <v>0</v>
       </c>
       <c r="Q344" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="345" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B345">
         <v>-35.592393000000001</v>
@@ -13971,7 +13976,7 @@
         <v>0</v>
       </c>
       <c r="Q345" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="346" spans="1:17" x14ac:dyDescent="0.3">
@@ -13991,7 +13996,7 @@
         <v>0</v>
       </c>
       <c r="Q346" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="347" spans="1:17" x14ac:dyDescent="0.3">
@@ -14125,7 +14130,7 @@
     </row>
     <row r="350" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B350">
         <v>-35.054707999999998</v>
@@ -14155,12 +14160,12 @@
         <v>47889</v>
       </c>
       <c r="Q350" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="351" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B351">
         <v>-35.719856700000001</v>
@@ -14210,7 +14215,7 @@
     </row>
     <row r="352" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B352">
         <v>-35.120863999999997</v>
@@ -14348,7 +14353,7 @@
     </row>
     <row r="355" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B355">
         <v>-35.738910099999998</v>
@@ -14398,7 +14403,7 @@
     </row>
     <row r="356" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B356">
         <v>-35.509267000000001</v>
@@ -14427,7 +14432,7 @@
     </row>
     <row r="357" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B357">
         <v>-35.509166999999998</v>
@@ -14462,7 +14467,7 @@
     </row>
     <row r="358" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B358">
         <v>-35.638145999999999</v>
@@ -14512,7 +14517,7 @@
     </row>
     <row r="359" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A359" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B359">
         <v>-35.671809099999997</v>
@@ -14673,7 +14678,7 @@
     </row>
     <row r="363" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B363">
         <v>-34.180396000000002</v>
@@ -14714,7 +14719,7 @@
     </row>
     <row r="364" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A364" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B364">
         <v>-34.176642000000001</v>
@@ -14746,7 +14751,7 @@
     </row>
     <row r="365" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A365" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B365">
         <v>-34.322853000000002</v>
@@ -14784,7 +14789,7 @@
     </row>
     <row r="366" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A366" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B366">
         <v>-34.377982000000003</v>
@@ -14822,7 +14827,7 @@
     </row>
     <row r="367" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A367" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B367">
         <v>-35.515507999999997</v>
@@ -14840,12 +14845,12 @@
         <v>222</v>
       </c>
       <c r="Q367" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="368" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A368" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B368">
         <v>-35.538469999999997</v>
@@ -14863,7 +14868,7 @@
         <v>0</v>
       </c>
       <c r="Q368" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="369" spans="1:17" x14ac:dyDescent="0.3">
@@ -14886,7 +14891,7 @@
         <v>111</v>
       </c>
       <c r="Q369" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="370" spans="1:17" x14ac:dyDescent="0.3">
@@ -14909,12 +14914,12 @@
         <v>222</v>
       </c>
       <c r="Q370" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="371" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A371" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B371">
         <v>-35.638637000000003</v>
@@ -14932,12 +14937,12 @@
         <v>111</v>
       </c>
       <c r="Q371" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="372" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A372" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B372">
         <v>-35.558100000000003</v>
@@ -14955,7 +14960,7 @@
         <v>167</v>
       </c>
       <c r="Q372" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="373" spans="1:17" x14ac:dyDescent="0.3">
@@ -15004,7 +15009,7 @@
     </row>
     <row r="374" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A374" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B374">
         <v>-35.093015000000001</v>
@@ -15034,7 +15039,7 @@
         <v>2444</v>
       </c>
       <c r="Q374" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="375" spans="1:17" x14ac:dyDescent="0.3">
@@ -15156,7 +15161,7 @@
     </row>
     <row r="378" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A378" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B378">
         <v>-35.6048446</v>
@@ -15191,7 +15196,7 @@
     </row>
     <row r="379" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A379" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B379">
         <v>-35.608333000000002</v>
@@ -15258,7 +15263,7 @@
     </row>
     <row r="381" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A381" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B381">
         <v>-35.63158</v>
@@ -15293,7 +15298,7 @@
     </row>
     <row r="382" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A382" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B382">
         <v>-35.61</v>
@@ -15372,7 +15377,7 @@
     </row>
     <row r="384" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A384" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B384">
         <v>-34.940480000000001</v>
@@ -15454,7 +15459,7 @@
     </row>
     <row r="386" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A386" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B386">
         <v>-35.081918000000002</v>
@@ -15484,12 +15489,12 @@
         <v>2389</v>
       </c>
       <c r="Q386" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="387" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A387" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B387">
         <v>-35.054707999999998</v>
@@ -15516,12 +15521,12 @@
         <v>205403</v>
       </c>
       <c r="Q387" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="388" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A388" s="10" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B388" s="10">
         <v>-35.586970000000001</v>
@@ -15571,7 +15576,7 @@
     </row>
     <row r="389" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A389" s="10" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B389" s="10">
         <v>-35.586869999999998</v>
@@ -15621,7 +15626,7 @@
     </row>
     <row r="390" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A390" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B390">
         <v>-35.115375999999998</v>
@@ -15651,12 +15656,12 @@
         <v>4444</v>
       </c>
       <c r="Q390" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="391" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A391" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B391">
         <v>-35.465475320000003</v>
@@ -15706,7 +15711,7 @@
     </row>
     <row r="392" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A392" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B392">
         <v>-35.788755899999998</v>
@@ -15756,7 +15761,7 @@
     </row>
     <row r="393" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A393" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B393">
         <v>-35.784914800000003</v>
@@ -15806,7 +15811,7 @@
     </row>
     <row r="394" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A394" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B394">
         <v>-35.054707999999998</v>
@@ -15830,12 +15835,12 @@
         <v>396000</v>
       </c>
       <c r="Q394" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="395" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A395" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B395">
         <v>-35.082030000000003</v>
@@ -15935,7 +15940,7 @@
     </row>
     <row r="397" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A397" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B397">
         <v>-35.788755899999998</v>
@@ -15985,7 +15990,7 @@
     </row>
     <row r="398" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A398" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B398">
         <v>-35.054707999999998</v>
@@ -16012,12 +16017,12 @@
         <v>150500</v>
       </c>
       <c r="Q398" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="399" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A399" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B399">
         <v>-35.081918000000002</v>
@@ -16047,7 +16052,7 @@
         <v>3778</v>
       </c>
       <c r="Q399" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="400" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.3">
@@ -16102,7 +16107,7 @@
     </row>
     <row r="401" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A401" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B401">
         <v>-34.824044999999998</v>
@@ -16152,7 +16157,7 @@
     </row>
     <row r="402" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A402" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B402">
         <v>-35.788755899999998</v>
@@ -16202,7 +16207,7 @@
     </row>
     <row r="403" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A403" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B403">
         <v>-35.671777499999997</v>
@@ -16252,7 +16257,7 @@
     </row>
     <row r="404" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A404" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B404">
         <v>-35.054707999999998</v>
@@ -16282,12 +16287,12 @@
         <v>88000</v>
       </c>
       <c r="Q404" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="405" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A405" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B405">
         <v>-35.793615000000003</v>
@@ -16337,7 +16342,7 @@
     </row>
     <row r="406" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A406" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B406">
         <v>-35.654400000000003</v>
@@ -16352,12 +16357,12 @@
         <v>0</v>
       </c>
       <c r="Q406" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="407" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A407" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B407">
         <v>-35.371586999999998</v>
@@ -16410,7 +16415,7 @@
     </row>
     <row r="408" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A408" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B408">
         <v>-35.017930999999997</v>
@@ -16463,7 +16468,7 @@
     </row>
     <row r="409" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A409" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B409">
         <v>-33.677014</v>
@@ -16490,12 +16495,12 @@
         <v>2556</v>
       </c>
       <c r="Q409" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="410" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A410" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B410">
         <v>-35.032207</v>
@@ -16548,7 +16553,7 @@
     </row>
     <row r="411" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A411" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B411">
         <v>-34.765895999999998</v>
@@ -16578,12 +16583,12 @@
         <v>3277</v>
       </c>
       <c r="Q411" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="412" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A412" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B412">
         <v>-34.765996000000001</v>
@@ -16613,7 +16618,7 @@
         <v>3222</v>
       </c>
       <c r="Q412" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="413" spans="1:17" x14ac:dyDescent="0.3">
@@ -16691,7 +16696,7 @@
     </row>
     <row r="415" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A415" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B415">
         <v>-35.515507999999997</v>
@@ -16706,12 +16711,12 @@
         <v>0</v>
       </c>
       <c r="Q415" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="416" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A416" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B416">
         <v>-35.538469999999997</v>
@@ -16726,7 +16731,7 @@
         <v>0</v>
       </c>
       <c r="Q416" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="417" spans="1:17" x14ac:dyDescent="0.3">
@@ -16746,12 +16751,12 @@
         <v>0</v>
       </c>
       <c r="Q417" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="418" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A418" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B418">
         <v>-35.592393000000001</v>
@@ -16766,7 +16771,7 @@
         <v>0</v>
       </c>
       <c r="Q418" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="419" spans="1:17" x14ac:dyDescent="0.3">
@@ -16786,12 +16791,12 @@
         <v>0</v>
       </c>
       <c r="Q419" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="420" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A420" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B420">
         <v>-35.558100000000003</v>
@@ -16806,12 +16811,12 @@
         <v>0</v>
       </c>
       <c r="Q420" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="421" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A421" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B421">
         <v>-35.793615000000003</v>
@@ -16861,7 +16866,7 @@
     </row>
     <row r="422" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A422" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B422">
         <v>-34.824044999999998</v>
@@ -16967,7 +16972,7 @@
     </row>
     <row r="424" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A424" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B424">
         <v>-35.193919999999999</v>
@@ -17020,7 +17025,7 @@
     </row>
     <row r="425" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A425" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B425">
         <v>-35.308790000000002</v>
@@ -17073,7 +17078,7 @@
     </row>
     <row r="426" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A426" s="10" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B426" s="9">
         <v>-35.787201000000003</v>
@@ -17123,7 +17128,7 @@
     </row>
     <row r="427" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A427" s="10" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B427" s="12">
         <v>-35.787233399999998</v>
@@ -17173,7 +17178,7 @@
     </row>
     <row r="428" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A428" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B428">
         <v>-35.093021</v>
@@ -17203,12 +17208,12 @@
         <v>2889</v>
       </c>
       <c r="Q428" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="429" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A429" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B429">
         <v>-35.115721999999998</v>
@@ -17238,12 +17243,12 @@
         <v>4722</v>
       </c>
       <c r="Q429" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="430" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A430" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B430">
         <v>-35.427987000000002</v>
@@ -17349,7 +17354,7 @@
     </row>
     <row r="432" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A432" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B432">
         <v>-34.860666999999999</v>
@@ -17455,7 +17460,7 @@
     </row>
     <row r="434" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A434" s="10" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B434" s="10">
         <v>-35.622483199999998</v>
@@ -17505,7 +17510,7 @@
     </row>
     <row r="435" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A435" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B435">
         <v>-35.081834999999998</v>
@@ -17535,12 +17540,12 @@
         <v>2389</v>
       </c>
       <c r="Q435" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="436" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A436" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B436">
         <v>-35.054707999999998</v>
@@ -17567,7 +17572,7 @@
         <v>110000</v>
       </c>
       <c r="Q436" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="437" spans="1:17" x14ac:dyDescent="0.3">
@@ -17648,7 +17653,7 @@
     </row>
     <row r="439" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A439" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B439">
         <v>-35.269129</v>
@@ -17678,7 +17683,7 @@
         <v>7778</v>
       </c>
       <c r="Q439" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="440" spans="1:17" x14ac:dyDescent="0.3">
@@ -17736,7 +17741,7 @@
     </row>
     <row r="441" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A441" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B441">
         <v>-34.838619999999999</v>
@@ -17789,7 +17794,7 @@
     </row>
     <row r="442" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A442" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B442">
         <v>-34.824044999999998</v>
@@ -17825,7 +17830,7 @@
         <v>5.4</v>
       </c>
       <c r="M442" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="N442">
         <v>0.1</v>
@@ -17895,7 +17900,7 @@
     </row>
     <row r="444" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A444" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B444">
         <v>-34.860666999999999</v>
@@ -17948,7 +17953,7 @@
     </row>
     <row r="445" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A445" s="10" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B445" s="9">
         <v>-35.787201000000003</v>
@@ -17998,7 +18003,7 @@
     </row>
     <row r="446" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A446" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B446">
         <v>-33.926485999999997</v>
@@ -18077,7 +18082,7 @@
     </row>
     <row r="448" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A448" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B448">
         <v>-35.738910099999998</v>
@@ -18127,7 +18132,7 @@
     </row>
     <row r="449" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A449" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B449">
         <v>-35.193919999999999</v>
@@ -18168,7 +18173,7 @@
     </row>
     <row r="450" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A450" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B450">
         <v>-35.054707999999998</v>
@@ -18195,12 +18200,12 @@
         <v>122667</v>
       </c>
       <c r="Q450" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="451" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A451" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B451">
         <v>-35.523274000000001</v>
@@ -18227,12 +18232,12 @@
         <v>19500</v>
       </c>
       <c r="Q451" s="10" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="452" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A452" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B452">
         <v>-35.793615000000003</v>
@@ -18320,7 +18325,7 @@
     </row>
     <row r="454" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A454" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B454">
         <v>-34.860666999999999</v>
@@ -18355,7 +18360,7 @@
     </row>
     <row r="455" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A455" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B455">
         <v>-34.908026999999997</v>
@@ -18399,7 +18404,7 @@
     </row>
     <row r="456" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A456" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B456">
         <v>-35.242910000000002</v>
@@ -18437,7 +18442,7 @@
     </row>
     <row r="457" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A457" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B457">
         <v>-35.668842900000001</v>
@@ -18487,7 +18492,7 @@
     </row>
     <row r="458" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A458" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B458">
         <v>-35.789543199999997</v>
@@ -18581,7 +18586,7 @@
     </row>
     <row r="460" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A460" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B460">
         <v>-35.085709299999998</v>
@@ -18626,12 +18631,12 @@
         <v>6333</v>
       </c>
       <c r="Q460" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="461" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A461" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B461">
         <v>-35.521411999999998</v>
@@ -18658,12 +18663,12 @@
         <v>1167</v>
       </c>
       <c r="Q461" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="462" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A462" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B462">
         <v>-32.486960000000003</v>
@@ -18687,12 +18692,12 @@
         <v>1666</v>
       </c>
       <c r="Q462" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="463" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A463" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B463">
         <v>-32.48724</v>
@@ -18716,12 +18721,12 @@
         <v>1049</v>
       </c>
       <c r="Q463" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="464" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A464" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B464">
         <v>-32.490589999999997</v>
@@ -18745,12 +18750,12 @@
         <v>1358</v>
       </c>
       <c r="Q464" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="465" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A465" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B465">
         <v>-35.579300000000003</v>
@@ -18788,7 +18793,7 @@
     </row>
     <row r="466" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A466" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B466">
         <v>-35.585419999999999</v>
@@ -18823,7 +18828,7 @@
     </row>
     <row r="467" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A467" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B467">
         <v>-35.570399999999999</v>
@@ -18858,7 +18863,7 @@
     </row>
     <row r="468" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A468" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B468">
         <v>-35.787201000000003</v>
@@ -18908,7 +18913,7 @@
     </row>
     <row r="469" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A469" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B469">
         <v>-35.787233000000001</v>
@@ -18955,7 +18960,7 @@
     </row>
     <row r="470" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A470" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B470">
         <v>-34.804662999999998</v>
@@ -18993,7 +18998,7 @@
     </row>
     <row r="471" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A471" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B471">
         <v>-34.824044999999998</v>
@@ -19065,7 +19070,7 @@
     </row>
     <row r="473" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A473" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B473">
         <v>-34.860666999999999</v>
@@ -19104,7 +19109,7 @@
     </row>
     <row r="474" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A474" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B474">
         <v>-34.838619999999999</v>
@@ -19140,7 +19145,7 @@
     </row>
     <row r="475" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A475" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B475">
         <v>-34.907184999999998</v>
@@ -19170,13 +19175,13 @@
         <v>5556</v>
       </c>
       <c r="Q475" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="T475" s="2"/>
     </row>
     <row r="476" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A476" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B476">
         <v>-35.092928999999998</v>
@@ -19206,13 +19211,13 @@
         <v>3944</v>
       </c>
       <c r="Q476" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="T476" s="2"/>
     </row>
     <row r="477" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A477" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B477">
         <v>-35.115721999999998</v>
@@ -19242,13 +19247,13 @@
         <v>2445</v>
       </c>
       <c r="Q477" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="T477" s="2"/>
     </row>
     <row r="478" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A478" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B478">
         <v>-34.860666999999999</v>
@@ -19296,7 +19301,7 @@
     </row>
     <row r="479" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A479" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B479">
         <v>-34.827359999999999</v>
@@ -19311,13 +19316,13 @@
         <v>0</v>
       </c>
       <c r="Q479" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="T479" s="2"/>
     </row>
     <row r="480" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A480" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B480">
         <v>-35.739091000000002</v>
@@ -19368,7 +19373,7 @@
     </row>
     <row r="481" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A481" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B481">
         <v>-34.827600699999998</v>
@@ -19407,7 +19412,7 @@
     </row>
     <row r="482" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A482" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B482">
         <v>-34.226579999999998</v>
@@ -19443,7 +19448,7 @@
     </row>
     <row r="483" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A483" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B483">
         <v>-34.917679100000001</v>
@@ -19467,13 +19472,13 @@
         <v>667</v>
       </c>
       <c r="Q483" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="T483" s="2"/>
     </row>
     <row r="484" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A484" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B484">
         <v>-34.929459999999999</v>
@@ -19488,13 +19493,13 @@
         <v>0</v>
       </c>
       <c r="Q484" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="T484" s="2"/>
     </row>
     <row r="485" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A485" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B485">
         <v>-34.970672</v>
@@ -19527,13 +19532,13 @@
         <v>19555</v>
       </c>
       <c r="Q485" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="T485" s="2"/>
     </row>
     <row r="486" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A486" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B486">
         <v>-35.011718100000003</v>
@@ -19566,13 +19571,13 @@
         <v>1779</v>
       </c>
       <c r="Q486" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="T486" s="2"/>
     </row>
     <row r="487" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A487" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B487">
         <v>-34.953057899999997</v>
@@ -19602,12 +19607,12 @@
         <v>29333</v>
       </c>
       <c r="Q487" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="488" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A488" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B488">
         <v>-34.906165799999997</v>
@@ -19640,12 +19645,12 @@
         <v>10222</v>
       </c>
       <c r="Q488" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="489" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A489" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="B489">
         <v>-35.510497000000001</v>
@@ -19672,7 +19677,7 @@
         <v>4666</v>
       </c>
       <c r="Q489" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="490" spans="1:20" x14ac:dyDescent="0.3">
@@ -19707,7 +19712,7 @@
         <v>2723</v>
       </c>
       <c r="Q490" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="491" spans="1:20" x14ac:dyDescent="0.3">
@@ -19776,7 +19781,7 @@
     </row>
     <row r="493" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A493" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B493">
         <v>-34.895150000000001</v>
@@ -19791,12 +19796,12 @@
         <v>306</v>
       </c>
       <c r="Q493" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="494" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A494" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B494">
         <v>-34.918889999999998</v>
@@ -19811,12 +19816,12 @@
         <v>0</v>
       </c>
       <c r="Q494" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="495" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A495" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B495">
         <v>-34.933680000000003</v>
@@ -19831,12 +19836,12 @@
         <v>0</v>
       </c>
       <c r="Q495" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="496" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A496" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B496">
         <v>-34.672490000000003</v>
@@ -19851,12 +19856,12 @@
         <v>0</v>
       </c>
       <c r="Q496" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="497" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A497" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B497">
         <v>-35.7987082</v>
@@ -19945,12 +19950,12 @@
         <v>1026</v>
       </c>
       <c r="Q498" t="s">
-        <v>271</v>
+        <v>149</v>
       </c>
     </row>
     <row r="499" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A499" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B499">
         <v>-35.110022000000001</v>
@@ -19980,12 +19985,12 @@
         <v>1888</v>
       </c>
       <c r="Q499" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="500" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A500" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B500">
         <v>-34.92989</v>
@@ -20003,12 +20008,12 @@
         <v>28</v>
       </c>
       <c r="Q500" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="501" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A501" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B501">
         <v>-34.933680000000003</v>
@@ -20023,12 +20028,12 @@
         <v>0</v>
       </c>
       <c r="Q501" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="502" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A502" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B502">
         <v>-34.630270000000003</v>
@@ -20055,12 +20060,12 @@
         <v>2889</v>
       </c>
       <c r="Q502" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="503" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A503" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B503">
         <v>-34.629179999999998</v>
@@ -20087,12 +20092,12 @@
         <v>945</v>
       </c>
       <c r="Q503" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="504" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A504" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B504">
         <v>-34.628860000000003</v>
@@ -20119,12 +20124,12 @@
         <v>723</v>
       </c>
       <c r="Q504" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="505" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A505" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B505">
         <v>-35.515507999999997</v>
@@ -20153,12 +20158,12 @@
       <c r="O505" s="1"/>
       <c r="P505" s="1"/>
       <c r="Q505" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="506" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A506" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B506">
         <v>-35.516800000000003</v>
@@ -20187,12 +20192,12 @@
       <c r="O506" s="1"/>
       <c r="P506" s="1"/>
       <c r="Q506" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="507" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A507" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B507">
         <v>-35.538469999999997</v>
@@ -20213,7 +20218,7 @@
         <v>111</v>
       </c>
       <c r="Q507" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="508" spans="1:17" x14ac:dyDescent="0.3">
@@ -20239,12 +20244,12 @@
         <v>0</v>
       </c>
       <c r="Q508" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="509" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A509" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B509">
         <v>-35.592393000000001</v>
@@ -20265,7 +20270,7 @@
         <v>111</v>
       </c>
       <c r="Q509" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="510" spans="1:17" x14ac:dyDescent="0.3">
@@ -20291,12 +20296,12 @@
         <v>111</v>
       </c>
       <c r="Q510" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="511" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A511" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B511">
         <v>-35.557977000000001</v>
@@ -20317,12 +20322,12 @@
         <v>167</v>
       </c>
       <c r="Q511" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="512" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A512" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B512">
         <v>-34.630270000000003</v>
@@ -20349,12 +20354,12 @@
         <v>2889</v>
       </c>
       <c r="Q512" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="513" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A513" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B513">
         <v>-34.630270000000003</v>
@@ -20381,12 +20386,12 @@
         <v>2889</v>
       </c>
       <c r="Q513" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="514" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A514" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B514">
         <v>-35.119663000000003</v>
@@ -20492,7 +20497,7 @@
     </row>
     <row r="516" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A516" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B516">
         <v>-35.031672</v>
@@ -20545,7 +20550,7 @@
     </row>
     <row r="517" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A517" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B517">
         <v>-35.762554199999997</v>
@@ -20595,7 +20600,7 @@
     </row>
     <row r="518" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A518" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B518">
         <v>-35.511125999999997</v>
@@ -20625,12 +20630,12 @@
         <v>4334</v>
       </c>
       <c r="Q518" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="519" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A519" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B519">
         <v>-35.793973000000001</v>
@@ -20680,7 +20685,7 @@
     </row>
     <row r="520" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A520" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B520">
         <v>-35.132868999999999</v>
@@ -20710,12 +20715,12 @@
         <v>1667</v>
       </c>
       <c r="Q520" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="521" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A521" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B521">
         <v>-34.899749999999997</v>
@@ -20742,12 +20747,12 @@
         <v>194</v>
       </c>
       <c r="Q521" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="522" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A522" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B522">
         <v>-35.054707999999998</v>
@@ -20777,12 +20782,12 @@
         <v>224333</v>
       </c>
       <c r="Q522" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="523" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A523" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B523">
         <v>-33.040959000000001</v>
@@ -20809,12 +20814,12 @@
         <v>3335</v>
       </c>
       <c r="Q523" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="524" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A524" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B524">
         <v>-33.917679999999997</v>
@@ -20844,12 +20849,12 @@
         <v>4334</v>
       </c>
       <c r="Q524" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="525" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A525" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B525">
         <v>-33.922530000000002</v>
@@ -20879,12 +20884,12 @@
         <v>12722</v>
       </c>
       <c r="Q525" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="526" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A526" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B526">
         <v>-33.912199999999999</v>
@@ -20914,12 +20919,12 @@
         <v>2334</v>
       </c>
       <c r="Q526" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="527" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A527" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B527">
         <v>-34.929459999999999</v>
@@ -20937,12 +20942,12 @@
         <v>0</v>
       </c>
       <c r="Q527" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="528" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A528" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B528">
         <v>-34.933680000000003</v>
@@ -20960,12 +20965,12 @@
         <v>0</v>
       </c>
       <c r="Q528" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="529" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A529" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B529">
         <v>-35.594605999999999</v>
@@ -20998,12 +21003,12 @@
         <v>10334</v>
       </c>
       <c r="Q529" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="530" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A530" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B530">
         <v>-35.510753999999999</v>
@@ -21036,7 +21041,7 @@
         <v>5333</v>
       </c>
       <c r="Q530" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="531" spans="1:17" x14ac:dyDescent="0.3">
@@ -21169,7 +21174,7 @@
     </row>
     <row r="535" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A535" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B535">
         <v>-35.6048446</v>
@@ -21204,7 +21209,7 @@
     </row>
     <row r="536" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A536" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B536">
         <v>-35.63158</v>
@@ -21239,7 +21244,7 @@
     </row>
     <row r="537" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A537" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B537">
         <v>-35.612963000000001</v>
@@ -21277,7 +21282,7 @@
     </row>
     <row r="538" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A538" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B538">
         <v>-34.911830000000002</v>
@@ -21301,12 +21306,12 @@
         <v>1723</v>
       </c>
       <c r="Q538" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="539" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A539" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B539">
         <v>-35.089612000000002</v>
@@ -21336,12 +21341,12 @@
         <v>2667</v>
       </c>
       <c r="Q539" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="540" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A540" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B540">
         <v>-34.994472000000002</v>
@@ -21368,12 +21373,12 @@
         <v>667</v>
       </c>
       <c r="Q540" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="541" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A541" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B541">
         <v>-35.522570000000002</v>
@@ -21406,12 +21411,12 @@
         <v>1612</v>
       </c>
       <c r="Q541" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="542" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A542" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B542">
         <v>-34.751460000000002</v>
@@ -21429,12 +21434,12 @@
         <v>0</v>
       </c>
       <c r="Q542" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="543" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A543" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B543">
         <v>-34.804662999999998</v>
@@ -21478,7 +21483,7 @@
     </row>
     <row r="544" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A544" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B544">
         <v>-34.824044999999998</v>
@@ -21575,7 +21580,7 @@
     </row>
     <row r="546" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A546" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B546">
         <v>-34.920539599999998</v>
@@ -21605,12 +21610,12 @@
         <v>8946</v>
       </c>
       <c r="Q546" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="547" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A547" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B547">
         <v>-35.085709299999998</v>
@@ -21637,12 +21642,12 @@
         <v>5888</v>
       </c>
       <c r="Q547" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="548" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A548" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B548">
         <v>-35.445188000000002</v>
@@ -21672,12 +21677,12 @@
         <v>890</v>
       </c>
       <c r="Q548" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="549" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A549" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B549">
         <v>-35.516500000000001</v>
@@ -21698,12 +21703,12 @@
         <v>56</v>
       </c>
       <c r="Q549" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="550" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A550" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B550">
         <v>-35.517899999999997</v>
@@ -21724,7 +21729,7 @@
         <v>500</v>
       </c>
       <c r="Q550" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="551" spans="1:17" x14ac:dyDescent="0.3">
@@ -21750,12 +21755,12 @@
         <v>56</v>
       </c>
       <c r="Q551" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="552" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A552" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B552">
         <v>-35.538600000000002</v>
@@ -21776,12 +21781,12 @@
         <v>0</v>
       </c>
       <c r="Q552" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="553" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A553" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B553">
         <v>-35.5565</v>
@@ -21802,12 +21807,12 @@
         <v>0</v>
       </c>
       <c r="Q553" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="554" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A554" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B554">
         <v>-35.563899999999997</v>
@@ -21828,12 +21833,12 @@
         <v>0</v>
       </c>
       <c r="Q554" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="555" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A555" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B555">
         <v>-35.592599999999997</v>
@@ -21854,12 +21859,12 @@
         <v>167</v>
       </c>
       <c r="Q555" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="556" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A556" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B556">
         <v>-35.634900000000002</v>
@@ -21880,12 +21885,12 @@
         <v>167</v>
       </c>
       <c r="Q556" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="557" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A557" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B557">
         <v>-34.929459999999999</v>
@@ -21903,12 +21908,12 @@
         <v>0</v>
       </c>
       <c r="Q557" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="558" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A558" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B558">
         <v>-34.928570000000001</v>
@@ -21926,12 +21931,12 @@
         <v>0</v>
       </c>
       <c r="Q558" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="559" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A559" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B559">
         <v>-34.901600000000002</v>
@@ -21949,12 +21954,12 @@
         <v>0</v>
       </c>
       <c r="Q559" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="560" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A560" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B560">
         <v>-34.630270000000003</v>
@@ -21987,12 +21992,12 @@
         <v>15888</v>
       </c>
       <c r="Q560" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="561" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A561" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B561">
         <v>-34.629179999999998</v>
@@ -22025,7 +22030,7 @@
         <v>23556</v>
       </c>
       <c r="Q561" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="562" spans="1:17" x14ac:dyDescent="0.3">
@@ -22074,7 +22079,7 @@
     </row>
     <row r="563" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A563" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B563">
         <v>-35.32508</v>
@@ -22104,12 +22109,12 @@
         <v>1167</v>
       </c>
       <c r="Q563" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="564" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A564" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B564">
         <v>-34.903820000000003</v>
@@ -22130,7 +22135,7 @@
         <v>722</v>
       </c>
       <c r="Q564" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="565" spans="1:17" x14ac:dyDescent="0.3">
@@ -22243,7 +22248,7 @@
     </row>
     <row r="568" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A568" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B568">
         <v>-34.911830000000002</v>
@@ -22264,12 +22269,12 @@
         <v>1611</v>
       </c>
       <c r="Q568" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="569" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A569" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B569">
         <v>-34.893770000000004</v>
@@ -22290,12 +22295,12 @@
         <v>389</v>
       </c>
       <c r="Q569" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="570" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A570" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B570" s="13">
         <f>-35.521088</f>
@@ -22330,12 +22335,12 @@
         <v>4556</v>
       </c>
       <c r="Q570" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="571" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A571" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="B571">
         <v>-34.495376</v>
@@ -22365,12 +22370,12 @@
         <v>889</v>
       </c>
       <c r="Q571" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="572" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A572" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B572">
         <v>-34.750552999999996</v>
@@ -22397,12 +22402,12 @@
         <v>778</v>
       </c>
       <c r="Q572" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="573" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A573" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B573">
         <v>-34.672504000000004</v>
@@ -22432,12 +22437,12 @@
         <v>1056</v>
       </c>
       <c r="Q573" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="574" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A574" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B574">
         <v>-34.588209999999997</v>
@@ -22464,12 +22469,12 @@
         <v>500</v>
       </c>
       <c r="Q574" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="575" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A575" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B575">
         <v>-34.899749999999997</v>
@@ -22499,12 +22504,12 @@
         <v>5834</v>
       </c>
       <c r="Q575" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="576" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A576" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B576">
         <v>-34.812609999999999</v>
@@ -22522,12 +22527,12 @@
         <v>0</v>
       </c>
       <c r="Q576" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="577" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A577" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B577">
         <v>-34.827359999999999</v>
@@ -22545,12 +22550,12 @@
         <v>0</v>
       </c>
       <c r="Q577" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="578" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A578" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B578">
         <v>-34.672490000000003</v>
@@ -22568,12 +22573,12 @@
         <v>0</v>
       </c>
       <c r="Q578" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="579" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A579" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B579">
         <v>-34.827359999999999</v>
@@ -22617,7 +22622,7 @@
     </row>
     <row r="580" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A580" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B580">
         <v>-34.912934499999999</v>
@@ -22647,12 +22652,12 @@
         <v>6222</v>
       </c>
       <c r="Q580" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="581" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A581" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B581">
         <v>-34.672490000000003</v>
@@ -22670,12 +22675,12 @@
         <v>0</v>
       </c>
       <c r="Q581" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="582" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A582" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B582">
         <v>-34.751460000000002</v>
@@ -22693,12 +22698,12 @@
         <v>0</v>
       </c>
       <c r="Q582" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="583" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A583" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B583">
         <v>-34.831850000000003</v>
@@ -22719,12 +22724,12 @@
         <v>56</v>
       </c>
       <c r="Q583" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="584" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A584" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B584">
         <v>-34.899749999999997</v>
@@ -22754,12 +22759,12 @@
         <v>6889</v>
       </c>
       <c r="Q584" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="585" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A585" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B585">
         <v>-34.920539599999998</v>
@@ -22804,12 +22809,12 @@
         <v>1444</v>
       </c>
       <c r="Q585" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="586" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A586" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B586">
         <v>-34.933680000000003</v>
@@ -22839,12 +22844,12 @@
         <v>10334</v>
       </c>
       <c r="Q586" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="587" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A587" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B587">
         <v>-34.804662999999998</v>
@@ -22897,7 +22902,7 @@
     </row>
     <row r="588" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A588" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B588">
         <v>-34.824044999999998</v>
@@ -23003,7 +23008,7 @@
     </row>
     <row r="590" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A590" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B590">
         <v>-34.860666999999999</v>
@@ -23123,7 +23128,7 @@
     </row>
     <row r="593" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A593" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B593">
         <v>-34.628860000000003</v>
@@ -23156,12 +23161,12 @@
         <v>1279</v>
       </c>
       <c r="Q593" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="594" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A594" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B594">
         <v>-34.519669999999998</v>
@@ -23194,12 +23199,12 @@
         <v>446</v>
       </c>
       <c r="Q594" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="595" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A595" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B595">
         <v>-34.535609999999998</v>
@@ -23223,12 +23228,12 @@
         <v>222</v>
       </c>
       <c r="Q595" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="596" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A596" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B596">
         <v>-34.827359999999999</v>
@@ -23261,12 +23266,12 @@
         <v>13889</v>
       </c>
       <c r="Q596" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="597" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A597" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B597">
         <v>-34.672490000000003</v>
@@ -23296,12 +23301,12 @@
         <v>2111</v>
       </c>
       <c r="Q597" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="598" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A598" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B598">
         <v>-34.890371899999998</v>
@@ -23334,12 +23339,12 @@
         <v>14444</v>
       </c>
       <c r="Q598" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="599" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A599" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B599">
         <v>-35.500242</v>
@@ -23373,12 +23378,12 @@
         <v>611</v>
       </c>
       <c r="Q599" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="600" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A600" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B600">
         <v>-34.672490000000003</v>
@@ -23393,12 +23398,12 @@
         <v>556</v>
       </c>
       <c r="Q600" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="601" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A601" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B601">
         <v>-34.751460000000002</v>
@@ -23413,12 +23418,12 @@
         <v>0</v>
       </c>
       <c r="Q601" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="602" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A602" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B602">
         <v>-34.670960000000001</v>
@@ -23433,12 +23438,12 @@
         <v>1167</v>
       </c>
       <c r="Q602" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="603" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A603" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B603">
         <v>-34.643329999999999</v>
@@ -23453,12 +23458,12 @@
         <v>1333</v>
       </c>
       <c r="Q603" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="604" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A604" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B604">
         <v>-34.586370000000002</v>
@@ -23473,12 +23478,12 @@
         <v>0</v>
       </c>
       <c r="Q604" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="605" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A605" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B605">
         <v>-34.9094768</v>
@@ -23523,7 +23528,7 @@
         <v>8222</v>
       </c>
       <c r="Q605" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="606" spans="1:17" x14ac:dyDescent="0.3">
@@ -23572,7 +23577,7 @@
     </row>
     <row r="607" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A607" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B607">
         <v>-34.899749999999997</v>
@@ -23590,12 +23595,12 @@
         <v>1778</v>
       </c>
       <c r="Q607" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="608" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A608" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B608">
         <v>-34.751460000000002</v>
@@ -23613,12 +23618,12 @@
         <v>2833</v>
       </c>
       <c r="Q608" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="609" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A609" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B609">
         <v>-34.672490000000003</v>
@@ -23636,12 +23641,12 @@
         <v>500</v>
       </c>
       <c r="Q609" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="610" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A610" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B610">
         <v>-34.586370000000002</v>
@@ -23659,12 +23664,12 @@
         <v>0</v>
       </c>
       <c r="Q610" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="611" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A611" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B611">
         <v>-34.507260000000002</v>
@@ -23682,12 +23687,12 @@
         <v>0</v>
       </c>
       <c r="Q611" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="612" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A612" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B612">
         <v>-34.827359999999999</v>
@@ -23705,12 +23710,12 @@
         <v>2000</v>
       </c>
       <c r="Q612" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="613" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A613" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B613">
         <v>-34.899749999999997</v>
@@ -23728,12 +23733,12 @@
         <v>4278</v>
       </c>
       <c r="Q613" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="614" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A614" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B614">
         <v>-34.911830000000002</v>
@@ -23751,12 +23756,12 @@
         <v>0</v>
       </c>
       <c r="Q614" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="615" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A615" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B615">
         <v>-34.899749999999997</v>
@@ -23774,12 +23779,12 @@
         <v>5500</v>
       </c>
       <c r="Q615" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="616" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A616" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B616">
         <v>-34.751460000000002</v>
@@ -23797,12 +23802,12 @@
         <v>222</v>
       </c>
       <c r="Q616" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="617" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A617" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B617">
         <v>-34.672490000000003</v>
@@ -23820,12 +23825,12 @@
         <v>0</v>
       </c>
       <c r="Q617" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="618" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A618" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B618">
         <v>-35.642456000000003</v>
@@ -23863,7 +23868,7 @@
     </row>
     <row r="619" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A619" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B619">
         <v>-34.824044999999998</v>
@@ -23950,7 +23955,7 @@
     </row>
     <row r="621" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A621" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B621">
         <v>-34.860666999999999</v>
@@ -24022,7 +24027,7 @@
     </row>
     <row r="623" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A623" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B623">
         <v>-34.899749999999997</v>
@@ -24040,12 +24045,12 @@
         <v>3889</v>
       </c>
       <c r="Q623" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="624" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A624" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B624">
         <v>-34.899749999999997</v>
@@ -24063,12 +24068,12 @@
         <v>4278</v>
       </c>
       <c r="Q624" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="625" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A625" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B625">
         <v>-34.672490000000003</v>
@@ -24086,12 +24091,12 @@
         <v>333</v>
       </c>
       <c r="Q625" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="626" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A626" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B626">
         <v>-34.66301</v>
@@ -24109,12 +24114,12 @@
         <v>7222</v>
       </c>
       <c r="Q626" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="627" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A627" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B627">
         <v>-34.586370000000002</v>
@@ -24132,12 +24137,12 @@
         <v>222</v>
       </c>
       <c r="Q627" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="628" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A628" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B628">
         <v>-34.52664</v>
@@ -24155,12 +24160,12 @@
         <v>222</v>
       </c>
       <c r="Q628" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="629" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A629" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B629">
         <v>-34.494970000000002</v>
@@ -24178,7 +24183,7 @@
         <v>56</v>
       </c>
       <c r="Q629" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="630" spans="1:17" x14ac:dyDescent="0.3">
@@ -24259,7 +24264,7 @@
     </row>
     <row r="632" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A632" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="B632">
         <v>-33.043101999999998</v>
@@ -24286,12 +24291,12 @@
         <v>2222</v>
       </c>
       <c r="Q632" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="633" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A633" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B633">
         <v>-35.445188000000002</v>
@@ -24319,12 +24324,12 @@
         <v>0</v>
       </c>
       <c r="Q633" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="634" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A634" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B634">
         <v>-34.637633999999998</v>
@@ -24348,12 +24353,12 @@
         <v>112</v>
       </c>
       <c r="Q634" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="635" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A635" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B635">
         <v>-34.864305100000003</v>
@@ -24377,7 +24382,7 @@
         <v>112</v>
       </c>
       <c r="Q635" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="636" spans="1:17" x14ac:dyDescent="0.3">
@@ -24418,7 +24423,7 @@
     </row>
     <row r="637" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A637" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B637">
         <v>-35.092981999999999</v>
@@ -24448,12 +24453,12 @@
         <v>5482</v>
       </c>
       <c r="Q637" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="638" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A638" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B638">
         <v>-34.672490000000003</v>
@@ -24471,12 +24476,12 @@
         <v>833</v>
       </c>
       <c r="Q638" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="639" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A639" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B639">
         <v>-34.899749999999997</v>
@@ -24494,7 +24499,7 @@
         <v>2611</v>
       </c>
       <c r="Q639" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="640" spans="1:17" x14ac:dyDescent="0.3">
@@ -24581,7 +24586,7 @@
     </row>
     <row r="642" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A642" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B642">
         <v>-34.672490000000003</v>
@@ -24609,12 +24614,12 @@
       <c r="O642" s="1"/>
       <c r="P642" s="1"/>
       <c r="Q642" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="643" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A643" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B643">
         <v>-34.934266999999998</v>
@@ -24647,12 +24652,12 @@
         <v>11723</v>
       </c>
       <c r="Q643" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="644" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A644" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B644">
         <v>-34.910024</v>
@@ -24682,7 +24687,7 @@
         <v>22944</v>
       </c>
       <c r="Q644" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="645" spans="1:17" x14ac:dyDescent="0.3">
@@ -24810,7 +24815,7 @@
     </row>
     <row r="648" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A648" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B648">
         <v>-35.612285999999997</v>
@@ -24851,7 +24856,7 @@
     </row>
     <row r="649" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A649" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="B649">
         <v>-34.933680000000003</v>
@@ -24881,12 +24886,12 @@
         <v>8000</v>
       </c>
       <c r="Q649" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="650" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A650" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B650">
         <v>-34.899749999999997</v>
@@ -24914,12 +24919,12 @@
       <c r="O650" s="1"/>
       <c r="P650" s="1"/>
       <c r="Q650" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="651" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A651" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B651">
         <v>-34.911830000000002</v>
@@ -24947,12 +24952,12 @@
       <c r="O651" s="1"/>
       <c r="P651" s="1"/>
       <c r="Q651" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="652" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A652" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B652">
         <v>-34.824044999999998</v>
@@ -25006,7 +25011,7 @@
     </row>
     <row r="653" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A653" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B653">
         <v>-34.860666999999999</v>
@@ -25114,7 +25119,7 @@
     </row>
     <row r="655" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A655" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B655">
         <v>-35.878667100000001</v>
@@ -25167,7 +25172,7 @@
     </row>
     <row r="656" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A656" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B656">
         <v>-34.586370000000002</v>
@@ -25195,12 +25200,12 @@
       <c r="O656" s="1"/>
       <c r="P656" s="1"/>
       <c r="Q656" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="657" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A657" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B657">
         <v>-34.751460000000002</v>
@@ -25228,12 +25233,12 @@
       <c r="O657" s="1"/>
       <c r="P657" s="1"/>
       <c r="Q657" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="658" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A658" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B658">
         <v>-35.853555700000001</v>
@@ -25286,7 +25291,7 @@
     </row>
     <row r="659" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A659" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B659">
         <v>-35.787276900000002</v>
@@ -25339,7 +25344,7 @@
     </row>
     <row r="660" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A660" s="17" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B660">
         <v>-34.776083</v>
@@ -25374,16 +25379,16 @@
         <v>56</v>
       </c>
       <c r="P660" s="17">
-        <f>SUM(F660:I660,K660:O660)</f>
+        <f t="shared" ref="P660:P666" si="0">SUM(F660:I660,K660:O660)</f>
         <v>1111</v>
       </c>
       <c r="Q660" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="661" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A661" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B661">
         <v>-35.515507999999997</v>
@@ -25407,11 +25412,11 @@
         <v>111</v>
       </c>
       <c r="P661">
-        <f>SUM(F661:I661,K661:O661)</f>
+        <f t="shared" si="0"/>
         <v>444</v>
       </c>
       <c r="Q661" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="662" spans="1:17" x14ac:dyDescent="0.3">
@@ -25440,16 +25445,16 @@
         <v>0</v>
       </c>
       <c r="P662">
-        <f>SUM(F662:I662,K662:O662)</f>
+        <f t="shared" si="0"/>
         <v>56</v>
       </c>
       <c r="Q662" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="663" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A663" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B663">
         <v>-35.538469999999997</v>
@@ -25473,16 +25478,16 @@
         <v>167</v>
       </c>
       <c r="P663">
-        <f>SUM(F663:I663,K663:O663)</f>
+        <f t="shared" si="0"/>
         <v>167</v>
       </c>
       <c r="Q663" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="664" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A664" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B664">
         <v>-35.5565</v>
@@ -25506,16 +25511,16 @@
         <v>56</v>
       </c>
       <c r="P664">
-        <f>SUM(F664:I664,K664:O664)</f>
+        <f t="shared" si="0"/>
         <v>112</v>
       </c>
       <c r="Q664" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="665" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A665" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B665">
         <v>-35.592393000000001</v>
@@ -25539,16 +25544,16 @@
         <v>0</v>
       </c>
       <c r="P665">
-        <f>SUM(F665:I665,K665:O665)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Q665" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="666" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A666" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B666">
         <v>-35.634602000000001</v>
@@ -25572,16 +25577,16 @@
         <v>222</v>
       </c>
       <c r="P666">
-        <f>SUM(F666:I666,K666:O666)</f>
+        <f t="shared" si="0"/>
         <v>278</v>
       </c>
       <c r="Q666" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="667" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A667" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="B667">
         <v>-34.918303199999997</v>
@@ -25608,12 +25613,12 @@
         <v>223</v>
       </c>
       <c r="Q667" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="668" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A668" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="B668">
         <v>-34.911405199999997</v>
@@ -25643,12 +25648,12 @@
         <v>390</v>
       </c>
       <c r="Q668" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="669" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A669" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B669">
         <v>-34.899749999999997</v>
@@ -25678,12 +25683,12 @@
       <c r="O669" s="1"/>
       <c r="P669" s="1"/>
       <c r="Q669" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="670" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A670" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B670">
         <v>-34.82743</v>
@@ -25713,12 +25718,12 @@
       <c r="O670" s="1"/>
       <c r="P670" s="1"/>
       <c r="Q670" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="671" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A671" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B671">
         <v>-34.751460000000002</v>
@@ -25746,7 +25751,7 @@
       <c r="O671" s="1"/>
       <c r="P671" s="1"/>
       <c r="Q671" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="672" spans="1:17" x14ac:dyDescent="0.3">
@@ -25834,7 +25839,7 @@
     </row>
     <row r="674" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A674" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B674">
         <v>-35.739091000000002</v>
@@ -25884,7 +25889,7 @@
     </row>
     <row r="675" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A675" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B675">
         <v>-34.494970000000002</v>
@@ -25912,7 +25917,7 @@
       <c r="O675" s="1"/>
       <c r="P675" s="1"/>
       <c r="Q675" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="676" spans="1:17" x14ac:dyDescent="0.3">
@@ -25971,7 +25976,7 @@
     </row>
     <row r="677" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A677" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B677">
         <v>-35.119663000000003</v>
@@ -26101,7 +26106,7 @@
     </row>
     <row r="680" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A680" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B680">
         <v>-34.759169999999997</v>
@@ -26119,12 +26124,12 @@
         <v>1833</v>
       </c>
       <c r="Q680" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="681" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A681" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B681">
         <v>-34.672490000000003</v>
@@ -26139,12 +26144,12 @@
         <v>333</v>
       </c>
       <c r="Q681" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="682" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A682" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B682">
         <v>-34.494970000000002</v>
@@ -26162,12 +26167,12 @@
         <v>167</v>
       </c>
       <c r="Q682" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="683" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A683" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B683">
         <v>-34.584389999999999</v>
@@ -26185,12 +26190,12 @@
         <v>0</v>
       </c>
       <c r="Q683" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="684" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A684" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B684">
         <v>-34.899749999999997</v>
@@ -26208,7 +26213,7 @@
         <v>4833</v>
       </c>
       <c r="Q684" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="685" spans="1:17" x14ac:dyDescent="0.3">
@@ -26260,7 +26265,7 @@
     </row>
     <row r="686" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A686" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B686">
         <v>-34.902070808541197</v>
@@ -26281,7 +26286,7 @@
         <v>167</v>
       </c>
       <c r="K686" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="L686">
         <v>167</v>
@@ -26296,12 +26301,12 @@
         <v>1390</v>
       </c>
       <c r="Q686" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="687" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A687" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="B687">
         <v>-34.933680000000003</v>
@@ -26331,12 +26336,12 @@
         <v>1057</v>
       </c>
       <c r="Q687" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="688" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A688" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B688">
         <v>-34.759169999999997</v>
@@ -26354,12 +26359,12 @@
         <v>1556</v>
       </c>
       <c r="Q688" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="689" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A689" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B689">
         <v>-34.075153</v>
@@ -26397,7 +26402,7 @@
     </row>
     <row r="690" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A690" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B690">
         <v>-35.762554199999997</v>
@@ -26450,7 +26455,7 @@
     </row>
     <row r="691" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A691" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B691">
         <v>-35.853555700000001</v>
@@ -26503,7 +26508,7 @@
     </row>
     <row r="692" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A692" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B692">
         <v>-35.852509699999999</v>
@@ -26553,7 +26558,7 @@
     </row>
     <row r="693" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A693" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B693">
         <v>-35.787201000000003</v>
@@ -26606,7 +26611,7 @@
     </row>
     <row r="694" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A694" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B694">
         <v>-34.759169999999997</v>
@@ -26624,12 +26629,12 @@
         <v>2667</v>
       </c>
       <c r="Q694" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="695" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A695" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B695">
         <v>-34.494970000000002</v>
@@ -26647,12 +26652,12 @@
         <v>222</v>
       </c>
       <c r="Q695" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="696" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A696" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="B696">
         <v>-36.866</v>
@@ -26693,7 +26698,7 @@
     </row>
     <row r="697" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A697" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B697">
         <v>-34.902070808541197</v>
@@ -26726,12 +26731,12 @@
         <v>1556</v>
       </c>
       <c r="Q697" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="698" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A698" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="B698">
         <v>-34.495376</v>
@@ -26764,12 +26769,12 @@
         <v>3889</v>
       </c>
       <c r="Q698" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="699" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A699" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B699">
         <v>-34.759169999999997</v>
@@ -26787,12 +26792,12 @@
         <v>167</v>
       </c>
       <c r="Q699" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="700" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A700" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B700">
         <v>-34.899749999999997</v>
@@ -26810,12 +26815,12 @@
         <v>3167</v>
       </c>
       <c r="Q700" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="701" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A701" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B701">
         <v>-34.759169999999997</v>
@@ -26833,12 +26838,12 @@
         <v>0</v>
       </c>
       <c r="Q701" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="702" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A702" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B702">
         <v>-35.853555700000001</v>
@@ -26891,7 +26896,7 @@
     </row>
     <row r="703" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A703" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B703">
         <v>-35.739091000000002</v>
@@ -26944,7 +26949,7 @@
     </row>
     <row r="704" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A704" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B704">
         <v>-34.824044999999998</v>
@@ -27064,7 +27069,7 @@
     </row>
     <row r="707" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A707" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B707">
         <v>-35.516800000000003</v>
@@ -27091,12 +27096,12 @@
         <v>222</v>
       </c>
       <c r="Q707" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="708" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A708" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B708">
         <v>-35.515900000000002</v>
@@ -27123,7 +27128,7 @@
         <v>333</v>
       </c>
       <c r="Q708" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="709" spans="1:17" x14ac:dyDescent="0.3">
@@ -27155,12 +27160,12 @@
         <v>167</v>
       </c>
       <c r="Q709" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="710" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A710" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B710">
         <v>-35.538600000000002</v>
@@ -27187,12 +27192,12 @@
         <v>0</v>
       </c>
       <c r="Q710" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="711" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A711" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B711">
         <v>-35.5565</v>
@@ -27219,12 +27224,12 @@
         <v>0</v>
       </c>
       <c r="Q711" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="712" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A712" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B712">
         <v>-35.5565</v>
@@ -27251,12 +27256,12 @@
         <v>167</v>
       </c>
       <c r="Q712" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="713" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A713" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B713">
         <v>-35.634900000000002</v>
@@ -27283,12 +27288,12 @@
         <v>111</v>
       </c>
       <c r="Q713" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="714" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A714" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="B714">
         <v>-35.510497000000001</v>
@@ -27321,12 +27326,12 @@
         <v>4722</v>
       </c>
       <c r="Q714" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="715" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A715" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B715">
         <v>-35.793973000000001</v>
@@ -27379,7 +27384,7 @@
     </row>
     <row r="716" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A716" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="B716">
         <v>-34.88823</v>
@@ -27397,7 +27402,7 @@
         <v>1722</v>
       </c>
       <c r="Q716" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="717" spans="1:17" x14ac:dyDescent="0.3">
@@ -27472,7 +27477,7 @@
     </row>
     <row r="719" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A719" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="B719">
         <v>-33.043101999999998</v>
@@ -27499,12 +27504,12 @@
         <v>1889</v>
       </c>
       <c r="Q719" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="720" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A720" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B720">
         <v>-35.878667100000001</v>
@@ -27595,7 +27600,7 @@
     </row>
     <row r="722" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A722" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="B722">
         <v>-34.842409000000004</v>
@@ -27639,7 +27644,7 @@
     </row>
     <row r="723" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A723" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B723">
         <v>-34.759169999999997</v>
@@ -27657,12 +27662,12 @@
         <v>167</v>
       </c>
       <c r="Q723" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="724" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A724" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B724">
         <v>-34.672490000000003</v>
@@ -27680,7 +27685,7 @@
         <v>0</v>
       </c>
       <c r="Q724" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="725" spans="1:17" x14ac:dyDescent="0.3">
@@ -27723,7 +27728,7 @@
     </row>
     <row r="726" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A726" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B726">
         <v>-35.786641000000003</v>
@@ -27776,7 +27781,7 @@
     </row>
     <row r="727" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A727" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B727">
         <v>-35.638145999999999</v>
@@ -27829,7 +27834,7 @@
     </row>
     <row r="728" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A728" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="B728">
         <v>-35.532783000000002</v>
@@ -27905,7 +27910,7 @@
     </row>
     <row r="730" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A730" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="B730">
         <v>-35.521971999999998</v>
@@ -27941,7 +27946,7 @@
         <v>1389</v>
       </c>
       <c r="Q730" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="731" spans="1:17" x14ac:dyDescent="0.3">
@@ -28025,7 +28030,7 @@
     </row>
     <row r="733" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A733" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="B733">
         <v>-35.557299999999998</v>
@@ -28183,7 +28188,7 @@
     </row>
     <row r="737" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A737" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B737">
         <v>-35.612285999999997</v>
@@ -28221,7 +28226,7 @@
     </row>
     <row r="738" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A738" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B738">
         <v>-35.61</v>
@@ -28256,7 +28261,7 @@
     </row>
     <row r="739" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A739" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="B739">
         <v>-34.958151000000001</v>
@@ -28291,7 +28296,7 @@
     </row>
     <row r="740" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A740" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B740">
         <v>-34.860666999999999</v>
@@ -28329,7 +28334,7 @@
     </row>
     <row r="741" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A741" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B741">
         <v>-35.445188000000002</v>
@@ -28362,12 +28367,12 @@
         <v>2056</v>
       </c>
       <c r="Q741" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="742" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A742" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B742">
         <v>-34.759169999999997</v>
@@ -28385,12 +28390,12 @@
         <v>0</v>
       </c>
       <c r="Q742" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="743" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A743" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B743">
         <v>-35.739091000000002</v>
@@ -28443,7 +28448,7 @@
     </row>
     <row r="744" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A744" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B744">
         <v>-35.853555700000001</v>
@@ -28496,7 +28501,7 @@
     </row>
     <row r="745" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A745" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="B745">
         <v>-34.323770000000003</v>
@@ -28514,12 +28519,12 @@
         <v>0</v>
       </c>
       <c r="Q745" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="746" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A746" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B746">
         <v>-34.494970000000002</v>
@@ -28537,12 +28542,12 @@
         <v>0</v>
       </c>
       <c r="Q746" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="747" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A747" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B747">
         <v>-34.899749999999997</v>
@@ -28560,12 +28565,12 @@
         <v>111</v>
       </c>
       <c r="Q747" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="748" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A748" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="B748">
         <v>-34.075042000000003</v>
@@ -28589,12 +28594,12 @@
         <v>167</v>
       </c>
       <c r="Q748" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="749" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A749" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B749">
         <v>-35.081918000000002</v>
@@ -28627,12 +28632,12 @@
         <v>1389</v>
       </c>
       <c r="Q749" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="750" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A750" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B750">
         <v>-35.081918000000002</v>
@@ -28665,12 +28670,12 @@
         <v>1389</v>
       </c>
       <c r="Q750" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="751" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A751" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B751">
         <v>-34.902070808541197</v>
@@ -28700,12 +28705,12 @@
         <v>500</v>
       </c>
       <c r="Q751" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="752" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A752" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B752">
         <v>-35.853555700000001</v>
@@ -28758,7 +28763,7 @@
     </row>
     <row r="753" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A753" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B753">
         <v>-34.899749999999997</v>
@@ -28776,12 +28781,12 @@
         <v>111</v>
       </c>
       <c r="Q753" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="754" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A754" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B754">
         <v>-34.672499999999999</v>
@@ -28796,7 +28801,7 @@
         <v>0</v>
       </c>
       <c r="Q754" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="755" spans="1:17" x14ac:dyDescent="0.3">
@@ -28868,7 +28873,7 @@
     </row>
     <row r="757" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A757" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B757">
         <v>-34.824044999999998</v>
@@ -28903,7 +28908,7 @@
     </row>
     <row r="758" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A758" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="B758">
         <v>-34.958151000000001</v>
@@ -28970,7 +28975,7 @@
     </row>
     <row r="760" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A760" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B760">
         <v>-35.739091000000002</v>
@@ -29023,7 +29028,7 @@
     </row>
     <row r="761" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A761" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="B761">
         <v>-34.903120000000001</v>
@@ -29050,12 +29055,12 @@
         <v>500</v>
       </c>
       <c r="Q761" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="762" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A762" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B762">
         <v>-35.054707999999998</v>
@@ -29085,12 +29090,12 @@
         <v>70167</v>
       </c>
       <c r="Q762" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="763" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A763" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B763">
         <v>-34.903466000000002</v>
@@ -29123,12 +29128,12 @@
         <v>1333</v>
       </c>
       <c r="Q763" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="764" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A764" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="B764">
         <v>-34.765996000000001</v>
@@ -29161,12 +29166,12 @@
         <v>667</v>
       </c>
       <c r="Q764" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="765" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A765" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="B765">
         <v>-35.510497000000001</v>
@@ -29196,12 +29201,12 @@
         <v>2334</v>
       </c>
       <c r="Q765" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="766" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A766" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="B766">
         <v>-35.793973000000001</v>
@@ -29254,7 +29259,7 @@
     </row>
     <row r="767" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A767" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B767">
         <v>-35.878667100000001</v>
@@ -29307,7 +29312,7 @@
     </row>
     <row r="768" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A768" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B768">
         <v>-35.445188000000002</v>
@@ -29337,12 +29342,12 @@
         <v>1722</v>
       </c>
       <c r="Q768" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="769" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A769" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B769">
         <v>-34.759169999999997</v>
@@ -29369,12 +29374,12 @@
         <v>167</v>
       </c>
       <c r="Q769" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="770" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A770" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B770">
         <v>-35.445186</v>
@@ -29407,12 +29412,12 @@
         <v>890</v>
       </c>
       <c r="Q770" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="771" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A771" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B771">
         <v>-34.672499999999999</v>
@@ -29442,12 +29447,12 @@
         <v>223</v>
       </c>
       <c r="Q771" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="772" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A772" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="B772">
         <v>-35.557499999999997</v>
@@ -29488,7 +29493,7 @@
     </row>
     <row r="773" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A773" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B773">
         <v>-34.860666999999999</v>
@@ -29596,7 +29601,7 @@
     </row>
     <row r="776" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A776" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B776">
         <v>-34.824044999999998</v>
@@ -29634,7 +29639,7 @@
     </row>
     <row r="777" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A777" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B777" s="1">
         <v>-35.516800000000003</v>
@@ -29665,16 +29670,16 @@
       <c r="N777" s="1"/>
       <c r="O777" s="1"/>
       <c r="P777">
-        <f>SUM(F777:I777,K777:O777)</f>
+        <f t="shared" ref="P777:P788" si="1">SUM(F777:I777,K777:O777)</f>
         <v>722</v>
       </c>
       <c r="Q777" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="778" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A778" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B778">
         <v>-35.515900000000002</v>
@@ -29698,11 +29703,11 @@
         <v>111</v>
       </c>
       <c r="P778">
-        <f>SUM(F778:I778,K778:O778)</f>
+        <f t="shared" si="1"/>
         <v>167</v>
       </c>
       <c r="Q778" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="779" spans="1:17" x14ac:dyDescent="0.3">
@@ -29731,16 +29736,16 @@
         <v>56</v>
       </c>
       <c r="P779">
-        <f>SUM(F779:I779,K779:O779)</f>
+        <f t="shared" si="1"/>
         <v>278</v>
       </c>
       <c r="Q779" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="780" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A780" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B780">
         <v>-35.538600000000002</v>
@@ -29764,16 +29769,16 @@
         <v>56</v>
       </c>
       <c r="P780">
-        <f>SUM(F780:I780,K780:O780)</f>
+        <f t="shared" si="1"/>
         <v>112</v>
       </c>
       <c r="Q780" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="781" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A781" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B781">
         <v>-35.5565</v>
@@ -29797,16 +29802,16 @@
         <v>0</v>
       </c>
       <c r="P781">
-        <f>SUM(F781:I781,K781:O781)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Q781" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="782" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A782" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B782">
         <v>-35.5565</v>
@@ -29830,16 +29835,16 @@
         <v>56</v>
       </c>
       <c r="P782">
-        <f>SUM(F782:I782,K782:O782)</f>
+        <f t="shared" si="1"/>
         <v>278</v>
       </c>
       <c r="Q782" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="783" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A783" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B783">
         <v>-35.634900000000002</v>
@@ -29863,16 +29868,16 @@
         <v>167</v>
       </c>
       <c r="P783">
-        <f>SUM(F783:I783,K783:O783)</f>
+        <f t="shared" si="1"/>
         <v>445</v>
       </c>
       <c r="Q783" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="784" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A784" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B784">
         <v>-35.563899999999997</v>
@@ -29896,16 +29901,16 @@
         <v>0</v>
       </c>
       <c r="P784">
-        <f>SUM(F784:I784,K784:O784)</f>
+        <f t="shared" si="1"/>
         <v>56</v>
       </c>
       <c r="Q784" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="785" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A785" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B785">
         <v>-35.548499999999997</v>
@@ -29929,16 +29934,16 @@
         <v>56</v>
       </c>
       <c r="P785">
-        <f>SUM(F785:I785,K785:O785)</f>
+        <f t="shared" si="1"/>
         <v>56</v>
       </c>
       <c r="Q785" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="786" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A786" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="B786">
         <v>-35.5595</v>
@@ -29962,16 +29967,16 @@
         <v>56</v>
       </c>
       <c r="P786">
-        <f>SUM(F786:I786,K786:O786)</f>
+        <f t="shared" si="1"/>
         <v>56</v>
       </c>
       <c r="Q786" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="787" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A787" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B787">
         <v>-35.585299999999997</v>
@@ -29995,11 +30000,11 @@
         <v>0</v>
       </c>
       <c r="P787">
-        <f>SUM(F787:I787,K787:O787)</f>
+        <f t="shared" si="1"/>
         <v>56</v>
       </c>
       <c r="Q787" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="788" spans="1:17" x14ac:dyDescent="0.3">
@@ -30028,16 +30033,16 @@
         <v>111</v>
       </c>
       <c r="P788">
-        <f>SUM(F788:I788,K788:O788)</f>
+        <f t="shared" si="1"/>
         <v>111</v>
       </c>
       <c r="Q788" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="789" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A789" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B789">
         <v>-35.500242</v>
@@ -30070,12 +30075,12 @@
         <v>8556</v>
       </c>
       <c r="Q789" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="790" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A790" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="B790">
         <v>-35.499946999999999</v>
@@ -30111,12 +30116,12 @@
         <v>8777</v>
       </c>
       <c r="Q790" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="791" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A791" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="B791">
         <v>-35.793973000000001</v>
@@ -30169,7 +30174,7 @@
     </row>
     <row r="792" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A792" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B792">
         <v>-35.739091000000002</v>
@@ -30222,7 +30227,7 @@
     </row>
     <row r="793" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A793" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B793">
         <v>-35.853555700000001</v>
@@ -30275,7 +30280,7 @@
     </row>
     <row r="794" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A794" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="B794">
         <v>-34.075042000000003</v>
@@ -30305,7 +30310,7 @@
         <v>3140</v>
       </c>
       <c r="Q794" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="795" spans="1:17" x14ac:dyDescent="0.3">
@@ -30380,7 +30385,7 @@
     </row>
     <row r="797" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A797" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B797">
         <v>-35.638145999999999</v>
@@ -30474,7 +30479,7 @@
     </row>
     <row r="799" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A799" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B799">
         <v>-35.149287000000001</v>
@@ -30509,7 +30514,7 @@
     </row>
     <row r="800" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A800" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="B800">
         <v>-36.825802000000003</v>
@@ -30547,7 +30552,7 @@
     </row>
     <row r="801" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A801" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B801">
         <v>-35.878667100000001</v>
@@ -30600,7 +30605,7 @@
     </row>
     <row r="802" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A802" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="B802">
         <v>-35.781129999999997</v>
@@ -30653,7 +30658,7 @@
     </row>
     <row r="803" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A803" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B803">
         <v>-35.054707999999998</v>
@@ -30686,12 +30691,12 @@
         <v>154500</v>
       </c>
       <c r="Q803" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="804" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A804" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B804">
         <v>-35.786641000000003</v>
@@ -30744,7 +30749,7 @@
     </row>
     <row r="805" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A805" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B805">
         <v>-32.915069000000003</v>
@@ -30771,12 +30776,12 @@
         <v>2333</v>
       </c>
       <c r="Q805" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="806" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A806" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="B806">
         <v>-32.913386000000003</v>
@@ -30803,7 +30808,7 @@
         <v>666</v>
       </c>
       <c r="Q806" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="807" spans="1:17" x14ac:dyDescent="0.3">
@@ -30881,7 +30886,7 @@
     </row>
     <row r="809" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A809" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="B809">
         <v>-35.533231000000001</v>
@@ -30922,7 +30927,7 @@
     </row>
     <row r="810" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A810" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B810">
         <v>-35.445188000000002</v>
@@ -30955,12 +30960,12 @@
         <v>56</v>
       </c>
       <c r="Q810" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="811" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A811" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="B811">
         <v>-35.510497000000001</v>
@@ -31005,12 +31010,12 @@
         <v>334</v>
       </c>
       <c r="Q811" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="812" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A812" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="B812">
         <v>-35.500024000000003</v>
@@ -31046,12 +31051,12 @@
         <v>555</v>
       </c>
       <c r="Q812" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="813" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A813" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="B813">
         <v>-35.739091000000002</v>
@@ -31104,7 +31109,7 @@
     </row>
     <row r="814" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A814" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B814">
         <v>-35.853557000000002</v>
@@ -31198,7 +31203,7 @@
     </row>
     <row r="816" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A816" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="B816">
         <v>-35.463515299999997</v>
@@ -31251,7 +31256,7 @@
     </row>
     <row r="817" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A817" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B817">
         <v>-35.605305999999999</v>
@@ -31287,12 +31292,12 @@
         <v>3501</v>
       </c>
       <c r="Q817" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="818" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A818" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B818">
         <v>-34.824044999999998</v>
@@ -31371,7 +31376,7 @@
     </row>
     <row r="820" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A820" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B820">
         <v>-34.875185999999999</v>
@@ -31412,7 +31417,7 @@
     </row>
     <row r="821" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A821" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B821">
         <v>-35.445188000000002</v>
@@ -31445,12 +31450,12 @@
         <v>778</v>
       </c>
       <c r="Q821" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="822" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A822" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B822">
         <v>-35.591330800000001</v>
@@ -31503,7 +31508,7 @@
     </row>
     <row r="823" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A823" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="B823">
         <v>-35.793973000000001</v>
@@ -31556,7 +31561,7 @@
     </row>
     <row r="824" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A824" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B824">
         <v>-35.638117999999999</v>
@@ -31597,7 +31602,7 @@
     </row>
     <row r="825" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A825" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="B825">
         <v>-35.500024000000003</v>
@@ -31636,7 +31641,7 @@
         <v>1334</v>
       </c>
       <c r="Q825" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="826" spans="1:17" x14ac:dyDescent="0.3">
@@ -31679,7 +31684,7 @@
     </row>
     <row r="827" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A827" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="B827">
         <v>-35.510497000000001</v>
@@ -31718,12 +31723,12 @@
         <v>389</v>
       </c>
       <c r="Q827" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="828" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A828" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="B828">
         <v>-34.980508999999998</v>
@@ -31802,7 +31807,7 @@
     </row>
     <row r="830" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A830" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B830">
         <v>-35.445188000000002</v>
@@ -31835,12 +31840,12 @@
         <v>2500</v>
       </c>
       <c r="Q830" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="831" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A831" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B831">
         <v>-35.878133800000001</v>
@@ -32025,7 +32030,7 @@
     </row>
     <row r="835" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A835" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="B835">
         <v>-35.574167000000003</v>
@@ -32107,7 +32112,7 @@
     </row>
     <row r="837" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A837" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B837">
         <v>-35.620086000000001</v>
@@ -32145,7 +32150,7 @@
     </row>
     <row r="838" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A838" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B838">
         <v>-35.591330800000001</v>
@@ -32198,7 +32203,7 @@
     </row>
     <row r="839" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A839" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B839">
         <v>-34.629179999999998</v>
@@ -32225,12 +32230,12 @@
         <v>564</v>
       </c>
       <c r="Q839" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="840" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A840" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B840">
         <v>-35.500242</v>
@@ -32269,7 +32274,7 @@
         <v>2778</v>
       </c>
       <c r="Q840" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="841" spans="1:17" x14ac:dyDescent="0.3">
@@ -32285,6 +32290,9 @@
       <c r="D841" s="2">
         <v>46138</v>
       </c>
+      <c r="J841">
+        <v>0</v>
+      </c>
       <c r="L841">
         <v>167</v>
       </c>
@@ -32317,6 +32325,9 @@
       <c r="G842">
         <v>111</v>
       </c>
+      <c r="J842">
+        <v>0</v>
+      </c>
       <c r="L842">
         <v>56</v>
       </c>
@@ -32335,7 +32346,7 @@
     </row>
     <row r="843" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A843" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B843">
         <v>-35.445188000000002</v>
@@ -32368,12 +32379,12 @@
         <v>667</v>
       </c>
       <c r="Q843" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="844" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A844" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="B844">
         <v>-35.410254000000002</v>
@@ -32412,12 +32423,12 @@
         <v>56</v>
       </c>
       <c r="Q844" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="845" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A845" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B845">
         <v>-34.629179999999998</v>
@@ -32447,12 +32458,12 @@
         <v>426</v>
       </c>
       <c r="Q845" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="846" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A846" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="B846">
         <v>-34.891616999999997</v>
@@ -32482,12 +32493,12 @@
         <v>168</v>
       </c>
       <c r="Q846" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="847" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A847" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B847">
         <v>-34.628860000000003</v>
@@ -32520,7 +32531,7 @@
         <v>287</v>
       </c>
       <c r="Q847" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="848" spans="1:17" x14ac:dyDescent="0.3">
@@ -32542,6 +32553,9 @@
       <c r="I848">
         <v>56</v>
       </c>
+      <c r="J848">
+        <v>0</v>
+      </c>
       <c r="L848">
         <v>278</v>
       </c>
@@ -32560,7 +32574,7 @@
     </row>
     <row r="849" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A849" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="B849">
         <v>-35.510497000000001</v>
@@ -32587,12 +32601,12 @@
         <v>111</v>
       </c>
       <c r="Q849" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="850" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A850" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B850">
         <v>-34.628860000000003</v>
@@ -32628,12 +32642,12 @@
         <v>46</v>
       </c>
       <c r="Q850" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="851" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A851" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B851">
         <v>-35.445188000000002</v>
@@ -32666,7 +32680,7 @@
         <v>1000</v>
       </c>
       <c r="Q851" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="852" spans="1:17" x14ac:dyDescent="0.3">
@@ -32720,6 +32734,9 @@
       <c r="I853">
         <v>56</v>
       </c>
+      <c r="J853">
+        <v>0</v>
+      </c>
       <c r="L853">
         <v>389</v>
       </c>
@@ -32738,7 +32755,7 @@
     </row>
     <row r="854" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A854" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="B854">
         <v>-35.500024000000003</v>
@@ -32783,7 +32800,7 @@
         <v>3223</v>
       </c>
       <c r="Q854" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="855" spans="1:17" x14ac:dyDescent="0.3">
@@ -32811,6 +32828,9 @@
       <c r="I855">
         <v>56</v>
       </c>
+      <c r="J855">
+        <v>0</v>
+      </c>
       <c r="L855">
         <v>0</v>
       </c>
@@ -32829,7 +32849,7 @@
     </row>
     <row r="856" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A856" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="B856">
         <v>-35.410254000000002</v>
@@ -32877,12 +32897,12 @@
         <v>5278</v>
       </c>
       <c r="Q856" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="857" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A857" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B857">
         <v>-34.54036</v>
@@ -32918,7 +32938,7 @@
         <v>29</v>
       </c>
       <c r="Q857" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="858" spans="1:17" x14ac:dyDescent="0.3">
@@ -32943,6 +32963,9 @@
       <c r="I858">
         <v>333</v>
       </c>
+      <c r="J858">
+        <v>0</v>
+      </c>
       <c r="L858">
         <v>56</v>
       </c>
@@ -32978,6 +33001,9 @@
       <c r="I859">
         <v>56</v>
       </c>
+      <c r="J859">
+        <v>0</v>
+      </c>
       <c r="L859">
         <v>167</v>
       </c>
@@ -32996,7 +33022,7 @@
     </row>
     <row r="860" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A860" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B860">
         <v>-34.628860000000003</v>
@@ -33032,12 +33058,12 @@
         <v>83</v>
       </c>
       <c r="Q860" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="861" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A861" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="B861">
         <v>-35.472737000000002</v>
@@ -33085,12 +33111,12 @@
         <v>1278</v>
       </c>
       <c r="Q861" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="862" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A862" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B862">
         <v>-34.628860000000003</v>
@@ -33126,12 +33152,12 @@
         <v>79</v>
       </c>
       <c r="Q862" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="863" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A863" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B863">
         <v>-35.445188000000002</v>
@@ -33179,7 +33205,7 @@
         <v>278</v>
       </c>
       <c r="Q863" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="864" spans="1:17" x14ac:dyDescent="0.3">
@@ -33201,6 +33227,9 @@
       <c r="G864">
         <v>56</v>
       </c>
+      <c r="J864">
+        <v>0</v>
+      </c>
       <c r="N864">
         <v>444</v>
       </c>
@@ -33233,6 +33262,9 @@
       <c r="I865">
         <v>167</v>
       </c>
+      <c r="J865">
+        <v>0</v>
+      </c>
       <c r="L865">
         <v>7000</v>
       </c>
@@ -33271,6 +33303,9 @@
       <c r="G866">
         <v>277</v>
       </c>
+      <c r="J866">
+        <v>0</v>
+      </c>
       <c r="L866">
         <v>0</v>
       </c>
@@ -33289,7 +33324,7 @@
     </row>
     <row r="867" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A867" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B867">
         <v>-34.628860000000003</v>
@@ -33319,7 +33354,7 @@
         <v>50</v>
       </c>
       <c r="Q867" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
   </sheetData>
@@ -33327,6 +33362,11 @@
     <sortCondition ref="D2:D867"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
+  <conditionalFormatting sqref="S229">
+    <cfRule type="containsText" dxfId="0" priority="25" operator="containsText" text="LAMW5607">
+      <formula>NOT(ISERROR(SEARCH("LAMW5607",S229)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>

--- a/MASTER spreadsheet of community summaries.xlsx
+++ b/MASTER spreadsheet of community summaries.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\peri\Dropbox\Delta\Projects\Laboratory\Algal blooms, bacterial counts  for community\For Luke's HAB data display\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24D5B567-794A-4681-93F4-DA73FFBA6FFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{359339F1-45FB-4A86-B74D-28A2EC1DF6ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{9286397E-2757-492B-865A-39B2D6A15FF6}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1751" uniqueCount="431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1775" uniqueCount="435">
   <si>
     <t>Date</t>
   </si>
@@ -1349,6 +1349,18 @@
   </si>
   <si>
     <t>Lady Bay</t>
+  </si>
+  <si>
+    <t>Horseshoe Bay</t>
+  </si>
+  <si>
+    <t>Offshore Waitpinga cliffs</t>
+  </si>
+  <si>
+    <t>Offshore from Wirrina</t>
+  </si>
+  <si>
+    <t>Port  Neill boat ramp</t>
   </si>
 </sst>
 </file>
@@ -1437,7 +1449,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1478,6 +1490,9 @@
     <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1829,7 +1844,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F307807-E5C9-4450-88E0-159CBB3E9A67}">
-  <dimension ref="A1:T867"/>
+  <dimension ref="A1:T879"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="39.33203125" customWidth="1"/>
@@ -21650,10 +21665,10 @@
         <v>312</v>
       </c>
       <c r="B548">
-        <v>-35.445188000000002</v>
+        <v>-35.445059999999998</v>
       </c>
       <c r="C548">
-        <v>138.307266</v>
+        <v>138.30758399999999</v>
       </c>
       <c r="D548" s="2">
         <v>46055</v>
@@ -24299,10 +24314,10 @@
         <v>312</v>
       </c>
       <c r="B633">
-        <v>-35.445188000000002</v>
+        <v>-35.445059999999998</v>
       </c>
       <c r="C633">
-        <v>138.307266</v>
+        <v>138.30758399999999</v>
       </c>
       <c r="D633" s="2">
         <v>46069</v>
@@ -28337,10 +28352,10 @@
         <v>312</v>
       </c>
       <c r="B741">
-        <v>-35.445188000000002</v>
+        <v>-35.445059999999998</v>
       </c>
       <c r="C741">
-        <v>138.307266</v>
+        <v>138.30758399999999</v>
       </c>
       <c r="D741" s="2">
         <v>46097</v>
@@ -29315,10 +29330,10 @@
         <v>312</v>
       </c>
       <c r="B768">
-        <v>-35.445188000000002</v>
+        <v>-35.445059999999998</v>
       </c>
       <c r="C768">
-        <v>138.307266</v>
+        <v>138.30758399999999</v>
       </c>
       <c r="D768" s="2">
         <v>46104</v>
@@ -29382,10 +29397,10 @@
         <v>312</v>
       </c>
       <c r="B770">
-        <v>-35.445186</v>
+        <v>-35.445059999999998</v>
       </c>
       <c r="C770">
-        <v>138.307424</v>
+        <v>138.30758399999999</v>
       </c>
       <c r="D770" s="2">
         <v>46104</v>
@@ -30083,10 +30098,10 @@
         <v>406</v>
       </c>
       <c r="B790">
-        <v>-35.499946999999999</v>
+        <v>-35.500024000000003</v>
       </c>
       <c r="C790">
-        <v>138.242954</v>
+        <v>138.24287699999999</v>
       </c>
       <c r="D790" s="2">
         <v>46109</v>
@@ -30930,10 +30945,10 @@
         <v>312</v>
       </c>
       <c r="B810">
-        <v>-35.445188000000002</v>
+        <v>-35.445059999999998</v>
       </c>
       <c r="C810">
-        <v>138.307266</v>
+        <v>138.30758399999999</v>
       </c>
       <c r="D810" s="2">
         <v>46118</v>
@@ -31420,10 +31435,10 @@
         <v>312</v>
       </c>
       <c r="B821">
-        <v>-35.445188000000002</v>
+        <v>-35.445059999999998</v>
       </c>
       <c r="C821">
-        <v>138.307266</v>
+        <v>138.30758399999999</v>
       </c>
       <c r="D821" s="2">
         <v>46125</v>
@@ -31810,10 +31825,10 @@
         <v>312</v>
       </c>
       <c r="B830">
-        <v>-35.445188000000002</v>
+        <v>-35.445059999999998</v>
       </c>
       <c r="C830">
-        <v>138.307266</v>
+        <v>138.30758399999999</v>
       </c>
       <c r="D830" s="2">
         <v>46132</v>
@@ -32349,10 +32364,10 @@
         <v>312</v>
       </c>
       <c r="B843">
-        <v>-35.445188000000002</v>
+        <v>-35.445059999999998</v>
       </c>
       <c r="C843">
-        <v>138.307266</v>
+        <v>138.30758399999999</v>
       </c>
       <c r="D843" s="2">
         <v>46139</v>
@@ -32650,10 +32665,10 @@
         <v>312</v>
       </c>
       <c r="B851">
-        <v>-35.445188000000002</v>
+        <v>-35.445059999999998</v>
       </c>
       <c r="C851">
-        <v>138.307266</v>
+        <v>138.30758399999999</v>
       </c>
       <c r="D851" s="2">
         <v>46147</v>
@@ -33160,10 +33175,10 @@
         <v>312</v>
       </c>
       <c r="B863">
-        <v>-35.445188000000002</v>
+        <v>-35.445059999999998</v>
       </c>
       <c r="C863">
-        <v>138.307266</v>
+        <v>138.30758399999999</v>
       </c>
       <c r="D863" s="2">
         <v>46153</v>
@@ -33354,6 +33369,546 @@
         <v>50</v>
       </c>
       <c r="Q867" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="868" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A868" t="s">
+        <v>431</v>
+      </c>
+      <c r="B868">
+        <v>-35.534041000000002</v>
+      </c>
+      <c r="C868">
+        <v>138.688445</v>
+      </c>
+      <c r="D868" s="2">
+        <v>46154</v>
+      </c>
+      <c r="E868" s="20">
+        <v>0.37152777777777779</v>
+      </c>
+      <c r="H868">
+        <v>111</v>
+      </c>
+      <c r="I868">
+        <v>2722</v>
+      </c>
+      <c r="J868">
+        <v>0</v>
+      </c>
+      <c r="N868">
+        <v>222</v>
+      </c>
+      <c r="O868">
+        <v>833</v>
+      </c>
+      <c r="P868">
+        <v>3888</v>
+      </c>
+      <c r="Q868" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="869" spans="1:17" s="24" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A869" s="24" t="s">
+        <v>87</v>
+      </c>
+      <c r="B869" s="24">
+        <v>-35.573300000000003</v>
+      </c>
+      <c r="C869" s="24">
+        <v>138.64250000000001</v>
+      </c>
+      <c r="D869" s="25">
+        <v>46154</v>
+      </c>
+      <c r="E869" s="26">
+        <v>0.38541666666666669</v>
+      </c>
+      <c r="G869" s="24">
+        <v>57</v>
+      </c>
+      <c r="H869" s="24">
+        <v>111</v>
+      </c>
+      <c r="I869" s="24">
+        <v>111</v>
+      </c>
+      <c r="J869" s="24">
+        <v>0</v>
+      </c>
+      <c r="K869" s="24">
+        <v>56</v>
+      </c>
+      <c r="L869" s="24">
+        <v>2112</v>
+      </c>
+      <c r="N869" s="24">
+        <v>389</v>
+      </c>
+      <c r="O869" s="24">
+        <v>833</v>
+      </c>
+      <c r="P869" s="24">
+        <v>3669</v>
+      </c>
+      <c r="Q869" s="24" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="870" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A870" t="s">
+        <v>88</v>
+      </c>
+      <c r="B870">
+        <v>-35.581124000000003</v>
+      </c>
+      <c r="C870">
+        <v>138.60879700000001</v>
+      </c>
+      <c r="D870" s="2">
+        <v>46154</v>
+      </c>
+      <c r="E870" s="20">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="G870">
+        <v>56</v>
+      </c>
+      <c r="H870">
+        <v>167</v>
+      </c>
+      <c r="J870">
+        <v>0</v>
+      </c>
+      <c r="K870">
+        <v>56</v>
+      </c>
+      <c r="N870">
+        <v>444</v>
+      </c>
+      <c r="O870">
+        <v>167</v>
+      </c>
+      <c r="P870">
+        <v>890</v>
+      </c>
+      <c r="Q870" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="871" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A871" t="s">
+        <v>89</v>
+      </c>
+      <c r="B871">
+        <v>-35.6048446</v>
+      </c>
+      <c r="C871">
+        <v>138.59278499999999</v>
+      </c>
+      <c r="D871" s="2">
+        <v>46154</v>
+      </c>
+      <c r="E871" s="20">
+        <v>0.40625</v>
+      </c>
+      <c r="G871">
+        <v>56</v>
+      </c>
+      <c r="I871">
+        <v>111</v>
+      </c>
+      <c r="J871">
+        <v>0</v>
+      </c>
+      <c r="K871">
+        <v>56</v>
+      </c>
+      <c r="L871">
+        <v>56</v>
+      </c>
+      <c r="N871">
+        <v>222</v>
+      </c>
+      <c r="O871">
+        <v>278</v>
+      </c>
+      <c r="P871">
+        <v>779</v>
+      </c>
+      <c r="Q871" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="872" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A872" t="s">
+        <v>375</v>
+      </c>
+      <c r="B872">
+        <v>-35.612285999999997</v>
+      </c>
+      <c r="C872">
+        <v>138.564302</v>
+      </c>
+      <c r="D872" s="2">
+        <v>46154</v>
+      </c>
+      <c r="E872" s="20">
+        <v>0.4152777777777778</v>
+      </c>
+      <c r="H872">
+        <v>167</v>
+      </c>
+      <c r="I872">
+        <v>500</v>
+      </c>
+      <c r="J872">
+        <v>0</v>
+      </c>
+      <c r="K872">
+        <v>56</v>
+      </c>
+      <c r="L872">
+        <v>56</v>
+      </c>
+      <c r="N872">
+        <v>778</v>
+      </c>
+      <c r="O872">
+        <v>1111</v>
+      </c>
+      <c r="P872">
+        <v>2668</v>
+      </c>
+      <c r="Q872" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="873" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A873" t="s">
+        <v>432</v>
+      </c>
+      <c r="B873">
+        <v>-35.619</v>
+      </c>
+      <c r="C873">
+        <v>138.58099999999999</v>
+      </c>
+      <c r="D873" s="2">
+        <v>46154</v>
+      </c>
+      <c r="E873" s="20">
+        <v>0.4201388888888889</v>
+      </c>
+      <c r="H873">
+        <v>56</v>
+      </c>
+      <c r="I873">
+        <v>111</v>
+      </c>
+      <c r="J873">
+        <v>0</v>
+      </c>
+      <c r="N873">
+        <v>611</v>
+      </c>
+      <c r="O873">
+        <v>333</v>
+      </c>
+      <c r="P873">
+        <v>1111</v>
+      </c>
+      <c r="Q873" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="874" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A874" t="s">
+        <v>422</v>
+      </c>
+      <c r="B874">
+        <v>-35.500024000000003</v>
+      </c>
+      <c r="C874">
+        <v>138.24287699999999</v>
+      </c>
+      <c r="D874" s="2">
+        <v>46154</v>
+      </c>
+      <c r="E874" s="20">
+        <v>0.67013888888888884</v>
+      </c>
+      <c r="F874">
+        <v>0</v>
+      </c>
+      <c r="G874">
+        <v>0</v>
+      </c>
+      <c r="H874">
+        <v>7222</v>
+      </c>
+      <c r="I874">
+        <v>889</v>
+      </c>
+      <c r="J874">
+        <v>0</v>
+      </c>
+      <c r="K874">
+        <v>0</v>
+      </c>
+      <c r="L874">
+        <v>167</v>
+      </c>
+      <c r="M874">
+        <v>0</v>
+      </c>
+      <c r="N874">
+        <v>2500</v>
+      </c>
+      <c r="O874">
+        <v>278</v>
+      </c>
+      <c r="P874">
+        <v>11056</v>
+      </c>
+      <c r="Q874" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="875" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A875" t="s">
+        <v>433</v>
+      </c>
+      <c r="B875">
+        <v>-35.297930000000001</v>
+      </c>
+      <c r="C875">
+        <v>138.14122</v>
+      </c>
+      <c r="D875" s="2">
+        <v>46159</v>
+      </c>
+      <c r="E875" s="20">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="F875">
+        <v>0</v>
+      </c>
+      <c r="G875">
+        <v>0</v>
+      </c>
+      <c r="H875">
+        <v>0</v>
+      </c>
+      <c r="I875">
+        <v>56</v>
+      </c>
+      <c r="J875">
+        <v>0</v>
+      </c>
+      <c r="K875">
+        <v>0</v>
+      </c>
+      <c r="L875">
+        <v>111</v>
+      </c>
+      <c r="M875">
+        <v>0</v>
+      </c>
+      <c r="N875">
+        <v>111</v>
+      </c>
+      <c r="O875">
+        <v>56</v>
+      </c>
+      <c r="P875">
+        <v>334</v>
+      </c>
+      <c r="Q875" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="876" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A876" t="s">
+        <v>312</v>
+      </c>
+      <c r="B876">
+        <v>-35.445059999999998</v>
+      </c>
+      <c r="C876">
+        <v>138.30758399999999</v>
+      </c>
+      <c r="D876" s="2">
+        <v>46160</v>
+      </c>
+      <c r="E876" s="20">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="F876">
+        <v>0</v>
+      </c>
+      <c r="G876">
+        <v>0</v>
+      </c>
+      <c r="H876">
+        <v>0</v>
+      </c>
+      <c r="I876">
+        <v>56</v>
+      </c>
+      <c r="J876">
+        <v>0</v>
+      </c>
+      <c r="K876">
+        <v>0</v>
+      </c>
+      <c r="L876">
+        <v>389</v>
+      </c>
+      <c r="M876">
+        <v>0</v>
+      </c>
+      <c r="N876">
+        <v>0</v>
+      </c>
+      <c r="O876">
+        <v>56</v>
+      </c>
+      <c r="P876">
+        <v>501</v>
+      </c>
+      <c r="Q876" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="877" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A877" t="s">
+        <v>427</v>
+      </c>
+      <c r="B877">
+        <v>-35.410254000000002</v>
+      </c>
+      <c r="C877">
+        <v>138.32751999999999</v>
+      </c>
+      <c r="D877" s="2">
+        <v>46160</v>
+      </c>
+      <c r="E877" s="20">
+        <v>0.46875</v>
+      </c>
+      <c r="F877">
+        <v>0</v>
+      </c>
+      <c r="G877">
+        <v>0</v>
+      </c>
+      <c r="H877">
+        <v>56</v>
+      </c>
+      <c r="I877">
+        <v>56</v>
+      </c>
+      <c r="J877">
+        <v>0</v>
+      </c>
+      <c r="K877">
+        <v>0</v>
+      </c>
+      <c r="L877">
+        <v>0</v>
+      </c>
+      <c r="M877">
+        <v>0</v>
+      </c>
+      <c r="N877">
+        <v>56</v>
+      </c>
+      <c r="O877">
+        <v>0</v>
+      </c>
+      <c r="P877">
+        <v>168</v>
+      </c>
+      <c r="Q877" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="878" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A878" t="s">
+        <v>59</v>
+      </c>
+      <c r="B878">
+        <v>-35.084850000000003</v>
+      </c>
+      <c r="C878">
+        <v>137.74889999999999</v>
+      </c>
+      <c r="D878" s="2">
+        <v>46162</v>
+      </c>
+      <c r="E878" s="20">
+        <v>0.5</v>
+      </c>
+      <c r="H878">
+        <v>56</v>
+      </c>
+      <c r="I878">
+        <v>56</v>
+      </c>
+      <c r="J878">
+        <v>0</v>
+      </c>
+      <c r="L878">
+        <v>0</v>
+      </c>
+      <c r="M878">
+        <v>0</v>
+      </c>
+      <c r="N878">
+        <v>722</v>
+      </c>
+      <c r="P878">
+        <v>834</v>
+      </c>
+      <c r="Q878" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="879" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A879" t="s">
+        <v>434</v>
+      </c>
+      <c r="B879">
+        <v>-34.116680000000002</v>
+      </c>
+      <c r="C879">
+        <v>136.35397</v>
+      </c>
+      <c r="D879" s="2">
+        <v>46162</v>
+      </c>
+      <c r="E879" s="20">
+        <v>0.51041666666666663</v>
+      </c>
+      <c r="I879">
+        <v>4</v>
+      </c>
+      <c r="J879">
+        <v>1</v>
+      </c>
+      <c r="L879">
+        <v>2</v>
+      </c>
+      <c r="O879">
+        <v>3</v>
+      </c>
+      <c r="P879">
+        <v>9</v>
+      </c>
+      <c r="Q879" t="s">
         <v>283</v>
       </c>
     </row>

--- a/MASTER spreadsheet of community summaries.xlsx
+++ b/MASTER spreadsheet of community summaries.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\peri\Dropbox\Delta\Projects\Laboratory\Algal blooms, bacterial counts  for community\For Luke's HAB data display\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{359339F1-45FB-4A86-B74D-28A2EC1DF6ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{535348DC-5802-48F8-9D1C-419AD87563FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{9286397E-2757-492B-865A-39B2D6A15FF6}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1775" uniqueCount="435">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1787" uniqueCount="438">
   <si>
     <t>Date</t>
   </si>
@@ -1361,6 +1361,15 @@
   </si>
   <si>
     <t>Port  Neill boat ramp</t>
+  </si>
+  <si>
+    <t>Louth Bay Jetty</t>
+  </si>
+  <si>
+    <t>Tumby Bay</t>
+  </si>
+  <si>
+    <t>Rapid Head New Jetty</t>
   </si>
 </sst>
 </file>
@@ -1449,7 +1458,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1490,9 +1499,6 @@
     <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1844,7 +1850,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F307807-E5C9-4450-88E0-159CBB3E9A67}">
-  <dimension ref="A1:T879"/>
+  <dimension ref="A1:T885"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="39.33203125" customWidth="1"/>
@@ -25394,7 +25400,7 @@
         <v>56</v>
       </c>
       <c r="P660" s="17">
-        <f t="shared" ref="P660:P666" si="0">SUM(F660:I660,K660:O660)</f>
+        <f>SUM(F660:I660,K660:O660)</f>
         <v>1111</v>
       </c>
       <c r="Q660" t="s">
@@ -25427,7 +25433,7 @@
         <v>111</v>
       </c>
       <c r="P661">
-        <f t="shared" si="0"/>
+        <f>SUM(F661:I661,K661:O661)</f>
         <v>444</v>
       </c>
       <c r="Q661" t="s">
@@ -25460,7 +25466,7 @@
         <v>0</v>
       </c>
       <c r="P662">
-        <f t="shared" si="0"/>
+        <f>SUM(F662:I662,K662:O662)</f>
         <v>56</v>
       </c>
       <c r="Q662" t="s">
@@ -25493,7 +25499,7 @@
         <v>167</v>
       </c>
       <c r="P663">
-        <f t="shared" si="0"/>
+        <f>SUM(F663:I663,K663:O663)</f>
         <v>167</v>
       </c>
       <c r="Q663" t="s">
@@ -25526,7 +25532,7 @@
         <v>56</v>
       </c>
       <c r="P664">
-        <f t="shared" si="0"/>
+        <f>SUM(F664:I664,K664:O664)</f>
         <v>112</v>
       </c>
       <c r="Q664" t="s">
@@ -25559,7 +25565,7 @@
         <v>0</v>
       </c>
       <c r="P665">
-        <f t="shared" si="0"/>
+        <f>SUM(F665:I665,K665:O665)</f>
         <v>0</v>
       </c>
       <c r="Q665" t="s">
@@ -25592,7 +25598,7 @@
         <v>222</v>
       </c>
       <c r="P666">
-        <f t="shared" si="0"/>
+        <f>SUM(F666:I666,K666:O666)</f>
         <v>278</v>
       </c>
       <c r="Q666" t="s">
@@ -29685,7 +29691,7 @@
       <c r="N777" s="1"/>
       <c r="O777" s="1"/>
       <c r="P777">
-        <f t="shared" ref="P777:P788" si="1">SUM(F777:I777,K777:O777)</f>
+        <f>SUM(F777:I777,K777:O777)</f>
         <v>722</v>
       </c>
       <c r="Q777" t="s">
@@ -29718,7 +29724,7 @@
         <v>111</v>
       </c>
       <c r="P778">
-        <f t="shared" si="1"/>
+        <f>SUM(F778:I778,K778:O778)</f>
         <v>167</v>
       </c>
       <c r="Q778" t="s">
@@ -29751,7 +29757,7 @@
         <v>56</v>
       </c>
       <c r="P779">
-        <f t="shared" si="1"/>
+        <f>SUM(F779:I779,K779:O779)</f>
         <v>278</v>
       </c>
       <c r="Q779" t="s">
@@ -29784,7 +29790,7 @@
         <v>56</v>
       </c>
       <c r="P780">
-        <f t="shared" si="1"/>
+        <f>SUM(F780:I780,K780:O780)</f>
         <v>112</v>
       </c>
       <c r="Q780" t="s">
@@ -29817,7 +29823,7 @@
         <v>0</v>
       </c>
       <c r="P781">
-        <f t="shared" si="1"/>
+        <f>SUM(F781:I781,K781:O781)</f>
         <v>0</v>
       </c>
       <c r="Q781" t="s">
@@ -29850,7 +29856,7 @@
         <v>56</v>
       </c>
       <c r="P782">
-        <f t="shared" si="1"/>
+        <f>SUM(F782:I782,K782:O782)</f>
         <v>278</v>
       </c>
       <c r="Q782" t="s">
@@ -29883,7 +29889,7 @@
         <v>167</v>
       </c>
       <c r="P783">
-        <f t="shared" si="1"/>
+        <f>SUM(F783:I783,K783:O783)</f>
         <v>445</v>
       </c>
       <c r="Q783" t="s">
@@ -29916,7 +29922,7 @@
         <v>0</v>
       </c>
       <c r="P784">
-        <f t="shared" si="1"/>
+        <f>SUM(F784:I784,K784:O784)</f>
         <v>56</v>
       </c>
       <c r="Q784" t="s">
@@ -29949,7 +29955,7 @@
         <v>56</v>
       </c>
       <c r="P785">
-        <f t="shared" si="1"/>
+        <f>SUM(F785:I785,K785:O785)</f>
         <v>56</v>
       </c>
       <c r="Q785" t="s">
@@ -29982,7 +29988,7 @@
         <v>56</v>
       </c>
       <c r="P786">
-        <f t="shared" si="1"/>
+        <f>SUM(F786:I786,K786:O786)</f>
         <v>56</v>
       </c>
       <c r="Q786" t="s">
@@ -30015,7 +30021,7 @@
         <v>0</v>
       </c>
       <c r="P787">
-        <f t="shared" si="1"/>
+        <f>SUM(F787:I787,K787:O787)</f>
         <v>56</v>
       </c>
       <c r="Q787" t="s">
@@ -30048,7 +30054,7 @@
         <v>111</v>
       </c>
       <c r="P788">
-        <f t="shared" si="1"/>
+        <f>SUM(F788:I788,K788:O788)</f>
         <v>111</v>
       </c>
       <c r="Q788" t="s">
@@ -33301,198 +33307,213 @@
     </row>
     <row r="866" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A866" t="s">
-        <v>59</v>
+        <v>431</v>
       </c>
       <c r="B866">
-        <v>-35.084850000000003</v>
+        <v>-35.534041000000002</v>
       </c>
       <c r="C866">
-        <v>137.74889999999999</v>
+        <v>138.688445</v>
       </c>
       <c r="D866" s="2">
-        <v>46155</v>
+        <v>46154</v>
       </c>
       <c r="E866" s="20">
-        <v>0.70833333333333337</v>
-      </c>
-      <c r="G866">
-        <v>277</v>
+        <v>0.37152777777777779</v>
+      </c>
+      <c r="H866">
+        <v>111</v>
+      </c>
+      <c r="I866">
+        <v>2722</v>
       </c>
       <c r="J866">
         <v>0</v>
       </c>
-      <c r="L866">
-        <v>0</v>
-      </c>
-      <c r="M866">
-        <v>0</v>
-      </c>
       <c r="N866">
-        <v>333</v>
+        <v>222</v>
+      </c>
+      <c r="O866">
+        <v>833</v>
       </c>
       <c r="P866">
-        <v>610</v>
+        <v>3888</v>
       </c>
       <c r="Q866" t="s">
-        <v>149</v>
+        <v>129</v>
       </c>
     </row>
     <row r="867" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A867" t="s">
-        <v>289</v>
+        <v>87</v>
       </c>
       <c r="B867">
-        <v>-34.628860000000003</v>
+        <v>-35.573300000000003</v>
       </c>
       <c r="C867">
-        <v>135.86708999999999</v>
+        <v>138.64250000000001</v>
       </c>
       <c r="D867" s="2">
-        <v>46155</v>
+        <v>46154</v>
       </c>
       <c r="E867" s="20">
-        <v>0.33333333333333331</v>
+        <v>0.38541666666666669</v>
+      </c>
+      <c r="G867">
+        <v>56</v>
+      </c>
+      <c r="H867">
+        <v>111</v>
       </c>
       <c r="I867">
-        <v>17</v>
+        <v>111</v>
       </c>
       <c r="J867">
         <v>0</v>
       </c>
+      <c r="K867">
+        <v>56</v>
+      </c>
       <c r="L867">
-        <v>33</v>
+        <v>2112</v>
+      </c>
+      <c r="N867">
+        <v>389</v>
       </c>
       <c r="O867">
-        <v>0</v>
+        <v>833</v>
       </c>
       <c r="P867">
-        <v>50</v>
+        <v>3668</v>
       </c>
       <c r="Q867" t="s">
-        <v>283</v>
+        <v>129</v>
       </c>
     </row>
     <row r="868" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A868" t="s">
-        <v>431</v>
+        <v>88</v>
       </c>
       <c r="B868">
-        <v>-35.534041000000002</v>
+        <v>-35.581124000000003</v>
       </c>
       <c r="C868">
-        <v>138.688445</v>
+        <v>138.60879700000001</v>
       </c>
       <c r="D868" s="2">
         <v>46154</v>
       </c>
       <c r="E868" s="20">
-        <v>0.37152777777777779</v>
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="G868">
+        <v>56</v>
       </c>
       <c r="H868">
-        <v>111</v>
-      </c>
-      <c r="I868">
-        <v>2722</v>
+        <v>167</v>
       </c>
       <c r="J868">
         <v>0</v>
       </c>
+      <c r="K868">
+        <v>56</v>
+      </c>
       <c r="N868">
-        <v>222</v>
+        <v>444</v>
       </c>
       <c r="O868">
-        <v>833</v>
+        <v>167</v>
       </c>
       <c r="P868">
-        <v>3888</v>
+        <v>890</v>
       </c>
       <c r="Q868" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="869" spans="1:17" s="24" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A869" s="24" t="s">
-        <v>87</v>
-      </c>
-      <c r="B869" s="24">
-        <v>-35.573300000000003</v>
-      </c>
-      <c r="C869" s="24">
-        <v>138.64250000000001</v>
-      </c>
-      <c r="D869" s="25">
+    <row r="869" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A869" t="s">
+        <v>89</v>
+      </c>
+      <c r="B869">
+        <v>-35.6048446</v>
+      </c>
+      <c r="C869">
+        <v>138.59278499999999</v>
+      </c>
+      <c r="D869" s="2">
         <v>46154</v>
       </c>
-      <c r="E869" s="26">
-        <v>0.38541666666666669</v>
-      </c>
-      <c r="G869" s="24">
-        <v>57</v>
-      </c>
-      <c r="H869" s="24">
+      <c r="E869" s="20">
+        <v>0.40625</v>
+      </c>
+      <c r="G869">
+        <v>56</v>
+      </c>
+      <c r="I869">
         <v>111</v>
       </c>
-      <c r="I869" s="24">
-        <v>111</v>
-      </c>
-      <c r="J869" s="24">
-        <v>0</v>
-      </c>
-      <c r="K869" s="24">
-        <v>56</v>
-      </c>
-      <c r="L869" s="24">
-        <v>2112</v>
-      </c>
-      <c r="N869" s="24">
-        <v>389</v>
-      </c>
-      <c r="O869" s="24">
-        <v>833</v>
-      </c>
-      <c r="P869" s="24">
-        <v>3669</v>
-      </c>
-      <c r="Q869" s="24" t="s">
+      <c r="J869">
+        <v>0</v>
+      </c>
+      <c r="K869">
+        <v>56</v>
+      </c>
+      <c r="L869">
+        <v>56</v>
+      </c>
+      <c r="N869">
+        <v>222</v>
+      </c>
+      <c r="O869">
+        <v>278</v>
+      </c>
+      <c r="P869">
+        <v>779</v>
+      </c>
+      <c r="Q869" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="870" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A870" t="s">
-        <v>88</v>
+        <v>375</v>
       </c>
       <c r="B870">
-        <v>-35.581124000000003</v>
+        <v>-35.612285999999997</v>
       </c>
       <c r="C870">
-        <v>138.60879700000001</v>
+        <v>138.564302</v>
       </c>
       <c r="D870" s="2">
         <v>46154</v>
       </c>
       <c r="E870" s="20">
-        <v>0.39583333333333331</v>
-      </c>
-      <c r="G870">
-        <v>56</v>
+        <v>0.4152777777777778</v>
       </c>
       <c r="H870">
         <v>167</v>
       </c>
+      <c r="I870">
+        <v>500</v>
+      </c>
       <c r="J870">
         <v>0</v>
       </c>
       <c r="K870">
         <v>56</v>
       </c>
+      <c r="L870">
+        <v>56</v>
+      </c>
       <c r="N870">
-        <v>444</v>
+        <v>778</v>
       </c>
       <c r="O870">
-        <v>167</v>
+        <v>1111</v>
       </c>
       <c r="P870">
-        <v>890</v>
+        <v>2668</v>
       </c>
       <c r="Q870" t="s">
         <v>129</v>
@@ -33500,21 +33521,21 @@
     </row>
     <row r="871" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A871" t="s">
-        <v>89</v>
+        <v>432</v>
       </c>
       <c r="B871">
-        <v>-35.6048446</v>
+        <v>-35.619</v>
       </c>
       <c r="C871">
-        <v>138.59278499999999</v>
+        <v>138.58099999999999</v>
       </c>
       <c r="D871" s="2">
         <v>46154</v>
       </c>
       <c r="E871" s="20">
-        <v>0.40625</v>
-      </c>
-      <c r="G871">
+        <v>0.4201388888888889</v>
+      </c>
+      <c r="H871">
         <v>56</v>
       </c>
       <c r="I871">
@@ -33523,20 +33544,14 @@
       <c r="J871">
         <v>0</v>
       </c>
-      <c r="K871">
-        <v>56</v>
-      </c>
-      <c r="L871">
-        <v>56</v>
-      </c>
       <c r="N871">
-        <v>222</v>
+        <v>611</v>
       </c>
       <c r="O871">
-        <v>278</v>
+        <v>333</v>
       </c>
       <c r="P871">
-        <v>779</v>
+        <v>1111</v>
       </c>
       <c r="Q871" t="s">
         <v>129</v>
@@ -33544,137 +33559,128 @@
     </row>
     <row r="872" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A872" t="s">
-        <v>375</v>
+        <v>422</v>
       </c>
       <c r="B872">
-        <v>-35.612285999999997</v>
+        <v>-35.500024000000003</v>
       </c>
       <c r="C872">
-        <v>138.564302</v>
+        <v>138.24287699999999</v>
       </c>
       <c r="D872" s="2">
         <v>46154</v>
       </c>
       <c r="E872" s="20">
-        <v>0.4152777777777778</v>
+        <v>0.67013888888888884</v>
+      </c>
+      <c r="F872">
+        <v>0</v>
+      </c>
+      <c r="G872">
+        <v>0</v>
       </c>
       <c r="H872">
+        <v>7222</v>
+      </c>
+      <c r="I872">
+        <v>889</v>
+      </c>
+      <c r="J872">
+        <v>0</v>
+      </c>
+      <c r="K872">
+        <v>0</v>
+      </c>
+      <c r="L872">
         <v>167</v>
       </c>
-      <c r="I872">
-        <v>500</v>
-      </c>
-      <c r="J872">
-        <v>0</v>
-      </c>
-      <c r="K872">
-        <v>56</v>
-      </c>
-      <c r="L872">
-        <v>56</v>
+      <c r="M872">
+        <v>0</v>
       </c>
       <c r="N872">
-        <v>778</v>
+        <v>2500</v>
       </c>
       <c r="O872">
-        <v>1111</v>
+        <v>278</v>
       </c>
       <c r="P872">
-        <v>2668</v>
+        <v>11056</v>
       </c>
       <c r="Q872" t="s">
-        <v>129</v>
+        <v>251</v>
       </c>
     </row>
     <row r="873" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A873" t="s">
-        <v>432</v>
+        <v>59</v>
       </c>
       <c r="B873">
-        <v>-35.619</v>
+        <v>-35.084850000000003</v>
       </c>
       <c r="C873">
-        <v>138.58099999999999</v>
+        <v>137.74889999999999</v>
       </c>
       <c r="D873" s="2">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="E873" s="20">
-        <v>0.4201388888888889</v>
-      </c>
-      <c r="H873">
-        <v>56</v>
-      </c>
-      <c r="I873">
-        <v>111</v>
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="G873">
+        <v>277</v>
       </c>
       <c r="J873">
         <v>0</v>
       </c>
+      <c r="L873">
+        <v>0</v>
+      </c>
+      <c r="M873">
+        <v>0</v>
+      </c>
       <c r="N873">
-        <v>611</v>
-      </c>
-      <c r="O873">
         <v>333</v>
       </c>
       <c r="P873">
-        <v>1111</v>
+        <v>610</v>
       </c>
       <c r="Q873" t="s">
-        <v>129</v>
+        <v>149</v>
       </c>
     </row>
     <row r="874" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A874" t="s">
-        <v>422</v>
+        <v>289</v>
       </c>
       <c r="B874">
-        <v>-35.500024000000003</v>
+        <v>-34.628860000000003</v>
       </c>
       <c r="C874">
-        <v>138.24287699999999</v>
+        <v>135.86708999999999</v>
       </c>
       <c r="D874" s="2">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="E874" s="20">
-        <v>0.67013888888888884</v>
-      </c>
-      <c r="F874">
-        <v>0</v>
-      </c>
-      <c r="G874">
-        <v>0</v>
-      </c>
-      <c r="H874">
-        <v>7222</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="I874">
-        <v>889</v>
+        <v>17</v>
       </c>
       <c r="J874">
         <v>0</v>
       </c>
-      <c r="K874">
-        <v>0</v>
-      </c>
       <c r="L874">
-        <v>167</v>
-      </c>
-      <c r="M874">
-        <v>0</v>
-      </c>
-      <c r="N874">
-        <v>2500</v>
+        <v>33</v>
       </c>
       <c r="O874">
-        <v>278</v>
+        <v>0</v>
       </c>
       <c r="P874">
-        <v>11056</v>
+        <v>50</v>
       </c>
       <c r="Q874" t="s">
-        <v>251</v>
+        <v>283</v>
       </c>
     </row>
     <row r="875" spans="1:17" x14ac:dyDescent="0.3">
@@ -33912,9 +33918,258 @@
         <v>283</v>
       </c>
     </row>
+    <row r="880" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A880" t="s">
+        <v>289</v>
+      </c>
+      <c r="B880">
+        <v>-34.628860000000003</v>
+      </c>
+      <c r="C880">
+        <v>135.86708999999999</v>
+      </c>
+      <c r="D880" s="2">
+        <v>46163</v>
+      </c>
+      <c r="E880" s="20">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="I880">
+        <v>74</v>
+      </c>
+      <c r="J880">
+        <v>13</v>
+      </c>
+      <c r="L880">
+        <v>13</v>
+      </c>
+      <c r="M880">
+        <v>0</v>
+      </c>
+      <c r="N880">
+        <v>0</v>
+      </c>
+      <c r="O880">
+        <v>4</v>
+      </c>
+      <c r="P880">
+        <v>91</v>
+      </c>
+      <c r="Q880" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="881" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A881" t="s">
+        <v>435</v>
+      </c>
+      <c r="B881">
+        <v>-34.540179999999999</v>
+      </c>
+      <c r="C881">
+        <v>135.93411</v>
+      </c>
+      <c r="D881" s="2">
+        <v>46165</v>
+      </c>
+      <c r="E881" s="20">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="I881">
+        <v>38</v>
+      </c>
+      <c r="J881">
+        <v>19</v>
+      </c>
+      <c r="L881">
+        <v>73</v>
+      </c>
+      <c r="P881">
+        <v>111</v>
+      </c>
+      <c r="Q881" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="882" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A882" t="s">
+        <v>289</v>
+      </c>
+      <c r="B882">
+        <v>-34.628860000000003</v>
+      </c>
+      <c r="C882">
+        <v>135.86708999999999</v>
+      </c>
+      <c r="D882" s="2">
+        <v>46166</v>
+      </c>
+      <c r="E882" s="20">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="I882">
+        <v>16</v>
+      </c>
+      <c r="J882">
+        <v>9</v>
+      </c>
+      <c r="L882">
+        <v>22</v>
+      </c>
+      <c r="O882">
+        <v>6</v>
+      </c>
+      <c r="P882">
+        <v>44</v>
+      </c>
+      <c r="Q882" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="883" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A883" t="s">
+        <v>437</v>
+      </c>
+      <c r="B883">
+        <v>-35.521467000000001</v>
+      </c>
+      <c r="C883">
+        <v>138.18532999999999</v>
+      </c>
+      <c r="D883" s="2">
+        <v>46166</v>
+      </c>
+      <c r="E883" s="20">
+        <v>0.4375</v>
+      </c>
+      <c r="F883">
+        <v>0</v>
+      </c>
+      <c r="G883">
+        <v>0</v>
+      </c>
+      <c r="H883">
+        <v>56</v>
+      </c>
+      <c r="I883">
+        <v>111</v>
+      </c>
+      <c r="J883">
+        <v>0</v>
+      </c>
+      <c r="K883">
+        <v>0</v>
+      </c>
+      <c r="L883">
+        <v>56</v>
+      </c>
+      <c r="M883">
+        <v>0</v>
+      </c>
+      <c r="N883">
+        <v>444</v>
+      </c>
+      <c r="O883">
+        <v>167</v>
+      </c>
+      <c r="P883">
+        <v>834</v>
+      </c>
+      <c r="Q883" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="884" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A884" t="s">
+        <v>312</v>
+      </c>
+      <c r="B884">
+        <v>-35.445059999999998</v>
+      </c>
+      <c r="C884">
+        <v>138.30758399999999</v>
+      </c>
+      <c r="D884" s="2">
+        <v>46167</v>
+      </c>
+      <c r="E884" s="20">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="F884">
+        <v>0</v>
+      </c>
+      <c r="G884">
+        <v>0</v>
+      </c>
+      <c r="H884">
+        <v>0</v>
+      </c>
+      <c r="I884">
+        <v>56</v>
+      </c>
+      <c r="J884">
+        <v>0</v>
+      </c>
+      <c r="K884">
+        <v>0</v>
+      </c>
+      <c r="L884">
+        <v>56</v>
+      </c>
+      <c r="M884">
+        <v>0</v>
+      </c>
+      <c r="N884">
+        <v>56</v>
+      </c>
+      <c r="O884">
+        <v>56</v>
+      </c>
+      <c r="P884">
+        <v>224</v>
+      </c>
+      <c r="Q884" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="885" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A885" t="s">
+        <v>436</v>
+      </c>
+      <c r="B885">
+        <v>-34.377519999999997</v>
+      </c>
+      <c r="C885">
+        <v>136.10475</v>
+      </c>
+      <c r="D885" s="2">
+        <v>46168</v>
+      </c>
+      <c r="E885" s="20">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="I885">
+        <v>20</v>
+      </c>
+      <c r="J885">
+        <v>3</v>
+      </c>
+      <c r="L885">
+        <v>2</v>
+      </c>
+      <c r="O885">
+        <v>4</v>
+      </c>
+      <c r="P885">
+        <v>26</v>
+      </c>
+      <c r="Q885" t="s">
+        <v>283</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q867">
-    <sortCondition ref="D2:D867"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q885">
+    <sortCondition ref="D2:D885"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="S229">

--- a/MASTER spreadsheet of community summaries.xlsx
+++ b/MASTER spreadsheet of community summaries.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\peri\Dropbox\Delta\Projects\Laboratory\Algal blooms, bacterial counts  for community\For Luke's HAB data display\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{535348DC-5802-48F8-9D1C-419AD87563FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34B04459-DC8C-4C8D-A8E8-DCA2CAD65BA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{9286397E-2757-492B-865A-39B2D6A15FF6}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1787" uniqueCount="438">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1805" uniqueCount="438">
   <si>
     <t>Date</t>
   </si>
@@ -1850,7 +1850,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F307807-E5C9-4450-88E0-159CBB3E9A67}">
-  <dimension ref="A1:T885"/>
+  <dimension ref="A1:T894"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="39.33203125" customWidth="1"/>
@@ -34167,9 +34167,402 @@
         <v>283</v>
       </c>
     </row>
+    <row r="886" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A886" t="s">
+        <v>59</v>
+      </c>
+      <c r="B886">
+        <v>-35.084850000000003</v>
+      </c>
+      <c r="C886">
+        <v>137.74889999999999</v>
+      </c>
+      <c r="D886" s="2">
+        <v>46169</v>
+      </c>
+      <c r="E886" s="20">
+        <v>0.5</v>
+      </c>
+      <c r="G886">
+        <v>111</v>
+      </c>
+      <c r="H886">
+        <v>167</v>
+      </c>
+      <c r="I886">
+        <v>333</v>
+      </c>
+      <c r="J886">
+        <v>0</v>
+      </c>
+      <c r="L886">
+        <v>111</v>
+      </c>
+      <c r="M886">
+        <v>0</v>
+      </c>
+      <c r="N886">
+        <v>1000</v>
+      </c>
+      <c r="O886">
+        <v>167</v>
+      </c>
+      <c r="P886">
+        <v>1889</v>
+      </c>
+      <c r="Q886" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="887" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A887" t="s">
+        <v>427</v>
+      </c>
+      <c r="B887">
+        <v>-35.410254000000002</v>
+      </c>
+      <c r="C887">
+        <v>138.32751999999999</v>
+      </c>
+      <c r="D887" s="2">
+        <v>46169</v>
+      </c>
+      <c r="E887" s="20">
+        <v>0.4375</v>
+      </c>
+      <c r="F887">
+        <v>0</v>
+      </c>
+      <c r="G887">
+        <v>56</v>
+      </c>
+      <c r="H887">
+        <v>333</v>
+      </c>
+      <c r="I887">
+        <v>167</v>
+      </c>
+      <c r="J887">
+        <v>0</v>
+      </c>
+      <c r="K887">
+        <v>0</v>
+      </c>
+      <c r="L887">
+        <v>56</v>
+      </c>
+      <c r="M887">
+        <v>0</v>
+      </c>
+      <c r="N887">
+        <v>1333</v>
+      </c>
+      <c r="O887">
+        <v>222</v>
+      </c>
+      <c r="P887">
+        <v>2167</v>
+      </c>
+      <c r="Q887" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="888" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A888" t="s">
+        <v>289</v>
+      </c>
+      <c r="B888">
+        <v>-34.628509999999999</v>
+      </c>
+      <c r="C888">
+        <v>135.86675</v>
+      </c>
+      <c r="D888" s="2">
+        <v>46170</v>
+      </c>
+      <c r="E888" s="20">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="I888">
+        <v>18</v>
+      </c>
+      <c r="J888">
+        <v>6</v>
+      </c>
+      <c r="L888">
+        <v>45</v>
+      </c>
+      <c r="O888">
+        <v>7</v>
+      </c>
+      <c r="P888">
+        <v>70</v>
+      </c>
+      <c r="Q888" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="889" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A889" t="s">
+        <v>435</v>
+      </c>
+      <c r="B889">
+        <v>-34.540819999999997</v>
+      </c>
+      <c r="C889">
+        <v>135.93379999999999</v>
+      </c>
+      <c r="D889" s="2">
+        <v>46172</v>
+      </c>
+      <c r="E889" s="20">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="I889">
+        <v>58</v>
+      </c>
+      <c r="J889">
+        <v>42</v>
+      </c>
+      <c r="L889">
+        <v>41</v>
+      </c>
+      <c r="O889">
+        <v>6</v>
+      </c>
+      <c r="P889">
+        <v>105</v>
+      </c>
+      <c r="Q889" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="890" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A890" t="s">
+        <v>422</v>
+      </c>
+      <c r="B890">
+        <v>-35.500024000000003</v>
+      </c>
+      <c r="C890">
+        <v>138.24287699999999</v>
+      </c>
+      <c r="D890" s="2">
+        <v>46173</v>
+      </c>
+      <c r="E890" s="20">
+        <v>0.38194444444444442</v>
+      </c>
+      <c r="F890">
+        <v>0</v>
+      </c>
+      <c r="G890">
+        <v>0</v>
+      </c>
+      <c r="H890">
+        <v>389</v>
+      </c>
+      <c r="I890">
+        <v>167</v>
+      </c>
+      <c r="J890">
+        <v>0</v>
+      </c>
+      <c r="K890">
+        <v>0</v>
+      </c>
+      <c r="L890">
+        <v>0</v>
+      </c>
+      <c r="M890">
+        <v>667</v>
+      </c>
+      <c r="N890">
+        <v>1611</v>
+      </c>
+      <c r="O890">
+        <v>111</v>
+      </c>
+      <c r="P890">
+        <v>2945</v>
+      </c>
+      <c r="Q890" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="891" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A891" t="s">
+        <v>289</v>
+      </c>
+      <c r="B891">
+        <v>-34.628509999999999</v>
+      </c>
+      <c r="C891">
+        <v>135.86675</v>
+      </c>
+      <c r="D891" s="2">
+        <v>46173</v>
+      </c>
+      <c r="E891" s="20">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="I891">
+        <v>34</v>
+      </c>
+      <c r="J891">
+        <v>21</v>
+      </c>
+      <c r="L891">
+        <v>6</v>
+      </c>
+      <c r="O891">
+        <v>5</v>
+      </c>
+      <c r="P891">
+        <v>45</v>
+      </c>
+      <c r="Q891" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="892" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A892" t="s">
+        <v>312</v>
+      </c>
+      <c r="B892">
+        <v>-35.445059999999998</v>
+      </c>
+      <c r="C892">
+        <v>138.30758399999999</v>
+      </c>
+      <c r="D892" s="2">
+        <v>46174</v>
+      </c>
+      <c r="E892" s="20">
+        <v>0.34375</v>
+      </c>
+      <c r="F892">
+        <v>0</v>
+      </c>
+      <c r="G892">
+        <v>0</v>
+      </c>
+      <c r="H892">
+        <v>0</v>
+      </c>
+      <c r="I892">
+        <v>56</v>
+      </c>
+      <c r="J892">
+        <v>0</v>
+      </c>
+      <c r="K892">
+        <v>0</v>
+      </c>
+      <c r="L892">
+        <v>56</v>
+      </c>
+      <c r="M892">
+        <v>0</v>
+      </c>
+      <c r="N892">
+        <v>56</v>
+      </c>
+      <c r="O892">
+        <v>56</v>
+      </c>
+      <c r="P892">
+        <v>222</v>
+      </c>
+      <c r="Q892" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="893" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A893" t="s">
+        <v>289</v>
+      </c>
+      <c r="B893">
+        <v>-34.628509999999999</v>
+      </c>
+      <c r="C893">
+        <v>135.86675</v>
+      </c>
+      <c r="D893" s="2">
+        <v>46175</v>
+      </c>
+      <c r="E893" s="20">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="I893">
+        <v>69</v>
+      </c>
+      <c r="J893">
+        <v>49</v>
+      </c>
+      <c r="L893">
+        <v>9</v>
+      </c>
+      <c r="O893">
+        <v>6</v>
+      </c>
+      <c r="P893">
+        <v>84</v>
+      </c>
+      <c r="Q893" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="894" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A894" t="s">
+        <v>59</v>
+      </c>
+      <c r="B894">
+        <v>-35.084850000000003</v>
+      </c>
+      <c r="C894">
+        <v>137.74889999999999</v>
+      </c>
+      <c r="D894" s="2">
+        <v>46176</v>
+      </c>
+      <c r="E894" s="20">
+        <v>0.5</v>
+      </c>
+      <c r="G894">
+        <v>333</v>
+      </c>
+      <c r="H894">
+        <v>111</v>
+      </c>
+      <c r="I894">
+        <v>111</v>
+      </c>
+      <c r="J894">
+        <v>0</v>
+      </c>
+      <c r="L894">
+        <v>222</v>
+      </c>
+      <c r="M894">
+        <v>0</v>
+      </c>
+      <c r="N894">
+        <v>555</v>
+      </c>
+      <c r="O894">
+        <v>0</v>
+      </c>
+      <c r="P894">
+        <v>1332</v>
+      </c>
+      <c r="Q894" t="s">
+        <v>149</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q885">
-    <sortCondition ref="D2:D885"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q894">
+    <sortCondition ref="D2:D894"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="S229">

--- a/MASTER spreadsheet of community summaries.xlsx
+++ b/MASTER spreadsheet of community summaries.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\peri\Dropbox\Delta\Projects\Laboratory\Algal blooms, bacterial counts  for community\For Luke's HAB data display\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34B04459-DC8C-4C8D-A8E8-DCA2CAD65BA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{005F6CEC-75B7-4CD3-95D3-CE52900DB64B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{9286397E-2757-492B-865A-39B2D6A15FF6}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1805" uniqueCount="438">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1855" uniqueCount="451">
   <si>
     <t>Date</t>
   </si>
@@ -982,9 +982,6 @@
     <t xml:space="preserve">Kemp Bay, Shoreline </t>
   </si>
   <si>
-    <t>Wool Bay Jetty Stairwell, 1m depth</t>
-  </si>
-  <si>
     <t xml:space="preserve">Edithburgh Boat Ramp, Bottom Sample </t>
   </si>
   <si>
@@ -1370,6 +1367,48 @@
   </si>
   <si>
     <t>Rapid Head New Jetty</t>
+  </si>
+  <si>
+    <t>Louth Bay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North Shields Jetty </t>
+  </si>
+  <si>
+    <t>Largs Bay Jetty</t>
+  </si>
+  <si>
+    <t>Brighton Jetty</t>
+  </si>
+  <si>
+    <t>Brighton Edward St</t>
+  </si>
+  <si>
+    <t>Brighton Young St</t>
+  </si>
+  <si>
+    <t>Seacliff South</t>
+  </si>
+  <si>
+    <t>Seacliff North</t>
+  </si>
+  <si>
+    <t>Murray Point sample A</t>
+  </si>
+  <si>
+    <t>Murray Point sample B sandy point</t>
+  </si>
+  <si>
+    <t>WILJ5045</t>
+  </si>
+  <si>
+    <t>Edithburgh Tidal Pool, Outside</t>
+  </si>
+  <si>
+    <t>Wool Bay Jetty Stairs</t>
+  </si>
+  <si>
+    <t>Morgan’s Beach</t>
   </si>
 </sst>
 </file>
@@ -1458,7 +1497,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1499,6 +1538,8 @@
     <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="18" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1850,7 +1891,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F307807-E5C9-4450-88E0-159CBB3E9A67}">
-  <dimension ref="A1:T894"/>
+  <dimension ref="A1:T919"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="39.33203125" customWidth="1"/>
@@ -1887,7 +1928,7 @@
         <v>0</v>
       </c>
       <c r="E1" s="19" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>64</v>
@@ -18425,7 +18466,7 @@
     </row>
     <row r="456" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A456" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B456">
         <v>-35.242910000000002</v>
@@ -18607,7 +18648,7 @@
     </row>
     <row r="460" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A460" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B460">
         <v>-35.085709299999998</v>
@@ -18776,7 +18817,7 @@
     </row>
     <row r="465" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A465" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B465">
         <v>-35.579300000000003</v>
@@ -18814,7 +18855,7 @@
     </row>
     <row r="466" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A466" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B466">
         <v>-35.585419999999999</v>
@@ -18849,7 +18890,7 @@
     </row>
     <row r="467" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A467" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B467">
         <v>-35.570399999999999</v>
@@ -19671,7 +19712,7 @@
     </row>
     <row r="489" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A489" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B489">
         <v>-35.510497000000001</v>
@@ -20808,7 +20849,7 @@
     </row>
     <row r="523" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A523" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B523">
         <v>-33.040959000000001</v>
@@ -20835,7 +20876,7 @@
         <v>3335</v>
       </c>
       <c r="Q523" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="524" spans="1:17" x14ac:dyDescent="0.3">
@@ -20994,10 +21035,10 @@
         <v>305</v>
       </c>
       <c r="B529">
-        <v>-35.594605999999999</v>
+        <v>-35.595986000000003</v>
       </c>
       <c r="C529">
-        <v>138.105254</v>
+        <v>138.104072</v>
       </c>
       <c r="D529" s="2">
         <v>46049</v>
@@ -21029,7 +21070,7 @@
     </row>
     <row r="530" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A530" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B530">
         <v>-35.510753999999999</v>
@@ -21303,7 +21344,7 @@
     </row>
     <row r="538" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A538" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B538">
         <v>-34.911830000000002</v>
@@ -21332,7 +21373,7 @@
     </row>
     <row r="539" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A539" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B539">
         <v>-35.089612000000002</v>
@@ -21367,7 +21408,7 @@
     </row>
     <row r="540" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A540" t="s">
-        <v>308</v>
+        <v>449</v>
       </c>
       <c r="B540">
         <v>-34.994472000000002</v>
@@ -21399,7 +21440,7 @@
     </row>
     <row r="541" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A541" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B541">
         <v>-35.522570000000002</v>
@@ -21601,7 +21642,7 @@
     </row>
     <row r="546" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A546" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B546">
         <v>-34.920539599999998</v>
@@ -21636,7 +21677,7 @@
     </row>
     <row r="547" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A547" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B547">
         <v>-35.085709299999998</v>
@@ -21668,7 +21709,7 @@
     </row>
     <row r="548" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A548" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B548">
         <v>-35.445059999999998</v>
@@ -21703,7 +21744,7 @@
     </row>
     <row r="549" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A549" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B549">
         <v>-35.516500000000001</v>
@@ -21729,7 +21770,7 @@
     </row>
     <row r="550" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A550" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B550">
         <v>-35.517899999999997</v>
@@ -21807,7 +21848,7 @@
     </row>
     <row r="553" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A553" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B553">
         <v>-35.5565</v>
@@ -21833,7 +21874,7 @@
     </row>
     <row r="554" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A554" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B554">
         <v>-35.563899999999997</v>
@@ -21885,7 +21926,7 @@
     </row>
     <row r="556" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A556" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B556">
         <v>-35.634900000000002</v>
@@ -21911,7 +21952,7 @@
     </row>
     <row r="557" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A557" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B557">
         <v>-34.929459999999999</v>
@@ -21934,7 +21975,7 @@
     </row>
     <row r="558" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A558" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B558">
         <v>-34.928570000000001</v>
@@ -21957,7 +21998,7 @@
     </row>
     <row r="559" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A559" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B559">
         <v>-34.901600000000002</v>
@@ -22100,7 +22141,7 @@
     </row>
     <row r="563" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A563" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B563">
         <v>-35.32508</v>
@@ -22135,7 +22176,7 @@
     </row>
     <row r="564" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A564" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B564">
         <v>-34.903820000000003</v>
@@ -22269,7 +22310,7 @@
     </row>
     <row r="568" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A568" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B568">
         <v>-34.911830000000002</v>
@@ -22295,7 +22336,7 @@
     </row>
     <row r="569" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A569" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B569">
         <v>-34.893770000000004</v>
@@ -22321,7 +22362,7 @@
     </row>
     <row r="570" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A570" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B570" s="13">
         <f>-35.521088</f>
@@ -22361,7 +22402,7 @@
     </row>
     <row r="571" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A571" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B571">
         <v>-34.495376</v>
@@ -22396,7 +22437,7 @@
     </row>
     <row r="572" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A572" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B572">
         <v>-34.750552999999996</v>
@@ -22428,7 +22469,7 @@
     </row>
     <row r="573" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A573" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B573">
         <v>-34.672504000000004</v>
@@ -22463,7 +22504,7 @@
     </row>
     <row r="574" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A574" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B574">
         <v>-34.588209999999997</v>
@@ -22530,7 +22571,7 @@
     </row>
     <row r="576" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A576" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B576">
         <v>-34.812609999999999</v>
@@ -22643,7 +22684,7 @@
     </row>
     <row r="580" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A580" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B580">
         <v>-34.912934499999999</v>
@@ -22724,7 +22765,7 @@
     </row>
     <row r="583" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A583" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B583">
         <v>-34.831850000000003</v>
@@ -22785,7 +22826,7 @@
     </row>
     <row r="585" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A585" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B585">
         <v>-34.920539599999998</v>
@@ -22835,7 +22876,7 @@
     </row>
     <row r="586" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A586" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B586">
         <v>-34.933680000000003</v>
@@ -23187,7 +23228,7 @@
     </row>
     <row r="594" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A594" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B594">
         <v>-34.519669999999998</v>
@@ -23225,7 +23266,7 @@
     </row>
     <row r="595" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A595" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B595">
         <v>-34.535609999999998</v>
@@ -23327,7 +23368,7 @@
     </row>
     <row r="598" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A598" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B598">
         <v>-34.890371899999998</v>
@@ -23365,7 +23406,7 @@
     </row>
     <row r="599" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A599" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B599">
         <v>-35.500242</v>
@@ -23444,7 +23485,7 @@
     </row>
     <row r="602" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A602" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B602">
         <v>-34.670960000000001</v>
@@ -23464,7 +23505,7 @@
     </row>
     <row r="603" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A603" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B603">
         <v>-34.643329999999999</v>
@@ -23484,7 +23525,7 @@
     </row>
     <row r="604" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A604" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B604">
         <v>-34.586370000000002</v>
@@ -23504,7 +23545,7 @@
     </row>
     <row r="605" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A605" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B605">
         <v>-34.9094768</v>
@@ -23644,7 +23685,7 @@
     </row>
     <row r="609" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A609" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B609">
         <v>-34.672490000000003</v>
@@ -23667,7 +23708,7 @@
     </row>
     <row r="610" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A610" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B610">
         <v>-34.586370000000002</v>
@@ -23690,7 +23731,7 @@
     </row>
     <row r="611" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A611" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B611">
         <v>-34.507260000000002</v>
@@ -23759,7 +23800,7 @@
     </row>
     <row r="614" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A614" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B614">
         <v>-34.911830000000002</v>
@@ -23828,7 +23869,7 @@
     </row>
     <row r="617" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A617" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B617">
         <v>-34.672490000000003</v>
@@ -23851,7 +23892,7 @@
     </row>
     <row r="618" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A618" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B618">
         <v>-35.642456000000003</v>
@@ -23976,7 +24017,7 @@
     </row>
     <row r="621" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A621" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B621">
         <v>-34.860666999999999</v>
@@ -24094,7 +24135,7 @@
     </row>
     <row r="625" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A625" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B625">
         <v>-34.672490000000003</v>
@@ -24117,7 +24158,7 @@
     </row>
     <row r="626" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A626" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B626">
         <v>-34.66301</v>
@@ -24140,7 +24181,7 @@
     </row>
     <row r="627" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A627" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B627">
         <v>-34.586370000000002</v>
@@ -24163,7 +24204,7 @@
     </row>
     <row r="628" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A628" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B628">
         <v>-34.52664</v>
@@ -24186,7 +24227,7 @@
     </row>
     <row r="629" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A629" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B629">
         <v>-34.494970000000002</v>
@@ -24285,7 +24326,7 @@
     </row>
     <row r="632" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A632" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B632">
         <v>-33.043101999999998</v>
@@ -24312,12 +24353,12 @@
         <v>2222</v>
       </c>
       <c r="Q632" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="633" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A633" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B633">
         <v>-35.445059999999998</v>
@@ -24345,12 +24386,12 @@
         <v>0</v>
       </c>
       <c r="Q633" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="634" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A634" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B634">
         <v>-34.637633999999998</v>
@@ -24379,7 +24420,7 @@
     </row>
     <row r="635" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A635" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B635">
         <v>-34.864305100000003</v>
@@ -24444,7 +24485,7 @@
     </row>
     <row r="637" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A637" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B637">
         <v>-35.092981999999999</v>
@@ -24479,7 +24520,7 @@
     </row>
     <row r="638" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A638" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B638">
         <v>-34.672490000000003</v>
@@ -24607,7 +24648,7 @@
     </row>
     <row r="642" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A642" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B642">
         <v>-34.672490000000003</v>
@@ -24640,7 +24681,7 @@
     </row>
     <row r="643" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A643" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B643">
         <v>-34.934266999999998</v>
@@ -24678,7 +24719,7 @@
     </row>
     <row r="644" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A644" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B644">
         <v>-34.910024</v>
@@ -24836,7 +24877,7 @@
     </row>
     <row r="648" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A648" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B648">
         <v>-35.612285999999997</v>
@@ -24877,7 +24918,7 @@
     </row>
     <row r="649" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A649" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B649">
         <v>-34.933680000000003</v>
@@ -24945,7 +24986,7 @@
     </row>
     <row r="651" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A651" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B651">
         <v>-34.911830000000002</v>
@@ -25032,7 +25073,7 @@
     </row>
     <row r="653" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A653" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B653">
         <v>-34.860666999999999</v>
@@ -25140,7 +25181,7 @@
     </row>
     <row r="655" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A655" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B655">
         <v>-35.878667100000001</v>
@@ -25193,7 +25234,7 @@
     </row>
     <row r="656" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A656" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B656">
         <v>-34.586370000000002</v>
@@ -25259,7 +25300,7 @@
     </row>
     <row r="658" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A658" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B658">
         <v>-35.853555700000001</v>
@@ -25312,7 +25353,7 @@
     </row>
     <row r="659" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A659" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B659">
         <v>-35.787276900000002</v>
@@ -25365,7 +25406,7 @@
     </row>
     <row r="660" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A660" s="17" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B660">
         <v>-34.776083</v>
@@ -25404,7 +25445,7 @@
         <v>1111</v>
       </c>
       <c r="Q660" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="661" spans="1:17" x14ac:dyDescent="0.3">
@@ -25508,7 +25549,7 @@
     </row>
     <row r="664" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A664" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B664">
         <v>-35.5565</v>
@@ -25574,7 +25615,7 @@
     </row>
     <row r="666" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A666" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B666">
         <v>-35.634602000000001</v>
@@ -25607,7 +25648,7 @@
     </row>
     <row r="667" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A667" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B667">
         <v>-34.918303199999997</v>
@@ -25639,7 +25680,7 @@
     </row>
     <row r="668" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A668" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B668">
         <v>-34.911405199999997</v>
@@ -25709,7 +25750,7 @@
     </row>
     <row r="670" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A670" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B670">
         <v>-34.82743</v>
@@ -25860,7 +25901,7 @@
     </row>
     <row r="674" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A674" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B674">
         <v>-35.739091000000002</v>
@@ -25910,7 +25951,7 @@
     </row>
     <row r="675" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A675" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B675">
         <v>-34.494970000000002</v>
@@ -25997,7 +26038,7 @@
     </row>
     <row r="677" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A677" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B677">
         <v>-35.119663000000003</v>
@@ -26127,7 +26168,7 @@
     </row>
     <row r="680" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A680" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B680">
         <v>-34.759169999999997</v>
@@ -26170,7 +26211,7 @@
     </row>
     <row r="682" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A682" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B682">
         <v>-34.494970000000002</v>
@@ -26193,7 +26234,7 @@
     </row>
     <row r="683" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A683" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B683">
         <v>-34.584389999999999</v>
@@ -26286,7 +26327,7 @@
     </row>
     <row r="686" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A686" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B686">
         <v>-34.902070808541197</v>
@@ -26307,7 +26348,7 @@
         <v>167</v>
       </c>
       <c r="K686" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="L686">
         <v>167</v>
@@ -26322,12 +26363,12 @@
         <v>1390</v>
       </c>
       <c r="Q686" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="687" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A687" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B687">
         <v>-34.933680000000003</v>
@@ -26362,7 +26403,7 @@
     </row>
     <row r="688" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A688" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B688">
         <v>-34.759169999999997</v>
@@ -26385,7 +26426,7 @@
     </row>
     <row r="689" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A689" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B689">
         <v>-34.075153</v>
@@ -26476,7 +26517,7 @@
     </row>
     <row r="691" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A691" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B691">
         <v>-35.853555700000001</v>
@@ -26529,7 +26570,7 @@
     </row>
     <row r="692" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A692" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B692">
         <v>-35.852509699999999</v>
@@ -26579,7 +26620,7 @@
     </row>
     <row r="693" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A693" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B693">
         <v>-35.787201000000003</v>
@@ -26632,7 +26673,7 @@
     </row>
     <row r="694" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A694" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B694">
         <v>-34.759169999999997</v>
@@ -26655,7 +26696,7 @@
     </row>
     <row r="695" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A695" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B695">
         <v>-34.494970000000002</v>
@@ -26678,7 +26719,7 @@
     </row>
     <row r="696" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A696" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B696">
         <v>-36.866</v>
@@ -26719,7 +26760,7 @@
     </row>
     <row r="697" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A697" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B697">
         <v>-34.902070808541197</v>
@@ -26752,12 +26793,12 @@
         <v>1556</v>
       </c>
       <c r="Q697" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="698" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A698" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B698">
         <v>-34.495376</v>
@@ -26795,7 +26836,7 @@
     </row>
     <row r="699" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A699" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B699">
         <v>-34.759169999999997</v>
@@ -26841,7 +26882,7 @@
     </row>
     <row r="701" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A701" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B701">
         <v>-34.759169999999997</v>
@@ -26864,7 +26905,7 @@
     </row>
     <row r="702" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A702" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B702">
         <v>-35.853555700000001</v>
@@ -26917,7 +26958,7 @@
     </row>
     <row r="703" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A703" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B703">
         <v>-35.739091000000002</v>
@@ -27090,7 +27131,7 @@
     </row>
     <row r="707" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A707" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B707">
         <v>-35.516800000000003</v>
@@ -27218,7 +27259,7 @@
     </row>
     <row r="711" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A711" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B711">
         <v>-35.5565</v>
@@ -27282,7 +27323,7 @@
     </row>
     <row r="713" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A713" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B713">
         <v>-35.634900000000002</v>
@@ -27314,7 +27355,7 @@
     </row>
     <row r="714" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A714" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B714">
         <v>-35.510497000000001</v>
@@ -27352,7 +27393,7 @@
     </row>
     <row r="715" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A715" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B715">
         <v>-35.793973000000001</v>
@@ -27405,7 +27446,7 @@
     </row>
     <row r="716" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A716" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B716">
         <v>-34.88823</v>
@@ -27498,7 +27539,7 @@
     </row>
     <row r="719" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A719" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B719">
         <v>-33.043101999999998</v>
@@ -27525,12 +27566,12 @@
         <v>1889</v>
       </c>
       <c r="Q719" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="720" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A720" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B720">
         <v>-35.878667100000001</v>
@@ -27621,7 +27662,7 @@
     </row>
     <row r="722" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A722" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B722">
         <v>-34.842409000000004</v>
@@ -27665,7 +27706,7 @@
     </row>
     <row r="723" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A723" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B723">
         <v>-34.759169999999997</v>
@@ -27688,7 +27729,7 @@
     </row>
     <row r="724" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A724" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B724">
         <v>-34.672490000000003</v>
@@ -27749,7 +27790,7 @@
     </row>
     <row r="726" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A726" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B726">
         <v>-35.786641000000003</v>
@@ -27855,7 +27896,7 @@
     </row>
     <row r="728" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A728" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B728">
         <v>-35.532783000000002</v>
@@ -27931,7 +27972,7 @@
     </row>
     <row r="730" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A730" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B730">
         <v>-35.521971999999998</v>
@@ -28051,7 +28092,7 @@
     </row>
     <row r="733" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A733" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B733">
         <v>-35.557299999999998</v>
@@ -28209,7 +28250,7 @@
     </row>
     <row r="737" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A737" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B737">
         <v>-35.612285999999997</v>
@@ -28282,7 +28323,7 @@
     </row>
     <row r="739" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A739" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B739">
         <v>-34.958151000000001</v>
@@ -28317,7 +28358,7 @@
     </row>
     <row r="740" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A740" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B740">
         <v>-34.860666999999999</v>
@@ -28355,7 +28396,7 @@
     </row>
     <row r="741" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A741" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B741">
         <v>-35.445059999999998</v>
@@ -28388,12 +28429,12 @@
         <v>2056</v>
       </c>
       <c r="Q741" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="742" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A742" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B742">
         <v>-34.759169999999997</v>
@@ -28416,7 +28457,7 @@
     </row>
     <row r="743" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A743" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B743">
         <v>-35.739091000000002</v>
@@ -28469,7 +28510,7 @@
     </row>
     <row r="744" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A744" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B744">
         <v>-35.853555700000001</v>
@@ -28522,7 +28563,7 @@
     </row>
     <row r="745" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A745" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B745">
         <v>-34.323770000000003</v>
@@ -28545,7 +28586,7 @@
     </row>
     <row r="746" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A746" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B746">
         <v>-34.494970000000002</v>
@@ -28591,7 +28632,7 @@
     </row>
     <row r="748" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A748" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B748">
         <v>-34.075042000000003</v>
@@ -28696,7 +28737,7 @@
     </row>
     <row r="751" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A751" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B751">
         <v>-34.902070808541197</v>
@@ -28726,12 +28767,12 @@
         <v>500</v>
       </c>
       <c r="Q751" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="752" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A752" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B752">
         <v>-35.853555700000001</v>
@@ -28807,7 +28848,7 @@
     </row>
     <row r="754" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A754" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B754">
         <v>-34.672499999999999</v>
@@ -28929,7 +28970,7 @@
     </row>
     <row r="758" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A758" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B758">
         <v>-34.958151000000001</v>
@@ -29049,7 +29090,7 @@
     </row>
     <row r="761" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A761" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B761">
         <v>-34.903120000000001</v>
@@ -29116,7 +29157,7 @@
     </row>
     <row r="763" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A763" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B763">
         <v>-34.903466000000002</v>
@@ -29154,7 +29195,7 @@
     </row>
     <row r="764" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A764" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B764">
         <v>-34.765996000000001</v>
@@ -29192,7 +29233,7 @@
     </row>
     <row r="765" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A765" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B765">
         <v>-35.510497000000001</v>
@@ -29227,7 +29268,7 @@
     </row>
     <row r="766" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A766" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B766">
         <v>-35.793973000000001</v>
@@ -29280,7 +29321,7 @@
     </row>
     <row r="767" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A767" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B767">
         <v>-35.878667100000001</v>
@@ -29333,7 +29374,7 @@
     </row>
     <row r="768" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A768" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B768">
         <v>-35.445059999999998</v>
@@ -29363,12 +29404,12 @@
         <v>1722</v>
       </c>
       <c r="Q768" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="769" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A769" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B769">
         <v>-34.759169999999997</v>
@@ -29400,7 +29441,7 @@
     </row>
     <row r="770" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A770" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B770">
         <v>-35.445059999999998</v>
@@ -29433,12 +29474,12 @@
         <v>890</v>
       </c>
       <c r="Q770" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="771" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A771" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B771">
         <v>-34.672499999999999</v>
@@ -29473,7 +29514,7 @@
     </row>
     <row r="772" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A772" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B772">
         <v>-35.557499999999997</v>
@@ -29514,7 +29555,7 @@
     </row>
     <row r="773" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A773" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B773">
         <v>-34.860666999999999</v>
@@ -29660,7 +29701,7 @@
     </row>
     <row r="777" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A777" s="1" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B777" s="1">
         <v>-35.516800000000003</v>
@@ -29799,7 +29840,7 @@
     </row>
     <row r="781" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A781" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B781">
         <v>-35.5565</v>
@@ -29865,7 +29906,7 @@
     </row>
     <row r="783" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A783" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B783">
         <v>-35.634900000000002</v>
@@ -29898,7 +29939,7 @@
     </row>
     <row r="784" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A784" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B784">
         <v>-35.563899999999997</v>
@@ -29931,7 +29972,7 @@
     </row>
     <row r="785" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A785" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B785">
         <v>-35.548499999999997</v>
@@ -29964,7 +30005,7 @@
     </row>
     <row r="786" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A786" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B786">
         <v>-35.5595</v>
@@ -29997,7 +30038,7 @@
     </row>
     <row r="787" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A787" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B787">
         <v>-35.585299999999997</v>
@@ -30063,7 +30104,7 @@
     </row>
     <row r="789" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A789" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B789">
         <v>-35.500242</v>
@@ -30101,7 +30142,7 @@
     </row>
     <row r="790" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A790" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B790">
         <v>-35.500024000000003</v>
@@ -30142,7 +30183,7 @@
     </row>
     <row r="791" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A791" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B791">
         <v>-35.793973000000001</v>
@@ -30248,7 +30289,7 @@
     </row>
     <row r="793" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A793" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B793">
         <v>-35.853555700000001</v>
@@ -30301,7 +30342,7 @@
     </row>
     <row r="794" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A794" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B794">
         <v>-34.075042000000003</v>
@@ -30500,7 +30541,7 @@
     </row>
     <row r="799" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A799" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B799">
         <v>-35.149287000000001</v>
@@ -30535,7 +30576,7 @@
     </row>
     <row r="800" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A800" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B800">
         <v>-36.825802000000003</v>
@@ -30573,7 +30614,7 @@
     </row>
     <row r="801" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A801" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B801">
         <v>-35.878667100000001</v>
@@ -30626,7 +30667,7 @@
     </row>
     <row r="802" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A802" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B802">
         <v>-35.781129999999997</v>
@@ -30717,7 +30758,7 @@
     </row>
     <row r="804" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A804" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B804">
         <v>-35.786641000000003</v>
@@ -30770,7 +30811,7 @@
     </row>
     <row r="805" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A805" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B805">
         <v>-32.915069000000003</v>
@@ -30797,12 +30838,12 @@
         <v>2333</v>
       </c>
       <c r="Q805" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="806" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A806" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B806">
         <v>-32.913386000000003</v>
@@ -30829,7 +30870,7 @@
         <v>666</v>
       </c>
       <c r="Q806" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="807" spans="1:17" x14ac:dyDescent="0.3">
@@ -30907,7 +30948,7 @@
     </row>
     <row r="809" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A809" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B809">
         <v>-35.533231000000001</v>
@@ -30948,7 +30989,7 @@
     </row>
     <row r="810" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A810" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B810">
         <v>-35.445059999999998</v>
@@ -30981,12 +31022,12 @@
         <v>56</v>
       </c>
       <c r="Q810" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="811" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A811" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B811">
         <v>-35.510497000000001</v>
@@ -31036,7 +31077,7 @@
     </row>
     <row r="812" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A812" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B812">
         <v>-35.500024000000003</v>
@@ -31077,7 +31118,7 @@
     </row>
     <row r="813" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A813" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B813">
         <v>-35.739091000000002</v>
@@ -31130,7 +31171,7 @@
     </row>
     <row r="814" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A814" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B814">
         <v>-35.853557000000002</v>
@@ -31224,7 +31265,7 @@
     </row>
     <row r="816" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A816" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B816">
         <v>-35.463515299999997</v>
@@ -31277,7 +31318,7 @@
     </row>
     <row r="817" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A817" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B817">
         <v>-35.605305999999999</v>
@@ -31397,7 +31438,7 @@
     </row>
     <row r="820" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A820" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B820">
         <v>-34.875185999999999</v>
@@ -31438,7 +31479,7 @@
     </row>
     <row r="821" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A821" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B821">
         <v>-35.445059999999998</v>
@@ -31471,12 +31512,12 @@
         <v>778</v>
       </c>
       <c r="Q821" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="822" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A822" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B822">
         <v>-35.591330800000001</v>
@@ -31529,7 +31570,7 @@
     </row>
     <row r="823" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A823" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B823">
         <v>-35.793973000000001</v>
@@ -31582,7 +31623,7 @@
     </row>
     <row r="824" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A824" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B824">
         <v>-35.638117999999999</v>
@@ -31623,7 +31664,7 @@
     </row>
     <row r="825" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A825" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B825">
         <v>-35.500024000000003</v>
@@ -31667,424 +31708,415 @@
     </row>
     <row r="826" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A826" t="s">
-        <v>89</v>
+        <v>448</v>
       </c>
       <c r="B826">
-        <v>-35.6048446</v>
+        <v>-35.081918000000002</v>
       </c>
       <c r="C826">
-        <v>138.59278499999999</v>
+        <v>137.74822499999999</v>
       </c>
       <c r="D826" s="2">
-        <v>46131</v>
-      </c>
-      <c r="G826">
+        <v>46130</v>
+      </c>
+      <c r="E826" s="25">
+        <v>0.82291666666666663</v>
+      </c>
+      <c r="I826">
         <v>111</v>
       </c>
-      <c r="I826">
+      <c r="J826">
+        <v>0</v>
+      </c>
+      <c r="L826">
+        <v>500</v>
+      </c>
+      <c r="N826">
+        <v>556</v>
+      </c>
+      <c r="O826">
         <v>222</v>
       </c>
-      <c r="J826">
-        <v>0</v>
-      </c>
-      <c r="L826">
-        <v>222</v>
-      </c>
-      <c r="N826">
-        <v>389</v>
-      </c>
-      <c r="O826">
-        <v>444</v>
-      </c>
       <c r="P826">
-        <v>1388</v>
+        <v>1389</v>
       </c>
       <c r="Q826" t="s">
-        <v>129</v>
+        <v>218</v>
       </c>
     </row>
     <row r="827" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A827" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="B827">
-        <v>-35.510497000000001</v>
+        <v>-34.903466000000002</v>
       </c>
       <c r="C827">
-        <v>138.21676299999999</v>
+        <v>137.79804799999999</v>
       </c>
       <c r="D827" s="2">
-        <v>46131</v>
-      </c>
-      <c r="E827" s="20">
-        <v>0.625</v>
+        <v>46130</v>
+      </c>
+      <c r="E827" s="25">
+        <v>0.67708333333333337</v>
       </c>
       <c r="I827">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="J827">
         <v>0</v>
       </c>
-      <c r="K827">
-        <v>0</v>
-      </c>
       <c r="L827">
-        <v>0</v>
-      </c>
-      <c r="M827">
-        <v>0</v>
+        <v>224</v>
       </c>
       <c r="N827">
-        <v>278</v>
+        <v>6</v>
       </c>
       <c r="O827">
-        <v>111</v>
+        <v>24</v>
       </c>
       <c r="P827">
-        <v>389</v>
+        <v>280</v>
       </c>
       <c r="Q827" t="s">
-        <v>251</v>
+        <v>218</v>
       </c>
     </row>
     <row r="828" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A828" t="s">
-        <v>423</v>
+        <v>89</v>
       </c>
       <c r="B828">
-        <v>-34.980508999999998</v>
+        <v>-35.6048446</v>
       </c>
       <c r="C828">
-        <v>138.508081</v>
+        <v>138.59278499999999</v>
       </c>
       <c r="D828" s="2">
         <v>46131</v>
       </c>
-      <c r="E828" s="20">
-        <v>0.45833333333333331</v>
-      </c>
       <c r="G828">
-        <v>0.12</v>
+        <v>111</v>
       </c>
       <c r="I828">
-        <v>4.68</v>
+        <v>222</v>
       </c>
       <c r="J828">
         <v>0</v>
       </c>
       <c r="L828">
-        <v>380.28</v>
+        <v>222</v>
       </c>
       <c r="N828">
-        <v>0.6</v>
+        <v>389</v>
       </c>
       <c r="O828">
-        <v>0.48</v>
+        <v>444</v>
       </c>
       <c r="P828">
-        <v>386.16</v>
+        <v>1388</v>
       </c>
       <c r="Q828" t="s">
-        <v>78</v>
+        <v>129</v>
       </c>
     </row>
     <row r="829" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A829" t="s">
-        <v>179</v>
+        <v>400</v>
       </c>
       <c r="B829">
-        <v>-35.078539999999997</v>
+        <v>-35.510497000000001</v>
       </c>
       <c r="C829">
-        <v>138.49587</v>
+        <v>138.21676299999999</v>
       </c>
       <c r="D829" s="2">
         <v>46131</v>
       </c>
       <c r="E829" s="20">
-        <v>0.54166666666666663</v>
-      </c>
-      <c r="H829">
-        <v>0.1</v>
+        <v>0.625</v>
       </c>
       <c r="I829">
-        <v>0.36699999999999999</v>
+        <v>0</v>
       </c>
       <c r="J829">
         <v>0</v>
       </c>
+      <c r="K829">
+        <v>0</v>
+      </c>
       <c r="L829">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="M829">
-        <v>6.7000000000000004E-2</v>
+        <v>0</v>
+      </c>
+      <c r="N829">
+        <v>278</v>
+      </c>
+      <c r="O829">
+        <v>111</v>
       </c>
       <c r="P829">
-        <v>5.0339999999999998</v>
+        <v>389</v>
       </c>
       <c r="Q829" t="s">
-        <v>78</v>
+        <v>251</v>
       </c>
     </row>
     <row r="830" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A830" t="s">
-        <v>312</v>
+        <v>422</v>
       </c>
       <c r="B830">
-        <v>-35.445059999999998</v>
+        <v>-34.980508999999998</v>
       </c>
       <c r="C830">
-        <v>138.30758399999999</v>
+        <v>138.508081</v>
       </c>
       <c r="D830" s="2">
-        <v>46132</v>
+        <v>46131</v>
       </c>
       <c r="E830" s="20">
-        <v>0.375</v>
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="G830">
+        <v>0.12</v>
       </c>
       <c r="I830">
-        <v>111</v>
+        <v>4.68</v>
       </c>
       <c r="J830">
         <v>0</v>
       </c>
       <c r="L830">
-        <v>222</v>
+        <v>380.28</v>
       </c>
       <c r="N830">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="O830">
-        <v>2167</v>
+        <v>0.48</v>
       </c>
       <c r="P830">
-        <v>2500</v>
+        <v>386.16</v>
       </c>
       <c r="Q830" t="s">
-        <v>350</v>
+        <v>78</v>
       </c>
     </row>
     <row r="831" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A831" t="s">
-        <v>421</v>
+        <v>179</v>
       </c>
       <c r="B831">
-        <v>-35.878133800000001</v>
+        <v>-35.078539999999997</v>
       </c>
       <c r="C831">
-        <v>137.69381060000001</v>
+        <v>138.49587</v>
       </c>
       <c r="D831" s="2">
-        <v>46133</v>
+        <v>46131</v>
       </c>
       <c r="E831" s="20">
-        <v>0.58333333333333337</v>
-      </c>
-      <c r="F831">
-        <v>0</v>
-      </c>
-      <c r="G831">
-        <v>0</v>
+        <v>0.54166666666666663</v>
       </c>
       <c r="H831">
-        <v>2778</v>
+        <v>0.1</v>
       </c>
       <c r="I831">
-        <v>0</v>
+        <v>0.36699999999999999</v>
       </c>
       <c r="J831">
         <v>0</v>
       </c>
-      <c r="K831">
-        <v>0</v>
-      </c>
       <c r="L831">
-        <v>18333</v>
+        <v>4.5</v>
       </c>
       <c r="M831">
-        <v>556</v>
-      </c>
-      <c r="N831">
-        <v>0</v>
-      </c>
-      <c r="O831">
-        <v>0</v>
+        <v>6.7000000000000004E-2</v>
       </c>
       <c r="P831">
-        <v>21667</v>
+        <v>5.0339999999999998</v>
       </c>
       <c r="Q831" t="s">
-        <v>151</v>
+        <v>78</v>
       </c>
     </row>
     <row r="832" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A832" t="s">
-        <v>59</v>
+        <v>311</v>
       </c>
       <c r="B832">
-        <v>-35.084850000000003</v>
+        <v>-35.445059999999998</v>
       </c>
       <c r="C832">
-        <v>137.74889999999999</v>
+        <v>138.30758399999999</v>
       </c>
       <c r="D832" s="2">
-        <v>46134</v>
+        <v>46132</v>
       </c>
       <c r="E832" s="20">
-        <v>0.5625</v>
-      </c>
-      <c r="G832">
-        <v>444</v>
+        <v>0.375</v>
       </c>
       <c r="I832">
-        <v>56</v>
+        <v>111</v>
       </c>
       <c r="J832">
         <v>0</v>
       </c>
       <c r="L832">
-        <v>0</v>
-      </c>
-      <c r="M832">
-        <v>0</v>
+        <v>222</v>
       </c>
       <c r="N832">
-        <v>389</v>
+        <v>0</v>
+      </c>
+      <c r="O832">
+        <v>2167</v>
       </c>
       <c r="P832">
-        <v>889</v>
+        <v>2500</v>
       </c>
       <c r="Q832" t="s">
-        <v>149</v>
+        <v>349</v>
       </c>
     </row>
     <row r="833" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A833" t="s">
-        <v>86</v>
+        <v>420</v>
       </c>
       <c r="B833">
-        <v>-35.540277000000003</v>
+        <v>-35.878133800000001</v>
       </c>
       <c r="C833">
-        <v>138.66416599999999</v>
+        <v>137.69381060000001</v>
       </c>
       <c r="D833" s="2">
-        <v>46135</v>
+        <v>46133</v>
       </c>
       <c r="E833" s="20">
-        <v>0.5180555555555556</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="F833">
+        <v>0</v>
       </c>
       <c r="G833">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="H833">
-        <v>278</v>
+        <v>2778</v>
       </c>
       <c r="I833">
-        <v>167</v>
+        <v>0</v>
       </c>
       <c r="J833">
         <v>0</v>
       </c>
       <c r="K833">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="L833">
-        <v>4389</v>
+        <v>18333</v>
+      </c>
+      <c r="M833">
+        <v>556</v>
       </c>
       <c r="N833">
-        <v>389</v>
+        <v>0</v>
       </c>
       <c r="O833">
-        <v>944</v>
+        <v>0</v>
       </c>
       <c r="P833">
-        <v>6279</v>
+        <v>21667</v>
       </c>
       <c r="Q833" t="s">
-        <v>129</v>
+        <v>151</v>
       </c>
     </row>
     <row r="834" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A834" t="s">
-        <v>87</v>
+        <v>59</v>
       </c>
       <c r="B834">
-        <v>-35.573300000000003</v>
+        <v>-35.084850000000003</v>
       </c>
       <c r="C834">
-        <v>138.64250000000001</v>
+        <v>137.74889999999999</v>
       </c>
       <c r="D834" s="2">
-        <v>46135</v>
+        <v>46134</v>
       </c>
       <c r="E834" s="20">
-        <v>0.50555555555555554</v>
+        <v>0.5625</v>
       </c>
       <c r="G834">
-        <v>56</v>
-      </c>
-      <c r="H834">
-        <v>111</v>
+        <v>444</v>
       </c>
       <c r="I834">
-        <v>278</v>
+        <v>56</v>
       </c>
       <c r="J834">
         <v>0</v>
       </c>
       <c r="L834">
-        <v>167</v>
+        <v>0</v>
+      </c>
+      <c r="M834">
+        <v>0</v>
       </c>
       <c r="N834">
-        <v>667</v>
-      </c>
-      <c r="O834">
-        <v>778</v>
+        <v>389</v>
       </c>
       <c r="P834">
-        <v>2057</v>
+        <v>889</v>
       </c>
       <c r="Q834" t="s">
-        <v>129</v>
+        <v>149</v>
       </c>
     </row>
     <row r="835" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A835" t="s">
-        <v>425</v>
+        <v>86</v>
       </c>
       <c r="B835">
-        <v>-35.574167000000003</v>
+        <v>-35.540277000000003</v>
       </c>
       <c r="C835">
-        <v>138.61528000000001</v>
+        <v>138.66416599999999</v>
       </c>
       <c r="D835" s="2">
         <v>46135</v>
       </c>
       <c r="E835" s="20">
-        <v>0.49652777777777779</v>
+        <v>0.5180555555555556</v>
       </c>
       <c r="G835">
-        <v>222</v>
+        <v>56</v>
+      </c>
+      <c r="H835">
+        <v>278</v>
       </c>
       <c r="I835">
-        <v>56</v>
+        <v>167</v>
       </c>
       <c r="J835">
         <v>0</v>
       </c>
+      <c r="K835">
+        <v>56</v>
+      </c>
       <c r="L835">
-        <v>111</v>
+        <v>4389</v>
       </c>
       <c r="N835">
-        <v>222</v>
+        <v>389</v>
       </c>
       <c r="O835">
-        <v>722</v>
+        <v>944</v>
       </c>
       <c r="P835">
-        <v>1333</v>
+        <v>6279</v>
       </c>
       <c r="Q835" t="s">
         <v>129</v>
@@ -32092,40 +32124,43 @@
     </row>
     <row r="836" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A836" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B836">
-        <v>-35.6048446</v>
+        <v>-35.573300000000003</v>
       </c>
       <c r="C836">
-        <v>138.59278499999999</v>
+        <v>138.64250000000001</v>
       </c>
       <c r="D836" s="2">
         <v>46135</v>
       </c>
       <c r="E836" s="20">
-        <v>0.48749999999999999</v>
+        <v>0.50555555555555554</v>
+      </c>
+      <c r="G836">
+        <v>56</v>
       </c>
       <c r="H836">
         <v>111</v>
       </c>
       <c r="I836">
-        <v>1667</v>
+        <v>278</v>
       </c>
       <c r="J836">
         <v>0</v>
       </c>
       <c r="L836">
-        <v>56</v>
+        <v>167</v>
       </c>
       <c r="N836">
-        <v>167</v>
+        <v>667</v>
       </c>
       <c r="O836">
-        <v>278</v>
+        <v>778</v>
       </c>
       <c r="P836">
-        <v>2279</v>
+        <v>2057</v>
       </c>
       <c r="Q836" t="s">
         <v>129</v>
@@ -32136,34 +32171,37 @@
         <v>424</v>
       </c>
       <c r="B837">
-        <v>-35.620086000000001</v>
+        <v>-35.574167000000003</v>
       </c>
       <c r="C837">
-        <v>138.56635800000001</v>
+        <v>138.61528000000001</v>
       </c>
       <c r="D837" s="2">
         <v>46135</v>
       </c>
       <c r="E837" s="20">
-        <v>0.47708333333333336</v>
+        <v>0.49652777777777779</v>
       </c>
       <c r="G837">
+        <v>222</v>
+      </c>
+      <c r="I837">
         <v>56</v>
       </c>
       <c r="J837">
         <v>0</v>
       </c>
       <c r="L837">
-        <v>56</v>
+        <v>111</v>
       </c>
       <c r="N837">
-        <v>167</v>
+        <v>222</v>
       </c>
       <c r="O837">
-        <v>222</v>
+        <v>722</v>
       </c>
       <c r="P837">
-        <v>501</v>
+        <v>1333</v>
       </c>
       <c r="Q837" t="s">
         <v>129</v>
@@ -32171,385 +32209,391 @@
     </row>
     <row r="838" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A838" t="s">
-        <v>426</v>
+        <v>89</v>
       </c>
       <c r="B838">
-        <v>-35.591330800000001</v>
+        <v>-35.6048446</v>
       </c>
       <c r="C838">
-        <v>137.5061887</v>
+        <v>138.59278499999999</v>
       </c>
       <c r="D838" s="2">
-        <v>46136</v>
+        <v>46135</v>
       </c>
       <c r="E838" s="20">
-        <v>0.54166666666666663</v>
-      </c>
-      <c r="F838">
-        <v>0</v>
-      </c>
-      <c r="G838">
-        <v>0</v>
+        <v>0.48749999999999999</v>
       </c>
       <c r="H838">
-        <v>778</v>
+        <v>111</v>
       </c>
       <c r="I838">
-        <v>667</v>
+        <v>1667</v>
       </c>
       <c r="J838">
         <v>0</v>
       </c>
-      <c r="K838">
-        <v>0</v>
-      </c>
       <c r="L838">
-        <v>778</v>
-      </c>
-      <c r="M838">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="N838">
-        <v>0</v>
+        <v>167</v>
       </c>
       <c r="O838">
-        <v>0</v>
+        <v>278</v>
       </c>
       <c r="P838">
-        <v>2223</v>
+        <v>2279</v>
       </c>
       <c r="Q838" t="s">
-        <v>151</v>
+        <v>129</v>
       </c>
     </row>
     <row r="839" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A839" t="s">
-        <v>288</v>
+        <v>423</v>
       </c>
       <c r="B839">
-        <v>-34.629179999999998</v>
+        <v>-35.620086000000001</v>
       </c>
       <c r="C839">
-        <v>135.86635000000001</v>
+        <v>138.56635800000001</v>
       </c>
       <c r="D839" s="2">
-        <v>46136</v>
-      </c>
-      <c r="I839">
-        <v>160</v>
+        <v>46135</v>
+      </c>
+      <c r="E839" s="20">
+        <v>0.47708333333333336</v>
+      </c>
+      <c r="G839">
+        <v>56</v>
       </c>
       <c r="J839">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="L839">
-        <v>311</v>
+        <v>56</v>
+      </c>
+      <c r="N839">
+        <v>167</v>
       </c>
       <c r="O839">
-        <v>93</v>
+        <v>222</v>
       </c>
       <c r="P839">
-        <v>564</v>
+        <v>501</v>
       </c>
       <c r="Q839" t="s">
-        <v>283</v>
+        <v>129</v>
       </c>
     </row>
     <row r="840" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A840" t="s">
-        <v>339</v>
+        <v>425</v>
       </c>
       <c r="B840">
-        <v>-35.500242</v>
+        <v>-35.591330800000001</v>
       </c>
       <c r="C840">
-        <v>138.24491</v>
+        <v>137.5061887</v>
       </c>
       <c r="D840" s="2">
-        <v>46137</v>
+        <v>46136</v>
       </c>
       <c r="E840" s="20">
-        <v>0.39583333333333331</v>
+        <v>0.54166666666666663</v>
       </c>
       <c r="F840">
         <v>0</v>
       </c>
+      <c r="G840">
+        <v>0</v>
+      </c>
       <c r="H840">
-        <v>278</v>
+        <v>778</v>
       </c>
       <c r="I840">
-        <v>222</v>
+        <v>667</v>
       </c>
       <c r="J840">
         <v>0</v>
       </c>
+      <c r="K840">
+        <v>0</v>
+      </c>
       <c r="L840">
-        <v>1000</v>
+        <v>778</v>
+      </c>
+      <c r="M840">
+        <v>0</v>
       </c>
       <c r="N840">
-        <v>1056</v>
+        <v>0</v>
       </c>
       <c r="O840">
-        <v>222</v>
+        <v>0</v>
       </c>
       <c r="P840">
-        <v>2778</v>
+        <v>2223</v>
       </c>
       <c r="Q840" t="s">
-        <v>251</v>
+        <v>151</v>
       </c>
     </row>
     <row r="841" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A841" t="s">
-        <v>94</v>
+        <v>288</v>
       </c>
       <c r="B841">
-        <v>-35.58858</v>
+        <v>-34.629179999999998</v>
       </c>
       <c r="C841">
-        <v>138.60474600000001</v>
+        <v>135.86635000000001</v>
       </c>
       <c r="D841" s="2">
-        <v>46138</v>
+        <v>46136</v>
+      </c>
+      <c r="I841">
+        <v>160</v>
       </c>
       <c r="J841">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L841">
-        <v>167</v>
-      </c>
-      <c r="N841">
-        <v>278</v>
+        <v>311</v>
       </c>
       <c r="O841">
-        <v>833</v>
+        <v>93</v>
       </c>
       <c r="P841">
-        <v>1278</v>
+        <v>564</v>
       </c>
       <c r="Q841" t="s">
-        <v>129</v>
+        <v>283</v>
       </c>
     </row>
     <row r="842" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A842" t="s">
-        <v>89</v>
+        <v>338</v>
       </c>
       <c r="B842">
-        <v>-35.6048446</v>
+        <v>-35.500242</v>
       </c>
       <c r="C842">
-        <v>138.59278499999999</v>
+        <v>138.24491</v>
       </c>
       <c r="D842" s="2">
-        <v>46138</v>
-      </c>
-      <c r="G842">
-        <v>111</v>
+        <v>46137</v>
+      </c>
+      <c r="E842" s="20">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="F842">
+        <v>0</v>
+      </c>
+      <c r="H842">
+        <v>278</v>
+      </c>
+      <c r="I842">
+        <v>222</v>
       </c>
       <c r="J842">
         <v>0</v>
       </c>
       <c r="L842">
-        <v>56</v>
+        <v>1000</v>
       </c>
       <c r="N842">
-        <v>722</v>
+        <v>1056</v>
       </c>
       <c r="O842">
-        <v>944</v>
+        <v>222</v>
       </c>
       <c r="P842">
-        <v>1833</v>
+        <v>2778</v>
       </c>
       <c r="Q842" t="s">
-        <v>129</v>
+        <v>251</v>
       </c>
     </row>
     <row r="843" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A843" t="s">
-        <v>312</v>
+        <v>94</v>
       </c>
       <c r="B843">
-        <v>-35.445059999999998</v>
+        <v>-35.58858</v>
       </c>
       <c r="C843">
-        <v>138.30758399999999</v>
+        <v>138.60474600000001</v>
       </c>
       <c r="D843" s="2">
-        <v>46139</v>
-      </c>
-      <c r="E843" s="20">
-        <v>0.47916666666666669</v>
-      </c>
-      <c r="I843">
-        <v>0</v>
+        <v>46138</v>
       </c>
       <c r="J843">
         <v>0</v>
       </c>
       <c r="L843">
-        <v>611</v>
+        <v>167</v>
       </c>
       <c r="N843">
-        <v>0</v>
+        <v>278</v>
       </c>
       <c r="O843">
-        <v>56</v>
+        <v>833</v>
       </c>
       <c r="P843">
-        <v>667</v>
+        <v>1278</v>
       </c>
       <c r="Q843" t="s">
-        <v>350</v>
+        <v>129</v>
       </c>
     </row>
     <row r="844" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A844" t="s">
-        <v>427</v>
+        <v>89</v>
       </c>
       <c r="B844">
-        <v>-35.410254000000002</v>
+        <v>-35.6048446</v>
       </c>
       <c r="C844">
-        <v>138.32751999999999</v>
+        <v>138.59278499999999</v>
       </c>
       <c r="D844" s="2">
-        <v>46139</v>
-      </c>
-      <c r="E844" s="20">
-        <v>0.30208333333333331</v>
-      </c>
-      <c r="H844">
-        <v>0</v>
-      </c>
-      <c r="I844">
-        <v>0</v>
+        <v>46138</v>
+      </c>
+      <c r="G844">
+        <v>111</v>
       </c>
       <c r="J844">
         <v>0</v>
       </c>
-      <c r="K844">
-        <v>0</v>
-      </c>
       <c r="L844">
         <v>56</v>
       </c>
-      <c r="M844">
-        <v>0</v>
-      </c>
       <c r="N844">
-        <v>0</v>
+        <v>722</v>
+      </c>
+      <c r="O844">
+        <v>944</v>
       </c>
       <c r="P844">
-        <v>56</v>
+        <v>1833</v>
       </c>
       <c r="Q844" t="s">
-        <v>350</v>
+        <v>129</v>
       </c>
     </row>
     <row r="845" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A845" t="s">
-        <v>288</v>
+        <v>311</v>
       </c>
       <c r="B845">
-        <v>-34.629179999999998</v>
+        <v>-35.445059999999998</v>
       </c>
       <c r="C845">
-        <v>135.86635000000001</v>
+        <v>138.30758399999999</v>
       </c>
       <c r="D845" s="2">
-        <v>46141</v>
+        <v>46139</v>
+      </c>
+      <c r="E845" s="20">
+        <v>0.47916666666666669</v>
       </c>
       <c r="I845">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="J845">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L845">
-        <v>65</v>
+        <v>611</v>
       </c>
       <c r="N845">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="O845">
-        <v>259</v>
+        <v>56</v>
       </c>
       <c r="P845">
-        <v>426</v>
+        <v>667</v>
       </c>
       <c r="Q845" t="s">
-        <v>283</v>
+        <v>349</v>
       </c>
     </row>
     <row r="846" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A846" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B846">
-        <v>-34.891616999999997</v>
+        <v>-35.410254000000002</v>
       </c>
       <c r="C846">
-        <v>137.83265</v>
+        <v>138.32751999999999</v>
       </c>
       <c r="D846" s="2">
-        <v>46142</v>
+        <v>46139</v>
       </c>
       <c r="E846" s="20">
-        <v>0.40625</v>
+        <v>0.30208333333333331</v>
+      </c>
+      <c r="H846">
+        <v>0</v>
       </c>
       <c r="I846">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="J846">
         <v>0</v>
       </c>
+      <c r="K846">
+        <v>0</v>
+      </c>
       <c r="L846">
         <v>56</v>
       </c>
+      <c r="M846">
+        <v>0</v>
+      </c>
       <c r="N846">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="P846">
-        <v>168</v>
+        <v>56</v>
       </c>
       <c r="Q846" t="s">
-        <v>365</v>
+        <v>349</v>
       </c>
     </row>
     <row r="847" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A847" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B847">
-        <v>-34.628860000000003</v>
+        <v>-34.629179999999998</v>
       </c>
       <c r="C847">
-        <v>135.86708999999999</v>
+        <v>135.86635000000001</v>
       </c>
       <c r="D847" s="2">
-        <v>46143</v>
+        <v>46141</v>
       </c>
       <c r="I847">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="J847">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="L847">
-        <v>74</v>
-      </c>
-      <c r="M847">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="N847">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="O847">
-        <v>185</v>
+        <v>259</v>
       </c>
       <c r="P847">
-        <v>287</v>
+        <v>426</v>
       </c>
       <c r="Q847" t="s">
         <v>283</v>
@@ -32557,19 +32601,19 @@
     </row>
     <row r="848" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A848" t="s">
-        <v>152</v>
+        <v>427</v>
       </c>
       <c r="B848">
-        <v>-35.824725999999998</v>
+        <v>-34.891616999999997</v>
       </c>
       <c r="C848">
-        <v>137.75102200000001</v>
+        <v>137.83265</v>
       </c>
       <c r="D848" s="2">
-        <v>46145</v>
-      </c>
-      <c r="G848">
-        <v>56</v>
+        <v>46142</v>
+      </c>
+      <c r="E848" s="20">
+        <v>0.40625</v>
       </c>
       <c r="I848">
         <v>56</v>
@@ -32578,493 +32622,481 @@
         <v>0</v>
       </c>
       <c r="L848">
-        <v>278</v>
+        <v>56</v>
       </c>
       <c r="N848">
-        <v>333</v>
-      </c>
-      <c r="O848">
-        <v>2722</v>
+        <v>56</v>
       </c>
       <c r="P848">
-        <v>3445</v>
+        <v>168</v>
       </c>
       <c r="Q848" t="s">
-        <v>129</v>
+        <v>364</v>
       </c>
     </row>
     <row r="849" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A849" t="s">
-        <v>401</v>
+        <v>289</v>
       </c>
       <c r="B849">
-        <v>-35.510497000000001</v>
+        <v>-34.628860000000003</v>
       </c>
       <c r="C849">
-        <v>138.21676299999999</v>
+        <v>135.86708999999999</v>
       </c>
       <c r="D849" s="2">
-        <v>46146</v>
-      </c>
-      <c r="E849" s="20">
-        <v>0.3923611111111111</v>
+        <v>46143</v>
       </c>
       <c r="I849">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="J849">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="L849">
-        <v>111</v>
+        <v>74</v>
+      </c>
+      <c r="M849">
+        <v>0</v>
+      </c>
+      <c r="N849">
+        <v>0</v>
+      </c>
+      <c r="O849">
+        <v>185</v>
       </c>
       <c r="P849">
-        <v>111</v>
+        <v>287</v>
       </c>
       <c r="Q849" t="s">
-        <v>251</v>
+        <v>283</v>
       </c>
     </row>
     <row r="850" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A850" t="s">
-        <v>289</v>
+        <v>449</v>
       </c>
       <c r="B850">
-        <v>-34.628860000000003</v>
+        <v>-34.994472000000002</v>
       </c>
       <c r="C850">
-        <v>135.86708999999999</v>
+        <v>137.75879399999999</v>
       </c>
       <c r="D850" s="2">
-        <v>46146</v>
-      </c>
-      <c r="E850" s="20">
-        <v>0.375</v>
+        <v>46145</v>
+      </c>
+      <c r="E850" s="25">
+        <v>0.60416666666666663</v>
       </c>
       <c r="I850">
-        <v>15</v>
+        <v>111</v>
       </c>
       <c r="J850">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L850">
-        <v>25</v>
-      </c>
-      <c r="M850">
-        <v>0</v>
+        <v>222</v>
       </c>
       <c r="N850">
-        <v>0</v>
-      </c>
-      <c r="O850">
-        <v>6</v>
+        <v>1222</v>
       </c>
       <c r="P850">
-        <v>46</v>
+        <v>1556</v>
       </c>
       <c r="Q850" t="s">
-        <v>283</v>
+        <v>218</v>
       </c>
     </row>
     <row r="851" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A851" t="s">
-        <v>312</v>
+        <v>152</v>
       </c>
       <c r="B851">
-        <v>-35.445059999999998</v>
+        <v>-35.824725999999998</v>
       </c>
       <c r="C851">
-        <v>138.30758399999999</v>
+        <v>137.75102200000001</v>
       </c>
       <c r="D851" s="2">
-        <v>46147</v>
-      </c>
-      <c r="E851" s="20">
-        <v>0.375</v>
+        <v>46145</v>
+      </c>
+      <c r="G851">
+        <v>56</v>
       </c>
       <c r="I851">
+        <v>56</v>
+      </c>
+      <c r="J851">
+        <v>0</v>
+      </c>
+      <c r="L851">
+        <v>278</v>
+      </c>
+      <c r="N851">
         <v>333</v>
       </c>
-      <c r="J851">
-        <v>0</v>
-      </c>
-      <c r="L851">
-        <v>444</v>
-      </c>
-      <c r="N851">
-        <v>167</v>
-      </c>
       <c r="O851">
-        <v>56</v>
+        <v>2722</v>
       </c>
       <c r="P851">
-        <v>1000</v>
+        <v>3445</v>
       </c>
       <c r="Q851" t="s">
-        <v>350</v>
+        <v>129</v>
       </c>
     </row>
     <row r="852" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A852" t="s">
-        <v>94</v>
+        <v>400</v>
       </c>
       <c r="B852">
-        <v>-35.58858</v>
+        <v>-35.510497000000001</v>
       </c>
       <c r="C852">
-        <v>138.60474600000001</v>
+        <v>138.21676299999999</v>
       </c>
       <c r="D852" s="2">
-        <v>46147</v>
+        <v>46146</v>
+      </c>
+      <c r="E852" s="20">
+        <v>0.3923611111111111</v>
       </c>
       <c r="I852">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="J852">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="L852">
-        <v>333</v>
-      </c>
-      <c r="N852">
-        <v>222</v>
-      </c>
-      <c r="O852">
-        <v>556</v>
+        <v>111</v>
       </c>
       <c r="P852">
-        <v>1167</v>
+        <v>111</v>
       </c>
       <c r="Q852" t="s">
-        <v>129</v>
+        <v>251</v>
       </c>
     </row>
     <row r="853" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A853" t="s">
-        <v>89</v>
+        <v>289</v>
       </c>
       <c r="B853">
-        <v>-35.6048446</v>
+        <v>-34.628860000000003</v>
       </c>
       <c r="C853">
-        <v>138.59278499999999</v>
+        <v>135.86708999999999</v>
       </c>
       <c r="D853" s="2">
-        <v>46147</v>
+        <v>46146</v>
+      </c>
+      <c r="E853" s="20">
+        <v>0.375</v>
       </c>
       <c r="I853">
-        <v>56</v>
+        <v>15</v>
       </c>
       <c r="J853">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L853">
-        <v>389</v>
+        <v>25</v>
+      </c>
+      <c r="M853">
+        <v>0</v>
       </c>
       <c r="N853">
-        <v>389</v>
+        <v>0</v>
       </c>
       <c r="O853">
-        <v>944</v>
+        <v>6</v>
       </c>
       <c r="P853">
-        <v>1778</v>
+        <v>46</v>
       </c>
       <c r="Q853" t="s">
-        <v>129</v>
+        <v>283</v>
       </c>
     </row>
     <row r="854" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A854" t="s">
-        <v>422</v>
+        <v>311</v>
       </c>
       <c r="B854">
-        <v>-35.500024000000003</v>
+        <v>-35.445059999999998</v>
       </c>
       <c r="C854">
-        <v>138.24287699999999</v>
+        <v>138.30758399999999</v>
       </c>
       <c r="D854" s="2">
         <v>46147</v>
       </c>
       <c r="E854" s="20">
-        <v>0.48958333333333331</v>
-      </c>
-      <c r="F854">
-        <v>0</v>
-      </c>
-      <c r="H854">
-        <v>500</v>
+        <v>0.375</v>
       </c>
       <c r="I854">
-        <v>111</v>
+        <v>333</v>
       </c>
       <c r="J854">
         <v>0</v>
       </c>
-      <c r="K854">
-        <v>0</v>
-      </c>
       <c r="L854">
-        <v>278</v>
-      </c>
-      <c r="M854">
-        <v>0</v>
+        <v>444</v>
       </c>
       <c r="N854">
-        <v>2167</v>
+        <v>167</v>
       </c>
       <c r="O854">
-        <v>167</v>
+        <v>56</v>
       </c>
       <c r="P854">
-        <v>3223</v>
+        <v>1000</v>
       </c>
       <c r="Q854" t="s">
-        <v>251</v>
+        <v>349</v>
       </c>
     </row>
     <row r="855" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A855" t="s">
-        <v>59</v>
+        <v>94</v>
       </c>
       <c r="B855">
-        <v>-35.084850000000003</v>
+        <v>-35.58858</v>
       </c>
       <c r="C855">
-        <v>137.74889999999999</v>
+        <v>138.60474600000001</v>
       </c>
       <c r="D855" s="2">
-        <v>46148</v>
-      </c>
-      <c r="E855" s="20">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="G855">
-        <v>277</v>
-      </c>
-      <c r="H855">
-        <v>56</v>
+        <v>46147</v>
       </c>
       <c r="I855">
         <v>56</v>
       </c>
       <c r="J855">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="L855">
-        <v>0</v>
-      </c>
-      <c r="M855">
-        <v>0</v>
+        <v>333</v>
       </c>
       <c r="N855">
-        <v>444</v>
+        <v>222</v>
+      </c>
+      <c r="O855">
+        <v>556</v>
       </c>
       <c r="P855">
-        <v>833</v>
+        <v>1167</v>
       </c>
       <c r="Q855" t="s">
-        <v>149</v>
+        <v>129</v>
       </c>
     </row>
     <row r="856" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A856" t="s">
-        <v>427</v>
+        <v>89</v>
       </c>
       <c r="B856">
-        <v>-35.410254000000002</v>
+        <v>-35.6048446</v>
       </c>
       <c r="C856">
-        <v>138.32751999999999</v>
+        <v>138.59278499999999</v>
       </c>
       <c r="D856" s="2">
-        <v>46148</v>
-      </c>
-      <c r="E856" s="20">
-        <v>0.36458333333333331</v>
-      </c>
-      <c r="F856">
-        <v>0</v>
-      </c>
-      <c r="G856">
-        <v>0</v>
-      </c>
-      <c r="H856">
-        <v>722</v>
+        <v>46147</v>
       </c>
       <c r="I856">
-        <v>333</v>
+        <v>56</v>
       </c>
       <c r="J856">
         <v>0</v>
       </c>
-      <c r="K856">
-        <v>0</v>
-      </c>
       <c r="L856">
-        <v>667</v>
-      </c>
-      <c r="M856">
-        <v>0</v>
+        <v>389</v>
       </c>
       <c r="N856">
-        <v>3389</v>
+        <v>389</v>
       </c>
       <c r="O856">
-        <v>167</v>
+        <v>944</v>
       </c>
       <c r="P856">
-        <v>5278</v>
+        <v>1778</v>
       </c>
       <c r="Q856" t="s">
-        <v>350</v>
+        <v>129</v>
       </c>
     </row>
     <row r="857" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A857" t="s">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="B857">
-        <v>-34.54036</v>
+        <v>-35.500024000000003</v>
       </c>
       <c r="C857">
-        <v>135.93406999999999</v>
+        <v>138.24287699999999</v>
       </c>
       <c r="D857" s="2">
-        <v>46149</v>
+        <v>46147</v>
       </c>
       <c r="E857" s="20">
-        <v>0.53125</v>
+        <v>0.48958333333333331</v>
+      </c>
+      <c r="F857">
+        <v>0</v>
+      </c>
+      <c r="H857">
+        <v>500</v>
       </c>
       <c r="I857">
-        <v>17</v>
+        <v>111</v>
       </c>
       <c r="J857">
-        <v>6</v>
+        <v>0</v>
+      </c>
+      <c r="K857">
+        <v>0</v>
       </c>
       <c r="L857">
-        <v>9</v>
+        <v>278</v>
       </c>
       <c r="M857">
         <v>0</v>
       </c>
       <c r="N857">
-        <v>0</v>
+        <v>2167</v>
       </c>
       <c r="O857">
-        <v>3</v>
+        <v>167</v>
       </c>
       <c r="P857">
-        <v>29</v>
+        <v>3223</v>
       </c>
       <c r="Q857" t="s">
-        <v>283</v>
+        <v>251</v>
       </c>
     </row>
     <row r="858" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A858" t="s">
-        <v>94</v>
+        <v>59</v>
       </c>
       <c r="B858">
-        <v>-35.58858</v>
+        <v>-35.084850000000003</v>
       </c>
       <c r="C858">
-        <v>138.60474600000001</v>
+        <v>137.74889999999999</v>
       </c>
       <c r="D858" s="2">
-        <v>46152</v>
+        <v>46148</v>
+      </c>
+      <c r="E858" s="20">
+        <v>0.66666666666666663</v>
       </c>
       <c r="G858">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H858">
-        <v>167</v>
+        <v>56</v>
       </c>
       <c r="I858">
-        <v>333</v>
+        <v>56</v>
       </c>
       <c r="J858">
         <v>0</v>
       </c>
       <c r="L858">
-        <v>56</v>
+        <v>0</v>
+      </c>
+      <c r="M858">
+        <v>0</v>
       </c>
       <c r="N858">
-        <v>389</v>
-      </c>
-      <c r="O858">
-        <v>944</v>
+        <v>444</v>
       </c>
       <c r="P858">
-        <v>2167</v>
+        <v>833</v>
       </c>
       <c r="Q858" t="s">
-        <v>129</v>
+        <v>149</v>
       </c>
     </row>
     <row r="859" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A859" t="s">
-        <v>89</v>
+        <v>426</v>
       </c>
       <c r="B859">
-        <v>-35.6048446</v>
+        <v>-35.410254000000002</v>
       </c>
       <c r="C859">
-        <v>138.59278499999999</v>
+        <v>138.32751999999999</v>
       </c>
       <c r="D859" s="2">
-        <v>46152</v>
+        <v>46148</v>
+      </c>
+      <c r="E859" s="20">
+        <v>0.36458333333333331</v>
+      </c>
+      <c r="F859">
+        <v>0</v>
       </c>
       <c r="G859">
-        <v>111</v>
+        <v>0</v>
+      </c>
+      <c r="H859">
+        <v>722</v>
       </c>
       <c r="I859">
-        <v>56</v>
+        <v>333</v>
       </c>
       <c r="J859">
         <v>0</v>
       </c>
+      <c r="K859">
+        <v>0</v>
+      </c>
       <c r="L859">
+        <v>667</v>
+      </c>
+      <c r="M859">
+        <v>0</v>
+      </c>
+      <c r="N859">
+        <v>3389</v>
+      </c>
+      <c r="O859">
         <v>167</v>
       </c>
-      <c r="N859">
-        <v>667</v>
-      </c>
-      <c r="O859">
-        <v>944</v>
-      </c>
       <c r="P859">
-        <v>1945</v>
+        <v>5278</v>
       </c>
       <c r="Q859" t="s">
-        <v>129</v>
+        <v>349</v>
       </c>
     </row>
     <row r="860" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A860" t="s">
-        <v>289</v>
+        <v>428</v>
       </c>
       <c r="B860">
-        <v>-34.628860000000003</v>
+        <v>-34.54036</v>
       </c>
       <c r="C860">
-        <v>135.86708999999999</v>
+        <v>135.93406999999999</v>
       </c>
       <c r="D860" s="2">
-        <v>46152</v>
+        <v>46149</v>
       </c>
       <c r="E860" s="20">
-        <v>0.4375</v>
+        <v>0.53125</v>
       </c>
       <c r="I860">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J860">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="L860">
-        <v>63</v>
+        <v>9</v>
       </c>
       <c r="M860">
         <v>0</v>
@@ -33073,10 +33105,10 @@
         <v>0</v>
       </c>
       <c r="O860">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P860">
-        <v>83</v>
+        <v>29</v>
       </c>
       <c r="Q860" t="s">
         <v>283</v>
@@ -33084,348 +33116,336 @@
     </row>
     <row r="861" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A861" t="s">
-        <v>430</v>
+        <v>94</v>
       </c>
       <c r="B861">
-        <v>-35.472737000000002</v>
+        <v>-35.58858</v>
       </c>
       <c r="C861">
-        <v>138.28932900000001</v>
+        <v>138.60474600000001</v>
       </c>
       <c r="D861" s="2">
         <v>46152</v>
       </c>
-      <c r="E861" s="20">
-        <v>0.36458333333333331</v>
-      </c>
-      <c r="F861">
-        <v>0</v>
-      </c>
       <c r="G861">
-        <v>0</v>
+        <v>278</v>
       </c>
       <c r="H861">
         <v>167</v>
       </c>
       <c r="I861">
-        <v>0</v>
+        <v>333</v>
       </c>
       <c r="J861">
         <v>0</v>
       </c>
-      <c r="K861">
-        <v>0</v>
-      </c>
       <c r="L861">
-        <v>333</v>
-      </c>
-      <c r="M861">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="N861">
-        <v>611</v>
+        <v>389</v>
       </c>
       <c r="O861">
-        <v>167</v>
+        <v>944</v>
       </c>
       <c r="P861">
-        <v>1278</v>
+        <v>2167</v>
       </c>
       <c r="Q861" t="s">
-        <v>251</v>
+        <v>129</v>
       </c>
     </row>
     <row r="862" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A862" t="s">
-        <v>289</v>
+        <v>89</v>
       </c>
       <c r="B862">
-        <v>-34.628860000000003</v>
+        <v>-35.6048446</v>
       </c>
       <c r="C862">
-        <v>135.86708999999999</v>
+        <v>138.59278499999999</v>
       </c>
       <c r="D862" s="2">
-        <v>46153</v>
-      </c>
-      <c r="E862" s="20">
-        <v>0.29166666666666669</v>
+        <v>46152</v>
+      </c>
+      <c r="G862">
+        <v>111</v>
       </c>
       <c r="I862">
-        <v>17</v>
+        <v>56</v>
       </c>
       <c r="J862">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="L862">
-        <v>56</v>
-      </c>
-      <c r="M862">
-        <v>0</v>
+        <v>167</v>
       </c>
       <c r="N862">
-        <v>0</v>
+        <v>667</v>
       </c>
       <c r="O862">
-        <v>6</v>
+        <v>944</v>
       </c>
       <c r="P862">
-        <v>79</v>
+        <v>1945</v>
       </c>
       <c r="Q862" t="s">
-        <v>283</v>
+        <v>129</v>
       </c>
     </row>
     <row r="863" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A863" t="s">
-        <v>312</v>
+        <v>289</v>
       </c>
       <c r="B863">
-        <v>-35.445059999999998</v>
+        <v>-34.628860000000003</v>
       </c>
       <c r="C863">
-        <v>138.30758399999999</v>
+        <v>135.86708999999999</v>
       </c>
       <c r="D863" s="2">
-        <v>46153</v>
+        <v>46152</v>
       </c>
       <c r="E863" s="20">
-        <v>0.375</v>
-      </c>
-      <c r="F863">
-        <v>0</v>
-      </c>
-      <c r="G863">
-        <v>0</v>
-      </c>
-      <c r="H863">
-        <v>56</v>
+        <v>0.4375</v>
       </c>
       <c r="I863">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="J863">
-        <v>0</v>
-      </c>
-      <c r="K863">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L863">
-        <v>111</v>
+        <v>63</v>
       </c>
       <c r="M863">
         <v>0</v>
       </c>
       <c r="N863">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="O863">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P863">
-        <v>278</v>
+        <v>83</v>
       </c>
       <c r="Q863" t="s">
-        <v>402</v>
+        <v>283</v>
       </c>
     </row>
     <row r="864" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A864" t="s">
-        <v>86</v>
+        <v>429</v>
       </c>
       <c r="B864">
-        <v>-35.540277000000003</v>
+        <v>-35.472737000000002</v>
       </c>
       <c r="C864">
-        <v>138.66416599999999</v>
+        <v>138.28932900000001</v>
       </c>
       <c r="D864" s="2">
-        <v>46154</v>
+        <v>46152</v>
       </c>
       <c r="E864" s="20">
-        <v>0.35972222222222222</v>
+        <v>0.36458333333333331</v>
+      </c>
+      <c r="F864">
+        <v>0</v>
       </c>
       <c r="G864">
-        <v>56</v>
+        <v>0</v>
+      </c>
+      <c r="H864">
+        <v>167</v>
+      </c>
+      <c r="I864">
+        <v>0</v>
       </c>
       <c r="J864">
         <v>0</v>
       </c>
+      <c r="K864">
+        <v>0</v>
+      </c>
+      <c r="L864">
+        <v>333</v>
+      </c>
+      <c r="M864">
+        <v>0</v>
+      </c>
       <c r="N864">
-        <v>444</v>
+        <v>611</v>
       </c>
       <c r="O864">
-        <v>278</v>
+        <v>167</v>
       </c>
       <c r="P864">
-        <v>778</v>
+        <v>1278</v>
       </c>
       <c r="Q864" t="s">
-        <v>129</v>
+        <v>251</v>
       </c>
     </row>
     <row r="865" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A865" t="s">
-        <v>100</v>
+        <v>230</v>
       </c>
       <c r="B865">
-        <v>-35.536745000000003</v>
+        <v>-35.054707999999998</v>
       </c>
       <c r="C865">
-        <v>138.6913744</v>
+        <v>137.725145</v>
       </c>
       <c r="D865" s="2">
-        <v>46154</v>
-      </c>
-      <c r="E865" s="20">
-        <v>0.36666666666666664</v>
+        <v>46152</v>
+      </c>
+      <c r="E865" s="25">
+        <v>0.71875</v>
       </c>
       <c r="I865">
-        <v>167</v>
+        <v>119000</v>
       </c>
       <c r="J865">
         <v>0</v>
       </c>
       <c r="L865">
-        <v>7000</v>
-      </c>
-      <c r="M865">
-        <v>167</v>
-      </c>
-      <c r="N865">
-        <v>222</v>
+        <v>2667</v>
       </c>
       <c r="O865">
-        <v>1667</v>
+        <v>333</v>
       </c>
       <c r="P865">
-        <v>9223</v>
+        <v>122000</v>
       </c>
       <c r="Q865" t="s">
-        <v>129</v>
+        <v>218</v>
       </c>
     </row>
     <row r="866" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A866" t="s">
-        <v>431</v>
+        <v>289</v>
       </c>
       <c r="B866">
-        <v>-35.534041000000002</v>
+        <v>-34.628860000000003</v>
       </c>
       <c r="C866">
-        <v>138.688445</v>
+        <v>135.86708999999999</v>
       </c>
       <c r="D866" s="2">
-        <v>46154</v>
+        <v>46153</v>
       </c>
       <c r="E866" s="20">
-        <v>0.37152777777777779</v>
-      </c>
-      <c r="H866">
-        <v>111</v>
+        <v>0.29166666666666669</v>
       </c>
       <c r="I866">
-        <v>2722</v>
+        <v>17</v>
       </c>
       <c r="J866">
+        <v>13</v>
+      </c>
+      <c r="L866">
+        <v>56</v>
+      </c>
+      <c r="M866">
         <v>0</v>
       </c>
       <c r="N866">
-        <v>222</v>
+        <v>0</v>
       </c>
       <c r="O866">
-        <v>833</v>
+        <v>6</v>
       </c>
       <c r="P866">
-        <v>3888</v>
+        <v>79</v>
       </c>
       <c r="Q866" t="s">
-        <v>129</v>
+        <v>283</v>
       </c>
     </row>
     <row r="867" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A867" t="s">
-        <v>87</v>
+        <v>311</v>
       </c>
       <c r="B867">
-        <v>-35.573300000000003</v>
+        <v>-35.445059999999998</v>
       </c>
       <c r="C867">
-        <v>138.64250000000001</v>
+        <v>138.30758399999999</v>
       </c>
       <c r="D867" s="2">
-        <v>46154</v>
+        <v>46153</v>
       </c>
       <c r="E867" s="20">
-        <v>0.38541666666666669</v>
+        <v>0.375</v>
+      </c>
+      <c r="F867">
+        <v>0</v>
       </c>
       <c r="G867">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="H867">
+        <v>56</v>
+      </c>
+      <c r="I867">
+        <v>0</v>
+      </c>
+      <c r="J867">
+        <v>0</v>
+      </c>
+      <c r="K867">
+        <v>0</v>
+      </c>
+      <c r="L867">
         <v>111</v>
       </c>
-      <c r="I867">
+      <c r="M867">
+        <v>0</v>
+      </c>
+      <c r="N867">
         <v>111</v>
       </c>
-      <c r="J867">
-        <v>0</v>
-      </c>
-      <c r="K867">
-        <v>56</v>
-      </c>
-      <c r="L867">
-        <v>2112</v>
-      </c>
-      <c r="N867">
-        <v>389</v>
-      </c>
       <c r="O867">
-        <v>833</v>
+        <v>0</v>
       </c>
       <c r="P867">
-        <v>3668</v>
+        <v>278</v>
       </c>
       <c r="Q867" t="s">
-        <v>129</v>
+        <v>401</v>
       </c>
     </row>
     <row r="868" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A868" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B868">
-        <v>-35.581124000000003</v>
+        <v>-35.540277000000003</v>
       </c>
       <c r="C868">
-        <v>138.60879700000001</v>
+        <v>138.66416599999999</v>
       </c>
       <c r="D868" s="2">
         <v>46154</v>
       </c>
       <c r="E868" s="20">
-        <v>0.39583333333333331</v>
+        <v>0.35972222222222222</v>
       </c>
       <c r="G868">
         <v>56</v>
       </c>
-      <c r="H868">
-        <v>167</v>
-      </c>
       <c r="J868">
         <v>0</v>
-      </c>
-      <c r="K868">
-        <v>56</v>
       </c>
       <c r="N868">
         <v>444</v>
       </c>
       <c r="O868">
-        <v>167</v>
+        <v>278</v>
       </c>
       <c r="P868">
-        <v>890</v>
+        <v>778</v>
       </c>
       <c r="Q868" t="s">
         <v>129</v>
@@ -33433,43 +33453,40 @@
     </row>
     <row r="869" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A869" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="B869">
-        <v>-35.6048446</v>
+        <v>-35.536745000000003</v>
       </c>
       <c r="C869">
-        <v>138.59278499999999</v>
+        <v>138.6913744</v>
       </c>
       <c r="D869" s="2">
         <v>46154</v>
       </c>
       <c r="E869" s="20">
-        <v>0.40625</v>
-      </c>
-      <c r="G869">
-        <v>56</v>
+        <v>0.36666666666666664</v>
       </c>
       <c r="I869">
-        <v>111</v>
+        <v>167</v>
       </c>
       <c r="J869">
         <v>0</v>
       </c>
-      <c r="K869">
-        <v>56</v>
-      </c>
       <c r="L869">
-        <v>56</v>
+        <v>7000</v>
+      </c>
+      <c r="M869">
+        <v>167</v>
       </c>
       <c r="N869">
         <v>222</v>
       </c>
       <c r="O869">
-        <v>278</v>
+        <v>1667</v>
       </c>
       <c r="P869">
-        <v>779</v>
+        <v>9223</v>
       </c>
       <c r="Q869" t="s">
         <v>129</v>
@@ -33477,43 +33494,37 @@
     </row>
     <row r="870" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A870" t="s">
-        <v>375</v>
+        <v>430</v>
       </c>
       <c r="B870">
-        <v>-35.612285999999997</v>
+        <v>-35.534041000000002</v>
       </c>
       <c r="C870">
-        <v>138.564302</v>
+        <v>138.688445</v>
       </c>
       <c r="D870" s="2">
         <v>46154</v>
       </c>
       <c r="E870" s="20">
-        <v>0.4152777777777778</v>
+        <v>0.37152777777777779</v>
       </c>
       <c r="H870">
-        <v>167</v>
+        <v>111</v>
       </c>
       <c r="I870">
-        <v>500</v>
+        <v>2722</v>
       </c>
       <c r="J870">
         <v>0</v>
       </c>
-      <c r="K870">
-        <v>56</v>
-      </c>
-      <c r="L870">
-        <v>56</v>
-      </c>
       <c r="N870">
-        <v>778</v>
+        <v>222</v>
       </c>
       <c r="O870">
-        <v>1111</v>
+        <v>833</v>
       </c>
       <c r="P870">
-        <v>2668</v>
+        <v>3888</v>
       </c>
       <c r="Q870" t="s">
         <v>129</v>
@@ -33521,22 +33532,25 @@
     </row>
     <row r="871" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A871" t="s">
-        <v>432</v>
+        <v>87</v>
       </c>
       <c r="B871">
-        <v>-35.619</v>
+        <v>-35.573300000000003</v>
       </c>
       <c r="C871">
-        <v>138.58099999999999</v>
+        <v>138.64250000000001</v>
       </c>
       <c r="D871" s="2">
         <v>46154</v>
       </c>
       <c r="E871" s="20">
-        <v>0.4201388888888889</v>
+        <v>0.38541666666666669</v>
+      </c>
+      <c r="G871">
+        <v>56</v>
       </c>
       <c r="H871">
-        <v>56</v>
+        <v>111</v>
       </c>
       <c r="I871">
         <v>111</v>
@@ -33544,14 +33558,20 @@
       <c r="J871">
         <v>0</v>
       </c>
+      <c r="K871">
+        <v>56</v>
+      </c>
+      <c r="L871">
+        <v>2112</v>
+      </c>
       <c r="N871">
-        <v>611</v>
+        <v>389</v>
       </c>
       <c r="O871">
-        <v>333</v>
+        <v>833</v>
       </c>
       <c r="P871">
-        <v>1111</v>
+        <v>3668</v>
       </c>
       <c r="Q871" t="s">
         <v>129</v>
@@ -33559,198 +33579,186 @@
     </row>
     <row r="872" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A872" t="s">
-        <v>422</v>
+        <v>88</v>
       </c>
       <c r="B872">
-        <v>-35.500024000000003</v>
+        <v>-35.581124000000003</v>
       </c>
       <c r="C872">
-        <v>138.24287699999999</v>
+        <v>138.60879700000001</v>
       </c>
       <c r="D872" s="2">
         <v>46154</v>
       </c>
       <c r="E872" s="20">
-        <v>0.67013888888888884</v>
-      </c>
-      <c r="F872">
-        <v>0</v>
+        <v>0.39583333333333331</v>
       </c>
       <c r="G872">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="H872">
-        <v>7222</v>
-      </c>
-      <c r="I872">
-        <v>889</v>
+        <v>167</v>
       </c>
       <c r="J872">
         <v>0</v>
       </c>
       <c r="K872">
-        <v>0</v>
-      </c>
-      <c r="L872">
+        <v>56</v>
+      </c>
+      <c r="N872">
+        <v>444</v>
+      </c>
+      <c r="O872">
         <v>167</v>
       </c>
-      <c r="M872">
-        <v>0</v>
-      </c>
-      <c r="N872">
-        <v>2500</v>
-      </c>
-      <c r="O872">
-        <v>278</v>
-      </c>
       <c r="P872">
-        <v>11056</v>
+        <v>890</v>
       </c>
       <c r="Q872" t="s">
-        <v>251</v>
+        <v>129</v>
       </c>
     </row>
     <row r="873" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A873" t="s">
-        <v>59</v>
+        <v>89</v>
       </c>
       <c r="B873">
-        <v>-35.084850000000003</v>
+        <v>-35.6048446</v>
       </c>
       <c r="C873">
-        <v>137.74889999999999</v>
+        <v>138.59278499999999</v>
       </c>
       <c r="D873" s="2">
-        <v>46155</v>
+        <v>46154</v>
       </c>
       <c r="E873" s="20">
-        <v>0.70833333333333337</v>
+        <v>0.40625</v>
       </c>
       <c r="G873">
-        <v>277</v>
+        <v>56</v>
+      </c>
+      <c r="I873">
+        <v>111</v>
       </c>
       <c r="J873">
         <v>0</v>
       </c>
+      <c r="K873">
+        <v>56</v>
+      </c>
       <c r="L873">
-        <v>0</v>
-      </c>
-      <c r="M873">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="N873">
-        <v>333</v>
+        <v>222</v>
+      </c>
+      <c r="O873">
+        <v>278</v>
       </c>
       <c r="P873">
-        <v>610</v>
+        <v>779</v>
       </c>
       <c r="Q873" t="s">
-        <v>149</v>
+        <v>129</v>
       </c>
     </row>
     <row r="874" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A874" t="s">
-        <v>289</v>
+        <v>374</v>
       </c>
       <c r="B874">
-        <v>-34.628860000000003</v>
+        <v>-35.612285999999997</v>
       </c>
       <c r="C874">
-        <v>135.86708999999999</v>
+        <v>138.564302</v>
       </c>
       <c r="D874" s="2">
-        <v>46155</v>
+        <v>46154</v>
       </c>
       <c r="E874" s="20">
-        <v>0.33333333333333331</v>
+        <v>0.4152777777777778</v>
+      </c>
+      <c r="H874">
+        <v>167</v>
       </c>
       <c r="I874">
-        <v>17</v>
+        <v>500</v>
       </c>
       <c r="J874">
         <v>0</v>
       </c>
+      <c r="K874">
+        <v>56</v>
+      </c>
       <c r="L874">
-        <v>33</v>
+        <v>56</v>
+      </c>
+      <c r="N874">
+        <v>778</v>
       </c>
       <c r="O874">
-        <v>0</v>
+        <v>1111</v>
       </c>
       <c r="P874">
-        <v>50</v>
+        <v>2668</v>
       </c>
       <c r="Q874" t="s">
-        <v>283</v>
+        <v>129</v>
       </c>
     </row>
     <row r="875" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A875" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B875">
-        <v>-35.297930000000001</v>
+        <v>-35.619</v>
       </c>
       <c r="C875">
-        <v>138.14122</v>
+        <v>138.58099999999999</v>
       </c>
       <c r="D875" s="2">
-        <v>46159</v>
+        <v>46154</v>
       </c>
       <c r="E875" s="20">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="F875">
-        <v>0</v>
-      </c>
-      <c r="G875">
-        <v>0</v>
+        <v>0.4201388888888889</v>
       </c>
       <c r="H875">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="I875">
-        <v>56</v>
+        <v>111</v>
       </c>
       <c r="J875">
         <v>0</v>
       </c>
-      <c r="K875">
-        <v>0</v>
-      </c>
-      <c r="L875">
-        <v>111</v>
-      </c>
-      <c r="M875">
-        <v>0</v>
-      </c>
       <c r="N875">
-        <v>111</v>
+        <v>611</v>
       </c>
       <c r="O875">
-        <v>56</v>
+        <v>333</v>
       </c>
       <c r="P875">
-        <v>334</v>
+        <v>1111</v>
       </c>
       <c r="Q875" t="s">
-        <v>350</v>
+        <v>129</v>
       </c>
     </row>
     <row r="876" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A876" t="s">
-        <v>312</v>
+        <v>421</v>
       </c>
       <c r="B876">
-        <v>-35.445059999999998</v>
+        <v>-35.500024000000003</v>
       </c>
       <c r="C876">
-        <v>138.30758399999999</v>
+        <v>138.24287699999999</v>
       </c>
       <c r="D876" s="2">
-        <v>46160</v>
+        <v>46154</v>
       </c>
       <c r="E876" s="20">
-        <v>0.33333333333333331</v>
+        <v>0.67013888888888884</v>
       </c>
       <c r="F876">
         <v>0</v>
@@ -33759,10 +33767,10 @@
         <v>0</v>
       </c>
       <c r="H876">
-        <v>0</v>
+        <v>7222</v>
       </c>
       <c r="I876">
-        <v>56</v>
+        <v>889</v>
       </c>
       <c r="J876">
         <v>0</v>
@@ -33771,58 +33779,46 @@
         <v>0</v>
       </c>
       <c r="L876">
-        <v>389</v>
+        <v>167</v>
       </c>
       <c r="M876">
         <v>0</v>
       </c>
       <c r="N876">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="O876">
-        <v>56</v>
+        <v>278</v>
       </c>
       <c r="P876">
-        <v>501</v>
+        <v>11056</v>
       </c>
       <c r="Q876" t="s">
-        <v>350</v>
+        <v>251</v>
       </c>
     </row>
     <row r="877" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A877" t="s">
-        <v>427</v>
+        <v>59</v>
       </c>
       <c r="B877">
-        <v>-35.410254000000002</v>
+        <v>-35.084850000000003</v>
       </c>
       <c r="C877">
-        <v>138.32751999999999</v>
+        <v>137.74889999999999</v>
       </c>
       <c r="D877" s="2">
-        <v>46160</v>
+        <v>46155</v>
       </c>
       <c r="E877" s="20">
-        <v>0.46875</v>
-      </c>
-      <c r="F877">
-        <v>0</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="G877">
-        <v>0</v>
-      </c>
-      <c r="H877">
-        <v>56</v>
-      </c>
-      <c r="I877">
-        <v>56</v>
+        <v>277</v>
       </c>
       <c r="J877">
         <v>0</v>
       </c>
-      <c r="K877">
-        <v>0</v>
-      </c>
       <c r="L877">
         <v>0</v>
       </c>
@@ -33830,217 +33826,235 @@
         <v>0</v>
       </c>
       <c r="N877">
-        <v>56</v>
-      </c>
-      <c r="O877">
-        <v>0</v>
+        <v>333</v>
       </c>
       <c r="P877">
-        <v>168</v>
+        <v>610</v>
       </c>
       <c r="Q877" t="s">
-        <v>350</v>
+        <v>149</v>
       </c>
     </row>
     <row r="878" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A878" t="s">
-        <v>59</v>
+        <v>289</v>
       </c>
       <c r="B878">
-        <v>-35.084850000000003</v>
+        <v>-34.628860000000003</v>
       </c>
       <c r="C878">
-        <v>137.74889999999999</v>
+        <v>135.86708999999999</v>
       </c>
       <c r="D878" s="2">
-        <v>46162</v>
+        <v>46155</v>
       </c>
       <c r="E878" s="20">
-        <v>0.5</v>
-      </c>
-      <c r="H878">
-        <v>56</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="I878">
-        <v>56</v>
+        <v>17</v>
       </c>
       <c r="J878">
         <v>0</v>
       </c>
       <c r="L878">
-        <v>0</v>
-      </c>
-      <c r="M878">
-        <v>0</v>
-      </c>
-      <c r="N878">
-        <v>722</v>
+        <v>33</v>
+      </c>
+      <c r="O878">
+        <v>0</v>
       </c>
       <c r="P878">
-        <v>834</v>
+        <v>50</v>
       </c>
       <c r="Q878" t="s">
-        <v>149</v>
+        <v>283</v>
       </c>
     </row>
     <row r="879" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A879" t="s">
-        <v>434</v>
+        <v>267</v>
       </c>
       <c r="B879">
-        <v>-34.116680000000002</v>
+        <v>-34.824044999999998</v>
       </c>
       <c r="C879">
-        <v>136.35397</v>
+        <v>138.48377600000001</v>
       </c>
       <c r="D879" s="2">
-        <v>46162</v>
+        <v>46157</v>
       </c>
       <c r="E879" s="20">
-        <v>0.51041666666666663</v>
+        <v>0.50694444444444442</v>
+      </c>
+      <c r="G879">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="H879">
+        <v>0.3</v>
       </c>
       <c r="I879">
-        <v>4</v>
+        <v>2.625</v>
       </c>
       <c r="J879">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L879">
-        <v>2</v>
+        <v>34.5</v>
       </c>
       <c r="O879">
-        <v>3</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="P879">
-        <v>9</v>
+        <v>37.575000000000003</v>
       </c>
       <c r="Q879" t="s">
-        <v>283</v>
+        <v>78</v>
       </c>
     </row>
     <row r="880" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A880" t="s">
-        <v>289</v>
+        <v>348</v>
       </c>
       <c r="B880">
-        <v>-34.628860000000003</v>
+        <v>-34.860666999999999</v>
       </c>
       <c r="C880">
-        <v>135.86708999999999</v>
+        <v>138.490938</v>
       </c>
       <c r="D880" s="2">
-        <v>46163</v>
+        <v>46157</v>
       </c>
       <c r="E880" s="20">
-        <v>0.67708333333333337</v>
+        <v>0.53472222222222221</v>
+      </c>
+      <c r="H880">
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="I880">
-        <v>74</v>
+        <v>11.1</v>
       </c>
       <c r="J880">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="L880">
-        <v>13</v>
-      </c>
-      <c r="M880">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="N880">
-        <v>0</v>
-      </c>
-      <c r="O880">
-        <v>4</v>
+        <v>0.3</v>
       </c>
       <c r="P880">
-        <v>91</v>
+        <v>21.074999999999999</v>
       </c>
       <c r="Q880" t="s">
-        <v>283</v>
+        <v>78</v>
       </c>
     </row>
     <row r="881" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A881" t="s">
-        <v>435</v>
+        <v>79</v>
       </c>
       <c r="B881">
-        <v>-34.540179999999999</v>
+        <v>-34.804662999999998</v>
       </c>
       <c r="C881">
-        <v>135.93411</v>
+        <v>138.540223</v>
       </c>
       <c r="D881" s="2">
-        <v>46165</v>
+        <v>46157</v>
       </c>
       <c r="E881" s="20">
-        <v>0.54166666666666663</v>
+        <v>0.48958333333333331</v>
       </c>
       <c r="I881">
-        <v>38</v>
+        <v>0.6</v>
       </c>
       <c r="J881">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="L881">
-        <v>73</v>
+        <v>5.9</v>
+      </c>
+      <c r="N881">
+        <v>0.05</v>
+      </c>
+      <c r="O881">
+        <v>0.1</v>
       </c>
       <c r="P881">
-        <v>111</v>
+        <v>6.6499999999999995</v>
       </c>
       <c r="Q881" t="s">
-        <v>283</v>
+        <v>78</v>
       </c>
     </row>
     <row r="882" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A882" t="s">
-        <v>289</v>
+        <v>432</v>
       </c>
       <c r="B882">
-        <v>-34.628860000000003</v>
+        <v>-35.297930000000001</v>
       </c>
       <c r="C882">
-        <v>135.86708999999999</v>
+        <v>138.14122</v>
       </c>
       <c r="D882" s="2">
-        <v>46166</v>
+        <v>46159</v>
       </c>
       <c r="E882" s="20">
-        <v>0.45833333333333331</v>
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="F882">
+        <v>0</v>
+      </c>
+      <c r="G882">
+        <v>0</v>
+      </c>
+      <c r="H882">
+        <v>0</v>
       </c>
       <c r="I882">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="J882">
-        <v>9</v>
+        <v>0</v>
+      </c>
+      <c r="K882">
+        <v>0</v>
       </c>
       <c r="L882">
-        <v>22</v>
+        <v>111</v>
+      </c>
+      <c r="M882">
+        <v>0</v>
+      </c>
+      <c r="N882">
+        <v>111</v>
       </c>
       <c r="O882">
-        <v>6</v>
+        <v>56</v>
       </c>
       <c r="P882">
-        <v>44</v>
+        <v>334</v>
       </c>
       <c r="Q882" t="s">
-        <v>283</v>
+        <v>349</v>
       </c>
     </row>
     <row r="883" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A883" t="s">
-        <v>437</v>
+        <v>311</v>
       </c>
       <c r="B883">
-        <v>-35.521467000000001</v>
+        <v>-35.445059999999998</v>
       </c>
       <c r="C883">
-        <v>138.18532999999999</v>
+        <v>138.30758399999999</v>
       </c>
       <c r="D883" s="2">
-        <v>46166</v>
+        <v>46160</v>
       </c>
       <c r="E883" s="20">
-        <v>0.4375</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="F883">
         <v>0</v>
@@ -34049,10 +34063,10 @@
         <v>0</v>
       </c>
       <c r="H883">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="I883">
-        <v>111</v>
+        <v>56</v>
       </c>
       <c r="J883">
         <v>0</v>
@@ -34061,39 +34075,39 @@
         <v>0</v>
       </c>
       <c r="L883">
-        <v>56</v>
+        <v>389</v>
       </c>
       <c r="M883">
         <v>0</v>
       </c>
       <c r="N883">
-        <v>444</v>
+        <v>0</v>
       </c>
       <c r="O883">
-        <v>167</v>
+        <v>56</v>
       </c>
       <c r="P883">
-        <v>834</v>
+        <v>501</v>
       </c>
       <c r="Q883" t="s">
-        <v>251</v>
+        <v>349</v>
       </c>
     </row>
     <row r="884" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A884" t="s">
-        <v>312</v>
+        <v>426</v>
       </c>
       <c r="B884">
-        <v>-35.445059999999998</v>
+        <v>-35.410254000000002</v>
       </c>
       <c r="C884">
-        <v>138.30758399999999</v>
+        <v>138.32751999999999</v>
       </c>
       <c r="D884" s="2">
-        <v>46167</v>
+        <v>46160</v>
       </c>
       <c r="E884" s="20">
-        <v>0.39583333333333331</v>
+        <v>0.46875</v>
       </c>
       <c r="F884">
         <v>0</v>
@@ -34102,7 +34116,7 @@
         <v>0</v>
       </c>
       <c r="H884">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="I884">
         <v>56</v>
@@ -34114,7 +34128,7 @@
         <v>0</v>
       </c>
       <c r="L884">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="M884">
         <v>0</v>
@@ -34123,180 +34137,159 @@
         <v>56</v>
       </c>
       <c r="O884">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="P884">
-        <v>224</v>
+        <v>168</v>
       </c>
       <c r="Q884" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="885" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A885" t="s">
-        <v>436</v>
+        <v>59</v>
       </c>
       <c r="B885">
-        <v>-34.377519999999997</v>
+        <v>-35.084850000000003</v>
       </c>
       <c r="C885">
-        <v>136.10475</v>
+        <v>137.74889999999999</v>
       </c>
       <c r="D885" s="2">
-        <v>46168</v>
+        <v>46162</v>
       </c>
       <c r="E885" s="20">
-        <v>0.41666666666666669</v>
+        <v>0.5</v>
+      </c>
+      <c r="H885">
+        <v>56</v>
       </c>
       <c r="I885">
-        <v>20</v>
+        <v>56</v>
       </c>
       <c r="J885">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L885">
-        <v>2</v>
-      </c>
-      <c r="O885">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="M885">
+        <v>0</v>
+      </c>
+      <c r="N885">
+        <v>722</v>
       </c>
       <c r="P885">
-        <v>26</v>
+        <v>834</v>
       </c>
       <c r="Q885" t="s">
-        <v>283</v>
+        <v>149</v>
       </c>
     </row>
     <row r="886" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A886" t="s">
-        <v>59</v>
+        <v>433</v>
       </c>
       <c r="B886">
-        <v>-35.084850000000003</v>
+        <v>-34.116680000000002</v>
       </c>
       <c r="C886">
-        <v>137.74889999999999</v>
+        <v>136.35397</v>
       </c>
       <c r="D886" s="2">
-        <v>46169</v>
+        <v>46162</v>
       </c>
       <c r="E886" s="20">
-        <v>0.5</v>
-      </c>
-      <c r="G886">
-        <v>111</v>
-      </c>
-      <c r="H886">
-        <v>167</v>
+        <v>0.51041666666666663</v>
       </c>
       <c r="I886">
-        <v>333</v>
+        <v>4</v>
       </c>
       <c r="J886">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L886">
-        <v>111</v>
-      </c>
-      <c r="M886">
-        <v>0</v>
-      </c>
-      <c r="N886">
-        <v>1000</v>
+        <v>2</v>
       </c>
       <c r="O886">
-        <v>167</v>
+        <v>3</v>
       </c>
       <c r="P886">
-        <v>1889</v>
+        <v>9</v>
       </c>
       <c r="Q886" t="s">
-        <v>149</v>
+        <v>283</v>
       </c>
     </row>
     <row r="887" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A887" t="s">
-        <v>427</v>
+        <v>289</v>
       </c>
       <c r="B887">
-        <v>-35.410254000000002</v>
+        <v>-34.628860000000003</v>
       </c>
       <c r="C887">
-        <v>138.32751999999999</v>
+        <v>135.86708999999999</v>
       </c>
       <c r="D887" s="2">
-        <v>46169</v>
+        <v>46163</v>
       </c>
       <c r="E887" s="20">
-        <v>0.4375</v>
-      </c>
-      <c r="F887">
-        <v>0</v>
-      </c>
-      <c r="G887">
-        <v>56</v>
-      </c>
-      <c r="H887">
-        <v>333</v>
+        <v>0.67708333333333337</v>
       </c>
       <c r="I887">
-        <v>167</v>
+        <v>74</v>
       </c>
       <c r="J887">
-        <v>0</v>
-      </c>
-      <c r="K887">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="L887">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="M887">
         <v>0</v>
       </c>
       <c r="N887">
-        <v>1333</v>
+        <v>0</v>
       </c>
       <c r="O887">
-        <v>222</v>
+        <v>4</v>
       </c>
       <c r="P887">
-        <v>2167</v>
+        <v>91</v>
       </c>
       <c r="Q887" t="s">
-        <v>251</v>
+        <v>283</v>
       </c>
     </row>
     <row r="888" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A888" t="s">
-        <v>289</v>
+        <v>434</v>
       </c>
       <c r="B888">
-        <v>-34.628509999999999</v>
+        <v>-34.540179999999999</v>
       </c>
       <c r="C888">
-        <v>135.86675</v>
+        <v>135.93411</v>
       </c>
       <c r="D888" s="2">
-        <v>46170</v>
+        <v>46165</v>
       </c>
       <c r="E888" s="20">
         <v>0.54166666666666663</v>
       </c>
       <c r="I888">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="J888">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="L888">
-        <v>45</v>
-      </c>
-      <c r="O888">
-        <v>7</v>
+        <v>73</v>
       </c>
       <c r="P888">
-        <v>70</v>
+        <v>111</v>
       </c>
       <c r="Q888" t="s">
         <v>283</v>
@@ -34304,34 +34297,34 @@
     </row>
     <row r="889" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A889" t="s">
-        <v>435</v>
+        <v>289</v>
       </c>
       <c r="B889">
-        <v>-34.540819999999997</v>
+        <v>-34.628860000000003</v>
       </c>
       <c r="C889">
-        <v>135.93379999999999</v>
+        <v>135.86708999999999</v>
       </c>
       <c r="D889" s="2">
-        <v>46172</v>
+        <v>46166</v>
       </c>
       <c r="E889" s="20">
-        <v>0.47916666666666669</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="I889">
-        <v>58</v>
+        <v>16</v>
       </c>
       <c r="J889">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="L889">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="O889">
         <v>6</v>
       </c>
       <c r="P889">
-        <v>105</v>
+        <v>44</v>
       </c>
       <c r="Q889" t="s">
         <v>283</v>
@@ -34339,19 +34332,19 @@
     </row>
     <row r="890" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A890" t="s">
-        <v>422</v>
+        <v>436</v>
       </c>
       <c r="B890">
-        <v>-35.500024000000003</v>
+        <v>-35.521467000000001</v>
       </c>
       <c r="C890">
-        <v>138.24287699999999</v>
+        <v>138.18532999999999</v>
       </c>
       <c r="D890" s="2">
-        <v>46173</v>
+        <v>46166</v>
       </c>
       <c r="E890" s="20">
-        <v>0.38194444444444442</v>
+        <v>0.4375</v>
       </c>
       <c r="F890">
         <v>0</v>
@@ -34360,31 +34353,31 @@
         <v>0</v>
       </c>
       <c r="H890">
-        <v>389</v>
+        <v>56</v>
       </c>
       <c r="I890">
+        <v>111</v>
+      </c>
+      <c r="J890">
+        <v>0</v>
+      </c>
+      <c r="K890">
+        <v>0</v>
+      </c>
+      <c r="L890">
+        <v>56</v>
+      </c>
+      <c r="M890">
+        <v>0</v>
+      </c>
+      <c r="N890">
+        <v>444</v>
+      </c>
+      <c r="O890">
         <v>167</v>
       </c>
-      <c r="J890">
-        <v>0</v>
-      </c>
-      <c r="K890">
-        <v>0</v>
-      </c>
-      <c r="L890">
-        <v>0</v>
-      </c>
-      <c r="M890">
-        <v>667</v>
-      </c>
-      <c r="N890">
-        <v>1611</v>
-      </c>
-      <c r="O890">
-        <v>111</v>
-      </c>
       <c r="P890">
-        <v>2945</v>
+        <v>834</v>
       </c>
       <c r="Q890" t="s">
         <v>251</v>
@@ -34392,177 +34385,1142 @@
     </row>
     <row r="891" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A891" t="s">
-        <v>289</v>
+        <v>311</v>
       </c>
       <c r="B891">
-        <v>-34.628509999999999</v>
+        <v>-35.445059999999998</v>
       </c>
       <c r="C891">
-        <v>135.86675</v>
+        <v>138.30758399999999</v>
       </c>
       <c r="D891" s="2">
-        <v>46173</v>
+        <v>46167</v>
       </c>
       <c r="E891" s="20">
-        <v>0.70833333333333337</v>
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="F891">
+        <v>0</v>
+      </c>
+      <c r="G891">
+        <v>0</v>
+      </c>
+      <c r="H891">
+        <v>0</v>
       </c>
       <c r="I891">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="J891">
-        <v>21</v>
+        <v>0</v>
+      </c>
+      <c r="K891">
+        <v>0</v>
       </c>
       <c r="L891">
-        <v>6</v>
+        <v>56</v>
+      </c>
+      <c r="M891">
+        <v>0</v>
+      </c>
+      <c r="N891">
+        <v>56</v>
       </c>
       <c r="O891">
-        <v>5</v>
+        <v>56</v>
       </c>
       <c r="P891">
-        <v>45</v>
+        <v>224</v>
       </c>
       <c r="Q891" t="s">
-        <v>283</v>
+        <v>349</v>
       </c>
     </row>
     <row r="892" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A892" t="s">
-        <v>312</v>
+        <v>435</v>
       </c>
       <c r="B892">
-        <v>-35.445059999999998</v>
+        <v>-34.377519999999997</v>
       </c>
       <c r="C892">
-        <v>138.30758399999999</v>
+        <v>136.10475</v>
       </c>
       <c r="D892" s="2">
-        <v>46174</v>
+        <v>46168</v>
       </c>
       <c r="E892" s="20">
-        <v>0.34375</v>
-      </c>
-      <c r="F892">
-        <v>0</v>
-      </c>
-      <c r="G892">
-        <v>0</v>
-      </c>
-      <c r="H892">
-        <v>0</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="I892">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="J892">
-        <v>0</v>
-      </c>
-      <c r="K892">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L892">
-        <v>56</v>
-      </c>
-      <c r="M892">
-        <v>0</v>
-      </c>
-      <c r="N892">
-        <v>56</v>
+        <v>2</v>
       </c>
       <c r="O892">
-        <v>56</v>
+        <v>4</v>
       </c>
       <c r="P892">
-        <v>222</v>
+        <v>26</v>
       </c>
       <c r="Q892" t="s">
-        <v>350</v>
+        <v>283</v>
       </c>
     </row>
     <row r="893" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A893" t="s">
-        <v>289</v>
+        <v>59</v>
       </c>
       <c r="B893">
-        <v>-34.628509999999999</v>
+        <v>-35.084850000000003</v>
       </c>
       <c r="C893">
-        <v>135.86675</v>
+        <v>137.74889999999999</v>
       </c>
       <c r="D893" s="2">
-        <v>46175</v>
+        <v>46169</v>
       </c>
       <c r="E893" s="20">
-        <v>0.52083333333333337</v>
+        <v>0.5</v>
+      </c>
+      <c r="G893">
+        <v>111</v>
+      </c>
+      <c r="H893">
+        <v>167</v>
       </c>
       <c r="I893">
-        <v>69</v>
+        <v>333</v>
       </c>
       <c r="J893">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="L893">
-        <v>9</v>
+        <v>111</v>
+      </c>
+      <c r="M893">
+        <v>0</v>
+      </c>
+      <c r="N893">
+        <v>1000</v>
       </c>
       <c r="O893">
-        <v>6</v>
+        <v>167</v>
       </c>
       <c r="P893">
-        <v>84</v>
+        <v>1889</v>
       </c>
       <c r="Q893" t="s">
-        <v>283</v>
+        <v>149</v>
       </c>
     </row>
     <row r="894" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A894" t="s">
+        <v>426</v>
+      </c>
+      <c r="B894">
+        <v>-35.410254000000002</v>
+      </c>
+      <c r="C894">
+        <v>138.32751999999999</v>
+      </c>
+      <c r="D894" s="2">
+        <v>46169</v>
+      </c>
+      <c r="E894" s="20">
+        <v>0.4375</v>
+      </c>
+      <c r="F894">
+        <v>0</v>
+      </c>
+      <c r="G894">
+        <v>56</v>
+      </c>
+      <c r="H894">
+        <v>333</v>
+      </c>
+      <c r="I894">
+        <v>167</v>
+      </c>
+      <c r="J894">
+        <v>0</v>
+      </c>
+      <c r="K894">
+        <v>0</v>
+      </c>
+      <c r="L894">
+        <v>56</v>
+      </c>
+      <c r="M894">
+        <v>0</v>
+      </c>
+      <c r="N894">
+        <v>1333</v>
+      </c>
+      <c r="O894">
+        <v>222</v>
+      </c>
+      <c r="P894">
+        <v>2167</v>
+      </c>
+      <c r="Q894" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="895" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A895" t="s">
+        <v>289</v>
+      </c>
+      <c r="B895">
+        <v>-34.628509999999999</v>
+      </c>
+      <c r="C895">
+        <v>135.86675</v>
+      </c>
+      <c r="D895" s="2">
+        <v>46170</v>
+      </c>
+      <c r="E895" s="20">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="I895">
+        <v>18</v>
+      </c>
+      <c r="J895">
+        <v>6</v>
+      </c>
+      <c r="L895">
+        <v>45</v>
+      </c>
+      <c r="O895">
+        <v>7</v>
+      </c>
+      <c r="P895">
+        <v>70</v>
+      </c>
+      <c r="Q895" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="896" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A896" t="s">
+        <v>434</v>
+      </c>
+      <c r="B896">
+        <v>-34.540819999999997</v>
+      </c>
+      <c r="C896">
+        <v>135.93379999999999</v>
+      </c>
+      <c r="D896" s="2">
+        <v>46172</v>
+      </c>
+      <c r="E896" s="20">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="I896">
+        <v>58</v>
+      </c>
+      <c r="J896">
+        <v>42</v>
+      </c>
+      <c r="L896">
+        <v>41</v>
+      </c>
+      <c r="O896">
+        <v>6</v>
+      </c>
+      <c r="P896">
+        <v>105</v>
+      </c>
+      <c r="Q896" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="897" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A897" t="s">
+        <v>79</v>
+      </c>
+      <c r="B897">
+        <v>-34.804662999999998</v>
+      </c>
+      <c r="C897">
+        <v>138.540223</v>
+      </c>
+      <c r="D897" s="2">
+        <v>46172</v>
+      </c>
+      <c r="E897" s="20">
+        <v>0.54861111111111116</v>
+      </c>
+      <c r="H897">
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="I897">
+        <v>1.343</v>
+      </c>
+      <c r="J897">
+        <v>0</v>
+      </c>
+      <c r="L897">
+        <v>6.0667</v>
+      </c>
+      <c r="O897">
+        <v>0.13</v>
+      </c>
+      <c r="P897" s="24">
+        <v>7.5827</v>
+      </c>
+      <c r="Q897" s="24" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="898" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A898" t="s">
+        <v>439</v>
+      </c>
+      <c r="B898">
+        <v>-34.823926999999998</v>
+      </c>
+      <c r="C898">
+        <v>138.482923</v>
+      </c>
+      <c r="D898" s="2">
+        <v>46172</v>
+      </c>
+      <c r="E898" s="20">
+        <v>0.57291666666666663</v>
+      </c>
+      <c r="I898">
+        <v>2.73</v>
+      </c>
+      <c r="J898">
+        <v>0</v>
+      </c>
+      <c r="L898">
+        <v>4.2032999999999996</v>
+      </c>
+      <c r="N898">
+        <v>0.13</v>
+      </c>
+      <c r="P898">
+        <v>7.063299999999999</v>
+      </c>
+      <c r="Q898" t="s">
+        <v>78</v>
+      </c>
+      <c r="R898" s="24"/>
+    </row>
+    <row r="899" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A899" t="s">
+        <v>348</v>
+      </c>
+      <c r="B899">
+        <v>-34.860666999999999</v>
+      </c>
+      <c r="C899">
+        <v>138.490938</v>
+      </c>
+      <c r="D899" s="2">
+        <v>46172</v>
+      </c>
+      <c r="E899" s="20">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="I899">
+        <v>12.9</v>
+      </c>
+      <c r="J899">
+        <v>0</v>
+      </c>
+      <c r="L899">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="N899">
+        <v>0.1</v>
+      </c>
+      <c r="O899">
+        <v>0.05</v>
+      </c>
+      <c r="P899">
+        <v>21.350000000000005</v>
+      </c>
+      <c r="Q899" t="s">
+        <v>78</v>
+      </c>
+      <c r="R899" s="24"/>
+    </row>
+    <row r="900" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A900" t="s">
+        <v>421</v>
+      </c>
+      <c r="B900">
+        <v>-35.500024000000003</v>
+      </c>
+      <c r="C900">
+        <v>138.24287699999999</v>
+      </c>
+      <c r="D900" s="2">
+        <v>46173</v>
+      </c>
+      <c r="E900" s="20">
+        <v>0.38194444444444442</v>
+      </c>
+      <c r="F900">
+        <v>0</v>
+      </c>
+      <c r="G900">
+        <v>0</v>
+      </c>
+      <c r="H900">
+        <v>389</v>
+      </c>
+      <c r="I900">
+        <v>167</v>
+      </c>
+      <c r="J900">
+        <v>0</v>
+      </c>
+      <c r="K900">
+        <v>0</v>
+      </c>
+      <c r="L900">
+        <v>0</v>
+      </c>
+      <c r="M900">
+        <v>667</v>
+      </c>
+      <c r="N900">
+        <v>1611</v>
+      </c>
+      <c r="O900">
+        <v>111</v>
+      </c>
+      <c r="P900">
+        <v>2945</v>
+      </c>
+      <c r="Q900" t="s">
+        <v>251</v>
+      </c>
+      <c r="R900" s="24"/>
+    </row>
+    <row r="901" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A901" t="s">
+        <v>289</v>
+      </c>
+      <c r="B901">
+        <v>-34.628509999999999</v>
+      </c>
+      <c r="C901">
+        <v>135.86675</v>
+      </c>
+      <c r="D901" s="2">
+        <v>46173</v>
+      </c>
+      <c r="E901" s="20">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="I901">
+        <v>34</v>
+      </c>
+      <c r="J901">
+        <v>21</v>
+      </c>
+      <c r="L901">
+        <v>6</v>
+      </c>
+      <c r="O901">
+        <v>5</v>
+      </c>
+      <c r="P901">
+        <v>45</v>
+      </c>
+      <c r="Q901" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="902" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A902" t="s">
+        <v>440</v>
+      </c>
+      <c r="B902">
+        <v>-35.017000000000003</v>
+      </c>
+      <c r="C902">
+        <v>138.51400000000001</v>
+      </c>
+      <c r="D902" s="2">
+        <v>46173</v>
+      </c>
+      <c r="I902">
+        <v>111</v>
+      </c>
+      <c r="J902">
+        <v>0</v>
+      </c>
+      <c r="L902">
+        <v>1444</v>
+      </c>
+      <c r="N902">
+        <v>444</v>
+      </c>
+      <c r="O902">
+        <v>1000</v>
+      </c>
+      <c r="P902">
+        <v>2999</v>
+      </c>
+      <c r="Q902" s="24" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="903" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A903" t="s">
+        <v>441</v>
+      </c>
+      <c r="B903">
+        <v>-35.023200000000003</v>
+      </c>
+      <c r="C903">
+        <v>138.5155</v>
+      </c>
+      <c r="D903" s="2">
+        <v>46173</v>
+      </c>
+      <c r="I903">
+        <v>333</v>
+      </c>
+      <c r="J903">
+        <v>0</v>
+      </c>
+      <c r="L903">
+        <v>778</v>
+      </c>
+      <c r="O903">
+        <v>889</v>
+      </c>
+      <c r="P903">
+        <v>2000</v>
+      </c>
+      <c r="Q903" s="24" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="904" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A904" t="s">
+        <v>442</v>
+      </c>
+      <c r="B904">
+        <v>-35.027099999999997</v>
+      </c>
+      <c r="C904">
+        <v>138.51599999999999</v>
+      </c>
+      <c r="D904" s="2">
+        <v>46173</v>
+      </c>
+      <c r="J904">
+        <v>0</v>
+      </c>
+      <c r="L904">
+        <v>1556</v>
+      </c>
+      <c r="N904">
+        <v>4667</v>
+      </c>
+      <c r="O904">
+        <v>2333</v>
+      </c>
+      <c r="P904">
+        <v>8556</v>
+      </c>
+      <c r="Q904" s="24" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="905" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A905" t="s">
+        <v>443</v>
+      </c>
+      <c r="B905">
+        <v>-35.034999999999997</v>
+      </c>
+      <c r="C905">
+        <v>138.5164</v>
+      </c>
+      <c r="D905" s="2">
+        <v>46173</v>
+      </c>
+      <c r="I905">
+        <v>167</v>
+      </c>
+      <c r="J905">
+        <v>0</v>
+      </c>
+      <c r="L905">
+        <v>167</v>
+      </c>
+      <c r="O905">
+        <v>1333</v>
+      </c>
+      <c r="P905">
+        <v>1667</v>
+      </c>
+      <c r="Q905" s="24" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="906" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A906" t="s">
+        <v>444</v>
+      </c>
+      <c r="B906">
+        <v>-35.029899999999998</v>
+      </c>
+      <c r="C906">
+        <v>138.51599999999999</v>
+      </c>
+      <c r="D906" s="2">
+        <v>46173</v>
+      </c>
+      <c r="J906">
+        <v>0</v>
+      </c>
+      <c r="L906">
+        <v>444</v>
+      </c>
+      <c r="O906">
+        <v>1333</v>
+      </c>
+      <c r="P906">
+        <v>1778</v>
+      </c>
+      <c r="Q906" s="24" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="907" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A907" t="s">
+        <v>311</v>
+      </c>
+      <c r="B907">
+        <v>-35.445059999999998</v>
+      </c>
+      <c r="C907">
+        <v>138.30758399999999</v>
+      </c>
+      <c r="D907" s="2">
+        <v>46174</v>
+      </c>
+      <c r="E907" s="20">
+        <v>0.34375</v>
+      </c>
+      <c r="F907">
+        <v>0</v>
+      </c>
+      <c r="G907">
+        <v>0</v>
+      </c>
+      <c r="H907">
+        <v>0</v>
+      </c>
+      <c r="I907">
+        <v>56</v>
+      </c>
+      <c r="J907">
+        <v>0</v>
+      </c>
+      <c r="K907">
+        <v>0</v>
+      </c>
+      <c r="L907">
+        <v>56</v>
+      </c>
+      <c r="M907">
+        <v>0</v>
+      </c>
+      <c r="N907">
+        <v>56</v>
+      </c>
+      <c r="O907">
+        <v>56</v>
+      </c>
+      <c r="P907">
+        <v>222</v>
+      </c>
+      <c r="Q907" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="908" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A908" t="s">
+        <v>289</v>
+      </c>
+      <c r="B908">
+        <v>-34.628509999999999</v>
+      </c>
+      <c r="C908">
+        <v>135.86675</v>
+      </c>
+      <c r="D908" s="2">
+        <v>46175</v>
+      </c>
+      <c r="E908" s="20">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="I908">
+        <v>69</v>
+      </c>
+      <c r="J908">
+        <v>49</v>
+      </c>
+      <c r="L908">
+        <v>9</v>
+      </c>
+      <c r="O908">
+        <v>6</v>
+      </c>
+      <c r="P908">
+        <v>84</v>
+      </c>
+      <c r="Q908" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="909" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A909" t="s">
         <v>59</v>
       </c>
-      <c r="B894">
+      <c r="B909">
         <v>-35.084850000000003</v>
       </c>
-      <c r="C894">
+      <c r="C909">
         <v>137.74889999999999</v>
       </c>
-      <c r="D894" s="2">
+      <c r="D909" s="2">
         <v>46176</v>
       </c>
-      <c r="E894" s="20">
+      <c r="E909" s="20">
         <v>0.5</v>
       </c>
-      <c r="G894">
+      <c r="G909">
         <v>333</v>
       </c>
-      <c r="H894">
+      <c r="H909">
         <v>111</v>
       </c>
-      <c r="I894">
+      <c r="I909">
         <v>111</v>
       </c>
-      <c r="J894">
-        <v>0</v>
-      </c>
-      <c r="L894">
+      <c r="J909">
+        <v>0</v>
+      </c>
+      <c r="L909">
         <v>222</v>
       </c>
-      <c r="M894">
-        <v>0</v>
-      </c>
-      <c r="N894">
+      <c r="M909">
+        <v>0</v>
+      </c>
+      <c r="N909">
         <v>555</v>
       </c>
-      <c r="O894">
-        <v>0</v>
-      </c>
-      <c r="P894">
+      <c r="O909">
+        <v>0</v>
+      </c>
+      <c r="P909">
         <v>1332</v>
       </c>
-      <c r="Q894" t="s">
+      <c r="Q909" t="s">
         <v>149</v>
       </c>
     </row>
+    <row r="910" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A910" t="s">
+        <v>438</v>
+      </c>
+      <c r="B910">
+        <v>-34.629060000000003</v>
+      </c>
+      <c r="C910">
+        <v>135.867411</v>
+      </c>
+      <c r="D910" s="2">
+        <v>46176</v>
+      </c>
+      <c r="I910">
+        <v>4.9169999999999998</v>
+      </c>
+      <c r="J910">
+        <v>4.6669999999999998</v>
+      </c>
+      <c r="L910">
+        <v>2.3332999999999999</v>
+      </c>
+      <c r="P910" s="24">
+        <v>7.2503000000000002</v>
+      </c>
+      <c r="Q910" s="24" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="911" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A911" t="s">
+        <v>437</v>
+      </c>
+      <c r="B911">
+        <v>-34.540291000000003</v>
+      </c>
+      <c r="C911">
+        <v>135.934124</v>
+      </c>
+      <c r="D911" s="2">
+        <v>46177</v>
+      </c>
+      <c r="I911">
+        <v>4.92</v>
+      </c>
+      <c r="J911">
+        <v>4.2</v>
+      </c>
+      <c r="L911">
+        <v>1.44</v>
+      </c>
+      <c r="O911">
+        <v>0.9</v>
+      </c>
+      <c r="P911" s="24">
+        <v>7.26</v>
+      </c>
+      <c r="Q911" s="24" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="912" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A912" t="s">
+        <v>378</v>
+      </c>
+      <c r="B912">
+        <v>-34.933680000000003</v>
+      </c>
+      <c r="C912">
+        <v>137.35257300000001</v>
+      </c>
+      <c r="D912" s="2">
+        <v>46178</v>
+      </c>
+      <c r="E912" s="25">
+        <v>0.75</v>
+      </c>
+      <c r="I912">
+        <v>500</v>
+      </c>
+      <c r="J912">
+        <v>111</v>
+      </c>
+      <c r="L912">
+        <v>111</v>
+      </c>
+      <c r="N912">
+        <v>278</v>
+      </c>
+      <c r="O912">
+        <v>278</v>
+      </c>
+      <c r="P912">
+        <v>1167</v>
+      </c>
+      <c r="Q912" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="913" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A913" t="s">
+        <v>445</v>
+      </c>
+      <c r="B913">
+        <v>-34.766939999999998</v>
+      </c>
+      <c r="C913">
+        <v>135.87030999999999</v>
+      </c>
+      <c r="D913" s="2">
+        <v>46180</v>
+      </c>
+      <c r="E913" s="20">
+        <v>0.5625</v>
+      </c>
+      <c r="I913">
+        <v>56</v>
+      </c>
+      <c r="J913">
+        <v>1</v>
+      </c>
+      <c r="L913">
+        <v>111</v>
+      </c>
+      <c r="O913">
+        <v>0</v>
+      </c>
+      <c r="P913">
+        <v>167</v>
+      </c>
+      <c r="Q913" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="914" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A914" t="s">
+        <v>446</v>
+      </c>
+      <c r="B914">
+        <v>-34.768819999999998</v>
+      </c>
+      <c r="C914">
+        <v>135.86268000000001</v>
+      </c>
+      <c r="D914" s="2">
+        <v>46180</v>
+      </c>
+      <c r="E914" s="20">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="I914">
+        <v>612</v>
+      </c>
+      <c r="J914">
+        <v>556</v>
+      </c>
+      <c r="L914">
+        <v>56</v>
+      </c>
+      <c r="O914">
+        <v>56</v>
+      </c>
+      <c r="P914">
+        <v>724</v>
+      </c>
+      <c r="Q914" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="915" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A915" t="s">
+        <v>450</v>
+      </c>
+      <c r="B915">
+        <v>-35.595986000000003</v>
+      </c>
+      <c r="C915">
+        <v>138.104072</v>
+      </c>
+      <c r="D915" s="2">
+        <v>46180</v>
+      </c>
+      <c r="E915" s="20">
+        <v>0.50347222222222221</v>
+      </c>
+      <c r="F915">
+        <v>0</v>
+      </c>
+      <c r="G915">
+        <v>0</v>
+      </c>
+      <c r="H915">
+        <v>56</v>
+      </c>
+      <c r="I915">
+        <v>167</v>
+      </c>
+      <c r="J915">
+        <v>0</v>
+      </c>
+      <c r="K915">
+        <v>0</v>
+      </c>
+      <c r="L915">
+        <v>56</v>
+      </c>
+      <c r="M915">
+        <v>0</v>
+      </c>
+      <c r="N915">
+        <v>778</v>
+      </c>
+      <c r="O915">
+        <v>0</v>
+      </c>
+      <c r="P915">
+        <v>1057</v>
+      </c>
+      <c r="Q915" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="916" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A916" t="s">
+        <v>421</v>
+      </c>
+      <c r="B916">
+        <v>-35.500024000000003</v>
+      </c>
+      <c r="C916">
+        <v>138.24287699999999</v>
+      </c>
+      <c r="D916" s="2">
+        <v>46180</v>
+      </c>
+      <c r="E916" s="20">
+        <v>0.49305555555555558</v>
+      </c>
+      <c r="F916">
+        <v>0</v>
+      </c>
+      <c r="G916">
+        <v>0</v>
+      </c>
+      <c r="H916">
+        <v>222</v>
+      </c>
+      <c r="I916">
+        <v>0</v>
+      </c>
+      <c r="J916">
+        <v>0</v>
+      </c>
+      <c r="K916">
+        <v>0</v>
+      </c>
+      <c r="L916">
+        <v>56</v>
+      </c>
+      <c r="M916">
+        <v>0</v>
+      </c>
+      <c r="N916">
+        <v>833</v>
+      </c>
+      <c r="O916">
+        <v>0</v>
+      </c>
+      <c r="P916">
+        <v>1111</v>
+      </c>
+      <c r="Q916" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="917" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A917" t="s">
+        <v>422</v>
+      </c>
+      <c r="B917">
+        <v>-34.979999999999997</v>
+      </c>
+      <c r="C917">
+        <v>138.50800000000001</v>
+      </c>
+      <c r="D917" s="2">
+        <v>46182</v>
+      </c>
+      <c r="I917">
+        <v>333</v>
+      </c>
+      <c r="J917">
+        <v>0</v>
+      </c>
+      <c r="L917">
+        <v>111</v>
+      </c>
+      <c r="N917">
+        <v>1556</v>
+      </c>
+      <c r="O917">
+        <v>1667</v>
+      </c>
+      <c r="P917">
+        <v>3667</v>
+      </c>
+      <c r="Q917" s="24" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="918" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A918" t="s">
+        <v>289</v>
+      </c>
+      <c r="B918">
+        <v>-34.628509999999999</v>
+      </c>
+      <c r="C918">
+        <v>135.86675</v>
+      </c>
+      <c r="D918" s="2">
+        <v>46182</v>
+      </c>
+      <c r="E918" s="20">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="I918">
+        <v>21</v>
+      </c>
+      <c r="J918">
+        <v>19</v>
+      </c>
+      <c r="L918">
+        <v>8</v>
+      </c>
+      <c r="O918">
+        <v>1</v>
+      </c>
+      <c r="P918">
+        <v>30</v>
+      </c>
+      <c r="Q918" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="919" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A919" t="s">
+        <v>434</v>
+      </c>
+      <c r="B919">
+        <v>-34.540930000000003</v>
+      </c>
+      <c r="C919">
+        <v>135.93384</v>
+      </c>
+      <c r="D919" s="2">
+        <v>46183</v>
+      </c>
+      <c r="E919" s="20">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="I919">
+        <v>106</v>
+      </c>
+      <c r="J919">
+        <v>81</v>
+      </c>
+      <c r="L919">
+        <v>28</v>
+      </c>
+      <c r="O919">
+        <v>44</v>
+      </c>
+      <c r="P919">
+        <v>178</v>
+      </c>
+      <c r="Q919" t="s">
+        <v>283</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q894">
-    <sortCondition ref="D2:D894"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q919">
+    <sortCondition ref="D2:D919"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="S229">

--- a/MASTER spreadsheet of community summaries.xlsx
+++ b/MASTER spreadsheet of community summaries.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\peri\Dropbox\Delta\Projects\Laboratory\Algal blooms, bacterial counts  for community\For Luke's HAB data display\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{005F6CEC-75B7-4CD3-95D3-CE52900DB64B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DF48534-1B97-4842-A34B-9ADFEC7C0C86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{9286397E-2757-492B-865A-39B2D6A15FF6}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1855" uniqueCount="451">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1869" uniqueCount="451">
   <si>
     <t>Date</t>
   </si>
@@ -1497,7 +1497,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1538,7 +1538,6 @@
     <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="18" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -1891,7 +1890,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F307807-E5C9-4450-88E0-159CBB3E9A67}">
-  <dimension ref="A1:T919"/>
+  <dimension ref="A1:T926"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="39.33203125" customWidth="1"/>
@@ -31719,7 +31718,7 @@
       <c r="D826" s="2">
         <v>46130</v>
       </c>
-      <c r="E826" s="25">
+      <c r="E826" s="24">
         <v>0.82291666666666663</v>
       </c>
       <c r="I826">
@@ -31757,7 +31756,7 @@
       <c r="D827" s="2">
         <v>46130</v>
       </c>
-      <c r="E827" s="25">
+      <c r="E827" s="24">
         <v>0.67708333333333337</v>
       </c>
       <c r="I827">
@@ -32685,7 +32684,7 @@
       <c r="D850" s="2">
         <v>46145</v>
       </c>
-      <c r="E850" s="25">
+      <c r="E850" s="24">
         <v>0.60416666666666663</v>
       </c>
       <c r="I850">
@@ -33300,7 +33299,7 @@
       <c r="D865" s="2">
         <v>46152</v>
       </c>
-      <c r="E865" s="25">
+      <c r="E865" s="24">
         <v>0.71875</v>
       </c>
       <c r="I865">
@@ -34641,7 +34640,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="897" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="897" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A897" t="s">
         <v>79</v>
       </c>
@@ -34672,14 +34671,14 @@
       <c r="O897">
         <v>0.13</v>
       </c>
-      <c r="P897" s="24">
+      <c r="P897">
         <v>7.5827</v>
       </c>
-      <c r="Q897" s="24" t="s">
+      <c r="Q897" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="898" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="898" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A898" t="s">
         <v>439</v>
       </c>
@@ -34713,9 +34712,8 @@
       <c r="Q898" t="s">
         <v>78</v>
       </c>
-      <c r="R898" s="24"/>
-    </row>
-    <row r="899" spans="1:18" x14ac:dyDescent="0.3">
+    </row>
+    <row r="899" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A899" t="s">
         <v>348</v>
       </c>
@@ -34752,9 +34750,8 @@
       <c r="Q899" t="s">
         <v>78</v>
       </c>
-      <c r="R899" s="24"/>
-    </row>
-    <row r="900" spans="1:18" x14ac:dyDescent="0.3">
+    </row>
+    <row r="900" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A900" t="s">
         <v>421</v>
       </c>
@@ -34806,9 +34803,8 @@
       <c r="Q900" t="s">
         <v>251</v>
       </c>
-      <c r="R900" s="24"/>
-    </row>
-    <row r="901" spans="1:18" x14ac:dyDescent="0.3">
+    </row>
+    <row r="901" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A901" t="s">
         <v>289</v>
       </c>
@@ -34843,7 +34839,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="902" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="902" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A902" t="s">
         <v>440</v>
       </c>
@@ -34874,11 +34870,11 @@
       <c r="P902">
         <v>2999</v>
       </c>
-      <c r="Q902" s="24" t="s">
+      <c r="Q902" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="903" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="903" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A903" t="s">
         <v>441</v>
       </c>
@@ -34906,11 +34902,11 @@
       <c r="P903">
         <v>2000</v>
       </c>
-      <c r="Q903" s="24" t="s">
+      <c r="Q903" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="904" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="904" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A904" t="s">
         <v>442</v>
       </c>
@@ -34938,11 +34934,11 @@
       <c r="P904">
         <v>8556</v>
       </c>
-      <c r="Q904" s="24" t="s">
+      <c r="Q904" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="905" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="905" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A905" t="s">
         <v>443</v>
       </c>
@@ -34970,11 +34966,11 @@
       <c r="P905">
         <v>1667</v>
       </c>
-      <c r="Q905" s="24" t="s">
+      <c r="Q905" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="906" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="906" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A906" t="s">
         <v>444</v>
       </c>
@@ -34999,11 +34995,11 @@
       <c r="P906">
         <v>1778</v>
       </c>
-      <c r="Q906" s="24" t="s">
+      <c r="Q906" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="907" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="907" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A907" t="s">
         <v>311</v>
       </c>
@@ -35056,7 +35052,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="908" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="908" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A908" t="s">
         <v>289</v>
       </c>
@@ -35091,7 +35087,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="909" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="909" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A909" t="s">
         <v>59</v>
       </c>
@@ -35138,7 +35134,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="910" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="910" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A910" t="s">
         <v>438</v>
       </c>
@@ -35160,14 +35156,14 @@
       <c r="L910">
         <v>2.3332999999999999</v>
       </c>
-      <c r="P910" s="24">
+      <c r="P910">
         <v>7.2503000000000002</v>
       </c>
-      <c r="Q910" s="24" t="s">
+      <c r="Q910" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="911" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="911" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A911" t="s">
         <v>437</v>
       </c>
@@ -35192,14 +35188,14 @@
       <c r="O911">
         <v>0.9</v>
       </c>
-      <c r="P911" s="24">
+      <c r="P911">
         <v>7.26</v>
       </c>
-      <c r="Q911" s="24" t="s">
+      <c r="Q911" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="912" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="912" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A912" t="s">
         <v>378</v>
       </c>
@@ -35212,7 +35208,7 @@
       <c r="D912" s="2">
         <v>46178</v>
       </c>
-      <c r="E912" s="25">
+      <c r="E912" s="24">
         <v>0.75</v>
       </c>
       <c r="I912">
@@ -35444,7 +35440,7 @@
       <c r="P917">
         <v>3667</v>
       </c>
-      <c r="Q917" s="24" t="s">
+      <c r="Q917" t="s">
         <v>447</v>
       </c>
     </row>
@@ -35518,9 +35514,311 @@
         <v>283</v>
       </c>
     </row>
+    <row r="920" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A920" t="s">
+        <v>426</v>
+      </c>
+      <c r="B920">
+        <v>-35.410254000000002</v>
+      </c>
+      <c r="C920">
+        <v>138.32751999999999</v>
+      </c>
+      <c r="D920" s="2">
+        <v>46183</v>
+      </c>
+      <c r="E920" s="20">
+        <v>0.65277777777777779</v>
+      </c>
+      <c r="F920">
+        <v>0</v>
+      </c>
+      <c r="G920">
+        <v>0</v>
+      </c>
+      <c r="H920">
+        <v>333</v>
+      </c>
+      <c r="I920">
+        <v>222</v>
+      </c>
+      <c r="J920">
+        <v>0</v>
+      </c>
+      <c r="K920">
+        <v>0</v>
+      </c>
+      <c r="L920">
+        <v>111</v>
+      </c>
+      <c r="M920">
+        <v>0</v>
+      </c>
+      <c r="N920">
+        <v>500</v>
+      </c>
+      <c r="O920">
+        <v>222</v>
+      </c>
+      <c r="P920">
+        <v>1388</v>
+      </c>
+      <c r="Q920" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="921" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A921" t="s">
+        <v>59</v>
+      </c>
+      <c r="B921">
+        <v>-35.084850000000003</v>
+      </c>
+      <c r="C921">
+        <v>137.74889999999999</v>
+      </c>
+      <c r="D921" s="2">
+        <v>46184</v>
+      </c>
+      <c r="E921" s="20">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="H921">
+        <v>222</v>
+      </c>
+      <c r="I921">
+        <v>388</v>
+      </c>
+      <c r="J921">
+        <v>0</v>
+      </c>
+      <c r="L921">
+        <v>444</v>
+      </c>
+      <c r="M921">
+        <v>0</v>
+      </c>
+      <c r="N921">
+        <v>1166</v>
+      </c>
+      <c r="O921">
+        <v>0</v>
+      </c>
+      <c r="P921">
+        <v>2220</v>
+      </c>
+      <c r="Q921" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="922" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A922" t="s">
+        <v>92</v>
+      </c>
+      <c r="B922">
+        <v>-35.632150000000003</v>
+      </c>
+      <c r="C922">
+        <v>138.48339999999999</v>
+      </c>
+      <c r="D922" s="2">
+        <v>46186</v>
+      </c>
+      <c r="E922" s="20">
+        <v>0.46875</v>
+      </c>
+      <c r="I922">
+        <v>0.35</v>
+      </c>
+      <c r="J922">
+        <v>0.05</v>
+      </c>
+      <c r="L922">
+        <v>14.25</v>
+      </c>
+      <c r="M922">
+        <v>0</v>
+      </c>
+      <c r="N922">
+        <v>0.15</v>
+      </c>
+      <c r="O922">
+        <v>0.1</v>
+      </c>
+      <c r="P922">
+        <v>14.85</v>
+      </c>
+      <c r="Q922" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="923" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A923" t="s">
+        <v>289</v>
+      </c>
+      <c r="B923">
+        <v>-34.628509999999999</v>
+      </c>
+      <c r="C923">
+        <v>135.86675</v>
+      </c>
+      <c r="D923" s="2">
+        <v>46187</v>
+      </c>
+      <c r="E923" s="20">
+        <v>0.69791666666666663</v>
+      </c>
+      <c r="I923">
+        <v>182</v>
+      </c>
+      <c r="J923">
+        <v>176</v>
+      </c>
+      <c r="L923">
+        <v>17</v>
+      </c>
+      <c r="O923">
+        <v>2</v>
+      </c>
+      <c r="P923">
+        <v>201</v>
+      </c>
+      <c r="Q923" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="924" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A924" t="s">
+        <v>311</v>
+      </c>
+      <c r="B924">
+        <v>-35.445059999999998</v>
+      </c>
+      <c r="C924">
+        <v>138.30758399999999</v>
+      </c>
+      <c r="D924" s="2">
+        <v>46188</v>
+      </c>
+      <c r="E924" s="20">
+        <v>0.375</v>
+      </c>
+      <c r="F924">
+        <v>0</v>
+      </c>
+      <c r="G924">
+        <v>0</v>
+      </c>
+      <c r="H924">
+        <v>0</v>
+      </c>
+      <c r="I924">
+        <v>56</v>
+      </c>
+      <c r="J924">
+        <v>0</v>
+      </c>
+      <c r="K924">
+        <v>0</v>
+      </c>
+      <c r="L924">
+        <v>56</v>
+      </c>
+      <c r="M924">
+        <v>0</v>
+      </c>
+      <c r="N924">
+        <v>0</v>
+      </c>
+      <c r="O924">
+        <v>111</v>
+      </c>
+      <c r="P924">
+        <v>223</v>
+      </c>
+      <c r="Q924" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="925" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A925" t="s">
+        <v>289</v>
+      </c>
+      <c r="B925">
+        <v>-34.628509999999999</v>
+      </c>
+      <c r="C925">
+        <v>135.86675</v>
+      </c>
+      <c r="D925" s="2">
+        <v>46189</v>
+      </c>
+      <c r="E925" s="20">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="I925">
+        <v>131</v>
+      </c>
+      <c r="J925">
+        <v>121</v>
+      </c>
+      <c r="L925">
+        <v>2</v>
+      </c>
+      <c r="O925">
+        <v>2</v>
+      </c>
+      <c r="P925">
+        <v>135</v>
+      </c>
+      <c r="Q925" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="926" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A926" t="s">
+        <v>59</v>
+      </c>
+      <c r="B926">
+        <v>-35.084850000000003</v>
+      </c>
+      <c r="C926">
+        <v>137.74889999999999</v>
+      </c>
+      <c r="D926" s="2">
+        <v>46190</v>
+      </c>
+      <c r="E926" s="20">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="G926">
+        <v>333</v>
+      </c>
+      <c r="H926">
+        <v>389</v>
+      </c>
+      <c r="I926">
+        <v>277</v>
+      </c>
+      <c r="M926">
+        <v>0</v>
+      </c>
+      <c r="N926">
+        <v>556</v>
+      </c>
+      <c r="O926">
+        <v>0</v>
+      </c>
+      <c r="P926">
+        <v>1555</v>
+      </c>
+      <c r="Q926" t="s">
+        <v>149</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q919">
-    <sortCondition ref="D2:D919"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q926">
+    <sortCondition ref="D2:D926"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="S229">

--- a/MASTER spreadsheet of community summaries.xlsx
+++ b/MASTER spreadsheet of community summaries.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\peri\Dropbox\Delta\Projects\Laboratory\Algal blooms, bacterial counts  for community\For Luke's HAB data display\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DF48534-1B97-4842-A34B-9ADFEC7C0C86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F594FAC7-76E9-4A2C-83BC-68B7AFFE897C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{9286397E-2757-492B-865A-39B2D6A15FF6}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1869" uniqueCount="451">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1931" uniqueCount="460">
   <si>
     <t>Date</t>
   </si>
@@ -1409,6 +1409,33 @@
   </si>
   <si>
     <t>Morgan’s Beach</t>
+  </si>
+  <si>
+    <t>Seal Island FOAM approach from north</t>
+  </si>
+  <si>
+    <t>Proper Bay Boat Ramp</t>
+  </si>
+  <si>
+    <t>Port Lincoln Jetty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Glenelg Jetty </t>
+  </si>
+  <si>
+    <t>Pullen Island</t>
+  </si>
+  <si>
+    <t>LEWK5222</t>
+  </si>
+  <si>
+    <t>Brownlow Sailing Club 20/6/26</t>
+  </si>
+  <si>
+    <t>LEWK522</t>
+  </si>
+  <si>
+    <t>Emu Bay Creek</t>
   </si>
 </sst>
 </file>
@@ -1890,7 +1917,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F307807-E5C9-4450-88E0-159CBB3E9A67}">
-  <dimension ref="A1:T926"/>
+  <dimension ref="A1:T957"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="39.33203125" customWidth="1"/>
@@ -35800,6 +35827,9 @@
       <c r="I926">
         <v>277</v>
       </c>
+      <c r="J926">
+        <v>0</v>
+      </c>
       <c r="M926">
         <v>0</v>
       </c>
@@ -35816,9 +35846,1304 @@
         <v>149</v>
       </c>
     </row>
+    <row r="927" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A927" t="s">
+        <v>289</v>
+      </c>
+      <c r="B927">
+        <v>-34.628509999999999</v>
+      </c>
+      <c r="C927">
+        <v>135.86675</v>
+      </c>
+      <c r="D927" s="2">
+        <v>46190</v>
+      </c>
+      <c r="E927" s="20">
+        <v>0.56944444444444442</v>
+      </c>
+      <c r="I927">
+        <v>611</v>
+      </c>
+      <c r="J927">
+        <v>611</v>
+      </c>
+      <c r="L927">
+        <v>222</v>
+      </c>
+      <c r="O927">
+        <v>56</v>
+      </c>
+      <c r="P927">
+        <v>889</v>
+      </c>
+      <c r="Q927" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="928" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A928" t="s">
+        <v>454</v>
+      </c>
+      <c r="B928">
+        <v>-34.978150999999997</v>
+      </c>
+      <c r="C928">
+        <v>138.50750400000001</v>
+      </c>
+      <c r="D928" s="2">
+        <v>46190</v>
+      </c>
+      <c r="E928" s="20">
+        <v>0.59236111111111112</v>
+      </c>
+      <c r="I928">
+        <v>167</v>
+      </c>
+      <c r="J928">
+        <v>0</v>
+      </c>
+      <c r="L928">
+        <v>333</v>
+      </c>
+      <c r="N928">
+        <v>667</v>
+      </c>
+      <c r="O928">
+        <v>389</v>
+      </c>
+      <c r="P928">
+        <v>1556</v>
+      </c>
+      <c r="Q928" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="929" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A929" t="s">
+        <v>426</v>
+      </c>
+      <c r="B929">
+        <v>-35.410254000000002</v>
+      </c>
+      <c r="C929">
+        <v>138.32751999999999</v>
+      </c>
+      <c r="D929" s="2">
+        <v>46190</v>
+      </c>
+      <c r="E929" s="20">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="F929">
+        <v>0</v>
+      </c>
+      <c r="G929">
+        <v>0</v>
+      </c>
+      <c r="H929">
+        <v>0</v>
+      </c>
+      <c r="I929">
+        <v>0</v>
+      </c>
+      <c r="J929">
+        <v>0</v>
+      </c>
+      <c r="K929">
+        <v>56</v>
+      </c>
+      <c r="L929">
+        <v>56</v>
+      </c>
+      <c r="M929">
+        <v>0</v>
+      </c>
+      <c r="N929">
+        <v>833</v>
+      </c>
+      <c r="O929">
+        <v>111</v>
+      </c>
+      <c r="P929">
+        <v>1056</v>
+      </c>
+      <c r="Q929" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="930" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A930" t="s">
+        <v>434</v>
+      </c>
+      <c r="B930">
+        <v>-34.540880000000001</v>
+      </c>
+      <c r="C930">
+        <v>135.93384</v>
+      </c>
+      <c r="D930" s="2">
+        <v>46191</v>
+      </c>
+      <c r="E930" s="20">
+        <v>0.44791666666666669</v>
+      </c>
+      <c r="I930">
+        <v>611</v>
+      </c>
+      <c r="J930">
+        <v>611</v>
+      </c>
+      <c r="L930">
+        <v>167</v>
+      </c>
+      <c r="O930">
+        <v>112</v>
+      </c>
+      <c r="P930">
+        <v>890</v>
+      </c>
+      <c r="Q930" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="931" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A931" t="s">
+        <v>289</v>
+      </c>
+      <c r="B931">
+        <v>-34.628509999999999</v>
+      </c>
+      <c r="C931">
+        <v>135.86675</v>
+      </c>
+      <c r="D931" s="2">
+        <v>46192</v>
+      </c>
+      <c r="I931">
+        <v>661</v>
+      </c>
+      <c r="J931">
+        <v>661</v>
+      </c>
+      <c r="L931">
+        <v>222</v>
+      </c>
+      <c r="O931">
+        <v>0</v>
+      </c>
+      <c r="P931">
+        <v>883</v>
+      </c>
+      <c r="Q931" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="932" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A932" t="s">
+        <v>452</v>
+      </c>
+      <c r="B932">
+        <v>-34.759</v>
+      </c>
+      <c r="C932">
+        <v>135.83886000000001</v>
+      </c>
+      <c r="D932" s="2">
+        <v>46193</v>
+      </c>
+      <c r="E932" s="20">
+        <v>0.53125</v>
+      </c>
+      <c r="I932">
+        <v>612</v>
+      </c>
+      <c r="J932">
+        <v>556</v>
+      </c>
+      <c r="L932">
+        <v>500</v>
+      </c>
+      <c r="O932">
+        <v>56</v>
+      </c>
+      <c r="P932">
+        <v>1168</v>
+      </c>
+      <c r="Q932" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="933" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A933" t="s">
+        <v>359</v>
+      </c>
+      <c r="B933">
+        <v>-35.878667100000001</v>
+      </c>
+      <c r="C933">
+        <v>137.6963188</v>
+      </c>
+      <c r="D933" s="2">
+        <v>46193</v>
+      </c>
+      <c r="F933">
+        <v>0</v>
+      </c>
+      <c r="G933">
+        <v>0</v>
+      </c>
+      <c r="H933">
+        <v>0</v>
+      </c>
+      <c r="I933">
+        <v>0</v>
+      </c>
+      <c r="J933">
+        <v>0</v>
+      </c>
+      <c r="K933">
+        <v>0</v>
+      </c>
+      <c r="L933">
+        <v>0</v>
+      </c>
+      <c r="M933">
+        <v>0</v>
+      </c>
+      <c r="N933">
+        <v>0</v>
+      </c>
+      <c r="O933">
+        <v>0</v>
+      </c>
+      <c r="P933">
+        <v>0</v>
+      </c>
+      <c r="Q933" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="934" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A934" t="s">
+        <v>457</v>
+      </c>
+      <c r="B934">
+        <v>-35.6614383</v>
+      </c>
+      <c r="C934">
+        <v>137.6319307</v>
+      </c>
+      <c r="D934" s="2">
+        <v>46193</v>
+      </c>
+      <c r="E934" s="20">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="F934">
+        <v>0</v>
+      </c>
+      <c r="G934">
+        <v>0</v>
+      </c>
+      <c r="H934">
+        <v>0</v>
+      </c>
+      <c r="I934">
+        <v>0</v>
+      </c>
+      <c r="J934">
+        <v>0</v>
+      </c>
+      <c r="K934">
+        <v>0</v>
+      </c>
+      <c r="L934">
+        <v>333</v>
+      </c>
+      <c r="M934">
+        <v>0</v>
+      </c>
+      <c r="N934">
+        <v>0</v>
+      </c>
+      <c r="O934">
+        <v>1</v>
+      </c>
+      <c r="P934">
+        <v>334</v>
+      </c>
+      <c r="Q934" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="935" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A935" t="s">
+        <v>86</v>
+      </c>
+      <c r="B935">
+        <v>-35.540277000000003</v>
+      </c>
+      <c r="C935">
+        <v>138.66416599999999</v>
+      </c>
+      <c r="D935" s="2">
+        <v>46194</v>
+      </c>
+      <c r="E935" s="20">
+        <v>0.36041666666666666</v>
+      </c>
+      <c r="G935">
+        <v>56</v>
+      </c>
+      <c r="H935">
+        <v>56</v>
+      </c>
+      <c r="I935">
+        <v>56</v>
+      </c>
+      <c r="J935">
+        <v>0</v>
+      </c>
+      <c r="L935">
+        <v>333</v>
+      </c>
+      <c r="N935">
+        <v>278</v>
+      </c>
+      <c r="O935">
+        <v>222</v>
+      </c>
+      <c r="P935">
+        <v>1001</v>
+      </c>
+      <c r="Q935" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="936" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A936" t="s">
+        <v>100</v>
+      </c>
+      <c r="B936">
+        <v>-35.536745000000003</v>
+      </c>
+      <c r="C936">
+        <v>138.6913744</v>
+      </c>
+      <c r="D936" s="2">
+        <v>46194</v>
+      </c>
+      <c r="E936" s="20">
+        <v>0.36666666666666664</v>
+      </c>
+      <c r="H936">
+        <v>222</v>
+      </c>
+      <c r="J936">
+        <v>0</v>
+      </c>
+      <c r="L936">
+        <v>222</v>
+      </c>
+      <c r="N936">
+        <v>500</v>
+      </c>
+      <c r="O936">
+        <v>834</v>
+      </c>
+      <c r="P936">
+        <v>1778</v>
+      </c>
+      <c r="Q936" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="937" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A937" t="s">
+        <v>451</v>
+      </c>
+      <c r="B937">
+        <v>-35.576688130000001</v>
+      </c>
+      <c r="C937">
+        <v>138.64694589999999</v>
+      </c>
+      <c r="D937" s="2">
+        <v>46194</v>
+      </c>
+      <c r="I937">
+        <v>111</v>
+      </c>
+      <c r="J937">
+        <v>0</v>
+      </c>
+      <c r="L937">
+        <v>722</v>
+      </c>
+      <c r="N937">
+        <v>167</v>
+      </c>
+      <c r="O937">
+        <v>1666</v>
+      </c>
+      <c r="P937">
+        <v>2666</v>
+      </c>
+      <c r="Q937" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="938" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A938" t="s">
+        <v>87</v>
+      </c>
+      <c r="B938">
+        <v>-35.573300000000003</v>
+      </c>
+      <c r="C938">
+        <v>138.64250000000001</v>
+      </c>
+      <c r="D938" s="2">
+        <v>46194</v>
+      </c>
+      <c r="G938">
+        <v>56</v>
+      </c>
+      <c r="J938">
+        <v>0</v>
+      </c>
+      <c r="L938">
+        <v>111</v>
+      </c>
+      <c r="N938">
+        <v>56</v>
+      </c>
+      <c r="O938">
+        <v>389</v>
+      </c>
+      <c r="P938">
+        <v>612</v>
+      </c>
+      <c r="Q938" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="939" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A939" t="s">
+        <v>88</v>
+      </c>
+      <c r="B939">
+        <v>-35.581124000000003</v>
+      </c>
+      <c r="C939">
+        <v>138.60879700000001</v>
+      </c>
+      <c r="D939" s="2">
+        <v>46194</v>
+      </c>
+      <c r="F939">
+        <v>56</v>
+      </c>
+      <c r="G939">
+        <v>167</v>
+      </c>
+      <c r="J939">
+        <v>0</v>
+      </c>
+      <c r="L939">
+        <v>222</v>
+      </c>
+      <c r="N939">
+        <v>278</v>
+      </c>
+      <c r="O939">
+        <v>389</v>
+      </c>
+      <c r="P939">
+        <v>1112</v>
+      </c>
+      <c r="Q939" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="940" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A940" t="s">
+        <v>89</v>
+      </c>
+      <c r="B940">
+        <v>-35.6048446</v>
+      </c>
+      <c r="C940">
+        <v>138.59278499999999</v>
+      </c>
+      <c r="D940" s="2">
+        <v>46194</v>
+      </c>
+      <c r="G940">
+        <v>111</v>
+      </c>
+      <c r="H940">
+        <v>167</v>
+      </c>
+      <c r="I940">
+        <v>167</v>
+      </c>
+      <c r="J940">
+        <v>0</v>
+      </c>
+      <c r="L940">
+        <v>56</v>
+      </c>
+      <c r="N940">
+        <v>778</v>
+      </c>
+      <c r="O940">
+        <v>667</v>
+      </c>
+      <c r="P940">
+        <v>1946</v>
+      </c>
+      <c r="Q940" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="941" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A941" t="s">
+        <v>374</v>
+      </c>
+      <c r="B941">
+        <v>-35.612285999999997</v>
+      </c>
+      <c r="C941">
+        <v>138.564302</v>
+      </c>
+      <c r="D941" s="2">
+        <v>46194</v>
+      </c>
+      <c r="H941">
+        <v>111</v>
+      </c>
+      <c r="I941">
+        <v>111</v>
+      </c>
+      <c r="J941">
+        <v>0</v>
+      </c>
+      <c r="N941">
+        <v>444</v>
+      </c>
+      <c r="O941">
+        <v>167</v>
+      </c>
+      <c r="P941">
+        <v>833</v>
+      </c>
+      <c r="Q941" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="942" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A942" t="s">
+        <v>431</v>
+      </c>
+      <c r="B942">
+        <v>-35.619</v>
+      </c>
+      <c r="C942">
+        <v>138.58099999999999</v>
+      </c>
+      <c r="D942" s="2">
+        <v>46194</v>
+      </c>
+      <c r="G942">
+        <v>56</v>
+      </c>
+      <c r="H942">
+        <v>111</v>
+      </c>
+      <c r="J942">
+        <v>0</v>
+      </c>
+      <c r="N942">
+        <v>1056</v>
+      </c>
+      <c r="O942">
+        <v>56</v>
+      </c>
+      <c r="P942">
+        <v>1279</v>
+      </c>
+      <c r="Q942" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="943" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A943" t="s">
+        <v>455</v>
+      </c>
+      <c r="B943">
+        <v>-35.576250000000002</v>
+      </c>
+      <c r="C943">
+        <v>138.64349999999999</v>
+      </c>
+      <c r="D943" s="2">
+        <v>46194</v>
+      </c>
+      <c r="E943" s="20">
+        <v>0.38541666666666669</v>
+      </c>
+      <c r="I943">
+        <v>56</v>
+      </c>
+      <c r="J943">
+        <v>0</v>
+      </c>
+      <c r="L943">
+        <v>1333</v>
+      </c>
+      <c r="N943">
+        <v>56</v>
+      </c>
+      <c r="O943">
+        <v>167</v>
+      </c>
+      <c r="P943">
+        <v>1612</v>
+      </c>
+      <c r="Q943" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="944" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A944" t="s">
+        <v>88</v>
+      </c>
+      <c r="B944">
+        <v>-35.581982000000004</v>
+      </c>
+      <c r="C944">
+        <v>138.60827699999999</v>
+      </c>
+      <c r="D944" s="2">
+        <v>46194</v>
+      </c>
+      <c r="E944" s="20">
+        <v>9</v>
+      </c>
+      <c r="J944">
+        <v>0</v>
+      </c>
+      <c r="N944">
+        <v>1611</v>
+      </c>
+      <c r="O944">
+        <v>222</v>
+      </c>
+      <c r="P944">
+        <v>1833</v>
+      </c>
+      <c r="Q944" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="945" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A945" t="s">
+        <v>400</v>
+      </c>
+      <c r="B945">
+        <v>-35.510497000000001</v>
+      </c>
+      <c r="C945">
+        <v>138.21676299999999</v>
+      </c>
+      <c r="D945" s="2">
+        <v>46194</v>
+      </c>
+      <c r="E945" s="20">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="F945">
+        <v>167</v>
+      </c>
+      <c r="G945">
+        <v>0</v>
+      </c>
+      <c r="H945">
+        <v>222</v>
+      </c>
+      <c r="I945">
+        <v>278</v>
+      </c>
+      <c r="J945">
+        <v>0</v>
+      </c>
+      <c r="K945">
+        <v>0</v>
+      </c>
+      <c r="L945">
+        <v>167</v>
+      </c>
+      <c r="M945">
+        <v>0</v>
+      </c>
+      <c r="N945">
+        <v>833</v>
+      </c>
+      <c r="O945">
+        <v>333</v>
+      </c>
+      <c r="P945">
+        <v>2000</v>
+      </c>
+      <c r="Q945" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="946" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A946" t="s">
+        <v>311</v>
+      </c>
+      <c r="B946">
+        <v>-35.445059999999998</v>
+      </c>
+      <c r="C946">
+        <v>138.30758399999999</v>
+      </c>
+      <c r="D946" s="2">
+        <v>46195</v>
+      </c>
+      <c r="E946" s="20">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="F946">
+        <v>0</v>
+      </c>
+      <c r="G946">
+        <v>0</v>
+      </c>
+      <c r="H946">
+        <v>0</v>
+      </c>
+      <c r="I946">
+        <v>56</v>
+      </c>
+      <c r="J946">
+        <v>0</v>
+      </c>
+      <c r="K946">
+        <v>0</v>
+      </c>
+      <c r="L946">
+        <v>0</v>
+      </c>
+      <c r="M946">
+        <v>0</v>
+      </c>
+      <c r="N946">
+        <v>611</v>
+      </c>
+      <c r="O946">
+        <v>56</v>
+      </c>
+      <c r="P946">
+        <v>723</v>
+      </c>
+      <c r="Q946" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="947" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A947" t="s">
+        <v>395</v>
+      </c>
+      <c r="B947">
+        <v>-35.793973000000001</v>
+      </c>
+      <c r="C947">
+        <v>137.852418</v>
+      </c>
+      <c r="D947" s="2">
+        <v>46195</v>
+      </c>
+      <c r="E947" s="20">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="F947">
+        <v>0</v>
+      </c>
+      <c r="G947">
+        <v>0</v>
+      </c>
+      <c r="H947">
+        <v>0</v>
+      </c>
+      <c r="I947">
+        <v>0</v>
+      </c>
+      <c r="J947">
+        <v>0</v>
+      </c>
+      <c r="K947">
+        <v>0</v>
+      </c>
+      <c r="L947">
+        <v>0</v>
+      </c>
+      <c r="M947">
+        <v>0</v>
+      </c>
+      <c r="N947">
+        <v>0</v>
+      </c>
+      <c r="O947">
+        <v>0</v>
+      </c>
+      <c r="P947">
+        <v>0</v>
+      </c>
+      <c r="Q947" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="948" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A948" t="s">
+        <v>256</v>
+      </c>
+      <c r="B948">
+        <v>-35.7987082</v>
+      </c>
+      <c r="C948">
+        <v>137.81647699999999</v>
+      </c>
+      <c r="D948" s="2">
+        <v>46195</v>
+      </c>
+      <c r="E948" s="20">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="F948">
+        <v>0</v>
+      </c>
+      <c r="G948">
+        <v>0</v>
+      </c>
+      <c r="H948">
+        <v>0</v>
+      </c>
+      <c r="I948">
+        <v>0</v>
+      </c>
+      <c r="J948">
+        <v>0</v>
+      </c>
+      <c r="K948">
+        <v>0</v>
+      </c>
+      <c r="L948">
+        <v>0</v>
+      </c>
+      <c r="M948">
+        <v>0</v>
+      </c>
+      <c r="N948">
+        <v>0</v>
+      </c>
+      <c r="O948">
+        <v>0</v>
+      </c>
+      <c r="P948">
+        <v>0</v>
+      </c>
+      <c r="Q948" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="949" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A949" t="s">
+        <v>434</v>
+      </c>
+      <c r="B949">
+        <v>-34.540880000000001</v>
+      </c>
+      <c r="C949">
+        <v>135.93384</v>
+      </c>
+      <c r="D949" s="2">
+        <v>46196</v>
+      </c>
+      <c r="E949" s="20">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="I949">
+        <v>1111</v>
+      </c>
+      <c r="J949">
+        <v>1111</v>
+      </c>
+      <c r="L949">
+        <v>611</v>
+      </c>
+      <c r="O949">
+        <v>56</v>
+      </c>
+      <c r="P949">
+        <v>1778</v>
+      </c>
+      <c r="Q949" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="950" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A950" t="s">
+        <v>453</v>
+      </c>
+      <c r="B950">
+        <v>-34.718809999999998</v>
+      </c>
+      <c r="C950">
+        <v>135.85857999999999</v>
+      </c>
+      <c r="D950" s="2">
+        <v>46196</v>
+      </c>
+      <c r="E950" s="20">
+        <v>46197.375</v>
+      </c>
+      <c r="I950">
+        <v>1167</v>
+      </c>
+      <c r="J950">
+        <v>1111</v>
+      </c>
+      <c r="O950">
+        <v>56</v>
+      </c>
+      <c r="P950">
+        <v>1223</v>
+      </c>
+      <c r="Q950" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="951" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A951" t="s">
+        <v>79</v>
+      </c>
+      <c r="B951">
+        <v>-34.804662999999998</v>
+      </c>
+      <c r="C951">
+        <v>138.540223</v>
+      </c>
+      <c r="D951" s="2">
+        <v>46196</v>
+      </c>
+      <c r="E951" s="20">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="I951">
+        <v>2.7749999999999999</v>
+      </c>
+      <c r="J951">
+        <v>0</v>
+      </c>
+      <c r="L951">
+        <v>6.2249999999999996</v>
+      </c>
+      <c r="O951">
+        <v>1.65</v>
+      </c>
+      <c r="P951">
+        <v>10.65</v>
+      </c>
+      <c r="Q951" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="952" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A952" t="s">
+        <v>267</v>
+      </c>
+      <c r="B952">
+        <v>-34.824044999999998</v>
+      </c>
+      <c r="C952">
+        <v>138.48377600000001</v>
+      </c>
+      <c r="D952" s="2">
+        <v>46196</v>
+      </c>
+      <c r="E952" s="20">
+        <v>0.55694444444444446</v>
+      </c>
+      <c r="G952">
+        <v>0.15</v>
+      </c>
+      <c r="I952">
+        <v>6.2</v>
+      </c>
+      <c r="J952">
+        <v>0</v>
+      </c>
+      <c r="L952">
+        <v>9</v>
+      </c>
+      <c r="N952">
+        <v>0.2</v>
+      </c>
+      <c r="O952">
+        <v>0.35</v>
+      </c>
+      <c r="P952">
+        <v>15.9</v>
+      </c>
+      <c r="Q952" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="953" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A953" t="s">
+        <v>348</v>
+      </c>
+      <c r="B953">
+        <v>-34.860666999999999</v>
+      </c>
+      <c r="C953">
+        <v>138.490938</v>
+      </c>
+      <c r="D953" s="2">
+        <v>46196</v>
+      </c>
+      <c r="E953" s="20">
+        <v>4.8611111111111112E-2</v>
+      </c>
+      <c r="G953">
+        <v>0.1</v>
+      </c>
+      <c r="H953">
+        <v>0.1</v>
+      </c>
+      <c r="I953">
+        <v>54.7</v>
+      </c>
+      <c r="J953">
+        <v>0</v>
+      </c>
+      <c r="L953">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="O953">
+        <v>0.3</v>
+      </c>
+      <c r="P953">
+        <v>57.5</v>
+      </c>
+      <c r="Q953" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="954" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A954" t="s">
+        <v>422</v>
+      </c>
+      <c r="B954">
+        <v>-34.978150999999997</v>
+      </c>
+      <c r="C954">
+        <v>138.50750400000001</v>
+      </c>
+      <c r="D954" s="2">
+        <v>46196</v>
+      </c>
+      <c r="E954" s="20">
+        <v>0.59375</v>
+      </c>
+      <c r="I954">
+        <v>111</v>
+      </c>
+      <c r="J954">
+        <v>0</v>
+      </c>
+      <c r="L954">
+        <v>222</v>
+      </c>
+      <c r="N954">
+        <v>222</v>
+      </c>
+      <c r="O954">
+        <v>667</v>
+      </c>
+      <c r="P954">
+        <v>1222</v>
+      </c>
+      <c r="Q954" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="955" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A955" t="s">
+        <v>421</v>
+      </c>
+      <c r="B955">
+        <v>-35.500024000000003</v>
+      </c>
+      <c r="C955">
+        <v>138.24287699999999</v>
+      </c>
+      <c r="D955" s="2">
+        <v>46196</v>
+      </c>
+      <c r="E955" s="20">
+        <v>0.38541666666666669</v>
+      </c>
+      <c r="F955">
+        <v>0</v>
+      </c>
+      <c r="G955">
+        <v>0</v>
+      </c>
+      <c r="H955">
+        <v>0</v>
+      </c>
+      <c r="I955">
+        <v>0</v>
+      </c>
+      <c r="J955">
+        <v>0</v>
+      </c>
+      <c r="K955">
+        <v>0</v>
+      </c>
+      <c r="L955">
+        <v>0</v>
+      </c>
+      <c r="M955">
+        <v>0</v>
+      </c>
+      <c r="N955">
+        <v>111</v>
+      </c>
+      <c r="O955">
+        <v>0</v>
+      </c>
+      <c r="P955">
+        <v>111</v>
+      </c>
+      <c r="Q955" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="956" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A956" t="s">
+        <v>418</v>
+      </c>
+      <c r="B956">
+        <v>-35.591330800000001</v>
+      </c>
+      <c r="C956">
+        <v>137.5061887</v>
+      </c>
+      <c r="D956" s="2">
+        <v>46196</v>
+      </c>
+      <c r="E956" s="20">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="F956">
+        <v>0</v>
+      </c>
+      <c r="G956">
+        <v>0</v>
+      </c>
+      <c r="H956">
+        <v>0</v>
+      </c>
+      <c r="I956">
+        <v>0</v>
+      </c>
+      <c r="J956">
+        <v>0</v>
+      </c>
+      <c r="K956">
+        <v>0</v>
+      </c>
+      <c r="L956">
+        <v>0</v>
+      </c>
+      <c r="M956">
+        <v>0</v>
+      </c>
+      <c r="N956">
+        <v>0</v>
+      </c>
+      <c r="O956">
+        <v>0</v>
+      </c>
+      <c r="P956">
+        <v>0</v>
+      </c>
+      <c r="Q956" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="957" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A957" t="s">
+        <v>459</v>
+      </c>
+      <c r="B957">
+        <v>-35.595789000000003</v>
+      </c>
+      <c r="C957">
+        <v>137.51194899999999</v>
+      </c>
+      <c r="D957" s="2">
+        <v>46196</v>
+      </c>
+      <c r="E957" s="20">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="F957">
+        <v>0</v>
+      </c>
+      <c r="G957">
+        <v>0</v>
+      </c>
+      <c r="H957">
+        <v>0</v>
+      </c>
+      <c r="I957">
+        <v>0</v>
+      </c>
+      <c r="J957">
+        <v>0</v>
+      </c>
+      <c r="K957">
+        <v>0</v>
+      </c>
+      <c r="L957">
+        <v>0</v>
+      </c>
+      <c r="M957">
+        <v>222</v>
+      </c>
+      <c r="N957">
+        <v>0</v>
+      </c>
+      <c r="O957">
+        <v>0</v>
+      </c>
+      <c r="P957">
+        <v>222</v>
+      </c>
+      <c r="Q957" t="s">
+        <v>456</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q926">
-    <sortCondition ref="D2:D926"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q957">
+    <sortCondition ref="D2:D957"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="S229">

--- a/MASTER spreadsheet of community summaries.xlsx
+++ b/MASTER spreadsheet of community summaries.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\peri\Dropbox\Delta\Projects\Laboratory\Algal blooms, bacterial counts  for community\For Luke's HAB data display\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F594FAC7-76E9-4A2C-83BC-68B7AFFE897C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5FF948E-C116-4285-B660-2509C5BFFD75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{9286397E-2757-492B-865A-39B2D6A15FF6}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1931" uniqueCount="460">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1965" uniqueCount="462">
   <si>
     <t>Date</t>
   </si>
@@ -1426,16 +1426,22 @@
     <t>Pullen Island</t>
   </si>
   <si>
-    <t>LEWK5222</t>
-  </si>
-  <si>
     <t>Brownlow Sailing Club 20/6/26</t>
   </si>
   <si>
-    <t>LEWK522</t>
-  </si>
-  <si>
     <t>Emu Bay Creek</t>
+  </si>
+  <si>
+    <t>Murray Mouth Coorong</t>
+  </si>
+  <si>
+    <t>Chapman river mouth 29 June</t>
+  </si>
+  <si>
+    <t>Antechamber Beach 29 June</t>
+  </si>
+  <si>
+    <t>Penneshaw 29 June</t>
   </si>
 </sst>
 </file>
@@ -1524,7 +1530,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1566,6 +1572,7 @@
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="18" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1917,7 +1924,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F307807-E5C9-4450-88E0-159CBB3E9A67}">
-  <dimension ref="A1:T957"/>
+  <dimension ref="A1:T974"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="39.33203125" customWidth="1"/>
@@ -34015,72 +34022,51 @@
     </row>
     <row r="882" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A882" t="s">
-        <v>432</v>
+        <v>412</v>
       </c>
       <c r="B882">
-        <v>-35.297930000000001</v>
+        <v>-33.043101999999998</v>
       </c>
       <c r="C882">
-        <v>138.14122</v>
+        <v>137.59395699999999</v>
       </c>
       <c r="D882" s="2">
-        <v>46159</v>
+        <v>46157</v>
       </c>
       <c r="E882" s="20">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="F882">
-        <v>0</v>
-      </c>
-      <c r="G882">
-        <v>0</v>
-      </c>
-      <c r="H882">
-        <v>0</v>
-      </c>
-      <c r="I882">
-        <v>56</v>
+        <v>0.65625</v>
       </c>
       <c r="J882">
         <v>0</v>
       </c>
-      <c r="K882">
-        <v>0</v>
-      </c>
       <c r="L882">
-        <v>111</v>
-      </c>
-      <c r="M882">
-        <v>0</v>
-      </c>
-      <c r="N882">
-        <v>111</v>
+        <v>5111</v>
       </c>
       <c r="O882">
         <v>56</v>
       </c>
       <c r="P882">
-        <v>334</v>
+        <v>5167</v>
       </c>
       <c r="Q882" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
     </row>
     <row r="883" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A883" t="s">
-        <v>311</v>
+        <v>432</v>
       </c>
       <c r="B883">
-        <v>-35.445059999999998</v>
+        <v>-35.297930000000001</v>
       </c>
       <c r="C883">
-        <v>138.30758399999999</v>
+        <v>138.14122</v>
       </c>
       <c r="D883" s="2">
-        <v>46160</v>
+        <v>46159</v>
       </c>
       <c r="E883" s="20">
-        <v>0.33333333333333331</v>
+        <v>0.52083333333333337</v>
       </c>
       <c r="F883">
         <v>0</v>
@@ -34101,19 +34087,19 @@
         <v>0</v>
       </c>
       <c r="L883">
-        <v>389</v>
+        <v>111</v>
       </c>
       <c r="M883">
         <v>0</v>
       </c>
       <c r="N883">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="O883">
         <v>56</v>
       </c>
       <c r="P883">
-        <v>501</v>
+        <v>334</v>
       </c>
       <c r="Q883" t="s">
         <v>349</v>
@@ -34121,19 +34107,19 @@
     </row>
     <row r="884" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A884" t="s">
-        <v>426</v>
+        <v>311</v>
       </c>
       <c r="B884">
-        <v>-35.410254000000002</v>
+        <v>-35.445059999999998</v>
       </c>
       <c r="C884">
-        <v>138.32751999999999</v>
+        <v>138.30758399999999</v>
       </c>
       <c r="D884" s="2">
         <v>46160</v>
       </c>
       <c r="E884" s="20">
-        <v>0.46875</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="F884">
         <v>0</v>
@@ -34142,7 +34128,7 @@
         <v>0</v>
       </c>
       <c r="H884">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="I884">
         <v>56</v>
@@ -34154,19 +34140,19 @@
         <v>0</v>
       </c>
       <c r="L884">
-        <v>0</v>
+        <v>389</v>
       </c>
       <c r="M884">
         <v>0</v>
       </c>
       <c r="N884">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="O884">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="P884">
-        <v>168</v>
+        <v>501</v>
       </c>
       <c r="Q884" t="s">
         <v>349</v>
@@ -34174,19 +34160,25 @@
     </row>
     <row r="885" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A885" t="s">
-        <v>59</v>
+        <v>426</v>
       </c>
       <c r="B885">
-        <v>-35.084850000000003</v>
+        <v>-35.410254000000002</v>
       </c>
       <c r="C885">
-        <v>137.74889999999999</v>
+        <v>138.32751999999999</v>
       </c>
       <c r="D885" s="2">
-        <v>46162</v>
+        <v>46160</v>
       </c>
       <c r="E885" s="20">
-        <v>0.5</v>
+        <v>0.46875</v>
+      </c>
+      <c r="F885">
+        <v>0</v>
+      </c>
+      <c r="G885">
+        <v>0</v>
       </c>
       <c r="H885">
         <v>56</v>
@@ -34197,6 +34189,9 @@
       <c r="J885">
         <v>0</v>
       </c>
+      <c r="K885">
+        <v>0</v>
+      </c>
       <c r="L885">
         <v>0</v>
       </c>
@@ -34204,86 +34199,89 @@
         <v>0</v>
       </c>
       <c r="N885">
-        <v>722</v>
+        <v>56</v>
+      </c>
+      <c r="O885">
+        <v>0</v>
       </c>
       <c r="P885">
-        <v>834</v>
+        <v>168</v>
       </c>
       <c r="Q885" t="s">
-        <v>149</v>
+        <v>349</v>
       </c>
     </row>
     <row r="886" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A886" t="s">
-        <v>433</v>
+        <v>59</v>
       </c>
       <c r="B886">
-        <v>-34.116680000000002</v>
+        <v>-35.084850000000003</v>
       </c>
       <c r="C886">
-        <v>136.35397</v>
+        <v>137.74889999999999</v>
       </c>
       <c r="D886" s="2">
         <v>46162</v>
       </c>
       <c r="E886" s="20">
-        <v>0.51041666666666663</v>
+        <v>0.5</v>
+      </c>
+      <c r="H886">
+        <v>56</v>
       </c>
       <c r="I886">
-        <v>4</v>
+        <v>56</v>
       </c>
       <c r="J886">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L886">
-        <v>2</v>
-      </c>
-      <c r="O886">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="M886">
+        <v>0</v>
+      </c>
+      <c r="N886">
+        <v>722</v>
       </c>
       <c r="P886">
-        <v>9</v>
+        <v>834</v>
       </c>
       <c r="Q886" t="s">
-        <v>283</v>
+        <v>149</v>
       </c>
     </row>
     <row r="887" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A887" t="s">
-        <v>289</v>
+        <v>433</v>
       </c>
       <c r="B887">
-        <v>-34.628860000000003</v>
+        <v>-34.116680000000002</v>
       </c>
       <c r="C887">
-        <v>135.86708999999999</v>
+        <v>136.35397</v>
       </c>
       <c r="D887" s="2">
-        <v>46163</v>
+        <v>46162</v>
       </c>
       <c r="E887" s="20">
-        <v>0.67708333333333337</v>
+        <v>0.51041666666666663</v>
       </c>
       <c r="I887">
-        <v>74</v>
+        <v>4</v>
       </c>
       <c r="J887">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="L887">
-        <v>13</v>
-      </c>
-      <c r="M887">
-        <v>0</v>
-      </c>
-      <c r="N887">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O887">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P887">
-        <v>91</v>
+        <v>9</v>
       </c>
       <c r="Q887" t="s">
         <v>283</v>
@@ -34291,31 +34289,40 @@
     </row>
     <row r="888" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A888" t="s">
-        <v>434</v>
+        <v>289</v>
       </c>
       <c r="B888">
-        <v>-34.540179999999999</v>
+        <v>-34.628860000000003</v>
       </c>
       <c r="C888">
-        <v>135.93411</v>
+        <v>135.86708999999999</v>
       </c>
       <c r="D888" s="2">
-        <v>46165</v>
+        <v>46163</v>
       </c>
       <c r="E888" s="20">
-        <v>0.54166666666666663</v>
+        <v>0.67708333333333337</v>
       </c>
       <c r="I888">
-        <v>38</v>
+        <v>74</v>
       </c>
       <c r="J888">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="L888">
-        <v>73</v>
+        <v>13</v>
+      </c>
+      <c r="M888">
+        <v>0</v>
+      </c>
+      <c r="N888">
+        <v>0</v>
+      </c>
+      <c r="O888">
+        <v>4</v>
       </c>
       <c r="P888">
-        <v>111</v>
+        <v>91</v>
       </c>
       <c r="Q888" t="s">
         <v>283</v>
@@ -34323,34 +34330,31 @@
     </row>
     <row r="889" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A889" t="s">
-        <v>289</v>
+        <v>434</v>
       </c>
       <c r="B889">
-        <v>-34.628860000000003</v>
+        <v>-34.540179999999999</v>
       </c>
       <c r="C889">
-        <v>135.86708999999999</v>
+        <v>135.93411</v>
       </c>
       <c r="D889" s="2">
-        <v>46166</v>
+        <v>46165</v>
       </c>
       <c r="E889" s="20">
-        <v>0.45833333333333331</v>
+        <v>0.54166666666666663</v>
       </c>
       <c r="I889">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="J889">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="L889">
-        <v>22</v>
-      </c>
-      <c r="O889">
-        <v>6</v>
+        <v>73</v>
       </c>
       <c r="P889">
-        <v>44</v>
+        <v>111</v>
       </c>
       <c r="Q889" t="s">
         <v>283</v>
@@ -34358,72 +34362,54 @@
     </row>
     <row r="890" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A890" t="s">
-        <v>436</v>
+        <v>289</v>
       </c>
       <c r="B890">
-        <v>-35.521467000000001</v>
+        <v>-34.628860000000003</v>
       </c>
       <c r="C890">
-        <v>138.18532999999999</v>
+        <v>135.86708999999999</v>
       </c>
       <c r="D890" s="2">
         <v>46166</v>
       </c>
       <c r="E890" s="20">
-        <v>0.4375</v>
-      </c>
-      <c r="F890">
-        <v>0</v>
-      </c>
-      <c r="G890">
-        <v>0</v>
-      </c>
-      <c r="H890">
-        <v>56</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="I890">
-        <v>111</v>
+        <v>16</v>
       </c>
       <c r="J890">
-        <v>0</v>
-      </c>
-      <c r="K890">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L890">
-        <v>56</v>
-      </c>
-      <c r="M890">
-        <v>0</v>
-      </c>
-      <c r="N890">
-        <v>444</v>
+        <v>22</v>
       </c>
       <c r="O890">
-        <v>167</v>
+        <v>6</v>
       </c>
       <c r="P890">
-        <v>834</v>
+        <v>44</v>
       </c>
       <c r="Q890" t="s">
-        <v>251</v>
+        <v>283</v>
       </c>
     </row>
     <row r="891" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A891" t="s">
-        <v>311</v>
+        <v>436</v>
       </c>
       <c r="B891">
-        <v>-35.445059999999998</v>
+        <v>-35.521467000000001</v>
       </c>
       <c r="C891">
-        <v>138.30758399999999</v>
+        <v>138.18532999999999</v>
       </c>
       <c r="D891" s="2">
-        <v>46167</v>
+        <v>46166</v>
       </c>
       <c r="E891" s="20">
-        <v>0.39583333333333331</v>
+        <v>0.4375</v>
       </c>
       <c r="F891">
         <v>0</v>
@@ -34432,10 +34418,10 @@
         <v>0</v>
       </c>
       <c r="H891">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="I891">
-        <v>56</v>
+        <v>111</v>
       </c>
       <c r="J891">
         <v>0</v>
@@ -34450,218 +34436,236 @@
         <v>0</v>
       </c>
       <c r="N891">
-        <v>56</v>
+        <v>444</v>
       </c>
       <c r="O891">
-        <v>56</v>
+        <v>167</v>
       </c>
       <c r="P891">
-        <v>224</v>
+        <v>834</v>
       </c>
       <c r="Q891" t="s">
-        <v>349</v>
+        <v>251</v>
       </c>
     </row>
     <row r="892" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A892" t="s">
-        <v>435</v>
+        <v>311</v>
       </c>
       <c r="B892">
-        <v>-34.377519999999997</v>
+        <v>-35.445059999999998</v>
       </c>
       <c r="C892">
-        <v>136.10475</v>
+        <v>138.30758399999999</v>
       </c>
       <c r="D892" s="2">
-        <v>46168</v>
+        <v>46167</v>
       </c>
       <c r="E892" s="20">
-        <v>0.41666666666666669</v>
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="F892">
+        <v>0</v>
+      </c>
+      <c r="G892">
+        <v>0</v>
+      </c>
+      <c r="H892">
+        <v>0</v>
       </c>
       <c r="I892">
-        <v>20</v>
+        <v>56</v>
       </c>
       <c r="J892">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="K892">
+        <v>0</v>
       </c>
       <c r="L892">
-        <v>2</v>
+        <v>56</v>
+      </c>
+      <c r="M892">
+        <v>0</v>
+      </c>
+      <c r="N892">
+        <v>56</v>
       </c>
       <c r="O892">
-        <v>4</v>
+        <v>56</v>
       </c>
       <c r="P892">
-        <v>26</v>
+        <v>224</v>
       </c>
       <c r="Q892" t="s">
-        <v>283</v>
+        <v>349</v>
       </c>
     </row>
     <row r="893" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A893" t="s">
-        <v>59</v>
+        <v>435</v>
       </c>
       <c r="B893">
-        <v>-35.084850000000003</v>
+        <v>-34.377519999999997</v>
       </c>
       <c r="C893">
-        <v>137.74889999999999</v>
+        <v>136.10475</v>
       </c>
       <c r="D893" s="2">
-        <v>46169</v>
+        <v>46168</v>
       </c>
       <c r="E893" s="20">
-        <v>0.5</v>
-      </c>
-      <c r="G893">
-        <v>111</v>
-      </c>
-      <c r="H893">
-        <v>167</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="I893">
-        <v>333</v>
+        <v>20</v>
       </c>
       <c r="J893">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L893">
-        <v>111</v>
-      </c>
-      <c r="M893">
-        <v>0</v>
-      </c>
-      <c r="N893">
-        <v>1000</v>
+        <v>2</v>
       </c>
       <c r="O893">
-        <v>167</v>
+        <v>4</v>
       </c>
       <c r="P893">
-        <v>1889</v>
+        <v>26</v>
       </c>
       <c r="Q893" t="s">
-        <v>149</v>
+        <v>283</v>
       </c>
     </row>
     <row r="894" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A894" t="s">
-        <v>426</v>
+        <v>59</v>
       </c>
       <c r="B894">
-        <v>-35.410254000000002</v>
+        <v>-35.084850000000003</v>
       </c>
       <c r="C894">
-        <v>138.32751999999999</v>
+        <v>137.74889999999999</v>
       </c>
       <c r="D894" s="2">
         <v>46169</v>
       </c>
       <c r="E894" s="20">
-        <v>0.4375</v>
-      </c>
-      <c r="F894">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G894">
-        <v>56</v>
+        <v>111</v>
       </c>
       <c r="H894">
+        <v>167</v>
+      </c>
+      <c r="I894">
         <v>333</v>
       </c>
-      <c r="I894">
+      <c r="J894">
+        <v>0</v>
+      </c>
+      <c r="L894">
+        <v>111</v>
+      </c>
+      <c r="M894">
+        <v>0</v>
+      </c>
+      <c r="N894">
+        <v>1000</v>
+      </c>
+      <c r="O894">
         <v>167</v>
       </c>
-      <c r="J894">
-        <v>0</v>
-      </c>
-      <c r="K894">
-        <v>0</v>
-      </c>
-      <c r="L894">
-        <v>56</v>
-      </c>
-      <c r="M894">
-        <v>0</v>
-      </c>
-      <c r="N894">
-        <v>1333</v>
-      </c>
-      <c r="O894">
-        <v>222</v>
-      </c>
       <c r="P894">
-        <v>2167</v>
+        <v>1889</v>
       </c>
       <c r="Q894" t="s">
-        <v>251</v>
+        <v>149</v>
       </c>
     </row>
     <row r="895" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A895" t="s">
-        <v>289</v>
+        <v>426</v>
       </c>
       <c r="B895">
-        <v>-34.628509999999999</v>
+        <v>-35.410254000000002</v>
       </c>
       <c r="C895">
-        <v>135.86675</v>
+        <v>138.32751999999999</v>
       </c>
       <c r="D895" s="2">
-        <v>46170</v>
+        <v>46169</v>
       </c>
       <c r="E895" s="20">
-        <v>0.54166666666666663</v>
+        <v>0.4375</v>
+      </c>
+      <c r="F895">
+        <v>0</v>
+      </c>
+      <c r="G895">
+        <v>56</v>
+      </c>
+      <c r="H895">
+        <v>333</v>
       </c>
       <c r="I895">
-        <v>18</v>
+        <v>167</v>
       </c>
       <c r="J895">
-        <v>6</v>
+        <v>0</v>
+      </c>
+      <c r="K895">
+        <v>0</v>
       </c>
       <c r="L895">
-        <v>45</v>
+        <v>56</v>
+      </c>
+      <c r="M895">
+        <v>0</v>
+      </c>
+      <c r="N895">
+        <v>1333</v>
       </c>
       <c r="O895">
-        <v>7</v>
+        <v>222</v>
       </c>
       <c r="P895">
-        <v>70</v>
+        <v>2167</v>
       </c>
       <c r="Q895" t="s">
-        <v>283</v>
+        <v>251</v>
       </c>
     </row>
     <row r="896" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A896" t="s">
-        <v>434</v>
+        <v>289</v>
       </c>
       <c r="B896">
-        <v>-34.540819999999997</v>
+        <v>-34.628509999999999</v>
       </c>
       <c r="C896">
-        <v>135.93379999999999</v>
+        <v>135.86675</v>
       </c>
       <c r="D896" s="2">
-        <v>46172</v>
+        <v>46170</v>
       </c>
       <c r="E896" s="20">
-        <v>0.47916666666666669</v>
+        <v>0.54166666666666663</v>
       </c>
       <c r="I896">
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="J896">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="L896">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="O896">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P896">
-        <v>105</v>
+        <v>70</v>
       </c>
       <c r="Q896" t="s">
         <v>283</v>
@@ -34669,72 +34673,72 @@
     </row>
     <row r="897" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A897" t="s">
-        <v>79</v>
+        <v>434</v>
       </c>
       <c r="B897">
-        <v>-34.804662999999998</v>
+        <v>-34.540819999999997</v>
       </c>
       <c r="C897">
-        <v>138.540223</v>
+        <v>135.93379999999999</v>
       </c>
       <c r="D897" s="2">
         <v>46172</v>
       </c>
       <c r="E897" s="20">
-        <v>0.54861111111111116</v>
-      </c>
-      <c r="H897">
-        <v>4.2999999999999997E-2</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="I897">
-        <v>1.343</v>
+        <v>58</v>
       </c>
       <c r="J897">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="L897">
-        <v>6.0667</v>
+        <v>41</v>
       </c>
       <c r="O897">
-        <v>0.13</v>
+        <v>6</v>
       </c>
       <c r="P897">
-        <v>7.5827</v>
+        <v>105</v>
       </c>
       <c r="Q897" t="s">
-        <v>78</v>
+        <v>283</v>
       </c>
     </row>
     <row r="898" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A898" t="s">
-        <v>439</v>
+        <v>79</v>
       </c>
       <c r="B898">
-        <v>-34.823926999999998</v>
+        <v>-34.804662999999998</v>
       </c>
       <c r="C898">
-        <v>138.482923</v>
+        <v>138.540223</v>
       </c>
       <c r="D898" s="2">
         <v>46172</v>
       </c>
       <c r="E898" s="20">
-        <v>0.57291666666666663</v>
+        <v>0.54861111111111116</v>
+      </c>
+      <c r="H898">
+        <v>4.2999999999999997E-2</v>
       </c>
       <c r="I898">
-        <v>2.73</v>
+        <v>1.343</v>
       </c>
       <c r="J898">
         <v>0</v>
       </c>
       <c r="L898">
-        <v>4.2032999999999996</v>
-      </c>
-      <c r="N898">
+        <v>6.0667</v>
+      </c>
+      <c r="O898">
         <v>0.13</v>
       </c>
       <c r="P898">
-        <v>7.063299999999999</v>
+        <v>7.5827</v>
       </c>
       <c r="Q898" t="s">
         <v>78</v>
@@ -34742,37 +34746,34 @@
     </row>
     <row r="899" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A899" t="s">
-        <v>348</v>
+        <v>439</v>
       </c>
       <c r="B899">
-        <v>-34.860666999999999</v>
+        <v>-34.823926999999998</v>
       </c>
       <c r="C899">
-        <v>138.490938</v>
+        <v>138.482923</v>
       </c>
       <c r="D899" s="2">
         <v>46172</v>
       </c>
       <c r="E899" s="20">
-        <v>0.58333333333333337</v>
+        <v>0.57291666666666663</v>
       </c>
       <c r="I899">
-        <v>12.9</v>
+        <v>2.73</v>
       </c>
       <c r="J899">
         <v>0</v>
       </c>
       <c r="L899">
-        <v>8.3000000000000007</v>
+        <v>4.2032999999999996</v>
       </c>
       <c r="N899">
-        <v>0.1</v>
-      </c>
-      <c r="O899">
-        <v>0.05</v>
+        <v>0.13</v>
       </c>
       <c r="P899">
-        <v>21.350000000000005</v>
+        <v>7.063299999999999</v>
       </c>
       <c r="Q899" t="s">
         <v>78</v>
@@ -34780,154 +34781,160 @@
     </row>
     <row r="900" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A900" t="s">
-        <v>421</v>
+        <v>348</v>
       </c>
       <c r="B900">
-        <v>-35.500024000000003</v>
+        <v>-34.860666999999999</v>
       </c>
       <c r="C900">
-        <v>138.24287699999999</v>
+        <v>138.490938</v>
       </c>
       <c r="D900" s="2">
-        <v>46173</v>
+        <v>46172</v>
       </c>
       <c r="E900" s="20">
-        <v>0.38194444444444442</v>
-      </c>
-      <c r="F900">
-        <v>0</v>
-      </c>
-      <c r="G900">
-        <v>0</v>
-      </c>
-      <c r="H900">
-        <v>389</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="I900">
-        <v>167</v>
+        <v>12.9</v>
       </c>
       <c r="J900">
         <v>0</v>
       </c>
-      <c r="K900">
-        <v>0</v>
-      </c>
       <c r="L900">
-        <v>0</v>
-      </c>
-      <c r="M900">
-        <v>667</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="N900">
-        <v>1611</v>
+        <v>0.1</v>
       </c>
       <c r="O900">
-        <v>111</v>
+        <v>0.05</v>
       </c>
       <c r="P900">
-        <v>2945</v>
+        <v>21.350000000000005</v>
       </c>
       <c r="Q900" t="s">
-        <v>251</v>
+        <v>78</v>
       </c>
     </row>
     <row r="901" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A901" t="s">
-        <v>289</v>
+        <v>421</v>
       </c>
       <c r="B901">
-        <v>-34.628509999999999</v>
+        <v>-35.500024000000003</v>
       </c>
       <c r="C901">
-        <v>135.86675</v>
+        <v>138.24287699999999</v>
       </c>
       <c r="D901" s="2">
         <v>46173</v>
       </c>
       <c r="E901" s="20">
-        <v>0.70833333333333337</v>
+        <v>0.38194444444444442</v>
+      </c>
+      <c r="F901">
+        <v>0</v>
+      </c>
+      <c r="G901">
+        <v>0</v>
+      </c>
+      <c r="H901">
+        <v>389</v>
       </c>
       <c r="I901">
-        <v>34</v>
+        <v>167</v>
       </c>
       <c r="J901">
-        <v>21</v>
+        <v>0</v>
+      </c>
+      <c r="K901">
+        <v>0</v>
       </c>
       <c r="L901">
-        <v>6</v>
+        <v>0</v>
+      </c>
+      <c r="M901">
+        <v>667</v>
+      </c>
+      <c r="N901">
+        <v>1611</v>
       </c>
       <c r="O901">
-        <v>5</v>
+        <v>111</v>
       </c>
       <c r="P901">
-        <v>45</v>
+        <v>2945</v>
       </c>
       <c r="Q901" t="s">
-        <v>283</v>
+        <v>251</v>
       </c>
     </row>
     <row r="902" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A902" t="s">
-        <v>440</v>
+        <v>289</v>
       </c>
       <c r="B902">
-        <v>-35.017000000000003</v>
+        <v>-34.628509999999999</v>
       </c>
       <c r="C902">
-        <v>138.51400000000001</v>
+        <v>135.86675</v>
       </c>
       <c r="D902" s="2">
         <v>46173</v>
       </c>
+      <c r="E902" s="20">
+        <v>0.70833333333333337</v>
+      </c>
       <c r="I902">
-        <v>111</v>
+        <v>34</v>
       </c>
       <c r="J902">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="L902">
-        <v>1444</v>
-      </c>
-      <c r="N902">
-        <v>444</v>
+        <v>6</v>
       </c>
       <c r="O902">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="P902">
-        <v>2999</v>
+        <v>45</v>
       </c>
       <c r="Q902" t="s">
-        <v>447</v>
+        <v>283</v>
       </c>
     </row>
     <row r="903" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A903" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B903">
-        <v>-35.023200000000003</v>
+        <v>-35.017000000000003</v>
       </c>
       <c r="C903">
-        <v>138.5155</v>
+        <v>138.51400000000001</v>
       </c>
       <c r="D903" s="2">
         <v>46173</v>
       </c>
       <c r="I903">
-        <v>333</v>
+        <v>111</v>
       </c>
       <c r="J903">
         <v>0</v>
       </c>
       <c r="L903">
-        <v>778</v>
+        <v>1444</v>
+      </c>
+      <c r="N903">
+        <v>444</v>
       </c>
       <c r="O903">
-        <v>889</v>
+        <v>1000</v>
       </c>
       <c r="P903">
-        <v>2000</v>
+        <v>2999</v>
       </c>
       <c r="Q903" t="s">
         <v>447</v>
@@ -34935,31 +34942,31 @@
     </row>
     <row r="904" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A904" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B904">
-        <v>-35.027099999999997</v>
+        <v>-35.023200000000003</v>
       </c>
       <c r="C904">
-        <v>138.51599999999999</v>
+        <v>138.5155</v>
       </c>
       <c r="D904" s="2">
         <v>46173</v>
       </c>
+      <c r="I904">
+        <v>333</v>
+      </c>
       <c r="J904">
         <v>0</v>
       </c>
       <c r="L904">
-        <v>1556</v>
-      </c>
-      <c r="N904">
-        <v>4667</v>
+        <v>778</v>
       </c>
       <c r="O904">
-        <v>2333</v>
+        <v>889</v>
       </c>
       <c r="P904">
-        <v>8556</v>
+        <v>2000</v>
       </c>
       <c r="Q904" t="s">
         <v>447</v>
@@ -34967,31 +34974,31 @@
     </row>
     <row r="905" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A905" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B905">
-        <v>-35.034999999999997</v>
+        <v>-35.027099999999997</v>
       </c>
       <c r="C905">
-        <v>138.5164</v>
+        <v>138.51599999999999</v>
       </c>
       <c r="D905" s="2">
         <v>46173</v>
       </c>
-      <c r="I905">
-        <v>167</v>
-      </c>
       <c r="J905">
         <v>0</v>
       </c>
       <c r="L905">
-        <v>167</v>
+        <v>1556</v>
+      </c>
+      <c r="N905">
+        <v>4667</v>
       </c>
       <c r="O905">
-        <v>1333</v>
+        <v>2333</v>
       </c>
       <c r="P905">
-        <v>1667</v>
+        <v>8556</v>
       </c>
       <c r="Q905" t="s">
         <v>447</v>
@@ -34999,28 +35006,31 @@
     </row>
     <row r="906" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A906" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B906">
-        <v>-35.029899999999998</v>
+        <v>-35.034999999999997</v>
       </c>
       <c r="C906">
-        <v>138.51599999999999</v>
+        <v>138.5164</v>
       </c>
       <c r="D906" s="2">
         <v>46173</v>
       </c>
+      <c r="I906">
+        <v>167</v>
+      </c>
       <c r="J906">
         <v>0</v>
       </c>
       <c r="L906">
-        <v>444</v>
+        <v>167</v>
       </c>
       <c r="O906">
         <v>1333</v>
       </c>
       <c r="P906">
-        <v>1778</v>
+        <v>1667</v>
       </c>
       <c r="Q906" t="s">
         <v>447</v>
@@ -35028,195 +35038,192 @@
     </row>
     <row r="907" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A907" t="s">
-        <v>311</v>
+        <v>444</v>
       </c>
       <c r="B907">
-        <v>-35.445059999999998</v>
+        <v>-35.029899999999998</v>
       </c>
       <c r="C907">
-        <v>138.30758399999999</v>
+        <v>138.51599999999999</v>
       </c>
       <c r="D907" s="2">
-        <v>46174</v>
-      </c>
-      <c r="E907" s="20">
-        <v>0.34375</v>
-      </c>
-      <c r="F907">
-        <v>0</v>
-      </c>
-      <c r="G907">
-        <v>0</v>
-      </c>
-      <c r="H907">
-        <v>0</v>
-      </c>
-      <c r="I907">
-        <v>56</v>
+        <v>46173</v>
       </c>
       <c r="J907">
         <v>0</v>
       </c>
-      <c r="K907">
-        <v>0</v>
-      </c>
       <c r="L907">
-        <v>56</v>
-      </c>
-      <c r="M907">
-        <v>0</v>
-      </c>
-      <c r="N907">
-        <v>56</v>
+        <v>444</v>
       </c>
       <c r="O907">
-        <v>56</v>
+        <v>1333</v>
       </c>
       <c r="P907">
-        <v>222</v>
+        <v>1778</v>
       </c>
       <c r="Q907" t="s">
-        <v>349</v>
+        <v>447</v>
       </c>
     </row>
     <row r="908" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A908" t="s">
-        <v>289</v>
+        <v>311</v>
       </c>
       <c r="B908">
-        <v>-34.628509999999999</v>
+        <v>-35.445059999999998</v>
       </c>
       <c r="C908">
-        <v>135.86675</v>
+        <v>138.30758399999999</v>
       </c>
       <c r="D908" s="2">
-        <v>46175</v>
+        <v>46174</v>
       </c>
       <c r="E908" s="20">
-        <v>0.52083333333333337</v>
+        <v>0.34375</v>
+      </c>
+      <c r="F908">
+        <v>0</v>
+      </c>
+      <c r="G908">
+        <v>0</v>
+      </c>
+      <c r="H908">
+        <v>0</v>
       </c>
       <c r="I908">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="J908">
-        <v>49</v>
+        <v>0</v>
+      </c>
+      <c r="K908">
+        <v>0</v>
       </c>
       <c r="L908">
-        <v>9</v>
+        <v>56</v>
+      </c>
+      <c r="M908">
+        <v>0</v>
+      </c>
+      <c r="N908">
+        <v>56</v>
       </c>
       <c r="O908">
-        <v>6</v>
+        <v>56</v>
       </c>
       <c r="P908">
-        <v>84</v>
+        <v>222</v>
       </c>
       <c r="Q908" t="s">
-        <v>283</v>
+        <v>349</v>
       </c>
     </row>
     <row r="909" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A909" t="s">
-        <v>59</v>
+        <v>289</v>
       </c>
       <c r="B909">
-        <v>-35.084850000000003</v>
+        <v>-34.628509999999999</v>
       </c>
       <c r="C909">
-        <v>137.74889999999999</v>
+        <v>135.86675</v>
       </c>
       <c r="D909" s="2">
-        <v>46176</v>
+        <v>46175</v>
       </c>
       <c r="E909" s="20">
-        <v>0.5</v>
-      </c>
-      <c r="G909">
-        <v>333</v>
-      </c>
-      <c r="H909">
-        <v>111</v>
+        <v>0.52083333333333337</v>
       </c>
       <c r="I909">
-        <v>111</v>
+        <v>69</v>
       </c>
       <c r="J909">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="L909">
-        <v>222</v>
-      </c>
-      <c r="M909">
-        <v>0</v>
-      </c>
-      <c r="N909">
-        <v>555</v>
+        <v>9</v>
       </c>
       <c r="O909">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P909">
-        <v>1332</v>
+        <v>84</v>
       </c>
       <c r="Q909" t="s">
-        <v>149</v>
+        <v>283</v>
       </c>
     </row>
     <row r="910" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A910" t="s">
-        <v>438</v>
+        <v>59</v>
       </c>
       <c r="B910">
-        <v>-34.629060000000003</v>
+        <v>-35.084850000000003</v>
       </c>
       <c r="C910">
-        <v>135.867411</v>
+        <v>137.74889999999999</v>
       </c>
       <c r="D910" s="2">
         <v>46176</v>
       </c>
+      <c r="E910" s="20">
+        <v>0.5</v>
+      </c>
+      <c r="G910">
+        <v>333</v>
+      </c>
+      <c r="H910">
+        <v>111</v>
+      </c>
       <c r="I910">
-        <v>4.9169999999999998</v>
+        <v>111</v>
       </c>
       <c r="J910">
-        <v>4.6669999999999998</v>
+        <v>0</v>
       </c>
       <c r="L910">
-        <v>2.3332999999999999</v>
+        <v>222</v>
+      </c>
+      <c r="M910">
+        <v>0</v>
+      </c>
+      <c r="N910">
+        <v>555</v>
+      </c>
+      <c r="O910">
+        <v>0</v>
       </c>
       <c r="P910">
-        <v>7.2503000000000002</v>
+        <v>1332</v>
       </c>
       <c r="Q910" t="s">
-        <v>78</v>
+        <v>149</v>
       </c>
     </row>
     <row r="911" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A911" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B911">
-        <v>-34.540291000000003</v>
+        <v>-34.629060000000003</v>
       </c>
       <c r="C911">
-        <v>135.934124</v>
+        <v>135.867411</v>
       </c>
       <c r="D911" s="2">
-        <v>46177</v>
+        <v>46176</v>
       </c>
       <c r="I911">
-        <v>4.92</v>
+        <v>4.9169999999999998</v>
       </c>
       <c r="J911">
-        <v>4.2</v>
+        <v>4.6669999999999998</v>
       </c>
       <c r="L911">
-        <v>1.44</v>
-      </c>
-      <c r="O911">
-        <v>0.9</v>
+        <v>2.3332999999999999</v>
       </c>
       <c r="P911">
-        <v>7.26</v>
+        <v>7.2503000000000002</v>
       </c>
       <c r="Q911" t="s">
         <v>78</v>
@@ -35224,769 +35231,739 @@
     </row>
     <row r="912" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A912" t="s">
-        <v>378</v>
+        <v>412</v>
       </c>
       <c r="B912">
-        <v>-34.933680000000003</v>
+        <v>-33.043101999999998</v>
       </c>
       <c r="C912">
-        <v>137.35257300000001</v>
+        <v>137.59395699999999</v>
       </c>
       <c r="D912" s="2">
-        <v>46178</v>
-      </c>
-      <c r="E912" s="24">
-        <v>0.75</v>
-      </c>
-      <c r="I912">
+        <v>46176</v>
+      </c>
+      <c r="E912" s="20">
+        <v>0.60763888888888884</v>
+      </c>
+      <c r="J912">
+        <v>0</v>
+      </c>
+      <c r="L912">
+        <v>2056</v>
+      </c>
+      <c r="O912">
         <v>500</v>
       </c>
-      <c r="J912">
-        <v>111</v>
-      </c>
-      <c r="L912">
-        <v>111</v>
-      </c>
-      <c r="N912">
-        <v>278</v>
-      </c>
-      <c r="O912">
-        <v>278</v>
-      </c>
       <c r="P912">
-        <v>1167</v>
+        <v>2556</v>
       </c>
       <c r="Q912" t="s">
-        <v>218</v>
+        <v>346</v>
       </c>
     </row>
     <row r="913" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A913" t="s">
-        <v>445</v>
+        <v>437</v>
       </c>
       <c r="B913">
-        <v>-34.766939999999998</v>
+        <v>-34.540291000000003</v>
       </c>
       <c r="C913">
-        <v>135.87030999999999</v>
+        <v>135.934124</v>
       </c>
       <c r="D913" s="2">
-        <v>46180</v>
-      </c>
-      <c r="E913" s="20">
-        <v>0.5625</v>
+        <v>46177</v>
       </c>
       <c r="I913">
-        <v>56</v>
+        <v>4.92</v>
       </c>
       <c r="J913">
-        <v>1</v>
+        <v>4.2</v>
       </c>
       <c r="L913">
-        <v>111</v>
+        <v>1.44</v>
       </c>
       <c r="O913">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="P913">
-        <v>167</v>
+        <v>7.26</v>
       </c>
       <c r="Q913" t="s">
-        <v>283</v>
+        <v>78</v>
       </c>
     </row>
     <row r="914" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A914" t="s">
-        <v>446</v>
+        <v>378</v>
       </c>
       <c r="B914">
-        <v>-34.768819999999998</v>
+        <v>-34.933680000000003</v>
       </c>
       <c r="C914">
-        <v>135.86268000000001</v>
+        <v>137.35257300000001</v>
       </c>
       <c r="D914" s="2">
-        <v>46180</v>
-      </c>
-      <c r="E914" s="20">
-        <v>0.58333333333333337</v>
+        <v>46178</v>
+      </c>
+      <c r="E914" s="24">
+        <v>0.75</v>
       </c>
       <c r="I914">
-        <v>612</v>
+        <v>500</v>
       </c>
       <c r="J914">
-        <v>556</v>
+        <v>111</v>
       </c>
       <c r="L914">
-        <v>56</v>
+        <v>111</v>
+      </c>
+      <c r="N914">
+        <v>278</v>
       </c>
       <c r="O914">
-        <v>56</v>
+        <v>278</v>
       </c>
       <c r="P914">
-        <v>724</v>
+        <v>1167</v>
       </c>
       <c r="Q914" t="s">
-        <v>283</v>
+        <v>218</v>
       </c>
     </row>
     <row r="915" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A915" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="B915">
-        <v>-35.595986000000003</v>
+        <v>-34.766939999999998</v>
       </c>
       <c r="C915">
-        <v>138.104072</v>
+        <v>135.87030999999999</v>
       </c>
       <c r="D915" s="2">
         <v>46180</v>
       </c>
       <c r="E915" s="20">
-        <v>0.50347222222222221</v>
-      </c>
-      <c r="F915">
-        <v>0</v>
-      </c>
-      <c r="G915">
-        <v>0</v>
-      </c>
-      <c r="H915">
-        <v>56</v>
+        <v>0.5625</v>
       </c>
       <c r="I915">
+        <v>56</v>
+      </c>
+      <c r="J915">
+        <v>1</v>
+      </c>
+      <c r="L915">
+        <v>111</v>
+      </c>
+      <c r="O915">
+        <v>0</v>
+      </c>
+      <c r="P915">
         <v>167</v>
       </c>
-      <c r="J915">
-        <v>0</v>
-      </c>
-      <c r="K915">
-        <v>0</v>
-      </c>
-      <c r="L915">
-        <v>56</v>
-      </c>
-      <c r="M915">
-        <v>0</v>
-      </c>
-      <c r="N915">
-        <v>778</v>
-      </c>
-      <c r="O915">
-        <v>0</v>
-      </c>
-      <c r="P915">
-        <v>1057</v>
-      </c>
       <c r="Q915" t="s">
-        <v>251</v>
+        <v>283</v>
       </c>
     </row>
     <row r="916" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A916" t="s">
-        <v>421</v>
+        <v>446</v>
       </c>
       <c r="B916">
-        <v>-35.500024000000003</v>
+        <v>-34.768819999999998</v>
       </c>
       <c r="C916">
-        <v>138.24287699999999</v>
+        <v>135.86268000000001</v>
       </c>
       <c r="D916" s="2">
         <v>46180</v>
       </c>
       <c r="E916" s="20">
-        <v>0.49305555555555558</v>
-      </c>
-      <c r="F916">
-        <v>0</v>
-      </c>
-      <c r="G916">
-        <v>0</v>
-      </c>
-      <c r="H916">
-        <v>222</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="I916">
-        <v>0</v>
+        <v>612</v>
       </c>
       <c r="J916">
-        <v>0</v>
-      </c>
-      <c r="K916">
-        <v>0</v>
+        <v>556</v>
       </c>
       <c r="L916">
         <v>56</v>
       </c>
-      <c r="M916">
-        <v>0</v>
-      </c>
-      <c r="N916">
-        <v>833</v>
-      </c>
       <c r="O916">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="P916">
-        <v>1111</v>
+        <v>724</v>
       </c>
       <c r="Q916" t="s">
-        <v>251</v>
+        <v>283</v>
       </c>
     </row>
     <row r="917" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A917" t="s">
-        <v>422</v>
+        <v>450</v>
       </c>
       <c r="B917">
-        <v>-34.979999999999997</v>
+        <v>-35.595986000000003</v>
       </c>
       <c r="C917">
-        <v>138.50800000000001</v>
+        <v>138.104072</v>
       </c>
       <c r="D917" s="2">
-        <v>46182</v>
+        <v>46180</v>
+      </c>
+      <c r="E917" s="20">
+        <v>0.50347222222222221</v>
+      </c>
+      <c r="F917">
+        <v>0</v>
+      </c>
+      <c r="G917">
+        <v>0</v>
+      </c>
+      <c r="H917">
+        <v>56</v>
       </c>
       <c r="I917">
-        <v>333</v>
+        <v>167</v>
       </c>
       <c r="J917">
         <v>0</v>
       </c>
+      <c r="K917">
+        <v>0</v>
+      </c>
       <c r="L917">
-        <v>111</v>
+        <v>56</v>
+      </c>
+      <c r="M917">
+        <v>0</v>
       </c>
       <c r="N917">
-        <v>1556</v>
+        <v>778</v>
       </c>
       <c r="O917">
-        <v>1667</v>
+        <v>0</v>
       </c>
       <c r="P917">
-        <v>3667</v>
+        <v>1057</v>
       </c>
       <c r="Q917" t="s">
-        <v>447</v>
+        <v>251</v>
       </c>
     </row>
     <row r="918" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A918" t="s">
-        <v>289</v>
+        <v>421</v>
       </c>
       <c r="B918">
-        <v>-34.628509999999999</v>
+        <v>-35.500024000000003</v>
       </c>
       <c r="C918">
-        <v>135.86675</v>
+        <v>138.24287699999999</v>
       </c>
       <c r="D918" s="2">
-        <v>46182</v>
+        <v>46180</v>
       </c>
       <c r="E918" s="20">
-        <v>0.54166666666666663</v>
+        <v>0.49305555555555558</v>
+      </c>
+      <c r="F918">
+        <v>0</v>
+      </c>
+      <c r="G918">
+        <v>0</v>
+      </c>
+      <c r="H918">
+        <v>222</v>
       </c>
       <c r="I918">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="J918">
-        <v>19</v>
+        <v>0</v>
+      </c>
+      <c r="K918">
+        <v>0</v>
       </c>
       <c r="L918">
-        <v>8</v>
+        <v>56</v>
+      </c>
+      <c r="M918">
+        <v>0</v>
+      </c>
+      <c r="N918">
+        <v>833</v>
       </c>
       <c r="O918">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P918">
-        <v>30</v>
+        <v>1111</v>
       </c>
       <c r="Q918" t="s">
-        <v>283</v>
+        <v>251</v>
       </c>
     </row>
     <row r="919" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A919" t="s">
-        <v>434</v>
+        <v>422</v>
       </c>
       <c r="B919">
-        <v>-34.540930000000003</v>
+        <v>-34.979999999999997</v>
       </c>
       <c r="C919">
-        <v>135.93384</v>
+        <v>138.50800000000001</v>
       </c>
       <c r="D919" s="2">
-        <v>46183</v>
-      </c>
-      <c r="E919" s="20">
-        <v>0.54166666666666663</v>
+        <v>46182</v>
       </c>
       <c r="I919">
-        <v>106</v>
+        <v>333</v>
       </c>
       <c r="J919">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="L919">
-        <v>28</v>
+        <v>111</v>
+      </c>
+      <c r="N919">
+        <v>1556</v>
       </c>
       <c r="O919">
-        <v>44</v>
+        <v>1667</v>
       </c>
       <c r="P919">
-        <v>178</v>
+        <v>3667</v>
       </c>
       <c r="Q919" t="s">
-        <v>283</v>
+        <v>447</v>
       </c>
     </row>
     <row r="920" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A920" t="s">
-        <v>426</v>
+        <v>289</v>
       </c>
       <c r="B920">
-        <v>-35.410254000000002</v>
+        <v>-34.628509999999999</v>
       </c>
       <c r="C920">
-        <v>138.32751999999999</v>
+        <v>135.86675</v>
       </c>
       <c r="D920" s="2">
-        <v>46183</v>
+        <v>46182</v>
       </c>
       <c r="E920" s="20">
-        <v>0.65277777777777779</v>
-      </c>
-      <c r="F920">
-        <v>0</v>
-      </c>
-      <c r="G920">
-        <v>0</v>
-      </c>
-      <c r="H920">
-        <v>333</v>
+        <v>0.54166666666666663</v>
       </c>
       <c r="I920">
-        <v>222</v>
+        <v>21</v>
       </c>
       <c r="J920">
-        <v>0</v>
-      </c>
-      <c r="K920">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="L920">
-        <v>111</v>
-      </c>
-      <c r="M920">
-        <v>0</v>
-      </c>
-      <c r="N920">
-        <v>500</v>
+        <v>8</v>
       </c>
       <c r="O920">
-        <v>222</v>
+        <v>1</v>
       </c>
       <c r="P920">
-        <v>1388</v>
+        <v>30</v>
       </c>
       <c r="Q920" t="s">
-        <v>251</v>
+        <v>283</v>
       </c>
     </row>
     <row r="921" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A921" t="s">
-        <v>59</v>
+        <v>434</v>
       </c>
       <c r="B921">
-        <v>-35.084850000000003</v>
+        <v>-34.540930000000003</v>
       </c>
       <c r="C921">
-        <v>137.74889999999999</v>
+        <v>135.93384</v>
       </c>
       <c r="D921" s="2">
-        <v>46184</v>
+        <v>46183</v>
       </c>
       <c r="E921" s="20">
-        <v>0.58333333333333337</v>
-      </c>
-      <c r="H921">
-        <v>222</v>
+        <v>0.54166666666666663</v>
       </c>
       <c r="I921">
-        <v>388</v>
+        <v>106</v>
       </c>
       <c r="J921">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="L921">
-        <v>444</v>
-      </c>
-      <c r="M921">
-        <v>0</v>
-      </c>
-      <c r="N921">
-        <v>1166</v>
+        <v>28</v>
       </c>
       <c r="O921">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="P921">
-        <v>2220</v>
+        <v>178</v>
       </c>
       <c r="Q921" t="s">
-        <v>149</v>
+        <v>283</v>
       </c>
     </row>
     <row r="922" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A922" t="s">
-        <v>92</v>
+        <v>426</v>
       </c>
       <c r="B922">
-        <v>-35.632150000000003</v>
+        <v>-35.410254000000002</v>
       </c>
       <c r="C922">
-        <v>138.48339999999999</v>
+        <v>138.32751999999999</v>
       </c>
       <c r="D922" s="2">
-        <v>46186</v>
+        <v>46183</v>
       </c>
       <c r="E922" s="20">
-        <v>0.46875</v>
+        <v>0.65277777777777779</v>
+      </c>
+      <c r="F922">
+        <v>0</v>
+      </c>
+      <c r="G922">
+        <v>0</v>
+      </c>
+      <c r="H922">
+        <v>333</v>
       </c>
       <c r="I922">
-        <v>0.35</v>
+        <v>222</v>
       </c>
       <c r="J922">
-        <v>0.05</v>
+        <v>0</v>
+      </c>
+      <c r="K922">
+        <v>0</v>
       </c>
       <c r="L922">
-        <v>14.25</v>
+        <v>111</v>
       </c>
       <c r="M922">
         <v>0</v>
       </c>
       <c r="N922">
-        <v>0.15</v>
+        <v>500</v>
       </c>
       <c r="O922">
-        <v>0.1</v>
+        <v>222</v>
       </c>
       <c r="P922">
-        <v>14.85</v>
+        <v>1388</v>
       </c>
       <c r="Q922" t="s">
-        <v>78</v>
+        <v>251</v>
       </c>
     </row>
     <row r="923" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A923" t="s">
-        <v>289</v>
+        <v>412</v>
       </c>
       <c r="B923">
-        <v>-34.628509999999999</v>
+        <v>-33.043101999999998</v>
       </c>
       <c r="C923">
-        <v>135.86675</v>
+        <v>137.59395699999999</v>
       </c>
       <c r="D923" s="2">
-        <v>46187</v>
+        <v>46183</v>
       </c>
       <c r="E923" s="20">
-        <v>0.69791666666666663</v>
-      </c>
-      <c r="I923">
-        <v>182</v>
+        <v>0.69444444444444442</v>
       </c>
       <c r="J923">
-        <v>176</v>
+        <v>0</v>
       </c>
       <c r="L923">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="O923">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="P923">
-        <v>201</v>
+        <v>74</v>
       </c>
       <c r="Q923" t="s">
-        <v>283</v>
+        <v>346</v>
       </c>
     </row>
     <row r="924" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A924" t="s">
-        <v>311</v>
+        <v>59</v>
       </c>
       <c r="B924">
-        <v>-35.445059999999998</v>
+        <v>-35.084850000000003</v>
       </c>
       <c r="C924">
-        <v>138.30758399999999</v>
+        <v>137.74889999999999</v>
       </c>
       <c r="D924" s="2">
-        <v>46188</v>
+        <v>46184</v>
       </c>
       <c r="E924" s="20">
-        <v>0.375</v>
-      </c>
-      <c r="F924">
-        <v>0</v>
-      </c>
-      <c r="G924">
-        <v>0</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="H924">
-        <v>0</v>
+        <v>222</v>
       </c>
       <c r="I924">
-        <v>56</v>
+        <v>388</v>
       </c>
       <c r="J924">
         <v>0</v>
       </c>
-      <c r="K924">
-        <v>0</v>
-      </c>
       <c r="L924">
-        <v>56</v>
+        <v>444</v>
       </c>
       <c r="M924">
         <v>0</v>
       </c>
       <c r="N924">
-        <v>0</v>
+        <v>1166</v>
       </c>
       <c r="O924">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="P924">
-        <v>223</v>
+        <v>2220</v>
       </c>
       <c r="Q924" t="s">
-        <v>401</v>
+        <v>149</v>
       </c>
     </row>
     <row r="925" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A925" t="s">
-        <v>289</v>
+        <v>92</v>
       </c>
       <c r="B925">
-        <v>-34.628509999999999</v>
+        <v>-35.632150000000003</v>
       </c>
       <c r="C925">
-        <v>135.86675</v>
+        <v>138.48339999999999</v>
       </c>
       <c r="D925" s="2">
-        <v>46189</v>
+        <v>46186</v>
       </c>
       <c r="E925" s="20">
-        <v>0.70833333333333337</v>
+        <v>0.46875</v>
       </c>
       <c r="I925">
-        <v>131</v>
+        <v>0.35</v>
       </c>
       <c r="J925">
-        <v>121</v>
+        <v>0.05</v>
       </c>
       <c r="L925">
-        <v>2</v>
+        <v>14.25</v>
+      </c>
+      <c r="M925">
+        <v>0</v>
+      </c>
+      <c r="N925">
+        <v>0.15</v>
       </c>
       <c r="O925">
-        <v>2</v>
+        <v>0.1</v>
       </c>
       <c r="P925">
-        <v>135</v>
+        <v>14.85</v>
       </c>
       <c r="Q925" t="s">
-        <v>283</v>
+        <v>78</v>
       </c>
     </row>
     <row r="926" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A926" t="s">
-        <v>59</v>
+        <v>289</v>
       </c>
       <c r="B926">
-        <v>-35.084850000000003</v>
+        <v>-34.628509999999999</v>
       </c>
       <c r="C926">
-        <v>137.74889999999999</v>
+        <v>135.86675</v>
       </c>
       <c r="D926" s="2">
-        <v>46190</v>
+        <v>46187</v>
       </c>
       <c r="E926" s="20">
-        <v>0.58333333333333337</v>
-      </c>
-      <c r="G926">
-        <v>333</v>
-      </c>
-      <c r="H926">
-        <v>389</v>
+        <v>0.69791666666666663</v>
       </c>
       <c r="I926">
-        <v>277</v>
+        <v>182</v>
       </c>
       <c r="J926">
-        <v>0</v>
-      </c>
-      <c r="M926">
-        <v>0</v>
-      </c>
-      <c r="N926">
-        <v>556</v>
+        <v>176</v>
+      </c>
+      <c r="L926">
+        <v>17</v>
       </c>
       <c r="O926">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P926">
-        <v>1555</v>
+        <v>201</v>
       </c>
       <c r="Q926" t="s">
-        <v>149</v>
+        <v>283</v>
       </c>
     </row>
     <row r="927" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A927" t="s">
-        <v>289</v>
+        <v>311</v>
       </c>
       <c r="B927">
-        <v>-34.628509999999999</v>
+        <v>-35.445059999999998</v>
       </c>
       <c r="C927">
-        <v>135.86675</v>
+        <v>138.30758399999999</v>
       </c>
       <c r="D927" s="2">
-        <v>46190</v>
+        <v>46188</v>
       </c>
       <c r="E927" s="20">
-        <v>0.56944444444444442</v>
+        <v>0.375</v>
+      </c>
+      <c r="F927">
+        <v>0</v>
+      </c>
+      <c r="G927">
+        <v>0</v>
+      </c>
+      <c r="H927">
+        <v>0</v>
       </c>
       <c r="I927">
-        <v>611</v>
+        <v>56</v>
       </c>
       <c r="J927">
-        <v>611</v>
+        <v>0</v>
+      </c>
+      <c r="K927">
+        <v>0</v>
       </c>
       <c r="L927">
-        <v>222</v>
+        <v>56</v>
+      </c>
+      <c r="M927">
+        <v>0</v>
+      </c>
+      <c r="N927">
+        <v>0</v>
       </c>
       <c r="O927">
-        <v>56</v>
+        <v>111</v>
       </c>
       <c r="P927">
-        <v>889</v>
+        <v>223</v>
       </c>
       <c r="Q927" t="s">
-        <v>283</v>
+        <v>401</v>
       </c>
     </row>
     <row r="928" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A928" t="s">
-        <v>454</v>
+        <v>289</v>
       </c>
       <c r="B928">
-        <v>-34.978150999999997</v>
+        <v>-34.628509999999999</v>
       </c>
       <c r="C928">
-        <v>138.50750400000001</v>
+        <v>135.86675</v>
       </c>
       <c r="D928" s="2">
-        <v>46190</v>
+        <v>46189</v>
       </c>
       <c r="E928" s="20">
-        <v>0.59236111111111112</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="I928">
-        <v>167</v>
+        <v>131</v>
       </c>
       <c r="J928">
-        <v>0</v>
+        <v>121</v>
       </c>
       <c r="L928">
-        <v>333</v>
-      </c>
-      <c r="N928">
-        <v>667</v>
+        <v>2</v>
       </c>
       <c r="O928">
-        <v>389</v>
+        <v>2</v>
       </c>
       <c r="P928">
-        <v>1556</v>
+        <v>135</v>
       </c>
       <c r="Q928" t="s">
-        <v>447</v>
+        <v>283</v>
       </c>
     </row>
     <row r="929" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A929" t="s">
-        <v>426</v>
+        <v>59</v>
       </c>
       <c r="B929">
-        <v>-35.410254000000002</v>
+        <v>-35.084850000000003</v>
       </c>
       <c r="C929">
-        <v>138.32751999999999</v>
+        <v>137.74889999999999</v>
       </c>
       <c r="D929" s="2">
         <v>46190</v>
       </c>
       <c r="E929" s="20">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="F929">
-        <v>0</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="G929">
-        <v>0</v>
+        <v>333</v>
       </c>
       <c r="H929">
-        <v>0</v>
+        <v>389</v>
       </c>
       <c r="I929">
-        <v>0</v>
+        <v>277</v>
       </c>
       <c r="J929">
         <v>0</v>
       </c>
-      <c r="K929">
-        <v>56</v>
-      </c>
-      <c r="L929">
-        <v>56</v>
-      </c>
       <c r="M929">
         <v>0</v>
       </c>
       <c r="N929">
-        <v>833</v>
+        <v>556</v>
       </c>
       <c r="O929">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="P929">
-        <v>1056</v>
+        <v>1555</v>
       </c>
       <c r="Q929" t="s">
-        <v>251</v>
+        <v>149</v>
       </c>
     </row>
     <row r="930" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A930" t="s">
-        <v>434</v>
+        <v>289</v>
       </c>
       <c r="B930">
-        <v>-34.540880000000001</v>
+        <v>-34.628509999999999</v>
       </c>
       <c r="C930">
-        <v>135.93384</v>
+        <v>135.86675</v>
       </c>
       <c r="D930" s="2">
-        <v>46191</v>
+        <v>46190</v>
       </c>
       <c r="E930" s="20">
-        <v>0.44791666666666669</v>
+        <v>0.56944444444444442</v>
       </c>
       <c r="I930">
         <v>611</v>
@@ -35995,13 +35972,13 @@
         <v>611</v>
       </c>
       <c r="L930">
-        <v>167</v>
+        <v>222</v>
       </c>
       <c r="O930">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="P930">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="Q930" t="s">
         <v>283</v>
@@ -36009,321 +35986,339 @@
     </row>
     <row r="931" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A931" t="s">
-        <v>289</v>
+        <v>454</v>
       </c>
       <c r="B931">
-        <v>-34.628509999999999</v>
+        <v>-34.978150999999997</v>
       </c>
       <c r="C931">
-        <v>135.86675</v>
+        <v>138.50750400000001</v>
       </c>
       <c r="D931" s="2">
-        <v>46192</v>
+        <v>46190</v>
+      </c>
+      <c r="E931" s="20">
+        <v>0.59236111111111112</v>
       </c>
       <c r="I931">
-        <v>661</v>
+        <v>167</v>
       </c>
       <c r="J931">
-        <v>661</v>
+        <v>0</v>
       </c>
       <c r="L931">
-        <v>222</v>
+        <v>333</v>
+      </c>
+      <c r="N931">
+        <v>667</v>
       </c>
       <c r="O931">
-        <v>0</v>
+        <v>389</v>
       </c>
       <c r="P931">
-        <v>883</v>
+        <v>1556</v>
       </c>
       <c r="Q931" t="s">
-        <v>283</v>
+        <v>447</v>
       </c>
     </row>
     <row r="932" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A932" t="s">
-        <v>452</v>
+        <v>426</v>
       </c>
       <c r="B932">
-        <v>-34.759</v>
+        <v>-35.410254000000002</v>
       </c>
       <c r="C932">
-        <v>135.83886000000001</v>
+        <v>138.32751999999999</v>
       </c>
       <c r="D932" s="2">
-        <v>46193</v>
+        <v>46190</v>
       </c>
       <c r="E932" s="20">
-        <v>0.53125</v>
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="F932">
+        <v>0</v>
+      </c>
+      <c r="G932">
+        <v>0</v>
+      </c>
+      <c r="H932">
+        <v>0</v>
       </c>
       <c r="I932">
-        <v>612</v>
+        <v>0</v>
       </c>
       <c r="J932">
-        <v>556</v>
+        <v>0</v>
+      </c>
+      <c r="K932">
+        <v>56</v>
       </c>
       <c r="L932">
-        <v>500</v>
+        <v>56</v>
+      </c>
+      <c r="M932">
+        <v>0</v>
+      </c>
+      <c r="N932">
+        <v>833</v>
       </c>
       <c r="O932">
-        <v>56</v>
+        <v>111</v>
       </c>
       <c r="P932">
-        <v>1168</v>
+        <v>1056</v>
       </c>
       <c r="Q932" t="s">
-        <v>283</v>
+        <v>251</v>
       </c>
     </row>
     <row r="933" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A933" t="s">
-        <v>359</v>
+        <v>434</v>
       </c>
       <c r="B933">
-        <v>-35.878667100000001</v>
+        <v>-34.540880000000001</v>
       </c>
       <c r="C933">
-        <v>137.6963188</v>
+        <v>135.93384</v>
       </c>
       <c r="D933" s="2">
-        <v>46193</v>
-      </c>
-      <c r="F933">
-        <v>0</v>
-      </c>
-      <c r="G933">
-        <v>0</v>
-      </c>
-      <c r="H933">
-        <v>0</v>
+        <v>46191</v>
+      </c>
+      <c r="E933" s="20">
+        <v>0.44791666666666669</v>
       </c>
       <c r="I933">
-        <v>0</v>
+        <v>611</v>
       </c>
       <c r="J933">
-        <v>0</v>
-      </c>
-      <c r="K933">
-        <v>0</v>
+        <v>611</v>
       </c>
       <c r="L933">
-        <v>0</v>
-      </c>
-      <c r="M933">
-        <v>0</v>
-      </c>
-      <c r="N933">
-        <v>0</v>
+        <v>167</v>
       </c>
       <c r="O933">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="P933">
-        <v>0</v>
+        <v>890</v>
       </c>
       <c r="Q933" t="s">
-        <v>456</v>
+        <v>283</v>
       </c>
     </row>
     <row r="934" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A934" t="s">
-        <v>457</v>
+        <v>289</v>
       </c>
       <c r="B934">
-        <v>-35.6614383</v>
+        <v>-34.628509999999999</v>
       </c>
       <c r="C934">
-        <v>137.6319307</v>
+        <v>135.86675</v>
       </c>
       <c r="D934" s="2">
-        <v>46193</v>
-      </c>
-      <c r="E934" s="20">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="F934">
-        <v>0</v>
-      </c>
-      <c r="G934">
-        <v>0</v>
-      </c>
-      <c r="H934">
-        <v>0</v>
+        <v>46192</v>
       </c>
       <c r="I934">
-        <v>0</v>
+        <v>661</v>
       </c>
       <c r="J934">
-        <v>0</v>
-      </c>
-      <c r="K934">
-        <v>0</v>
+        <v>661</v>
       </c>
       <c r="L934">
-        <v>333</v>
-      </c>
-      <c r="M934">
-        <v>0</v>
-      </c>
-      <c r="N934">
-        <v>0</v>
+        <v>222</v>
       </c>
       <c r="O934">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P934">
-        <v>334</v>
+        <v>883</v>
       </c>
       <c r="Q934" t="s">
-        <v>456</v>
+        <v>283</v>
       </c>
     </row>
     <row r="935" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A935" t="s">
-        <v>86</v>
+        <v>452</v>
       </c>
       <c r="B935">
-        <v>-35.540277000000003</v>
+        <v>-34.759</v>
       </c>
       <c r="C935">
-        <v>138.66416599999999</v>
+        <v>135.83886000000001</v>
       </c>
       <c r="D935" s="2">
-        <v>46194</v>
+        <v>46193</v>
       </c>
       <c r="E935" s="20">
-        <v>0.36041666666666666</v>
-      </c>
-      <c r="G935">
-        <v>56</v>
-      </c>
-      <c r="H935">
-        <v>56</v>
+        <v>0.53125</v>
       </c>
       <c r="I935">
-        <v>56</v>
+        <v>612</v>
       </c>
       <c r="J935">
-        <v>0</v>
+        <v>556</v>
       </c>
       <c r="L935">
-        <v>333</v>
-      </c>
-      <c r="N935">
-        <v>278</v>
+        <v>500</v>
       </c>
       <c r="O935">
-        <v>222</v>
+        <v>56</v>
       </c>
       <c r="P935">
-        <v>1001</v>
+        <v>1168</v>
       </c>
       <c r="Q935" t="s">
-        <v>129</v>
+        <v>283</v>
       </c>
     </row>
     <row r="936" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A936" t="s">
-        <v>100</v>
+        <v>359</v>
       </c>
       <c r="B936">
-        <v>-35.536745000000003</v>
+        <v>-35.878667100000001</v>
       </c>
       <c r="C936">
-        <v>138.6913744</v>
+        <v>137.6963188</v>
       </c>
       <c r="D936" s="2">
-        <v>46194</v>
-      </c>
-      <c r="E936" s="20">
-        <v>0.36666666666666664</v>
+        <v>46193</v>
+      </c>
+      <c r="F936">
+        <v>0</v>
+      </c>
+      <c r="G936">
+        <v>0</v>
       </c>
       <c r="H936">
-        <v>222</v>
+        <v>0</v>
+      </c>
+      <c r="I936">
+        <v>0</v>
       </c>
       <c r="J936">
         <v>0</v>
       </c>
+      <c r="K936">
+        <v>0</v>
+      </c>
       <c r="L936">
-        <v>222</v>
+        <v>0</v>
+      </c>
+      <c r="M936">
+        <v>0</v>
       </c>
       <c r="N936">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="O936">
-        <v>834</v>
+        <v>0</v>
       </c>
       <c r="P936">
-        <v>1778</v>
+        <v>0</v>
       </c>
       <c r="Q936" t="s">
-        <v>129</v>
+        <v>151</v>
       </c>
     </row>
     <row r="937" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A937" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="B937">
-        <v>-35.576688130000001</v>
+        <v>-35.6614383</v>
       </c>
       <c r="C937">
-        <v>138.64694589999999</v>
+        <v>137.6319307</v>
       </c>
       <c r="D937" s="2">
-        <v>46194</v>
+        <v>46193</v>
+      </c>
+      <c r="E937" s="20">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="F937">
+        <v>0</v>
+      </c>
+      <c r="G937">
+        <v>0</v>
+      </c>
+      <c r="H937">
+        <v>0</v>
       </c>
       <c r="I937">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="J937">
         <v>0</v>
       </c>
+      <c r="K937">
+        <v>0</v>
+      </c>
       <c r="L937">
-        <v>722</v>
+        <v>333</v>
+      </c>
+      <c r="M937">
+        <v>0</v>
       </c>
       <c r="N937">
-        <v>167</v>
+        <v>0</v>
       </c>
       <c r="O937">
-        <v>1666</v>
+        <v>1</v>
       </c>
       <c r="P937">
-        <v>2666</v>
+        <v>334</v>
       </c>
       <c r="Q937" t="s">
-        <v>129</v>
+        <v>151</v>
       </c>
     </row>
     <row r="938" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A938" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B938">
-        <v>-35.573300000000003</v>
+        <v>-35.540277000000003</v>
       </c>
       <c r="C938">
-        <v>138.64250000000001</v>
+        <v>138.66416599999999</v>
       </c>
       <c r="D938" s="2">
         <v>46194</v>
       </c>
+      <c r="E938" s="20">
+        <v>0.36041666666666666</v>
+      </c>
       <c r="G938">
         <v>56</v>
       </c>
+      <c r="H938">
+        <v>56</v>
+      </c>
+      <c r="I938">
+        <v>56</v>
+      </c>
       <c r="J938">
         <v>0</v>
       </c>
       <c r="L938">
-        <v>111</v>
+        <v>333</v>
       </c>
       <c r="N938">
-        <v>56</v>
+        <v>278</v>
       </c>
       <c r="O938">
-        <v>389</v>
+        <v>222</v>
       </c>
       <c r="P938">
-        <v>612</v>
+        <v>1001</v>
       </c>
       <c r="Q938" t="s">
         <v>129</v>
@@ -36331,22 +36326,22 @@
     </row>
     <row r="939" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A939" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="B939">
-        <v>-35.581124000000003</v>
+        <v>-35.536745000000003</v>
       </c>
       <c r="C939">
-        <v>138.60879700000001</v>
+        <v>138.6913744</v>
       </c>
       <c r="D939" s="2">
         <v>46194</v>
       </c>
-      <c r="F939">
-        <v>56</v>
-      </c>
-      <c r="G939">
-        <v>167</v>
+      <c r="E939" s="20">
+        <v>0.36666666666666664</v>
+      </c>
+      <c r="H939">
+        <v>222</v>
       </c>
       <c r="J939">
         <v>0</v>
@@ -36355,13 +36350,13 @@
         <v>222</v>
       </c>
       <c r="N939">
-        <v>278</v>
+        <v>500</v>
       </c>
       <c r="O939">
-        <v>389</v>
+        <v>834</v>
       </c>
       <c r="P939">
-        <v>1112</v>
+        <v>1778</v>
       </c>
       <c r="Q939" t="s">
         <v>129</v>
@@ -36369,40 +36364,34 @@
     </row>
     <row r="940" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A940" t="s">
-        <v>89</v>
+        <v>451</v>
       </c>
       <c r="B940">
-        <v>-35.6048446</v>
+        <v>-35.576688130000001</v>
       </c>
       <c r="C940">
-        <v>138.59278499999999</v>
+        <v>138.64694589999999</v>
       </c>
       <c r="D940" s="2">
         <v>46194</v>
       </c>
-      <c r="G940">
+      <c r="I940">
         <v>111</v>
       </c>
-      <c r="H940">
+      <c r="J940">
+        <v>0</v>
+      </c>
+      <c r="L940">
+        <v>722</v>
+      </c>
+      <c r="N940">
         <v>167</v>
       </c>
-      <c r="I940">
-        <v>167</v>
-      </c>
-      <c r="J940">
-        <v>0</v>
-      </c>
-      <c r="L940">
-        <v>56</v>
-      </c>
-      <c r="N940">
-        <v>778</v>
-      </c>
       <c r="O940">
-        <v>667</v>
+        <v>1666</v>
       </c>
       <c r="P940">
-        <v>1946</v>
+        <v>2666</v>
       </c>
       <c r="Q940" t="s">
         <v>129</v>
@@ -36410,34 +36399,34 @@
     </row>
     <row r="941" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A941" t="s">
-        <v>374</v>
+        <v>87</v>
       </c>
       <c r="B941">
-        <v>-35.612285999999997</v>
+        <v>-35.573300000000003</v>
       </c>
       <c r="C941">
-        <v>138.564302</v>
+        <v>138.64250000000001</v>
       </c>
       <c r="D941" s="2">
         <v>46194</v>
       </c>
-      <c r="H941">
+      <c r="G941">
+        <v>56</v>
+      </c>
+      <c r="J941">
+        <v>0</v>
+      </c>
+      <c r="L941">
         <v>111</v>
       </c>
-      <c r="I941">
-        <v>111</v>
-      </c>
-      <c r="J941">
-        <v>0</v>
-      </c>
       <c r="N941">
-        <v>444</v>
+        <v>56</v>
       </c>
       <c r="O941">
-        <v>167</v>
+        <v>389</v>
       </c>
       <c r="P941">
-        <v>833</v>
+        <v>612</v>
       </c>
       <c r="Q941" t="s">
         <v>129</v>
@@ -36445,34 +36434,37 @@
     </row>
     <row r="942" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A942" t="s">
-        <v>431</v>
+        <v>88</v>
       </c>
       <c r="B942">
-        <v>-35.619</v>
+        <v>-35.581124000000003</v>
       </c>
       <c r="C942">
-        <v>138.58099999999999</v>
+        <v>138.60879700000001</v>
       </c>
       <c r="D942" s="2">
         <v>46194</v>
       </c>
+      <c r="F942">
+        <v>56</v>
+      </c>
       <c r="G942">
-        <v>56</v>
-      </c>
-      <c r="H942">
-        <v>111</v>
+        <v>167</v>
       </c>
       <c r="J942">
         <v>0</v>
       </c>
+      <c r="L942">
+        <v>222</v>
+      </c>
       <c r="N942">
-        <v>1056</v>
+        <v>278</v>
       </c>
       <c r="O942">
-        <v>56</v>
+        <v>389</v>
       </c>
       <c r="P942">
-        <v>1279</v>
+        <v>1112</v>
       </c>
       <c r="Q942" t="s">
         <v>129</v>
@@ -36480,151 +36472,130 @@
     </row>
     <row r="943" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A943" t="s">
-        <v>455</v>
+        <v>89</v>
       </c>
       <c r="B943">
-        <v>-35.576250000000002</v>
+        <v>-35.6048446</v>
       </c>
       <c r="C943">
-        <v>138.64349999999999</v>
+        <v>138.59278499999999</v>
       </c>
       <c r="D943" s="2">
         <v>46194</v>
       </c>
-      <c r="E943" s="20">
-        <v>0.38541666666666669</v>
+      <c r="G943">
+        <v>111</v>
+      </c>
+      <c r="H943">
+        <v>167</v>
       </c>
       <c r="I943">
-        <v>56</v>
+        <v>167</v>
       </c>
       <c r="J943">
         <v>0</v>
       </c>
       <c r="L943">
-        <v>1333</v>
+        <v>56</v>
       </c>
       <c r="N943">
-        <v>56</v>
+        <v>778</v>
       </c>
       <c r="O943">
-        <v>167</v>
+        <v>667</v>
       </c>
       <c r="P943">
-        <v>1612</v>
+        <v>1946</v>
       </c>
       <c r="Q943" t="s">
-        <v>447</v>
+        <v>129</v>
       </c>
     </row>
     <row r="944" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A944" t="s">
-        <v>88</v>
+        <v>374</v>
       </c>
       <c r="B944">
-        <v>-35.581982000000004</v>
+        <v>-35.612285999999997</v>
       </c>
       <c r="C944">
-        <v>138.60827699999999</v>
+        <v>138.564302</v>
       </c>
       <c r="D944" s="2">
         <v>46194</v>
       </c>
-      <c r="E944" s="20">
-        <v>9</v>
+      <c r="H944">
+        <v>111</v>
+      </c>
+      <c r="I944">
+        <v>111</v>
       </c>
       <c r="J944">
         <v>0</v>
       </c>
       <c r="N944">
-        <v>1611</v>
+        <v>444</v>
       </c>
       <c r="O944">
-        <v>222</v>
+        <v>167</v>
       </c>
       <c r="P944">
-        <v>1833</v>
+        <v>833</v>
       </c>
       <c r="Q944" t="s">
-        <v>447</v>
+        <v>129</v>
       </c>
     </row>
     <row r="945" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A945" t="s">
-        <v>400</v>
+        <v>431</v>
       </c>
       <c r="B945">
-        <v>-35.510497000000001</v>
+        <v>-35.619</v>
       </c>
       <c r="C945">
-        <v>138.21676299999999</v>
+        <v>138.58099999999999</v>
       </c>
       <c r="D945" s="2">
         <v>46194</v>
       </c>
-      <c r="E945" s="20">
-        <v>0.58333333333333337</v>
-      </c>
-      <c r="F945">
-        <v>167</v>
-      </c>
       <c r="G945">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="H945">
-        <v>222</v>
-      </c>
-      <c r="I945">
-        <v>278</v>
+        <v>111</v>
       </c>
       <c r="J945">
         <v>0</v>
       </c>
-      <c r="K945">
-        <v>0</v>
-      </c>
-      <c r="L945">
-        <v>167</v>
-      </c>
-      <c r="M945">
-        <v>0</v>
-      </c>
       <c r="N945">
-        <v>833</v>
+        <v>1056</v>
       </c>
       <c r="O945">
-        <v>333</v>
+        <v>56</v>
       </c>
       <c r="P945">
-        <v>2000</v>
+        <v>1279</v>
       </c>
       <c r="Q945" t="s">
-        <v>251</v>
+        <v>129</v>
       </c>
     </row>
     <row r="946" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A946" t="s">
-        <v>311</v>
+        <v>455</v>
       </c>
       <c r="B946">
-        <v>-35.445059999999998</v>
+        <v>-35.576250000000002</v>
       </c>
       <c r="C946">
-        <v>138.30758399999999</v>
+        <v>138.64349999999999</v>
       </c>
       <c r="D946" s="2">
-        <v>46195</v>
+        <v>46194</v>
       </c>
       <c r="E946" s="20">
-        <v>0.39583333333333331</v>
-      </c>
-      <c r="F946">
-        <v>0</v>
-      </c>
-      <c r="G946">
-        <v>0</v>
-      </c>
-      <c r="H946">
-        <v>0</v>
+        <v>0.38541666666666669</v>
       </c>
       <c r="I946">
         <v>56</v>
@@ -36632,108 +36603,81 @@
       <c r="J946">
         <v>0</v>
       </c>
-      <c r="K946">
-        <v>0</v>
-      </c>
       <c r="L946">
-        <v>0</v>
-      </c>
-      <c r="M946">
-        <v>0</v>
+        <v>1333</v>
       </c>
       <c r="N946">
-        <v>611</v>
+        <v>56</v>
       </c>
       <c r="O946">
-        <v>56</v>
+        <v>167</v>
       </c>
       <c r="P946">
-        <v>723</v>
+        <v>1612</v>
       </c>
       <c r="Q946" t="s">
-        <v>401</v>
+        <v>447</v>
       </c>
     </row>
     <row r="947" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A947" t="s">
-        <v>395</v>
+        <v>88</v>
       </c>
       <c r="B947">
-        <v>-35.793973000000001</v>
+        <v>-35.581982000000004</v>
       </c>
       <c r="C947">
-        <v>137.852418</v>
+        <v>138.60827699999999</v>
       </c>
       <c r="D947" s="2">
-        <v>46195</v>
+        <v>46194</v>
       </c>
       <c r="E947" s="20">
-        <v>0.58333333333333337</v>
-      </c>
-      <c r="F947">
-        <v>0</v>
-      </c>
-      <c r="G947">
-        <v>0</v>
-      </c>
-      <c r="H947">
-        <v>0</v>
-      </c>
-      <c r="I947">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J947">
         <v>0</v>
       </c>
-      <c r="K947">
-        <v>0</v>
-      </c>
-      <c r="L947">
-        <v>0</v>
-      </c>
-      <c r="M947">
-        <v>0</v>
-      </c>
       <c r="N947">
-        <v>0</v>
+        <v>1611</v>
       </c>
       <c r="O947">
-        <v>0</v>
+        <v>222</v>
       </c>
       <c r="P947">
-        <v>0</v>
+        <v>1833</v>
       </c>
       <c r="Q947" t="s">
-        <v>456</v>
+        <v>447</v>
       </c>
     </row>
     <row r="948" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A948" t="s">
-        <v>256</v>
+        <v>400</v>
       </c>
       <c r="B948">
-        <v>-35.7987082</v>
+        <v>-35.510497000000001</v>
       </c>
       <c r="C948">
-        <v>137.81647699999999</v>
+        <v>138.21676299999999</v>
       </c>
       <c r="D948" s="2">
-        <v>46195</v>
+        <v>46194</v>
       </c>
       <c r="E948" s="20">
-        <v>0.60416666666666663</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="F948">
-        <v>0</v>
+        <v>167</v>
       </c>
       <c r="G948">
         <v>0</v>
       </c>
       <c r="H948">
-        <v>0</v>
+        <v>222</v>
       </c>
       <c r="I948">
-        <v>0</v>
+        <v>278</v>
       </c>
       <c r="J948">
         <v>0</v>
@@ -36742,408 +36686,1207 @@
         <v>0</v>
       </c>
       <c r="L948">
-        <v>0</v>
+        <v>167</v>
       </c>
       <c r="M948">
         <v>0</v>
       </c>
       <c r="N948">
-        <v>0</v>
+        <v>833</v>
       </c>
       <c r="O948">
-        <v>0</v>
+        <v>333</v>
       </c>
       <c r="P948">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="Q948" t="s">
-        <v>456</v>
+        <v>251</v>
       </c>
     </row>
     <row r="949" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A949" t="s">
-        <v>434</v>
+        <v>311</v>
       </c>
       <c r="B949">
-        <v>-34.540880000000001</v>
+        <v>-35.445059999999998</v>
       </c>
       <c r="C949">
-        <v>135.93384</v>
+        <v>138.30758399999999</v>
       </c>
       <c r="D949" s="2">
-        <v>46196</v>
+        <v>46195</v>
       </c>
       <c r="E949" s="20">
-        <v>0.35416666666666669</v>
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="F949">
+        <v>0</v>
+      </c>
+      <c r="G949">
+        <v>0</v>
+      </c>
+      <c r="H949">
+        <v>0</v>
       </c>
       <c r="I949">
-        <v>1111</v>
+        <v>56</v>
       </c>
       <c r="J949">
-        <v>1111</v>
+        <v>0</v>
+      </c>
+      <c r="K949">
+        <v>0</v>
       </c>
       <c r="L949">
+        <v>0</v>
+      </c>
+      <c r="M949">
+        <v>0</v>
+      </c>
+      <c r="N949">
         <v>611</v>
       </c>
       <c r="O949">
         <v>56</v>
       </c>
       <c r="P949">
-        <v>1778</v>
+        <v>723</v>
       </c>
       <c r="Q949" t="s">
-        <v>283</v>
+        <v>401</v>
       </c>
     </row>
     <row r="950" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A950" t="s">
-        <v>453</v>
+        <v>395</v>
       </c>
       <c r="B950">
-        <v>-34.718809999999998</v>
+        <v>-35.793973000000001</v>
       </c>
       <c r="C950">
-        <v>135.85857999999999</v>
+        <v>137.852418</v>
       </c>
       <c r="D950" s="2">
-        <v>46196</v>
+        <v>46195</v>
       </c>
       <c r="E950" s="20">
-        <v>46197.375</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="F950">
+        <v>0</v>
+      </c>
+      <c r="G950">
+        <v>0</v>
+      </c>
+      <c r="H950">
+        <v>0</v>
       </c>
       <c r="I950">
-        <v>1167</v>
+        <v>0</v>
       </c>
       <c r="J950">
-        <v>1111</v>
+        <v>0</v>
+      </c>
+      <c r="K950">
+        <v>0</v>
+      </c>
+      <c r="L950">
+        <v>0</v>
+      </c>
+      <c r="M950">
+        <v>0</v>
+      </c>
+      <c r="N950">
+        <v>0</v>
       </c>
       <c r="O950">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="P950">
-        <v>1223</v>
+        <v>0</v>
       </c>
       <c r="Q950" t="s">
-        <v>283</v>
+        <v>151</v>
       </c>
     </row>
     <row r="951" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A951" t="s">
-        <v>79</v>
+        <v>256</v>
       </c>
       <c r="B951">
-        <v>-34.804662999999998</v>
+        <v>-35.7987082</v>
       </c>
       <c r="C951">
-        <v>138.540223</v>
+        <v>137.81647699999999</v>
       </c>
       <c r="D951" s="2">
-        <v>46196</v>
+        <v>46195</v>
       </c>
       <c r="E951" s="20">
-        <v>0.58333333333333337</v>
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="F951">
+        <v>0</v>
+      </c>
+      <c r="G951">
+        <v>0</v>
+      </c>
+      <c r="H951">
+        <v>0</v>
       </c>
       <c r="I951">
-        <v>2.7749999999999999</v>
+        <v>0</v>
       </c>
       <c r="J951">
         <v>0</v>
       </c>
+      <c r="K951">
+        <v>0</v>
+      </c>
       <c r="L951">
-        <v>6.2249999999999996</v>
+        <v>0</v>
+      </c>
+      <c r="M951">
+        <v>0</v>
+      </c>
+      <c r="N951">
+        <v>0</v>
       </c>
       <c r="O951">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="P951">
-        <v>10.65</v>
+        <v>0</v>
       </c>
       <c r="Q951" t="s">
-        <v>78</v>
+        <v>151</v>
       </c>
     </row>
     <row r="952" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A952" t="s">
-        <v>267</v>
+        <v>434</v>
       </c>
       <c r="B952">
-        <v>-34.824044999999998</v>
+        <v>-34.540880000000001</v>
       </c>
       <c r="C952">
-        <v>138.48377600000001</v>
+        <v>135.93384</v>
       </c>
       <c r="D952" s="2">
         <v>46196</v>
       </c>
       <c r="E952" s="20">
-        <v>0.55694444444444446</v>
-      </c>
-      <c r="G952">
-        <v>0.15</v>
+        <v>0.35416666666666669</v>
       </c>
       <c r="I952">
-        <v>6.2</v>
+        <v>1111</v>
       </c>
       <c r="J952">
-        <v>0</v>
+        <v>1111</v>
       </c>
       <c r="L952">
-        <v>9</v>
-      </c>
-      <c r="N952">
-        <v>0.2</v>
+        <v>611</v>
       </c>
       <c r="O952">
-        <v>0.35</v>
+        <v>56</v>
       </c>
       <c r="P952">
-        <v>15.9</v>
+        <v>1778</v>
       </c>
       <c r="Q952" t="s">
-        <v>78</v>
+        <v>283</v>
       </c>
     </row>
     <row r="953" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A953" t="s">
-        <v>348</v>
+        <v>453</v>
       </c>
       <c r="B953">
-        <v>-34.860666999999999</v>
+        <v>-34.718809999999998</v>
       </c>
       <c r="C953">
-        <v>138.490938</v>
+        <v>135.85857999999999</v>
       </c>
       <c r="D953" s="2">
         <v>46196</v>
       </c>
       <c r="E953" s="20">
-        <v>4.8611111111111112E-2</v>
-      </c>
-      <c r="G953">
-        <v>0.1</v>
-      </c>
-      <c r="H953">
-        <v>0.1</v>
+        <v>46197.375</v>
       </c>
       <c r="I953">
-        <v>54.7</v>
+        <v>1167</v>
       </c>
       <c r="J953">
-        <v>0</v>
-      </c>
-      <c r="L953">
-        <v>2.2999999999999998</v>
+        <v>1111</v>
       </c>
       <c r="O953">
-        <v>0.3</v>
+        <v>56</v>
       </c>
       <c r="P953">
-        <v>57.5</v>
+        <v>1223</v>
       </c>
       <c r="Q953" t="s">
-        <v>78</v>
+        <v>283</v>
       </c>
     </row>
     <row r="954" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A954" t="s">
-        <v>422</v>
+        <v>79</v>
       </c>
       <c r="B954">
-        <v>-34.978150999999997</v>
+        <v>-34.804662999999998</v>
       </c>
       <c r="C954">
-        <v>138.50750400000001</v>
+        <v>138.540223</v>
       </c>
       <c r="D954" s="2">
         <v>46196</v>
       </c>
       <c r="E954" s="20">
-        <v>0.59375</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="I954">
-        <v>111</v>
+        <v>2.7749999999999999</v>
       </c>
       <c r="J954">
         <v>0</v>
       </c>
       <c r="L954">
-        <v>222</v>
-      </c>
-      <c r="N954">
-        <v>222</v>
+        <v>6.2249999999999996</v>
       </c>
       <c r="O954">
-        <v>667</v>
+        <v>1.65</v>
       </c>
       <c r="P954">
-        <v>1222</v>
+        <v>10.65</v>
       </c>
       <c r="Q954" t="s">
-        <v>447</v>
+        <v>78</v>
       </c>
     </row>
     <row r="955" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A955" t="s">
-        <v>421</v>
+        <v>267</v>
       </c>
       <c r="B955">
-        <v>-35.500024000000003</v>
+        <v>-34.824044999999998</v>
       </c>
       <c r="C955">
-        <v>138.24287699999999</v>
+        <v>138.48377600000001</v>
       </c>
       <c r="D955" s="2">
         <v>46196</v>
       </c>
       <c r="E955" s="20">
-        <v>0.38541666666666669</v>
-      </c>
-      <c r="F955">
-        <v>0</v>
+        <v>0.55694444444444446</v>
       </c>
       <c r="G955">
-        <v>0</v>
-      </c>
-      <c r="H955">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="I955">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="J955">
         <v>0</v>
       </c>
-      <c r="K955">
-        <v>0</v>
-      </c>
       <c r="L955">
-        <v>0</v>
-      </c>
-      <c r="M955">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N955">
-        <v>111</v>
+        <v>0.2</v>
       </c>
       <c r="O955">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="P955">
-        <v>111</v>
+        <v>15.9</v>
       </c>
       <c r="Q955" t="s">
-        <v>251</v>
+        <v>78</v>
       </c>
     </row>
     <row r="956" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A956" t="s">
-        <v>418</v>
+        <v>348</v>
       </c>
       <c r="B956">
-        <v>-35.591330800000001</v>
+        <v>-34.860666999999999</v>
       </c>
       <c r="C956">
-        <v>137.5061887</v>
+        <v>138.490938</v>
       </c>
       <c r="D956" s="2">
         <v>46196</v>
       </c>
       <c r="E956" s="20">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="F956">
-        <v>0</v>
+        <v>4.8611111111111112E-2</v>
       </c>
       <c r="G956">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="H956">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="I956">
-        <v>0</v>
+        <v>54.7</v>
       </c>
       <c r="J956">
         <v>0</v>
       </c>
-      <c r="K956">
-        <v>0</v>
-      </c>
       <c r="L956">
-        <v>0</v>
-      </c>
-      <c r="M956">
-        <v>0</v>
-      </c>
-      <c r="N956">
-        <v>0</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="O956">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="P956">
-        <v>0</v>
+        <v>57.5</v>
       </c>
       <c r="Q956" t="s">
-        <v>458</v>
+        <v>78</v>
       </c>
     </row>
     <row r="957" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A957" t="s">
-        <v>459</v>
+        <v>422</v>
       </c>
       <c r="B957">
-        <v>-35.595789000000003</v>
+        <v>-34.978150999999997</v>
       </c>
       <c r="C957">
-        <v>137.51194899999999</v>
+        <v>138.50750400000001</v>
       </c>
       <c r="D957" s="2">
         <v>46196</v>
       </c>
       <c r="E957" s="20">
+        <v>0.59375</v>
+      </c>
+      <c r="I957">
+        <v>111</v>
+      </c>
+      <c r="J957">
+        <v>0</v>
+      </c>
+      <c r="L957">
+        <v>222</v>
+      </c>
+      <c r="N957">
+        <v>222</v>
+      </c>
+      <c r="O957">
+        <v>667</v>
+      </c>
+      <c r="P957">
+        <v>1222</v>
+      </c>
+      <c r="Q957" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="958" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A958" t="s">
+        <v>421</v>
+      </c>
+      <c r="B958">
+        <v>-35.500024000000003</v>
+      </c>
+      <c r="C958">
+        <v>138.24287699999999</v>
+      </c>
+      <c r="D958" s="2">
+        <v>46196</v>
+      </c>
+      <c r="E958" s="20">
+        <v>0.38541666666666669</v>
+      </c>
+      <c r="F958">
+        <v>0</v>
+      </c>
+      <c r="G958">
+        <v>0</v>
+      </c>
+      <c r="H958">
+        <v>0</v>
+      </c>
+      <c r="I958">
+        <v>0</v>
+      </c>
+      <c r="J958">
+        <v>0</v>
+      </c>
+      <c r="K958">
+        <v>0</v>
+      </c>
+      <c r="L958">
+        <v>0</v>
+      </c>
+      <c r="M958">
+        <v>0</v>
+      </c>
+      <c r="N958">
+        <v>111</v>
+      </c>
+      <c r="O958">
+        <v>0</v>
+      </c>
+      <c r="P958">
+        <v>111</v>
+      </c>
+      <c r="Q958" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="959" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A959" t="s">
+        <v>418</v>
+      </c>
+      <c r="B959">
+        <v>-35.591330800000001</v>
+      </c>
+      <c r="C959">
+        <v>137.5061887</v>
+      </c>
+      <c r="D959" s="2">
+        <v>46196</v>
+      </c>
+      <c r="E959" s="20">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="F959">
+        <v>0</v>
+      </c>
+      <c r="G959">
+        <v>0</v>
+      </c>
+      <c r="H959">
+        <v>0</v>
+      </c>
+      <c r="I959">
+        <v>0</v>
+      </c>
+      <c r="J959">
+        <v>0</v>
+      </c>
+      <c r="K959">
+        <v>0</v>
+      </c>
+      <c r="L959">
+        <v>0</v>
+      </c>
+      <c r="M959">
+        <v>0</v>
+      </c>
+      <c r="N959">
+        <v>0</v>
+      </c>
+      <c r="O959">
+        <v>0</v>
+      </c>
+      <c r="P959">
+        <v>0</v>
+      </c>
+      <c r="Q959" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="960" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A960" t="s">
+        <v>457</v>
+      </c>
+      <c r="B960">
+        <v>-35.595789000000003</v>
+      </c>
+      <c r="C960">
+        <v>137.51194899999999</v>
+      </c>
+      <c r="D960" s="2">
+        <v>46196</v>
+      </c>
+      <c r="E960" s="20">
         <v>0.47916666666666669</v>
       </c>
-      <c r="F957">
-        <v>0</v>
-      </c>
-      <c r="G957">
-        <v>0</v>
-      </c>
-      <c r="H957">
-        <v>0</v>
-      </c>
-      <c r="I957">
-        <v>0</v>
-      </c>
-      <c r="J957">
-        <v>0</v>
-      </c>
-      <c r="K957">
-        <v>0</v>
-      </c>
-      <c r="L957">
-        <v>0</v>
-      </c>
-      <c r="M957">
+      <c r="F960">
+        <v>0</v>
+      </c>
+      <c r="G960">
+        <v>0</v>
+      </c>
+      <c r="H960">
+        <v>0</v>
+      </c>
+      <c r="I960">
+        <v>0</v>
+      </c>
+      <c r="J960">
+        <v>0</v>
+      </c>
+      <c r="K960">
+        <v>0</v>
+      </c>
+      <c r="L960">
+        <v>0</v>
+      </c>
+      <c r="M960">
         <v>222</v>
       </c>
-      <c r="N957">
-        <v>0</v>
-      </c>
-      <c r="O957">
-        <v>0</v>
-      </c>
-      <c r="P957">
+      <c r="N960">
+        <v>0</v>
+      </c>
+      <c r="O960">
+        <v>0</v>
+      </c>
+      <c r="P960">
         <v>222</v>
       </c>
-      <c r="Q957" t="s">
-        <v>456</v>
+      <c r="Q960" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="961" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A961" t="s">
+        <v>59</v>
+      </c>
+      <c r="B961">
+        <v>-35.084850000000003</v>
+      </c>
+      <c r="C961">
+        <v>137.74889999999999</v>
+      </c>
+      <c r="D961" s="2">
+        <v>46196</v>
+      </c>
+      <c r="E961" s="20">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="G961">
+        <v>0</v>
+      </c>
+      <c r="H961">
+        <v>0</v>
+      </c>
+      <c r="I961">
+        <v>0</v>
+      </c>
+      <c r="J961">
+        <v>0</v>
+      </c>
+      <c r="L961">
+        <v>111</v>
+      </c>
+      <c r="M961">
+        <v>0</v>
+      </c>
+      <c r="N961">
+        <v>333</v>
+      </c>
+      <c r="O961">
+        <v>0</v>
+      </c>
+      <c r="P961">
+        <v>444</v>
+      </c>
+      <c r="Q961" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="962" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A962" t="s">
+        <v>450</v>
+      </c>
+      <c r="B962">
+        <v>-35.595986000000003</v>
+      </c>
+      <c r="C962">
+        <v>138.104072</v>
+      </c>
+      <c r="D962" s="2">
+        <v>46197</v>
+      </c>
+      <c r="E962" s="20">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="F962">
+        <v>0</v>
+      </c>
+      <c r="G962">
+        <v>0</v>
+      </c>
+      <c r="H962">
+        <v>0</v>
+      </c>
+      <c r="I962">
+        <v>0</v>
+      </c>
+      <c r="J962">
+        <v>0</v>
+      </c>
+      <c r="K962">
+        <v>0</v>
+      </c>
+      <c r="L962">
+        <v>0</v>
+      </c>
+      <c r="M962">
+        <v>0</v>
+      </c>
+      <c r="N962">
+        <v>833</v>
+      </c>
+      <c r="O962">
+        <v>56</v>
+      </c>
+      <c r="P962">
+        <v>889</v>
+      </c>
+      <c r="Q962" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="963" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A963" t="s">
+        <v>426</v>
+      </c>
+      <c r="B963">
+        <v>-35.410254000000002</v>
+      </c>
+      <c r="C963">
+        <v>138.32751999999999</v>
+      </c>
+      <c r="D963" s="2">
+        <v>46197</v>
+      </c>
+      <c r="E963" s="20">
+        <v>0.3125</v>
+      </c>
+      <c r="F963">
+        <v>0</v>
+      </c>
+      <c r="G963">
+        <v>167</v>
+      </c>
+      <c r="H963">
+        <v>56</v>
+      </c>
+      <c r="I963">
+        <v>500</v>
+      </c>
+      <c r="J963">
+        <v>0</v>
+      </c>
+      <c r="K963">
+        <v>0</v>
+      </c>
+      <c r="L963">
+        <v>56</v>
+      </c>
+      <c r="M963">
+        <v>0</v>
+      </c>
+      <c r="N963">
+        <v>389</v>
+      </c>
+      <c r="O963">
+        <v>111</v>
+      </c>
+      <c r="P963">
+        <v>1279</v>
+      </c>
+      <c r="Q963" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="964" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A964" t="s">
+        <v>94</v>
+      </c>
+      <c r="B964">
+        <v>-35.58858</v>
+      </c>
+      <c r="C964">
+        <v>138.60474600000001</v>
+      </c>
+      <c r="D964" s="2">
+        <v>46201</v>
+      </c>
+      <c r="J964">
+        <v>0</v>
+      </c>
+      <c r="L964">
+        <v>500</v>
+      </c>
+      <c r="N964">
+        <v>56</v>
+      </c>
+      <c r="O964">
+        <v>278</v>
+      </c>
+      <c r="P964">
+        <v>834</v>
+      </c>
+      <c r="Q964" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="965" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A965" t="s">
+        <v>89</v>
+      </c>
+      <c r="B965">
+        <v>-35.6048446</v>
+      </c>
+      <c r="C965">
+        <v>138.59278499999999</v>
+      </c>
+      <c r="D965" s="2">
+        <v>46201</v>
+      </c>
+      <c r="G965">
+        <v>56</v>
+      </c>
+      <c r="H965">
+        <v>56</v>
+      </c>
+      <c r="J965">
+        <v>0</v>
+      </c>
+      <c r="N965">
+        <v>278</v>
+      </c>
+      <c r="O965">
+        <v>167</v>
+      </c>
+      <c r="P965">
+        <v>557</v>
+      </c>
+      <c r="Q965" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="966" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A966" t="s">
+        <v>436</v>
+      </c>
+      <c r="B966">
+        <v>-35.521467000000001</v>
+      </c>
+      <c r="C966">
+        <v>138.18532999999999</v>
+      </c>
+      <c r="D966" s="2">
+        <v>46201</v>
+      </c>
+      <c r="E966" s="20">
+        <v>0.52430555555555558</v>
+      </c>
+      <c r="F966">
+        <v>0</v>
+      </c>
+      <c r="G966">
+        <v>0</v>
+      </c>
+      <c r="H966">
+        <v>0</v>
+      </c>
+      <c r="I966">
+        <v>0</v>
+      </c>
+      <c r="J966">
+        <v>0</v>
+      </c>
+      <c r="K966">
+        <v>0</v>
+      </c>
+      <c r="L966">
+        <v>56</v>
+      </c>
+      <c r="M966">
+        <v>0</v>
+      </c>
+      <c r="N966">
+        <v>1167</v>
+      </c>
+      <c r="O966">
+        <v>0</v>
+      </c>
+      <c r="P966">
+        <v>1223</v>
+      </c>
+      <c r="Q966" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="967" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A967" t="s">
+        <v>421</v>
+      </c>
+      <c r="B967">
+        <v>-35.500024000000003</v>
+      </c>
+      <c r="C967">
+        <v>138.24287699999999</v>
+      </c>
+      <c r="D967" s="2">
+        <v>46201</v>
+      </c>
+      <c r="E967" s="20">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="F967">
+        <v>0</v>
+      </c>
+      <c r="G967">
+        <v>0</v>
+      </c>
+      <c r="H967">
+        <v>0</v>
+      </c>
+      <c r="I967">
+        <v>0</v>
+      </c>
+      <c r="J967">
+        <v>0</v>
+      </c>
+      <c r="K967">
+        <v>0</v>
+      </c>
+      <c r="L967">
+        <v>0</v>
+      </c>
+      <c r="M967">
+        <v>0</v>
+      </c>
+      <c r="N967">
+        <v>56</v>
+      </c>
+      <c r="O967">
+        <v>56</v>
+      </c>
+      <c r="P967">
+        <v>112</v>
+      </c>
+      <c r="Q967" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="968" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A968" t="s">
+        <v>459</v>
+      </c>
+      <c r="B968" s="25">
+        <v>-35.788674999999998</v>
+      </c>
+      <c r="C968" s="25">
+        <v>138.070415</v>
+      </c>
+      <c r="D968" s="2">
+        <v>46202</v>
+      </c>
+      <c r="E968" s="20">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="F968">
+        <v>158333</v>
+      </c>
+      <c r="G968">
+        <v>0</v>
+      </c>
+      <c r="H968">
+        <v>0</v>
+      </c>
+      <c r="I968">
+        <v>7333</v>
+      </c>
+      <c r="J968">
+        <v>0</v>
+      </c>
+      <c r="K968">
+        <v>0</v>
+      </c>
+      <c r="L968">
+        <v>17500</v>
+      </c>
+      <c r="M968">
+        <v>4667</v>
+      </c>
+      <c r="N968">
+        <v>0</v>
+      </c>
+      <c r="O968">
+        <v>0</v>
+      </c>
+      <c r="P968">
+        <v>187833</v>
+      </c>
+      <c r="Q968" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="969" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A969" t="s">
+        <v>460</v>
+      </c>
+      <c r="B969">
+        <v>-35.787862699999998</v>
+      </c>
+      <c r="C969">
+        <v>138.07130670000001</v>
+      </c>
+      <c r="D969" s="2">
+        <v>46202</v>
+      </c>
+      <c r="E969" s="20">
+        <v>14.3</v>
+      </c>
+      <c r="F969">
+        <v>2667</v>
+      </c>
+      <c r="G969">
+        <v>0</v>
+      </c>
+      <c r="H969">
+        <v>0</v>
+      </c>
+      <c r="I969">
+        <v>111</v>
+      </c>
+      <c r="J969">
+        <v>0</v>
+      </c>
+      <c r="K969">
+        <v>0</v>
+      </c>
+      <c r="L969">
+        <v>167</v>
+      </c>
+      <c r="M969">
+        <v>0</v>
+      </c>
+      <c r="N969">
+        <v>0</v>
+      </c>
+      <c r="P969">
+        <v>2945</v>
+      </c>
+      <c r="Q969" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="970" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A970" t="s">
+        <v>461</v>
+      </c>
+      <c r="B970">
+        <v>-35.720106999999999</v>
+      </c>
+      <c r="C970">
+        <v>137.94337100000001</v>
+      </c>
+      <c r="D970" s="2">
+        <v>46202</v>
+      </c>
+      <c r="E970" s="20">
+        <v>1.3</v>
+      </c>
+      <c r="F970">
+        <v>1167</v>
+      </c>
+      <c r="G970">
+        <v>0</v>
+      </c>
+      <c r="H970">
+        <v>0</v>
+      </c>
+      <c r="I970">
+        <v>1000</v>
+      </c>
+      <c r="J970">
+        <v>0</v>
+      </c>
+      <c r="K970">
+        <v>0</v>
+      </c>
+      <c r="L970">
+        <v>167</v>
+      </c>
+      <c r="M970">
+        <v>0</v>
+      </c>
+      <c r="N970">
+        <v>0</v>
+      </c>
+      <c r="O970">
+        <v>0</v>
+      </c>
+      <c r="P970">
+        <v>2334</v>
+      </c>
+      <c r="Q970" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="971" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A971" t="s">
+        <v>311</v>
+      </c>
+      <c r="B971">
+        <v>-35.445059999999998</v>
+      </c>
+      <c r="C971">
+        <v>138.30758399999999</v>
+      </c>
+      <c r="D971" s="2">
+        <v>46202</v>
+      </c>
+      <c r="E971" s="20">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="F971">
+        <v>0</v>
+      </c>
+      <c r="G971">
+        <v>0</v>
+      </c>
+      <c r="H971">
+        <v>0</v>
+      </c>
+      <c r="I971">
+        <v>278</v>
+      </c>
+      <c r="J971">
+        <v>0</v>
+      </c>
+      <c r="K971">
+        <v>0</v>
+      </c>
+      <c r="L971">
+        <v>222</v>
+      </c>
+      <c r="M971">
+        <v>0</v>
+      </c>
+      <c r="N971">
+        <v>333</v>
+      </c>
+      <c r="O971">
+        <v>56</v>
+      </c>
+      <c r="P971">
+        <v>889</v>
+      </c>
+      <c r="Q971" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="972" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A972" t="s">
+        <v>458</v>
+      </c>
+      <c r="B972">
+        <v>-35.557200000000002</v>
+      </c>
+      <c r="C972">
+        <v>138.886</v>
+      </c>
+      <c r="D972" s="2">
+        <v>46203</v>
+      </c>
+      <c r="J972">
+        <v>0</v>
+      </c>
+      <c r="N972">
+        <v>222</v>
+      </c>
+      <c r="O972">
+        <v>389</v>
+      </c>
+      <c r="P972">
+        <v>611</v>
+      </c>
+      <c r="Q972" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="973" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A973" t="s">
+        <v>301</v>
+      </c>
+      <c r="B973">
+        <v>-34.899749999999997</v>
+      </c>
+      <c r="C973">
+        <v>137.45174</v>
+      </c>
+      <c r="D973" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E973" s="20">
+        <v>0.3125</v>
+      </c>
+      <c r="I973">
+        <v>167</v>
+      </c>
+      <c r="J973">
+        <v>111</v>
+      </c>
+      <c r="L973">
+        <v>278</v>
+      </c>
+      <c r="Q973" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="974" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A974" t="s">
+        <v>59</v>
+      </c>
+      <c r="B974">
+        <v>-35.084850000000003</v>
+      </c>
+      <c r="C974">
+        <v>137.74889999999999</v>
+      </c>
+      <c r="D974" s="2">
+        <v>46204</v>
+      </c>
+      <c r="E974" s="24">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="G974">
+        <v>28</v>
+      </c>
+      <c r="H974">
+        <v>139</v>
+      </c>
+      <c r="I974">
+        <v>278</v>
+      </c>
+      <c r="J974">
+        <v>0</v>
+      </c>
+      <c r="L974">
+        <v>139</v>
+      </c>
+      <c r="M974">
+        <v>0</v>
+      </c>
+      <c r="N974">
+        <v>611</v>
+      </c>
+      <c r="O974">
+        <v>0</v>
+      </c>
+      <c r="P974">
+        <v>1195</v>
+      </c>
+      <c r="Q974" t="s">
+        <v>149</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q957">
-    <sortCondition ref="D2:D957"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q974">
+    <sortCondition ref="D2:D974"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="S229">

--- a/MASTER spreadsheet of community summaries.xlsx
+++ b/MASTER spreadsheet of community summaries.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\peri\Dropbox\Delta\Projects\Laboratory\Algal blooms, bacterial counts  for community\For Luke's HAB data display\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5FF948E-C116-4285-B660-2509C5BFFD75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{537F61FA-3B1A-4AA7-906F-CB8996409249}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{9286397E-2757-492B-865A-39B2D6A15FF6}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1965" uniqueCount="462">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1992" uniqueCount="466">
   <si>
     <t>Date</t>
   </si>
@@ -1442,6 +1442,18 @@
   </si>
   <si>
     <t>Penneshaw 29 June</t>
+  </si>
+  <si>
+    <t>Hardwicke Bay Boat Ramp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tod River beach </t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Kingscote</t>
   </si>
 </sst>
 </file>
@@ -1530,7 +1542,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1572,7 +1584,6 @@
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="18" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1924,7 +1935,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F307807-E5C9-4450-88E0-159CBB3E9A67}">
-  <dimension ref="A1:T974"/>
+  <dimension ref="A1:T987"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="39.33203125" customWidth="1"/>
@@ -35509,104 +35520,95 @@
     </row>
     <row r="919" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A919" t="s">
-        <v>422</v>
+        <v>462</v>
       </c>
       <c r="B919">
-        <v>-34.979999999999997</v>
+        <v>-34.899749999999997</v>
       </c>
       <c r="C919">
-        <v>138.50800000000001</v>
+        <v>137.45174</v>
       </c>
       <c r="D919" s="2">
-        <v>46182</v>
+        <v>46180</v>
+      </c>
+      <c r="E919" s="20">
+        <v>0.5625</v>
       </c>
       <c r="I919">
-        <v>333</v>
+        <v>111</v>
       </c>
       <c r="J919">
         <v>0</v>
       </c>
-      <c r="L919">
-        <v>111</v>
-      </c>
-      <c r="N919">
-        <v>1556</v>
-      </c>
-      <c r="O919">
-        <v>1667</v>
-      </c>
-      <c r="P919">
-        <v>3667</v>
-      </c>
       <c r="Q919" t="s">
-        <v>447</v>
+        <v>265</v>
       </c>
     </row>
     <row r="920" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A920" t="s">
-        <v>289</v>
+        <v>422</v>
       </c>
       <c r="B920">
-        <v>-34.628509999999999</v>
+        <v>-34.979999999999997</v>
       </c>
       <c r="C920">
-        <v>135.86675</v>
+        <v>138.50800000000001</v>
       </c>
       <c r="D920" s="2">
         <v>46182</v>
       </c>
-      <c r="E920" s="20">
-        <v>0.54166666666666663</v>
-      </c>
       <c r="I920">
-        <v>21</v>
+        <v>333</v>
       </c>
       <c r="J920">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="L920">
-        <v>8</v>
+        <v>111</v>
+      </c>
+      <c r="N920">
+        <v>1556</v>
       </c>
       <c r="O920">
-        <v>1</v>
+        <v>1667</v>
       </c>
       <c r="P920">
-        <v>30</v>
+        <v>3667</v>
       </c>
       <c r="Q920" t="s">
-        <v>283</v>
+        <v>447</v>
       </c>
     </row>
     <row r="921" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A921" t="s">
-        <v>434</v>
+        <v>289</v>
       </c>
       <c r="B921">
-        <v>-34.540930000000003</v>
+        <v>-34.628509999999999</v>
       </c>
       <c r="C921">
-        <v>135.93384</v>
+        <v>135.86675</v>
       </c>
       <c r="D921" s="2">
-        <v>46183</v>
+        <v>46182</v>
       </c>
       <c r="E921" s="20">
         <v>0.54166666666666663</v>
       </c>
       <c r="I921">
-        <v>106</v>
+        <v>21</v>
       </c>
       <c r="J921">
-        <v>81</v>
+        <v>19</v>
       </c>
       <c r="L921">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="O921">
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="P921">
-        <v>178</v>
+        <v>30</v>
       </c>
       <c r="Q921" t="s">
         <v>283</v>
@@ -35614,529 +35616,532 @@
     </row>
     <row r="922" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A922" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="B922">
-        <v>-35.410254000000002</v>
+        <v>-34.540930000000003</v>
       </c>
       <c r="C922">
-        <v>138.32751999999999</v>
+        <v>135.93384</v>
       </c>
       <c r="D922" s="2">
         <v>46183</v>
       </c>
       <c r="E922" s="20">
-        <v>0.65277777777777779</v>
-      </c>
-      <c r="F922">
-        <v>0</v>
-      </c>
-      <c r="G922">
-        <v>0</v>
-      </c>
-      <c r="H922">
-        <v>333</v>
+        <v>0.54166666666666663</v>
       </c>
       <c r="I922">
-        <v>222</v>
+        <v>106</v>
       </c>
       <c r="J922">
-        <v>0</v>
-      </c>
-      <c r="K922">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="L922">
-        <v>111</v>
-      </c>
-      <c r="M922">
-        <v>0</v>
-      </c>
-      <c r="N922">
-        <v>500</v>
+        <v>28</v>
       </c>
       <c r="O922">
-        <v>222</v>
+        <v>44</v>
       </c>
       <c r="P922">
-        <v>1388</v>
+        <v>178</v>
       </c>
       <c r="Q922" t="s">
-        <v>251</v>
+        <v>283</v>
       </c>
     </row>
     <row r="923" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A923" t="s">
-        <v>412</v>
+        <v>426</v>
       </c>
       <c r="B923">
-        <v>-33.043101999999998</v>
+        <v>-35.410254000000002</v>
       </c>
       <c r="C923">
-        <v>137.59395699999999</v>
+        <v>138.32751999999999</v>
       </c>
       <c r="D923" s="2">
         <v>46183</v>
       </c>
       <c r="E923" s="20">
-        <v>0.69444444444444442</v>
+        <v>0.65277777777777779</v>
+      </c>
+      <c r="F923">
+        <v>0</v>
+      </c>
+      <c r="G923">
+        <v>0</v>
+      </c>
+      <c r="H923">
+        <v>333</v>
+      </c>
+      <c r="I923">
+        <v>222</v>
       </c>
       <c r="J923">
         <v>0</v>
       </c>
+      <c r="K923">
+        <v>0</v>
+      </c>
       <c r="L923">
-        <v>37</v>
+        <v>111</v>
+      </c>
+      <c r="M923">
+        <v>0</v>
+      </c>
+      <c r="N923">
+        <v>500</v>
       </c>
       <c r="O923">
-        <v>37</v>
+        <v>222</v>
       </c>
       <c r="P923">
-        <v>74</v>
+        <v>1388</v>
       </c>
       <c r="Q923" t="s">
-        <v>346</v>
+        <v>251</v>
       </c>
     </row>
     <row r="924" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A924" t="s">
-        <v>59</v>
+        <v>412</v>
       </c>
       <c r="B924">
-        <v>-35.084850000000003</v>
+        <v>-33.043101999999998</v>
       </c>
       <c r="C924">
-        <v>137.74889999999999</v>
+        <v>137.59395699999999</v>
       </c>
       <c r="D924" s="2">
-        <v>46184</v>
+        <v>46183</v>
       </c>
       <c r="E924" s="20">
-        <v>0.58333333333333337</v>
-      </c>
-      <c r="H924">
-        <v>222</v>
-      </c>
-      <c r="I924">
-        <v>388</v>
+        <v>0.69444444444444442</v>
       </c>
       <c r="J924">
         <v>0</v>
       </c>
       <c r="L924">
-        <v>444</v>
-      </c>
-      <c r="M924">
-        <v>0</v>
-      </c>
-      <c r="N924">
-        <v>1166</v>
+        <v>37</v>
       </c>
       <c r="O924">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="P924">
-        <v>2220</v>
+        <v>74</v>
       </c>
       <c r="Q924" t="s">
-        <v>149</v>
+        <v>346</v>
       </c>
     </row>
     <row r="925" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A925" t="s">
-        <v>92</v>
+        <v>59</v>
       </c>
       <c r="B925">
-        <v>-35.632150000000003</v>
+        <v>-35.084850000000003</v>
       </c>
       <c r="C925">
-        <v>138.48339999999999</v>
+        <v>137.74889999999999</v>
       </c>
       <c r="D925" s="2">
-        <v>46186</v>
+        <v>46184</v>
       </c>
       <c r="E925" s="20">
-        <v>0.46875</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="H925">
+        <v>222</v>
       </c>
       <c r="I925">
-        <v>0.35</v>
+        <v>388</v>
       </c>
       <c r="J925">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="L925">
-        <v>14.25</v>
+        <v>444</v>
       </c>
       <c r="M925">
         <v>0</v>
       </c>
       <c r="N925">
-        <v>0.15</v>
+        <v>1166</v>
       </c>
       <c r="O925">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="P925">
-        <v>14.85</v>
+        <v>2220</v>
       </c>
       <c r="Q925" t="s">
-        <v>78</v>
+        <v>149</v>
       </c>
     </row>
     <row r="926" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A926" t="s">
-        <v>289</v>
+        <v>92</v>
       </c>
       <c r="B926">
-        <v>-34.628509999999999</v>
+        <v>-35.632150000000003</v>
       </c>
       <c r="C926">
-        <v>135.86675</v>
+        <v>138.48339999999999</v>
       </c>
       <c r="D926" s="2">
-        <v>46187</v>
+        <v>46186</v>
       </c>
       <c r="E926" s="20">
-        <v>0.69791666666666663</v>
+        <v>0.46875</v>
       </c>
       <c r="I926">
-        <v>182</v>
+        <v>0.35</v>
       </c>
       <c r="J926">
-        <v>176</v>
+        <v>0.05</v>
       </c>
       <c r="L926">
-        <v>17</v>
+        <v>14.25</v>
+      </c>
+      <c r="M926">
+        <v>0</v>
+      </c>
+      <c r="N926">
+        <v>0.15</v>
       </c>
       <c r="O926">
-        <v>2</v>
+        <v>0.1</v>
       </c>
       <c r="P926">
-        <v>201</v>
+        <v>14.85</v>
       </c>
       <c r="Q926" t="s">
-        <v>283</v>
+        <v>78</v>
       </c>
     </row>
     <row r="927" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A927" t="s">
-        <v>311</v>
+        <v>289</v>
       </c>
       <c r="B927">
-        <v>-35.445059999999998</v>
+        <v>-34.628509999999999</v>
       </c>
       <c r="C927">
-        <v>138.30758399999999</v>
+        <v>135.86675</v>
       </c>
       <c r="D927" s="2">
-        <v>46188</v>
+        <v>46187</v>
       </c>
       <c r="E927" s="20">
-        <v>0.375</v>
-      </c>
-      <c r="F927">
-        <v>0</v>
-      </c>
-      <c r="G927">
-        <v>0</v>
-      </c>
-      <c r="H927">
-        <v>0</v>
+        <v>0.69791666666666663</v>
       </c>
       <c r="I927">
-        <v>56</v>
+        <v>182</v>
       </c>
       <c r="J927">
-        <v>0</v>
-      </c>
-      <c r="K927">
-        <v>0</v>
+        <v>176</v>
       </c>
       <c r="L927">
-        <v>56</v>
-      </c>
-      <c r="M927">
-        <v>0</v>
-      </c>
-      <c r="N927">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="O927">
-        <v>111</v>
+        <v>2</v>
       </c>
       <c r="P927">
-        <v>223</v>
+        <v>201</v>
       </c>
       <c r="Q927" t="s">
-        <v>401</v>
+        <v>283</v>
       </c>
     </row>
     <row r="928" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A928" t="s">
-        <v>289</v>
+        <v>311</v>
       </c>
       <c r="B928">
-        <v>-34.628509999999999</v>
+        <v>-35.445059999999998</v>
       </c>
       <c r="C928">
-        <v>135.86675</v>
+        <v>138.30758399999999</v>
       </c>
       <c r="D928" s="2">
-        <v>46189</v>
+        <v>46188</v>
       </c>
       <c r="E928" s="20">
-        <v>0.70833333333333337</v>
+        <v>0.375</v>
+      </c>
+      <c r="F928">
+        <v>0</v>
+      </c>
+      <c r="G928">
+        <v>0</v>
+      </c>
+      <c r="H928">
+        <v>0</v>
       </c>
       <c r="I928">
-        <v>131</v>
+        <v>56</v>
       </c>
       <c r="J928">
-        <v>121</v>
+        <v>0</v>
+      </c>
+      <c r="K928">
+        <v>0</v>
       </c>
       <c r="L928">
-        <v>2</v>
+        <v>56</v>
+      </c>
+      <c r="M928">
+        <v>0</v>
+      </c>
+      <c r="N928">
+        <v>0</v>
       </c>
       <c r="O928">
-        <v>2</v>
+        <v>111</v>
       </c>
       <c r="P928">
-        <v>135</v>
+        <v>223</v>
       </c>
       <c r="Q928" t="s">
-        <v>283</v>
+        <v>401</v>
       </c>
     </row>
     <row r="929" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A929" t="s">
-        <v>59</v>
+        <v>289</v>
       </c>
       <c r="B929">
-        <v>-35.084850000000003</v>
+        <v>-34.628509999999999</v>
       </c>
       <c r="C929">
-        <v>137.74889999999999</v>
+        <v>135.86675</v>
       </c>
       <c r="D929" s="2">
-        <v>46190</v>
+        <v>46189</v>
       </c>
       <c r="E929" s="20">
-        <v>0.58333333333333337</v>
-      </c>
-      <c r="G929">
-        <v>333</v>
-      </c>
-      <c r="H929">
-        <v>389</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="I929">
-        <v>277</v>
+        <v>131</v>
       </c>
       <c r="J929">
-        <v>0</v>
-      </c>
-      <c r="M929">
-        <v>0</v>
-      </c>
-      <c r="N929">
-        <v>556</v>
+        <v>121</v>
+      </c>
+      <c r="L929">
+        <v>2</v>
       </c>
       <c r="O929">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P929">
-        <v>1555</v>
+        <v>135</v>
       </c>
       <c r="Q929" t="s">
-        <v>149</v>
+        <v>283</v>
       </c>
     </row>
     <row r="930" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A930" t="s">
-        <v>289</v>
+        <v>59</v>
       </c>
       <c r="B930">
-        <v>-34.628509999999999</v>
+        <v>-35.084850000000003</v>
       </c>
       <c r="C930">
-        <v>135.86675</v>
+        <v>137.74889999999999</v>
       </c>
       <c r="D930" s="2">
         <v>46190</v>
       </c>
       <c r="E930" s="20">
-        <v>0.56944444444444442</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="G930">
+        <v>333</v>
+      </c>
+      <c r="H930">
+        <v>389</v>
       </c>
       <c r="I930">
-        <v>611</v>
+        <v>277</v>
       </c>
       <c r="J930">
-        <v>611</v>
-      </c>
-      <c r="L930">
-        <v>222</v>
+        <v>0</v>
+      </c>
+      <c r="M930">
+        <v>0</v>
+      </c>
+      <c r="N930">
+        <v>556</v>
       </c>
       <c r="O930">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="P930">
-        <v>889</v>
+        <v>1555</v>
       </c>
       <c r="Q930" t="s">
-        <v>283</v>
+        <v>149</v>
       </c>
     </row>
     <row r="931" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A931" t="s">
-        <v>454</v>
+        <v>289</v>
       </c>
       <c r="B931">
-        <v>-34.978150999999997</v>
+        <v>-34.628509999999999</v>
       </c>
       <c r="C931">
-        <v>138.50750400000001</v>
+        <v>135.86675</v>
       </c>
       <c r="D931" s="2">
         <v>46190</v>
       </c>
       <c r="E931" s="20">
-        <v>0.59236111111111112</v>
+        <v>0.56944444444444442</v>
       </c>
       <c r="I931">
-        <v>167</v>
+        <v>611</v>
       </c>
       <c r="J931">
-        <v>0</v>
+        <v>611</v>
       </c>
       <c r="L931">
-        <v>333</v>
-      </c>
-      <c r="N931">
-        <v>667</v>
+        <v>222</v>
       </c>
       <c r="O931">
-        <v>389</v>
+        <v>56</v>
       </c>
       <c r="P931">
-        <v>1556</v>
+        <v>889</v>
       </c>
       <c r="Q931" t="s">
-        <v>447</v>
+        <v>283</v>
       </c>
     </row>
     <row r="932" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A932" t="s">
-        <v>426</v>
+        <v>454</v>
       </c>
       <c r="B932">
-        <v>-35.410254000000002</v>
+        <v>-34.978150999999997</v>
       </c>
       <c r="C932">
-        <v>138.32751999999999</v>
+        <v>138.50750400000001</v>
       </c>
       <c r="D932" s="2">
         <v>46190</v>
       </c>
       <c r="E932" s="20">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="F932">
-        <v>0</v>
-      </c>
-      <c r="G932">
-        <v>0</v>
-      </c>
-      <c r="H932">
-        <v>0</v>
+        <v>0.59236111111111112</v>
       </c>
       <c r="I932">
-        <v>0</v>
+        <v>167</v>
       </c>
       <c r="J932">
         <v>0</v>
       </c>
-      <c r="K932">
-        <v>56</v>
-      </c>
       <c r="L932">
-        <v>56</v>
-      </c>
-      <c r="M932">
-        <v>0</v>
+        <v>333</v>
       </c>
       <c r="N932">
-        <v>833</v>
+        <v>667</v>
       </c>
       <c r="O932">
-        <v>111</v>
+        <v>389</v>
       </c>
       <c r="P932">
-        <v>1056</v>
+        <v>1556</v>
       </c>
       <c r="Q932" t="s">
-        <v>251</v>
+        <v>447</v>
       </c>
     </row>
     <row r="933" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A933" t="s">
-        <v>434</v>
+        <v>426</v>
       </c>
       <c r="B933">
-        <v>-34.540880000000001</v>
+        <v>-35.410254000000002</v>
       </c>
       <c r="C933">
-        <v>135.93384</v>
+        <v>138.32751999999999</v>
       </c>
       <c r="D933" s="2">
-        <v>46191</v>
+        <v>46190</v>
       </c>
       <c r="E933" s="20">
-        <v>0.44791666666666669</v>
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="F933">
+        <v>0</v>
+      </c>
+      <c r="G933">
+        <v>0</v>
+      </c>
+      <c r="H933">
+        <v>0</v>
       </c>
       <c r="I933">
-        <v>611</v>
+        <v>0</v>
       </c>
       <c r="J933">
-        <v>611</v>
+        <v>0</v>
+      </c>
+      <c r="K933">
+        <v>56</v>
       </c>
       <c r="L933">
-        <v>167</v>
+        <v>56</v>
+      </c>
+      <c r="M933">
+        <v>0</v>
+      </c>
+      <c r="N933">
+        <v>833</v>
       </c>
       <c r="O933">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="P933">
-        <v>890</v>
+        <v>1056</v>
       </c>
       <c r="Q933" t="s">
-        <v>283</v>
+        <v>251</v>
       </c>
     </row>
     <row r="934" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A934" t="s">
-        <v>289</v>
+        <v>434</v>
       </c>
       <c r="B934">
-        <v>-34.628509999999999</v>
+        <v>-34.540880000000001</v>
       </c>
       <c r="C934">
-        <v>135.86675</v>
+        <v>135.93384</v>
       </c>
       <c r="D934" s="2">
-        <v>46192</v>
+        <v>46191</v>
+      </c>
+      <c r="E934" s="20">
+        <v>0.44791666666666669</v>
       </c>
       <c r="I934">
-        <v>661</v>
+        <v>611</v>
       </c>
       <c r="J934">
-        <v>661</v>
+        <v>611</v>
       </c>
       <c r="L934">
-        <v>222</v>
+        <v>167</v>
       </c>
       <c r="O934">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="P934">
-        <v>883</v>
+        <v>890</v>
       </c>
       <c r="Q934" t="s">
         <v>283</v>
@@ -36144,34 +36149,31 @@
     </row>
     <row r="935" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A935" t="s">
-        <v>452</v>
+        <v>289</v>
       </c>
       <c r="B935">
-        <v>-34.759</v>
+        <v>-34.628509999999999</v>
       </c>
       <c r="C935">
-        <v>135.83886000000001</v>
+        <v>135.86675</v>
       </c>
       <c r="D935" s="2">
-        <v>46193</v>
-      </c>
-      <c r="E935" s="20">
-        <v>0.53125</v>
+        <v>46192</v>
       </c>
       <c r="I935">
-        <v>612</v>
+        <v>661</v>
       </c>
       <c r="J935">
-        <v>556</v>
+        <v>661</v>
       </c>
       <c r="L935">
-        <v>500</v>
+        <v>222</v>
       </c>
       <c r="O935">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="P935">
-        <v>1168</v>
+        <v>883</v>
       </c>
       <c r="Q935" t="s">
         <v>283</v>
@@ -36179,70 +36181,52 @@
     </row>
     <row r="936" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A936" t="s">
-        <v>359</v>
+        <v>452</v>
       </c>
       <c r="B936">
-        <v>-35.878667100000001</v>
+        <v>-34.759</v>
       </c>
       <c r="C936">
-        <v>137.6963188</v>
+        <v>135.83886000000001</v>
       </c>
       <c r="D936" s="2">
         <v>46193</v>
       </c>
-      <c r="F936">
-        <v>0</v>
-      </c>
-      <c r="G936">
-        <v>0</v>
-      </c>
-      <c r="H936">
-        <v>0</v>
+      <c r="E936" s="20">
+        <v>0.53125</v>
       </c>
       <c r="I936">
-        <v>0</v>
+        <v>612</v>
       </c>
       <c r="J936">
-        <v>0</v>
-      </c>
-      <c r="K936">
-        <v>0</v>
+        <v>556</v>
       </c>
       <c r="L936">
-        <v>0</v>
-      </c>
-      <c r="M936">
-        <v>0</v>
-      </c>
-      <c r="N936">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="O936">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="P936">
-        <v>0</v>
+        <v>1168</v>
       </c>
       <c r="Q936" t="s">
-        <v>151</v>
+        <v>283</v>
       </c>
     </row>
     <row r="937" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A937" t="s">
-        <v>456</v>
+        <v>359</v>
       </c>
       <c r="B937">
-        <v>-35.6614383</v>
+        <v>-35.878667100000001</v>
       </c>
       <c r="C937">
-        <v>137.6319307</v>
+        <v>137.6963188</v>
       </c>
       <c r="D937" s="2">
         <v>46193</v>
       </c>
-      <c r="E937" s="20">
-        <v>0.52083333333333337</v>
-      </c>
       <c r="F937">
         <v>0</v>
       </c>
@@ -36262,7 +36246,7 @@
         <v>0</v>
       </c>
       <c r="L937">
-        <v>333</v>
+        <v>0</v>
       </c>
       <c r="M937">
         <v>0</v>
@@ -36271,10 +36255,10 @@
         <v>0</v>
       </c>
       <c r="O937">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P937">
-        <v>334</v>
+        <v>0</v>
       </c>
       <c r="Q937" t="s">
         <v>151</v>
@@ -36282,81 +36266,96 @@
     </row>
     <row r="938" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A938" t="s">
-        <v>86</v>
+        <v>456</v>
       </c>
       <c r="B938">
-        <v>-35.540277000000003</v>
+        <v>-35.6614383</v>
       </c>
       <c r="C938">
-        <v>138.66416599999999</v>
+        <v>137.6319307</v>
       </c>
       <c r="D938" s="2">
-        <v>46194</v>
+        <v>46193</v>
       </c>
       <c r="E938" s="20">
-        <v>0.36041666666666666</v>
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="F938">
+        <v>0</v>
       </c>
       <c r="G938">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="H938">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="I938">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="J938">
+        <v>0</v>
+      </c>
+      <c r="K938">
         <v>0</v>
       </c>
       <c r="L938">
         <v>333</v>
       </c>
+      <c r="M938">
+        <v>0</v>
+      </c>
       <c r="N938">
-        <v>278</v>
+        <v>0</v>
       </c>
       <c r="O938">
-        <v>222</v>
+        <v>1</v>
       </c>
       <c r="P938">
-        <v>1001</v>
+        <v>334</v>
       </c>
       <c r="Q938" t="s">
-        <v>129</v>
+        <v>151</v>
       </c>
     </row>
     <row r="939" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A939" t="s">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="B939">
-        <v>-35.536745000000003</v>
+        <v>-35.540277000000003</v>
       </c>
       <c r="C939">
-        <v>138.6913744</v>
+        <v>138.66416599999999</v>
       </c>
       <c r="D939" s="2">
         <v>46194</v>
       </c>
       <c r="E939" s="20">
-        <v>0.36666666666666664</v>
+        <v>0.36041666666666666</v>
+      </c>
+      <c r="G939">
+        <v>56</v>
       </c>
       <c r="H939">
+        <v>56</v>
+      </c>
+      <c r="I939">
+        <v>56</v>
+      </c>
+      <c r="J939">
+        <v>0</v>
+      </c>
+      <c r="L939">
+        <v>333</v>
+      </c>
+      <c r="N939">
+        <v>278</v>
+      </c>
+      <c r="O939">
         <v>222</v>
       </c>
-      <c r="J939">
-        <v>0</v>
-      </c>
-      <c r="L939">
-        <v>222</v>
-      </c>
-      <c r="N939">
-        <v>500</v>
-      </c>
-      <c r="O939">
-        <v>834</v>
-      </c>
       <c r="P939">
-        <v>1778</v>
+        <v>1001</v>
       </c>
       <c r="Q939" t="s">
         <v>129</v>
@@ -36364,34 +36363,37 @@
     </row>
     <row r="940" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A940" t="s">
-        <v>451</v>
+        <v>100</v>
       </c>
       <c r="B940">
-        <v>-35.576688130000001</v>
+        <v>-35.536745000000003</v>
       </c>
       <c r="C940">
-        <v>138.64694589999999</v>
+        <v>138.6913744</v>
       </c>
       <c r="D940" s="2">
         <v>46194</v>
       </c>
-      <c r="I940">
-        <v>111</v>
+      <c r="E940" s="20">
+        <v>0.36666666666666664</v>
+      </c>
+      <c r="H940">
+        <v>222</v>
       </c>
       <c r="J940">
         <v>0</v>
       </c>
       <c r="L940">
-        <v>722</v>
+        <v>222</v>
       </c>
       <c r="N940">
-        <v>167</v>
+        <v>500</v>
       </c>
       <c r="O940">
-        <v>1666</v>
+        <v>834</v>
       </c>
       <c r="P940">
-        <v>2666</v>
+        <v>1778</v>
       </c>
       <c r="Q940" t="s">
         <v>129</v>
@@ -36399,34 +36401,34 @@
     </row>
     <row r="941" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A941" t="s">
-        <v>87</v>
+        <v>451</v>
       </c>
       <c r="B941">
-        <v>-35.573300000000003</v>
+        <v>-35.576688130000001</v>
       </c>
       <c r="C941">
-        <v>138.64250000000001</v>
+        <v>138.64694589999999</v>
       </c>
       <c r="D941" s="2">
         <v>46194</v>
       </c>
-      <c r="G941">
-        <v>56</v>
+      <c r="I941">
+        <v>111</v>
       </c>
       <c r="J941">
         <v>0</v>
       </c>
       <c r="L941">
-        <v>111</v>
+        <v>722</v>
       </c>
       <c r="N941">
-        <v>56</v>
+        <v>167</v>
       </c>
       <c r="O941">
-        <v>389</v>
+        <v>1666</v>
       </c>
       <c r="P941">
-        <v>612</v>
+        <v>2666</v>
       </c>
       <c r="Q941" t="s">
         <v>129</v>
@@ -36434,37 +36436,34 @@
     </row>
     <row r="942" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A942" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B942">
-        <v>-35.581124000000003</v>
+        <v>-35.573300000000003</v>
       </c>
       <c r="C942">
-        <v>138.60879700000001</v>
+        <v>138.64250000000001</v>
       </c>
       <c r="D942" s="2">
         <v>46194</v>
       </c>
-      <c r="F942">
-        <v>56</v>
-      </c>
       <c r="G942">
-        <v>167</v>
+        <v>56</v>
       </c>
       <c r="J942">
         <v>0</v>
       </c>
       <c r="L942">
-        <v>222</v>
+        <v>111</v>
       </c>
       <c r="N942">
-        <v>278</v>
+        <v>56</v>
       </c>
       <c r="O942">
         <v>389</v>
       </c>
       <c r="P942">
-        <v>1112</v>
+        <v>612</v>
       </c>
       <c r="Q942" t="s">
         <v>129</v>
@@ -36472,40 +36471,37 @@
     </row>
     <row r="943" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A943" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B943">
-        <v>-35.6048446</v>
+        <v>-35.581124000000003</v>
       </c>
       <c r="C943">
-        <v>138.59278499999999</v>
+        <v>138.60879700000001</v>
       </c>
       <c r="D943" s="2">
         <v>46194</v>
       </c>
+      <c r="F943">
+        <v>56</v>
+      </c>
       <c r="G943">
-        <v>111</v>
-      </c>
-      <c r="H943">
         <v>167</v>
       </c>
-      <c r="I943">
-        <v>167</v>
-      </c>
       <c r="J943">
         <v>0</v>
       </c>
       <c r="L943">
-        <v>56</v>
+        <v>222</v>
       </c>
       <c r="N943">
-        <v>778</v>
+        <v>278</v>
       </c>
       <c r="O943">
-        <v>667</v>
+        <v>389</v>
       </c>
       <c r="P943">
-        <v>1946</v>
+        <v>1112</v>
       </c>
       <c r="Q943" t="s">
         <v>129</v>
@@ -36513,34 +36509,40 @@
     </row>
     <row r="944" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A944" t="s">
-        <v>374</v>
+        <v>89</v>
       </c>
       <c r="B944">
-        <v>-35.612285999999997</v>
+        <v>-35.6048446</v>
       </c>
       <c r="C944">
-        <v>138.564302</v>
+        <v>138.59278499999999</v>
       </c>
       <c r="D944" s="2">
         <v>46194</v>
       </c>
+      <c r="G944">
+        <v>111</v>
+      </c>
       <c r="H944">
-        <v>111</v>
+        <v>167</v>
       </c>
       <c r="I944">
-        <v>111</v>
+        <v>167</v>
       </c>
       <c r="J944">
         <v>0</v>
       </c>
+      <c r="L944">
+        <v>56</v>
+      </c>
       <c r="N944">
-        <v>444</v>
+        <v>778</v>
       </c>
       <c r="O944">
-        <v>167</v>
+        <v>667</v>
       </c>
       <c r="P944">
-        <v>833</v>
+        <v>1946</v>
       </c>
       <c r="Q944" t="s">
         <v>129</v>
@@ -36548,34 +36550,34 @@
     </row>
     <row r="945" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A945" t="s">
-        <v>431</v>
+        <v>374</v>
       </c>
       <c r="B945">
-        <v>-35.619</v>
+        <v>-35.612285999999997</v>
       </c>
       <c r="C945">
-        <v>138.58099999999999</v>
+        <v>138.564302</v>
       </c>
       <c r="D945" s="2">
         <v>46194</v>
       </c>
-      <c r="G945">
-        <v>56</v>
-      </c>
       <c r="H945">
         <v>111</v>
       </c>
+      <c r="I945">
+        <v>111</v>
+      </c>
       <c r="J945">
         <v>0</v>
       </c>
       <c r="N945">
-        <v>1056</v>
+        <v>444</v>
       </c>
       <c r="O945">
-        <v>56</v>
+        <v>167</v>
       </c>
       <c r="P945">
-        <v>1279</v>
+        <v>833</v>
       </c>
       <c r="Q945" t="s">
         <v>129</v>
@@ -36583,69 +36585,72 @@
     </row>
     <row r="946" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A946" t="s">
-        <v>455</v>
+        <v>431</v>
       </c>
       <c r="B946">
-        <v>-35.576250000000002</v>
+        <v>-35.619</v>
       </c>
       <c r="C946">
-        <v>138.64349999999999</v>
+        <v>138.58099999999999</v>
       </c>
       <c r="D946" s="2">
         <v>46194</v>
       </c>
-      <c r="E946" s="20">
-        <v>0.38541666666666669</v>
-      </c>
-      <c r="I946">
-        <v>56</v>
+      <c r="G946">
+        <v>56</v>
+      </c>
+      <c r="H946">
+        <v>111</v>
       </c>
       <c r="J946">
         <v>0</v>
       </c>
-      <c r="L946">
-        <v>1333</v>
-      </c>
       <c r="N946">
-        <v>56</v>
+        <v>1056</v>
       </c>
       <c r="O946">
-        <v>167</v>
+        <v>56</v>
       </c>
       <c r="P946">
-        <v>1612</v>
+        <v>1279</v>
       </c>
       <c r="Q946" t="s">
-        <v>447</v>
+        <v>129</v>
       </c>
     </row>
     <row r="947" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A947" t="s">
-        <v>88</v>
+        <v>455</v>
       </c>
       <c r="B947">
-        <v>-35.581982000000004</v>
+        <v>-35.576250000000002</v>
       </c>
       <c r="C947">
-        <v>138.60827699999999</v>
+        <v>138.64349999999999</v>
       </c>
       <c r="D947" s="2">
         <v>46194</v>
       </c>
       <c r="E947" s="20">
-        <v>9</v>
+        <v>0.38541666666666669</v>
+      </c>
+      <c r="I947">
+        <v>56</v>
       </c>
       <c r="J947">
         <v>0</v>
       </c>
+      <c r="L947">
+        <v>1333</v>
+      </c>
       <c r="N947">
-        <v>1611</v>
+        <v>56</v>
       </c>
       <c r="O947">
-        <v>222</v>
+        <v>167</v>
       </c>
       <c r="P947">
-        <v>1833</v>
+        <v>1612</v>
       </c>
       <c r="Q947" t="s">
         <v>447</v>
@@ -36653,84 +36658,63 @@
     </row>
     <row r="948" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A948" t="s">
-        <v>400</v>
+        <v>88</v>
       </c>
       <c r="B948">
-        <v>-35.510497000000001</v>
+        <v>-35.581982000000004</v>
       </c>
       <c r="C948">
-        <v>138.21676299999999</v>
+        <v>138.60827699999999</v>
       </c>
       <c r="D948" s="2">
         <v>46194</v>
       </c>
       <c r="E948" s="20">
-        <v>0.58333333333333337</v>
-      </c>
-      <c r="F948">
-        <v>167</v>
-      </c>
-      <c r="G948">
-        <v>0</v>
-      </c>
-      <c r="H948">
+        <v>9</v>
+      </c>
+      <c r="J948">
+        <v>0</v>
+      </c>
+      <c r="N948">
+        <v>1611</v>
+      </c>
+      <c r="O948">
         <v>222</v>
       </c>
-      <c r="I948">
-        <v>278</v>
-      </c>
-      <c r="J948">
-        <v>0</v>
-      </c>
-      <c r="K948">
-        <v>0</v>
-      </c>
-      <c r="L948">
-        <v>167</v>
-      </c>
-      <c r="M948">
-        <v>0</v>
-      </c>
-      <c r="N948">
-        <v>833</v>
-      </c>
-      <c r="O948">
-        <v>333</v>
-      </c>
       <c r="P948">
-        <v>2000</v>
+        <v>1833</v>
       </c>
       <c r="Q948" t="s">
-        <v>251</v>
+        <v>447</v>
       </c>
     </row>
     <row r="949" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A949" t="s">
-        <v>311</v>
+        <v>400</v>
       </c>
       <c r="B949">
-        <v>-35.445059999999998</v>
+        <v>-35.510497000000001</v>
       </c>
       <c r="C949">
-        <v>138.30758399999999</v>
+        <v>138.21676299999999</v>
       </c>
       <c r="D949" s="2">
-        <v>46195</v>
+        <v>46194</v>
       </c>
       <c r="E949" s="20">
-        <v>0.39583333333333331</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="F949">
-        <v>0</v>
+        <v>167</v>
       </c>
       <c r="G949">
         <v>0</v>
       </c>
       <c r="H949">
-        <v>0</v>
+        <v>222</v>
       </c>
       <c r="I949">
-        <v>56</v>
+        <v>278</v>
       </c>
       <c r="J949">
         <v>0</v>
@@ -36739,39 +36723,39 @@
         <v>0</v>
       </c>
       <c r="L949">
-        <v>0</v>
+        <v>167</v>
       </c>
       <c r="M949">
         <v>0</v>
       </c>
       <c r="N949">
-        <v>611</v>
+        <v>833</v>
       </c>
       <c r="O949">
-        <v>56</v>
+        <v>333</v>
       </c>
       <c r="P949">
-        <v>723</v>
+        <v>2000</v>
       </c>
       <c r="Q949" t="s">
-        <v>401</v>
+        <v>251</v>
       </c>
     </row>
     <row r="950" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A950" t="s">
-        <v>395</v>
+        <v>311</v>
       </c>
       <c r="B950">
-        <v>-35.793973000000001</v>
+        <v>-35.445059999999998</v>
       </c>
       <c r="C950">
-        <v>137.852418</v>
+        <v>138.30758399999999</v>
       </c>
       <c r="D950" s="2">
         <v>46195</v>
       </c>
       <c r="E950" s="20">
-        <v>0.58333333333333337</v>
+        <v>0.39583333333333331</v>
       </c>
       <c r="F950">
         <v>0</v>
@@ -36783,7 +36767,7 @@
         <v>0</v>
       </c>
       <c r="I950">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="J950">
         <v>0</v>
@@ -36798,33 +36782,33 @@
         <v>0</v>
       </c>
       <c r="N950">
-        <v>0</v>
+        <v>611</v>
       </c>
       <c r="O950">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="P950">
-        <v>0</v>
+        <v>723</v>
       </c>
       <c r="Q950" t="s">
-        <v>151</v>
+        <v>401</v>
       </c>
     </row>
     <row r="951" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A951" t="s">
-        <v>256</v>
+        <v>395</v>
       </c>
       <c r="B951">
-        <v>-35.7987082</v>
+        <v>-35.793973000000001</v>
       </c>
       <c r="C951">
-        <v>137.81647699999999</v>
+        <v>137.852418</v>
       </c>
       <c r="D951" s="2">
         <v>46195</v>
       </c>
       <c r="E951" s="20">
-        <v>0.60416666666666663</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="F951">
         <v>0</v>
@@ -36865,66 +36849,87 @@
     </row>
     <row r="952" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A952" t="s">
-        <v>434</v>
+        <v>256</v>
       </c>
       <c r="B952">
-        <v>-34.540880000000001</v>
+        <v>-35.7987082</v>
       </c>
       <c r="C952">
-        <v>135.93384</v>
+        <v>137.81647699999999</v>
       </c>
       <c r="D952" s="2">
-        <v>46196</v>
+        <v>46195</v>
       </c>
       <c r="E952" s="20">
-        <v>0.35416666666666669</v>
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="F952">
+        <v>0</v>
+      </c>
+      <c r="G952">
+        <v>0</v>
+      </c>
+      <c r="H952">
+        <v>0</v>
       </c>
       <c r="I952">
-        <v>1111</v>
+        <v>0</v>
       </c>
       <c r="J952">
-        <v>1111</v>
+        <v>0</v>
+      </c>
+      <c r="K952">
+        <v>0</v>
       </c>
       <c r="L952">
-        <v>611</v>
+        <v>0</v>
+      </c>
+      <c r="M952">
+        <v>0</v>
+      </c>
+      <c r="N952">
+        <v>0</v>
       </c>
       <c r="O952">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="P952">
-        <v>1778</v>
+        <v>0</v>
       </c>
       <c r="Q952" t="s">
-        <v>283</v>
+        <v>151</v>
       </c>
     </row>
     <row r="953" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A953" t="s">
-        <v>453</v>
+        <v>434</v>
       </c>
       <c r="B953">
-        <v>-34.718809999999998</v>
+        <v>-34.540880000000001</v>
       </c>
       <c r="C953">
-        <v>135.85857999999999</v>
+        <v>135.93384</v>
       </c>
       <c r="D953" s="2">
         <v>46196</v>
       </c>
       <c r="E953" s="20">
-        <v>46197.375</v>
+        <v>0.35416666666666669</v>
       </c>
       <c r="I953">
-        <v>1167</v>
+        <v>1111</v>
       </c>
       <c r="J953">
         <v>1111</v>
       </c>
+      <c r="L953">
+        <v>611</v>
+      </c>
       <c r="O953">
         <v>56</v>
       </c>
       <c r="P953">
-        <v>1223</v>
+        <v>1778</v>
       </c>
       <c r="Q953" t="s">
         <v>283</v>
@@ -36932,75 +36937,66 @@
     </row>
     <row r="954" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A954" t="s">
-        <v>79</v>
+        <v>453</v>
       </c>
       <c r="B954">
-        <v>-34.804662999999998</v>
+        <v>-34.718809999999998</v>
       </c>
       <c r="C954">
-        <v>138.540223</v>
+        <v>135.85857999999999</v>
       </c>
       <c r="D954" s="2">
         <v>46196</v>
       </c>
       <c r="E954" s="20">
-        <v>0.58333333333333337</v>
+        <v>46197.375</v>
       </c>
       <c r="I954">
-        <v>2.7749999999999999</v>
+        <v>1167</v>
       </c>
       <c r="J954">
-        <v>0</v>
-      </c>
-      <c r="L954">
-        <v>6.2249999999999996</v>
+        <v>1111</v>
       </c>
       <c r="O954">
-        <v>1.65</v>
+        <v>56</v>
       </c>
       <c r="P954">
-        <v>10.65</v>
+        <v>1223</v>
       </c>
       <c r="Q954" t="s">
-        <v>78</v>
+        <v>283</v>
       </c>
     </row>
     <row r="955" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A955" t="s">
-        <v>267</v>
+        <v>79</v>
       </c>
       <c r="B955">
-        <v>-34.824044999999998</v>
+        <v>-34.804662999999998</v>
       </c>
       <c r="C955">
-        <v>138.48377600000001</v>
+        <v>138.540223</v>
       </c>
       <c r="D955" s="2">
         <v>46196</v>
       </c>
       <c r="E955" s="20">
-        <v>0.55694444444444446</v>
-      </c>
-      <c r="G955">
-        <v>0.15</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="I955">
-        <v>6.2</v>
+        <v>2.7749999999999999</v>
       </c>
       <c r="J955">
         <v>0</v>
       </c>
       <c r="L955">
-        <v>9</v>
-      </c>
-      <c r="N955">
-        <v>0.2</v>
+        <v>6.2249999999999996</v>
       </c>
       <c r="O955">
-        <v>0.35</v>
+        <v>1.65</v>
       </c>
       <c r="P955">
-        <v>15.9</v>
+        <v>10.65</v>
       </c>
       <c r="Q955" t="s">
         <v>78</v>
@@ -37008,40 +37004,40 @@
     </row>
     <row r="956" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A956" t="s">
-        <v>348</v>
+        <v>267</v>
       </c>
       <c r="B956">
-        <v>-34.860666999999999</v>
+        <v>-34.824044999999998</v>
       </c>
       <c r="C956">
-        <v>138.490938</v>
+        <v>138.48377600000001</v>
       </c>
       <c r="D956" s="2">
         <v>46196</v>
       </c>
       <c r="E956" s="20">
-        <v>4.8611111111111112E-2</v>
+        <v>0.55694444444444446</v>
       </c>
       <c r="G956">
-        <v>0.1</v>
-      </c>
-      <c r="H956">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="I956">
-        <v>54.7</v>
+        <v>6.2</v>
       </c>
       <c r="J956">
         <v>0</v>
       </c>
       <c r="L956">
-        <v>2.2999999999999998</v>
+        <v>9</v>
+      </c>
+      <c r="N956">
+        <v>0.2</v>
       </c>
       <c r="O956">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="P956">
-        <v>57.5</v>
+        <v>15.9</v>
       </c>
       <c r="Q956" t="s">
         <v>78</v>
@@ -37049,110 +37045,98 @@
     </row>
     <row r="957" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A957" t="s">
-        <v>422</v>
+        <v>348</v>
       </c>
       <c r="B957">
-        <v>-34.978150999999997</v>
+        <v>-34.860666999999999</v>
       </c>
       <c r="C957">
-        <v>138.50750400000001</v>
+        <v>138.490938</v>
       </c>
       <c r="D957" s="2">
         <v>46196</v>
       </c>
       <c r="E957" s="20">
-        <v>0.59375</v>
+        <v>4.8611111111111112E-2</v>
+      </c>
+      <c r="G957">
+        <v>0.1</v>
+      </c>
+      <c r="H957">
+        <v>0.1</v>
       </c>
       <c r="I957">
-        <v>111</v>
+        <v>54.7</v>
       </c>
       <c r="J957">
         <v>0</v>
       </c>
       <c r="L957">
-        <v>222</v>
-      </c>
-      <c r="N957">
-        <v>222</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="O957">
-        <v>667</v>
+        <v>0.3</v>
       </c>
       <c r="P957">
-        <v>1222</v>
+        <v>57.5</v>
       </c>
       <c r="Q957" t="s">
-        <v>447</v>
+        <v>78</v>
       </c>
     </row>
     <row r="958" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A958" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B958">
-        <v>-35.500024000000003</v>
+        <v>-34.978150999999997</v>
       </c>
       <c r="C958">
-        <v>138.24287699999999</v>
+        <v>138.50750400000001</v>
       </c>
       <c r="D958" s="2">
         <v>46196</v>
       </c>
       <c r="E958" s="20">
-        <v>0.38541666666666669</v>
-      </c>
-      <c r="F958">
-        <v>0</v>
-      </c>
-      <c r="G958">
-        <v>0</v>
-      </c>
-      <c r="H958">
-        <v>0</v>
+        <v>0.59375</v>
       </c>
       <c r="I958">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="J958">
         <v>0</v>
       </c>
-      <c r="K958">
-        <v>0</v>
-      </c>
       <c r="L958">
-        <v>0</v>
-      </c>
-      <c r="M958">
-        <v>0</v>
+        <v>222</v>
       </c>
       <c r="N958">
-        <v>111</v>
+        <v>222</v>
       </c>
       <c r="O958">
-        <v>0</v>
+        <v>667</v>
       </c>
       <c r="P958">
-        <v>111</v>
+        <v>1222</v>
       </c>
       <c r="Q958" t="s">
-        <v>251</v>
+        <v>447</v>
       </c>
     </row>
     <row r="959" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A959" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="B959">
-        <v>-35.591330800000001</v>
+        <v>-35.500024000000003</v>
       </c>
       <c r="C959">
-        <v>137.5061887</v>
+        <v>138.24287699999999</v>
       </c>
       <c r="D959" s="2">
         <v>46196</v>
       </c>
       <c r="E959" s="20">
-        <v>0.45833333333333331</v>
+        <v>0.38541666666666669</v>
       </c>
       <c r="F959">
         <v>0</v>
@@ -37179,33 +37163,33 @@
         <v>0</v>
       </c>
       <c r="N959">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="O959">
         <v>0</v>
       </c>
       <c r="P959">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="Q959" t="s">
-        <v>151</v>
+        <v>251</v>
       </c>
     </row>
     <row r="960" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A960" t="s">
-        <v>457</v>
+        <v>418</v>
       </c>
       <c r="B960">
-        <v>-35.595789000000003</v>
+        <v>-35.591330800000001</v>
       </c>
       <c r="C960">
-        <v>137.51194899999999</v>
+        <v>137.5061887</v>
       </c>
       <c r="D960" s="2">
         <v>46196</v>
       </c>
       <c r="E960" s="20">
-        <v>0.47916666666666669</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="F960">
         <v>0</v>
@@ -37229,7 +37213,7 @@
         <v>0</v>
       </c>
       <c r="M960">
-        <v>222</v>
+        <v>0</v>
       </c>
       <c r="N960">
         <v>0</v>
@@ -37238,7 +37222,7 @@
         <v>0</v>
       </c>
       <c r="P960">
-        <v>222</v>
+        <v>0</v>
       </c>
       <c r="Q960" t="s">
         <v>151</v>
@@ -37246,19 +37230,22 @@
     </row>
     <row r="961" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A961" t="s">
-        <v>59</v>
+        <v>457</v>
       </c>
       <c r="B961">
-        <v>-35.084850000000003</v>
+        <v>-35.595789000000003</v>
       </c>
       <c r="C961">
-        <v>137.74889999999999</v>
+        <v>137.51194899999999</v>
       </c>
       <c r="D961" s="2">
         <v>46196</v>
       </c>
       <c r="E961" s="20">
-        <v>0.58333333333333337</v>
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="F961">
+        <v>0</v>
       </c>
       <c r="G961">
         <v>0</v>
@@ -37272,43 +37259,43 @@
       <c r="J961">
         <v>0</v>
       </c>
+      <c r="K961">
+        <v>0</v>
+      </c>
       <c r="L961">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="M961">
-        <v>0</v>
+        <v>222</v>
       </c>
       <c r="N961">
-        <v>333</v>
+        <v>0</v>
       </c>
       <c r="O961">
         <v>0</v>
       </c>
       <c r="P961">
-        <v>444</v>
+        <v>222</v>
       </c>
       <c r="Q961" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="962" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A962" t="s">
-        <v>450</v>
+        <v>59</v>
       </c>
       <c r="B962">
-        <v>-35.595986000000003</v>
+        <v>-35.084850000000003</v>
       </c>
       <c r="C962">
-        <v>138.104072</v>
+        <v>137.74889999999999</v>
       </c>
       <c r="D962" s="2">
-        <v>46197</v>
+        <v>46196</v>
       </c>
       <c r="E962" s="20">
-        <v>0.54166666666666663</v>
-      </c>
-      <c r="F962">
-        <v>0</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="G962">
         <v>0</v>
@@ -37322,55 +37309,52 @@
       <c r="J962">
         <v>0</v>
       </c>
-      <c r="K962">
-        <v>0</v>
-      </c>
       <c r="L962">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="M962">
         <v>0</v>
       </c>
       <c r="N962">
-        <v>833</v>
+        <v>333</v>
       </c>
       <c r="O962">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="P962">
-        <v>889</v>
+        <v>444</v>
       </c>
       <c r="Q962" t="s">
-        <v>251</v>
+        <v>149</v>
       </c>
     </row>
     <row r="963" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A963" t="s">
-        <v>426</v>
+        <v>450</v>
       </c>
       <c r="B963">
-        <v>-35.410254000000002</v>
+        <v>-35.595986000000003</v>
       </c>
       <c r="C963">
-        <v>138.32751999999999</v>
+        <v>138.104072</v>
       </c>
       <c r="D963" s="2">
         <v>46197</v>
       </c>
       <c r="E963" s="20">
-        <v>0.3125</v>
+        <v>0.54166666666666663</v>
       </c>
       <c r="F963">
         <v>0</v>
       </c>
       <c r="G963">
-        <v>167</v>
+        <v>0</v>
       </c>
       <c r="H963">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="I963">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="J963">
         <v>0</v>
@@ -37379,19 +37363,19 @@
         <v>0</v>
       </c>
       <c r="L963">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="M963">
         <v>0</v>
       </c>
       <c r="N963">
-        <v>389</v>
+        <v>833</v>
       </c>
       <c r="O963">
-        <v>111</v>
+        <v>56</v>
       </c>
       <c r="P963">
-        <v>1279</v>
+        <v>889</v>
       </c>
       <c r="Q963" t="s">
         <v>251</v>
@@ -37399,66 +37383,84 @@
     </row>
     <row r="964" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A964" t="s">
-        <v>94</v>
+        <v>426</v>
       </c>
       <c r="B964">
-        <v>-35.58858</v>
+        <v>-35.410254000000002</v>
       </c>
       <c r="C964">
-        <v>138.60474600000001</v>
+        <v>138.32751999999999</v>
       </c>
       <c r="D964" s="2">
-        <v>46201</v>
+        <v>46197</v>
+      </c>
+      <c r="E964" s="20">
+        <v>0.3125</v>
+      </c>
+      <c r="F964">
+        <v>0</v>
+      </c>
+      <c r="G964">
+        <v>167</v>
+      </c>
+      <c r="H964">
+        <v>56</v>
+      </c>
+      <c r="I964">
+        <v>500</v>
       </c>
       <c r="J964">
         <v>0</v>
       </c>
+      <c r="K964">
+        <v>0</v>
+      </c>
       <c r="L964">
-        <v>500</v>
+        <v>56</v>
+      </c>
+      <c r="M964">
+        <v>0</v>
       </c>
       <c r="N964">
-        <v>56</v>
+        <v>389</v>
       </c>
       <c r="O964">
-        <v>278</v>
+        <v>111</v>
       </c>
       <c r="P964">
-        <v>834</v>
+        <v>1279</v>
       </c>
       <c r="Q964" t="s">
-        <v>129</v>
+        <v>251</v>
       </c>
     </row>
     <row r="965" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A965" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="B965">
-        <v>-35.6048446</v>
+        <v>-35.58858</v>
       </c>
       <c r="C965">
-        <v>138.59278499999999</v>
+        <v>138.60474600000001</v>
       </c>
       <c r="D965" s="2">
         <v>46201</v>
       </c>
-      <c r="G965">
-        <v>56</v>
-      </c>
-      <c r="H965">
-        <v>56</v>
-      </c>
       <c r="J965">
         <v>0</v>
       </c>
+      <c r="L965">
+        <v>500</v>
+      </c>
       <c r="N965">
+        <v>56</v>
+      </c>
+      <c r="O965">
         <v>278</v>
       </c>
-      <c r="O965">
-        <v>167</v>
-      </c>
       <c r="P965">
-        <v>557</v>
+        <v>834</v>
       </c>
       <c r="Q965" t="s">
         <v>129</v>
@@ -37466,72 +37468,54 @@
     </row>
     <row r="966" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A966" t="s">
-        <v>436</v>
+        <v>89</v>
       </c>
       <c r="B966">
-        <v>-35.521467000000001</v>
+        <v>-35.6048446</v>
       </c>
       <c r="C966">
-        <v>138.18532999999999</v>
+        <v>138.59278499999999</v>
       </c>
       <c r="D966" s="2">
         <v>46201</v>
       </c>
-      <c r="E966" s="20">
-        <v>0.52430555555555558</v>
-      </c>
-      <c r="F966">
-        <v>0</v>
-      </c>
       <c r="G966">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="H966">
-        <v>0</v>
-      </c>
-      <c r="I966">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="J966">
         <v>0</v>
       </c>
-      <c r="K966">
-        <v>0</v>
-      </c>
-      <c r="L966">
-        <v>56</v>
-      </c>
-      <c r="M966">
-        <v>0</v>
-      </c>
       <c r="N966">
-        <v>1167</v>
+        <v>278</v>
       </c>
       <c r="O966">
-        <v>0</v>
+        <v>167</v>
       </c>
       <c r="P966">
-        <v>1223</v>
+        <v>557</v>
       </c>
       <c r="Q966" t="s">
-        <v>251</v>
+        <v>129</v>
       </c>
     </row>
     <row r="967" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A967" t="s">
-        <v>421</v>
+        <v>436</v>
       </c>
       <c r="B967">
-        <v>-35.500024000000003</v>
+        <v>-35.521467000000001</v>
       </c>
       <c r="C967">
-        <v>138.24287699999999</v>
+        <v>138.18532999999999</v>
       </c>
       <c r="D967" s="2">
         <v>46201</v>
       </c>
       <c r="E967" s="20">
-        <v>0.67708333333333337</v>
+        <v>0.52430555555555558</v>
       </c>
       <c r="F967">
         <v>0</v>
@@ -37552,42 +37536,42 @@
         <v>0</v>
       </c>
       <c r="L967">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="M967">
         <v>0</v>
       </c>
       <c r="N967">
-        <v>56</v>
+        <v>1167</v>
       </c>
       <c r="O967">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="P967">
-        <v>112</v>
+        <v>1223</v>
       </c>
       <c r="Q967" t="s">
-        <v>401</v>
+        <v>251</v>
       </c>
     </row>
     <row r="968" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A968" t="s">
-        <v>459</v>
-      </c>
-      <c r="B968" s="25">
-        <v>-35.788674999999998</v>
-      </c>
-      <c r="C968" s="25">
-        <v>138.070415</v>
+        <v>421</v>
+      </c>
+      <c r="B968">
+        <v>-35.500024000000003</v>
+      </c>
+      <c r="C968">
+        <v>138.24287699999999</v>
       </c>
       <c r="D968" s="2">
-        <v>46202</v>
+        <v>46201</v>
       </c>
       <c r="E968" s="20">
-        <v>0.58333333333333337</v>
+        <v>0.67708333333333337</v>
       </c>
       <c r="F968">
-        <v>158333</v>
+        <v>0</v>
       </c>
       <c r="G968">
         <v>0</v>
@@ -37596,7 +37580,7 @@
         <v>0</v>
       </c>
       <c r="I968">
-        <v>7333</v>
+        <v>0</v>
       </c>
       <c r="J968">
         <v>0</v>
@@ -37605,42 +37589,42 @@
         <v>0</v>
       </c>
       <c r="L968">
-        <v>17500</v>
+        <v>0</v>
       </c>
       <c r="M968">
-        <v>4667</v>
+        <v>0</v>
       </c>
       <c r="N968">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="O968">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="P968">
-        <v>187833</v>
+        <v>112</v>
       </c>
       <c r="Q968" t="s">
-        <v>151</v>
+        <v>401</v>
       </c>
     </row>
     <row r="969" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A969" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B969">
-        <v>-35.787862699999998</v>
+        <v>-35.788674999999998</v>
       </c>
       <c r="C969">
-        <v>138.07130670000001</v>
+        <v>138.070415</v>
       </c>
       <c r="D969" s="2">
         <v>46202</v>
       </c>
       <c r="E969" s="20">
-        <v>14.3</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="F969">
-        <v>2667</v>
+        <v>158333</v>
       </c>
       <c r="G969">
         <v>0</v>
@@ -37649,7 +37633,7 @@
         <v>0</v>
       </c>
       <c r="I969">
-        <v>111</v>
+        <v>7333</v>
       </c>
       <c r="J969">
         <v>0</v>
@@ -37658,16 +37642,19 @@
         <v>0</v>
       </c>
       <c r="L969">
-        <v>167</v>
+        <v>17500</v>
       </c>
       <c r="M969">
-        <v>0</v>
+        <v>4667</v>
       </c>
       <c r="N969">
         <v>0</v>
       </c>
+      <c r="O969">
+        <v>0</v>
+      </c>
       <c r="P969">
-        <v>2945</v>
+        <v>187833</v>
       </c>
       <c r="Q969" t="s">
         <v>151</v>
@@ -37675,22 +37662,22 @@
     </row>
     <row r="970" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A970" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B970">
-        <v>-35.720106999999999</v>
+        <v>-35.787862699999998</v>
       </c>
       <c r="C970">
-        <v>137.94337100000001</v>
+        <v>138.07130670000001</v>
       </c>
       <c r="D970" s="2">
         <v>46202</v>
       </c>
       <c r="E970" s="20">
-        <v>1.3</v>
+        <v>14.3</v>
       </c>
       <c r="F970">
-        <v>1167</v>
+        <v>2667</v>
       </c>
       <c r="G970">
         <v>0</v>
@@ -37699,7 +37686,7 @@
         <v>0</v>
       </c>
       <c r="I970">
-        <v>1000</v>
+        <v>111</v>
       </c>
       <c r="J970">
         <v>0</v>
@@ -37716,11 +37703,8 @@
       <c r="N970">
         <v>0</v>
       </c>
-      <c r="O970">
-        <v>0</v>
-      </c>
       <c r="P970">
-        <v>2334</v>
+        <v>2945</v>
       </c>
       <c r="Q970" t="s">
         <v>151</v>
@@ -37728,22 +37712,22 @@
     </row>
     <row r="971" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A971" t="s">
-        <v>311</v>
+        <v>461</v>
       </c>
       <c r="B971">
-        <v>-35.445059999999998</v>
+        <v>-35.720106999999999</v>
       </c>
       <c r="C971">
-        <v>138.30758399999999</v>
+        <v>137.94337100000001</v>
       </c>
       <c r="D971" s="2">
         <v>46202</v>
       </c>
       <c r="E971" s="20">
-        <v>0.35416666666666669</v>
+        <v>1.3</v>
       </c>
       <c r="F971">
-        <v>0</v>
+        <v>1167</v>
       </c>
       <c r="G971">
         <v>0</v>
@@ -37752,7 +37736,7 @@
         <v>0</v>
       </c>
       <c r="I971">
-        <v>278</v>
+        <v>1000</v>
       </c>
       <c r="J971">
         <v>0</v>
@@ -37761,132 +37745,719 @@
         <v>0</v>
       </c>
       <c r="L971">
-        <v>222</v>
+        <v>167</v>
       </c>
       <c r="M971">
         <v>0</v>
       </c>
       <c r="N971">
-        <v>333</v>
+        <v>0</v>
       </c>
       <c r="O971">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="P971">
-        <v>889</v>
+        <v>2334</v>
       </c>
       <c r="Q971" t="s">
-        <v>401</v>
+        <v>151</v>
       </c>
     </row>
     <row r="972" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A972" t="s">
-        <v>458</v>
+        <v>311</v>
       </c>
       <c r="B972">
-        <v>-35.557200000000002</v>
+        <v>-35.445059999999998</v>
       </c>
       <c r="C972">
-        <v>138.886</v>
+        <v>138.30758399999999</v>
       </c>
       <c r="D972" s="2">
-        <v>46203</v>
+        <v>46202</v>
+      </c>
+      <c r="E972" s="20">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="F972">
+        <v>0</v>
+      </c>
+      <c r="G972">
+        <v>0</v>
+      </c>
+      <c r="H972">
+        <v>0</v>
+      </c>
+      <c r="I972">
+        <v>278</v>
       </c>
       <c r="J972">
         <v>0</v>
       </c>
+      <c r="K972">
+        <v>0</v>
+      </c>
+      <c r="L972">
+        <v>222</v>
+      </c>
+      <c r="M972">
+        <v>0</v>
+      </c>
       <c r="N972">
-        <v>222</v>
+        <v>333</v>
       </c>
       <c r="O972">
-        <v>389</v>
+        <v>56</v>
       </c>
       <c r="P972">
-        <v>611</v>
+        <v>889</v>
       </c>
       <c r="Q972" t="s">
-        <v>129</v>
+        <v>401</v>
       </c>
     </row>
     <row r="973" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A973" t="s">
-        <v>301</v>
+        <v>458</v>
       </c>
       <c r="B973">
-        <v>-34.899749999999997</v>
+        <v>-35.557200000000002</v>
       </c>
       <c r="C973">
-        <v>137.45174</v>
+        <v>138.886</v>
       </c>
       <c r="D973" s="2">
         <v>46203</v>
       </c>
-      <c r="E973" s="20">
-        <v>0.3125</v>
-      </c>
-      <c r="I973">
-        <v>167</v>
-      </c>
       <c r="J973">
-        <v>111</v>
-      </c>
-      <c r="L973">
-        <v>278</v>
+        <v>0</v>
+      </c>
+      <c r="N973">
+        <v>222</v>
+      </c>
+      <c r="O973">
+        <v>389</v>
+      </c>
+      <c r="P973">
+        <v>611</v>
       </c>
       <c r="Q973" t="s">
-        <v>265</v>
+        <v>129</v>
       </c>
     </row>
     <row r="974" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A974" t="s">
+        <v>301</v>
+      </c>
+      <c r="B974">
+        <v>-34.899749999999997</v>
+      </c>
+      <c r="C974">
+        <v>137.45174</v>
+      </c>
+      <c r="D974" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E974" s="20">
+        <v>0.3125</v>
+      </c>
+      <c r="I974">
+        <v>167</v>
+      </c>
+      <c r="J974">
+        <v>111</v>
+      </c>
+      <c r="L974">
+        <v>278</v>
+      </c>
+      <c r="Q974" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="975" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A975" t="s">
         <v>59</v>
       </c>
-      <c r="B974">
+      <c r="B975">
         <v>-35.084850000000003</v>
       </c>
-      <c r="C974">
+      <c r="C975">
         <v>137.74889999999999</v>
       </c>
-      <c r="D974" s="2">
+      <c r="D975" s="2">
         <v>46204</v>
       </c>
-      <c r="E974" s="24">
+      <c r="E975" s="24">
         <v>0.58333333333333337</v>
       </c>
-      <c r="G974">
+      <c r="G975">
         <v>28</v>
       </c>
-      <c r="H974">
+      <c r="H975">
         <v>139</v>
       </c>
-      <c r="I974">
+      <c r="I975">
         <v>278</v>
       </c>
-      <c r="J974">
-        <v>0</v>
-      </c>
-      <c r="L974">
+      <c r="J975">
+        <v>0</v>
+      </c>
+      <c r="L975">
         <v>139</v>
       </c>
-      <c r="M974">
-        <v>0</v>
-      </c>
-      <c r="N974">
+      <c r="M975">
+        <v>0</v>
+      </c>
+      <c r="N975">
         <v>611</v>
       </c>
-      <c r="O974">
-        <v>0</v>
-      </c>
-      <c r="P974">
+      <c r="O975">
+        <v>0</v>
+      </c>
+      <c r="P975">
         <v>1195</v>
       </c>
-      <c r="Q974" t="s">
+      <c r="Q975" t="s">
         <v>149</v>
       </c>
     </row>
+    <row r="976" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A976" t="s">
+        <v>453</v>
+      </c>
+      <c r="B976">
+        <v>-34.718809999999998</v>
+      </c>
+      <c r="C976">
+        <v>135.85857999999999</v>
+      </c>
+      <c r="D976" s="2">
+        <v>46205</v>
+      </c>
+      <c r="E976" s="20">
+        <v>0.46875</v>
+      </c>
+      <c r="I976">
+        <v>180</v>
+      </c>
+      <c r="J976">
+        <v>161</v>
+      </c>
+      <c r="L976">
+        <v>11</v>
+      </c>
+      <c r="O976">
+        <v>8</v>
+      </c>
+      <c r="P976">
+        <v>199</v>
+      </c>
+      <c r="Q976" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="977" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A977" t="s">
+        <v>465</v>
+      </c>
+      <c r="B977">
+        <v>-35.653578199999998</v>
+      </c>
+      <c r="C977">
+        <v>137.64360360000001</v>
+      </c>
+      <c r="D977" s="2">
+        <v>46206</v>
+      </c>
+      <c r="E977" s="20">
+        <v>0.5</v>
+      </c>
+      <c r="F977">
+        <v>0</v>
+      </c>
+      <c r="G977">
+        <v>0</v>
+      </c>
+      <c r="H977">
+        <v>0</v>
+      </c>
+      <c r="I977">
+        <v>0</v>
+      </c>
+      <c r="J977">
+        <v>0</v>
+      </c>
+      <c r="K977">
+        <v>0</v>
+      </c>
+      <c r="L977">
+        <v>0</v>
+      </c>
+      <c r="M977">
+        <v>0</v>
+      </c>
+      <c r="N977">
+        <v>0</v>
+      </c>
+      <c r="O977">
+        <v>0</v>
+      </c>
+      <c r="P977">
+        <v>0</v>
+      </c>
+      <c r="Q977" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="978" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A978" t="s">
+        <v>79</v>
+      </c>
+      <c r="B978">
+        <v>-34.804662999999998</v>
+      </c>
+      <c r="C978">
+        <v>138.540223</v>
+      </c>
+      <c r="D978" s="2">
+        <v>46207</v>
+      </c>
+      <c r="E978" s="20">
+        <v>0.55555555555555558</v>
+      </c>
+      <c r="I978">
+        <v>1.8</v>
+      </c>
+      <c r="J978">
+        <v>0</v>
+      </c>
+      <c r="L978">
+        <v>5.1749999999999998</v>
+      </c>
+      <c r="M978">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="P978">
+        <v>7.05</v>
+      </c>
+      <c r="Q978" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="979" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A979" t="s">
+        <v>267</v>
+      </c>
+      <c r="B979">
+        <v>-34.824044999999998</v>
+      </c>
+      <c r="C979">
+        <v>138.48377600000001</v>
+      </c>
+      <c r="D979" s="2">
+        <v>46207</v>
+      </c>
+      <c r="E979" s="20">
+        <v>0.57291666666666663</v>
+      </c>
+      <c r="H979">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="I979">
+        <v>0.97499999999999998</v>
+      </c>
+      <c r="J979">
+        <v>0</v>
+      </c>
+      <c r="L979">
+        <v>19.350000000000001</v>
+      </c>
+      <c r="M979">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="N979">
+        <v>0.15</v>
+      </c>
+      <c r="P979">
+        <v>20.625</v>
+      </c>
+      <c r="Q979" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="980" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A980" t="s">
+        <v>348</v>
+      </c>
+      <c r="B980">
+        <v>-34.860666999999999</v>
+      </c>
+      <c r="C980">
+        <v>138.490938</v>
+      </c>
+      <c r="D980" s="2">
+        <v>46207</v>
+      </c>
+      <c r="E980" s="20">
+        <v>0.59027777777777779</v>
+      </c>
+      <c r="H980">
+        <v>1</v>
+      </c>
+      <c r="I980">
+        <v>68.5</v>
+      </c>
+      <c r="J980">
+        <v>0</v>
+      </c>
+      <c r="L980">
+        <v>10.25</v>
+      </c>
+      <c r="P980">
+        <v>79.75</v>
+      </c>
+      <c r="Q980" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="981" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A981" t="s">
+        <v>463</v>
+      </c>
+      <c r="B981">
+        <v>-34.589910000000003</v>
+      </c>
+      <c r="C981">
+        <v>135.90476000000001</v>
+      </c>
+      <c r="D981" s="2">
+        <v>46207</v>
+      </c>
+      <c r="E981" s="20">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="I981">
+        <v>2</v>
+      </c>
+      <c r="J981">
+        <v>0</v>
+      </c>
+      <c r="L981">
+        <v>87</v>
+      </c>
+      <c r="O981">
+        <v>2</v>
+      </c>
+      <c r="P981">
+        <v>91</v>
+      </c>
+      <c r="Q981" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="982" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A982" t="s">
+        <v>395</v>
+      </c>
+      <c r="B982">
+        <v>-35.793973000000001</v>
+      </c>
+      <c r="C982">
+        <v>137.852418</v>
+      </c>
+      <c r="D982" s="2">
+        <v>46207</v>
+      </c>
+      <c r="E982" s="20">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="F982">
+        <v>111</v>
+      </c>
+      <c r="G982">
+        <v>0</v>
+      </c>
+      <c r="H982">
+        <v>0</v>
+      </c>
+      <c r="I982">
+        <v>0</v>
+      </c>
+      <c r="J982">
+        <v>0</v>
+      </c>
+      <c r="K982">
+        <v>0</v>
+      </c>
+      <c r="L982">
+        <v>556</v>
+      </c>
+      <c r="M982">
+        <v>0</v>
+      </c>
+      <c r="N982" t="s">
+        <v>464</v>
+      </c>
+      <c r="O982">
+        <v>0</v>
+      </c>
+      <c r="P982">
+        <v>667</v>
+      </c>
+      <c r="Q982" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="983" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A983" t="s">
+        <v>209</v>
+      </c>
+      <c r="B983" s="7">
+        <v>-35.739091000000002</v>
+      </c>
+      <c r="C983" s="7">
+        <v>137.67788400000001</v>
+      </c>
+      <c r="D983" s="2">
+        <v>46207</v>
+      </c>
+      <c r="E983" s="20">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="F983">
+        <v>0</v>
+      </c>
+      <c r="G983">
+        <v>0</v>
+      </c>
+      <c r="H983">
+        <v>0</v>
+      </c>
+      <c r="I983">
+        <v>0</v>
+      </c>
+      <c r="J983">
+        <v>0</v>
+      </c>
+      <c r="K983">
+        <v>0</v>
+      </c>
+      <c r="L983">
+        <v>222</v>
+      </c>
+      <c r="M983">
+        <v>0</v>
+      </c>
+      <c r="N983">
+        <v>0</v>
+      </c>
+      <c r="O983">
+        <v>0</v>
+      </c>
+      <c r="P983">
+        <v>222</v>
+      </c>
+      <c r="Q983" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="984" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A984" t="s">
+        <v>311</v>
+      </c>
+      <c r="B984">
+        <v>-35.445059999999998</v>
+      </c>
+      <c r="C984">
+        <v>138.30758399999999</v>
+      </c>
+      <c r="D984" s="2">
+        <v>46209</v>
+      </c>
+      <c r="E984" s="20">
+        <v>0.34375</v>
+      </c>
+      <c r="F984">
+        <v>0</v>
+      </c>
+      <c r="G984">
+        <v>0</v>
+      </c>
+      <c r="H984">
+        <v>0</v>
+      </c>
+      <c r="I984">
+        <v>111</v>
+      </c>
+      <c r="J984">
+        <v>0</v>
+      </c>
+      <c r="K984">
+        <v>0</v>
+      </c>
+      <c r="L984">
+        <v>167</v>
+      </c>
+      <c r="M984">
+        <v>0</v>
+      </c>
+      <c r="N984">
+        <v>167</v>
+      </c>
+      <c r="O984">
+        <v>56</v>
+      </c>
+      <c r="P984">
+        <v>500</v>
+      </c>
+      <c r="Q984" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="985" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A985" t="s">
+        <v>418</v>
+      </c>
+      <c r="B985">
+        <v>-35.352541899999999</v>
+      </c>
+      <c r="C985">
+        <v>137.3023116</v>
+      </c>
+      <c r="D985" s="2">
+        <v>46209</v>
+      </c>
+      <c r="E985" s="20">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="F985">
+        <v>0</v>
+      </c>
+      <c r="G985">
+        <v>111</v>
+      </c>
+      <c r="H985">
+        <v>0</v>
+      </c>
+      <c r="I985">
+        <v>111</v>
+      </c>
+      <c r="J985">
+        <v>0</v>
+      </c>
+      <c r="K985">
+        <v>111</v>
+      </c>
+      <c r="L985">
+        <v>1667</v>
+      </c>
+      <c r="M985">
+        <v>556</v>
+      </c>
+      <c r="N985">
+        <v>0</v>
+      </c>
+      <c r="O985">
+        <v>111</v>
+      </c>
+      <c r="P985">
+        <v>2667</v>
+      </c>
+      <c r="Q985" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="986" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A986" t="s">
+        <v>426</v>
+      </c>
+      <c r="B986">
+        <v>-35.410254000000002</v>
+      </c>
+      <c r="C986">
+        <v>138.32751999999999</v>
+      </c>
+      <c r="D986" s="2">
+        <v>46210</v>
+      </c>
+      <c r="E986" s="20">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="F986">
+        <v>0</v>
+      </c>
+      <c r="G986">
+        <v>0</v>
+      </c>
+      <c r="H986">
+        <v>0</v>
+      </c>
+      <c r="I986">
+        <v>278</v>
+      </c>
+      <c r="J986">
+        <v>0</v>
+      </c>
+      <c r="K986">
+        <v>0</v>
+      </c>
+      <c r="L986">
+        <v>111</v>
+      </c>
+      <c r="M986">
+        <v>0</v>
+      </c>
+      <c r="N986">
+        <v>722</v>
+      </c>
+      <c r="O986">
+        <v>56</v>
+      </c>
+      <c r="P986">
+        <v>1167</v>
+      </c>
+      <c r="Q986" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="987" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A987" t="s">
+        <v>453</v>
+      </c>
+      <c r="B987">
+        <v>-34.718809999999998</v>
+      </c>
+      <c r="C987">
+        <v>135.85857999999999</v>
+      </c>
+      <c r="D987" s="2">
+        <v>46211</v>
+      </c>
+      <c r="E987" s="20">
+        <v>0.40277777777777779</v>
+      </c>
+      <c r="I987">
+        <v>25</v>
+      </c>
+      <c r="J987">
+        <v>19</v>
+      </c>
+      <c r="L987">
+        <v>11</v>
+      </c>
+      <c r="O987">
+        <v>2</v>
+      </c>
+      <c r="P987">
+        <v>38</v>
+      </c>
+      <c r="Q987" t="s">
+        <v>283</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q974">
-    <sortCondition ref="D2:D974"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q987">
+    <sortCondition ref="D2:D987"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="S229">

--- a/MASTER spreadsheet of community summaries.xlsx
+++ b/MASTER spreadsheet of community summaries.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\peri\Dropbox\Delta\Projects\Laboratory\Algal blooms, bacterial counts  for community\For Luke's HAB data display\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{537F61FA-3B1A-4AA7-906F-CB8996409249}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC3DD23B-E590-4A62-9B1E-CC61DC406BAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{9286397E-2757-492B-865A-39B2D6A15FF6}"/>
   </bookViews>
@@ -25485,7 +25485,7 @@
         <v>56</v>
       </c>
       <c r="P660" s="17">
-        <f>SUM(F660:I660,K660:O660)</f>
+        <f t="shared" ref="P660:P666" si="0">SUM(F660:I660,K660:O660)</f>
         <v>1111</v>
       </c>
       <c r="Q660" t="s">
@@ -25518,7 +25518,7 @@
         <v>111</v>
       </c>
       <c r="P661">
-        <f>SUM(F661:I661,K661:O661)</f>
+        <f t="shared" si="0"/>
         <v>444</v>
       </c>
       <c r="Q661" t="s">
@@ -25551,7 +25551,7 @@
         <v>0</v>
       </c>
       <c r="P662">
-        <f>SUM(F662:I662,K662:O662)</f>
+        <f t="shared" si="0"/>
         <v>56</v>
       </c>
       <c r="Q662" t="s">
@@ -25584,7 +25584,7 @@
         <v>167</v>
       </c>
       <c r="P663">
-        <f>SUM(F663:I663,K663:O663)</f>
+        <f t="shared" si="0"/>
         <v>167</v>
       </c>
       <c r="Q663" t="s">
@@ -25617,7 +25617,7 @@
         <v>56</v>
       </c>
       <c r="P664">
-        <f>SUM(F664:I664,K664:O664)</f>
+        <f t="shared" si="0"/>
         <v>112</v>
       </c>
       <c r="Q664" t="s">
@@ -25650,7 +25650,7 @@
         <v>0</v>
       </c>
       <c r="P665">
-        <f>SUM(F665:I665,K665:O665)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Q665" t="s">
@@ -25683,7 +25683,7 @@
         <v>222</v>
       </c>
       <c r="P666">
-        <f>SUM(F666:I666,K666:O666)</f>
+        <f t="shared" si="0"/>
         <v>278</v>
       </c>
       <c r="Q666" t="s">
@@ -29776,7 +29776,7 @@
       <c r="N777" s="1"/>
       <c r="O777" s="1"/>
       <c r="P777">
-        <f>SUM(F777:I777,K777:O777)</f>
+        <f t="shared" ref="P777:P788" si="1">SUM(F777:I777,K777:O777)</f>
         <v>722</v>
       </c>
       <c r="Q777" t="s">
@@ -29809,7 +29809,7 @@
         <v>111</v>
       </c>
       <c r="P778">
-        <f>SUM(F778:I778,K778:O778)</f>
+        <f t="shared" si="1"/>
         <v>167</v>
       </c>
       <c r="Q778" t="s">
@@ -29842,7 +29842,7 @@
         <v>56</v>
       </c>
       <c r="P779">
-        <f>SUM(F779:I779,K779:O779)</f>
+        <f t="shared" si="1"/>
         <v>278</v>
       </c>
       <c r="Q779" t="s">
@@ -29875,7 +29875,7 @@
         <v>56</v>
       </c>
       <c r="P780">
-        <f>SUM(F780:I780,K780:O780)</f>
+        <f t="shared" si="1"/>
         <v>112</v>
       </c>
       <c r="Q780" t="s">
@@ -29908,7 +29908,7 @@
         <v>0</v>
       </c>
       <c r="P781">
-        <f>SUM(F781:I781,K781:O781)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Q781" t="s">
@@ -29941,7 +29941,7 @@
         <v>56</v>
       </c>
       <c r="P782">
-        <f>SUM(F782:I782,K782:O782)</f>
+        <f t="shared" si="1"/>
         <v>278</v>
       </c>
       <c r="Q782" t="s">
@@ -29974,7 +29974,7 @@
         <v>167</v>
       </c>
       <c r="P783">
-        <f>SUM(F783:I783,K783:O783)</f>
+        <f t="shared" si="1"/>
         <v>445</v>
       </c>
       <c r="Q783" t="s">
@@ -30007,7 +30007,7 @@
         <v>0</v>
       </c>
       <c r="P784">
-        <f>SUM(F784:I784,K784:O784)</f>
+        <f t="shared" si="1"/>
         <v>56</v>
       </c>
       <c r="Q784" t="s">
@@ -30040,7 +30040,7 @@
         <v>56</v>
       </c>
       <c r="P785">
-        <f>SUM(F785:I785,K785:O785)</f>
+        <f t="shared" si="1"/>
         <v>56</v>
       </c>
       <c r="Q785" t="s">
@@ -30073,7 +30073,7 @@
         <v>56</v>
       </c>
       <c r="P786">
-        <f>SUM(F786:I786,K786:O786)</f>
+        <f t="shared" si="1"/>
         <v>56</v>
       </c>
       <c r="Q786" t="s">
@@ -30106,7 +30106,7 @@
         <v>0</v>
       </c>
       <c r="P787">
-        <f>SUM(F787:I787,K787:O787)</f>
+        <f t="shared" si="1"/>
         <v>56</v>
       </c>
       <c r="Q787" t="s">
@@ -30139,7 +30139,7 @@
         <v>111</v>
       </c>
       <c r="P788">
-        <f>SUM(F788:I788,K788:O788)</f>
+        <f t="shared" si="1"/>
         <v>111</v>
       </c>
       <c r="Q788" t="s">
@@ -38319,10 +38319,10 @@
         <v>418</v>
       </c>
       <c r="B985">
-        <v>-35.352541899999999</v>
+        <v>-35.591330800000001</v>
       </c>
       <c r="C985">
-        <v>137.3023116</v>
+        <v>137.5061887</v>
       </c>
       <c r="D985" s="2">
         <v>46209</v>

--- a/MASTER spreadsheet of community summaries.xlsx
+++ b/MASTER spreadsheet of community summaries.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\peri\Dropbox\Delta\Projects\Laboratory\Algal blooms, bacterial counts  for community\For Luke's HAB data display\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC3DD23B-E590-4A62-9B1E-CC61DC406BAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0C7BB3F-F300-45C7-B969-63B890F9265F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{9286397E-2757-492B-865A-39B2D6A15FF6}"/>
   </bookViews>
   <sheets>
     <sheet name="Cells per mL" sheetId="1" r:id="rId1"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId2"/>
+  </externalReferences>
   <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -36,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1992" uniqueCount="466">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2036" uniqueCount="477">
   <si>
     <t>Date</t>
   </si>
@@ -1454,6 +1457,39 @@
   </si>
   <si>
     <t>Kingscote</t>
+  </si>
+  <si>
+    <t>Bluff Beach</t>
+  </si>
+  <si>
+    <t>Petrel Cove bluff side</t>
+  </si>
+  <si>
+    <t>Penneshaw</t>
+  </si>
+  <si>
+    <t>Edithburgh Boat Ramp</t>
+  </si>
+  <si>
+    <t>Edithburgh Tidal Pool</t>
+  </si>
+  <si>
+    <t>Fowlers Bay # 1 Beginning of Whale Nursery</t>
+  </si>
+  <si>
+    <t>Fowlers Bay # 2 Bottom of Bay</t>
+  </si>
+  <si>
+    <t>Fowlers Bay # 3 Windmills</t>
+  </si>
+  <si>
+    <t>Fowlers Bay # 4 Centre of Bay</t>
+  </si>
+  <si>
+    <t>Fowlers Bay # 5 Point Fowler</t>
+  </si>
+  <si>
+    <t>Fowlers Bay # 6 Pontoon</t>
   </si>
 </sst>
 </file>
@@ -1616,6 +1652,28 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Sheet1"/>
+      <sheetName val="Sheet1-1"/>
+      <sheetName val="Form Data"/>
+      <sheetName val="Sheet 1"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1935,7 +1993,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F307807-E5C9-4450-88E0-159CBB3E9A67}">
-  <dimension ref="A1:T987"/>
+  <dimension ref="A1:T1009"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="39.33203125" customWidth="1"/>
@@ -25485,7 +25543,7 @@
         <v>56</v>
       </c>
       <c r="P660" s="17">
-        <f t="shared" ref="P660:P666" si="0">SUM(F660:I660,K660:O660)</f>
+        <f>SUM(F660:I660,K660:O660)</f>
         <v>1111</v>
       </c>
       <c r="Q660" t="s">
@@ -25518,7 +25576,7 @@
         <v>111</v>
       </c>
       <c r="P661">
-        <f t="shared" si="0"/>
+        <f>SUM(F661:I661,K661:O661)</f>
         <v>444</v>
       </c>
       <c r="Q661" t="s">
@@ -25551,7 +25609,7 @@
         <v>0</v>
       </c>
       <c r="P662">
-        <f t="shared" si="0"/>
+        <f>SUM(F662:I662,K662:O662)</f>
         <v>56</v>
       </c>
       <c r="Q662" t="s">
@@ -25584,7 +25642,7 @@
         <v>167</v>
       </c>
       <c r="P663">
-        <f t="shared" si="0"/>
+        <f>SUM(F663:I663,K663:O663)</f>
         <v>167</v>
       </c>
       <c r="Q663" t="s">
@@ -25617,7 +25675,7 @@
         <v>56</v>
       </c>
       <c r="P664">
-        <f t="shared" si="0"/>
+        <f>SUM(F664:I664,K664:O664)</f>
         <v>112</v>
       </c>
       <c r="Q664" t="s">
@@ -25650,7 +25708,7 @@
         <v>0</v>
       </c>
       <c r="P665">
-        <f t="shared" si="0"/>
+        <f>SUM(F665:I665,K665:O665)</f>
         <v>0</v>
       </c>
       <c r="Q665" t="s">
@@ -25683,7 +25741,7 @@
         <v>222</v>
       </c>
       <c r="P666">
-        <f t="shared" si="0"/>
+        <f>SUM(F666:I666,K666:O666)</f>
         <v>278</v>
       </c>
       <c r="Q666" t="s">
@@ -29776,7 +29834,7 @@
       <c r="N777" s="1"/>
       <c r="O777" s="1"/>
       <c r="P777">
-        <f t="shared" ref="P777:P788" si="1">SUM(F777:I777,K777:O777)</f>
+        <f>SUM(F777:I777,K777:O777)</f>
         <v>722</v>
       </c>
       <c r="Q777" t="s">
@@ -29809,7 +29867,7 @@
         <v>111</v>
       </c>
       <c r="P778">
-        <f t="shared" si="1"/>
+        <f>SUM(F778:I778,K778:O778)</f>
         <v>167</v>
       </c>
       <c r="Q778" t="s">
@@ -29842,7 +29900,7 @@
         <v>56</v>
       </c>
       <c r="P779">
-        <f t="shared" si="1"/>
+        <f>SUM(F779:I779,K779:O779)</f>
         <v>278</v>
       </c>
       <c r="Q779" t="s">
@@ -29875,7 +29933,7 @@
         <v>56</v>
       </c>
       <c r="P780">
-        <f t="shared" si="1"/>
+        <f>SUM(F780:I780,K780:O780)</f>
         <v>112</v>
       </c>
       <c r="Q780" t="s">
@@ -29908,7 +29966,7 @@
         <v>0</v>
       </c>
       <c r="P781">
-        <f t="shared" si="1"/>
+        <f>SUM(F781:I781,K781:O781)</f>
         <v>0</v>
       </c>
       <c r="Q781" t="s">
@@ -29941,7 +29999,7 @@
         <v>56</v>
       </c>
       <c r="P782">
-        <f t="shared" si="1"/>
+        <f>SUM(F782:I782,K782:O782)</f>
         <v>278</v>
       </c>
       <c r="Q782" t="s">
@@ -29974,7 +30032,7 @@
         <v>167</v>
       </c>
       <c r="P783">
-        <f t="shared" si="1"/>
+        <f>SUM(F783:I783,K783:O783)</f>
         <v>445</v>
       </c>
       <c r="Q783" t="s">
@@ -30007,7 +30065,7 @@
         <v>0</v>
       </c>
       <c r="P784">
-        <f t="shared" si="1"/>
+        <f>SUM(F784:I784,K784:O784)</f>
         <v>56</v>
       </c>
       <c r="Q784" t="s">
@@ -30040,7 +30098,7 @@
         <v>56</v>
       </c>
       <c r="P785">
-        <f t="shared" si="1"/>
+        <f>SUM(F785:I785,K785:O785)</f>
         <v>56</v>
       </c>
       <c r="Q785" t="s">
@@ -30073,7 +30131,7 @@
         <v>56</v>
       </c>
       <c r="P786">
-        <f t="shared" si="1"/>
+        <f>SUM(F786:I786,K786:O786)</f>
         <v>56</v>
       </c>
       <c r="Q786" t="s">
@@ -30106,7 +30164,7 @@
         <v>0</v>
       </c>
       <c r="P787">
-        <f t="shared" si="1"/>
+        <f>SUM(F787:I787,K787:O787)</f>
         <v>56</v>
       </c>
       <c r="Q787" t="s">
@@ -30139,7 +30197,7 @@
         <v>111</v>
       </c>
       <c r="P788">
-        <f t="shared" si="1"/>
+        <f>SUM(F788:I788,K788:O788)</f>
         <v>111</v>
       </c>
       <c r="Q788" t="s">
@@ -35856,324 +35914,330 @@
     </row>
     <row r="928" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A928" t="s">
-        <v>311</v>
+        <v>369</v>
       </c>
       <c r="B928">
-        <v>-35.445059999999998</v>
+        <v>-34.934266999999998</v>
       </c>
       <c r="C928">
-        <v>138.30758399999999</v>
+        <v>137.35267999999999</v>
       </c>
       <c r="D928" s="2">
-        <v>46188</v>
+        <v>46187</v>
       </c>
       <c r="E928" s="20">
-        <v>0.375</v>
-      </c>
-      <c r="F928">
-        <v>0</v>
-      </c>
-      <c r="G928">
-        <v>0</v>
+        <v>0.60416666666666663</v>
       </c>
       <c r="H928">
-        <v>0</v>
+        <v>667</v>
       </c>
       <c r="I928">
-        <v>56</v>
+        <v>167</v>
       </c>
       <c r="J928">
         <v>0</v>
       </c>
-      <c r="K928">
-        <v>0</v>
-      </c>
       <c r="L928">
-        <v>56</v>
-      </c>
-      <c r="M928">
-        <v>0</v>
-      </c>
-      <c r="N928">
-        <v>0</v>
+        <v>889</v>
       </c>
       <c r="O928">
-        <v>111</v>
+        <v>222</v>
       </c>
       <c r="P928">
-        <v>223</v>
+        <v>1945</v>
       </c>
       <c r="Q928" t="s">
-        <v>401</v>
+        <v>218</v>
       </c>
     </row>
     <row r="929" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A929" t="s">
-        <v>289</v>
+        <v>311</v>
       </c>
       <c r="B929">
-        <v>-34.628509999999999</v>
+        <v>-35.445059999999998</v>
       </c>
       <c r="C929">
-        <v>135.86675</v>
+        <v>138.30758399999999</v>
       </c>
       <c r="D929" s="2">
-        <v>46189</v>
+        <v>46188</v>
       </c>
       <c r="E929" s="20">
-        <v>0.70833333333333337</v>
+        <v>0.375</v>
+      </c>
+      <c r="F929">
+        <v>0</v>
+      </c>
+      <c r="G929">
+        <v>0</v>
+      </c>
+      <c r="H929">
+        <v>0</v>
       </c>
       <c r="I929">
-        <v>131</v>
+        <v>56</v>
       </c>
       <c r="J929">
-        <v>121</v>
+        <v>0</v>
+      </c>
+      <c r="K929">
+        <v>0</v>
       </c>
       <c r="L929">
-        <v>2</v>
+        <v>56</v>
+      </c>
+      <c r="M929">
+        <v>0</v>
+      </c>
+      <c r="N929">
+        <v>0</v>
       </c>
       <c r="O929">
-        <v>2</v>
+        <v>111</v>
       </c>
       <c r="P929">
-        <v>135</v>
+        <v>223</v>
       </c>
       <c r="Q929" t="s">
-        <v>283</v>
+        <v>401</v>
       </c>
     </row>
     <row r="930" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A930" t="s">
-        <v>59</v>
+        <v>289</v>
       </c>
       <c r="B930">
-        <v>-35.084850000000003</v>
+        <v>-34.628509999999999</v>
       </c>
       <c r="C930">
-        <v>137.74889999999999</v>
+        <v>135.86675</v>
       </c>
       <c r="D930" s="2">
-        <v>46190</v>
+        <v>46189</v>
       </c>
       <c r="E930" s="20">
-        <v>0.58333333333333337</v>
-      </c>
-      <c r="G930">
-        <v>333</v>
-      </c>
-      <c r="H930">
-        <v>389</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="I930">
-        <v>277</v>
+        <v>131</v>
       </c>
       <c r="J930">
-        <v>0</v>
-      </c>
-      <c r="M930">
-        <v>0</v>
-      </c>
-      <c r="N930">
-        <v>556</v>
+        <v>121</v>
+      </c>
+      <c r="L930">
+        <v>2</v>
       </c>
       <c r="O930">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P930">
-        <v>1555</v>
+        <v>135</v>
       </c>
       <c r="Q930" t="s">
-        <v>149</v>
+        <v>283</v>
       </c>
     </row>
     <row r="931" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A931" t="s">
-        <v>289</v>
+        <v>59</v>
       </c>
       <c r="B931">
-        <v>-34.628509999999999</v>
+        <v>-35.084850000000003</v>
       </c>
       <c r="C931">
-        <v>135.86675</v>
+        <v>137.74889999999999</v>
       </c>
       <c r="D931" s="2">
         <v>46190</v>
       </c>
       <c r="E931" s="20">
-        <v>0.56944444444444442</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="G931">
+        <v>333</v>
+      </c>
+      <c r="H931">
+        <v>389</v>
       </c>
       <c r="I931">
-        <v>611</v>
+        <v>277</v>
       </c>
       <c r="J931">
-        <v>611</v>
-      </c>
-      <c r="L931">
-        <v>222</v>
+        <v>0</v>
+      </c>
+      <c r="M931">
+        <v>0</v>
+      </c>
+      <c r="N931">
+        <v>556</v>
       </c>
       <c r="O931">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="P931">
-        <v>889</v>
+        <v>1555</v>
       </c>
       <c r="Q931" t="s">
-        <v>283</v>
+        <v>149</v>
       </c>
     </row>
     <row r="932" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A932" t="s">
-        <v>454</v>
+        <v>289</v>
       </c>
       <c r="B932">
-        <v>-34.978150999999997</v>
+        <v>-34.628509999999999</v>
       </c>
       <c r="C932">
-        <v>138.50750400000001</v>
+        <v>135.86675</v>
       </c>
       <c r="D932" s="2">
         <v>46190</v>
       </c>
       <c r="E932" s="20">
-        <v>0.59236111111111112</v>
+        <v>0.56944444444444442</v>
       </c>
       <c r="I932">
-        <v>167</v>
+        <v>611</v>
       </c>
       <c r="J932">
-        <v>0</v>
+        <v>611</v>
       </c>
       <c r="L932">
-        <v>333</v>
-      </c>
-      <c r="N932">
-        <v>667</v>
+        <v>222</v>
       </c>
       <c r="O932">
-        <v>389</v>
+        <v>56</v>
       </c>
       <c r="P932">
-        <v>1556</v>
+        <v>889</v>
       </c>
       <c r="Q932" t="s">
-        <v>447</v>
+        <v>283</v>
       </c>
     </row>
     <row r="933" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A933" t="s">
-        <v>426</v>
+        <v>454</v>
       </c>
       <c r="B933">
-        <v>-35.410254000000002</v>
+        <v>-34.978150999999997</v>
       </c>
       <c r="C933">
-        <v>138.32751999999999</v>
+        <v>138.50750400000001</v>
       </c>
       <c r="D933" s="2">
         <v>46190</v>
       </c>
       <c r="E933" s="20">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="F933">
-        <v>0</v>
-      </c>
-      <c r="G933">
-        <v>0</v>
-      </c>
-      <c r="H933">
-        <v>0</v>
+        <v>0.59236111111111112</v>
       </c>
       <c r="I933">
-        <v>0</v>
+        <v>167</v>
       </c>
       <c r="J933">
         <v>0</v>
       </c>
-      <c r="K933">
-        <v>56</v>
-      </c>
       <c r="L933">
-        <v>56</v>
-      </c>
-      <c r="M933">
-        <v>0</v>
+        <v>333</v>
       </c>
       <c r="N933">
-        <v>833</v>
+        <v>667</v>
       </c>
       <c r="O933">
-        <v>111</v>
+        <v>389</v>
       </c>
       <c r="P933">
-        <v>1056</v>
+        <v>1556</v>
       </c>
       <c r="Q933" t="s">
-        <v>251</v>
+        <v>447</v>
       </c>
     </row>
     <row r="934" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A934" t="s">
-        <v>434</v>
+        <v>426</v>
       </c>
       <c r="B934">
-        <v>-34.540880000000001</v>
+        <v>-35.410254000000002</v>
       </c>
       <c r="C934">
-        <v>135.93384</v>
+        <v>138.32751999999999</v>
       </c>
       <c r="D934" s="2">
-        <v>46191</v>
+        <v>46190</v>
       </c>
       <c r="E934" s="20">
-        <v>0.44791666666666669</v>
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="F934">
+        <v>0</v>
+      </c>
+      <c r="G934">
+        <v>0</v>
+      </c>
+      <c r="H934">
+        <v>0</v>
       </c>
       <c r="I934">
-        <v>611</v>
+        <v>0</v>
       </c>
       <c r="J934">
-        <v>611</v>
+        <v>0</v>
+      </c>
+      <c r="K934">
+        <v>56</v>
       </c>
       <c r="L934">
-        <v>167</v>
+        <v>56</v>
+      </c>
+      <c r="M934">
+        <v>0</v>
+      </c>
+      <c r="N934">
+        <v>833</v>
       </c>
       <c r="O934">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="P934">
-        <v>890</v>
+        <v>1056</v>
       </c>
       <c r="Q934" t="s">
-        <v>283</v>
+        <v>251</v>
       </c>
     </row>
     <row r="935" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A935" t="s">
-        <v>289</v>
+        <v>434</v>
       </c>
       <c r="B935">
-        <v>-34.628509999999999</v>
+        <v>-34.540880000000001</v>
       </c>
       <c r="C935">
-        <v>135.86675</v>
+        <v>135.93384</v>
       </c>
       <c r="D935" s="2">
-        <v>46192</v>
+        <v>46191</v>
+      </c>
+      <c r="E935" s="20">
+        <v>0.44791666666666669</v>
       </c>
       <c r="I935">
-        <v>661</v>
+        <v>611</v>
       </c>
       <c r="J935">
-        <v>661</v>
+        <v>611</v>
       </c>
       <c r="L935">
-        <v>222</v>
+        <v>167</v>
       </c>
       <c r="O935">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="P935">
-        <v>883</v>
+        <v>890</v>
       </c>
       <c r="Q935" t="s">
         <v>283</v>
@@ -36181,34 +36245,31 @@
     </row>
     <row r="936" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A936" t="s">
-        <v>452</v>
+        <v>289</v>
       </c>
       <c r="B936">
-        <v>-34.759</v>
+        <v>-34.628509999999999</v>
       </c>
       <c r="C936">
-        <v>135.83886000000001</v>
+        <v>135.86675</v>
       </c>
       <c r="D936" s="2">
-        <v>46193</v>
-      </c>
-      <c r="E936" s="20">
-        <v>0.53125</v>
+        <v>46192</v>
       </c>
       <c r="I936">
-        <v>612</v>
+        <v>661</v>
       </c>
       <c r="J936">
-        <v>556</v>
+        <v>661</v>
       </c>
       <c r="L936">
-        <v>500</v>
+        <v>222</v>
       </c>
       <c r="O936">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="P936">
-        <v>1168</v>
+        <v>883</v>
       </c>
       <c r="Q936" t="s">
         <v>283</v>
@@ -36216,70 +36277,52 @@
     </row>
     <row r="937" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A937" t="s">
-        <v>359</v>
+        <v>452</v>
       </c>
       <c r="B937">
-        <v>-35.878667100000001</v>
+        <v>-34.759</v>
       </c>
       <c r="C937">
-        <v>137.6963188</v>
+        <v>135.83886000000001</v>
       </c>
       <c r="D937" s="2">
         <v>46193</v>
       </c>
-      <c r="F937">
-        <v>0</v>
-      </c>
-      <c r="G937">
-        <v>0</v>
-      </c>
-      <c r="H937">
-        <v>0</v>
+      <c r="E937" s="20">
+        <v>0.53125</v>
       </c>
       <c r="I937">
-        <v>0</v>
+        <v>612</v>
       </c>
       <c r="J937">
-        <v>0</v>
-      </c>
-      <c r="K937">
-        <v>0</v>
+        <v>556</v>
       </c>
       <c r="L937">
-        <v>0</v>
-      </c>
-      <c r="M937">
-        <v>0</v>
-      </c>
-      <c r="N937">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="O937">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="P937">
-        <v>0</v>
+        <v>1168</v>
       </c>
       <c r="Q937" t="s">
-        <v>151</v>
+        <v>283</v>
       </c>
     </row>
     <row r="938" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A938" t="s">
-        <v>456</v>
+        <v>359</v>
       </c>
       <c r="B938">
-        <v>-35.6614383</v>
+        <v>-35.878667100000001</v>
       </c>
       <c r="C938">
-        <v>137.6319307</v>
+        <v>137.6963188</v>
       </c>
       <c r="D938" s="2">
         <v>46193</v>
       </c>
-      <c r="E938" s="20">
-        <v>0.52083333333333337</v>
-      </c>
       <c r="F938">
         <v>0</v>
       </c>
@@ -36299,7 +36342,7 @@
         <v>0</v>
       </c>
       <c r="L938">
-        <v>333</v>
+        <v>0</v>
       </c>
       <c r="M938">
         <v>0</v>
@@ -36308,10 +36351,10 @@
         <v>0</v>
       </c>
       <c r="O938">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P938">
-        <v>334</v>
+        <v>0</v>
       </c>
       <c r="Q938" t="s">
         <v>151</v>
@@ -36319,81 +36362,96 @@
     </row>
     <row r="939" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A939" t="s">
-        <v>86</v>
+        <v>456</v>
       </c>
       <c r="B939">
-        <v>-35.540277000000003</v>
+        <v>-35.6614383</v>
       </c>
       <c r="C939">
-        <v>138.66416599999999</v>
+        <v>137.6319307</v>
       </c>
       <c r="D939" s="2">
-        <v>46194</v>
+        <v>46193</v>
       </c>
       <c r="E939" s="20">
-        <v>0.36041666666666666</v>
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="F939">
+        <v>0</v>
       </c>
       <c r="G939">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="H939">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="I939">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="J939">
+        <v>0</v>
+      </c>
+      <c r="K939">
         <v>0</v>
       </c>
       <c r="L939">
         <v>333</v>
       </c>
+      <c r="M939">
+        <v>0</v>
+      </c>
       <c r="N939">
-        <v>278</v>
+        <v>0</v>
       </c>
       <c r="O939">
-        <v>222</v>
+        <v>1</v>
       </c>
       <c r="P939">
-        <v>1001</v>
+        <v>334</v>
       </c>
       <c r="Q939" t="s">
-        <v>129</v>
+        <v>151</v>
       </c>
     </row>
     <row r="940" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A940" t="s">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="B940">
-        <v>-35.536745000000003</v>
+        <v>-35.540277000000003</v>
       </c>
       <c r="C940">
-        <v>138.6913744</v>
+        <v>138.66416599999999</v>
       </c>
       <c r="D940" s="2">
         <v>46194</v>
       </c>
       <c r="E940" s="20">
-        <v>0.36666666666666664</v>
+        <v>0.36041666666666666</v>
+      </c>
+      <c r="G940">
+        <v>56</v>
       </c>
       <c r="H940">
+        <v>56</v>
+      </c>
+      <c r="I940">
+        <v>56</v>
+      </c>
+      <c r="J940">
+        <v>0</v>
+      </c>
+      <c r="L940">
+        <v>333</v>
+      </c>
+      <c r="N940">
+        <v>278</v>
+      </c>
+      <c r="O940">
         <v>222</v>
       </c>
-      <c r="J940">
-        <v>0</v>
-      </c>
-      <c r="L940">
-        <v>222</v>
-      </c>
-      <c r="N940">
-        <v>500</v>
-      </c>
-      <c r="O940">
-        <v>834</v>
-      </c>
       <c r="P940">
-        <v>1778</v>
+        <v>1001</v>
       </c>
       <c r="Q940" t="s">
         <v>129</v>
@@ -36401,34 +36459,37 @@
     </row>
     <row r="941" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A941" t="s">
-        <v>451</v>
+        <v>100</v>
       </c>
       <c r="B941">
-        <v>-35.576688130000001</v>
+        <v>-35.536745000000003</v>
       </c>
       <c r="C941">
-        <v>138.64694589999999</v>
+        <v>138.6913744</v>
       </c>
       <c r="D941" s="2">
         <v>46194</v>
       </c>
-      <c r="I941">
-        <v>111</v>
+      <c r="E941" s="20">
+        <v>0.36666666666666664</v>
+      </c>
+      <c r="H941">
+        <v>222</v>
       </c>
       <c r="J941">
         <v>0</v>
       </c>
       <c r="L941">
-        <v>722</v>
+        <v>222</v>
       </c>
       <c r="N941">
-        <v>167</v>
+        <v>500</v>
       </c>
       <c r="O941">
-        <v>1666</v>
+        <v>834</v>
       </c>
       <c r="P941">
-        <v>2666</v>
+        <v>1778</v>
       </c>
       <c r="Q941" t="s">
         <v>129</v>
@@ -36436,34 +36497,34 @@
     </row>
     <row r="942" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A942" t="s">
-        <v>87</v>
+        <v>451</v>
       </c>
       <c r="B942">
-        <v>-35.573300000000003</v>
+        <v>-35.576688130000001</v>
       </c>
       <c r="C942">
-        <v>138.64250000000001</v>
+        <v>138.64694589999999</v>
       </c>
       <c r="D942" s="2">
         <v>46194</v>
       </c>
-      <c r="G942">
-        <v>56</v>
+      <c r="I942">
+        <v>111</v>
       </c>
       <c r="J942">
         <v>0</v>
       </c>
       <c r="L942">
-        <v>111</v>
+        <v>722</v>
       </c>
       <c r="N942">
-        <v>56</v>
+        <v>167</v>
       </c>
       <c r="O942">
-        <v>389</v>
+        <v>1666</v>
       </c>
       <c r="P942">
-        <v>612</v>
+        <v>2666</v>
       </c>
       <c r="Q942" t="s">
         <v>129</v>
@@ -36471,37 +36532,34 @@
     </row>
     <row r="943" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A943" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B943">
-        <v>-35.581124000000003</v>
+        <v>-35.573300000000003</v>
       </c>
       <c r="C943">
-        <v>138.60879700000001</v>
+        <v>138.64250000000001</v>
       </c>
       <c r="D943" s="2">
         <v>46194</v>
       </c>
-      <c r="F943">
-        <v>56</v>
-      </c>
       <c r="G943">
-        <v>167</v>
+        <v>56</v>
       </c>
       <c r="J943">
         <v>0</v>
       </c>
       <c r="L943">
-        <v>222</v>
+        <v>111</v>
       </c>
       <c r="N943">
-        <v>278</v>
+        <v>56</v>
       </c>
       <c r="O943">
         <v>389</v>
       </c>
       <c r="P943">
-        <v>1112</v>
+        <v>612</v>
       </c>
       <c r="Q943" t="s">
         <v>129</v>
@@ -36509,40 +36567,37 @@
     </row>
     <row r="944" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A944" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B944">
-        <v>-35.6048446</v>
+        <v>-35.581124000000003</v>
       </c>
       <c r="C944">
-        <v>138.59278499999999</v>
+        <v>138.60879700000001</v>
       </c>
       <c r="D944" s="2">
         <v>46194</v>
       </c>
+      <c r="F944">
+        <v>56</v>
+      </c>
       <c r="G944">
-        <v>111</v>
-      </c>
-      <c r="H944">
         <v>167</v>
       </c>
-      <c r="I944">
-        <v>167</v>
-      </c>
       <c r="J944">
         <v>0</v>
       </c>
       <c r="L944">
-        <v>56</v>
+        <v>222</v>
       </c>
       <c r="N944">
-        <v>778</v>
+        <v>278</v>
       </c>
       <c r="O944">
-        <v>667</v>
+        <v>389</v>
       </c>
       <c r="P944">
-        <v>1946</v>
+        <v>1112</v>
       </c>
       <c r="Q944" t="s">
         <v>129</v>
@@ -36550,34 +36605,40 @@
     </row>
     <row r="945" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A945" t="s">
-        <v>374</v>
+        <v>89</v>
       </c>
       <c r="B945">
-        <v>-35.612285999999997</v>
+        <v>-35.6048446</v>
       </c>
       <c r="C945">
-        <v>138.564302</v>
+        <v>138.59278499999999</v>
       </c>
       <c r="D945" s="2">
         <v>46194</v>
       </c>
+      <c r="G945">
+        <v>111</v>
+      </c>
       <c r="H945">
-        <v>111</v>
+        <v>167</v>
       </c>
       <c r="I945">
-        <v>111</v>
+        <v>167</v>
       </c>
       <c r="J945">
         <v>0</v>
       </c>
+      <c r="L945">
+        <v>56</v>
+      </c>
       <c r="N945">
-        <v>444</v>
+        <v>778</v>
       </c>
       <c r="O945">
-        <v>167</v>
+        <v>667</v>
       </c>
       <c r="P945">
-        <v>833</v>
+        <v>1946</v>
       </c>
       <c r="Q945" t="s">
         <v>129</v>
@@ -36585,34 +36646,34 @@
     </row>
     <row r="946" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A946" t="s">
-        <v>431</v>
+        <v>374</v>
       </c>
       <c r="B946">
-        <v>-35.619</v>
+        <v>-35.612285999999997</v>
       </c>
       <c r="C946">
-        <v>138.58099999999999</v>
+        <v>138.564302</v>
       </c>
       <c r="D946" s="2">
         <v>46194</v>
       </c>
-      <c r="G946">
-        <v>56</v>
-      </c>
       <c r="H946">
         <v>111</v>
       </c>
+      <c r="I946">
+        <v>111</v>
+      </c>
       <c r="J946">
         <v>0</v>
       </c>
       <c r="N946">
-        <v>1056</v>
+        <v>444</v>
       </c>
       <c r="O946">
-        <v>56</v>
+        <v>167</v>
       </c>
       <c r="P946">
-        <v>1279</v>
+        <v>833</v>
       </c>
       <c r="Q946" t="s">
         <v>129</v>
@@ -36620,69 +36681,72 @@
     </row>
     <row r="947" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A947" t="s">
-        <v>455</v>
+        <v>431</v>
       </c>
       <c r="B947">
-        <v>-35.576250000000002</v>
+        <v>-35.619</v>
       </c>
       <c r="C947">
-        <v>138.64349999999999</v>
+        <v>138.58099999999999</v>
       </c>
       <c r="D947" s="2">
         <v>46194</v>
       </c>
-      <c r="E947" s="20">
-        <v>0.38541666666666669</v>
-      </c>
-      <c r="I947">
-        <v>56</v>
+      <c r="G947">
+        <v>56</v>
+      </c>
+      <c r="H947">
+        <v>111</v>
       </c>
       <c r="J947">
         <v>0</v>
       </c>
-      <c r="L947">
-        <v>1333</v>
-      </c>
       <c r="N947">
-        <v>56</v>
+        <v>1056</v>
       </c>
       <c r="O947">
-        <v>167</v>
+        <v>56</v>
       </c>
       <c r="P947">
-        <v>1612</v>
+        <v>1279</v>
       </c>
       <c r="Q947" t="s">
-        <v>447</v>
+        <v>129</v>
       </c>
     </row>
     <row r="948" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A948" t="s">
-        <v>88</v>
+        <v>455</v>
       </c>
       <c r="B948">
-        <v>-35.581982000000004</v>
+        <v>-35.576250000000002</v>
       </c>
       <c r="C948">
-        <v>138.60827699999999</v>
+        <v>138.64349999999999</v>
       </c>
       <c r="D948" s="2">
         <v>46194</v>
       </c>
       <c r="E948" s="20">
-        <v>9</v>
+        <v>0.38541666666666669</v>
+      </c>
+      <c r="I948">
+        <v>56</v>
       </c>
       <c r="J948">
         <v>0</v>
       </c>
+      <c r="L948">
+        <v>1333</v>
+      </c>
       <c r="N948">
-        <v>1611</v>
+        <v>56</v>
       </c>
       <c r="O948">
-        <v>222</v>
+        <v>167</v>
       </c>
       <c r="P948">
-        <v>1833</v>
+        <v>1612</v>
       </c>
       <c r="Q948" t="s">
         <v>447</v>
@@ -36690,84 +36754,63 @@
     </row>
     <row r="949" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A949" t="s">
-        <v>400</v>
+        <v>88</v>
       </c>
       <c r="B949">
-        <v>-35.510497000000001</v>
+        <v>-35.581982000000004</v>
       </c>
       <c r="C949">
-        <v>138.21676299999999</v>
+        <v>138.60827699999999</v>
       </c>
       <c r="D949" s="2">
         <v>46194</v>
       </c>
       <c r="E949" s="20">
-        <v>0.58333333333333337</v>
-      </c>
-      <c r="F949">
-        <v>167</v>
-      </c>
-      <c r="G949">
-        <v>0</v>
-      </c>
-      <c r="H949">
+        <v>9</v>
+      </c>
+      <c r="J949">
+        <v>0</v>
+      </c>
+      <c r="N949">
+        <v>1611</v>
+      </c>
+      <c r="O949">
         <v>222</v>
       </c>
-      <c r="I949">
-        <v>278</v>
-      </c>
-      <c r="J949">
-        <v>0</v>
-      </c>
-      <c r="K949">
-        <v>0</v>
-      </c>
-      <c r="L949">
-        <v>167</v>
-      </c>
-      <c r="M949">
-        <v>0</v>
-      </c>
-      <c r="N949">
-        <v>833</v>
-      </c>
-      <c r="O949">
-        <v>333</v>
-      </c>
       <c r="P949">
-        <v>2000</v>
+        <v>1833</v>
       </c>
       <c r="Q949" t="s">
-        <v>251</v>
+        <v>447</v>
       </c>
     </row>
     <row r="950" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A950" t="s">
-        <v>311</v>
+        <v>400</v>
       </c>
       <c r="B950">
-        <v>-35.445059999999998</v>
+        <v>-35.510497000000001</v>
       </c>
       <c r="C950">
-        <v>138.30758399999999</v>
+        <v>138.21676299999999</v>
       </c>
       <c r="D950" s="2">
-        <v>46195</v>
+        <v>46194</v>
       </c>
       <c r="E950" s="20">
-        <v>0.39583333333333331</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="F950">
-        <v>0</v>
+        <v>167</v>
       </c>
       <c r="G950">
         <v>0</v>
       </c>
       <c r="H950">
-        <v>0</v>
+        <v>222</v>
       </c>
       <c r="I950">
-        <v>56</v>
+        <v>278</v>
       </c>
       <c r="J950">
         <v>0</v>
@@ -36776,39 +36819,39 @@
         <v>0</v>
       </c>
       <c r="L950">
-        <v>0</v>
+        <v>167</v>
       </c>
       <c r="M950">
         <v>0</v>
       </c>
       <c r="N950">
-        <v>611</v>
+        <v>833</v>
       </c>
       <c r="O950">
-        <v>56</v>
+        <v>333</v>
       </c>
       <c r="P950">
-        <v>723</v>
+        <v>2000</v>
       </c>
       <c r="Q950" t="s">
-        <v>401</v>
+        <v>251</v>
       </c>
     </row>
     <row r="951" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A951" t="s">
-        <v>395</v>
+        <v>311</v>
       </c>
       <c r="B951">
-        <v>-35.793973000000001</v>
+        <v>-35.445059999999998</v>
       </c>
       <c r="C951">
-        <v>137.852418</v>
+        <v>138.30758399999999</v>
       </c>
       <c r="D951" s="2">
         <v>46195</v>
       </c>
       <c r="E951" s="20">
-        <v>0.58333333333333337</v>
+        <v>0.39583333333333331</v>
       </c>
       <c r="F951">
         <v>0</v>
@@ -36820,7 +36863,7 @@
         <v>0</v>
       </c>
       <c r="I951">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="J951">
         <v>0</v>
@@ -36835,33 +36878,33 @@
         <v>0</v>
       </c>
       <c r="N951">
-        <v>0</v>
+        <v>611</v>
       </c>
       <c r="O951">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="P951">
-        <v>0</v>
+        <v>723</v>
       </c>
       <c r="Q951" t="s">
-        <v>151</v>
+        <v>401</v>
       </c>
     </row>
     <row r="952" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A952" t="s">
-        <v>256</v>
+        <v>395</v>
       </c>
       <c r="B952">
-        <v>-35.7987082</v>
+        <v>-35.793973000000001</v>
       </c>
       <c r="C952">
-        <v>137.81647699999999</v>
+        <v>137.852418</v>
       </c>
       <c r="D952" s="2">
         <v>46195</v>
       </c>
       <c r="E952" s="20">
-        <v>0.60416666666666663</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="F952">
         <v>0</v>
@@ -36902,66 +36945,87 @@
     </row>
     <row r="953" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A953" t="s">
-        <v>434</v>
+        <v>256</v>
       </c>
       <c r="B953">
-        <v>-34.540880000000001</v>
+        <v>-35.7987082</v>
       </c>
       <c r="C953">
-        <v>135.93384</v>
+        <v>137.81647699999999</v>
       </c>
       <c r="D953" s="2">
-        <v>46196</v>
+        <v>46195</v>
       </c>
       <c r="E953" s="20">
-        <v>0.35416666666666669</v>
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="F953">
+        <v>0</v>
+      </c>
+      <c r="G953">
+        <v>0</v>
+      </c>
+      <c r="H953">
+        <v>0</v>
       </c>
       <c r="I953">
-        <v>1111</v>
+        <v>0</v>
       </c>
       <c r="J953">
-        <v>1111</v>
+        <v>0</v>
+      </c>
+      <c r="K953">
+        <v>0</v>
       </c>
       <c r="L953">
-        <v>611</v>
+        <v>0</v>
+      </c>
+      <c r="M953">
+        <v>0</v>
+      </c>
+      <c r="N953">
+        <v>0</v>
       </c>
       <c r="O953">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="P953">
-        <v>1778</v>
+        <v>0</v>
       </c>
       <c r="Q953" t="s">
-        <v>283</v>
+        <v>151</v>
       </c>
     </row>
     <row r="954" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A954" t="s">
-        <v>453</v>
+        <v>434</v>
       </c>
       <c r="B954">
-        <v>-34.718809999999998</v>
+        <v>-34.540880000000001</v>
       </c>
       <c r="C954">
-        <v>135.85857999999999</v>
+        <v>135.93384</v>
       </c>
       <c r="D954" s="2">
         <v>46196</v>
       </c>
       <c r="E954" s="20">
-        <v>46197.375</v>
+        <v>0.35416666666666669</v>
       </c>
       <c r="I954">
-        <v>1167</v>
+        <v>1111</v>
       </c>
       <c r="J954">
         <v>1111</v>
       </c>
+      <c r="L954">
+        <v>611</v>
+      </c>
       <c r="O954">
         <v>56</v>
       </c>
       <c r="P954">
-        <v>1223</v>
+        <v>1778</v>
       </c>
       <c r="Q954" t="s">
         <v>283</v>
@@ -36969,75 +37033,66 @@
     </row>
     <row r="955" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A955" t="s">
-        <v>79</v>
+        <v>453</v>
       </c>
       <c r="B955">
-        <v>-34.804662999999998</v>
+        <v>-34.718809999999998</v>
       </c>
       <c r="C955">
-        <v>138.540223</v>
+        <v>135.85857999999999</v>
       </c>
       <c r="D955" s="2">
         <v>46196</v>
       </c>
       <c r="E955" s="20">
-        <v>0.58333333333333337</v>
+        <v>46197.375</v>
       </c>
       <c r="I955">
-        <v>2.7749999999999999</v>
+        <v>1167</v>
       </c>
       <c r="J955">
-        <v>0</v>
-      </c>
-      <c r="L955">
-        <v>6.2249999999999996</v>
+        <v>1111</v>
       </c>
       <c r="O955">
-        <v>1.65</v>
+        <v>56</v>
       </c>
       <c r="P955">
-        <v>10.65</v>
+        <v>1223</v>
       </c>
       <c r="Q955" t="s">
-        <v>78</v>
+        <v>283</v>
       </c>
     </row>
     <row r="956" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A956" t="s">
-        <v>267</v>
+        <v>79</v>
       </c>
       <c r="B956">
-        <v>-34.824044999999998</v>
+        <v>-34.804662999999998</v>
       </c>
       <c r="C956">
-        <v>138.48377600000001</v>
+        <v>138.540223</v>
       </c>
       <c r="D956" s="2">
         <v>46196</v>
       </c>
       <c r="E956" s="20">
-        <v>0.55694444444444446</v>
-      </c>
-      <c r="G956">
-        <v>0.15</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="I956">
-        <v>6.2</v>
+        <v>2.7749999999999999</v>
       </c>
       <c r="J956">
         <v>0</v>
       </c>
       <c r="L956">
-        <v>9</v>
-      </c>
-      <c r="N956">
-        <v>0.2</v>
+        <v>6.2249999999999996</v>
       </c>
       <c r="O956">
-        <v>0.35</v>
+        <v>1.65</v>
       </c>
       <c r="P956">
-        <v>15.9</v>
+        <v>10.65</v>
       </c>
       <c r="Q956" t="s">
         <v>78</v>
@@ -37045,40 +37100,40 @@
     </row>
     <row r="957" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A957" t="s">
-        <v>348</v>
+        <v>267</v>
       </c>
       <c r="B957">
-        <v>-34.860666999999999</v>
+        <v>-34.824044999999998</v>
       </c>
       <c r="C957">
-        <v>138.490938</v>
+        <v>138.48377600000001</v>
       </c>
       <c r="D957" s="2">
         <v>46196</v>
       </c>
       <c r="E957" s="20">
-        <v>4.8611111111111112E-2</v>
+        <v>0.55694444444444446</v>
       </c>
       <c r="G957">
-        <v>0.1</v>
-      </c>
-      <c r="H957">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="I957">
-        <v>54.7</v>
+        <v>6.2</v>
       </c>
       <c r="J957">
         <v>0</v>
       </c>
       <c r="L957">
-        <v>2.2999999999999998</v>
+        <v>9</v>
+      </c>
+      <c r="N957">
+        <v>0.2</v>
       </c>
       <c r="O957">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="P957">
-        <v>57.5</v>
+        <v>15.9</v>
       </c>
       <c r="Q957" t="s">
         <v>78</v>
@@ -37086,110 +37141,98 @@
     </row>
     <row r="958" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A958" t="s">
-        <v>422</v>
+        <v>348</v>
       </c>
       <c r="B958">
-        <v>-34.978150999999997</v>
+        <v>-34.860666999999999</v>
       </c>
       <c r="C958">
-        <v>138.50750400000001</v>
+        <v>138.490938</v>
       </c>
       <c r="D958" s="2">
         <v>46196</v>
       </c>
       <c r="E958" s="20">
-        <v>0.59375</v>
+        <v>4.8611111111111112E-2</v>
+      </c>
+      <c r="G958">
+        <v>0.1</v>
+      </c>
+      <c r="H958">
+        <v>0.1</v>
       </c>
       <c r="I958">
-        <v>111</v>
+        <v>54.7</v>
       </c>
       <c r="J958">
         <v>0</v>
       </c>
       <c r="L958">
-        <v>222</v>
-      </c>
-      <c r="N958">
-        <v>222</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="O958">
-        <v>667</v>
+        <v>0.3</v>
       </c>
       <c r="P958">
-        <v>1222</v>
+        <v>57.5</v>
       </c>
       <c r="Q958" t="s">
-        <v>447</v>
+        <v>78</v>
       </c>
     </row>
     <row r="959" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A959" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B959">
-        <v>-35.500024000000003</v>
+        <v>-34.978150999999997</v>
       </c>
       <c r="C959">
-        <v>138.24287699999999</v>
+        <v>138.50750400000001</v>
       </c>
       <c r="D959" s="2">
         <v>46196</v>
       </c>
       <c r="E959" s="20">
-        <v>0.38541666666666669</v>
-      </c>
-      <c r="F959">
-        <v>0</v>
-      </c>
-      <c r="G959">
-        <v>0</v>
-      </c>
-      <c r="H959">
-        <v>0</v>
+        <v>0.59375</v>
       </c>
       <c r="I959">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="J959">
         <v>0</v>
       </c>
-      <c r="K959">
-        <v>0</v>
-      </c>
       <c r="L959">
-        <v>0</v>
-      </c>
-      <c r="M959">
-        <v>0</v>
+        <v>222</v>
       </c>
       <c r="N959">
-        <v>111</v>
+        <v>222</v>
       </c>
       <c r="O959">
-        <v>0</v>
+        <v>667</v>
       </c>
       <c r="P959">
-        <v>111</v>
+        <v>1222</v>
       </c>
       <c r="Q959" t="s">
-        <v>251</v>
+        <v>447</v>
       </c>
     </row>
     <row r="960" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A960" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="B960">
-        <v>-35.591330800000001</v>
+        <v>-35.500024000000003</v>
       </c>
       <c r="C960">
-        <v>137.5061887</v>
+        <v>138.24287699999999</v>
       </c>
       <c r="D960" s="2">
         <v>46196</v>
       </c>
       <c r="E960" s="20">
-        <v>0.45833333333333331</v>
+        <v>0.38541666666666669</v>
       </c>
       <c r="F960">
         <v>0</v>
@@ -37216,33 +37259,33 @@
         <v>0</v>
       </c>
       <c r="N960">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="O960">
         <v>0</v>
       </c>
       <c r="P960">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="Q960" t="s">
-        <v>151</v>
+        <v>251</v>
       </c>
     </row>
     <row r="961" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A961" t="s">
-        <v>457</v>
+        <v>418</v>
       </c>
       <c r="B961">
-        <v>-35.595789000000003</v>
+        <v>-35.591330800000001</v>
       </c>
       <c r="C961">
-        <v>137.51194899999999</v>
+        <v>137.5061887</v>
       </c>
       <c r="D961" s="2">
         <v>46196</v>
       </c>
       <c r="E961" s="20">
-        <v>0.47916666666666669</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="F961">
         <v>0</v>
@@ -37266,7 +37309,7 @@
         <v>0</v>
       </c>
       <c r="M961">
-        <v>222</v>
+        <v>0</v>
       </c>
       <c r="N961">
         <v>0</v>
@@ -37275,7 +37318,7 @@
         <v>0</v>
       </c>
       <c r="P961">
-        <v>222</v>
+        <v>0</v>
       </c>
       <c r="Q961" t="s">
         <v>151</v>
@@ -37283,19 +37326,22 @@
     </row>
     <row r="962" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A962" t="s">
-        <v>59</v>
+        <v>457</v>
       </c>
       <c r="B962">
-        <v>-35.084850000000003</v>
+        <v>-35.595789000000003</v>
       </c>
       <c r="C962">
-        <v>137.74889999999999</v>
+        <v>137.51194899999999</v>
       </c>
       <c r="D962" s="2">
         <v>46196</v>
       </c>
       <c r="E962" s="20">
-        <v>0.58333333333333337</v>
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="F962">
+        <v>0</v>
       </c>
       <c r="G962">
         <v>0</v>
@@ -37309,43 +37355,43 @@
       <c r="J962">
         <v>0</v>
       </c>
+      <c r="K962">
+        <v>0</v>
+      </c>
       <c r="L962">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="M962">
-        <v>0</v>
+        <v>222</v>
       </c>
       <c r="N962">
-        <v>333</v>
+        <v>0</v>
       </c>
       <c r="O962">
         <v>0</v>
       </c>
       <c r="P962">
-        <v>444</v>
+        <v>222</v>
       </c>
       <c r="Q962" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="963" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A963" t="s">
-        <v>450</v>
+        <v>59</v>
       </c>
       <c r="B963">
-        <v>-35.595986000000003</v>
+        <v>-35.084850000000003</v>
       </c>
       <c r="C963">
-        <v>138.104072</v>
+        <v>137.74889999999999</v>
       </c>
       <c r="D963" s="2">
-        <v>46197</v>
+        <v>46196</v>
       </c>
       <c r="E963" s="20">
-        <v>0.54166666666666663</v>
-      </c>
-      <c r="F963">
-        <v>0</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="G963">
         <v>0</v>
@@ -37359,272 +37405,254 @@
       <c r="J963">
         <v>0</v>
       </c>
-      <c r="K963">
-        <v>0</v>
-      </c>
       <c r="L963">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="M963">
         <v>0</v>
       </c>
       <c r="N963">
-        <v>833</v>
+        <v>333</v>
       </c>
       <c r="O963">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="P963">
-        <v>889</v>
+        <v>444</v>
       </c>
       <c r="Q963" t="s">
-        <v>251</v>
+        <v>149</v>
       </c>
     </row>
     <row r="964" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A964" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="B964">
-        <v>-35.410254000000002</v>
+        <v>-34.978150999999997</v>
       </c>
       <c r="C964">
-        <v>138.32751999999999</v>
+        <v>138.50750400000001</v>
       </c>
       <c r="D964" s="2">
-        <v>46197</v>
+        <v>46196</v>
       </c>
       <c r="E964" s="20">
-        <v>0.3125</v>
-      </c>
-      <c r="F964">
-        <v>0</v>
-      </c>
-      <c r="G964">
-        <v>167</v>
-      </c>
-      <c r="H964">
-        <v>56</v>
+        <v>0.59375</v>
       </c>
       <c r="I964">
-        <v>500</v>
+        <v>111</v>
       </c>
       <c r="J964">
         <v>0</v>
       </c>
-      <c r="K964">
-        <v>0</v>
-      </c>
       <c r="L964">
-        <v>56</v>
-      </c>
-      <c r="M964">
-        <v>0</v>
+        <v>222</v>
       </c>
       <c r="N964">
-        <v>389</v>
+        <v>222</v>
       </c>
       <c r="O964">
-        <v>111</v>
+        <v>667</v>
       </c>
       <c r="P964">
-        <v>1279</v>
+        <v>1222</v>
       </c>
       <c r="Q964" t="s">
-        <v>251</v>
+        <v>447</v>
       </c>
     </row>
     <row r="965" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A965" t="s">
-        <v>94</v>
+        <v>450</v>
       </c>
       <c r="B965">
-        <v>-35.58858</v>
+        <v>-35.595986000000003</v>
       </c>
       <c r="C965">
-        <v>138.60474600000001</v>
+        <v>138.104072</v>
       </c>
       <c r="D965" s="2">
-        <v>46201</v>
+        <v>46197</v>
+      </c>
+      <c r="E965" s="20">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="F965">
+        <v>0</v>
+      </c>
+      <c r="G965">
+        <v>0</v>
+      </c>
+      <c r="H965">
+        <v>0</v>
+      </c>
+      <c r="I965">
+        <v>0</v>
       </c>
       <c r="J965">
         <v>0</v>
       </c>
+      <c r="K965">
+        <v>0</v>
+      </c>
       <c r="L965">
-        <v>500</v>
+        <v>0</v>
+      </c>
+      <c r="M965">
+        <v>0</v>
       </c>
       <c r="N965">
-        <v>56</v>
+        <v>833</v>
       </c>
       <c r="O965">
-        <v>278</v>
+        <v>56</v>
       </c>
       <c r="P965">
-        <v>834</v>
+        <v>889</v>
       </c>
       <c r="Q965" t="s">
-        <v>129</v>
+        <v>251</v>
       </c>
     </row>
     <row r="966" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A966" t="s">
-        <v>89</v>
+        <v>426</v>
       </c>
       <c r="B966">
-        <v>-35.6048446</v>
+        <v>-35.410254000000002</v>
       </c>
       <c r="C966">
-        <v>138.59278499999999</v>
+        <v>138.32751999999999</v>
       </c>
       <c r="D966" s="2">
-        <v>46201</v>
+        <v>46197</v>
+      </c>
+      <c r="E966" s="20">
+        <v>0.3125</v>
+      </c>
+      <c r="F966">
+        <v>0</v>
       </c>
       <c r="G966">
-        <v>56</v>
+        <v>167</v>
       </c>
       <c r="H966">
         <v>56</v>
       </c>
+      <c r="I966">
+        <v>500</v>
+      </c>
       <c r="J966">
         <v>0</v>
       </c>
+      <c r="K966">
+        <v>0</v>
+      </c>
+      <c r="L966">
+        <v>56</v>
+      </c>
+      <c r="M966">
+        <v>0</v>
+      </c>
       <c r="N966">
-        <v>278</v>
+        <v>389</v>
       </c>
       <c r="O966">
-        <v>167</v>
+        <v>111</v>
       </c>
       <c r="P966">
-        <v>557</v>
+        <v>1279</v>
       </c>
       <c r="Q966" t="s">
-        <v>129</v>
+        <v>251</v>
       </c>
     </row>
     <row r="967" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A967" t="s">
-        <v>436</v>
+        <v>94</v>
       </c>
       <c r="B967">
-        <v>-35.521467000000001</v>
+        <v>-35.58858</v>
       </c>
       <c r="C967">
-        <v>138.18532999999999</v>
+        <v>138.60474600000001</v>
       </c>
       <c r="D967" s="2">
         <v>46201</v>
       </c>
-      <c r="E967" s="20">
-        <v>0.52430555555555558</v>
-      </c>
-      <c r="F967">
-        <v>0</v>
-      </c>
-      <c r="G967">
-        <v>0</v>
-      </c>
-      <c r="H967">
-        <v>0</v>
-      </c>
-      <c r="I967">
-        <v>0</v>
-      </c>
       <c r="J967">
         <v>0</v>
       </c>
-      <c r="K967">
-        <v>0</v>
-      </c>
       <c r="L967">
-        <v>56</v>
-      </c>
-      <c r="M967">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="N967">
-        <v>1167</v>
+        <v>56</v>
       </c>
       <c r="O967">
-        <v>0</v>
+        <v>278</v>
       </c>
       <c r="P967">
-        <v>1223</v>
+        <v>834</v>
       </c>
       <c r="Q967" t="s">
-        <v>251</v>
+        <v>129</v>
       </c>
     </row>
     <row r="968" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A968" t="s">
-        <v>421</v>
+        <v>89</v>
       </c>
       <c r="B968">
-        <v>-35.500024000000003</v>
+        <v>-35.6048446</v>
       </c>
       <c r="C968">
-        <v>138.24287699999999</v>
+        <v>138.59278499999999</v>
       </c>
       <c r="D968" s="2">
         <v>46201</v>
       </c>
-      <c r="E968" s="20">
-        <v>0.67708333333333337</v>
-      </c>
-      <c r="F968">
-        <v>0</v>
-      </c>
       <c r="G968">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="H968">
-        <v>0</v>
-      </c>
-      <c r="I968">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="J968">
         <v>0</v>
       </c>
-      <c r="K968">
-        <v>0</v>
-      </c>
-      <c r="L968">
-        <v>0</v>
-      </c>
-      <c r="M968">
-        <v>0</v>
-      </c>
       <c r="N968">
-        <v>56</v>
+        <v>278</v>
       </c>
       <c r="O968">
-        <v>56</v>
+        <v>167</v>
       </c>
       <c r="P968">
-        <v>112</v>
+        <v>557</v>
       </c>
       <c r="Q968" t="s">
-        <v>401</v>
+        <v>129</v>
       </c>
     </row>
     <row r="969" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A969" t="s">
-        <v>459</v>
+        <v>436</v>
       </c>
       <c r="B969">
-        <v>-35.788674999999998</v>
+        <v>-35.521467000000001</v>
       </c>
       <c r="C969">
-        <v>138.070415</v>
+        <v>138.18532999999999</v>
       </c>
       <c r="D969" s="2">
-        <v>46202</v>
+        <v>46201</v>
       </c>
       <c r="E969" s="20">
-        <v>0.58333333333333337</v>
+        <v>0.52430555555555558</v>
       </c>
       <c r="F969">
-        <v>158333</v>
+        <v>0</v>
       </c>
       <c r="G969">
         <v>0</v>
@@ -37633,7 +37661,7 @@
         <v>0</v>
       </c>
       <c r="I969">
-        <v>7333</v>
+        <v>0</v>
       </c>
       <c r="J969">
         <v>0</v>
@@ -37642,42 +37670,42 @@
         <v>0</v>
       </c>
       <c r="L969">
-        <v>17500</v>
+        <v>56</v>
       </c>
       <c r="M969">
-        <v>4667</v>
+        <v>0</v>
       </c>
       <c r="N969">
-        <v>0</v>
+        <v>1167</v>
       </c>
       <c r="O969">
         <v>0</v>
       </c>
       <c r="P969">
-        <v>187833</v>
+        <v>1223</v>
       </c>
       <c r="Q969" t="s">
-        <v>151</v>
+        <v>251</v>
       </c>
     </row>
     <row r="970" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A970" t="s">
-        <v>460</v>
+        <v>421</v>
       </c>
       <c r="B970">
-        <v>-35.787862699999998</v>
+        <v>-35.500024000000003</v>
       </c>
       <c r="C970">
-        <v>138.07130670000001</v>
+        <v>138.24287699999999</v>
       </c>
       <c r="D970" s="2">
-        <v>46202</v>
+        <v>46201</v>
       </c>
       <c r="E970" s="20">
-        <v>14.3</v>
+        <v>0.67708333333333337</v>
       </c>
       <c r="F970">
-        <v>2667</v>
+        <v>0</v>
       </c>
       <c r="G970">
         <v>0</v>
@@ -37686,7 +37714,7 @@
         <v>0</v>
       </c>
       <c r="I970">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="J970">
         <v>0</v>
@@ -37695,39 +37723,42 @@
         <v>0</v>
       </c>
       <c r="L970">
-        <v>167</v>
+        <v>0</v>
       </c>
       <c r="M970">
         <v>0</v>
       </c>
       <c r="N970">
-        <v>0</v>
+        <v>56</v>
+      </c>
+      <c r="O970">
+        <v>56</v>
       </c>
       <c r="P970">
-        <v>2945</v>
+        <v>112</v>
       </c>
       <c r="Q970" t="s">
-        <v>151</v>
+        <v>401</v>
       </c>
     </row>
     <row r="971" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A971" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="B971">
-        <v>-35.720106999999999</v>
+        <v>-35.788674999999998</v>
       </c>
       <c r="C971">
-        <v>137.94337100000001</v>
+        <v>138.070415</v>
       </c>
       <c r="D971" s="2">
         <v>46202</v>
       </c>
       <c r="E971" s="20">
-        <v>1.3</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="F971">
-        <v>1167</v>
+        <v>158333</v>
       </c>
       <c r="G971">
         <v>0</v>
@@ -37736,7 +37767,7 @@
         <v>0</v>
       </c>
       <c r="I971">
-        <v>1000</v>
+        <v>7333</v>
       </c>
       <c r="J971">
         <v>0</v>
@@ -37745,10 +37776,10 @@
         <v>0</v>
       </c>
       <c r="L971">
-        <v>167</v>
+        <v>17500</v>
       </c>
       <c r="M971">
-        <v>0</v>
+        <v>4667</v>
       </c>
       <c r="N971">
         <v>0</v>
@@ -37757,7 +37788,7 @@
         <v>0</v>
       </c>
       <c r="P971">
-        <v>2334</v>
+        <v>187833</v>
       </c>
       <c r="Q971" t="s">
         <v>151</v>
@@ -37765,22 +37796,22 @@
     </row>
     <row r="972" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A972" t="s">
-        <v>311</v>
+        <v>460</v>
       </c>
       <c r="B972">
-        <v>-35.445059999999998</v>
+        <v>-35.787862699999998</v>
       </c>
       <c r="C972">
-        <v>138.30758399999999</v>
+        <v>138.07130670000001</v>
       </c>
       <c r="D972" s="2">
         <v>46202</v>
       </c>
       <c r="E972" s="20">
-        <v>0.35416666666666669</v>
+        <v>14.3</v>
       </c>
       <c r="F972">
-        <v>0</v>
+        <v>2667</v>
       </c>
       <c r="G972">
         <v>0</v>
@@ -37789,7 +37820,7 @@
         <v>0</v>
       </c>
       <c r="I972">
-        <v>278</v>
+        <v>111</v>
       </c>
       <c r="J972">
         <v>0</v>
@@ -37798,323 +37829,350 @@
         <v>0</v>
       </c>
       <c r="L972">
-        <v>222</v>
+        <v>167</v>
       </c>
       <c r="M972">
         <v>0</v>
       </c>
       <c r="N972">
-        <v>333</v>
-      </c>
-      <c r="O972">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="P972">
-        <v>889</v>
+        <v>2945</v>
       </c>
       <c r="Q972" t="s">
-        <v>401</v>
+        <v>151</v>
       </c>
     </row>
     <row r="973" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A973" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="B973">
-        <v>-35.557200000000002</v>
+        <v>-35.720106999999999</v>
       </c>
       <c r="C973">
-        <v>138.886</v>
+        <v>137.94337100000001</v>
       </c>
       <c r="D973" s="2">
-        <v>46203</v>
+        <v>46202</v>
+      </c>
+      <c r="E973" s="20">
+        <v>1.3</v>
+      </c>
+      <c r="F973">
+        <v>1167</v>
+      </c>
+      <c r="G973">
+        <v>0</v>
+      </c>
+      <c r="H973">
+        <v>0</v>
+      </c>
+      <c r="I973">
+        <v>1000</v>
       </c>
       <c r="J973">
         <v>0</v>
       </c>
+      <c r="K973">
+        <v>0</v>
+      </c>
+      <c r="L973">
+        <v>167</v>
+      </c>
+      <c r="M973">
+        <v>0</v>
+      </c>
       <c r="N973">
-        <v>222</v>
+        <v>0</v>
       </c>
       <c r="O973">
-        <v>389</v>
+        <v>0</v>
       </c>
       <c r="P973">
-        <v>611</v>
+        <v>2334</v>
       </c>
       <c r="Q973" t="s">
-        <v>129</v>
+        <v>151</v>
       </c>
     </row>
     <row r="974" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A974" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="B974">
-        <v>-34.899749999999997</v>
+        <v>-35.445059999999998</v>
       </c>
       <c r="C974">
-        <v>137.45174</v>
+        <v>138.30758399999999</v>
       </c>
       <c r="D974" s="2">
-        <v>46203</v>
+        <v>46202</v>
       </c>
       <c r="E974" s="20">
-        <v>0.3125</v>
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="F974">
+        <v>0</v>
+      </c>
+      <c r="G974">
+        <v>0</v>
+      </c>
+      <c r="H974">
+        <v>0</v>
       </c>
       <c r="I974">
-        <v>167</v>
+        <v>278</v>
       </c>
       <c r="J974">
-        <v>111</v>
+        <v>0</v>
+      </c>
+      <c r="K974">
+        <v>0</v>
       </c>
       <c r="L974">
-        <v>278</v>
+        <v>222</v>
+      </c>
+      <c r="M974">
+        <v>0</v>
+      </c>
+      <c r="N974">
+        <v>333</v>
+      </c>
+      <c r="O974">
+        <v>56</v>
+      </c>
+      <c r="P974">
+        <v>889</v>
       </c>
       <c r="Q974" t="s">
-        <v>265</v>
+        <v>401</v>
       </c>
     </row>
     <row r="975" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A975" t="s">
-        <v>59</v>
+        <v>458</v>
       </c>
       <c r="B975">
-        <v>-35.084850000000003</v>
+        <v>-35.557200000000002</v>
       </c>
       <c r="C975">
-        <v>137.74889999999999</v>
+        <v>138.886</v>
       </c>
       <c r="D975" s="2">
-        <v>46204</v>
-      </c>
-      <c r="E975" s="24">
-        <v>0.58333333333333337</v>
-      </c>
-      <c r="G975">
-        <v>28</v>
-      </c>
-      <c r="H975">
-        <v>139</v>
-      </c>
-      <c r="I975">
-        <v>278</v>
+        <v>46203</v>
       </c>
       <c r="J975">
         <v>0</v>
       </c>
-      <c r="L975">
-        <v>139</v>
-      </c>
-      <c r="M975">
-        <v>0</v>
-      </c>
       <c r="N975">
+        <v>222</v>
+      </c>
+      <c r="O975">
+        <v>389</v>
+      </c>
+      <c r="P975">
         <v>611</v>
       </c>
-      <c r="O975">
-        <v>0</v>
-      </c>
-      <c r="P975">
-        <v>1195</v>
-      </c>
       <c r="Q975" t="s">
-        <v>149</v>
+        <v>129</v>
       </c>
     </row>
     <row r="976" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A976" t="s">
-        <v>453</v>
+        <v>301</v>
       </c>
       <c r="B976">
-        <v>-34.718809999999998</v>
+        <v>-34.899749999999997</v>
       </c>
       <c r="C976">
-        <v>135.85857999999999</v>
+        <v>137.45174</v>
       </c>
       <c r="D976" s="2">
-        <v>46205</v>
+        <v>46203</v>
       </c>
       <c r="E976" s="20">
-        <v>0.46875</v>
+        <v>0.3125</v>
       </c>
       <c r="I976">
-        <v>180</v>
+        <v>167</v>
       </c>
       <c r="J976">
-        <v>161</v>
+        <v>111</v>
       </c>
       <c r="L976">
-        <v>11</v>
-      </c>
-      <c r="O976">
-        <v>8</v>
-      </c>
-      <c r="P976">
-        <v>199</v>
+        <v>278</v>
       </c>
       <c r="Q976" t="s">
-        <v>283</v>
+        <v>265</v>
       </c>
     </row>
     <row r="977" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A977" t="s">
-        <v>465</v>
+        <v>59</v>
       </c>
       <c r="B977">
-        <v>-35.653578199999998</v>
+        <v>-35.084850000000003</v>
       </c>
       <c r="C977">
-        <v>137.64360360000001</v>
+        <v>137.74889999999999</v>
       </c>
       <c r="D977" s="2">
-        <v>46206</v>
-      </c>
-      <c r="E977" s="20">
-        <v>0.5</v>
-      </c>
-      <c r="F977">
-        <v>0</v>
+        <v>46204</v>
+      </c>
+      <c r="E977" s="24">
+        <v>0.58333333333333337</v>
       </c>
       <c r="G977">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="H977">
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="I977">
-        <v>0</v>
+        <v>278</v>
       </c>
       <c r="J977">
         <v>0</v>
       </c>
-      <c r="K977">
-        <v>0</v>
-      </c>
       <c r="L977">
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="M977">
         <v>0</v>
       </c>
       <c r="N977">
-        <v>0</v>
+        <v>611</v>
       </c>
       <c r="O977">
         <v>0</v>
       </c>
       <c r="P977">
-        <v>0</v>
+        <v>1195</v>
       </c>
       <c r="Q977" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="978" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A978" t="s">
-        <v>79</v>
+        <v>453</v>
       </c>
       <c r="B978">
-        <v>-34.804662999999998</v>
+        <v>-34.718809999999998</v>
       </c>
       <c r="C978">
-        <v>138.540223</v>
+        <v>135.85857999999999</v>
       </c>
       <c r="D978" s="2">
-        <v>46207</v>
+        <v>46205</v>
       </c>
       <c r="E978" s="20">
-        <v>0.55555555555555558</v>
+        <v>0.46875</v>
       </c>
       <c r="I978">
-        <v>1.8</v>
+        <v>180</v>
       </c>
       <c r="J978">
-        <v>0</v>
+        <v>161</v>
       </c>
       <c r="L978">
-        <v>5.1749999999999998</v>
-      </c>
-      <c r="M978">
-        <v>7.4999999999999997E-2</v>
+        <v>11</v>
+      </c>
+      <c r="O978">
+        <v>8</v>
       </c>
       <c r="P978">
-        <v>7.05</v>
+        <v>199</v>
       </c>
       <c r="Q978" t="s">
-        <v>78</v>
+        <v>283</v>
       </c>
     </row>
     <row r="979" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A979" t="s">
-        <v>267</v>
+        <v>465</v>
       </c>
       <c r="B979">
-        <v>-34.824044999999998</v>
+        <v>-35.653578199999998</v>
       </c>
       <c r="C979">
-        <v>138.48377600000001</v>
+        <v>137.64360360000001</v>
       </c>
       <c r="D979" s="2">
-        <v>46207</v>
+        <v>46206</v>
       </c>
       <c r="E979" s="20">
-        <v>0.57291666666666663</v>
+        <v>0.5</v>
+      </c>
+      <c r="F979">
+        <v>0</v>
+      </c>
+      <c r="G979">
+        <v>0</v>
       </c>
       <c r="H979">
-        <v>7.4999999999999997E-2</v>
+        <v>0</v>
       </c>
       <c r="I979">
-        <v>0.97499999999999998</v>
+        <v>0</v>
       </c>
       <c r="J979">
         <v>0</v>
       </c>
+      <c r="K979">
+        <v>0</v>
+      </c>
       <c r="L979">
-        <v>19.350000000000001</v>
+        <v>0</v>
       </c>
       <c r="M979">
-        <v>7.4999999999999997E-2</v>
+        <v>0</v>
       </c>
       <c r="N979">
-        <v>0.15</v>
+        <v>0</v>
+      </c>
+      <c r="O979">
+        <v>0</v>
       </c>
       <c r="P979">
-        <v>20.625</v>
+        <v>0</v>
       </c>
       <c r="Q979" t="s">
-        <v>78</v>
+        <v>151</v>
       </c>
     </row>
     <row r="980" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A980" t="s">
-        <v>348</v>
+        <v>79</v>
       </c>
       <c r="B980">
-        <v>-34.860666999999999</v>
+        <v>-34.804662999999998</v>
       </c>
       <c r="C980">
-        <v>138.490938</v>
+        <v>138.540223</v>
       </c>
       <c r="D980" s="2">
         <v>46207</v>
       </c>
       <c r="E980" s="20">
-        <v>0.59027777777777779</v>
-      </c>
-      <c r="H980">
-        <v>1</v>
+        <v>0.55555555555555558</v>
       </c>
       <c r="I980">
-        <v>68.5</v>
+        <v>1.8</v>
       </c>
       <c r="J980">
         <v>0</v>
       </c>
       <c r="L980">
-        <v>10.25</v>
+        <v>5.1749999999999998</v>
+      </c>
+      <c r="M980">
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="P980">
-        <v>79.75</v>
+        <v>7.05</v>
       </c>
       <c r="Q980" t="s">
         <v>78</v>
@@ -38122,163 +38180,133 @@
     </row>
     <row r="981" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A981" t="s">
-        <v>463</v>
+        <v>267</v>
       </c>
       <c r="B981">
-        <v>-34.589910000000003</v>
+        <v>-34.824044999999998</v>
       </c>
       <c r="C981">
-        <v>135.90476000000001</v>
+        <v>138.48377600000001</v>
       </c>
       <c r="D981" s="2">
         <v>46207</v>
       </c>
       <c r="E981" s="20">
-        <v>0.60416666666666663</v>
+        <v>0.57291666666666663</v>
+      </c>
+      <c r="H981">
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="I981">
-        <v>2</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="J981">
         <v>0</v>
       </c>
       <c r="L981">
-        <v>87</v>
-      </c>
-      <c r="O981">
-        <v>2</v>
+        <v>19.350000000000001</v>
+      </c>
+      <c r="M981">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="N981">
+        <v>0.15</v>
       </c>
       <c r="P981">
-        <v>91</v>
+        <v>20.625</v>
       </c>
       <c r="Q981" t="s">
-        <v>283</v>
+        <v>78</v>
       </c>
     </row>
     <row r="982" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A982" t="s">
-        <v>395</v>
+        <v>348</v>
       </c>
       <c r="B982">
-        <v>-35.793973000000001</v>
+        <v>-34.860666999999999</v>
       </c>
       <c r="C982">
-        <v>137.852418</v>
+        <v>138.490938</v>
       </c>
       <c r="D982" s="2">
         <v>46207</v>
       </c>
       <c r="E982" s="20">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="F982">
-        <v>111</v>
-      </c>
-      <c r="G982">
-        <v>0</v>
+        <v>0.59027777777777779</v>
       </c>
       <c r="H982">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I982">
-        <v>0</v>
+        <v>68.5</v>
       </c>
       <c r="J982">
         <v>0</v>
       </c>
-      <c r="K982">
-        <v>0</v>
-      </c>
       <c r="L982">
-        <v>556</v>
-      </c>
-      <c r="M982">
-        <v>0</v>
-      </c>
-      <c r="N982" t="s">
-        <v>464</v>
-      </c>
-      <c r="O982">
-        <v>0</v>
+        <v>10.25</v>
       </c>
       <c r="P982">
-        <v>667</v>
+        <v>79.75</v>
       </c>
       <c r="Q982" t="s">
-        <v>151</v>
+        <v>78</v>
       </c>
     </row>
     <row r="983" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A983" t="s">
-        <v>209</v>
-      </c>
-      <c r="B983" s="7">
-        <v>-35.739091000000002</v>
-      </c>
-      <c r="C983" s="7">
-        <v>137.67788400000001</v>
+        <v>463</v>
+      </c>
+      <c r="B983">
+        <v>-34.589910000000003</v>
+      </c>
+      <c r="C983">
+        <v>135.90476000000001</v>
       </c>
       <c r="D983" s="2">
         <v>46207</v>
       </c>
       <c r="E983" s="20">
-        <v>4.1666666666666664E-2</v>
-      </c>
-      <c r="F983">
-        <v>0</v>
-      </c>
-      <c r="G983">
-        <v>0</v>
-      </c>
-      <c r="H983">
-        <v>0</v>
+        <v>0.60416666666666663</v>
       </c>
       <c r="I983">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J983">
         <v>0</v>
       </c>
-      <c r="K983">
-        <v>0</v>
-      </c>
       <c r="L983">
-        <v>222</v>
-      </c>
-      <c r="M983">
-        <v>0</v>
-      </c>
-      <c r="N983">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="O983">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P983">
-        <v>222</v>
+        <v>91</v>
       </c>
       <c r="Q983" t="s">
-        <v>151</v>
+        <v>283</v>
       </c>
     </row>
     <row r="984" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A984" t="s">
-        <v>311</v>
+        <v>395</v>
       </c>
       <c r="B984">
-        <v>-35.445059999999998</v>
+        <v>-35.793973000000001</v>
       </c>
       <c r="C984">
-        <v>138.30758399999999</v>
+        <v>137.852418</v>
       </c>
       <c r="D984" s="2">
-        <v>46209</v>
+        <v>46207</v>
       </c>
       <c r="E984" s="20">
-        <v>0.34375</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="F984">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="G984">
         <v>0</v>
@@ -38287,7 +38315,7 @@
         <v>0</v>
       </c>
       <c r="I984">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="J984">
         <v>0</v>
@@ -38296,36 +38324,36 @@
         <v>0</v>
       </c>
       <c r="L984">
-        <v>167</v>
+        <v>556</v>
       </c>
       <c r="M984">
         <v>0</v>
       </c>
-      <c r="N984">
-        <v>167</v>
+      <c r="N984" t="s">
+        <v>464</v>
       </c>
       <c r="O984">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="P984">
-        <v>500</v>
+        <v>667</v>
       </c>
       <c r="Q984" t="s">
-        <v>401</v>
+        <v>151</v>
       </c>
     </row>
     <row r="985" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A985" t="s">
-        <v>418</v>
-      </c>
-      <c r="B985">
-        <v>-35.591330800000001</v>
-      </c>
-      <c r="C985">
-        <v>137.5061887</v>
+        <v>209</v>
+      </c>
+      <c r="B985" s="7">
+        <v>-35.739091000000002</v>
+      </c>
+      <c r="C985" s="7">
+        <v>137.67788400000001</v>
       </c>
       <c r="D985" s="2">
-        <v>46209</v>
+        <v>46207</v>
       </c>
       <c r="E985" s="20">
         <v>4.1666666666666664E-2</v>
@@ -38334,34 +38362,34 @@
         <v>0</v>
       </c>
       <c r="G985">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="H985">
         <v>0</v>
       </c>
       <c r="I985">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="J985">
         <v>0</v>
       </c>
       <c r="K985">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="L985">
-        <v>1667</v>
+        <v>222</v>
       </c>
       <c r="M985">
-        <v>556</v>
+        <v>0</v>
       </c>
       <c r="N985">
         <v>0</v>
       </c>
       <c r="O985">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="P985">
-        <v>2667</v>
+        <v>222</v>
       </c>
       <c r="Q985" t="s">
         <v>151</v>
@@ -38369,95 +38397,1000 @@
     </row>
     <row r="986" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A986" t="s">
-        <v>426</v>
+        <v>449</v>
       </c>
       <c r="B986">
-        <v>-35.410254000000002</v>
+        <v>-34.994472000000002</v>
       </c>
       <c r="C986">
-        <v>138.32751999999999</v>
+        <v>137.75879399999999</v>
       </c>
       <c r="D986" s="2">
-        <v>46210</v>
+        <v>46207</v>
       </c>
       <c r="E986" s="20">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="F986">
-        <v>0</v>
-      </c>
-      <c r="G986">
-        <v>0</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="H986">
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="I986">
-        <v>278</v>
+        <v>139</v>
       </c>
       <c r="J986">
         <v>0</v>
       </c>
-      <c r="K986">
-        <v>0</v>
-      </c>
       <c r="L986">
-        <v>111</v>
-      </c>
-      <c r="M986">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="N986">
-        <v>722</v>
+        <v>1000</v>
       </c>
       <c r="O986">
-        <v>56</v>
+        <v>250</v>
       </c>
       <c r="P986">
-        <v>1167</v>
+        <v>1611</v>
       </c>
       <c r="Q986" t="s">
-        <v>401</v>
+        <v>218</v>
       </c>
     </row>
     <row r="987" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A987" t="s">
+        <v>469</v>
+      </c>
+      <c r="B987">
+        <v>-35.089612000000002</v>
+      </c>
+      <c r="C987">
+        <v>137.748391</v>
+      </c>
+      <c r="D987" s="2">
+        <v>46207</v>
+      </c>
+      <c r="E987" s="20">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="G987">
+        <v>167</v>
+      </c>
+      <c r="H987">
+        <v>778</v>
+      </c>
+      <c r="I987">
+        <v>278</v>
+      </c>
+      <c r="J987">
+        <v>0</v>
+      </c>
+      <c r="L987">
+        <v>167</v>
+      </c>
+      <c r="N987">
+        <v>556</v>
+      </c>
+      <c r="P987">
+        <v>1946</v>
+      </c>
+      <c r="Q987" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="988" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A988" t="s">
+        <v>230</v>
+      </c>
+      <c r="B988">
+        <v>-35.054707999999998</v>
+      </c>
+      <c r="C988">
+        <v>137.725145</v>
+      </c>
+      <c r="D988" s="2">
+        <v>46207</v>
+      </c>
+      <c r="E988" s="20">
+        <v>0.65972222222222221</v>
+      </c>
+      <c r="H988">
+        <v>556</v>
+      </c>
+      <c r="I988">
+        <v>2895</v>
+      </c>
+      <c r="J988">
+        <v>167</v>
+      </c>
+      <c r="L988">
+        <v>611</v>
+      </c>
+      <c r="O988">
+        <v>56</v>
+      </c>
+      <c r="P988">
+        <v>4118</v>
+      </c>
+      <c r="Q988" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="989" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A989" t="s">
+        <v>311</v>
+      </c>
+      <c r="B989">
+        <v>-35.445059999999998</v>
+      </c>
+      <c r="C989">
+        <v>138.30758399999999</v>
+      </c>
+      <c r="D989" s="2">
+        <v>46209</v>
+      </c>
+      <c r="E989" s="20">
+        <v>0.34375</v>
+      </c>
+      <c r="F989">
+        <v>0</v>
+      </c>
+      <c r="G989">
+        <v>0</v>
+      </c>
+      <c r="H989">
+        <v>0</v>
+      </c>
+      <c r="I989">
+        <v>111</v>
+      </c>
+      <c r="J989">
+        <v>0</v>
+      </c>
+      <c r="K989">
+        <v>0</v>
+      </c>
+      <c r="L989">
+        <v>167</v>
+      </c>
+      <c r="M989">
+        <v>0</v>
+      </c>
+      <c r="N989">
+        <v>167</v>
+      </c>
+      <c r="O989">
+        <v>56</v>
+      </c>
+      <c r="P989">
+        <v>500</v>
+      </c>
+      <c r="Q989" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="990" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A990" t="s">
+        <v>418</v>
+      </c>
+      <c r="B990">
+        <v>-35.591330800000001</v>
+      </c>
+      <c r="C990">
+        <v>137.5061887</v>
+      </c>
+      <c r="D990" s="2">
+        <v>46209</v>
+      </c>
+      <c r="E990" s="20">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="F990">
+        <v>0</v>
+      </c>
+      <c r="G990">
+        <v>111</v>
+      </c>
+      <c r="H990">
+        <v>0</v>
+      </c>
+      <c r="I990">
+        <v>111</v>
+      </c>
+      <c r="J990">
+        <v>0</v>
+      </c>
+      <c r="K990">
+        <v>111</v>
+      </c>
+      <c r="L990">
+        <v>1667</v>
+      </c>
+      <c r="M990">
+        <v>556</v>
+      </c>
+      <c r="N990">
+        <v>0</v>
+      </c>
+      <c r="O990">
+        <v>111</v>
+      </c>
+      <c r="P990">
+        <v>2667</v>
+      </c>
+      <c r="Q990" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="991" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A991" t="s">
+        <v>471</v>
+      </c>
+      <c r="B991">
+        <v>-31.974415</v>
+      </c>
+      <c r="C991">
+        <v>132.44960900000001</v>
+      </c>
+      <c r="D991" s="2">
+        <v>46209</v>
+      </c>
+      <c r="E991" s="20">
+        <v>0.4375</v>
+      </c>
+      <c r="I991">
+        <v>56</v>
+      </c>
+      <c r="J991">
+        <v>0</v>
+      </c>
+      <c r="L991">
+        <v>1</v>
+      </c>
+      <c r="O991">
+        <v>500</v>
+      </c>
+      <c r="P991">
+        <v>557</v>
+      </c>
+      <c r="Q991" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="992" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A992" t="s">
+        <v>472</v>
+      </c>
+      <c r="B992">
+        <v>-31.958428000000001</v>
+      </c>
+      <c r="C992">
+        <v>132.467792</v>
+      </c>
+      <c r="D992" s="2">
+        <v>46209</v>
+      </c>
+      <c r="E992" s="20">
+        <v>0.44861111111111113</v>
+      </c>
+      <c r="I992">
+        <v>56</v>
+      </c>
+      <c r="J992">
+        <v>0</v>
+      </c>
+      <c r="L992">
+        <v>56</v>
+      </c>
+      <c r="O992">
+        <v>56</v>
+      </c>
+      <c r="P992">
+        <v>168</v>
+      </c>
+      <c r="Q992" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="993" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A993" t="s">
+        <v>473</v>
+      </c>
+      <c r="B993">
+        <v>31.948198999999999</v>
+      </c>
+      <c r="C993">
+        <v>132.49790300000001</v>
+      </c>
+      <c r="D993" s="2">
+        <v>46209</v>
+      </c>
+      <c r="E993" s="20">
+        <v>0.46180555555555558</v>
+      </c>
+      <c r="J993">
+        <v>0</v>
+      </c>
+      <c r="L993">
+        <v>111</v>
+      </c>
+      <c r="P993">
+        <v>111</v>
+      </c>
+      <c r="Q993" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="994" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A994" t="s">
+        <v>474</v>
+      </c>
+      <c r="B994">
+        <v>-31.985513999999998</v>
+      </c>
+      <c r="C994">
+        <v>132.49972700000001</v>
+      </c>
+      <c r="D994" s="2">
+        <v>46209</v>
+      </c>
+      <c r="E994" s="20">
+        <v>0.4826388888888889</v>
+      </c>
+      <c r="J994">
+        <v>0</v>
+      </c>
+      <c r="O994">
+        <v>56</v>
+      </c>
+      <c r="P994">
+        <v>56</v>
+      </c>
+      <c r="Q994" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="995" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A995" t="s">
+        <v>475</v>
+      </c>
+      <c r="B995">
+        <v>-32.023009000000002</v>
+      </c>
+      <c r="C995">
+        <v>132.48193800000001</v>
+      </c>
+      <c r="D995" s="2">
+        <v>46209</v>
+      </c>
+      <c r="E995" s="20">
+        <v>0.50486111111111109</v>
+      </c>
+      <c r="I995">
+        <v>500</v>
+      </c>
+      <c r="J995">
+        <v>0</v>
+      </c>
+      <c r="L995">
+        <v>111</v>
+      </c>
+      <c r="O995">
+        <v>389</v>
+      </c>
+      <c r="P995">
+        <v>1000</v>
+      </c>
+      <c r="Q995" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="996" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A996" t="s">
+        <v>476</v>
+      </c>
+      <c r="B996">
+        <v>-31.990354</v>
+      </c>
+      <c r="C996">
+        <v>132.4407879</v>
+      </c>
+      <c r="D996" s="2">
+        <v>46209</v>
+      </c>
+      <c r="E996" s="20">
+        <v>0.53888888888888886</v>
+      </c>
+      <c r="I996">
+        <v>389</v>
+      </c>
+      <c r="J996">
+        <v>0</v>
+      </c>
+      <c r="L996">
+        <v>278</v>
+      </c>
+      <c r="O996">
+        <v>222</v>
+      </c>
+      <c r="P996">
+        <v>889</v>
+      </c>
+      <c r="Q996" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="997" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A997" t="s">
+        <v>426</v>
+      </c>
+      <c r="B997">
+        <v>-35.410254000000002</v>
+      </c>
+      <c r="C997">
+        <v>138.32751999999999</v>
+      </c>
+      <c r="D997" s="2">
+        <v>46210</v>
+      </c>
+      <c r="E997" s="20">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="F997">
+        <v>0</v>
+      </c>
+      <c r="G997">
+        <v>0</v>
+      </c>
+      <c r="H997">
+        <v>0</v>
+      </c>
+      <c r="I997">
+        <v>278</v>
+      </c>
+      <c r="J997">
+        <v>0</v>
+      </c>
+      <c r="K997">
+        <v>0</v>
+      </c>
+      <c r="L997">
+        <v>111</v>
+      </c>
+      <c r="M997">
+        <v>0</v>
+      </c>
+      <c r="N997">
+        <v>722</v>
+      </c>
+      <c r="O997">
+        <v>56</v>
+      </c>
+      <c r="P997">
+        <v>1167</v>
+      </c>
+      <c r="Q997" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="998" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A998" t="s">
+        <v>59</v>
+      </c>
+      <c r="B998">
+        <v>-35.084850000000003</v>
+      </c>
+      <c r="C998">
+        <v>137.74889999999999</v>
+      </c>
+      <c r="D998" s="2">
+        <v>46210</v>
+      </c>
+      <c r="E998" s="20">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="G998">
+        <v>56</v>
+      </c>
+      <c r="H998">
+        <v>166</v>
+      </c>
+      <c r="I998">
+        <v>277</v>
+      </c>
+      <c r="J998">
+        <v>0</v>
+      </c>
+      <c r="L998">
+        <v>277</v>
+      </c>
+      <c r="M998">
+        <v>0</v>
+      </c>
+      <c r="N998">
+        <v>722</v>
+      </c>
+      <c r="O998">
+        <v>0</v>
+      </c>
+      <c r="P998">
+        <v>1498</v>
+      </c>
+      <c r="Q998" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="999" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A999" t="s">
         <v>453</v>
       </c>
-      <c r="B987">
+      <c r="B999">
         <v>-34.718809999999998</v>
       </c>
-      <c r="C987">
+      <c r="C999">
         <v>135.85857999999999</v>
       </c>
-      <c r="D987" s="2">
+      <c r="D999" s="2">
         <v>46211</v>
       </c>
-      <c r="E987" s="20">
+      <c r="E999" s="20">
         <v>0.40277777777777779</v>
       </c>
-      <c r="I987">
+      <c r="I999">
         <v>25</v>
       </c>
-      <c r="J987">
+      <c r="J999">
         <v>19</v>
       </c>
-      <c r="L987">
+      <c r="L999">
         <v>11</v>
       </c>
-      <c r="O987">
+      <c r="O999">
         <v>2</v>
       </c>
-      <c r="P987">
+      <c r="P999">
         <v>38</v>
       </c>
-      <c r="Q987" t="s">
+      <c r="Q999" t="s">
         <v>283</v>
       </c>
     </row>
+    <row r="1000" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A1000" t="s">
+        <v>466</v>
+      </c>
+      <c r="B1000">
+        <v>-35.587468999999999</v>
+      </c>
+      <c r="C1000">
+        <v>138.60170199999999</v>
+      </c>
+      <c r="D1000" s="2">
+        <v>46213</v>
+      </c>
+      <c r="J1000">
+        <v>0</v>
+      </c>
+      <c r="L1000">
+        <v>278</v>
+      </c>
+      <c r="N1000">
+        <v>389</v>
+      </c>
+      <c r="O1000">
+        <v>722</v>
+      </c>
+      <c r="P1000">
+        <v>1389</v>
+      </c>
+      <c r="Q1000" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="1001" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A1001" t="s">
+        <v>467</v>
+      </c>
+      <c r="B1001">
+        <v>-35.592480999999999</v>
+      </c>
+      <c r="C1001">
+        <v>138.600776</v>
+      </c>
+      <c r="D1001" s="2">
+        <v>46213</v>
+      </c>
+      <c r="G1001">
+        <v>56</v>
+      </c>
+      <c r="J1001">
+        <v>0</v>
+      </c>
+      <c r="L1001">
+        <v>222</v>
+      </c>
+      <c r="N1001">
+        <v>167</v>
+      </c>
+      <c r="O1001">
+        <v>333</v>
+      </c>
+      <c r="P1001">
+        <v>778</v>
+      </c>
+      <c r="Q1001" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="1002" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A1002" t="s">
+        <v>221</v>
+      </c>
+      <c r="B1002">
+        <v>-35.638145999999999</v>
+      </c>
+      <c r="C1002">
+        <v>137.6249325</v>
+      </c>
+      <c r="D1002" s="2">
+        <v>46214</v>
+      </c>
+      <c r="E1002" s="20">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="F1002">
+        <v>0</v>
+      </c>
+      <c r="G1002">
+        <v>0</v>
+      </c>
+      <c r="H1002">
+        <v>0</v>
+      </c>
+      <c r="I1002">
+        <v>0</v>
+      </c>
+      <c r="J1002">
+        <v>0</v>
+      </c>
+      <c r="K1002">
+        <v>0</v>
+      </c>
+      <c r="L1002">
+        <v>0</v>
+      </c>
+      <c r="M1002">
+        <v>0</v>
+      </c>
+      <c r="N1002">
+        <v>0</v>
+      </c>
+      <c r="O1002">
+        <v>0</v>
+      </c>
+      <c r="P1002">
+        <v>0</v>
+      </c>
+      <c r="Q1002" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="1003" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A1003" t="s">
+        <v>470</v>
+      </c>
+      <c r="B1003">
+        <v>-35.081918000000002</v>
+      </c>
+      <c r="C1003">
+        <v>137.74822499999999</v>
+      </c>
+      <c r="D1003" s="2">
+        <v>46215</v>
+      </c>
+      <c r="E1003" s="20">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="I1003">
+        <v>278</v>
+      </c>
+      <c r="J1003">
+        <v>0</v>
+      </c>
+      <c r="L1003">
+        <v>56</v>
+      </c>
+      <c r="N1003">
+        <v>556</v>
+      </c>
+      <c r="P1003">
+        <v>890</v>
+      </c>
+      <c r="Q1003" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="1004" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A1004" t="s">
+        <v>399</v>
+      </c>
+      <c r="B1004">
+        <v>-34.765996000000001</v>
+      </c>
+      <c r="C1004">
+        <v>137.86211299999999</v>
+      </c>
+      <c r="D1004" s="2">
+        <v>46215</v>
+      </c>
+      <c r="E1004" s="20">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="G1004">
+        <v>56</v>
+      </c>
+      <c r="H1004">
+        <v>56</v>
+      </c>
+      <c r="I1004">
+        <v>56</v>
+      </c>
+      <c r="J1004">
+        <v>0</v>
+      </c>
+      <c r="L1004">
+        <v>333</v>
+      </c>
+      <c r="N1004">
+        <v>500</v>
+      </c>
+      <c r="P1004">
+        <v>1001</v>
+      </c>
+      <c r="Q1004" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="1005" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A1005" t="s">
+        <v>449</v>
+      </c>
+      <c r="B1005">
+        <v>-34.994472000000002</v>
+      </c>
+      <c r="C1005">
+        <v>137.75879399999999</v>
+      </c>
+      <c r="D1005" s="2">
+        <v>46215</v>
+      </c>
+      <c r="E1005" s="20">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="G1005">
+        <v>56</v>
+      </c>
+      <c r="H1005">
+        <v>1389</v>
+      </c>
+      <c r="I1005">
+        <v>4222</v>
+      </c>
+      <c r="J1005">
+        <v>111</v>
+      </c>
+      <c r="L1005">
+        <v>944</v>
+      </c>
+      <c r="N1005">
+        <v>1944</v>
+      </c>
+      <c r="O1005">
+        <v>611</v>
+      </c>
+      <c r="P1005">
+        <v>9166</v>
+      </c>
+      <c r="Q1005" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="1006" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A1006" t="s">
+        <v>289</v>
+      </c>
+      <c r="B1006">
+        <v>-34.629109999999997</v>
+      </c>
+      <c r="C1006">
+        <v>135.86744999999999</v>
+      </c>
+      <c r="D1006" s="2">
+        <v>46216</v>
+      </c>
+      <c r="E1006" s="20">
+        <v>0.69791666666666663</v>
+      </c>
+      <c r="I1006">
+        <v>16</v>
+      </c>
+      <c r="J1006">
+        <v>10</v>
+      </c>
+      <c r="L1006">
+        <v>7</v>
+      </c>
+      <c r="O1006">
+        <v>3</v>
+      </c>
+      <c r="P1006">
+        <v>26</v>
+      </c>
+      <c r="Q1006" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="1007" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A1007" t="s">
+        <v>468</v>
+      </c>
+      <c r="B1007">
+        <v>-35.720106999999999</v>
+      </c>
+      <c r="C1007">
+        <v>137.94337100000001</v>
+      </c>
+      <c r="D1007" s="2">
+        <v>46216</v>
+      </c>
+      <c r="E1007" s="20">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="F1007">
+        <v>0</v>
+      </c>
+      <c r="G1007">
+        <v>0</v>
+      </c>
+      <c r="H1007">
+        <v>0</v>
+      </c>
+      <c r="I1007">
+        <v>0</v>
+      </c>
+      <c r="J1007">
+        <v>0</v>
+      </c>
+      <c r="K1007">
+        <v>0</v>
+      </c>
+      <c r="L1007">
+        <v>222</v>
+      </c>
+      <c r="M1007">
+        <v>0</v>
+      </c>
+      <c r="N1007">
+        <v>0</v>
+      </c>
+      <c r="O1007">
+        <v>0</v>
+      </c>
+      <c r="P1007">
+        <v>222</v>
+      </c>
+      <c r="Q1007" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="1008" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A1008" t="s">
+        <v>395</v>
+      </c>
+      <c r="B1008">
+        <v>-35.793973000000001</v>
+      </c>
+      <c r="C1008">
+        <v>137.852418</v>
+      </c>
+      <c r="D1008" s="2">
+        <v>46216</v>
+      </c>
+      <c r="E1008" s="20">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="F1008">
+        <v>0</v>
+      </c>
+      <c r="G1008">
+        <v>0</v>
+      </c>
+      <c r="H1008">
+        <v>111</v>
+      </c>
+      <c r="I1008">
+        <v>0</v>
+      </c>
+      <c r="J1008">
+        <v>0</v>
+      </c>
+      <c r="K1008">
+        <v>0</v>
+      </c>
+      <c r="L1008">
+        <v>222</v>
+      </c>
+      <c r="M1008">
+        <v>0</v>
+      </c>
+      <c r="N1008">
+        <v>0</v>
+      </c>
+      <c r="O1008">
+        <v>0</v>
+      </c>
+      <c r="P1008">
+        <v>333</v>
+      </c>
+      <c r="Q1008" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="1009" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A1009" t="s">
+        <v>311</v>
+      </c>
+      <c r="B1009">
+        <v>-35.445059999999998</v>
+      </c>
+      <c r="C1009">
+        <v>138.30758399999999</v>
+      </c>
+      <c r="D1009" s="2">
+        <v>46216</v>
+      </c>
+      <c r="E1009" s="20">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="F1009">
+        <v>167</v>
+      </c>
+      <c r="G1009">
+        <v>0</v>
+      </c>
+      <c r="H1009">
+        <v>0</v>
+      </c>
+      <c r="I1009">
+        <v>111</v>
+      </c>
+      <c r="J1009">
+        <v>0</v>
+      </c>
+      <c r="K1009">
+        <v>0</v>
+      </c>
+      <c r="L1009">
+        <v>111</v>
+      </c>
+      <c r="M1009">
+        <v>0</v>
+      </c>
+      <c r="N1009">
+        <v>0</v>
+      </c>
+      <c r="O1009">
+        <v>0</v>
+      </c>
+      <c r="P1009">
+        <v>389</v>
+      </c>
+      <c r="Q1009" t="s">
+        <v>349</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q987">
-    <sortCondition ref="D2:D987"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q1009">
+    <sortCondition ref="D2:D1009"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="S229">

--- a/MASTER spreadsheet of community summaries.xlsx
+++ b/MASTER spreadsheet of community summaries.xlsx
@@ -5,19 +5,16 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\peri\Dropbox\Delta\Projects\Laboratory\Algal blooms, bacterial counts  for community\For Luke's HAB data display\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\a1675510\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0C7BB3F-F300-45C7-B969-63B890F9265F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84932979-99FF-46DE-8BFE-CCB68807F64A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{9286397E-2757-492B-865A-39B2D6A15FF6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{9286397E-2757-492B-865A-39B2D6A15FF6}"/>
   </bookViews>
   <sheets>
     <sheet name="Cells per mL" sheetId="1" r:id="rId1"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId2"/>
-  </externalReferences>
   <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -1652,28 +1649,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Sheet1"/>
-      <sheetName val="Sheet1-1"/>
-      <sheetName val="Form Data"/>
-      <sheetName val="Sheet 1"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1994,29 +1969,29 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F307807-E5C9-4450-88E0-159CBB3E9A67}">
   <dimension ref="A1:T1009"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="39.33203125" customWidth="1"/>
-    <col min="2" max="2" width="17.77734375" customWidth="1"/>
-    <col min="3" max="3" width="14.6640625" customWidth="1"/>
-    <col min="4" max="4" width="13.109375" customWidth="1"/>
-    <col min="5" max="5" width="16.6640625" style="20" customWidth="1"/>
+    <col min="1" max="1" width="39.28515625" customWidth="1"/>
+    <col min="2" max="2" width="17.7109375" customWidth="1"/>
+    <col min="3" max="3" width="14.7109375" customWidth="1"/>
+    <col min="4" max="4" width="13.140625" customWidth="1"/>
+    <col min="5" max="5" width="16.7109375" style="20" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="15.44140625" customWidth="1"/>
-    <col min="8" max="8" width="11.88671875" customWidth="1"/>
-    <col min="9" max="9" width="14.109375" customWidth="1"/>
-    <col min="10" max="10" width="11.88671875" customWidth="1"/>
-    <col min="11" max="11" width="14.109375" customWidth="1"/>
-    <col min="12" max="12" width="10.44140625" customWidth="1"/>
-    <col min="13" max="13" width="15.5546875" customWidth="1"/>
+    <col min="7" max="7" width="15.42578125" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" customWidth="1"/>
+    <col min="9" max="9" width="14.140625" customWidth="1"/>
+    <col min="10" max="10" width="11.85546875" customWidth="1"/>
+    <col min="11" max="11" width="14.140625" customWidth="1"/>
+    <col min="12" max="12" width="10.42578125" customWidth="1"/>
+    <col min="13" max="13" width="15.5703125" customWidth="1"/>
     <col min="14" max="14" width="13" customWidth="1"/>
-    <col min="15" max="15" width="7.6640625" customWidth="1"/>
-    <col min="16" max="16" width="12.44140625" customWidth="1"/>
-    <col min="17" max="17" width="10.33203125" customWidth="1"/>
+    <col min="15" max="15" width="7.7109375" customWidth="1"/>
+    <col min="16" max="16" width="12.42578125" customWidth="1"/>
+    <col min="17" max="17" width="10.28515625" customWidth="1"/>
     <col min="18" max="18" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -2069,7 +2044,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -2098,7 +2073,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -2136,7 +2111,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -2177,7 +2152,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -2212,7 +2187,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -2256,7 +2231,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -2300,7 +2275,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -2338,7 +2313,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -2379,7 +2354,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>92</v>
       </c>
@@ -2405,7 +2380,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>91</v>
       </c>
@@ -2431,7 +2406,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>86</v>
       </c>
@@ -2457,7 +2432,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>87</v>
       </c>
@@ -2483,7 +2458,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>88</v>
       </c>
@@ -2509,7 +2484,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>89</v>
       </c>
@@ -2535,7 +2510,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>90</v>
       </c>
@@ -2561,7 +2536,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>91</v>
       </c>
@@ -2587,7 +2562,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>93</v>
       </c>
@@ -2613,7 +2588,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>8</v>
       </c>
@@ -2657,7 +2632,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>9</v>
       </c>
@@ -2689,7 +2664,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>10</v>
       </c>
@@ -2721,7 +2696,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>93</v>
       </c>
@@ -2747,7 +2722,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>8</v>
       </c>
@@ -2791,7 +2766,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>11</v>
       </c>
@@ -2838,7 +2813,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>12</v>
       </c>
@@ -2870,7 +2845,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>13</v>
       </c>
@@ -2911,7 +2886,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>14</v>
       </c>
@@ -2955,7 +2930,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>15</v>
       </c>
@@ -2996,7 +2971,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>5</v>
       </c>
@@ -3034,7 +3009,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>16</v>
       </c>
@@ -3066,7 +3041,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>94</v>
       </c>
@@ -3092,7 +3067,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>17</v>
       </c>
@@ -3136,7 +3111,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>95</v>
       </c>
@@ -3168,7 +3143,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>96</v>
       </c>
@@ -3197,7 +3172,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>18</v>
       </c>
@@ -3238,7 +3213,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>19</v>
       </c>
@@ -3282,7 +3257,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>20</v>
       </c>
@@ -3326,7 +3301,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>21</v>
       </c>
@@ -3367,7 +3342,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>22</v>
       </c>
@@ -3417,7 +3392,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>23</v>
       </c>
@@ -3464,7 +3439,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>97</v>
       </c>
@@ -3496,7 +3471,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>98</v>
       </c>
@@ -3531,7 +3506,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>99</v>
       </c>
@@ -3560,7 +3535,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>87</v>
       </c>
@@ -3586,7 +3561,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>100</v>
       </c>
@@ -3615,7 +3590,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>88</v>
       </c>
@@ -3644,7 +3619,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>86</v>
       </c>
@@ -3673,7 +3648,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>101</v>
       </c>
@@ -3702,7 +3677,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>90</v>
       </c>
@@ -3731,7 +3706,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>102</v>
       </c>
@@ -3772,7 +3747,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>103</v>
       </c>
@@ -3810,7 +3785,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>104</v>
       </c>
@@ -3839,7 +3814,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>24</v>
       </c>
@@ -3877,7 +3852,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>105</v>
       </c>
@@ -3909,7 +3884,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>106</v>
       </c>
@@ -3941,7 +3916,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>107</v>
       </c>
@@ -3973,7 +3948,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>108</v>
       </c>
@@ -4005,7 +3980,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>25</v>
       </c>
@@ -4043,7 +4018,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>19</v>
       </c>
@@ -4081,7 +4056,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>26</v>
       </c>
@@ -4122,7 +4097,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>27</v>
       </c>
@@ -4160,7 +4135,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>20</v>
       </c>
@@ -4198,7 +4173,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>105</v>
       </c>
@@ -4230,7 +4205,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>109</v>
       </c>
@@ -4262,7 +4237,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>110</v>
       </c>
@@ -4294,7 +4269,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>111</v>
       </c>
@@ -4326,7 +4301,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>112</v>
       </c>
@@ -4358,7 +4333,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>113</v>
       </c>
@@ -4390,7 +4365,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>105</v>
       </c>
@@ -4422,7 +4397,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>114</v>
       </c>
@@ -4454,7 +4429,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>28</v>
       </c>
@@ -4498,7 +4473,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>28</v>
       </c>
@@ -4540,7 +4515,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>28</v>
       </c>
@@ -4582,7 +4557,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>28</v>
       </c>
@@ -4624,7 +4599,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>28</v>
       </c>
@@ -4668,7 +4643,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>28</v>
       </c>
@@ -4712,7 +4687,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>115</v>
       </c>
@@ -4741,7 +4716,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>116</v>
       </c>
@@ -4770,7 +4745,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>157</v>
       </c>
@@ -4799,7 +4774,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>158</v>
       </c>
@@ -4825,7 +4800,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>29</v>
       </c>
@@ -4869,7 +4844,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>30</v>
       </c>
@@ -4913,7 +4888,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>31</v>
       </c>
@@ -4960,7 +4935,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>32</v>
       </c>
@@ -5004,7 +4979,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>33</v>
       </c>
@@ -5050,7 +5025,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>153</v>
       </c>
@@ -5082,7 +5057,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>155</v>
       </c>
@@ -5108,7 +5083,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>156</v>
       </c>
@@ -5134,7 +5109,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>159</v>
       </c>
@@ -5163,7 +5138,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>34</v>
       </c>
@@ -5210,7 +5185,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>35</v>
       </c>
@@ -5251,7 +5226,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>36</v>
       </c>
@@ -5283,7 +5258,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>37</v>
       </c>
@@ -5325,7 +5300,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>153</v>
       </c>
@@ -5351,7 +5326,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>154</v>
       </c>
@@ -5377,7 +5352,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>94</v>
       </c>
@@ -5406,7 +5381,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>140</v>
       </c>
@@ -5432,7 +5407,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>141</v>
       </c>
@@ -5464,7 +5439,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>152</v>
       </c>
@@ -5490,7 +5465,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>160</v>
       </c>
@@ -5519,7 +5494,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>34</v>
       </c>
@@ -5563,7 +5538,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>38</v>
       </c>
@@ -5598,7 +5573,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>39</v>
       </c>
@@ -5639,7 +5614,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>40</v>
       </c>
@@ -5677,7 +5652,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>41</v>
       </c>
@@ -5715,7 +5690,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>41</v>
       </c>
@@ -5756,7 +5731,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>92</v>
       </c>
@@ -5785,7 +5760,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>42</v>
       </c>
@@ -5817,7 +5792,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>43</v>
       </c>
@@ -5861,7 +5836,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>86</v>
       </c>
@@ -5893,7 +5868,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>101</v>
       </c>
@@ -5922,7 +5897,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>87</v>
       </c>
@@ -5954,7 +5929,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>88</v>
       </c>
@@ -5980,7 +5955,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>89</v>
       </c>
@@ -6009,7 +5984,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>90</v>
       </c>
@@ -6035,7 +6010,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>44</v>
       </c>
@@ -6079,7 +6054,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>45</v>
       </c>
@@ -6123,7 +6098,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>46</v>
       </c>
@@ -6164,7 +6139,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>47</v>
       </c>
@@ -6202,7 +6177,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>48</v>
       </c>
@@ -6243,7 +6218,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>49</v>
       </c>
@@ -6281,7 +6256,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>5</v>
       </c>
@@ -6328,7 +6303,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>37</v>
       </c>
@@ -6369,7 +6344,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>77</v>
       </c>
@@ -6401,7 +6376,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>80</v>
       </c>
@@ -6433,7 +6408,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>130</v>
       </c>
@@ -6468,7 +6443,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>117</v>
       </c>
@@ -6497,7 +6472,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>118</v>
       </c>
@@ -6523,7 +6498,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>81</v>
       </c>
@@ -6555,7 +6530,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>161</v>
       </c>
@@ -6584,7 +6559,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="131" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>79</v>
       </c>
@@ -6616,7 +6591,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="132" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>157</v>
       </c>
@@ -6645,7 +6620,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="133" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>158</v>
       </c>
@@ -6677,7 +6652,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="134" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>125</v>
       </c>
@@ -6709,7 +6684,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="135" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>126</v>
       </c>
@@ -6750,7 +6725,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="136" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>127</v>
       </c>
@@ -6788,7 +6763,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="137" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>128</v>
       </c>
@@ -6826,7 +6801,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="138" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>132</v>
       </c>
@@ -6867,7 +6842,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>133</v>
       </c>
@@ -6908,7 +6883,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="140" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>134</v>
       </c>
@@ -6946,7 +6921,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="141" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>135</v>
       </c>
@@ -6984,7 +6959,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="142" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>136</v>
       </c>
@@ -7019,7 +6994,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="143" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>137</v>
       </c>
@@ -7054,7 +7029,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="144" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>138</v>
       </c>
@@ -7092,7 +7067,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="145" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>139</v>
       </c>
@@ -7127,7 +7102,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="146" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>37</v>
       </c>
@@ -7168,7 +7143,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="147" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>119</v>
       </c>
@@ -7206,7 +7181,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="148" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>120</v>
       </c>
@@ -7241,7 +7216,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="149" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>79</v>
       </c>
@@ -7276,7 +7251,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="150" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>235</v>
       </c>
@@ -7311,7 +7286,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="151" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>85</v>
       </c>
@@ -7343,7 +7318,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="152" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>18</v>
       </c>
@@ -7384,7 +7359,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="153" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>50</v>
       </c>
@@ -7422,7 +7397,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="154" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>27</v>
       </c>
@@ -7457,7 +7432,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="155" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>37</v>
       </c>
@@ -7498,7 +7473,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="156" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>79</v>
       </c>
@@ -7530,7 +7505,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="157" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>131</v>
       </c>
@@ -7562,7 +7537,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="158" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>235</v>
       </c>
@@ -7597,7 +7572,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="159" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>85</v>
       </c>
@@ -7629,7 +7604,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="160" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>51</v>
       </c>
@@ -7667,7 +7642,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="161" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>121</v>
       </c>
@@ -7699,7 +7674,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="162" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>18</v>
       </c>
@@ -7740,7 +7715,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="163" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>122</v>
       </c>
@@ -7769,7 +7744,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="164" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>79</v>
       </c>
@@ -7801,7 +7776,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="165" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>235</v>
       </c>
@@ -7833,7 +7808,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="166" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>85</v>
       </c>
@@ -7865,7 +7840,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="167" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>52</v>
       </c>
@@ -7909,7 +7884,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="168" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>53</v>
       </c>
@@ -7953,7 +7928,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="169" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>37</v>
       </c>
@@ -7994,7 +7969,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="170" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>82</v>
       </c>
@@ -8026,7 +8001,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="171" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>82</v>
       </c>
@@ -8058,7 +8033,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="172" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>84</v>
       </c>
@@ -8090,7 +8065,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="173" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>84</v>
       </c>
@@ -8122,7 +8097,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="174" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>54</v>
       </c>
@@ -8160,7 +8135,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="175" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>55</v>
       </c>
@@ -8198,7 +8173,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="176" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>56</v>
       </c>
@@ -8236,7 +8211,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="177" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>57</v>
       </c>
@@ -8271,7 +8246,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="178" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>58</v>
       </c>
@@ -8312,7 +8287,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="179" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>59</v>
       </c>
@@ -8347,7 +8322,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="180" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>15</v>
       </c>
@@ -8388,7 +8363,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="181" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>15</v>
       </c>
@@ -8429,7 +8404,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="182" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>60</v>
       </c>
@@ -8470,7 +8445,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="183" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>37</v>
       </c>
@@ -8511,7 +8486,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="184" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>131</v>
       </c>
@@ -8543,7 +8518,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="185" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>61</v>
       </c>
@@ -8584,7 +8559,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="186" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>62</v>
       </c>
@@ -8622,7 +8597,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="187" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>63</v>
       </c>
@@ -8660,7 +8635,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="188" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>94</v>
       </c>
@@ -8689,7 +8664,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="189" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>176</v>
       </c>
@@ -8730,7 +8705,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="190" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>79</v>
       </c>
@@ -8765,7 +8740,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="191" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>235</v>
       </c>
@@ -8797,7 +8772,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="192" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>85</v>
       </c>
@@ -8829,7 +8804,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="193" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>37</v>
       </c>
@@ -8870,7 +8845,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="194" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>130</v>
       </c>
@@ -8905,7 +8880,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="195" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>83</v>
       </c>
@@ -8937,7 +8912,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="196" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>18</v>
       </c>
@@ -8981,7 +8956,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="197" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>86</v>
       </c>
@@ -9010,7 +8985,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="198" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>100</v>
       </c>
@@ -9048,7 +9023,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="199" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>87</v>
       </c>
@@ -9092,7 +9067,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="200" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>123</v>
       </c>
@@ -9130,7 +9105,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="201" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>124</v>
       </c>
@@ -9159,7 +9134,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="202" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>89</v>
       </c>
@@ -9191,7 +9166,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="203" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>90</v>
       </c>
@@ -9226,7 +9201,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="204" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>25</v>
       </c>
@@ -9273,7 +9248,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="205" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>79</v>
       </c>
@@ -9305,7 +9280,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="206" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>130</v>
       </c>
@@ -9337,7 +9312,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="207" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>85</v>
       </c>
@@ -9369,7 +9344,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="208" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>37</v>
       </c>
@@ -9407,7 +9382,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="209" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>162</v>
       </c>
@@ -9442,7 +9417,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="210" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>162</v>
       </c>
@@ -9474,7 +9449,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="211" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>162</v>
       </c>
@@ -9506,7 +9481,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="212" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>142</v>
       </c>
@@ -9532,7 +9507,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="213" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>144</v>
       </c>
@@ -9558,7 +9533,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="214" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>145</v>
       </c>
@@ -9584,7 +9559,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="215" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>146</v>
       </c>
@@ -9610,7 +9585,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="216" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>37</v>
       </c>
@@ -9648,7 +9623,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="217" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>142</v>
       </c>
@@ -9674,7 +9649,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="218" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>144</v>
       </c>
@@ -9700,7 +9675,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="219" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>145</v>
       </c>
@@ -9726,7 +9701,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="220" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>146</v>
       </c>
@@ -9752,7 +9727,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="221" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>18</v>
       </c>
@@ -9796,7 +9771,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="222" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>79</v>
       </c>
@@ -9828,7 +9803,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="223" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>130</v>
       </c>
@@ -9861,7 +9836,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="224" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>235</v>
       </c>
@@ -9894,7 +9869,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="225" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>85</v>
       </c>
@@ -9927,7 +9902,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="226" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>142</v>
       </c>
@@ -9953,7 +9928,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="227" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>59</v>
       </c>
@@ -9997,7 +9972,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="228" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>37</v>
       </c>
@@ -10041,7 +10016,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="229" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>147</v>
       </c>
@@ -10067,7 +10042,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="230" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A230" s="7" t="s">
         <v>168</v>
       </c>
@@ -10118,7 +10093,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="231" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>79</v>
       </c>
@@ -10150,7 +10125,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="232" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>235</v>
       </c>
@@ -10182,7 +10157,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="233" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>85</v>
       </c>
@@ -10214,7 +10189,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="234" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>59</v>
       </c>
@@ -10240,7 +10215,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="235" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>156</v>
       </c>
@@ -10278,7 +10253,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="236" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>154</v>
       </c>
@@ -10313,7 +10288,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="237" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>37</v>
       </c>
@@ -10357,7 +10332,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="238" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>141</v>
       </c>
@@ -10389,7 +10364,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="239" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>93</v>
       </c>
@@ -10424,7 +10399,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="240" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>152</v>
       </c>
@@ -10459,7 +10434,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="241" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>142</v>
       </c>
@@ -10485,7 +10460,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="242" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>145</v>
       </c>
@@ -10511,7 +10486,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="243" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>146</v>
       </c>
@@ -10537,7 +10512,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="244" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>142</v>
       </c>
@@ -10563,7 +10538,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="245" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>148</v>
       </c>
@@ -10589,7 +10564,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="246" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>163</v>
       </c>
@@ -10627,7 +10602,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="247" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>164</v>
       </c>
@@ -10659,7 +10634,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="248" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>59</v>
       </c>
@@ -10691,7 +10666,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="249" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A249" s="7" t="s">
         <v>167</v>
       </c>
@@ -10726,7 +10701,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="250" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>142</v>
       </c>
@@ -10752,7 +10727,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="251" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>177</v>
       </c>
@@ -10787,7 +10762,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="252" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>37</v>
       </c>
@@ -10834,7 +10809,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="253" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>142</v>
       </c>
@@ -10860,7 +10835,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="254" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>150</v>
       </c>
@@ -10886,7 +10861,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="255" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>38</v>
       </c>
@@ -10933,7 +10908,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="256" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>165</v>
       </c>
@@ -10968,7 +10943,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="257" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>88</v>
       </c>
@@ -11003,7 +10978,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="258" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A258" s="7" t="s">
         <v>166</v>
       </c>
@@ -11052,7 +11027,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="259" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>89</v>
       </c>
@@ -11081,7 +11056,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="260" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>174</v>
       </c>
@@ -11119,7 +11094,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="261" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>175</v>
       </c>
@@ -11148,7 +11123,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="262" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>59</v>
       </c>
@@ -11183,7 +11158,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="263" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>37</v>
       </c>
@@ -11230,7 +11205,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="264" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A264" s="7" t="s">
         <v>169</v>
       </c>
@@ -11276,7 +11251,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="265" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A265" s="7" t="s">
         <v>171</v>
       </c>
@@ -11323,7 +11298,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="266" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A266" s="7" t="s">
         <v>172</v>
       </c>
@@ -11370,7 +11345,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="267" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A267" s="7" t="s">
         <v>170</v>
       </c>
@@ -11418,7 +11393,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="268" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A268" s="7" t="s">
         <v>173</v>
       </c>
@@ -11465,7 +11440,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="269" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>178</v>
       </c>
@@ -11509,7 +11484,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="270" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>37</v>
       </c>
@@ -11556,7 +11531,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="271" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>180</v>
       </c>
@@ -11597,7 +11572,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="272" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>181</v>
       </c>
@@ -11641,7 +11616,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="273" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>79</v>
       </c>
@@ -11676,7 +11651,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="274" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>235</v>
       </c>
@@ -11711,7 +11686,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="275" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>85</v>
       </c>
@@ -11746,7 +11721,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="276" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>179</v>
       </c>
@@ -11781,7 +11756,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="277" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>121</v>
       </c>
@@ -11816,7 +11791,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="278" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>92</v>
       </c>
@@ -11836,7 +11811,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="279" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>94</v>
       </c>
@@ -11871,7 +11846,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="280" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>185</v>
       </c>
@@ -11891,7 +11866,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="281" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>92</v>
       </c>
@@ -11911,7 +11886,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="282" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>182</v>
       </c>
@@ -11961,7 +11936,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="283" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>183</v>
       </c>
@@ -12011,7 +11986,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="284" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>184</v>
       </c>
@@ -12061,7 +12036,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="285" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>79</v>
       </c>
@@ -12096,7 +12071,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="286" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>235</v>
       </c>
@@ -12131,7 +12106,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="287" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>85</v>
       </c>
@@ -12166,7 +12141,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="288" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>86</v>
       </c>
@@ -12201,7 +12176,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="289" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>100</v>
       </c>
@@ -12239,7 +12214,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="290" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>87</v>
       </c>
@@ -12271,7 +12246,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="291" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>88</v>
       </c>
@@ -12300,7 +12275,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="292" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>89</v>
       </c>
@@ -12323,7 +12298,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="293" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>174</v>
       </c>
@@ -12361,7 +12336,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="294" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>91</v>
       </c>
@@ -12381,7 +12356,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="295" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>187</v>
       </c>
@@ -12401,7 +12376,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="296" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A296" s="10" t="s">
         <v>198</v>
       </c>
@@ -12451,7 +12426,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="297" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A297" s="10" t="s">
         <v>199</v>
       </c>
@@ -12501,7 +12476,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="298" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>59</v>
       </c>
@@ -12548,7 +12523,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="299" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>211</v>
       </c>
@@ -12568,7 +12543,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="300" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>187</v>
       </c>
@@ -12588,7 +12563,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="301" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>91</v>
       </c>
@@ -12608,7 +12583,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="302" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>185</v>
       </c>
@@ -12628,7 +12603,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="303" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>188</v>
       </c>
@@ -12648,7 +12623,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="304" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>92</v>
       </c>
@@ -12668,7 +12643,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="305" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
         <v>189</v>
       </c>
@@ -12688,7 +12663,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="306" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
         <v>37</v>
       </c>
@@ -12732,7 +12707,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="307" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>191</v>
       </c>
@@ -12767,7 +12742,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="308" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>190</v>
       </c>
@@ -12802,7 +12777,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="309" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>192</v>
       </c>
@@ -12837,7 +12812,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="310" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>94</v>
       </c>
@@ -12875,7 +12850,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="311" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A311" s="10" t="s">
         <v>197</v>
       </c>
@@ -12923,7 +12898,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="312" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A312" s="9" t="s">
         <v>195</v>
       </c>
@@ -12973,7 +12948,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="313" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A313" s="10" t="s">
         <v>200</v>
       </c>
@@ -13023,7 +12998,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="314" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A314" s="9" t="s">
         <v>201</v>
       </c>
@@ -13073,7 +13048,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="315" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
         <v>193</v>
       </c>
@@ -13102,7 +13077,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="316" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
         <v>194</v>
       </c>
@@ -13137,7 +13112,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="317" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A317" s="10" t="s">
         <v>202</v>
       </c>
@@ -13187,7 +13162,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="318" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A318" s="9" t="s">
         <v>195</v>
       </c>
@@ -13237,7 +13212,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="319" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A319" s="10" t="s">
         <v>196</v>
       </c>
@@ -13287,7 +13262,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="320" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
         <v>178</v>
       </c>
@@ -13331,7 +13306,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="321" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
         <v>204</v>
       </c>
@@ -13381,7 +13356,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="322" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
         <v>205</v>
       </c>
@@ -13431,7 +13406,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="323" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
         <v>208</v>
       </c>
@@ -13481,7 +13456,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="324" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
         <v>79</v>
       </c>
@@ -13516,7 +13491,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="325" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
         <v>203</v>
       </c>
@@ -13551,7 +13526,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="326" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
         <v>85</v>
       </c>
@@ -13586,7 +13561,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="327" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
         <v>197</v>
       </c>
@@ -13636,7 +13611,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="328" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
         <v>94</v>
       </c>
@@ -13668,7 +13643,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="329" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
         <v>86</v>
       </c>
@@ -13706,7 +13681,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="330" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
         <v>210</v>
       </c>
@@ -13741,7 +13716,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="331" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
         <v>87</v>
       </c>
@@ -13776,7 +13751,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="332" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
         <v>209</v>
       </c>
@@ -13826,7 +13801,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="333" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
         <v>206</v>
       </c>
@@ -13876,7 +13851,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="334" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
         <v>207</v>
       </c>
@@ -13923,7 +13898,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="335" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
         <v>211</v>
       </c>
@@ -13943,7 +13918,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="336" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
         <v>185</v>
       </c>
@@ -13963,7 +13938,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="337" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
         <v>91</v>
       </c>
@@ -13983,7 +13958,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="338" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
         <v>92</v>
       </c>
@@ -14003,7 +13978,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="339" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
         <v>212</v>
       </c>
@@ -14023,7 +13998,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="340" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
         <v>213</v>
       </c>
@@ -14043,7 +14018,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="341" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
         <v>211</v>
       </c>
@@ -14063,7 +14038,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="342" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
         <v>91</v>
       </c>
@@ -14083,7 +14058,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="343" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
         <v>185</v>
       </c>
@@ -14103,7 +14078,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="344" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
         <v>213</v>
       </c>
@@ -14123,7 +14098,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="345" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
         <v>188</v>
       </c>
@@ -14143,7 +14118,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="346" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
         <v>92</v>
       </c>
@@ -14163,7 +14138,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="347" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
         <v>178</v>
       </c>
@@ -14210,7 +14185,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="348" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
         <v>156</v>
       </c>
@@ -14248,7 +14223,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="349" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
         <v>37</v>
       </c>
@@ -14292,7 +14267,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="350" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
         <v>230</v>
       </c>
@@ -14327,7 +14302,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="351" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
         <v>219</v>
       </c>
@@ -14377,7 +14352,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="352" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
         <v>224</v>
       </c>
@@ -14427,7 +14402,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="353" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
         <v>179</v>
       </c>
@@ -14477,7 +14452,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="354" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
         <v>154</v>
       </c>
@@ -14515,7 +14490,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="355" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
         <v>220</v>
       </c>
@@ -14565,7 +14540,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="356" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
         <v>293</v>
       </c>
@@ -14594,7 +14569,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="357" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
         <v>294</v>
       </c>
@@ -14629,7 +14604,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="358" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
         <v>221</v>
       </c>
@@ -14679,7 +14654,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="359" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
         <v>222</v>
       </c>
@@ -14729,7 +14704,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="360" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
         <v>94</v>
       </c>
@@ -14767,7 +14742,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="361" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
         <v>89</v>
       </c>
@@ -14805,7 +14780,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="362" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
         <v>18</v>
       </c>
@@ -14840,7 +14815,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="363" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
         <v>214</v>
       </c>
@@ -14881,7 +14856,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="364" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
         <v>215</v>
       </c>
@@ -14913,7 +14888,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="365" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
         <v>216</v>
       </c>
@@ -14951,7 +14926,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="366" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
         <v>217</v>
       </c>
@@ -14989,7 +14964,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="367" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
         <v>211</v>
       </c>
@@ -15012,7 +14987,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="368" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
         <v>185</v>
       </c>
@@ -15035,7 +15010,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="369" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
         <v>91</v>
       </c>
@@ -15058,7 +15033,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="370" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
         <v>92</v>
       </c>
@@ -15081,7 +15056,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="371" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
         <v>189</v>
       </c>
@@ -15104,7 +15079,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="372" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
         <v>223</v>
       </c>
@@ -15127,7 +15102,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="373" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
         <v>59</v>
       </c>
@@ -15171,7 +15146,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="374" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
         <v>228</v>
       </c>
@@ -15206,7 +15181,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="375" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
         <v>100</v>
       </c>
@@ -15247,7 +15222,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="376" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
         <v>87</v>
       </c>
@@ -15282,7 +15257,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="377" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
         <v>88</v>
       </c>
@@ -15323,7 +15298,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="378" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
         <v>295</v>
       </c>
@@ -15358,7 +15333,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="379" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
         <v>296</v>
       </c>
@@ -15393,7 +15368,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="380" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
         <v>174</v>
       </c>
@@ -15425,7 +15400,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="381" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
         <v>297</v>
       </c>
@@ -15460,7 +15435,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="382" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
         <v>298</v>
       </c>
@@ -15495,7 +15470,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="383" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
         <v>79</v>
       </c>
@@ -15539,7 +15514,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="384" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
         <v>235</v>
       </c>
@@ -15586,7 +15561,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="385" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
         <v>85</v>
       </c>
@@ -15621,7 +15596,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="386" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
         <v>229</v>
       </c>
@@ -15656,7 +15631,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="387" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
         <v>230</v>
       </c>
@@ -15688,7 +15663,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="388" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A388" s="10" t="s">
         <v>225</v>
       </c>
@@ -15738,7 +15713,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="389" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A389" s="10" t="s">
         <v>226</v>
       </c>
@@ -15788,7 +15763,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="390" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
         <v>231</v>
       </c>
@@ -15823,7 +15798,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="391" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
         <v>233</v>
       </c>
@@ -15873,7 +15848,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="392" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
         <v>207</v>
       </c>
@@ -15923,7 +15898,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="393" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
         <v>227</v>
       </c>
@@ -15973,7 +15948,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="394" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
         <v>230</v>
       </c>
@@ -16002,7 +15977,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="395" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
         <v>232</v>
       </c>
@@ -16052,7 +16027,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="396" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
         <v>37</v>
       </c>
@@ -16102,7 +16077,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="397" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
         <v>207</v>
       </c>
@@ -16152,7 +16127,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="398" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
         <v>230</v>
       </c>
@@ -16184,7 +16159,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="399" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
         <v>229</v>
       </c>
@@ -16219,7 +16194,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="400" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
         <v>79</v>
       </c>
@@ -16269,7 +16244,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="401" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
         <v>235</v>
       </c>
@@ -16319,7 +16294,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="402" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
         <v>207</v>
       </c>
@@ -16369,7 +16344,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="403" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
         <v>208</v>
       </c>
@@ -16419,7 +16394,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="404" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
         <v>230</v>
       </c>
@@ -16454,7 +16429,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="405" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
         <v>197</v>
       </c>
@@ -16504,7 +16479,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="406" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
         <v>234</v>
       </c>
@@ -16524,7 +16499,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="407" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
         <v>236</v>
       </c>
@@ -16577,7 +16552,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="408" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
         <v>237</v>
       </c>
@@ -16630,7 +16605,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="409" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
         <v>282</v>
       </c>
@@ -16662,7 +16637,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="410" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
         <v>238</v>
       </c>
@@ -16715,7 +16690,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="411" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
         <v>270</v>
       </c>
@@ -16750,7 +16725,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="412" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
         <v>271</v>
       </c>
@@ -16785,7 +16760,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="413" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
         <v>94</v>
       </c>
@@ -16826,7 +16801,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="414" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
         <v>89</v>
       </c>
@@ -16858,7 +16833,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="415" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
         <v>211</v>
       </c>
@@ -16878,7 +16853,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="416" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
         <v>185</v>
       </c>
@@ -16898,7 +16873,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="417" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
         <v>91</v>
       </c>
@@ -16918,7 +16893,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="418" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
         <v>188</v>
       </c>
@@ -16938,7 +16913,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="419" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
         <v>92</v>
       </c>
@@ -16958,7 +16933,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="420" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
         <v>223</v>
       </c>
@@ -16978,7 +16953,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="421" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
         <v>197</v>
       </c>
@@ -17028,7 +17003,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="422" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
         <v>235</v>
       </c>
@@ -17081,7 +17056,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="423" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
         <v>79</v>
       </c>
@@ -17134,7 +17109,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="424" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
         <v>240</v>
       </c>
@@ -17187,7 +17162,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="425" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
         <v>239</v>
       </c>
@@ -17240,7 +17215,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="426" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A426" s="10" t="s">
         <v>245</v>
       </c>
@@ -17290,7 +17265,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="427" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A427" s="10" t="s">
         <v>247</v>
       </c>
@@ -17340,7 +17315,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="428" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
         <v>272</v>
       </c>
@@ -17375,7 +17350,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="429" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
         <v>276</v>
       </c>
@@ -17410,7 +17385,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="430" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
         <v>241</v>
       </c>
@@ -17463,7 +17438,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="431" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
         <v>92</v>
       </c>
@@ -17516,7 +17491,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="432" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
         <v>242</v>
       </c>
@@ -17569,7 +17544,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="433" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
         <v>85</v>
       </c>
@@ -17622,7 +17597,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="434" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A434" s="10" t="s">
         <v>248</v>
       </c>
@@ -17672,7 +17647,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="435" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
         <v>273</v>
       </c>
@@ -17707,7 +17682,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="436" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
         <v>230</v>
       </c>
@@ -17739,7 +17714,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="437" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
         <v>94</v>
       </c>
@@ -17771,7 +17746,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="438" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
         <v>89</v>
       </c>
@@ -17815,7 +17790,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="439" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
         <v>246</v>
       </c>
@@ -17850,7 +17825,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="440" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
         <v>79</v>
       </c>
@@ -17903,7 +17878,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="441" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
         <v>243</v>
       </c>
@@ -17956,7 +17931,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="442" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
         <v>235</v>
       </c>
@@ -18009,7 +17984,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="443" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
         <v>85</v>
       </c>
@@ -18062,7 +18037,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="444" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
         <v>242</v>
       </c>
@@ -18115,7 +18090,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="445" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A445" s="10" t="s">
         <v>245</v>
       </c>
@@ -18165,7 +18140,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="446" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
         <v>249</v>
       </c>
@@ -18206,7 +18181,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="447" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
         <v>37</v>
       </c>
@@ -18244,7 +18219,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="448" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
         <v>220</v>
       </c>
@@ -18294,7 +18269,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="449" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
         <v>240</v>
       </c>
@@ -18335,7 +18310,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="450" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
         <v>230</v>
       </c>
@@ -18367,7 +18342,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="451" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
         <v>250</v>
       </c>
@@ -18399,7 +18374,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="452" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
         <v>197</v>
       </c>
@@ -18449,7 +18424,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="453" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
         <v>85</v>
       </c>
@@ -18487,7 +18462,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="454" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
         <v>242</v>
       </c>
@@ -18522,7 +18497,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="455" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
         <v>255</v>
       </c>
@@ -18566,7 +18541,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="456" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
         <v>341</v>
       </c>
@@ -18604,7 +18579,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="457" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
         <v>253</v>
       </c>
@@ -18654,7 +18629,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="458" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
         <v>256</v>
       </c>
@@ -18704,7 +18679,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="459" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
         <v>59</v>
       </c>
@@ -18748,7 +18723,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="460" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
         <v>322</v>
       </c>
@@ -18798,7 +18773,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="461" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
         <v>252</v>
       </c>
@@ -18830,7 +18805,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="462" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
         <v>284</v>
       </c>
@@ -18859,7 +18834,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="463" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
         <v>285</v>
       </c>
@@ -18888,7 +18863,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="464" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
         <v>286</v>
       </c>
@@ -18917,7 +18892,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="465" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
         <v>342</v>
       </c>
@@ -18955,7 +18930,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="466" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
         <v>343</v>
       </c>
@@ -18990,7 +18965,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="467" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
         <v>344</v>
       </c>
@@ -19025,7 +19000,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="468" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
         <v>245</v>
       </c>
@@ -19075,7 +19050,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="469" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
         <v>264</v>
       </c>
@@ -19122,7 +19097,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="470" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
         <v>266</v>
       </c>
@@ -19160,7 +19135,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="471" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
         <v>267</v>
       </c>
@@ -19196,7 +19171,7 @@
       </c>
       <c r="T471" s="2"/>
     </row>
-    <row r="472" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
         <v>85</v>
       </c>
@@ -19232,7 +19207,7 @@
       </c>
       <c r="T472" s="2"/>
     </row>
-    <row r="473" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
         <v>242</v>
       </c>
@@ -19271,7 +19246,7 @@
       </c>
       <c r="T473" s="2"/>
     </row>
-    <row r="474" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
         <v>243</v>
       </c>
@@ -19307,7 +19282,7 @@
       </c>
       <c r="T474" s="2"/>
     </row>
-    <row r="475" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
         <v>274</v>
       </c>
@@ -19343,7 +19318,7 @@
       </c>
       <c r="T475" s="2"/>
     </row>
-    <row r="476" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
         <v>275</v>
       </c>
@@ -19379,7 +19354,7 @@
       </c>
       <c r="T476" s="2"/>
     </row>
-    <row r="477" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
         <v>276</v>
       </c>
@@ -19415,7 +19390,7 @@
       </c>
       <c r="T477" s="2"/>
     </row>
-    <row r="478" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
         <v>242</v>
       </c>
@@ -19463,7 +19438,7 @@
       </c>
       <c r="T478" s="2"/>
     </row>
-    <row r="479" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
         <v>257</v>
       </c>
@@ -19484,7 +19459,7 @@
       </c>
       <c r="T479" s="2"/>
     </row>
-    <row r="480" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
         <v>209</v>
       </c>
@@ -19535,7 +19510,7 @@
       </c>
       <c r="T480" s="2"/>
     </row>
-    <row r="481" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
         <v>269</v>
       </c>
@@ -19574,7 +19549,7 @@
       </c>
       <c r="T481" s="2"/>
     </row>
-    <row r="482" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
         <v>268</v>
       </c>
@@ -19610,7 +19585,7 @@
       </c>
       <c r="T482" s="2"/>
     </row>
-    <row r="483" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
         <v>280</v>
       </c>
@@ -19640,7 +19615,7 @@
       </c>
       <c r="T483" s="2"/>
     </row>
-    <row r="484" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
         <v>258</v>
       </c>
@@ -19661,7 +19636,7 @@
       </c>
       <c r="T484" s="2"/>
     </row>
-    <row r="485" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
         <v>277</v>
       </c>
@@ -19700,7 +19675,7 @@
       </c>
       <c r="T485" s="2"/>
     </row>
-    <row r="486" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
         <v>278</v>
       </c>
@@ -19739,7 +19714,7 @@
       </c>
       <c r="T486" s="2"/>
     </row>
-    <row r="487" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
         <v>279</v>
       </c>
@@ -19774,7 +19749,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="488" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
         <v>281</v>
       </c>
@@ -19812,7 +19787,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="489" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
         <v>384</v>
       </c>
@@ -19844,7 +19819,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="490" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
         <v>120</v>
       </c>
@@ -19879,7 +19854,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="491" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
         <v>94</v>
       </c>
@@ -19908,7 +19883,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="492" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
         <v>89</v>
       </c>
@@ -19943,7 +19918,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="493" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
         <v>259</v>
       </c>
@@ -19963,7 +19938,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="494" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
         <v>260</v>
       </c>
@@ -19983,7 +19958,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="495" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
         <v>261</v>
       </c>
@@ -20003,7 +19978,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="496" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
         <v>262</v>
       </c>
@@ -20023,7 +19998,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="497" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
         <v>207</v>
       </c>
@@ -20073,7 +20048,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="498" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
         <v>59</v>
       </c>
@@ -20117,7 +20092,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="499" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
         <v>306</v>
       </c>
@@ -20152,7 +20127,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="500" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
         <v>263</v>
       </c>
@@ -20175,7 +20150,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="501" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
         <v>261</v>
       </c>
@@ -20195,7 +20170,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="502" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
         <v>287</v>
       </c>
@@ -20227,7 +20202,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="503" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
         <v>288</v>
       </c>
@@ -20259,7 +20234,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="504" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
         <v>289</v>
       </c>
@@ -20291,7 +20266,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="505" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
         <v>211</v>
       </c>
@@ -20325,7 +20300,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="506" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
         <v>187</v>
       </c>
@@ -20359,7 +20334,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="507" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
         <v>185</v>
       </c>
@@ -20385,7 +20360,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="508" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
         <v>91</v>
       </c>
@@ -20411,7 +20386,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="509" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A509" t="s">
         <v>188</v>
       </c>
@@ -20437,7 +20412,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="510" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A510" t="s">
         <v>92</v>
       </c>
@@ -20463,7 +20438,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="511" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A511" t="s">
         <v>223</v>
       </c>
@@ -20489,7 +20464,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="512" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A512" t="s">
         <v>287</v>
       </c>
@@ -20521,7 +20496,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="513" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A513" t="s">
         <v>287</v>
       </c>
@@ -20553,7 +20528,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="514" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A514" t="s">
         <v>299</v>
       </c>
@@ -20606,7 +20581,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="515" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A515" t="s">
         <v>179</v>
       </c>
@@ -20659,7 +20634,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="516" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
         <v>300</v>
       </c>
@@ -20712,7 +20687,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="517" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A517" t="s">
         <v>302</v>
       </c>
@@ -20762,7 +20737,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="518" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A518" t="s">
         <v>304</v>
       </c>
@@ -20797,7 +20772,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="519" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A519" t="s">
         <v>303</v>
       </c>
@@ -20847,7 +20822,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="520" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A520" t="s">
         <v>307</v>
       </c>
@@ -20882,7 +20857,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="521" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A521" t="s">
         <v>301</v>
       </c>
@@ -20914,7 +20889,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="522" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A522" t="s">
         <v>230</v>
       </c>
@@ -20949,7 +20924,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="523" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A523" t="s">
         <v>345</v>
       </c>
@@ -20981,7 +20956,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="524" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A524" t="s">
         <v>290</v>
       </c>
@@ -21016,7 +20991,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="525" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A525" t="s">
         <v>291</v>
       </c>
@@ -21051,7 +21026,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="526" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A526" t="s">
         <v>292</v>
       </c>
@@ -21086,7 +21061,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="527" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A527" t="s">
         <v>258</v>
       </c>
@@ -21109,7 +21084,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="528" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A528" t="s">
         <v>261</v>
       </c>
@@ -21132,7 +21107,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="529" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A529" t="s">
         <v>305</v>
       </c>
@@ -21170,7 +21145,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="530" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A530" t="s">
         <v>310</v>
       </c>
@@ -21208,7 +21183,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="531" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A531" t="s">
         <v>100</v>
       </c>
@@ -21234,7 +21209,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="532" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A532" t="s">
         <v>86</v>
       </c>
@@ -21263,7 +21238,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="533" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
         <v>87</v>
       </c>
@@ -21298,7 +21273,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="534" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A534" t="s">
         <v>88</v>
       </c>
@@ -21336,7 +21311,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="535" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A535" t="s">
         <v>295</v>
       </c>
@@ -21371,7 +21346,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="536" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A536" t="s">
         <v>297</v>
       </c>
@@ -21406,7 +21381,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="537" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A537" t="s">
         <v>298</v>
       </c>
@@ -21444,7 +21419,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="538" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A538" t="s">
         <v>317</v>
       </c>
@@ -21473,7 +21448,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="539" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A539" t="s">
         <v>308</v>
       </c>
@@ -21508,7 +21483,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="540" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A540" t="s">
         <v>449</v>
       </c>
@@ -21540,7 +21515,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="541" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A541" t="s">
         <v>309</v>
       </c>
@@ -21578,7 +21553,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="542" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A542" t="s">
         <v>212</v>
       </c>
@@ -21601,7 +21576,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="543" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A543" t="s">
         <v>266</v>
       </c>
@@ -21645,7 +21620,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="544" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A544" t="s">
         <v>267</v>
       </c>
@@ -21695,7 +21670,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="545" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A545" t="s">
         <v>85</v>
       </c>
@@ -21742,7 +21717,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="546" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A546" t="s">
         <v>323</v>
       </c>
@@ -21777,7 +21752,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="547" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A547" t="s">
         <v>322</v>
       </c>
@@ -21809,7 +21784,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="548" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A548" t="s">
         <v>311</v>
       </c>
@@ -21844,7 +21819,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="549" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A549" t="s">
         <v>312</v>
       </c>
@@ -21870,7 +21845,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="550" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A550" t="s">
         <v>313</v>
       </c>
@@ -21896,7 +21871,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="551" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A551" t="s">
         <v>91</v>
       </c>
@@ -21922,7 +21897,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="552" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A552" t="s">
         <v>185</v>
       </c>
@@ -21948,7 +21923,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="553" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A553" t="s">
         <v>314</v>
       </c>
@@ -21974,7 +21949,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="554" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A554" t="s">
         <v>315</v>
       </c>
@@ -22000,7 +21975,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="555" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A555" t="s">
         <v>188</v>
       </c>
@@ -22026,7 +22001,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="556" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A556" t="s">
         <v>316</v>
       </c>
@@ -22052,7 +22027,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="557" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A557" t="s">
         <v>318</v>
       </c>
@@ -22075,7 +22050,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="558" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A558" t="s">
         <v>319</v>
       </c>
@@ -22098,7 +22073,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="559" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A559" t="s">
         <v>320</v>
       </c>
@@ -22121,7 +22096,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="560" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A560" t="s">
         <v>287</v>
       </c>
@@ -22159,7 +22134,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="561" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A561" t="s">
         <v>288</v>
       </c>
@@ -22197,7 +22172,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="562" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A562" t="s">
         <v>59</v>
       </c>
@@ -22241,7 +22216,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="563" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A563" t="s">
         <v>321</v>
       </c>
@@ -22276,7 +22251,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="564" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A564" t="s">
         <v>327</v>
       </c>
@@ -22302,7 +22277,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="565" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="565" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A565" t="s">
         <v>94</v>
       </c>
@@ -22331,7 +22306,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="566" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="566" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A566" t="s">
         <v>89</v>
       </c>
@@ -22363,7 +22338,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="567" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A567" t="s">
         <v>37</v>
       </c>
@@ -22410,7 +22385,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="568" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A568" t="s">
         <v>317</v>
       </c>
@@ -22436,7 +22411,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="569" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A569" t="s">
         <v>328</v>
       </c>
@@ -22462,7 +22437,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="570" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A570" t="s">
         <v>337</v>
       </c>
@@ -22502,7 +22477,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="571" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A571" t="s">
         <v>377</v>
       </c>
@@ -22537,7 +22512,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="572" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A572" t="s">
         <v>324</v>
       </c>
@@ -22569,7 +22544,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="573" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A573" t="s">
         <v>325</v>
       </c>
@@ -22604,7 +22579,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="574" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A574" t="s">
         <v>326</v>
       </c>
@@ -22636,7 +22611,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="575" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A575" t="s">
         <v>301</v>
       </c>
@@ -22671,7 +22646,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="576" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A576" t="s">
         <v>329</v>
       </c>
@@ -22694,7 +22669,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="577" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A577" t="s">
         <v>257</v>
       </c>
@@ -22717,7 +22692,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="578" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="578" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A578" t="s">
         <v>262</v>
       </c>
@@ -22740,7 +22715,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="579" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="579" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A579" t="s">
         <v>257</v>
       </c>
@@ -22784,7 +22759,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="580" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="580" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A580" t="s">
         <v>332</v>
       </c>
@@ -22819,7 +22794,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="581" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="581" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A581" t="s">
         <v>262</v>
       </c>
@@ -22842,7 +22817,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="582" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A582" t="s">
         <v>212</v>
       </c>
@@ -22865,7 +22840,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="583" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="583" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A583" t="s">
         <v>330</v>
       </c>
@@ -22891,7 +22866,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="584" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="584" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A584" t="s">
         <v>301</v>
       </c>
@@ -22926,7 +22901,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="585" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="585" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A585" t="s">
         <v>323</v>
       </c>
@@ -22976,7 +22951,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="586" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="586" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A586" t="s">
         <v>331</v>
       </c>
@@ -23011,7 +22986,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="587" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="587" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A587" t="s">
         <v>266</v>
       </c>
@@ -23064,7 +23039,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="588" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="588" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A588" t="s">
         <v>267</v>
       </c>
@@ -23117,7 +23092,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="589" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="589" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A589" t="s">
         <v>85</v>
       </c>
@@ -23170,7 +23145,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="590" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="590" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A590" t="s">
         <v>242</v>
       </c>
@@ -23223,7 +23198,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="591" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="591" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A591" t="s">
         <v>94</v>
       </c>
@@ -23258,7 +23233,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="592" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="592" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A592" t="s">
         <v>89</v>
       </c>
@@ -23290,7 +23265,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="593" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="593" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A593" t="s">
         <v>289</v>
       </c>
@@ -23328,7 +23303,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="594" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="594" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A594" t="s">
         <v>333</v>
       </c>
@@ -23366,7 +23341,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="595" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="595" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A595" t="s">
         <v>334</v>
       </c>
@@ -23395,7 +23370,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="596" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="596" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A596" t="s">
         <v>257</v>
       </c>
@@ -23433,7 +23408,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="597" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="597" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A597" t="s">
         <v>262</v>
       </c>
@@ -23468,7 +23443,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="598" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="598" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A598" t="s">
         <v>336</v>
       </c>
@@ -23506,7 +23481,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="599" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="599" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A599" t="s">
         <v>338</v>
       </c>
@@ -23545,7 +23520,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="600" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="600" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A600" t="s">
         <v>262</v>
       </c>
@@ -23565,7 +23540,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="601" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="601" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A601" t="s">
         <v>212</v>
       </c>
@@ -23585,7 +23560,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="602" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="602" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A602" t="s">
         <v>339</v>
       </c>
@@ -23605,7 +23580,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="603" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="603" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A603" t="s">
         <v>340</v>
       </c>
@@ -23625,7 +23600,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="604" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="604" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A604" t="s">
         <v>351</v>
       </c>
@@ -23645,7 +23620,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="605" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="605" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A605" t="s">
         <v>335</v>
       </c>
@@ -23695,7 +23670,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="606" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="606" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A606" t="s">
         <v>59</v>
       </c>
@@ -23739,7 +23714,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="607" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="607" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A607" t="s">
         <v>301</v>
       </c>
@@ -23762,7 +23737,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="608" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="608" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A608" t="s">
         <v>212</v>
       </c>
@@ -23785,7 +23760,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="609" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="609" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A609" t="s">
         <v>352</v>
       </c>
@@ -23808,7 +23783,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="610" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="610" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A610" t="s">
         <v>351</v>
       </c>
@@ -23831,7 +23806,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="611" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="611" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A611" t="s">
         <v>353</v>
       </c>
@@ -23854,7 +23829,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="612" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="612" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A612" t="s">
         <v>257</v>
       </c>
@@ -23877,7 +23852,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="613" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="613" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A613" t="s">
         <v>301</v>
       </c>
@@ -23900,7 +23875,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="614" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="614" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A614" t="s">
         <v>317</v>
       </c>
@@ -23923,7 +23898,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="615" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="615" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A615" t="s">
         <v>301</v>
       </c>
@@ -23946,7 +23921,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="616" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="616" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A616" t="s">
         <v>212</v>
       </c>
@@ -23969,7 +23944,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="617" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="617" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A617" t="s">
         <v>352</v>
       </c>
@@ -23992,7 +23967,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="618" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="618" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A618" t="s">
         <v>362</v>
       </c>
@@ -24030,7 +24005,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="619" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="619" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A619" t="s">
         <v>267</v>
       </c>
@@ -24075,7 +24050,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="620" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="620" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A620" t="s">
         <v>85</v>
       </c>
@@ -24117,7 +24092,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="621" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="621" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A621" t="s">
         <v>348</v>
       </c>
@@ -24150,7 +24125,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="622" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="622" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A622" t="s">
         <v>79</v>
       </c>
@@ -24189,7 +24164,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="623" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="623" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A623" t="s">
         <v>301</v>
       </c>
@@ -24212,7 +24187,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="624" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="624" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A624" t="s">
         <v>301</v>
       </c>
@@ -24235,7 +24210,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="625" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="625" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A625" t="s">
         <v>352</v>
       </c>
@@ -24258,7 +24233,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="626" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="626" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A626" t="s">
         <v>354</v>
       </c>
@@ -24281,7 +24256,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="627" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="627" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A627" t="s">
         <v>351</v>
       </c>
@@ -24304,7 +24279,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="628" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="628" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A628" t="s">
         <v>355</v>
       </c>
@@ -24327,7 +24302,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="629" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="629" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A629" t="s">
         <v>356</v>
       </c>
@@ -24350,7 +24325,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="630" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="630" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A630" t="s">
         <v>94</v>
       </c>
@@ -24391,7 +24366,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="631" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="631" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A631" t="s">
         <v>89</v>
       </c>
@@ -24426,7 +24401,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="632" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="632" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A632" t="s">
         <v>412</v>
       </c>
@@ -24458,7 +24433,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="633" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="633" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A633" t="s">
         <v>311</v>
       </c>
@@ -24491,7 +24466,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="634" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="634" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A634" t="s">
         <v>357</v>
       </c>
@@ -24520,7 +24495,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="635" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="635" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A635" t="s">
         <v>358</v>
       </c>
@@ -24549,7 +24524,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="636" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="636" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A636" t="s">
         <v>59</v>
       </c>
@@ -24585,7 +24560,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="637" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="637" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A637" t="s">
         <v>350</v>
       </c>
@@ -24620,7 +24595,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="638" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="638" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A638" t="s">
         <v>352</v>
       </c>
@@ -24643,7 +24618,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="639" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="639" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A639" t="s">
         <v>301</v>
       </c>
@@ -24666,7 +24641,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="640" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="640" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A640" t="s">
         <v>86</v>
       </c>
@@ -24707,7 +24682,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="641" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="641" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A641" t="s">
         <v>100</v>
       </c>
@@ -24748,7 +24723,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="642" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="642" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A642" t="s">
         <v>352</v>
       </c>
@@ -24781,7 +24756,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="643" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="643" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A643" t="s">
         <v>369</v>
       </c>
@@ -24819,7 +24794,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="644" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="644" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A644" t="s">
         <v>370</v>
       </c>
@@ -24854,7 +24829,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="645" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="645" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A645" t="s">
         <v>87</v>
       </c>
@@ -24892,7 +24867,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="646" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="646" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A646" t="s">
         <v>88</v>
       </c>
@@ -24933,7 +24908,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="647" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="647" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A647" t="s">
         <v>89</v>
       </c>
@@ -24977,7 +24952,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="648" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="648" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A648" t="s">
         <v>374</v>
       </c>
@@ -25018,7 +24993,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="649" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="649" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A649" t="s">
         <v>378</v>
       </c>
@@ -25053,7 +25028,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="650" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="650" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A650" t="s">
         <v>301</v>
       </c>
@@ -25086,7 +25061,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="651" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="651" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A651" t="s">
         <v>317</v>
       </c>
@@ -25119,7 +25094,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="652" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="652" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A652" t="s">
         <v>267</v>
       </c>
@@ -25173,7 +25148,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="653" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="653" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A653" t="s">
         <v>348</v>
       </c>
@@ -25227,7 +25202,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="654" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="654" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A654" t="s">
         <v>79</v>
       </c>
@@ -25281,7 +25256,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="655" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="655" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A655" t="s">
         <v>359</v>
       </c>
@@ -25334,7 +25309,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="656" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="656" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A656" t="s">
         <v>351</v>
       </c>
@@ -25367,7 +25342,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="657" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="657" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A657" t="s">
         <v>212</v>
       </c>
@@ -25400,7 +25375,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="658" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="658" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A658" t="s">
         <v>360</v>
       </c>
@@ -25453,7 +25428,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="659" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="659" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A659" t="s">
         <v>361</v>
       </c>
@@ -25506,7 +25481,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="660" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="660" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A660" s="17" t="s">
         <v>363</v>
       </c>
@@ -25543,14 +25518,14 @@
         <v>56</v>
       </c>
       <c r="P660" s="17">
-        <f>SUM(F660:I660,K660:O660)</f>
+        <f t="shared" ref="P660:P666" si="0">SUM(F660:I660,K660:O660)</f>
         <v>1111</v>
       </c>
       <c r="Q660" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="661" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="661" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A661" t="s">
         <v>211</v>
       </c>
@@ -25576,14 +25551,14 @@
         <v>111</v>
       </c>
       <c r="P661">
-        <f>SUM(F661:I661,K661:O661)</f>
+        <f t="shared" si="0"/>
         <v>444</v>
       </c>
       <c r="Q661" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="662" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="662" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A662" t="s">
         <v>91</v>
       </c>
@@ -25609,14 +25584,14 @@
         <v>0</v>
       </c>
       <c r="P662">
-        <f>SUM(F662:I662,K662:O662)</f>
+        <f t="shared" si="0"/>
         <v>56</v>
       </c>
       <c r="Q662" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="663" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="663" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A663" t="s">
         <v>185</v>
       </c>
@@ -25642,14 +25617,14 @@
         <v>167</v>
       </c>
       <c r="P663">
-        <f>SUM(F663:I663,K663:O663)</f>
+        <f t="shared" si="0"/>
         <v>167</v>
       </c>
       <c r="Q663" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="664" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="664" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A664" t="s">
         <v>314</v>
       </c>
@@ -25675,14 +25650,14 @@
         <v>56</v>
       </c>
       <c r="P664">
-        <f>SUM(F664:I664,K664:O664)</f>
+        <f t="shared" si="0"/>
         <v>112</v>
       </c>
       <c r="Q664" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="665" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="665" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A665" t="s">
         <v>188</v>
       </c>
@@ -25708,14 +25683,14 @@
         <v>0</v>
       </c>
       <c r="P665">
-        <f>SUM(F665:I665,K665:O665)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Q665" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="666" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="666" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A666" t="s">
         <v>316</v>
       </c>
@@ -25741,14 +25716,14 @@
         <v>222</v>
       </c>
       <c r="P666">
-        <f>SUM(F666:I666,K666:O666)</f>
+        <f t="shared" si="0"/>
         <v>278</v>
       </c>
       <c r="Q666" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="667" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="667" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A667" t="s">
         <v>367</v>
       </c>
@@ -25780,7 +25755,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="668" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="668" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A668" t="s">
         <v>368</v>
       </c>
@@ -25815,7 +25790,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="669" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="669" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A669" t="s">
         <v>301</v>
       </c>
@@ -25850,7 +25825,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="670" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="670" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A670" t="s">
         <v>365</v>
       </c>
@@ -25885,7 +25860,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="671" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="671" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A671" t="s">
         <v>212</v>
       </c>
@@ -25918,7 +25893,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="672" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="672" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A672" t="s">
         <v>92</v>
       </c>
@@ -25972,7 +25947,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="673" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="673" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A673" t="s">
         <v>89</v>
       </c>
@@ -26001,7 +25976,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="674" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="674" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A674" t="s">
         <v>386</v>
       </c>
@@ -26051,7 +26026,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="675" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="675" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A675" t="s">
         <v>356</v>
       </c>
@@ -26084,7 +26059,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="676" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="676" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A676" t="s">
         <v>130</v>
       </c>
@@ -26138,7 +26113,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="677" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="677" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A677" t="s">
         <v>366</v>
       </c>
@@ -26192,7 +26167,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="678" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="678" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A678" t="s">
         <v>59</v>
       </c>
@@ -26230,7 +26205,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="679" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="679" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A679" t="s">
         <v>59</v>
       </c>
@@ -26268,7 +26243,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="680" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="680" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A680" t="s">
         <v>380</v>
       </c>
@@ -26291,7 +26266,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="681" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="681" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A681" t="s">
         <v>262</v>
       </c>
@@ -26311,7 +26286,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="682" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="682" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A682" t="s">
         <v>381</v>
       </c>
@@ -26334,7 +26309,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="683" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="683" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A683" t="s">
         <v>382</v>
       </c>
@@ -26357,7 +26332,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="684" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="684" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A684" t="s">
         <v>301</v>
       </c>
@@ -26380,7 +26355,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="685" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="685" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A685" t="s">
         <v>37</v>
       </c>
@@ -26427,7 +26402,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="686" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="686" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A686" t="s">
         <v>373</v>
       </c>
@@ -26468,7 +26443,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="687" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="687" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A687" t="s">
         <v>378</v>
       </c>
@@ -26503,7 +26478,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="688" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="688" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A688" t="s">
         <v>380</v>
       </c>
@@ -26526,7 +26501,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="689" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="689" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A689" t="s">
         <v>372</v>
       </c>
@@ -26564,7 +26539,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="690" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="690" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A690" t="s">
         <v>302</v>
       </c>
@@ -26617,7 +26592,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="691" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="691" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A691" t="s">
         <v>360</v>
       </c>
@@ -26670,7 +26645,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="692" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="692" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A692" t="s">
         <v>375</v>
       </c>
@@ -26720,7 +26695,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="693" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="693" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A693" t="s">
         <v>376</v>
       </c>
@@ -26773,7 +26748,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="694" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="694" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A694" t="s">
         <v>380</v>
       </c>
@@ -26796,7 +26771,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="695" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="695" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A695" t="s">
         <v>381</v>
       </c>
@@ -26819,7 +26794,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="696" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="696" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A696" t="s">
         <v>393</v>
       </c>
@@ -26860,7 +26835,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="697" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="697" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A697" t="s">
         <v>373</v>
       </c>
@@ -26898,7 +26873,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="698" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="698" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A698" t="s">
         <v>379</v>
       </c>
@@ -26936,7 +26911,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="699" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="699" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A699" t="s">
         <v>380</v>
       </c>
@@ -26959,7 +26934,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="700" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="700" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A700" t="s">
         <v>301</v>
       </c>
@@ -26982,7 +26957,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="701" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="701" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A701" t="s">
         <v>380</v>
       </c>
@@ -27005,7 +26980,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="702" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="702" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A702" t="s">
         <v>375</v>
       </c>
@@ -27058,7 +27033,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="703" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="703" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A703" t="s">
         <v>386</v>
       </c>
@@ -27111,7 +27086,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="704" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="704" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A704" t="s">
         <v>267</v>
       </c>
@@ -27153,7 +27128,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="705" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="705" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A705" t="s">
         <v>85</v>
       </c>
@@ -27192,7 +27167,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="706" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="706" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A706" t="s">
         <v>79</v>
       </c>
@@ -27231,7 +27206,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="707" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="707" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A707" t="s">
         <v>312</v>
       </c>
@@ -27263,7 +27238,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="708" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="708" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A708" t="s">
         <v>187</v>
       </c>
@@ -27295,7 +27270,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="709" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="709" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A709" t="s">
         <v>91</v>
       </c>
@@ -27327,7 +27302,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="710" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="710" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A710" t="s">
         <v>185</v>
       </c>
@@ -27359,7 +27334,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="711" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="711" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A711" t="s">
         <v>314</v>
       </c>
@@ -27391,7 +27366,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="712" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="712" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A712" t="s">
         <v>188</v>
       </c>
@@ -27423,7 +27398,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="713" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="713" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A713" t="s">
         <v>316</v>
       </c>
@@ -27455,7 +27430,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="714" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="714" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A714" t="s">
         <v>384</v>
       </c>
@@ -27493,7 +27468,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="715" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="715" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A715" t="s">
         <v>385</v>
       </c>
@@ -27546,7 +27521,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="716" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="716" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A716" t="s">
         <v>383</v>
       </c>
@@ -27569,7 +27544,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="717" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="717" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A717" t="s">
         <v>94</v>
       </c>
@@ -27604,7 +27579,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="718" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="718" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A718" t="s">
         <v>89</v>
       </c>
@@ -27639,7 +27614,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="719" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="719" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A719" t="s">
         <v>412</v>
       </c>
@@ -27671,7 +27646,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="720" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="720" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A720" t="s">
         <v>359</v>
       </c>
@@ -27724,7 +27699,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="721" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="721" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A721" t="s">
         <v>59</v>
       </c>
@@ -27762,7 +27737,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="722" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="722" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A722" t="s">
         <v>387</v>
       </c>
@@ -27806,7 +27781,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="723" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="723" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A723" t="s">
         <v>380</v>
       </c>
@@ -27829,7 +27804,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="724" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="724" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A724" t="s">
         <v>352</v>
       </c>
@@ -27852,7 +27827,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="725" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="725" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A725" t="s">
         <v>59</v>
       </c>
@@ -27890,7 +27865,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="726" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="726" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A726" t="s">
         <v>390</v>
       </c>
@@ -27943,7 +27918,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="727" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="727" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A727" t="s">
         <v>221</v>
       </c>
@@ -27996,7 +27971,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="728" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="728" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A728" t="s">
         <v>389</v>
       </c>
@@ -28031,7 +28006,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="729" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="729" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A729" t="s">
         <v>92</v>
       </c>
@@ -28072,7 +28047,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="730" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="730" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A730" t="s">
         <v>391</v>
       </c>
@@ -28113,7 +28088,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="731" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="731" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A731" t="s">
         <v>86</v>
       </c>
@@ -28154,7 +28129,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="732" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="732" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A732" t="s">
         <v>100</v>
       </c>
@@ -28192,7 +28167,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="733" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="733" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A733" t="s">
         <v>394</v>
       </c>
@@ -28233,7 +28208,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="734" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="734" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A734" t="s">
         <v>87</v>
       </c>
@@ -28271,7 +28246,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="735" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="735" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A735" t="s">
         <v>88</v>
       </c>
@@ -28312,7 +28287,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="736" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="736" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A736" t="s">
         <v>89</v>
       </c>
@@ -28350,7 +28325,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="737" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="737" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A737" t="s">
         <v>374</v>
       </c>
@@ -28388,7 +28363,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="738" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="738" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A738" t="s">
         <v>298</v>
       </c>
@@ -28423,7 +28398,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="739" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="739" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A739" t="s">
         <v>388</v>
       </c>
@@ -28458,7 +28433,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="740" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="740" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A740" t="s">
         <v>348</v>
       </c>
@@ -28496,7 +28471,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="741" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="741" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A741" t="s">
         <v>311</v>
       </c>
@@ -28534,7 +28509,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="742" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="742" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A742" t="s">
         <v>380</v>
       </c>
@@ -28557,7 +28532,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="743" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="743" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A743" t="s">
         <v>386</v>
       </c>
@@ -28610,7 +28585,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="744" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="744" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A744" t="s">
         <v>375</v>
       </c>
@@ -28663,7 +28638,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="745" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="745" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A745" t="s">
         <v>392</v>
       </c>
@@ -28686,7 +28661,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="746" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="746" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A746" t="s">
         <v>356</v>
       </c>
@@ -28709,7 +28684,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="747" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="747" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A747" t="s">
         <v>301</v>
       </c>
@@ -28732,7 +28707,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="748" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="748" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A748" t="s">
         <v>396</v>
       </c>
@@ -28761,7 +28736,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="749" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="749" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A749" t="s">
         <v>229</v>
       </c>
@@ -28799,7 +28774,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="750" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="750" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A750" t="s">
         <v>229</v>
       </c>
@@ -28837,7 +28812,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="751" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="751" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A751" t="s">
         <v>373</v>
       </c>
@@ -28872,7 +28847,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="752" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="752" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A752" t="s">
         <v>375</v>
       </c>
@@ -28925,7 +28900,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="753" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="753" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A753" t="s">
         <v>301</v>
       </c>
@@ -28948,7 +28923,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="754" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="754" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A754" t="s">
         <v>352</v>
       </c>
@@ -28968,7 +28943,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="755" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="755" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A755" t="s">
         <v>79</v>
       </c>
@@ -29000,7 +28975,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="756" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="756" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A756" t="s">
         <v>85</v>
       </c>
@@ -29035,7 +29010,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="757" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="757" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A757" t="s">
         <v>267</v>
       </c>
@@ -29070,7 +29045,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="758" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="758" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A758" t="s">
         <v>388</v>
       </c>
@@ -29105,7 +29080,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="759" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="759" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A759" t="s">
         <v>179</v>
       </c>
@@ -29137,7 +29112,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="760" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="760" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A760" t="s">
         <v>209</v>
       </c>
@@ -29190,7 +29165,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="761" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="761" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A761" t="s">
         <v>397</v>
       </c>
@@ -29222,7 +29197,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="762" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="762" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A762" t="s">
         <v>230</v>
       </c>
@@ -29257,7 +29232,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="763" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="763" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A763" t="s">
         <v>398</v>
       </c>
@@ -29295,7 +29270,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="764" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="764" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A764" t="s">
         <v>399</v>
       </c>
@@ -29333,7 +29308,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="765" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="765" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A765" t="s">
         <v>400</v>
       </c>
@@ -29368,7 +29343,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="766" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="766" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A766" t="s">
         <v>395</v>
       </c>
@@ -29421,7 +29396,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="767" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="767" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A767" t="s">
         <v>359</v>
       </c>
@@ -29474,7 +29449,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="768" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="768" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A768" t="s">
         <v>311</v>
       </c>
@@ -29509,7 +29484,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="769" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="769" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A769" t="s">
         <v>380</v>
       </c>
@@ -29541,7 +29516,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="770" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="770" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A770" t="s">
         <v>311</v>
       </c>
@@ -29579,7 +29554,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="771" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="771" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A771" t="s">
         <v>352</v>
       </c>
@@ -29614,7 +29589,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="772" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="772" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A772" t="s">
         <v>406</v>
       </c>
@@ -29655,7 +29630,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="773" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="773" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A773" t="s">
         <v>348</v>
       </c>
@@ -29696,7 +29671,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="774" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="774" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A774" t="s">
         <v>85</v>
       </c>
@@ -29731,7 +29706,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="775" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="775" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A775" t="s">
         <v>79</v>
       </c>
@@ -29763,7 +29738,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="776" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="776" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A776" t="s">
         <v>267</v>
       </c>
@@ -29801,7 +29776,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="777" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="777" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A777" s="1" t="s">
         <v>312</v>
       </c>
@@ -29834,14 +29809,14 @@
       <c r="N777" s="1"/>
       <c r="O777" s="1"/>
       <c r="P777">
-        <f>SUM(F777:I777,K777:O777)</f>
+        <f t="shared" ref="P777:P788" si="1">SUM(F777:I777,K777:O777)</f>
         <v>722</v>
       </c>
       <c r="Q777" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="778" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="778" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A778" t="s">
         <v>187</v>
       </c>
@@ -29867,14 +29842,14 @@
         <v>111</v>
       </c>
       <c r="P778">
-        <f>SUM(F778:I778,K778:O778)</f>
+        <f t="shared" si="1"/>
         <v>167</v>
       </c>
       <c r="Q778" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="779" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="779" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A779" t="s">
         <v>91</v>
       </c>
@@ -29900,14 +29875,14 @@
         <v>56</v>
       </c>
       <c r="P779">
-        <f>SUM(F779:I779,K779:O779)</f>
+        <f t="shared" si="1"/>
         <v>278</v>
       </c>
       <c r="Q779" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="780" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="780" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A780" t="s">
         <v>185</v>
       </c>
@@ -29933,14 +29908,14 @@
         <v>56</v>
       </c>
       <c r="P780">
-        <f>SUM(F780:I780,K780:O780)</f>
+        <f t="shared" si="1"/>
         <v>112</v>
       </c>
       <c r="Q780" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="781" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="781" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A781" t="s">
         <v>314</v>
       </c>
@@ -29966,14 +29941,14 @@
         <v>0</v>
       </c>
       <c r="P781">
-        <f>SUM(F781:I781,K781:O781)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Q781" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="782" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="782" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A782" t="s">
         <v>188</v>
       </c>
@@ -29999,14 +29974,14 @@
         <v>56</v>
       </c>
       <c r="P782">
-        <f>SUM(F782:I782,K782:O782)</f>
+        <f t="shared" si="1"/>
         <v>278</v>
       </c>
       <c r="Q782" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="783" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="783" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A783" t="s">
         <v>316</v>
       </c>
@@ -30032,14 +30007,14 @@
         <v>167</v>
       </c>
       <c r="P783">
-        <f>SUM(F783:I783,K783:O783)</f>
+        <f t="shared" si="1"/>
         <v>445</v>
       </c>
       <c r="Q783" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="784" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="784" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A784" t="s">
         <v>315</v>
       </c>
@@ -30065,14 +30040,14 @@
         <v>0</v>
       </c>
       <c r="P784">
-        <f>SUM(F784:I784,K784:O784)</f>
+        <f t="shared" si="1"/>
         <v>56</v>
       </c>
       <c r="Q784" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="785" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="785" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A785" t="s">
         <v>402</v>
       </c>
@@ -30098,14 +30073,14 @@
         <v>56</v>
       </c>
       <c r="P785">
-        <f>SUM(F785:I785,K785:O785)</f>
+        <f t="shared" si="1"/>
         <v>56</v>
       </c>
       <c r="Q785" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="786" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="786" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A786" t="s">
         <v>403</v>
       </c>
@@ -30131,14 +30106,14 @@
         <v>56</v>
       </c>
       <c r="P786">
-        <f>SUM(F786:I786,K786:O786)</f>
+        <f t="shared" si="1"/>
         <v>56</v>
       </c>
       <c r="Q786" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="787" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="787" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A787" t="s">
         <v>404</v>
       </c>
@@ -30164,14 +30139,14 @@
         <v>0</v>
       </c>
       <c r="P787">
-        <f>SUM(F787:I787,K787:O787)</f>
+        <f t="shared" si="1"/>
         <v>56</v>
       </c>
       <c r="Q787" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="788" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="788" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A788" t="s">
         <v>86</v>
       </c>
@@ -30197,14 +30172,14 @@
         <v>111</v>
       </c>
       <c r="P788">
-        <f>SUM(F788:I788,K788:O788)</f>
+        <f t="shared" si="1"/>
         <v>111</v>
       </c>
       <c r="Q788" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="789" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="789" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A789" t="s">
         <v>338</v>
       </c>
@@ -30242,7 +30217,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="790" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="790" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A790" t="s">
         <v>405</v>
       </c>
@@ -30283,7 +30258,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="791" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="791" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A791" t="s">
         <v>395</v>
       </c>
@@ -30336,7 +30311,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="792" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="792" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A792" t="s">
         <v>209</v>
       </c>
@@ -30389,7 +30364,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="793" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="793" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A793" t="s">
         <v>375</v>
       </c>
@@ -30442,7 +30417,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="794" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="794" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A794" t="s">
         <v>409</v>
       </c>
@@ -30477,7 +30452,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="795" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="795" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A795" t="s">
         <v>93</v>
       </c>
@@ -30512,7 +30487,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="796" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="796" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A796" t="s">
         <v>93</v>
       </c>
@@ -30547,7 +30522,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="797" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="797" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A797" t="s">
         <v>221</v>
       </c>
@@ -30600,7 +30575,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="798" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="798" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A798" t="s">
         <v>59</v>
       </c>
@@ -30641,7 +30616,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="799" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="799" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A799" t="s">
         <v>407</v>
       </c>
@@ -30676,7 +30651,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="800" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="800" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A800" t="s">
         <v>408</v>
       </c>
@@ -30714,7 +30689,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="801" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="801" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A801" t="s">
         <v>359</v>
       </c>
@@ -30767,7 +30742,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="802" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="802" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A802" t="s">
         <v>410</v>
       </c>
@@ -30820,7 +30795,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="803" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="803" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A803" t="s">
         <v>230</v>
       </c>
@@ -30858,7 +30833,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="804" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="804" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A804" t="s">
         <v>390</v>
       </c>
@@ -30911,7 +30886,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="805" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="805" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A805" t="s">
         <v>413</v>
       </c>
@@ -30943,7 +30918,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="806" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="806" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A806" t="s">
         <v>414</v>
       </c>
@@ -30975,7 +30950,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="807" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="807" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A807" t="s">
         <v>94</v>
       </c>
@@ -31007,7 +30982,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="808" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="808" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A808" t="s">
         <v>92</v>
       </c>
@@ -31048,7 +31023,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="809" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="809" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A809" t="s">
         <v>389</v>
       </c>
@@ -31089,7 +31064,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="810" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="810" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A810" t="s">
         <v>311</v>
       </c>
@@ -31127,7 +31102,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="811" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="811" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A811" t="s">
         <v>400</v>
       </c>
@@ -31177,7 +31152,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="812" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="812" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A812" t="s">
         <v>405</v>
       </c>
@@ -31218,7 +31193,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="813" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="813" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A813" t="s">
         <v>411</v>
       </c>
@@ -31271,7 +31246,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="814" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="814" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A814" t="s">
         <v>375</v>
       </c>
@@ -31324,7 +31299,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="815" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="815" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A815" t="s">
         <v>59</v>
       </c>
@@ -31365,7 +31340,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="816" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="816" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A816" t="s">
         <v>417</v>
       </c>
@@ -31418,7 +31393,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="817" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="817" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A817" t="s">
         <v>416</v>
       </c>
@@ -31459,7 +31434,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="818" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="818" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A818" t="s">
         <v>267</v>
       </c>
@@ -31506,7 +31481,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="819" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="819" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A819" t="s">
         <v>79</v>
       </c>
@@ -31538,7 +31513,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="820" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="820" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A820" t="s">
         <v>415</v>
       </c>
@@ -31579,7 +31554,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="821" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="821" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A821" t="s">
         <v>311</v>
       </c>
@@ -31617,7 +31592,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="822" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="822" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A822" t="s">
         <v>418</v>
       </c>
@@ -31670,7 +31645,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="823" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="823" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A823" t="s">
         <v>395</v>
       </c>
@@ -31723,7 +31698,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="824" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="824" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A824" t="s">
         <v>419</v>
       </c>
@@ -31764,7 +31739,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="825" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="825" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A825" t="s">
         <v>421</v>
       </c>
@@ -31808,7 +31783,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="826" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="826" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A826" t="s">
         <v>448</v>
       </c>
@@ -31846,7 +31821,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="827" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="827" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A827" t="s">
         <v>398</v>
       </c>
@@ -31884,7 +31859,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="828" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="828" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A828" t="s">
         <v>89</v>
       </c>
@@ -31922,7 +31897,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="829" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="829" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A829" t="s">
         <v>400</v>
       </c>
@@ -31966,7 +31941,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="830" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="830" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A830" t="s">
         <v>422</v>
       </c>
@@ -32007,7 +31982,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="831" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="831" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A831" t="s">
         <v>179</v>
       </c>
@@ -32045,7 +32020,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="832" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="832" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A832" t="s">
         <v>311</v>
       </c>
@@ -32083,7 +32058,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="833" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="833" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A833" t="s">
         <v>420</v>
       </c>
@@ -32136,7 +32111,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="834" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="834" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A834" t="s">
         <v>59</v>
       </c>
@@ -32177,7 +32152,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="835" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="835" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A835" t="s">
         <v>86</v>
       </c>
@@ -32224,7 +32199,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="836" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="836" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A836" t="s">
         <v>87</v>
       </c>
@@ -32268,7 +32243,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="837" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="837" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A837" t="s">
         <v>424</v>
       </c>
@@ -32309,7 +32284,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="838" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="838" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A838" t="s">
         <v>89</v>
       </c>
@@ -32350,7 +32325,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="839" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="839" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A839" t="s">
         <v>423</v>
       </c>
@@ -32388,7 +32363,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="840" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="840" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A840" t="s">
         <v>425</v>
       </c>
@@ -32441,7 +32416,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="841" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="841" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A841" t="s">
         <v>288</v>
       </c>
@@ -32473,7 +32448,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="842" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="842" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A842" t="s">
         <v>338</v>
       </c>
@@ -32517,7 +32492,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="843" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="843" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A843" t="s">
         <v>94</v>
       </c>
@@ -32549,7 +32524,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="844" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="844" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A844" t="s">
         <v>89</v>
       </c>
@@ -32584,7 +32559,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="845" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="845" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A845" t="s">
         <v>311</v>
       </c>
@@ -32622,7 +32597,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="846" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="846" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A846" t="s">
         <v>426</v>
       </c>
@@ -32666,7 +32641,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="847" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="847" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A847" t="s">
         <v>288</v>
       </c>
@@ -32701,7 +32676,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="848" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="848" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A848" t="s">
         <v>427</v>
       </c>
@@ -32736,7 +32711,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="849" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="849" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A849" t="s">
         <v>289</v>
       </c>
@@ -32774,7 +32749,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="850" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="850" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A850" t="s">
         <v>449</v>
       </c>
@@ -32809,7 +32784,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="851" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="851" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A851" t="s">
         <v>152</v>
       </c>
@@ -32847,7 +32822,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="852" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="852" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A852" t="s">
         <v>400</v>
       </c>
@@ -32879,7 +32854,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="853" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="853" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A853" t="s">
         <v>289</v>
       </c>
@@ -32920,7 +32895,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="854" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="854" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A854" t="s">
         <v>311</v>
       </c>
@@ -32958,7 +32933,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="855" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="855" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A855" t="s">
         <v>94</v>
       </c>
@@ -32993,7 +32968,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="856" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="856" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A856" t="s">
         <v>89</v>
       </c>
@@ -33028,7 +33003,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="857" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="857" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A857" t="s">
         <v>421</v>
       </c>
@@ -33078,7 +33053,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="858" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="858" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A858" t="s">
         <v>59</v>
       </c>
@@ -33122,7 +33097,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="859" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="859" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A859" t="s">
         <v>426</v>
       </c>
@@ -33175,7 +33150,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="860" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="860" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A860" t="s">
         <v>428</v>
       </c>
@@ -33216,7 +33191,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="861" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="861" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A861" t="s">
         <v>94</v>
       </c>
@@ -33257,7 +33232,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="862" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="862" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A862" t="s">
         <v>89</v>
       </c>
@@ -33295,7 +33270,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="863" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="863" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A863" t="s">
         <v>289</v>
       </c>
@@ -33336,7 +33311,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="864" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="864" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A864" t="s">
         <v>429</v>
       </c>
@@ -33389,7 +33364,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="865" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="865" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A865" t="s">
         <v>230</v>
       </c>
@@ -33424,7 +33399,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="866" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="866" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A866" t="s">
         <v>289</v>
       </c>
@@ -33465,7 +33440,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="867" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="867" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A867" t="s">
         <v>311</v>
       </c>
@@ -33518,7 +33493,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="868" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="868" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A868" t="s">
         <v>86</v>
       </c>
@@ -33553,7 +33528,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="869" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="869" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A869" t="s">
         <v>100</v>
       </c>
@@ -33594,7 +33569,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="870" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="870" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A870" t="s">
         <v>430</v>
       </c>
@@ -33632,7 +33607,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="871" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="871" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A871" t="s">
         <v>87</v>
       </c>
@@ -33679,7 +33654,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="872" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="872" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A872" t="s">
         <v>88</v>
       </c>
@@ -33720,7 +33695,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="873" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="873" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A873" t="s">
         <v>89</v>
       </c>
@@ -33764,7 +33739,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="874" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="874" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A874" t="s">
         <v>374</v>
       </c>
@@ -33808,7 +33783,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="875" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="875" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A875" t="s">
         <v>431</v>
       </c>
@@ -33846,7 +33821,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="876" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="876" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A876" t="s">
         <v>421</v>
       </c>
@@ -33899,7 +33874,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="877" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="877" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A877" t="s">
         <v>59</v>
       </c>
@@ -33937,7 +33912,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="878" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="878" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A878" t="s">
         <v>289</v>
       </c>
@@ -33972,7 +33947,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="879" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="879" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A879" t="s">
         <v>267</v>
       </c>
@@ -34013,7 +33988,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="880" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="880" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A880" t="s">
         <v>348</v>
       </c>
@@ -34051,7 +34026,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="881" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="881" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A881" t="s">
         <v>79</v>
       </c>
@@ -34089,7 +34064,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="882" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="882" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A882" t="s">
         <v>412</v>
       </c>
@@ -34121,7 +34096,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="883" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="883" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A883" t="s">
         <v>432</v>
       </c>
@@ -34174,7 +34149,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="884" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="884" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A884" t="s">
         <v>311</v>
       </c>
@@ -34227,7 +34202,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="885" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="885" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A885" t="s">
         <v>426</v>
       </c>
@@ -34280,7 +34255,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="886" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="886" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A886" t="s">
         <v>59</v>
       </c>
@@ -34321,7 +34296,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="887" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="887" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A887" t="s">
         <v>433</v>
       </c>
@@ -34356,7 +34331,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="888" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="888" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A888" t="s">
         <v>289</v>
       </c>
@@ -34397,7 +34372,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="889" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="889" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A889" t="s">
         <v>434</v>
       </c>
@@ -34429,7 +34404,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="890" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="890" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A890" t="s">
         <v>289</v>
       </c>
@@ -34464,7 +34439,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="891" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="891" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A891" t="s">
         <v>436</v>
       </c>
@@ -34517,7 +34492,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="892" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="892" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A892" t="s">
         <v>311</v>
       </c>
@@ -34570,7 +34545,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="893" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="893" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A893" t="s">
         <v>435</v>
       </c>
@@ -34605,7 +34580,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="894" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="894" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A894" t="s">
         <v>59</v>
       </c>
@@ -34652,7 +34627,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="895" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="895" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A895" t="s">
         <v>426</v>
       </c>
@@ -34705,7 +34680,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="896" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="896" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A896" t="s">
         <v>289</v>
       </c>
@@ -34740,7 +34715,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="897" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="897" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A897" t="s">
         <v>434</v>
       </c>
@@ -34775,7 +34750,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="898" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="898" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A898" t="s">
         <v>79</v>
       </c>
@@ -34813,7 +34788,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="899" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="899" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A899" t="s">
         <v>439</v>
       </c>
@@ -34848,7 +34823,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="900" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="900" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A900" t="s">
         <v>348</v>
       </c>
@@ -34886,7 +34861,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="901" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="901" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A901" t="s">
         <v>421</v>
       </c>
@@ -34939,7 +34914,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="902" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="902" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A902" t="s">
         <v>289</v>
       </c>
@@ -34974,7 +34949,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="903" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="903" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A903" t="s">
         <v>440</v>
       </c>
@@ -35009,7 +34984,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="904" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="904" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A904" t="s">
         <v>441</v>
       </c>
@@ -35041,7 +35016,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="905" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="905" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A905" t="s">
         <v>442</v>
       </c>
@@ -35073,7 +35048,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="906" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="906" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A906" t="s">
         <v>443</v>
       </c>
@@ -35105,7 +35080,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="907" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="907" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A907" t="s">
         <v>444</v>
       </c>
@@ -35134,7 +35109,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="908" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="908" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A908" t="s">
         <v>311</v>
       </c>
@@ -35187,7 +35162,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="909" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="909" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A909" t="s">
         <v>289</v>
       </c>
@@ -35222,7 +35197,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="910" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="910" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A910" t="s">
         <v>59</v>
       </c>
@@ -35269,7 +35244,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="911" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="911" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A911" t="s">
         <v>438</v>
       </c>
@@ -35298,7 +35273,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="912" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="912" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A912" t="s">
         <v>412</v>
       </c>
@@ -35330,7 +35305,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="913" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="913" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A913" t="s">
         <v>437</v>
       </c>
@@ -35362,7 +35337,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="914" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="914" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A914" t="s">
         <v>378</v>
       </c>
@@ -35400,7 +35375,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="915" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="915" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A915" t="s">
         <v>445</v>
       </c>
@@ -35435,7 +35410,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="916" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="916" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A916" t="s">
         <v>446</v>
       </c>
@@ -35470,7 +35445,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="917" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="917" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A917" t="s">
         <v>450</v>
       </c>
@@ -35523,7 +35498,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="918" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="918" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A918" t="s">
         <v>421</v>
       </c>
@@ -35576,7 +35551,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="919" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="919" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A919" t="s">
         <v>462</v>
       </c>
@@ -35602,7 +35577,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="920" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="920" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A920" t="s">
         <v>422</v>
       </c>
@@ -35637,7 +35612,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="921" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="921" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A921" t="s">
         <v>289</v>
       </c>
@@ -35672,7 +35647,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="922" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="922" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A922" t="s">
         <v>434</v>
       </c>
@@ -35707,7 +35682,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="923" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="923" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A923" t="s">
         <v>426</v>
       </c>
@@ -35760,7 +35735,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="924" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="924" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A924" t="s">
         <v>412</v>
       </c>
@@ -35792,7 +35767,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="925" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="925" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A925" t="s">
         <v>59</v>
       </c>
@@ -35836,7 +35811,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="926" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="926" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A926" t="s">
         <v>92</v>
       </c>
@@ -35877,7 +35852,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="927" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="927" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A927" t="s">
         <v>289</v>
       </c>
@@ -35912,7 +35887,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="928" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="928" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A928" t="s">
         <v>369</v>
       </c>
@@ -35950,7 +35925,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="929" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="929" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A929" t="s">
         <v>311</v>
       </c>
@@ -36003,7 +35978,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="930" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="930" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A930" t="s">
         <v>289</v>
       </c>
@@ -36038,7 +36013,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="931" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="931" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A931" t="s">
         <v>59</v>
       </c>
@@ -36082,7 +36057,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="932" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="932" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A932" t="s">
         <v>289</v>
       </c>
@@ -36117,7 +36092,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="933" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="933" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A933" t="s">
         <v>454</v>
       </c>
@@ -36155,7 +36130,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="934" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="934" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A934" t="s">
         <v>426</v>
       </c>
@@ -36208,7 +36183,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="935" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="935" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A935" t="s">
         <v>434</v>
       </c>
@@ -36243,7 +36218,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="936" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="936" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A936" t="s">
         <v>289</v>
       </c>
@@ -36275,7 +36250,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="937" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="937" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A937" t="s">
         <v>452</v>
       </c>
@@ -36310,7 +36285,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="938" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="938" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A938" t="s">
         <v>359</v>
       </c>
@@ -36360,7 +36335,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="939" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="939" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A939" t="s">
         <v>456</v>
       </c>
@@ -36413,7 +36388,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="940" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="940" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A940" t="s">
         <v>86</v>
       </c>
@@ -36457,7 +36432,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="941" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="941" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A941" t="s">
         <v>100</v>
       </c>
@@ -36495,7 +36470,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="942" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="942" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A942" t="s">
         <v>451</v>
       </c>
@@ -36530,7 +36505,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="943" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="943" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A943" t="s">
         <v>87</v>
       </c>
@@ -36565,7 +36540,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="944" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="944" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A944" t="s">
         <v>88</v>
       </c>
@@ -36603,7 +36578,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="945" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="945" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A945" t="s">
         <v>89</v>
       </c>
@@ -36644,7 +36619,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="946" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="946" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A946" t="s">
         <v>374</v>
       </c>
@@ -36679,7 +36654,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="947" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="947" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A947" t="s">
         <v>431</v>
       </c>
@@ -36714,7 +36689,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="948" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="948" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A948" t="s">
         <v>455</v>
       </c>
@@ -36752,7 +36727,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="949" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="949" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A949" t="s">
         <v>88</v>
       </c>
@@ -36784,7 +36759,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="950" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="950" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A950" t="s">
         <v>400</v>
       </c>
@@ -36837,7 +36812,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="951" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="951" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A951" t="s">
         <v>311</v>
       </c>
@@ -36890,7 +36865,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="952" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="952" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A952" t="s">
         <v>395</v>
       </c>
@@ -36943,7 +36918,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="953" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="953" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A953" t="s">
         <v>256</v>
       </c>
@@ -36996,7 +36971,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="954" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="954" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A954" t="s">
         <v>434</v>
       </c>
@@ -37031,7 +37006,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="955" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="955" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A955" t="s">
         <v>453</v>
       </c>
@@ -37063,7 +37038,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="956" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="956" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A956" t="s">
         <v>79</v>
       </c>
@@ -37098,7 +37073,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="957" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="957" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A957" t="s">
         <v>267</v>
       </c>
@@ -37139,7 +37114,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="958" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="958" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A958" t="s">
         <v>348</v>
       </c>
@@ -37180,7 +37155,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="959" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="959" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A959" t="s">
         <v>422</v>
       </c>
@@ -37218,7 +37193,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="960" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="960" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A960" t="s">
         <v>421</v>
       </c>
@@ -37271,7 +37246,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="961" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="961" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A961" t="s">
         <v>418</v>
       </c>
@@ -37324,7 +37299,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="962" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="962" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A962" t="s">
         <v>457</v>
       </c>
@@ -37377,7 +37352,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="963" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="963" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A963" t="s">
         <v>59</v>
       </c>
@@ -37424,7 +37399,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="964" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="964" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A964" t="s">
         <v>422</v>
       </c>
@@ -37462,7 +37437,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="965" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="965" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A965" t="s">
         <v>450</v>
       </c>
@@ -37515,7 +37490,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="966" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="966" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A966" t="s">
         <v>426</v>
       </c>
@@ -37568,7 +37543,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="967" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="967" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A967" t="s">
         <v>94</v>
       </c>
@@ -37600,7 +37575,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="968" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="968" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A968" t="s">
         <v>89</v>
       </c>
@@ -37635,7 +37610,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="969" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="969" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A969" t="s">
         <v>436</v>
       </c>
@@ -37688,7 +37663,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="970" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="970" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A970" t="s">
         <v>421</v>
       </c>
@@ -37741,7 +37716,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="971" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="971" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A971" t="s">
         <v>459</v>
       </c>
@@ -37794,7 +37769,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="972" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="972" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A972" t="s">
         <v>460</v>
       </c>
@@ -37844,7 +37819,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="973" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="973" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A973" t="s">
         <v>461</v>
       </c>
@@ -37897,7 +37872,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="974" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="974" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A974" t="s">
         <v>311</v>
       </c>
@@ -37950,7 +37925,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="975" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="975" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A975" t="s">
         <v>458</v>
       </c>
@@ -37979,7 +37954,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="976" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="976" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A976" t="s">
         <v>301</v>
       </c>
@@ -38008,7 +37983,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="977" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="977" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A977" t="s">
         <v>59</v>
       </c>
@@ -38055,7 +38030,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="978" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="978" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A978" t="s">
         <v>453</v>
       </c>
@@ -38090,7 +38065,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="979" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="979" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A979" t="s">
         <v>465</v>
       </c>
@@ -38143,7 +38118,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="980" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="980" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A980" t="s">
         <v>79</v>
       </c>
@@ -38178,7 +38153,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="981" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="981" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A981" t="s">
         <v>267</v>
       </c>
@@ -38219,7 +38194,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="982" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="982" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A982" t="s">
         <v>348</v>
       </c>
@@ -38254,7 +38229,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="983" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="983" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A983" t="s">
         <v>463</v>
       </c>
@@ -38289,7 +38264,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="984" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="984" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A984" t="s">
         <v>395</v>
       </c>
@@ -38342,7 +38317,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="985" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="985" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A985" t="s">
         <v>209</v>
       </c>
@@ -38395,7 +38370,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="986" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="986" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A986" t="s">
         <v>449</v>
       </c>
@@ -38436,7 +38411,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="987" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="987" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A987" t="s">
         <v>469</v>
       </c>
@@ -38477,7 +38452,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="988" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="988" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A988" t="s">
         <v>230</v>
       </c>
@@ -38515,7 +38490,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="989" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="989" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A989" t="s">
         <v>311</v>
       </c>
@@ -38568,7 +38543,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="990" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="990" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A990" t="s">
         <v>418</v>
       </c>
@@ -38621,7 +38596,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="991" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="991" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A991" t="s">
         <v>471</v>
       </c>
@@ -38656,7 +38631,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="992" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="992" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A992" t="s">
         <v>472</v>
       </c>
@@ -38691,12 +38666,12 @@
         <v>447</v>
       </c>
     </row>
-    <row r="993" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="993" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A993" t="s">
         <v>473</v>
       </c>
       <c r="B993">
-        <v>31.948198999999999</v>
+        <v>-31.948198999999999</v>
       </c>
       <c r="C993">
         <v>132.49790300000001</v>
@@ -38720,7 +38695,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="994" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="994" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A994" t="s">
         <v>474</v>
       </c>
@@ -38749,7 +38724,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="995" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="995" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A995" t="s">
         <v>475</v>
       </c>
@@ -38784,7 +38759,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="996" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="996" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A996" t="s">
         <v>476</v>
       </c>
@@ -38819,7 +38794,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="997" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="997" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A997" t="s">
         <v>426</v>
       </c>
@@ -38872,7 +38847,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="998" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="998" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A998" t="s">
         <v>59</v>
       </c>
@@ -38919,7 +38894,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="999" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="999" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A999" t="s">
         <v>453</v>
       </c>
@@ -38954,7 +38929,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="1000" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1000" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1000" t="s">
         <v>466</v>
       </c>
@@ -38986,7 +38961,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="1001" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1001" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1001" t="s">
         <v>467</v>
       </c>
@@ -39021,7 +38996,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="1002" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1002" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1002" t="s">
         <v>221</v>
       </c>
@@ -39074,7 +39049,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="1003" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1003" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1003" t="s">
         <v>470</v>
       </c>
@@ -39109,7 +39084,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="1004" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1004" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1004" t="s">
         <v>399</v>
       </c>
@@ -39150,7 +39125,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="1005" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1005" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1005" t="s">
         <v>449</v>
       </c>
@@ -39194,7 +39169,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="1006" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1006" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1006" t="s">
         <v>289</v>
       </c>
@@ -39229,7 +39204,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="1007" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1007" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1007" t="s">
         <v>468</v>
       </c>
@@ -39282,7 +39257,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="1008" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1008" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1008" t="s">
         <v>395</v>
       </c>
@@ -39335,7 +39310,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="1009" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1009" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1009" t="s">
         <v>311</v>
       </c>
